--- a/Расчёт.xlsx
+++ b/Расчёт.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Professional\Downloads\интститут\курсач детмаш\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A7B866-FBDD-4C58-AACC-177AB6E3A704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2939E34B-5052-4F0D-9610-E457AC857C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Электродвигатель" sheetId="1" r:id="rId1"/>
+    <sheet name="Передача" sheetId="2" r:id="rId2"/>
+    <sheet name="Вал" sheetId="4" r:id="rId3"/>
+    <sheet name="Корпус" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="183">
   <si>
     <t>Окружная сила</t>
   </si>
@@ -135,9 +138,6 @@
     <t>КПД до</t>
   </si>
   <si>
-    <t>Прямозубая</t>
-  </si>
-  <si>
     <t>Планетарная 1</t>
   </si>
   <si>
@@ -177,9 +177,6 @@
     <t>Передаточное от/до</t>
   </si>
   <si>
-    <t>Прямозубая 1</t>
-  </si>
-  <si>
     <t>Прямозубая 2</t>
   </si>
   <si>
@@ -216,9 +213,6 @@
     <t>Максимум:</t>
   </si>
   <si>
-    <t>Мощность</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -330,15 +324,9 @@
     <t>160M8</t>
   </si>
   <si>
-    <t>Мотор</t>
-  </si>
-  <si>
     <t>Редуктор</t>
   </si>
   <si>
-    <t>подшипники</t>
-  </si>
-  <si>
     <t>Подшипники</t>
   </si>
   <si>
@@ -357,9 +345,6 @@
     <t>Н*м</t>
   </si>
   <si>
-    <t>Выбран:</t>
-  </si>
-  <si>
     <t>?</t>
   </si>
   <si>
@@ -397,16 +382,224 @@
   </si>
   <si>
     <t>Наклон</t>
+  </si>
+  <si>
+    <t>Элемент</t>
+  </si>
+  <si>
+    <t>Частота 1/мин</t>
+  </si>
+  <si>
+    <t>Момент Н*м</t>
+  </si>
+  <si>
+    <t>Двигатель</t>
+  </si>
+  <si>
+    <t>Мощность [кВт]</t>
+  </si>
+  <si>
+    <t>Частота [1/мин]</t>
+  </si>
+  <si>
+    <t>Диаметр</t>
+  </si>
+  <si>
+    <t>Варианты:</t>
+  </si>
+  <si>
+    <t>Отношение</t>
+  </si>
+  <si>
+    <t>Частота поля</t>
+  </si>
+  <si>
+    <t>Редуктор:</t>
+  </si>
+  <si>
+    <t>Страницы в атласе</t>
+  </si>
+  <si>
+    <t>Колесо</t>
+  </si>
+  <si>
+    <t>238-239</t>
+  </si>
+  <si>
+    <t>193-194</t>
+  </si>
+  <si>
+    <t>Страницы в pdf</t>
+  </si>
+  <si>
+    <t>Квалитет шестерни</t>
+  </si>
+  <si>
+    <t>Вариант передачи</t>
+  </si>
+  <si>
+    <t>Прямозубая/коническая/шевронная</t>
+  </si>
+  <si>
+    <t>6/7/8/9</t>
+  </si>
+  <si>
+    <t>Цилиндрическая 1</t>
+  </si>
+  <si>
+    <t>Цилиндрическая</t>
+  </si>
+  <si>
+    <t>Вопросы:</t>
+  </si>
+  <si>
+    <t>Как определить квалитет от массовости производтсва?</t>
+  </si>
+  <si>
+    <t>Нормальный</t>
+  </si>
+  <si>
+    <t>Диаметр вала [мм]</t>
+  </si>
+  <si>
+    <t>Диаметр вала электродвигателя</t>
+  </si>
+  <si>
+    <t>28 не подходит</t>
+  </si>
+  <si>
+    <t>Отношение:</t>
+  </si>
+  <si>
+    <t>Барабан</t>
+  </si>
+  <si>
+    <t>Параметры передачи</t>
+  </si>
+  <si>
+    <t>Параметры производства</t>
+  </si>
+  <si>
+    <t>Параметры валов</t>
+  </si>
+  <si>
+    <t>Диаметр быстроходного</t>
+  </si>
+  <si>
+    <t>Диаметр тихоходного</t>
+  </si>
+  <si>
+    <t>Диаметр электродвигателя</t>
+  </si>
+  <si>
+    <t>Объём партии</t>
+  </si>
+  <si>
+    <t>Ресурс</t>
+  </si>
+  <si>
+    <t>Коэф. Ширины</t>
+  </si>
+  <si>
+    <t>Межосевое расстояние</t>
+  </si>
+  <si>
+    <t>HRC шестерни</t>
+  </si>
+  <si>
+    <t>HRC колеса</t>
+  </si>
+  <si>
+    <t>Масса механизма</t>
+  </si>
+  <si>
+    <t>Прямозубый вариант</t>
+  </si>
+  <si>
+    <t>Межосевое расстояние мм</t>
+  </si>
+  <si>
+    <t>Диаметр впадин шестерни мм</t>
+  </si>
+  <si>
+    <t>Вариант</t>
+  </si>
+  <si>
+    <t>Масса колеса</t>
+  </si>
+  <si>
+    <t>Модуль</t>
+  </si>
+  <si>
+    <t>кг</t>
+  </si>
+  <si>
+    <t>Радиальная сила</t>
+  </si>
+  <si>
+    <t>Осевая сила</t>
+  </si>
+  <si>
+    <t>Н</t>
+  </si>
+  <si>
+    <t>Параметр</t>
+  </si>
+  <si>
+    <t>Шестрерня</t>
+  </si>
+  <si>
+    <t>Число зубьев</t>
+  </si>
+  <si>
+    <t>Делительный</t>
+  </si>
+  <si>
+    <t>Диаметры [мм]</t>
+  </si>
+  <si>
+    <t>Впадин</t>
+  </si>
+  <si>
+    <t>Вершин</t>
+  </si>
+  <si>
+    <t>Ширина</t>
+  </si>
+  <si>
+    <t>Твёрдость</t>
+  </si>
+  <si>
+    <t>Смещение</t>
+  </si>
+  <si>
+    <t>K быстроходного вала</t>
+  </si>
+  <si>
+    <t>Налазит на вал</t>
+  </si>
+  <si>
+    <t>Обработка</t>
+  </si>
+  <si>
+    <t>ТВЧ</t>
+  </si>
+  <si>
+    <t>Улучшение</t>
+  </si>
+  <si>
+    <t>Подходит</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -415,8 +608,22 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -432,6 +639,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -565,7 +796,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -575,7 +806,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -601,75 +831,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -686,7 +853,212 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -702,6 +1074,99 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>579120</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>247400</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>124539</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C86946C7-18E7-4C53-9483-5AB1F1EDAB0D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6065520" y="3238500"/>
+          <a:ext cx="11860280" cy="5115639"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>480060</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>318623</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>8029</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Рисунок 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84BC5CB4-C806-4EA9-BFAE-4CDC530164F1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5966460" y="0"/>
+          <a:ext cx="3496163" cy="2934109"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1001,53 +1466,53 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2958CC72-8A25-4698-8914-B1180636D74D}">
-  <dimension ref="A1:AK60"/>
+  <dimension ref="A1:AK65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="28" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="20">
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="19">
         <v>4</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="6"/>
-      <c r="I2" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40">
+      <c r="I2" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49">
         <f>E2*E3</f>
         <v>6.4</v>
       </c>
-      <c r="N2" s="41"/>
-      <c r="Q2" s="42" t="s">
+      <c r="N2" s="50"/>
+      <c r="Q2" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="R2" s="40"/>
-      <c r="S2" s="40"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="49"/>
       <c r="T2" s="8" t="s">
         <v>30</v>
       </c>
@@ -1057,13 +1522,13 @@
       <c r="V2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AC2" s="42" t="s">
+      <c r="AC2" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="40"/>
-      <c r="AE2" s="40"/>
+      <c r="AD2" s="49"/>
+      <c r="AE2" s="49"/>
       <c r="AF2" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AG2" s="8"/>
       <c r="AH2" s="8" t="s">
@@ -1073,39 +1538,39 @@
         <v>31</v>
       </c>
       <c r="AJ2" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="AK2" s="32" t="s">
-        <v>119</v>
+        <v>112</v>
+      </c>
+      <c r="AK2" s="29" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="21">
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="20">
         <v>1.6</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="3"/>
-      <c r="I3" s="36" t="s">
+      <c r="I3" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="37"/>
-      <c r="K3" s="37"/>
-      <c r="L3" s="37"/>
-      <c r="M3" s="37"/>
-      <c r="N3" s="46"/>
-      <c r="Q3" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="R3" s="37"/>
-      <c r="S3" s="37"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="53"/>
+      <c r="Q3" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
       <c r="T3" s="1">
         <v>0.96</v>
       </c>
@@ -1116,11 +1581,11 @@
         <f>AVERAGE(T3:U3)</f>
         <v>0.97</v>
       </c>
-      <c r="AC3" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD3" s="37"/>
-      <c r="AE3" s="37"/>
+      <c r="AC3" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="AD3" s="43"/>
+      <c r="AE3" s="43"/>
       <c r="AF3" s="1">
         <v>1.6</v>
       </c>
@@ -1145,30 +1610,30 @@
       </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="43" t="s">
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="43"/>
-      <c r="G4" s="44"/>
-      <c r="I4" s="36" t="s">
+      <c r="F4" s="44"/>
+      <c r="G4" s="45"/>
+      <c r="I4" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="37"/>
-      <c r="N4" s="46"/>
-      <c r="Q4" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="R4" s="37"/>
-      <c r="S4" s="37"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="53"/>
+      <c r="Q4" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="R4" s="43"/>
+      <c r="S4" s="43"/>
       <c r="T4" s="1">
         <v>0.95</v>
       </c>
@@ -1179,11 +1644,11 @@
         <f t="shared" ref="V4:V12" si="1">AVERAGE(T4:U4)</f>
         <v>0.96</v>
       </c>
-      <c r="AC4" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD4" s="37"/>
-      <c r="AE4" s="37"/>
+      <c r="AC4" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD4" s="43"/>
+      <c r="AE4" s="43"/>
       <c r="AF4" s="1">
         <v>1</v>
       </c>
@@ -1208,13 +1673,13 @@
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="22">
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="21">
         <v>10000</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -1223,19 +1688,19 @@
       <c r="G5" s="3"/>
       <c r="I5" s="7"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="37" t="s">
+      <c r="K5" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="37"/>
-      <c r="M5" s="37" t="s">
+      <c r="L5" s="43"/>
+      <c r="M5" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="46"/>
-      <c r="Q5" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="R5" s="37"/>
-      <c r="S5" s="37"/>
+      <c r="N5" s="53"/>
+      <c r="Q5" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5" s="43"/>
+      <c r="S5" s="43"/>
       <c r="T5" s="1">
         <v>0.95</v>
       </c>
@@ -1246,11 +1711,11 @@
         <f t="shared" si="1"/>
         <v>0.96</v>
       </c>
-      <c r="AC5" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD5" s="37"/>
-      <c r="AE5" s="37"/>
+      <c r="AC5" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD5" s="43"/>
+      <c r="AE5" s="43"/>
       <c r="AF5" s="1">
         <v>3.15</v>
       </c>
@@ -1275,34 +1740,34 @@
       </c>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="22">
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="21">
         <v>0.9</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="3"/>
-      <c r="I6" s="36" t="s">
+      <c r="I6" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="37"/>
-      <c r="K6" s="43">
+      <c r="J6" s="43"/>
+      <c r="K6" s="44">
         <v>2</v>
       </c>
-      <c r="L6" s="43"/>
-      <c r="M6" s="37">
+      <c r="L6" s="44"/>
+      <c r="M6" s="43">
         <v>0.99</v>
       </c>
-      <c r="N6" s="46"/>
-      <c r="Q6" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="R6" s="37"/>
-      <c r="S6" s="37"/>
+      <c r="N6" s="53"/>
+      <c r="Q6" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="R6" s="43"/>
+      <c r="S6" s="43"/>
       <c r="T6" s="1">
         <v>0.92</v>
       </c>
@@ -1313,11 +1778,11 @@
         <f t="shared" si="1"/>
         <v>0.94</v>
       </c>
-      <c r="AC6" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="AD6" s="37"/>
-      <c r="AE6" s="37"/>
+      <c r="AC6" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD6" s="43"/>
+      <c r="AE6" s="43"/>
       <c r="AF6" s="1">
         <v>12.5</v>
       </c>
@@ -1342,34 +1807,34 @@
       </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="22">
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="21">
         <v>3</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="3"/>
-      <c r="I7" s="36" t="s">
+      <c r="I7" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="37"/>
-      <c r="K7" s="43">
+      <c r="J7" s="43"/>
+      <c r="K7" s="44">
         <v>2</v>
       </c>
-      <c r="L7" s="43"/>
-      <c r="M7" s="37">
+      <c r="L7" s="44"/>
+      <c r="M7" s="43">
         <v>0.98</v>
       </c>
-      <c r="N7" s="46"/>
-      <c r="Q7" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="R7" s="37"/>
-      <c r="S7" s="37"/>
+      <c r="N7" s="53"/>
+      <c r="Q7" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="R7" s="43"/>
+      <c r="S7" s="43"/>
       <c r="T7" s="1">
         <v>0.72</v>
       </c>
@@ -1380,11 +1845,11 @@
         <f t="shared" si="1"/>
         <v>0.77</v>
       </c>
-      <c r="AC7" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="AD7" s="37"/>
-      <c r="AE7" s="37"/>
+      <c r="AC7" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD7" s="43"/>
+      <c r="AE7" s="43"/>
       <c r="AF7" s="1">
         <v>16</v>
       </c>
@@ -1409,35 +1874,35 @@
       </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="23">
+      <c r="B8" s="47"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="47"/>
+      <c r="E8" s="22">
         <v>2.2000000000000002</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="5"/>
-      <c r="I8" s="36" t="s">
+      <c r="I8" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="J8" s="37"/>
-      <c r="K8" s="43">
+      <c r="J8" s="43"/>
+      <c r="K8" s="44">
         <v>0</v>
       </c>
-      <c r="L8" s="43"/>
-      <c r="M8" s="43">
+      <c r="L8" s="44"/>
+      <c r="M8" s="60">
         <f>V11</f>
         <v>0.95</v>
       </c>
-      <c r="N8" s="44"/>
-      <c r="Q8" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="R8" s="37"/>
-      <c r="S8" s="37"/>
+      <c r="N8" s="74"/>
+      <c r="Q8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="R8" s="43"/>
+      <c r="S8" s="43"/>
       <c r="T8" s="1">
         <v>0.7</v>
       </c>
@@ -1448,11 +1913,11 @@
         <f t="shared" si="1"/>
         <v>0.75</v>
       </c>
-      <c r="AC8" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD8" s="37"/>
-      <c r="AE8" s="37"/>
+      <c r="AC8" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD8" s="43"/>
+      <c r="AE8" s="43"/>
       <c r="AF8" s="1">
         <v>10</v>
       </c>
@@ -1477,31 +1942,31 @@
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="3"/>
-      <c r="I9" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="47">
+      <c r="B9" s="56"/>
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="70"/>
+      <c r="I9" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+      <c r="L9" s="43"/>
+      <c r="M9" s="58">
         <f>M7^K7*M6^K6*M8^K8</f>
         <v>0.94128803999999988</v>
       </c>
-      <c r="N9" s="48"/>
-      <c r="Q9" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="R9" s="37"/>
-      <c r="S9" s="37"/>
+      <c r="N9" s="59"/>
+      <c r="Q9" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="R9" s="43"/>
+      <c r="S9" s="43"/>
       <c r="T9" s="1">
         <v>0.75</v>
       </c>
@@ -1512,11 +1977,11 @@
         <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="AC9" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD9" s="37"/>
-      <c r="AE9" s="37"/>
+      <c r="AC9" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD9" s="43"/>
+      <c r="AE9" s="43"/>
       <c r="AF9" s="1">
         <v>8</v>
       </c>
@@ -1541,30 +2006,30 @@
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="11"/>
-      <c r="I10" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="37"/>
-      <c r="M10" s="43">
+      <c r="B10" s="72"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="73"/>
+      <c r="I10" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="44">
         <v>0.97</v>
       </c>
-      <c r="N10" s="44"/>
-      <c r="Q10" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="R10" s="37"/>
-      <c r="S10" s="37"/>
+      <c r="N10" s="45"/>
+      <c r="Q10" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="R10" s="43"/>
+      <c r="S10" s="43"/>
       <c r="T10" s="1">
         <v>0.8</v>
       </c>
@@ -1575,11 +2040,11 @@
         <f t="shared" si="1"/>
         <v>0.85000000000000009</v>
       </c>
-      <c r="AC10" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD10" s="39"/>
-      <c r="AE10" s="39"/>
+      <c r="AC10" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD10" s="47"/>
+      <c r="AE10" s="47"/>
       <c r="AF10" s="4">
         <v>70</v>
       </c>
@@ -1604,31 +2069,31 @@
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="5"/>
-      <c r="I11" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="70"/>
+      <c r="I11" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="J11" s="47"/>
+      <c r="K11" s="47"/>
+      <c r="L11" s="47"/>
       <c r="M11" s="51">
         <f>M2/M10/M9</f>
         <v>7.0094783572623509</v>
       </c>
       <c r="N11" s="52"/>
-      <c r="Q11" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="R11" s="37"/>
-      <c r="S11" s="37"/>
+      <c r="Q11" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="R11" s="43"/>
+      <c r="S11" s="43"/>
       <c r="T11" s="1">
         <v>0.94</v>
       </c>
@@ -1639,30 +2104,30 @@
         <f t="shared" si="1"/>
         <v>0.95</v>
       </c>
-      <c r="AC11" s="17"/>
-      <c r="AD11" s="17"/>
-      <c r="AE11" s="17"/>
+      <c r="AC11" s="16"/>
+      <c r="AD11" s="16"/>
+      <c r="AE11" s="16"/>
       <c r="AF11" s="1"/>
       <c r="AG11" s="1"/>
       <c r="AH11" s="1"/>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40" t="s">
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="40"/>
-      <c r="G12" s="41"/>
-      <c r="Q12" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="R12" s="39"/>
-      <c r="S12" s="39"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="50"/>
+      <c r="Q12" s="46" t="s">
+        <v>39</v>
+      </c>
+      <c r="R12" s="47"/>
+      <c r="S12" s="47"/>
       <c r="T12" s="4">
         <v>0.92</v>
       </c>
@@ -1674,17 +2139,17 @@
         <v>0.93500000000000005</v>
       </c>
       <c r="AC12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="22">
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="21">
         <v>400</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -1694,17 +2159,17 @@
         <v>20</v>
       </c>
       <c r="AC13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A14" s="36" t="s">
+      <c r="A14" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="22">
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="21">
         <v>400</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -1713,13 +2178,13 @@
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+      <c r="A15" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="23">
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="22">
         <v>300</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -1728,96 +2193,98 @@
       <c r="G15" s="5"/>
     </row>
     <row r="19" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I19" s="12"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="42">
+      <c r="I19" s="48" t="s">
+        <v>123</v>
+      </c>
+      <c r="J19" s="50"/>
+      <c r="K19" s="48">
         <v>3000</v>
       </c>
-      <c r="L19" s="40"/>
-      <c r="M19" s="40"/>
-      <c r="N19" s="41"/>
-      <c r="O19" s="40">
+      <c r="L19" s="49"/>
+      <c r="M19" s="49"/>
+      <c r="N19" s="50"/>
+      <c r="O19" s="49">
         <v>1500</v>
       </c>
-      <c r="P19" s="40"/>
-      <c r="Q19" s="40"/>
-      <c r="R19" s="40"/>
-      <c r="S19" s="42">
+      <c r="P19" s="49"/>
+      <c r="Q19" s="49"/>
+      <c r="R19" s="49"/>
+      <c r="S19" s="48">
         <v>1000</v>
       </c>
-      <c r="T19" s="40"/>
-      <c r="U19" s="40"/>
-      <c r="V19" s="41"/>
-      <c r="W19" s="40">
+      <c r="T19" s="49"/>
+      <c r="U19" s="49"/>
+      <c r="V19" s="50"/>
+      <c r="W19" s="49">
         <v>750</v>
       </c>
-      <c r="X19" s="40"/>
-      <c r="Y19" s="40"/>
-      <c r="Z19" s="41"/>
+      <c r="X19" s="49"/>
+      <c r="Y19" s="49"/>
+      <c r="Z19" s="50"/>
     </row>
     <row r="20" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I20" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="J20" s="37"/>
-      <c r="K20" s="13" t="s">
-        <v>75</v>
+      <c r="I20" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="J20" s="54"/>
+      <c r="K20" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="N20" s="5" t="s">
         <v>27</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="R20" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="S20" s="13" t="s">
-        <v>75</v>
+      <c r="S20" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="V20" s="5" t="s">
         <v>27</v>
       </c>
       <c r="W20" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="X20" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="Y20" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Z20" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="21" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I21" s="36">
+      <c r="I21" s="42">
         <v>0.37</v>
       </c>
-      <c r="J21" s="37"/>
-      <c r="K21" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="L21" s="25">
+      <c r="J21" s="43"/>
+      <c r="K21" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="L21" s="24">
         <v>0</v>
       </c>
       <c r="M21" s="1">
@@ -1826,10 +2293,10 @@
       <c r="N21" s="3">
         <v>0</v>
       </c>
-      <c r="O21" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="P21" s="25">
+      <c r="O21" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="P21" s="24">
         <v>0</v>
       </c>
       <c r="Q21" s="1">
@@ -1848,14 +2315,14 @@
       <c r="Z21" s="3"/>
     </row>
     <row r="22" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I22" s="36">
+      <c r="I22" s="42">
         <v>0.55000000000000004</v>
       </c>
-      <c r="J22" s="37"/>
-      <c r="K22" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="L22" s="25">
+      <c r="J22" s="43"/>
+      <c r="K22" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="L22" s="24">
         <v>0</v>
       </c>
       <c r="M22" s="1">
@@ -1865,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="P22" s="1">
         <v>1357</v>
@@ -1884,12 +2351,12 @@
       <c r="Z22" s="3"/>
     </row>
     <row r="23" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I23" s="36">
+      <c r="I23" s="42">
         <v>0.75</v>
       </c>
-      <c r="J23" s="37"/>
+      <c r="J23" s="43"/>
       <c r="K23" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="L23" s="1">
         <v>2820</v>
@@ -1901,7 +2368,7 @@
         <v>0.75</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="P23" s="1">
         <v>1350</v>
@@ -1920,12 +2387,12 @@
       <c r="Z23" s="3"/>
     </row>
     <row r="24" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I24" s="36">
+      <c r="I24" s="42">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J24" s="37"/>
+      <c r="J24" s="43"/>
       <c r="K24" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="L24" s="1">
         <v>2805</v>
@@ -1933,11 +2400,11 @@
       <c r="M24" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="N24" s="24">
+      <c r="N24" s="23">
         <v>0.77</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="P24" s="1">
         <v>1395</v>
@@ -1956,12 +2423,12 @@
       <c r="Z24" s="3"/>
     </row>
     <row r="25" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I25" s="36">
+      <c r="I25" s="42">
         <v>1.5</v>
       </c>
-      <c r="J25" s="37"/>
+      <c r="J25" s="43"/>
       <c r="K25" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L25" s="1">
         <v>2850</v>
@@ -1969,11 +2436,11 @@
       <c r="M25" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="N25" s="24">
+      <c r="N25" s="23">
         <v>0.78500000000000003</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P25" s="1">
         <v>1395</v>
@@ -1992,12 +2459,12 @@
       <c r="Z25" s="3"/>
     </row>
     <row r="26" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I26" s="36">
+      <c r="I26" s="42">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J26" s="37"/>
+      <c r="J26" s="43"/>
       <c r="K26" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L26" s="1">
         <v>2850</v>
@@ -2005,11 +2472,11 @@
       <c r="M26" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="N26" s="24">
+      <c r="N26" s="23">
         <v>0.81</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P26" s="1">
         <v>1395</v>
@@ -2028,12 +2495,12 @@
       <c r="Z26" s="3"/>
     </row>
     <row r="27" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I27" s="36">
+      <c r="I27" s="42">
         <v>3</v>
       </c>
-      <c r="J27" s="37"/>
+      <c r="J27" s="43"/>
       <c r="K27" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="L27" s="1">
         <v>2850</v>
@@ -2043,7 +2510,7 @@
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="P27" s="1">
         <v>1410</v>
@@ -2062,12 +2529,12 @@
       <c r="Z27" s="3"/>
     </row>
     <row r="28" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I28" s="36">
+      <c r="I28" s="42">
         <v>4</v>
       </c>
-      <c r="J28" s="37"/>
+      <c r="J28" s="43"/>
       <c r="K28" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="L28" s="1">
         <v>2850</v>
@@ -2077,7 +2544,7 @@
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="P28" s="1">
         <v>1410</v>
@@ -2096,12 +2563,12 @@
       <c r="Z28" s="3"/>
     </row>
     <row r="29" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I29" s="36">
+      <c r="I29" s="42">
         <v>5.5</v>
       </c>
-      <c r="J29" s="37"/>
+      <c r="J29" s="43"/>
       <c r="K29" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="L29" s="1">
         <v>2850</v>
@@ -2109,11 +2576,11 @@
       <c r="M29" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="N29" s="24">
+      <c r="N29" s="23">
         <v>0.88</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="P29" s="1">
         <v>1432</v>
@@ -2121,28 +2588,28 @@
       <c r="Q29" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="R29" s="26">
+      <c r="R29" s="25">
         <v>0.86599999999999999</v>
       </c>
       <c r="S29" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="T29" s="25">
+        <v>960</v>
+      </c>
+      <c r="U29" s="25">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="V29" s="23">
+        <v>0.85</v>
+      </c>
+      <c r="W29" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="T29" s="26">
-        <v>960</v>
-      </c>
-      <c r="U29" s="26">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="V29" s="24">
-        <v>0.85</v>
-      </c>
-      <c r="W29" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="X29" s="26">
+      <c r="X29" s="25">
         <v>712</v>
       </c>
-      <c r="Y29" s="26">
+      <c r="Y29" s="25">
         <v>2.2000000000000002</v>
       </c>
       <c r="Z29" s="3">
@@ -2150,12 +2617,12 @@
       </c>
     </row>
     <row r="30" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I30" s="36">
+      <c r="I30" s="42">
         <v>7.5</v>
       </c>
-      <c r="J30" s="37"/>
+      <c r="J30" s="43"/>
       <c r="K30" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="L30" s="1">
         <v>2895</v>
@@ -2167,7 +2634,7 @@
         <v>0.87</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P30" s="1">
         <v>1440</v>
@@ -2175,28 +2642,28 @@
       <c r="Q30" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="R30" s="26">
+      <c r="R30" s="25">
         <v>0.872</v>
       </c>
       <c r="S30" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="T30" s="25">
+        <v>960</v>
+      </c>
+      <c r="U30" s="25">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="V30" s="23">
+        <v>0.86</v>
+      </c>
+      <c r="W30" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="T30" s="26">
-        <v>960</v>
-      </c>
-      <c r="U30" s="26">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="V30" s="24">
-        <v>0.86</v>
-      </c>
-      <c r="W30" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="X30" s="26">
+      <c r="X30" s="25">
         <v>727</v>
       </c>
-      <c r="Y30" s="26">
+      <c r="Y30" s="25">
         <v>2.4</v>
       </c>
       <c r="Z30" s="3">
@@ -2204,12 +2671,12 @@
       </c>
     </row>
     <row r="31" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I31" s="36">
+      <c r="I31" s="42">
         <v>11</v>
       </c>
-      <c r="J31" s="37"/>
+      <c r="J31" s="43"/>
       <c r="K31" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L31" s="1">
         <v>2910</v>
@@ -2221,7 +2688,7 @@
         <v>0.88</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="P31" s="1">
         <v>1447</v>
@@ -2229,28 +2696,28 @@
       <c r="Q31" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="R31" s="26">
+      <c r="R31" s="25">
         <v>0.87</v>
       </c>
       <c r="S31" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="T31" s="26">
+        <v>90</v>
+      </c>
+      <c r="T31" s="25">
         <v>970</v>
       </c>
-      <c r="U31" s="26">
+      <c r="U31" s="25">
         <v>2.5</v>
       </c>
       <c r="V31" s="3">
         <v>0.86799999999999999</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="X31" s="26">
+        <v>93</v>
+      </c>
+      <c r="X31" s="25">
         <v>727</v>
       </c>
-      <c r="Y31" s="26">
+      <c r="Y31" s="25">
         <v>2.4</v>
       </c>
       <c r="Z31" s="3">
@@ -2258,12 +2725,12 @@
       </c>
     </row>
     <row r="32" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I32" s="36">
+      <c r="I32" s="42">
         <v>15</v>
       </c>
-      <c r="J32" s="37"/>
+      <c r="J32" s="43"/>
       <c r="K32" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L32" s="1">
         <v>2910</v>
@@ -2273,7 +2740,7 @@
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P32" s="1">
         <v>1455</v>
@@ -2292,12 +2759,12 @@
       <c r="Z32" s="3"/>
     </row>
     <row r="33" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="I33" s="36">
+      <c r="I33" s="42">
         <v>18.5</v>
       </c>
-      <c r="J33" s="37"/>
+      <c r="J33" s="43"/>
       <c r="K33" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L33" s="1">
         <v>2910</v>
@@ -2307,7 +2774,7 @@
       </c>
       <c r="N33" s="3"/>
       <c r="O33" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P33" s="1">
         <v>1455</v>
@@ -2326,12 +2793,12 @@
       <c r="Z33" s="3"/>
     </row>
     <row r="34" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="I34" s="36">
+      <c r="I34" s="42">
         <v>22</v>
       </c>
-      <c r="J34" s="37"/>
+      <c r="J34" s="43"/>
       <c r="K34" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L34" s="1">
         <v>2919</v>
@@ -2341,7 +2808,7 @@
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P34" s="1">
         <v>1462</v>
@@ -2360,12 +2827,12 @@
       <c r="Z34" s="3"/>
     </row>
     <row r="35" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="I35" s="38">
+      <c r="I35" s="46">
         <v>30</v>
       </c>
-      <c r="J35" s="39"/>
-      <c r="K35" s="13" t="s">
-        <v>72</v>
+      <c r="J35" s="47"/>
+      <c r="K35" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="L35" s="4">
         <v>2925</v>
@@ -2375,7 +2842,7 @@
       </c>
       <c r="N35" s="5"/>
       <c r="O35" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="P35" s="4">
         <v>1470</v>
@@ -2384,7 +2851,7 @@
         <v>2.7</v>
       </c>
       <c r="R35" s="4"/>
-      <c r="S35" s="13"/>
+      <c r="S35" s="12"/>
       <c r="T35" s="4"/>
       <c r="U35" s="4"/>
       <c r="V35" s="5"/>
@@ -2394,121 +2861,121 @@
       <c r="Z35" s="5"/>
     </row>
     <row r="36" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G36" s="45" t="s">
-        <v>106</v>
-      </c>
-      <c r="H36" s="45"/>
-      <c r="I36" s="54">
+      <c r="G36" s="61" t="s">
+        <v>121</v>
+      </c>
+      <c r="H36" s="61"/>
+      <c r="I36" s="55">
         <f>_xlfn.MINIFS(I21:J35,I21:J35,"&gt;="&amp;M11)</f>
         <v>7.5</v>
       </c>
-      <c r="J36" s="55"/>
-      <c r="K36" s="10" t="str">
+      <c r="J36" s="56"/>
+      <c r="K36" s="9" t="str">
         <f>VLOOKUP($I$36,$I$21:$R$35,3)</f>
         <v>112M2</v>
       </c>
-      <c r="L36" s="10">
+      <c r="L36" s="9">
         <f>VLOOKUP($I$36,$I$21:$R$35,4)</f>
         <v>2895</v>
       </c>
-      <c r="M36" s="10">
+      <c r="M36" s="9">
         <f>VLOOKUP($I$36,$I$21:$R$35,5)</f>
         <v>2.2000000000000002</v>
       </c>
-      <c r="N36" s="10">
+      <c r="N36" s="9">
         <f>VLOOKUP($I$36,$I$21:$R$35,6)</f>
         <v>0.87</v>
       </c>
-      <c r="O36" s="65" t="str">
+      <c r="O36" s="41" t="str">
         <f>VLOOKUP($I$36,$I$21:$R$35,7)</f>
         <v>132S4</v>
       </c>
-      <c r="P36" s="65">
+      <c r="P36" s="41">
         <f>VLOOKUP($I$36,$I$21:$R$35,8)</f>
         <v>1440</v>
       </c>
-      <c r="Q36" s="65">
+      <c r="Q36" s="41">
         <f>VLOOKUP($I$36,$I$21:$R$35,9)</f>
         <v>2.2000000000000002</v>
       </c>
-      <c r="R36" s="65">
+      <c r="R36" s="41">
         <f>VLOOKUP($I$36,$I$21:$R$35,10)</f>
         <v>0.872</v>
       </c>
-      <c r="S36" s="10" t="str">
+      <c r="S36" s="9" t="str">
         <f>VLOOKUP($I$36,$I$21:$Z$35,11)</f>
         <v>132M6</v>
       </c>
-      <c r="T36" s="10">
+      <c r="T36" s="9">
         <f>VLOOKUP($I$36,$I$21:$Z$35,12)</f>
         <v>960</v>
       </c>
-      <c r="U36" s="10">
+      <c r="U36" s="9">
         <f>VLOOKUP($I$36,$I$21:$Z$35,13)</f>
         <v>2.2000000000000002</v>
       </c>
-      <c r="V36" s="10">
+      <c r="V36" s="9">
         <f>VLOOKUP($I$36,$I$21:$Z$35,14)</f>
         <v>0.86</v>
       </c>
-      <c r="W36" s="10" t="str">
+      <c r="W36" s="9" t="str">
         <f>VLOOKUP($I$36,$I$21:$Z$35,15)</f>
         <v>160S8</v>
       </c>
-      <c r="X36" s="10">
+      <c r="X36" s="9">
         <f>VLOOKUP($I$36,$I$21:$Z$35,16)</f>
         <v>727</v>
       </c>
-      <c r="Y36" s="10">
+      <c r="Y36" s="9">
         <f>VLOOKUP($I$36,$I$21:$Z$35,17)</f>
         <v>2.4</v>
       </c>
-      <c r="Z36" s="11">
+      <c r="Z36" s="10">
         <f>VLOOKUP($I$36,$I$21:$Z$35,18)</f>
         <v>0.85</v>
       </c>
     </row>
     <row r="38" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B38" s="42" t="s">
-        <v>41</v>
-      </c>
-      <c r="C38" s="40"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="12"/>
-      <c r="L38" s="19"/>
-      <c r="M38" s="19"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="H38" s="49"/>
+      <c r="I38" s="49"/>
+      <c r="J38" s="50"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
       <c r="N38" s="8"/>
-      <c r="O38" s="18"/>
-      <c r="P38" s="19"/>
-      <c r="Q38" s="19"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="18"/>
+      <c r="Q38" s="18"/>
       <c r="R38" s="6"/>
-      <c r="S38" s="19"/>
-      <c r="T38" s="19"/>
-      <c r="U38" s="19"/>
+      <c r="S38" s="18"/>
+      <c r="T38" s="18"/>
+      <c r="U38" s="18"/>
       <c r="V38" s="8"/>
-      <c r="W38" s="18"/>
-      <c r="X38" s="19"/>
-      <c r="Y38" s="19"/>
+      <c r="W38" s="17"/>
+      <c r="X38" s="18"/>
+      <c r="Y38" s="18"/>
       <c r="Z38" s="6"/>
     </row>
     <row r="39" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B39" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="C39" s="37"/>
-      <c r="D39" s="37"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="37"/>
-      <c r="H39" s="37"/>
-      <c r="I39" s="37"/>
-      <c r="J39" s="37"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="53"/>
       <c r="K39" s="7"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -2539,54 +3006,54 @@
       </c>
     </row>
     <row r="40" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B40" s="56"/>
-      <c r="C40" s="17"/>
+      <c r="B40" s="16"/>
+      <c r="C40" s="16"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
-      <c r="F40" s="37" t="s">
-        <v>113</v>
-      </c>
-      <c r="G40" s="37"/>
-      <c r="H40" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="I40" s="37"/>
-      <c r="J40" s="37"/>
-      <c r="K40" s="28" t="s">
-        <v>42</v>
+      <c r="F40" s="1"/>
+      <c r="G40" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="J40" s="53"/>
+      <c r="K40" s="27" t="s">
+        <v>122</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="M40" s="4"/>
       <c r="N40" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="O40" s="28" t="s">
-        <v>42</v>
+      <c r="O40" s="27" t="s">
+        <v>122</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="Q40" s="4"/>
       <c r="R40" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="S40" s="29" t="s">
-        <v>42</v>
+      <c r="S40" s="27" t="s">
+        <v>122</v>
       </c>
       <c r="T40" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="U40" s="4"/>
       <c r="V40" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="W40" s="28" t="s">
-        <v>42</v>
+      <c r="W40" s="27" t="s">
+        <v>122</v>
       </c>
       <c r="X40" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="Y40" s="4"/>
       <c r="Z40" s="5" t="s">
@@ -2594,29 +3061,29 @@
       </c>
     </row>
     <row r="41" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B41" s="7"/>
+      <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
-      <c r="F41" s="49">
+      <c r="F41" s="1"/>
+      <c r="G41" s="68">
         <v>160</v>
       </c>
-      <c r="G41" s="49"/>
-      <c r="H41" s="49">
-        <f>$E$3*60000/PI()/F41</f>
+      <c r="H41" s="57"/>
+      <c r="I41" s="62">
+        <f>$E$3*60000/PI()/G41</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="I41" s="49"/>
-      <c r="J41" s="50"/>
-      <c r="K41" s="16">
-        <f>IF($H41,L$36/$H41,"-")</f>
+      <c r="J41" s="63"/>
+      <c r="K41" s="15">
+        <f>IF($I41,L$36/$I41,"-")</f>
         <v>15.15818455357075</v>
       </c>
       <c r="L41" s="8" t="str">
         <f>AC6</f>
         <v>Прямозубая 2</v>
       </c>
-      <c r="M41" s="34">
+      <c r="M41" s="31">
         <f ca="1">IF(K41&lt;&gt;"-",SUMIF($AC:$AE,L41,$AJ:$AJ)-K41*SUMIF($AC:$AE,L41,$AK:$AK),0)</f>
         <v>0.95497170733270809</v>
       </c>
@@ -2624,31 +3091,31 @@
         <f ca="1">M41*N$39</f>
         <v>0.78204599858607271</v>
       </c>
-      <c r="O41" s="62">
-        <f>IF($H41,P$36/$H41,"-")</f>
+      <c r="O41" s="38">
+        <f>IF($I41,P$36/$I41,"-")</f>
         <v>7.5398223686155026</v>
       </c>
-      <c r="P41" s="63" t="str">
+      <c r="P41" s="39" t="str">
         <f>AC3</f>
-        <v>Прямозубая 1</v>
-      </c>
-      <c r="Q41" s="64">
+        <v>Цилиндрическая 1</v>
+      </c>
+      <c r="Q41" s="40">
         <f ca="1">IF(O41&lt;&gt;"-",SUMIF($AC:$AE,P41,$AJ:$AJ)-O41*SUMIF($AC:$AE,P41,$AK:$AK),0)</f>
         <v>0.96143805509807656</v>
       </c>
-      <c r="R41" s="63">
+      <c r="R41" s="39">
         <f ca="1">Q41*R$39</f>
         <v>0.78915140422920127</v>
       </c>
-      <c r="S41" s="16">
-        <f>IF($H41,T$36/$H41,"-")</f>
+      <c r="S41" s="15">
+        <f>IF($I41,T$36/$I41,"-")</f>
         <v>5.0265482457436681</v>
       </c>
       <c r="T41" s="8" t="str">
         <f>AC3</f>
-        <v>Прямозубая 1</v>
-      </c>
-      <c r="U41" s="34">
+        <v>Цилиндрическая 1</v>
+      </c>
+      <c r="U41" s="31">
         <f ca="1">IF(S41&lt;&gt;"-",SUMIF($AC:$AE,T41,$AJ:$AJ)-S41*SUMIF($AC:$AE,T41,$AK:$AK),0)</f>
         <v>0.969292036732051</v>
       </c>
@@ -2656,15 +3123,15 @@
         <f ca="1">U41*V$39</f>
         <v>0.78464938124108341</v>
       </c>
-      <c r="W41" s="16">
-        <f>IF($H41,X$36/$H41,"-")</f>
+      <c r="W41" s="15">
+        <f>IF($I41,X$36/$I41,"-")</f>
         <v>3.8065630985996322</v>
       </c>
       <c r="X41" s="8" t="str">
         <f>AC3</f>
-        <v>Прямозубая 1</v>
-      </c>
-      <c r="Y41" s="34">
+        <v>Цилиндрическая 1</v>
+      </c>
+      <c r="Y41" s="31">
         <f ca="1">IF(W41&lt;&gt;"-",SUMIF($AC:$AE,X41,$AJ:$AJ)-W41*SUMIF($AC:$AE,X41,$AK:$AK),0)</f>
         <v>0.97310449031687618</v>
       </c>
@@ -2674,374 +3141,374 @@
       </c>
     </row>
     <row r="42" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B42" s="7"/>
+      <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="57">
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="69">
         <v>200</v>
       </c>
-      <c r="G42" s="57"/>
-      <c r="H42" s="37">
-        <f t="shared" ref="H42:H46" si="4">$E$3*60000/PI()/F42</f>
+      <c r="H42" s="60"/>
+      <c r="I42" s="64">
+        <f>$E$3*60000/PI()/G42</f>
         <v>152.78874536821954</v>
       </c>
-      <c r="I42" s="37"/>
-      <c r="J42" s="46"/>
-      <c r="K42" s="14">
-        <f t="shared" ref="K42:K55" si="5">IF($H42,L$36/$H42,"-")</f>
+      <c r="J42" s="65"/>
+      <c r="K42" s="13">
+        <f>IF($I42,L$36/$I42,"-")</f>
         <v>18.947730691963439</v>
       </c>
       <c r="L42" s="1" t="str">
         <f>AC6</f>
         <v>Прямозубая 2</v>
       </c>
-      <c r="M42" s="33">
-        <f t="shared" ref="M42:M55" ca="1" si="6">IF(K42&lt;&gt;"-",SUMIF($AC:$AE,L42,$AJ:$AJ)-K42*SUMIF($AC:$AE,L42,$AK:$AK),0)</f>
+      <c r="M42" s="30">
+        <f ca="1">IF(K42&lt;&gt;"-",SUMIF($AC:$AE,L42,$AJ:$AJ)-K42*SUMIF($AC:$AE,L42,$AK:$AK),0)</f>
         <v>0.94723305521851664</v>
       </c>
       <c r="N42" s="1">
-        <f t="shared" ref="N42:N55" ca="1" si="7">M42*N$39</f>
+        <f ca="1">M42*N$39</f>
         <v>0.77570865699376879</v>
       </c>
-      <c r="O42" s="58">
-        <f t="shared" ref="O42:O55" si="8">IF($H42,P$36/$H42,"-")</f>
+      <c r="O42" s="34">
+        <f>IF($I42,P$36/$I42,"-")</f>
         <v>9.4247779607693793</v>
       </c>
-      <c r="P42" s="26"/>
-      <c r="Q42" s="59">
-        <f t="shared" ref="Q42:Q55" ca="1" si="9">IF(O42&lt;&gt;"-",SUMIF($AC:$AE,P42,$AJ:$AJ)-O42*SUMIF($AC:$AE,P42,$AK:$AK),0)</f>
+      <c r="P42" s="25"/>
+      <c r="Q42" s="35">
+        <f ca="1">IF(O42&lt;&gt;"-",SUMIF($AC:$AE,P42,$AJ:$AJ)-O42*SUMIF($AC:$AE,P42,$AK:$AK),0)</f>
         <v>0</v>
       </c>
-      <c r="R42" s="26">
-        <f t="shared" ref="R42:R55" ca="1" si="10">Q42*R$39</f>
+      <c r="R42" s="25">
+        <f ca="1">Q42*R$39</f>
         <v>0</v>
       </c>
-      <c r="S42" s="14">
-        <f t="shared" ref="S42:S55" si="11">IF($H42,T$36/$H42,"-")</f>
+      <c r="S42" s="13">
+        <f>IF($I42,T$36/$I42,"-")</f>
         <v>6.2831853071795862</v>
       </c>
       <c r="T42" s="1" t="str">
         <f>AC3</f>
-        <v>Прямозубая 1</v>
-      </c>
-      <c r="U42" s="33">
-        <f t="shared" ref="U42:U55" ca="1" si="12">IF(S42&lt;&gt;"-",SUMIF($AC:$AE,T42,$AJ:$AJ)-S42*SUMIF($AC:$AE,T42,$AK:$AK),0)</f>
+        <v>Цилиндрическая 1</v>
+      </c>
+      <c r="U42" s="30">
+        <f ca="1">IF(S42&lt;&gt;"-",SUMIF($AC:$AE,T42,$AJ:$AJ)-S42*SUMIF($AC:$AE,T42,$AK:$AK),0)</f>
         <v>0.96536504591506378</v>
       </c>
       <c r="V42" s="1">
-        <f t="shared" ref="V42:V55" ca="1" si="13">U42*V$39</f>
+        <f ca="1">U42*V$39</f>
         <v>0.78147045188035424</v>
       </c>
-      <c r="W42" s="14">
-        <f t="shared" ref="W42:W55" si="14">IF($H42,X$36/$H42,"-")</f>
+      <c r="W42" s="13">
+        <f>IF($I42,X$36/$I42,"-")</f>
         <v>4.7582038732495402</v>
       </c>
       <c r="X42" s="1" t="str">
         <f>AC3</f>
-        <v>Прямозубая 1</v>
-      </c>
-      <c r="Y42" s="33">
-        <f t="shared" ref="Y42:Y55" ca="1" si="15">IF(W42&lt;&gt;"-",SUMIF($AC:$AE,X42,$AJ:$AJ)-W42*SUMIF($AC:$AE,X42,$AK:$AK),0)</f>
+        <v>Цилиндрическая 1</v>
+      </c>
+      <c r="Y42" s="30">
+        <f ca="1">IF(W42&lt;&gt;"-",SUMIF($AC:$AE,X42,$AJ:$AJ)-W42*SUMIF($AC:$AE,X42,$AK:$AK),0)</f>
         <v>0.97013061289609515</v>
       </c>
       <c r="Z42" s="3">
-        <f t="shared" ref="Z42:Z55" ca="1" si="16">Y42*Z$39</f>
+        <f ca="1">Y42*Z$39</f>
         <v>0.77619649168341942</v>
       </c>
     </row>
     <row r="43" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B43" s="7"/>
+      <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
-      <c r="F43" s="37">
+      <c r="F43" s="1"/>
+      <c r="G43" s="42">
         <v>250</v>
       </c>
-      <c r="G43" s="37"/>
-      <c r="H43" s="37">
-        <f t="shared" si="4"/>
+      <c r="H43" s="43"/>
+      <c r="I43" s="64">
+        <f>$E$3*60000/PI()/G43</f>
         <v>122.23099629457563</v>
       </c>
-      <c r="I43" s="37"/>
-      <c r="J43" s="46"/>
-      <c r="K43" s="14">
-        <f t="shared" si="5"/>
+      <c r="J43" s="65"/>
+      <c r="K43" s="13">
+        <f>IF($I43,L$36/$I43,"-")</f>
         <v>23.684663364954297</v>
       </c>
       <c r="L43" s="1" t="str">
         <f>AC6</f>
         <v>Прямозубая 2</v>
       </c>
-      <c r="M43" s="33">
-        <f t="shared" ca="1" si="6"/>
+      <c r="M43" s="30">
+        <f ca="1">IF(K43&lt;&gt;"-",SUMIF($AC:$AE,L43,$AJ:$AJ)-K43*SUMIF($AC:$AE,L43,$AK:$AK),0)</f>
         <v>0.93755974007577747</v>
       </c>
       <c r="N43" s="1">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">M43*N$39</f>
         <v>0.76778698000338896</v>
       </c>
-      <c r="O43" s="14">
-        <f t="shared" si="8"/>
+      <c r="O43" s="13">
+        <f>IF($I43,P$36/$I43,"-")</f>
         <v>11.780972450961723</v>
       </c>
       <c r="P43" s="1"/>
-      <c r="Q43" s="33">
-        <f t="shared" ca="1" si="9"/>
+      <c r="Q43" s="30">
+        <f ca="1">IF(O43&lt;&gt;"-",SUMIF($AC:$AE,P43,$AJ:$AJ)-O43*SUMIF($AC:$AE,P43,$AK:$AK),0)</f>
         <v>0</v>
       </c>
       <c r="R43" s="1">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">Q43*R$39</f>
         <v>0</v>
       </c>
-      <c r="S43" s="14">
-        <f t="shared" si="11"/>
+      <c r="S43" s="13">
+        <f>IF($I43,T$36/$I43,"-")</f>
         <v>7.8539816339744819</v>
       </c>
       <c r="T43" s="1" t="str">
         <f>AC3</f>
-        <v>Прямозубая 1</v>
-      </c>
-      <c r="U43" s="33">
-        <f t="shared" ca="1" si="12"/>
+        <v>Цилиндрическая 1</v>
+      </c>
+      <c r="U43" s="30">
+        <f ca="1">IF(S43&lt;&gt;"-",SUMIF($AC:$AE,T43,$AJ:$AJ)-S43*SUMIF($AC:$AE,T43,$AK:$AK),0)</f>
         <v>0.9604563073938297</v>
       </c>
       <c r="V43" s="1">
-        <f t="shared" ca="1" si="13"/>
+        <f ca="1">U43*V$39</f>
         <v>0.77749679017944284</v>
       </c>
-      <c r="W43" s="14">
-        <f t="shared" si="14"/>
+      <c r="W43" s="13">
+        <f>IF($I43,X$36/$I43,"-")</f>
         <v>5.9477548415619257</v>
       </c>
       <c r="X43" s="1" t="str">
         <f>AC3</f>
-        <v>Прямозубая 1</v>
-      </c>
-      <c r="Y43" s="33">
-        <f t="shared" ca="1" si="15"/>
+        <v>Цилиндрическая 1</v>
+      </c>
+      <c r="Y43" s="30">
+        <f ca="1">IF(W43&lt;&gt;"-",SUMIF($AC:$AE,X43,$AJ:$AJ)-W43*SUMIF($AC:$AE,X43,$AK:$AK),0)</f>
         <v>0.96641326612011891</v>
       </c>
       <c r="Z43" s="3">
-        <f t="shared" ca="1" si="16"/>
+        <f ca="1">Y43*Z$39</f>
         <v>0.77322226173177433</v>
       </c>
     </row>
     <row r="44" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B44" s="7"/>
+      <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
-      <c r="F44" s="37">
+      <c r="F44" s="1"/>
+      <c r="G44" s="42">
         <v>315</v>
       </c>
-      <c r="G44" s="37"/>
-      <c r="H44" s="37">
-        <f t="shared" si="4"/>
+      <c r="H44" s="43"/>
+      <c r="I44" s="64">
+        <f>$E$3*60000/PI()/G44</f>
         <v>97.008727217917169</v>
       </c>
-      <c r="I44" s="37"/>
-      <c r="J44" s="46"/>
-      <c r="K44" s="14">
-        <f t="shared" si="5"/>
+      <c r="J44" s="65"/>
+      <c r="K44" s="13">
+        <f>IF($I44,L$36/$I44,"-")</f>
         <v>29.842675839842414</v>
       </c>
       <c r="L44" s="1" t="str">
         <f>AC6</f>
         <v>Прямозубая 2</v>
       </c>
-      <c r="M44" s="33">
-        <f t="shared" ca="1" si="6"/>
+      <c r="M44" s="30">
+        <f ca="1">IF(K44&lt;&gt;"-",SUMIF($AC:$AE,L44,$AJ:$AJ)-K44*SUMIF($AC:$AE,L44,$AK:$AK),0)</f>
         <v>0.92498443039021649</v>
       </c>
       <c r="N44" s="1">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">M44*N$39</f>
         <v>0.75748879991589524</v>
       </c>
-      <c r="O44" s="14">
-        <f t="shared" si="8"/>
+      <c r="O44" s="13">
+        <f>IF($I44,P$36/$I44,"-")</f>
         <v>14.844025288211771</v>
       </c>
       <c r="P44" s="1"/>
-      <c r="Q44" s="33">
-        <f t="shared" ca="1" si="9"/>
+      <c r="Q44" s="30">
+        <f ca="1">IF(O44&lt;&gt;"-",SUMIF($AC:$AE,P44,$AJ:$AJ)-O44*SUMIF($AC:$AE,P44,$AK:$AK),0)</f>
         <v>0</v>
       </c>
       <c r="R44" s="1">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">Q44*R$39</f>
         <v>0</v>
       </c>
-      <c r="S44" s="14">
-        <f t="shared" si="11"/>
+      <c r="S44" s="13">
+        <f>IF($I44,T$36/$I44,"-")</f>
         <v>9.8960168588078474</v>
       </c>
       <c r="T44" s="1"/>
-      <c r="U44" s="33">
-        <f t="shared" ca="1" si="12"/>
+      <c r="U44" s="30">
+        <f ca="1">IF(S44&lt;&gt;"-",SUMIF($AC:$AE,T44,$AJ:$AJ)-S44*SUMIF($AC:$AE,T44,$AK:$AK),0)</f>
         <v>0</v>
       </c>
       <c r="V44" s="1">
-        <f t="shared" ca="1" si="13"/>
+        <f ca="1">U44*V$39</f>
         <v>0</v>
       </c>
-      <c r="W44" s="14">
-        <f t="shared" si="14"/>
+      <c r="W44" s="13">
+        <f>IF($I44,X$36/$I44,"-")</f>
         <v>7.4941711003680265</v>
       </c>
       <c r="X44" s="1"/>
-      <c r="Y44" s="33">
-        <f t="shared" ca="1" si="15"/>
+      <c r="Y44" s="30">
+        <f ca="1">IF(W44&lt;&gt;"-",SUMIF($AC:$AE,X44,$AJ:$AJ)-W44*SUMIF($AC:$AE,X44,$AK:$AK),0)</f>
         <v>0</v>
       </c>
       <c r="Z44" s="3">
-        <f t="shared" ca="1" si="16"/>
+        <f ca="1">Y44*Z$39</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B45" s="7"/>
+      <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
-      <c r="F45" s="37">
+      <c r="F45" s="1"/>
+      <c r="G45" s="42">
         <v>400</v>
       </c>
-      <c r="G45" s="37"/>
-      <c r="H45" s="37">
-        <f t="shared" si="4"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="64">
+        <f>$E$3*60000/PI()/G45</f>
         <v>76.394372684109769</v>
       </c>
-      <c r="I45" s="37"/>
-      <c r="J45" s="46"/>
-      <c r="K45" s="14">
-        <f t="shared" si="5"/>
+      <c r="J45" s="65"/>
+      <c r="K45" s="13">
+        <f>IF($I45,L$36/$I45,"-")</f>
         <v>37.895461383926879</v>
       </c>
       <c r="L45" s="1"/>
-      <c r="M45" s="33">
-        <f t="shared" ca="1" si="6"/>
+      <c r="M45" s="30">
+        <f ca="1">IF(K45&lt;&gt;"-",SUMIF($AC:$AE,L45,$AJ:$AJ)-K45*SUMIF($AC:$AE,L45,$AK:$AK),0)</f>
         <v>0</v>
       </c>
       <c r="N45" s="1">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">M45*N$39</f>
         <v>0</v>
       </c>
-      <c r="O45" s="14">
-        <f t="shared" si="8"/>
+      <c r="O45" s="13">
+        <f>IF($I45,P$36/$I45,"-")</f>
         <v>18.849555921538759</v>
       </c>
       <c r="P45" s="1"/>
-      <c r="Q45" s="33">
-        <f t="shared" ca="1" si="9"/>
+      <c r="Q45" s="30">
+        <f ca="1">IF(O45&lt;&gt;"-",SUMIF($AC:$AE,P45,$AJ:$AJ)-O45*SUMIF($AC:$AE,P45,$AK:$AK),0)</f>
         <v>0</v>
       </c>
       <c r="R45" s="1">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">Q45*R$39</f>
         <v>0</v>
       </c>
-      <c r="S45" s="14">
-        <f t="shared" si="11"/>
+      <c r="S45" s="13">
+        <f>IF($I45,T$36/$I45,"-")</f>
         <v>12.566370614359172</v>
       </c>
       <c r="T45" s="1"/>
-      <c r="U45" s="33">
-        <f t="shared" ca="1" si="12"/>
+      <c r="U45" s="30">
+        <f ca="1">IF(S45&lt;&gt;"-",SUMIF($AC:$AE,T45,$AJ:$AJ)-S45*SUMIF($AC:$AE,T45,$AK:$AK),0)</f>
         <v>0</v>
       </c>
       <c r="V45" s="1">
-        <f t="shared" ca="1" si="13"/>
+        <f ca="1">U45*V$39</f>
         <v>0</v>
       </c>
-      <c r="W45" s="14">
-        <f t="shared" si="14"/>
+      <c r="W45" s="13">
+        <f>IF($I45,X$36/$I45,"-")</f>
         <v>9.5164077464990804</v>
       </c>
       <c r="X45" s="1"/>
-      <c r="Y45" s="33">
-        <f t="shared" ca="1" si="15"/>
+      <c r="Y45" s="30">
+        <f ca="1">IF(W45&lt;&gt;"-",SUMIF($AC:$AE,X45,$AJ:$AJ)-W45*SUMIF($AC:$AE,X45,$AK:$AK),0)</f>
         <v>0</v>
       </c>
       <c r="Z45" s="3">
-        <f t="shared" ca="1" si="16"/>
+        <f ca="1">Y45*Z$39</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B46" s="13"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="39">
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="46">
         <v>500</v>
       </c>
-      <c r="G46" s="39"/>
-      <c r="H46" s="39">
-        <f t="shared" si="4"/>
+      <c r="H46" s="47"/>
+      <c r="I46" s="66">
+        <f>$E$3*60000/PI()/G46</f>
         <v>61.115498147287816</v>
       </c>
-      <c r="I46" s="39"/>
-      <c r="J46" s="53"/>
-      <c r="K46" s="15">
-        <f t="shared" si="5"/>
+      <c r="J46" s="67"/>
+      <c r="K46" s="14">
+        <f>IF($I46,L$36/$I46,"-")</f>
         <v>47.369326729908593</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="M46" s="35">
-        <f t="shared" ca="1" si="6"/>
+        <v>101</v>
+      </c>
+      <c r="M46" s="32">
+        <f ca="1">IF(K46&lt;&gt;"-",SUMIF($AC:$AE,L46,$AJ:$AJ)-K46*SUMIF($AC:$AE,L46,$AK:$AK),0)</f>
         <v>0</v>
       </c>
       <c r="N46" s="4">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">M46*N$39</f>
         <v>0</v>
       </c>
-      <c r="O46" s="15">
-        <f t="shared" si="8"/>
+      <c r="O46" s="14">
+        <f>IF($I46,P$36/$I46,"-")</f>
         <v>23.561944901923447</v>
       </c>
-      <c r="P46" s="61" t="str">
+      <c r="P46" s="37" t="str">
         <f>AC3</f>
-        <v>Прямозубая 1</v>
-      </c>
-      <c r="Q46" s="35">
-        <f t="shared" ca="1" si="9"/>
+        <v>Цилиндрическая 1</v>
+      </c>
+      <c r="Q46" s="32">
+        <f ca="1">IF(O46&lt;&gt;"-",SUMIF($AC:$AE,P46,$AJ:$AJ)-O46*SUMIF($AC:$AE,P46,$AK:$AK),0)</f>
         <v>0.91136892218148913</v>
       </c>
       <c r="R46" s="4">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">Q46*R$39</f>
         <v>0.74805450116805416</v>
       </c>
-      <c r="S46" s="15">
-        <f t="shared" si="11"/>
+      <c r="S46" s="14">
+        <f>IF($I46,T$36/$I46,"-")</f>
         <v>15.707963267948964</v>
       </c>
       <c r="T46" s="4" t="str">
         <f>AC3</f>
-        <v>Прямозубая 1</v>
-      </c>
-      <c r="U46" s="35">
-        <f t="shared" ca="1" si="12"/>
+        <v>Цилиндрическая 1</v>
+      </c>
+      <c r="U46" s="32">
+        <f ca="1">IF(S46&lt;&gt;"-",SUMIF($AC:$AE,T46,$AJ:$AJ)-S46*SUMIF($AC:$AE,T46,$AK:$AK),0)</f>
         <v>0.93591261478765941</v>
       </c>
       <c r="V46" s="4">
-        <f t="shared" ca="1" si="13"/>
+        <f ca="1">U46*V$39</f>
         <v>0.75762848167488572</v>
       </c>
-      <c r="W46" s="15">
-        <f t="shared" si="14"/>
+      <c r="W46" s="14">
+        <f>IF($I46,X$36/$I46,"-")</f>
         <v>11.895509683123851</v>
       </c>
       <c r="X46" s="4" t="str">
         <f>AC3</f>
-        <v>Прямозубая 1</v>
-      </c>
-      <c r="Y46" s="35">
-        <f t="shared" ca="1" si="15"/>
+        <v>Цилиндрическая 1</v>
+      </c>
+      <c r="Y46" s="32">
+        <f ca="1">IF(W46&lt;&gt;"-",SUMIF($AC:$AE,X46,$AJ:$AJ)-W46*SUMIF($AC:$AE,X46,$AK:$AK),0)</f>
         <v>0.94782653224023794</v>
       </c>
       <c r="Z46" s="5">
-        <f t="shared" ca="1" si="16"/>
+        <f ca="1">Y46*Z$39</f>
         <v>0.75835111197354876</v>
       </c>
     </row>
@@ -3050,401 +3517,725 @@
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
-      <c r="F47" s="17"/>
-      <c r="G47" s="17"/>
-      <c r="H47" s="17"/>
-      <c r="I47" s="17"/>
-      <c r="J47" s="17"/>
-      <c r="K47" s="60"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="16"/>
+      <c r="H47" s="16"/>
+      <c r="I47" s="16"/>
+      <c r="J47" s="16"/>
+      <c r="K47" s="36"/>
       <c r="L47" s="1"/>
-      <c r="M47" s="33"/>
+      <c r="M47" s="30"/>
       <c r="N47" s="1"/>
-      <c r="O47" s="60"/>
+      <c r="O47" s="36"/>
       <c r="P47" s="1"/>
-      <c r="Q47" s="33"/>
+      <c r="Q47" s="30"/>
       <c r="R47" s="1"/>
-      <c r="S47" s="60"/>
+      <c r="S47" s="36"/>
       <c r="T47" s="1"/>
-      <c r="U47" s="33"/>
+      <c r="U47" s="30"/>
       <c r="V47" s="1"/>
-      <c r="W47" s="60"/>
+      <c r="W47" s="36"/>
       <c r="X47" s="1"/>
-      <c r="Y47" s="33"/>
+      <c r="Y47" s="30"/>
       <c r="Z47" s="1"/>
     </row>
     <row r="48" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B48" s="42" t="s">
-        <v>116</v>
-      </c>
-      <c r="C48" s="40"/>
-      <c r="D48" s="40"/>
-      <c r="E48" s="40"/>
-      <c r="F48" s="40" t="str">
+      <c r="B48" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="C48" s="49"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="49" t="str">
         <f>P46</f>
-        <v>Прямозубая 1</v>
-      </c>
-      <c r="G48" s="41"/>
-      <c r="H48" s="17"/>
-      <c r="I48" s="17"/>
-      <c r="J48" s="17"/>
-      <c r="K48" s="60"/>
-      <c r="L48" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="M48" s="37"/>
-      <c r="N48" s="30">
-        <f ca="1">MAX(Z41:Z55,V41:V55,R41:R55,N41:N55)</f>
+        <v>Цилиндрическая 1</v>
+      </c>
+      <c r="G48" s="50"/>
+      <c r="H48" s="16"/>
+      <c r="I48" s="16"/>
+      <c r="J48" s="16"/>
+      <c r="K48" s="36"/>
+      <c r="L48" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="M48" s="43"/>
+      <c r="N48" s="28">
+        <f ca="1">MAX(Z41:Z46,V41:V46,R41:R46,N41:N46)</f>
         <v>0.78915140422920127</v>
       </c>
-      <c r="O48" s="60"/>
+      <c r="O48" s="36"/>
       <c r="P48" s="1"/>
-      <c r="Q48" s="33"/>
+      <c r="Q48" s="30"/>
       <c r="R48" s="1"/>
-      <c r="S48" s="60"/>
+      <c r="S48" s="36"/>
       <c r="T48" s="1"/>
-      <c r="U48" s="33"/>
+      <c r="U48" s="30"/>
       <c r="V48" s="1"/>
-      <c r="W48" s="60"/>
+      <c r="W48" s="36"/>
       <c r="X48" s="1"/>
-      <c r="Y48" s="33"/>
+      <c r="Y48" s="30"/>
       <c r="Z48" s="1"/>
     </row>
     <row r="49" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B49" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="C49" s="37"/>
-      <c r="D49" s="37"/>
-      <c r="E49" s="37"/>
-      <c r="F49" s="31">
+      <c r="B49" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="C49" s="43"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="43"/>
+      <c r="F49" s="87">
         <f>O41</f>
         <v>7.5398223686155026</v>
       </c>
-      <c r="G49" s="3"/>
-      <c r="H49" s="17"/>
-      <c r="I49" s="17"/>
-      <c r="J49" s="17"/>
-      <c r="K49" s="60"/>
+      <c r="G49" s="91"/>
+      <c r="I49" s="16"/>
+      <c r="J49" s="16"/>
+      <c r="K49" s="36"/>
       <c r="L49" s="1"/>
-      <c r="M49" s="33"/>
+      <c r="M49" s="30"/>
       <c r="N49" s="1"/>
-      <c r="O49" s="60"/>
+      <c r="O49" s="36"/>
       <c r="P49" s="1"/>
-      <c r="Q49" s="33"/>
+      <c r="Q49" s="30"/>
       <c r="R49" s="1"/>
-      <c r="S49" s="60"/>
+      <c r="S49" s="36"/>
       <c r="T49" s="1"/>
-      <c r="U49" s="33"/>
+      <c r="U49" s="30"/>
       <c r="V49" s="1"/>
-      <c r="W49" s="60"/>
+      <c r="W49" s="36"/>
       <c r="X49" s="1"/>
-      <c r="Y49" s="33"/>
+      <c r="Y49" s="30"/>
       <c r="Z49" s="1"/>
     </row>
     <row r="50" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B50" s="36" t="s">
-        <v>101</v>
-      </c>
-      <c r="C50" s="37"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="37"/>
-      <c r="F50" s="17">
+      <c r="B50" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="43"/>
+      <c r="F50" s="16">
         <f>P36</f>
         <v>1440</v>
       </c>
-      <c r="G50" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H50" s="17"/>
-      <c r="J50" t="s">
-        <v>97</v>
-      </c>
-      <c r="K50" t="s">
-        <v>28</v>
-      </c>
-      <c r="L50" t="s">
-        <v>100</v>
-      </c>
-      <c r="M50" t="s">
-        <v>98</v>
-      </c>
-      <c r="N50" t="s">
-        <v>28</v>
-      </c>
-      <c r="O50" t="s">
-        <v>99</v>
-      </c>
+      <c r="G50" s="91" t="s">
+        <v>105</v>
+      </c>
+      <c r="H50" s="16"/>
       <c r="P50" s="1"/>
-      <c r="Q50" s="33"/>
-      <c r="R50" s="1"/>
-      <c r="S50" s="60"/>
-      <c r="T50" s="1"/>
-      <c r="U50" s="33"/>
-      <c r="V50" s="1"/>
-      <c r="W50" s="60"/>
+      <c r="Q50" s="30"/>
       <c r="X50" s="1"/>
-      <c r="Y50" s="33"/>
+      <c r="Y50" s="30"/>
       <c r="Z50" s="1"/>
     </row>
     <row r="51" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B51" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="C51" s="37"/>
-      <c r="D51" s="37"/>
-      <c r="E51" s="37"/>
+      <c r="B51" s="42" t="s">
+        <v>104</v>
+      </c>
+      <c r="C51" s="43"/>
+      <c r="D51" s="43"/>
+      <c r="E51" s="43"/>
       <c r="F51" s="1">
         <f>F50*PI()/30</f>
         <v>150.79644737231007</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H51" s="17"/>
-      <c r="I51" t="s">
+      <c r="G51" s="91" t="s">
+        <v>106</v>
+      </c>
+      <c r="H51" s="16"/>
+      <c r="I51" s="55" t="s">
+        <v>114</v>
+      </c>
+      <c r="J51" s="70"/>
+      <c r="K51" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="J51">
+      <c r="L51" s="49" t="s">
+        <v>122</v>
+      </c>
+      <c r="M51" s="49"/>
+      <c r="N51" s="76" t="s">
+        <v>115</v>
+      </c>
+      <c r="O51" s="76"/>
+      <c r="P51" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q51" s="49"/>
+      <c r="R51" s="76" t="s">
+        <v>118</v>
+      </c>
+      <c r="S51" s="76"/>
+      <c r="T51" s="77" t="s">
+        <v>139</v>
+      </c>
+      <c r="U51" s="77"/>
+      <c r="V51" s="78"/>
+      <c r="X51" s="1"/>
+      <c r="Y51" s="30"/>
+      <c r="Z51" s="1"/>
+    </row>
+    <row r="52" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B52" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="C52" s="43"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="43"/>
+      <c r="F52" s="86">
+        <f>I41</f>
+        <v>190.98593171027443</v>
+      </c>
+      <c r="G52" s="91" t="s">
+        <v>105</v>
+      </c>
+      <c r="H52" s="16"/>
+      <c r="I52" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="J52" s="43"/>
+      <c r="K52" s="80">
         <f>R36</f>
         <v>0.872</v>
       </c>
-      <c r="K51">
+      <c r="L52" s="49">
+        <v>1</v>
+      </c>
+      <c r="M52" s="49"/>
+      <c r="N52" s="83">
+        <f>F50</f>
+        <v>1440</v>
+      </c>
+      <c r="O52" s="83"/>
+      <c r="P52" s="81">
+        <f ca="1">F55</f>
+        <v>46.89699496864425</v>
+      </c>
+      <c r="Q52" s="81"/>
+      <c r="R52" s="76">
+        <f ca="1">P52*N52*PI()/1000/30</f>
+        <v>7.0719002337086527</v>
+      </c>
+      <c r="S52" s="76"/>
+      <c r="T52" s="49">
+        <f>F61</f>
+        <v>38</v>
+      </c>
+      <c r="U52" s="49"/>
+      <c r="V52" s="50"/>
+      <c r="X52" s="1"/>
+      <c r="Y52" s="30"/>
+      <c r="Z52" s="1"/>
+    </row>
+    <row r="53" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B53" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C53" s="43"/>
+      <c r="D53" s="43"/>
+      <c r="E53" s="43"/>
+      <c r="F53" s="16">
+        <f>G41</f>
+        <v>160</v>
+      </c>
+      <c r="G53" s="91" t="s">
+        <v>16</v>
+      </c>
+      <c r="H53" s="16"/>
+      <c r="I53" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="J53" s="43"/>
+      <c r="K53" s="7">
         <f>M7</f>
         <v>0.98</v>
       </c>
-      <c r="L51">
+      <c r="L53" s="43">
+        <v>1</v>
+      </c>
+      <c r="M53" s="43"/>
+      <c r="N53" s="84">
+        <f>N52/L53</f>
+        <v>1440</v>
+      </c>
+      <c r="O53" s="84"/>
+      <c r="P53" s="58">
+        <f ca="1">P52*L53*K53</f>
+        <v>45.959055069271365</v>
+      </c>
+      <c r="Q53" s="58"/>
+      <c r="R53" s="75">
+        <f ca="1">P53*N53*PI()/1000/30</f>
+        <v>6.9304622290344788</v>
+      </c>
+      <c r="S53" s="75"/>
+      <c r="T53" s="1">
+        <f ca="1">$F$62*(P53)^(1/3)</f>
+        <v>25.073891195818355</v>
+      </c>
+      <c r="U53" s="75">
+        <f ca="1">MAX(T53:T54)</f>
+        <v>25.073891195818355</v>
+      </c>
+      <c r="V53" s="79">
+        <v>32</v>
+      </c>
+      <c r="W53" t="s">
+        <v>142</v>
+      </c>
+      <c r="X53" s="36">
+        <f>T52/V53</f>
+        <v>1.1875</v>
+      </c>
+      <c r="Y53" s="30"/>
+      <c r="Z53" s="1"/>
+    </row>
+    <row r="54" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B54" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="C54" s="43"/>
+      <c r="D54" s="43"/>
+      <c r="E54" s="43"/>
+      <c r="F54" s="85">
+        <f>E2*F53/2</f>
+        <v>320</v>
+      </c>
+      <c r="G54" s="91" t="s">
+        <v>100</v>
+      </c>
+      <c r="H54" s="16"/>
+      <c r="I54" s="42" t="s">
+        <v>95</v>
+      </c>
+      <c r="J54" s="43"/>
+      <c r="K54" s="7">
         <f>M6</f>
         <v>0.99</v>
       </c>
-      <c r="M51" s="66">
-        <f ca="1">Q41</f>
-        <v>0.96143805509807656</v>
-      </c>
-      <c r="N51">
-        <f>M7</f>
-        <v>0.98</v>
-      </c>
-      <c r="O51">
-        <f>M6</f>
-        <v>0.99</v>
-      </c>
-      <c r="P51" s="1"/>
-      <c r="Q51" s="33"/>
-      <c r="R51" s="1"/>
-      <c r="S51" s="60"/>
-      <c r="T51" s="1"/>
-      <c r="U51" s="33"/>
-      <c r="V51" s="1"/>
-      <c r="W51" s="60"/>
-      <c r="X51" s="1"/>
-      <c r="Y51" s="33"/>
-      <c r="Z51" s="1"/>
-    </row>
-    <row r="52" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B52" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="C52" s="37"/>
-      <c r="D52" s="37"/>
-      <c r="E52" s="37"/>
-      <c r="F52" s="17">
-        <f>H41</f>
-        <v>190.98593171027443</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H52" s="17"/>
-      <c r="I52" s="17"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="60"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="33"/>
-      <c r="N52" s="1"/>
-      <c r="O52" s="60"/>
-      <c r="P52" s="1"/>
-      <c r="Q52" s="33"/>
-      <c r="R52" s="1"/>
-      <c r="S52" s="60"/>
-      <c r="T52" s="1"/>
-      <c r="U52" s="33"/>
-      <c r="V52" s="1"/>
-      <c r="W52" s="60"/>
-      <c r="X52" s="1"/>
-      <c r="Y52" s="33"/>
-      <c r="Z52" s="1"/>
-    </row>
-    <row r="53" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B53" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="C53" s="37"/>
-      <c r="D53" s="37"/>
-      <c r="E53" s="37"/>
-      <c r="F53" s="17">
-        <f>F41</f>
-        <v>160</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H53" s="17"/>
-      <c r="I53" s="17"/>
-      <c r="J53" s="17"/>
-      <c r="K53" s="60"/>
-      <c r="L53" s="1"/>
-      <c r="M53" s="33"/>
-      <c r="N53" s="1"/>
-      <c r="O53" s="60"/>
-      <c r="P53" s="1"/>
-      <c r="Q53" s="33"/>
-      <c r="R53" s="1"/>
-      <c r="S53" s="60"/>
-      <c r="T53" s="1"/>
-      <c r="U53" s="33"/>
-      <c r="V53" s="1"/>
-      <c r="W53" s="60"/>
-      <c r="X53" s="1"/>
-      <c r="Y53" s="33"/>
-      <c r="Z53" s="1"/>
-    </row>
-    <row r="54" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B54" s="36" t="s">
-        <v>102</v>
-      </c>
-      <c r="C54" s="37"/>
-      <c r="D54" s="37"/>
-      <c r="E54" s="37"/>
-      <c r="F54" s="1">
-        <f>E2*F53/2</f>
-        <v>320</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="H54" s="17"/>
-      <c r="I54" s="17"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="60"/>
-      <c r="L54" s="1"/>
-      <c r="M54" s="33"/>
-      <c r="N54" s="1"/>
-      <c r="O54" s="60"/>
-      <c r="P54" s="1"/>
-      <c r="Q54" s="33"/>
-      <c r="R54" s="1"/>
-      <c r="S54" s="60"/>
-      <c r="T54" s="1"/>
-      <c r="U54" s="33"/>
-      <c r="V54" s="1"/>
-      <c r="W54" s="60"/>
+      <c r="L54" s="43">
+        <v>1</v>
+      </c>
+      <c r="M54" s="43"/>
+      <c r="N54" s="84">
+        <f>N53/L54</f>
+        <v>1440</v>
+      </c>
+      <c r="O54" s="84"/>
+      <c r="P54" s="58">
+        <f ca="1">P53*L54*K54</f>
+        <v>45.499464518578648</v>
+      </c>
+      <c r="Q54" s="58"/>
+      <c r="R54" s="75">
+        <f ca="1">P54*N54*PI()/1000/30</f>
+        <v>6.8611576067441344</v>
+      </c>
+      <c r="S54" s="75"/>
+      <c r="T54" s="1">
+        <f ca="1">$F$62*(P54)^(1/3)</f>
+        <v>24.990031401542105</v>
+      </c>
+      <c r="U54" s="75"/>
+      <c r="V54" s="79"/>
+      <c r="W54" s="95" t="s">
+        <v>141</v>
+      </c>
       <c r="X54" s="1"/>
-      <c r="Y54" s="33"/>
+      <c r="Y54" s="30"/>
       <c r="Z54" s="1"/>
     </row>
     <row r="55" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B55" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="C55" s="37"/>
-      <c r="D55" s="37"/>
-      <c r="E55" s="37"/>
+      <c r="B55" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="C55" s="43"/>
+      <c r="D55" s="43"/>
+      <c r="E55" s="43"/>
       <c r="F55" s="1">
         <f ca="1">F54/F59/F49</f>
         <v>46.89699496864425</v>
       </c>
-      <c r="G55" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="H55" s="17"/>
-      <c r="I55" s="17"/>
-      <c r="J55" s="17"/>
-      <c r="K55" s="60"/>
-      <c r="L55" s="1"/>
-      <c r="M55" s="33"/>
-      <c r="N55" s="1"/>
-      <c r="O55" s="60"/>
-      <c r="P55" s="1"/>
-      <c r="Q55" s="33"/>
-      <c r="R55" s="1"/>
-      <c r="S55" s="60"/>
-      <c r="T55" s="1"/>
-      <c r="U55" s="33"/>
-      <c r="V55" s="1"/>
-      <c r="W55" s="60"/>
+      <c r="G55" s="91" t="s">
+        <v>100</v>
+      </c>
+      <c r="H55" s="16"/>
+      <c r="I55" s="42" t="s">
+        <v>94</v>
+      </c>
+      <c r="J55" s="43"/>
+      <c r="K55" s="82">
+        <f ca="1">Q41</f>
+        <v>0.96143805509807656</v>
+      </c>
+      <c r="L55" s="58">
+        <f>F49</f>
+        <v>7.5398223686155026</v>
+      </c>
+      <c r="M55" s="58"/>
+      <c r="N55" s="58">
+        <f>N54/L55</f>
+        <v>190.98593171027443</v>
+      </c>
+      <c r="O55" s="58"/>
+      <c r="P55" s="64">
+        <f ca="1">P54*L55*K55</f>
+        <v>329.82890125747264</v>
+      </c>
+      <c r="Q55" s="64"/>
+      <c r="R55" s="75">
+        <f ca="1">P55*N55*PI()/1000/30</f>
+        <v>6.5965780251494532</v>
+      </c>
+      <c r="S55" s="75"/>
+      <c r="T55" s="1">
+        <f ca="1">$F$62*(P55)^(1/3)</f>
+        <v>48.364601010180287</v>
+      </c>
+      <c r="U55" s="75">
+        <f ca="1">MAX(T55:T57)</f>
+        <v>48.364601010180287</v>
+      </c>
+      <c r="V55" s="79">
+        <v>50</v>
+      </c>
+      <c r="W55" s="36"/>
       <c r="X55" s="1"/>
-      <c r="Y55" s="33"/>
+      <c r="Y55" s="30"/>
       <c r="Z55" s="1"/>
     </row>
     <row r="56" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B56" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="C56" s="37"/>
-      <c r="D56" s="37"/>
-      <c r="E56" s="37"/>
+      <c r="B56" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="C56" s="43"/>
+      <c r="D56" s="43"/>
+      <c r="E56" s="43"/>
       <c r="F56" s="1">
         <f ca="1">F55*F51/1000</f>
         <v>7.0719002337086527</v>
       </c>
-      <c r="G56" s="3" t="s">
-        <v>114</v>
-      </c>
+      <c r="G56" s="91" t="s">
+        <v>108</v>
+      </c>
+      <c r="I56" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="J56" s="43"/>
+      <c r="K56" s="7">
+        <f>M7</f>
+        <v>0.98</v>
+      </c>
+      <c r="L56" s="43">
+        <v>1</v>
+      </c>
+      <c r="M56" s="43"/>
+      <c r="N56" s="58">
+        <f>N55/L56</f>
+        <v>190.98593171027443</v>
+      </c>
+      <c r="O56" s="58"/>
+      <c r="P56" s="64">
+        <f ca="1">P55*L56*K56</f>
+        <v>323.23232323232315</v>
+      </c>
+      <c r="Q56" s="64"/>
+      <c r="R56" s="75">
+        <f ca="1">P56*N56*PI()/1000/30</f>
+        <v>6.4646464646464636</v>
+      </c>
+      <c r="S56" s="75"/>
+      <c r="T56" s="1">
+        <f t="shared" ref="T56:T57" ca="1" si="4">$F$62*(P56)^(1/3)</f>
+        <v>48.039996592008322</v>
+      </c>
+      <c r="U56" s="75"/>
+      <c r="V56" s="79"/>
     </row>
     <row r="57" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B57" s="36" t="s">
-        <v>108</v>
-      </c>
-      <c r="C57" s="37"/>
-      <c r="D57" s="37"/>
-      <c r="E57" s="37"/>
+      <c r="B57" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="C57" s="43"/>
+      <c r="D57" s="43"/>
+      <c r="E57" s="43"/>
       <c r="F57" s="1">
         <f>Q36</f>
         <v>2.2000000000000002</v>
       </c>
-      <c r="G57" s="3"/>
+      <c r="G57" s="91"/>
+      <c r="I57" s="42" t="s">
+        <v>95</v>
+      </c>
+      <c r="J57" s="43"/>
+      <c r="K57" s="7">
+        <f>M6</f>
+        <v>0.99</v>
+      </c>
+      <c r="L57" s="43">
+        <v>1</v>
+      </c>
+      <c r="M57" s="43"/>
+      <c r="N57" s="58">
+        <f>N56/L57</f>
+        <v>190.98593171027443</v>
+      </c>
+      <c r="O57" s="58"/>
+      <c r="P57" s="64">
+        <f ca="1">P56*L57*K57</f>
+        <v>319.99999999999994</v>
+      </c>
+      <c r="Q57" s="64"/>
+      <c r="R57" s="75">
+        <f ca="1">P57*N57*PI()/1000/30</f>
+        <v>6.3999999999999995</v>
+      </c>
+      <c r="S57" s="75"/>
+      <c r="T57" s="1">
+        <f t="shared" ca="1" si="4"/>
+        <v>47.879326506947514</v>
+      </c>
+      <c r="U57" s="75"/>
+      <c r="V57" s="79"/>
     </row>
     <row r="58" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B58" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="C58" s="37"/>
-      <c r="D58" s="37"/>
-      <c r="E58" s="37"/>
-      <c r="F58" s="1">
+      <c r="B58" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="C58" s="43"/>
+      <c r="D58" s="43"/>
+      <c r="E58" s="43"/>
+      <c r="F58" s="85">
         <f>MAX(F57,E8)</f>
         <v>2.2000000000000002</v>
       </c>
-      <c r="G58" s="3"/>
+      <c r="G58" s="91"/>
+      <c r="I58" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="J58" s="47"/>
+      <c r="K58" s="12"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4"/>
+      <c r="N58" s="51">
+        <f>N57</f>
+        <v>190.98593171027443</v>
+      </c>
+      <c r="O58" s="51"/>
+      <c r="P58" s="66">
+        <f ca="1">P57</f>
+        <v>319.99999999999994</v>
+      </c>
+      <c r="Q58" s="66"/>
+      <c r="R58" s="4"/>
+      <c r="S58" s="4"/>
+      <c r="T58" s="47">
+        <f>F54</f>
+        <v>320</v>
+      </c>
+      <c r="U58" s="47"/>
+      <c r="V58" s="54"/>
     </row>
     <row r="59" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B59" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="C59" s="37"/>
-      <c r="D59" s="37"/>
-      <c r="E59" s="37"/>
+      <c r="B59" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C59" s="43"/>
+      <c r="D59" s="43"/>
+      <c r="E59" s="43"/>
       <c r="F59" s="1">
-        <f ca="1">O51*M51*N51*L51*K51</f>
+        <f ca="1">K57*K55*K56*K54*K53</f>
         <v>0.90499014246468046</v>
       </c>
-      <c r="G59" s="3"/>
+      <c r="G59" s="91"/>
     </row>
     <row r="60" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B60" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="C60" s="39"/>
-      <c r="D60" s="39"/>
-      <c r="E60" s="39"/>
+      <c r="B60" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="C60" s="47"/>
+      <c r="D60" s="47"/>
+      <c r="E60" s="47"/>
       <c r="F60" s="4">
-        <f ca="1">F59*J51</f>
+        <f ca="1">F59*K52</f>
         <v>0.78915140422920138</v>
       </c>
-      <c r="G60" s="5"/>
+      <c r="G60" s="92"/>
+    </row>
+    <row r="61" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B61" s="56" t="s">
+        <v>140</v>
+      </c>
+      <c r="C61" s="56"/>
+      <c r="D61" s="56"/>
+      <c r="E61" s="56"/>
+      <c r="F61" s="94">
+        <v>38</v>
+      </c>
+      <c r="G61" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B62" s="61" t="s">
+        <v>177</v>
+      </c>
+      <c r="C62" s="61"/>
+      <c r="D62" s="61"/>
+      <c r="E62" s="61"/>
+      <c r="F62" s="89">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B63" s="89"/>
+      <c r="C63" s="89"/>
+      <c r="D63" s="89"/>
+      <c r="E63" s="89"/>
+      <c r="F63" s="89"/>
+    </row>
+    <row r="65" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G65" s="93"/>
     </row>
   </sheetData>
-  <mergeCells count="111">
+  <mergeCells count="159">
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="P56:Q56"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="L54:M54"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="N56:O56"/>
+    <mergeCell ref="N57:O57"/>
+    <mergeCell ref="T51:V51"/>
+    <mergeCell ref="V55:V57"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="R53:S53"/>
+    <mergeCell ref="R54:S54"/>
+    <mergeCell ref="R55:S55"/>
+    <mergeCell ref="R56:S56"/>
+    <mergeCell ref="R57:S57"/>
+    <mergeCell ref="U53:U54"/>
+    <mergeCell ref="V53:V54"/>
+    <mergeCell ref="T52:V52"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="U55:U57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="I55:J55"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="T58:V58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="Q6:S6"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="AC2:AE2"/>
+    <mergeCell ref="AC3:AE3"/>
+    <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="AC5:AE5"/>
+    <mergeCell ref="AC7:AE7"/>
+    <mergeCell ref="AC10:AE10"/>
+    <mergeCell ref="AC9:AE9"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="S19:V19"/>
+    <mergeCell ref="W19:Z19"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="Q12:S12"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="M8:N8"/>
@@ -3467,97 +4258,1331 @@
     <mergeCell ref="I27:J27"/>
     <mergeCell ref="I28:J28"/>
     <mergeCell ref="M11:N11"/>
-    <mergeCell ref="AC5:AE5"/>
-    <mergeCell ref="AC7:AE7"/>
-    <mergeCell ref="AC10:AE10"/>
-    <mergeCell ref="AC9:AE9"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="S19:V19"/>
-    <mergeCell ref="W19:Z19"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="H44:J44"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="H42:J42"/>
-    <mergeCell ref="H43:J43"/>
-    <mergeCell ref="AC2:AE2"/>
-    <mergeCell ref="AC3:AE3"/>
-    <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="I4:N4"/>
-    <mergeCell ref="I3:N3"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="Q6:S6"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="B39:G39"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B56:E56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4C98D27-F275-4550-B7FB-3917876B2935}">
+  <dimension ref="A1:Z57"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="30" width="6.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A1" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A2" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43" t="str">
+        <f>Электродвигатель!F48</f>
+        <v>Цилиндрическая 1</v>
+      </c>
+      <c r="F2" s="53"/>
+      <c r="K2" s="48" t="s">
+        <v>157</v>
+      </c>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="1"/>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A3" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="98">
+        <f>Электродвигатель!F49</f>
+        <v>7.5398223686155026</v>
+      </c>
+      <c r="F3" s="91"/>
+      <c r="K3" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="R3" s="25" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A4" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="98">
+        <f>Электродвигатель!F52</f>
+        <v>190.98593171027443</v>
+      </c>
+      <c r="F4" s="91" t="s">
+        <v>105</v>
+      </c>
+      <c r="K4" s="11">
+        <v>1</v>
+      </c>
+      <c r="L4" s="8">
+        <v>28.5</v>
+      </c>
+      <c r="M4" s="8">
+        <v>24.8</v>
+      </c>
+      <c r="N4" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="O4" s="8">
+        <v>280</v>
+      </c>
+      <c r="P4" s="8">
+        <v>56.4</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="R4" s="1">
+        <f>IF(P4&gt;$E$15,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A5" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="25">
+        <f>Электродвигатель!F54</f>
+        <v>320</v>
+      </c>
+      <c r="F5" s="91" t="s">
+        <v>100</v>
+      </c>
+      <c r="K5" s="7">
+        <v>2</v>
+      </c>
+      <c r="L5" s="1">
+        <v>28.5</v>
+      </c>
+      <c r="M5" s="1">
+        <v>24.8</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="O5" s="1">
+        <v>250</v>
+      </c>
+      <c r="P5" s="1">
+        <v>52.85</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>74.900000000000006</v>
+      </c>
+      <c r="R5" s="1">
+        <f t="shared" ref="R5:R15" si="0">IF(P5&gt;$E$15,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A6" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="25">
+        <f>Электродвигатель!F58</f>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="K6" s="7">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1">
+        <v>28.5</v>
+      </c>
+      <c r="M6" s="1">
+        <v>24.8</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0.315</v>
+      </c>
+      <c r="O6" s="1">
+        <v>200</v>
+      </c>
+      <c r="P6" s="1">
+        <v>42.3</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>68.900000000000006</v>
+      </c>
+      <c r="R6" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A7" s="61" t="s">
+        <v>151</v>
+      </c>
+      <c r="B7" s="61"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7">
+        <f>Электродвигатель!E5</f>
+        <v>10000</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="7">
+        <v>4</v>
+      </c>
+      <c r="L7" s="1">
+        <v>28.5</v>
+      </c>
+      <c r="M7" s="1">
+        <v>24.8</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="O7" s="1">
+        <v>190</v>
+      </c>
+      <c r="P7" s="1">
+        <v>38.75</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>70.8</v>
+      </c>
+      <c r="R7" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A8" s="61" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" s="61"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="K8" s="7">
+        <v>5</v>
+      </c>
+      <c r="L8" s="1">
+        <v>49</v>
+      </c>
+      <c r="M8" s="1">
+        <v>28.5</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="O8" s="1">
+        <v>250</v>
+      </c>
+      <c r="P8" s="1">
+        <v>52.85</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>64.599999999999994</v>
+      </c>
+      <c r="R8" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="S8" s="1"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A9" s="61" t="s">
+        <v>150</v>
+      </c>
+      <c r="B9" s="61"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
+      <c r="E9">
+        <f>Электродвигатель!E15</f>
+        <v>300</v>
+      </c>
+      <c r="F9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="7">
+        <v>6</v>
+      </c>
+      <c r="L9" s="1">
+        <v>49</v>
+      </c>
+      <c r="M9" s="1">
+        <v>28.5</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="O9" s="1">
+        <v>240</v>
+      </c>
+      <c r="P9" s="1">
+        <v>49.35</v>
+      </c>
+      <c r="Q9" s="90">
+        <v>69.400000000000006</v>
+      </c>
+      <c r="R9" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="S9" s="96"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A10" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="16">
+        <f>Электродвигатель!E7</f>
+        <v>3</v>
+      </c>
+      <c r="F10" s="91" t="s">
+        <v>138</v>
+      </c>
+      <c r="K10" s="100">
+        <v>7</v>
+      </c>
+      <c r="L10" s="85">
+        <v>49</v>
+      </c>
+      <c r="M10" s="85">
+        <v>28.5</v>
+      </c>
+      <c r="N10" s="85">
+        <v>0.315</v>
+      </c>
+      <c r="O10" s="85">
+        <v>180</v>
+      </c>
+      <c r="P10" s="85">
+        <v>37.75</v>
+      </c>
+      <c r="Q10" s="86">
+        <v>57.3</v>
+      </c>
+      <c r="R10" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="S10" s="96"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A11" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="88" t="s">
+        <v>101</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="K11" s="7">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
+        <v>49</v>
+      </c>
+      <c r="M11" s="1">
+        <v>28.5</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="O11" s="1">
+        <v>180</v>
+      </c>
+      <c r="P11" s="16">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="Q11" s="90">
+        <v>64.2</v>
+      </c>
+      <c r="R11" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="S11" s="96"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A12" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="97" t="s">
+        <v>101</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="K12" s="7">
+        <v>9</v>
+      </c>
+      <c r="L12" s="1">
+        <v>59</v>
+      </c>
+      <c r="M12" s="1">
+        <v>59</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="O12" s="1">
+        <v>160</v>
+      </c>
+      <c r="P12" s="90">
+        <v>32.75</v>
+      </c>
+      <c r="Q12" s="90">
+        <v>34.4</v>
+      </c>
+      <c r="R12" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="S12" s="96"/>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A13" s="61" t="s">
+        <v>146</v>
+      </c>
+      <c r="B13" s="61"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="K13" s="7">
+        <v>10</v>
+      </c>
+      <c r="L13" s="1">
+        <v>59</v>
+      </c>
+      <c r="M13" s="1">
+        <v>59</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="O13" s="1">
+        <v>140</v>
+      </c>
+      <c r="P13" s="90">
+        <v>28.75</v>
+      </c>
+      <c r="Q13" s="90">
+        <v>31.8</v>
+      </c>
+      <c r="R13" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S13" s="96"/>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A14" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="B14" s="61"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14">
+        <f>Электродвигатель!T52</f>
+        <v>38</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="7">
+        <v>11</v>
+      </c>
+      <c r="L14" s="1">
+        <v>59</v>
+      </c>
+      <c r="M14" s="1">
+        <v>59</v>
+      </c>
+      <c r="N14" s="25">
+        <v>0.315</v>
+      </c>
+      <c r="O14" s="25">
+        <v>120</v>
+      </c>
+      <c r="P14" s="90">
+        <v>24.2</v>
+      </c>
+      <c r="Q14" s="90">
+        <v>31.9</v>
+      </c>
+      <c r="R14" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S14" s="96"/>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A15" s="43" t="s">
+        <v>147</v>
+      </c>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15">
+        <f>Электродвигатель!V53</f>
+        <v>32</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" s="12">
+        <v>12</v>
+      </c>
+      <c r="L15" s="4">
+        <v>59</v>
+      </c>
+      <c r="M15" s="4">
+        <v>59</v>
+      </c>
+      <c r="N15" s="37">
+        <v>0.4</v>
+      </c>
+      <c r="O15" s="37">
+        <v>130</v>
+      </c>
+      <c r="P15" s="99">
+        <v>26.25</v>
+      </c>
+      <c r="Q15" s="99">
+        <v>38.1</v>
+      </c>
+      <c r="R15" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A16" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16">
+        <f>Электродвигатель!V55</f>
+        <v>50</v>
+      </c>
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z16" s="101"/>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="Z17" s="101"/>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="Z18" s="101"/>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z19" s="101"/>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>137</v>
+      </c>
+      <c r="M20" s="111" t="s">
+        <v>160</v>
+      </c>
+      <c r="N20" s="112"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="112"/>
+      <c r="Q20" s="102">
+        <v>7</v>
+      </c>
+      <c r="R20" s="103"/>
+      <c r="T20" s="111" t="s">
+        <v>160</v>
+      </c>
+      <c r="U20" s="112"/>
+      <c r="V20" s="112"/>
+      <c r="W20" s="112"/>
+      <c r="X20" s="102">
+        <v>8</v>
+      </c>
+      <c r="Y20" s="103"/>
+      <c r="Z20" s="101"/>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="M21" s="113" t="s">
+        <v>156</v>
+      </c>
+      <c r="N21" s="114"/>
+      <c r="O21" s="114"/>
+      <c r="P21" s="114"/>
+      <c r="Q21" s="115">
+        <v>57</v>
+      </c>
+      <c r="R21" s="104" t="s">
+        <v>163</v>
+      </c>
+      <c r="T21" s="113" t="s">
+        <v>156</v>
+      </c>
+      <c r="U21" s="114"/>
+      <c r="V21" s="114"/>
+      <c r="W21" s="114"/>
+      <c r="X21" s="115">
+        <v>64</v>
+      </c>
+      <c r="Y21" s="104" t="s">
+        <v>163</v>
+      </c>
+      <c r="Z21" s="101"/>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="M22" s="113" t="s">
+        <v>161</v>
+      </c>
+      <c r="N22" s="114"/>
+      <c r="O22" s="114"/>
+      <c r="P22" s="114"/>
+      <c r="Q22" s="105">
+        <v>20</v>
+      </c>
+      <c r="R22" s="104" t="s">
+        <v>163</v>
+      </c>
+      <c r="T22" s="113" t="s">
+        <v>161</v>
+      </c>
+      <c r="U22" s="114"/>
+      <c r="V22" s="114"/>
+      <c r="W22" s="114"/>
+      <c r="X22" s="105">
+        <v>25.3</v>
+      </c>
+      <c r="Y22" s="104" t="s">
+        <v>163</v>
+      </c>
+      <c r="Z22" s="101"/>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="M23" s="113" t="s">
+        <v>153</v>
+      </c>
+      <c r="N23" s="114"/>
+      <c r="O23" s="114"/>
+      <c r="P23" s="114"/>
+      <c r="Q23" s="105">
+        <v>180</v>
+      </c>
+      <c r="R23" s="104" t="s">
+        <v>16</v>
+      </c>
+      <c r="T23" s="113" t="s">
+        <v>153</v>
+      </c>
+      <c r="U23" s="114"/>
+      <c r="V23" s="114"/>
+      <c r="W23" s="114"/>
+      <c r="X23" s="105">
+        <v>180</v>
+      </c>
+      <c r="Y23" s="104" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z23" s="101"/>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="M24" s="113" t="s">
+        <v>162</v>
+      </c>
+      <c r="N24" s="114"/>
+      <c r="O24" s="114"/>
+      <c r="P24" s="114"/>
+      <c r="Q24" s="105">
+        <v>2.5</v>
+      </c>
+      <c r="R24" s="104" t="s">
+        <v>16</v>
+      </c>
+      <c r="T24" s="113" t="s">
+        <v>162</v>
+      </c>
+      <c r="U24" s="114"/>
+      <c r="V24" s="114"/>
+      <c r="W24" s="114"/>
+      <c r="X24" s="105">
+        <v>3</v>
+      </c>
+      <c r="Y24" s="104" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z24" s="101"/>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="M25" s="113" t="s">
+        <v>0</v>
+      </c>
+      <c r="N25" s="114"/>
+      <c r="O25" s="114"/>
+      <c r="P25" s="114"/>
+      <c r="Q25" s="105">
+        <v>2016</v>
+      </c>
+      <c r="R25" s="104" t="s">
+        <v>166</v>
+      </c>
+      <c r="T25" s="113" t="s">
+        <v>0</v>
+      </c>
+      <c r="U25" s="114"/>
+      <c r="V25" s="114"/>
+      <c r="W25" s="114"/>
+      <c r="X25" s="105">
+        <v>2013</v>
+      </c>
+      <c r="Y25" s="104" t="s">
+        <v>166</v>
+      </c>
+      <c r="Z25" s="101"/>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="M26" s="113" t="s">
+        <v>164</v>
+      </c>
+      <c r="N26" s="114"/>
+      <c r="O26" s="114"/>
+      <c r="P26" s="114"/>
+      <c r="Q26" s="105">
+        <v>734</v>
+      </c>
+      <c r="R26" s="104" t="s">
+        <v>166</v>
+      </c>
+      <c r="T26" s="113" t="s">
+        <v>164</v>
+      </c>
+      <c r="U26" s="114"/>
+      <c r="V26" s="114"/>
+      <c r="W26" s="114"/>
+      <c r="X26" s="105">
+        <v>733</v>
+      </c>
+      <c r="Y26" s="104" t="s">
+        <v>166</v>
+      </c>
+      <c r="Z26" s="101"/>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="M27" s="116" t="s">
+        <v>165</v>
+      </c>
+      <c r="N27" s="117"/>
+      <c r="O27" s="117"/>
+      <c r="P27" s="117"/>
+      <c r="Q27" s="120">
+        <v>0</v>
+      </c>
+      <c r="R27" s="121" t="s">
+        <v>166</v>
+      </c>
+      <c r="T27" s="116" t="s">
+        <v>165</v>
+      </c>
+      <c r="U27" s="117"/>
+      <c r="V27" s="117"/>
+      <c r="W27" s="117"/>
+      <c r="X27" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="121" t="s">
+        <v>166</v>
+      </c>
+      <c r="Z27" s="101"/>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="M28" s="115"/>
+      <c r="N28" s="115"/>
+      <c r="O28" s="115"/>
+      <c r="P28" s="115"/>
+      <c r="Q28" s="115"/>
+      <c r="R28" s="115"/>
+      <c r="T28" s="115"/>
+      <c r="U28" s="115"/>
+      <c r="V28" s="115"/>
+      <c r="W28" s="115"/>
+      <c r="X28" s="115"/>
+      <c r="Y28" s="115"/>
+      <c r="Z28" s="101"/>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="M29" s="111" t="s">
+        <v>167</v>
+      </c>
+      <c r="N29" s="112"/>
+      <c r="O29" s="118" t="s">
+        <v>168</v>
+      </c>
+      <c r="P29" s="118"/>
+      <c r="Q29" s="118" t="s">
+        <v>126</v>
+      </c>
+      <c r="R29" s="119"/>
+      <c r="T29" s="111" t="s">
+        <v>167</v>
+      </c>
+      <c r="U29" s="112"/>
+      <c r="V29" s="118" t="s">
+        <v>168</v>
+      </c>
+      <c r="W29" s="118"/>
+      <c r="X29" s="118" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y29" s="119"/>
+      <c r="Z29" s="101"/>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="M30" s="113" t="s">
+        <v>169</v>
+      </c>
+      <c r="N30" s="114"/>
+      <c r="O30" s="106">
+        <v>17</v>
+      </c>
+      <c r="P30" s="106"/>
+      <c r="Q30" s="106">
+        <v>127</v>
+      </c>
+      <c r="R30" s="107"/>
+      <c r="T30" s="113" t="s">
+        <v>169</v>
+      </c>
+      <c r="U30" s="114"/>
+      <c r="V30" s="106">
+        <v>14</v>
+      </c>
+      <c r="W30" s="106"/>
+      <c r="X30" s="106">
+        <v>106</v>
+      </c>
+      <c r="Y30" s="107"/>
+      <c r="Z30" s="101"/>
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="M31" s="108" t="s">
+        <v>176</v>
+      </c>
+      <c r="N31" s="106"/>
+      <c r="O31" s="106">
+        <v>-0.3</v>
+      </c>
+      <c r="P31" s="106"/>
+      <c r="Q31" s="106">
+        <v>0.3</v>
+      </c>
+      <c r="R31" s="107"/>
+      <c r="T31" s="108" t="s">
+        <v>176</v>
+      </c>
+      <c r="U31" s="106"/>
+      <c r="V31" s="106">
+        <v>0.3</v>
+      </c>
+      <c r="W31" s="106"/>
+      <c r="X31" s="106">
+        <v>-0.3</v>
+      </c>
+      <c r="Y31" s="107"/>
+      <c r="Z31" s="101"/>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="M32" s="108" t="s">
+        <v>175</v>
+      </c>
+      <c r="N32" s="106"/>
+      <c r="O32" s="106">
+        <v>49</v>
+      </c>
+      <c r="P32" s="106"/>
+      <c r="Q32" s="106">
+        <v>28.5</v>
+      </c>
+      <c r="R32" s="107"/>
+      <c r="T32" s="108" t="s">
+        <v>175</v>
+      </c>
+      <c r="U32" s="106"/>
+      <c r="V32" s="106">
+        <v>49</v>
+      </c>
+      <c r="W32" s="106"/>
+      <c r="X32" s="106">
+        <v>28.5</v>
+      </c>
+      <c r="Y32" s="107"/>
+      <c r="Z32" s="101"/>
+    </row>
+    <row r="33" spans="11:26" x14ac:dyDescent="0.3">
+      <c r="M33" s="46" t="s">
+        <v>179</v>
+      </c>
+      <c r="N33" s="47"/>
+      <c r="O33" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="P33" s="47"/>
+      <c r="Q33" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="R33" s="54"/>
+      <c r="T33" s="46" t="s">
+        <v>179</v>
+      </c>
+      <c r="U33" s="47"/>
+      <c r="V33" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="W33" s="47"/>
+      <c r="X33" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y33" s="54"/>
+      <c r="Z33" s="101"/>
+    </row>
+    <row r="34" spans="11:26" x14ac:dyDescent="0.3">
+      <c r="L34" s="101"/>
+      <c r="M34" s="108" t="s">
+        <v>171</v>
+      </c>
+      <c r="N34" s="106"/>
+      <c r="O34" s="106"/>
+      <c r="P34" s="106"/>
+      <c r="Q34" s="106"/>
+      <c r="R34" s="107"/>
+      <c r="T34" s="108" t="s">
+        <v>171</v>
+      </c>
+      <c r="U34" s="106"/>
+      <c r="V34" s="106"/>
+      <c r="W34" s="106"/>
+      <c r="X34" s="106"/>
+      <c r="Y34" s="107"/>
+      <c r="Z34" s="101"/>
+    </row>
+    <row r="35" spans="11:26" x14ac:dyDescent="0.3">
+      <c r="M35" s="113" t="s">
+        <v>170</v>
+      </c>
+      <c r="N35" s="114"/>
+      <c r="O35" s="106">
+        <v>42.5</v>
+      </c>
+      <c r="P35" s="106"/>
+      <c r="Q35" s="106">
+        <v>317.5</v>
+      </c>
+      <c r="R35" s="107"/>
+      <c r="T35" s="113" t="s">
+        <v>170</v>
+      </c>
+      <c r="U35" s="114"/>
+      <c r="V35" s="106">
+        <v>42</v>
+      </c>
+      <c r="W35" s="106"/>
+      <c r="X35" s="106">
+        <v>318</v>
+      </c>
+      <c r="Y35" s="107"/>
+      <c r="Z35" s="101"/>
+    </row>
+    <row r="36" spans="11:26" x14ac:dyDescent="0.3">
+      <c r="M36" s="113" t="s">
+        <v>173</v>
+      </c>
+      <c r="N36" s="114"/>
+      <c r="O36" s="106">
+        <v>49</v>
+      </c>
+      <c r="P36" s="106"/>
+      <c r="Q36" s="106">
+        <v>321</v>
+      </c>
+      <c r="R36" s="107"/>
+      <c r="T36" s="113" t="s">
+        <v>173</v>
+      </c>
+      <c r="U36" s="114"/>
+      <c r="V36" s="106">
+        <v>49.8</v>
+      </c>
+      <c r="W36" s="106"/>
+      <c r="X36" s="106">
+        <v>322</v>
+      </c>
+      <c r="Y36" s="107"/>
+      <c r="Z36" s="101"/>
+    </row>
+    <row r="37" spans="11:26" x14ac:dyDescent="0.3">
+      <c r="M37" s="113" t="s">
+        <v>172</v>
+      </c>
+      <c r="N37" s="114"/>
+      <c r="O37" s="106">
+        <v>37.75</v>
+      </c>
+      <c r="P37" s="106"/>
+      <c r="Q37" s="106">
+        <v>309.75</v>
+      </c>
+      <c r="R37" s="107"/>
+      <c r="T37" s="113" t="s">
+        <v>172</v>
+      </c>
+      <c r="U37" s="114"/>
+      <c r="V37" s="106">
+        <v>36.6</v>
+      </c>
+      <c r="W37" s="106"/>
+      <c r="X37" s="106">
+        <v>308.7</v>
+      </c>
+      <c r="Y37" s="107"/>
+      <c r="Z37" s="101"/>
+    </row>
+    <row r="38" spans="11:26" x14ac:dyDescent="0.3">
+      <c r="M38" s="116" t="s">
+        <v>174</v>
+      </c>
+      <c r="N38" s="117"/>
+      <c r="O38" s="109">
+        <v>62</v>
+      </c>
+      <c r="P38" s="109"/>
+      <c r="Q38" s="109">
+        <v>57</v>
+      </c>
+      <c r="R38" s="110"/>
+      <c r="T38" s="116" t="s">
+        <v>174</v>
+      </c>
+      <c r="U38" s="117"/>
+      <c r="V38" s="109">
+        <v>79</v>
+      </c>
+      <c r="W38" s="109"/>
+      <c r="X38" s="109">
+        <v>72</v>
+      </c>
+      <c r="Y38" s="110"/>
+      <c r="Z38" s="101"/>
+    </row>
+    <row r="39" spans="11:26" x14ac:dyDescent="0.3">
+      <c r="Z39" s="101"/>
+    </row>
+    <row r="40" spans="11:26" x14ac:dyDescent="0.3">
+      <c r="K40" s="89"/>
+      <c r="L40" s="89"/>
+      <c r="M40" s="61" t="s">
+        <v>178</v>
+      </c>
+      <c r="N40" s="61"/>
+      <c r="O40" s="61" t="b">
+        <f>O37&gt;$E$15</f>
+        <v>1</v>
+      </c>
+      <c r="P40" s="61"/>
+      <c r="Q40" s="61" t="b">
+        <f>Q37&gt;$E$16</f>
+        <v>1</v>
+      </c>
+      <c r="R40" s="61"/>
+      <c r="V40" s="61" t="b">
+        <f>V37&gt;$E$15</f>
+        <v>1</v>
+      </c>
+      <c r="W40" s="61"/>
+      <c r="X40" s="61" t="b">
+        <f>X37&gt;$E$16</f>
+        <v>1</v>
+      </c>
+      <c r="Y40" s="61"/>
+      <c r="Z40" s="101"/>
+    </row>
+    <row r="41" spans="11:26" x14ac:dyDescent="0.3">
+      <c r="Z41" s="101"/>
+    </row>
+    <row r="42" spans="11:26" x14ac:dyDescent="0.3">
+      <c r="Z42" s="101"/>
+    </row>
+    <row r="43" spans="11:26" x14ac:dyDescent="0.3">
+      <c r="Z43" s="101"/>
+    </row>
+    <row r="44" spans="11:26" x14ac:dyDescent="0.3">
+      <c r="Z44" s="101"/>
+    </row>
+    <row r="45" spans="11:26" x14ac:dyDescent="0.3">
+      <c r="Z45" s="101"/>
+    </row>
+    <row r="46" spans="11:26" x14ac:dyDescent="0.3">
+      <c r="Z46" s="101"/>
+    </row>
+    <row r="47" spans="11:26" x14ac:dyDescent="0.3">
+      <c r="Z47" s="101"/>
+    </row>
+    <row r="48" spans="11:26" x14ac:dyDescent="0.3">
+      <c r="Z48" s="101"/>
+    </row>
+    <row r="49" spans="26:26" x14ac:dyDescent="0.3">
+      <c r="Z49" s="101"/>
+    </row>
+    <row r="50" spans="26:26" x14ac:dyDescent="0.3">
+      <c r="Z50" s="101"/>
+    </row>
+    <row r="51" spans="26:26" x14ac:dyDescent="0.3">
+      <c r="Z51" s="101"/>
+    </row>
+    <row r="52" spans="26:26" x14ac:dyDescent="0.3">
+      <c r="Z52" s="101"/>
+    </row>
+    <row r="53" spans="26:26" x14ac:dyDescent="0.3">
+      <c r="Z53" s="101"/>
+    </row>
+    <row r="54" spans="26:26" x14ac:dyDescent="0.3">
+      <c r="Z54" s="101"/>
+    </row>
+    <row r="55" spans="26:26" x14ac:dyDescent="0.3">
+      <c r="Z55" s="101"/>
+    </row>
+    <row r="56" spans="26:26" x14ac:dyDescent="0.3">
+      <c r="Z56" s="101"/>
+    </row>
+    <row r="57" spans="26:26" x14ac:dyDescent="0.3">
+      <c r="Z57" s="101"/>
+    </row>
+  </sheetData>
+  <mergeCells count="95">
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="T38:U38"/>
+    <mergeCell ref="V38:W38"/>
+    <mergeCell ref="X38:Y38"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="V40:W40"/>
+    <mergeCell ref="X40:Y40"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="V36:W36"/>
+    <mergeCell ref="X36:Y36"/>
+    <mergeCell ref="T37:U37"/>
+    <mergeCell ref="V37:W37"/>
+    <mergeCell ref="X37:Y37"/>
+    <mergeCell ref="T33:U33"/>
+    <mergeCell ref="V33:W33"/>
+    <mergeCell ref="X33:Y33"/>
+    <mergeCell ref="T34:Y34"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="V35:W35"/>
+    <mergeCell ref="X35:Y35"/>
+    <mergeCell ref="T31:U31"/>
+    <mergeCell ref="V31:W31"/>
+    <mergeCell ref="X31:Y31"/>
+    <mergeCell ref="T32:U32"/>
+    <mergeCell ref="V32:W32"/>
+    <mergeCell ref="X32:Y32"/>
+    <mergeCell ref="T26:W26"/>
+    <mergeCell ref="T27:W27"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="V29:W29"/>
+    <mergeCell ref="X29:Y29"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="V30:W30"/>
+    <mergeCell ref="X30:Y30"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="T20:W20"/>
+    <mergeCell ref="T21:W21"/>
+    <mergeCell ref="T22:W22"/>
+    <mergeCell ref="T23:W23"/>
+    <mergeCell ref="T24:W24"/>
+    <mergeCell ref="T25:W25"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="M34:R34"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="M22:P22"/>
+    <mergeCell ref="M23:P23"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="M26:P26"/>
+    <mergeCell ref="M27:P27"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="K2:Q2"/>
+    <mergeCell ref="M20:P20"/>
+    <mergeCell ref="M21:P21"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A416109-A6F9-42CB-B875-F300C0970630}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B080B891-BABE-48BC-B741-A9DC893B6424}">
+  <dimension ref="B4:G6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="1"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="61" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4" s="61"/>
+      <c r="F4" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="43"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="75" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="75"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="75" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="75"/>
+      <c r="D6" s="43" t="s">
+        <v>127</v>
+      </c>
+      <c r="E6" s="43"/>
+      <c r="F6" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="G6" s="58"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Расчёт.xlsx
+++ b/Расчёт.xlsx
@@ -8,15 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Professional\Downloads\интститут\курсач детмаш\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2939E34B-5052-4F0D-9610-E457AC857C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEDC2F2-8B91-4C25-95AF-B0D24392336C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
   </bookViews>
   <sheets>
     <sheet name="Электродвигатель" sheetId="1" r:id="rId1"/>
     <sheet name="Передача" sheetId="2" r:id="rId2"/>
     <sheet name="Вал" sheetId="4" r:id="rId3"/>
-    <sheet name="Корпус" sheetId="3" r:id="rId4"/>
+    <sheet name="Установка" sheetId="9" r:id="rId4"/>
+    <sheet name="Подшипники" sheetId="6" r:id="rId5"/>
+    <sheet name="Колесо" sheetId="7" r:id="rId6"/>
+    <sheet name="Вал-шестерня" sheetId="8" r:id="rId7"/>
+    <sheet name="Корпус" sheetId="3" r:id="rId8"/>
+    <sheet name="Ra40" sheetId="5" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="272">
   <si>
     <t>Окружная сила</t>
   </si>
@@ -432,9 +437,6 @@
     <t>Страницы в pdf</t>
   </si>
   <si>
-    <t>Квалитет шестерни</t>
-  </si>
-  <si>
     <t>Вариант передачи</t>
   </si>
   <si>
@@ -459,18 +461,9 @@
     <t>Нормальный</t>
   </si>
   <si>
-    <t>Диаметр вала [мм]</t>
-  </si>
-  <si>
     <t>Диаметр вала электродвигателя</t>
   </si>
   <si>
-    <t>28 не подходит</t>
-  </si>
-  <si>
-    <t>Отношение:</t>
-  </si>
-  <si>
     <t>Барабан</t>
   </si>
   <si>
@@ -573,9 +566,6 @@
     <t>Смещение</t>
   </si>
   <si>
-    <t>K быстроходного вала</t>
-  </si>
-  <si>
     <t>Налазит на вал</t>
   </si>
   <si>
@@ -589,6 +579,288 @@
   </si>
   <si>
     <t>Подходит</t>
+  </si>
+  <si>
+    <t>Момент</t>
+  </si>
+  <si>
+    <t>Вал электродвигатель</t>
+  </si>
+  <si>
+    <t>Выбран:</t>
+  </si>
+  <si>
+    <t>Диаметр впадин</t>
+  </si>
+  <si>
+    <t>Шестерня</t>
+  </si>
+  <si>
+    <t>Ширина шестерни</t>
+  </si>
+  <si>
+    <t>Ширина колеса</t>
+  </si>
+  <si>
+    <t>t цилинд</t>
+  </si>
+  <si>
+    <t>t конич</t>
+  </si>
+  <si>
+    <t>Диаметр от</t>
+  </si>
+  <si>
+    <t>Диаметр до</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>Диаметр вершин</t>
+  </si>
+  <si>
+    <t>Тихоходный вал (выходной)</t>
+  </si>
+  <si>
+    <t>Быстроходный вал (входной)</t>
+  </si>
+  <si>
+    <t>Вал</t>
+  </si>
+  <si>
+    <t>Диаметр 1</t>
+  </si>
+  <si>
+    <t>Диаметр 2</t>
+  </si>
+  <si>
+    <t>Диаметр 3</t>
+  </si>
+  <si>
+    <t>7-8</t>
+  </si>
+  <si>
+    <t>5-6</t>
+  </si>
+  <si>
+    <t>Диаметр 2 расчётный</t>
+  </si>
+  <si>
+    <t>Диаметр 3 расчётный</t>
+  </si>
+  <si>
+    <t>Макс. Отношение</t>
+  </si>
+  <si>
+    <t>Диаметр моментный</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>Ra40</t>
+  </si>
+  <si>
+    <t>Мин отношение</t>
+  </si>
+  <si>
+    <t>Диаметр от электродвигателя</t>
+  </si>
+  <si>
+    <t>Берём по Ra40 для всех диаметровв валов?</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Вершины шестерни</t>
+  </si>
+  <si>
+    <t>Вершины колеса</t>
+  </si>
+  <si>
+    <t>b0</t>
+  </si>
+  <si>
+    <t>Толщина стенки</t>
+  </si>
+  <si>
+    <t>Ширина уха</t>
+  </si>
+  <si>
+    <t>Длинна</t>
+  </si>
+  <si>
+    <t>Габариты корпуса</t>
+  </si>
+  <si>
+    <t>Квалитет</t>
+  </si>
+  <si>
+    <t>Двустороняя штамповка</t>
+  </si>
+  <si>
+    <t>Способ производства</t>
+  </si>
+  <si>
+    <t>Фаска</t>
+  </si>
+  <si>
+    <t>Диаметр делительный</t>
+  </si>
+  <si>
+    <t>Шестерня (меньшая)</t>
+  </si>
+  <si>
+    <t>Впадины</t>
+  </si>
+  <si>
+    <t>Вершины</t>
+  </si>
+  <si>
+    <t>Дельтельный</t>
+  </si>
+  <si>
+    <t>Колесо (большее)</t>
+  </si>
+  <si>
+    <t>Фаска f</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>&gt;=6</t>
+  </si>
+  <si>
+    <t>γ</t>
+  </si>
+  <si>
+    <t>град</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Sст</t>
+  </si>
+  <si>
+    <t>Силы</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Шпонка не подходит из-за массовости</t>
+  </si>
+  <si>
+    <t>Шлицы</t>
+  </si>
+  <si>
+    <t>Соединение с натягом</t>
+  </si>
+  <si>
+    <t>Как соединяется тихоходный вал с барабаном</t>
+  </si>
+  <si>
+    <t>Установка - с натягом</t>
+  </si>
+  <si>
+    <t>K запаса</t>
+  </si>
+  <si>
+    <t>Давление</t>
+  </si>
+  <si>
+    <t>Коэф трения</t>
+  </si>
+  <si>
+    <t>(Для муфты)</t>
+  </si>
+  <si>
+    <t>Длинна lст</t>
+  </si>
+  <si>
+    <t>Мпа</t>
+  </si>
+  <si>
+    <t>Предположительно</t>
+  </si>
+  <si>
+    <t>Предположительно, сталь-сталь, запрессовкой</t>
+  </si>
+  <si>
+    <t>Деформация</t>
+  </si>
+  <si>
+    <t>Коэффициент Пуассона</t>
+  </si>
+  <si>
+    <t>Диаметр вала d</t>
+  </si>
+  <si>
+    <t>lст</t>
+  </si>
+  <si>
+    <t>dст</t>
+  </si>
+  <si>
+    <t>Отношение b/lст</t>
+  </si>
+  <si>
+    <t>мкм</t>
+  </si>
+  <si>
+    <t>Поправка на шероховатость</t>
+  </si>
+  <si>
+    <t>Поправка на температуру</t>
+  </si>
+  <si>
+    <t>Минимальный натяг</t>
+  </si>
+  <si>
+    <t>Максимальный натяг</t>
+  </si>
+  <si>
+    <t>Предел текучести [МПа]</t>
+  </si>
+  <si>
+    <t>Модуль упругости [МПа]</t>
+  </si>
+  <si>
+    <t>Коэф жёсткости C1,С2</t>
+  </si>
+  <si>
+    <t>Максимальное давление [МПа]</t>
+  </si>
+  <si>
+    <t>Диаметр внутренний [мм]</t>
+  </si>
+  <si>
+    <t>Максимальная деформация</t>
+  </si>
+  <si>
+    <t>Диаметр внешний [мм]</t>
+  </si>
+  <si>
+    <t>Расчёт</t>
+  </si>
+  <si>
+    <t>H8/z8</t>
+  </si>
+  <si>
+    <t>Сила запрессовки</t>
+  </si>
+  <si>
+    <t>Трение запрессовки</t>
+  </si>
+  <si>
+    <t>Ремень</t>
   </si>
 </sst>
 </file>
@@ -597,9 +869,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -620,6 +892,20 @@
       <color theme="1"/>
       <name val="Courier New"/>
       <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="204"/>
     </font>
   </fonts>
@@ -796,7 +1082,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -853,131 +1139,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -987,9 +1150,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1016,13 +1176,146 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1030,11 +1323,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1042,13 +1338,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1057,8 +1350,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1080,16 +1380,163 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>579120</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>197527</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>75277</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{835CBBC7-233D-4AED-93FF-512452705E27}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6621780" y="350520"/>
+          <a:ext cx="9402487" cy="7039957"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>480060</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>244749</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>53989</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{663FF092-D9BC-489E-B5A6-1E2F3A22076A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12390120" y="342900"/>
+          <a:ext cx="6516009" cy="4648849"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>600925</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>181256</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DE2E17A-B778-4EDE-BCF9-B7ACBC0E7AAE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="182880"/>
+          <a:ext cx="6087325" cy="2010056"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
-      <xdr:colOff>247400</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>124539</xdr:rowOff>
+      <xdr:colOff>567440</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>177879</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1112,7 +1559,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6065520" y="3238500"/>
+          <a:off x="4648200" y="4206240"/>
           <a:ext cx="11860280" cy="5115639"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1124,16 +1571,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>480060</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>434340</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>318623</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>8029</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>272903</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>409</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1156,8 +1603,52 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5966460" y="0"/>
+          <a:off x="10279380" y="358140"/>
           <a:ext cx="3496163" cy="2934109"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>318602</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>151052</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Рисунок 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A9DF619-19F9-40D4-88BE-5841ECB468BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4991100" y="0"/>
+          <a:ext cx="3343742" cy="3991532"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1473,23 +1964,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
       <c r="E2" s="19">
         <v>4</v>
       </c>
@@ -1497,22 +1988,22 @@
         <v>4</v>
       </c>
       <c r="G2" s="6"/>
-      <c r="I2" s="48" t="s">
+      <c r="I2" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49">
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78">
         <f>E2*E3</f>
         <v>6.4</v>
       </c>
-      <c r="N2" s="50"/>
-      <c r="Q2" s="48" t="s">
+      <c r="N2" s="100"/>
+      <c r="Q2" s="92" t="s">
         <v>29</v>
       </c>
-      <c r="R2" s="49"/>
-      <c r="S2" s="49"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
       <c r="T2" s="8" t="s">
         <v>30</v>
       </c>
@@ -1522,11 +2013,11 @@
       <c r="V2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AC2" s="48" t="s">
+      <c r="AC2" s="92" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="49"/>
-      <c r="AE2" s="49"/>
+      <c r="AD2" s="78"/>
+      <c r="AE2" s="78"/>
       <c r="AF2" s="8" t="s">
         <v>44</v>
       </c>
@@ -1545,12 +2036,12 @@
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
       <c r="E3" s="20">
         <v>1.6</v>
       </c>
@@ -1558,19 +2049,19 @@
         <v>5</v>
       </c>
       <c r="G3" s="3"/>
-      <c r="I3" s="42" t="s">
+      <c r="I3" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="53"/>
-      <c r="Q3" s="42" t="s">
-        <v>135</v>
-      </c>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="83"/>
+      <c r="N3" s="95"/>
+      <c r="Q3" s="87" t="s">
+        <v>134</v>
+      </c>
+      <c r="R3" s="83"/>
+      <c r="S3" s="83"/>
       <c r="T3" s="1">
         <v>0.96</v>
       </c>
@@ -1581,11 +2072,11 @@
         <f>AVERAGE(T3:U3)</f>
         <v>0.97</v>
       </c>
-      <c r="AC3" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="AD3" s="43"/>
-      <c r="AE3" s="43"/>
+      <c r="AC3" s="87" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD3" s="83"/>
+      <c r="AE3" s="83"/>
       <c r="AF3" s="1">
         <v>1.6</v>
       </c>
@@ -1610,30 +2101,30 @@
       </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="44" t="s">
+      <c r="B4" s="83"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="44"/>
-      <c r="G4" s="45"/>
-      <c r="I4" s="42" t="s">
+      <c r="F4" s="93"/>
+      <c r="G4" s="94"/>
+      <c r="I4" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="53"/>
-      <c r="Q4" s="42" t="s">
+      <c r="J4" s="83"/>
+      <c r="K4" s="83"/>
+      <c r="L4" s="83"/>
+      <c r="M4" s="83"/>
+      <c r="N4" s="95"/>
+      <c r="Q4" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="R4" s="43"/>
-      <c r="S4" s="43"/>
+      <c r="R4" s="83"/>
+      <c r="S4" s="83"/>
       <c r="T4" s="1">
         <v>0.95</v>
       </c>
@@ -1644,11 +2135,11 @@
         <f t="shared" ref="V4:V12" si="1">AVERAGE(T4:U4)</f>
         <v>0.96</v>
       </c>
-      <c r="AC4" s="42" t="s">
+      <c r="AC4" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="AD4" s="43"/>
-      <c r="AE4" s="43"/>
+      <c r="AD4" s="83"/>
+      <c r="AE4" s="83"/>
       <c r="AF4" s="1">
         <v>1</v>
       </c>
@@ -1673,12 +2164,12 @@
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
       <c r="E5" s="21">
         <v>10000</v>
       </c>
@@ -1688,19 +2179,19 @@
       <c r="G5" s="3"/>
       <c r="I5" s="7"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="43" t="s">
+      <c r="K5" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43" t="s">
+      <c r="L5" s="83"/>
+      <c r="M5" s="83" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="53"/>
-      <c r="Q5" s="42" t="s">
+      <c r="N5" s="95"/>
+      <c r="Q5" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="R5" s="43"/>
-      <c r="S5" s="43"/>
+      <c r="R5" s="83"/>
+      <c r="S5" s="83"/>
       <c r="T5" s="1">
         <v>0.95</v>
       </c>
@@ -1711,11 +2202,11 @@
         <f t="shared" si="1"/>
         <v>0.96</v>
       </c>
-      <c r="AC5" s="42" t="s">
+      <c r="AC5" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="AD5" s="43"/>
-      <c r="AE5" s="43"/>
+      <c r="AD5" s="83"/>
+      <c r="AE5" s="83"/>
       <c r="AF5" s="1">
         <v>3.15</v>
       </c>
@@ -1740,34 +2231,34 @@
       </c>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
       <c r="E6" s="21">
         <v>0.9</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="3"/>
-      <c r="I6" s="42" t="s">
+      <c r="I6" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="43"/>
-      <c r="K6" s="44">
+      <c r="J6" s="83"/>
+      <c r="K6" s="93">
         <v>2</v>
       </c>
-      <c r="L6" s="44"/>
-      <c r="M6" s="43">
+      <c r="L6" s="93"/>
+      <c r="M6" s="83">
         <v>0.99</v>
       </c>
-      <c r="N6" s="53"/>
-      <c r="Q6" s="42" t="s">
+      <c r="N6" s="95"/>
+      <c r="Q6" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="R6" s="43"/>
-      <c r="S6" s="43"/>
+      <c r="R6" s="83"/>
+      <c r="S6" s="83"/>
       <c r="T6" s="1">
         <v>0.92</v>
       </c>
@@ -1778,11 +2269,11 @@
         <f t="shared" si="1"/>
         <v>0.94</v>
       </c>
-      <c r="AC6" s="42" t="s">
+      <c r="AC6" s="87" t="s">
         <v>45</v>
       </c>
-      <c r="AD6" s="43"/>
-      <c r="AE6" s="43"/>
+      <c r="AD6" s="83"/>
+      <c r="AE6" s="83"/>
       <c r="AF6" s="1">
         <v>12.5</v>
       </c>
@@ -1807,34 +2298,34 @@
       </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A7" s="42" t="s">
+      <c r="A7" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
       <c r="E7" s="21">
         <v>3</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="3"/>
-      <c r="I7" s="42" t="s">
+      <c r="I7" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="43"/>
-      <c r="K7" s="44">
+      <c r="J7" s="83"/>
+      <c r="K7" s="93">
         <v>2</v>
       </c>
-      <c r="L7" s="44"/>
-      <c r="M7" s="43">
+      <c r="L7" s="93"/>
+      <c r="M7" s="83">
         <v>0.98</v>
       </c>
-      <c r="N7" s="53"/>
-      <c r="Q7" s="42" t="s">
+      <c r="N7" s="95"/>
+      <c r="Q7" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="R7" s="43"/>
-      <c r="S7" s="43"/>
+      <c r="R7" s="83"/>
+      <c r="S7" s="83"/>
       <c r="T7" s="1">
         <v>0.72</v>
       </c>
@@ -1845,11 +2336,11 @@
         <f t="shared" si="1"/>
         <v>0.77</v>
       </c>
-      <c r="AC7" s="42" t="s">
+      <c r="AC7" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="AD7" s="43"/>
-      <c r="AE7" s="43"/>
+      <c r="AD7" s="83"/>
+      <c r="AE7" s="83"/>
       <c r="AF7" s="1">
         <v>16</v>
       </c>
@@ -1874,35 +2365,35 @@
       </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
+      <c r="B8" s="89"/>
+      <c r="C8" s="89"/>
+      <c r="D8" s="89"/>
       <c r="E8" s="22">
         <v>2.2000000000000002</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="5"/>
-      <c r="I8" s="42" t="s">
-        <v>29</v>
-      </c>
-      <c r="J8" s="43"/>
-      <c r="K8" s="44">
+      <c r="I8" s="87" t="s">
+        <v>271</v>
+      </c>
+      <c r="J8" s="83"/>
+      <c r="K8" s="93">
         <v>0</v>
       </c>
-      <c r="L8" s="44"/>
-      <c r="M8" s="60">
+      <c r="L8" s="93"/>
+      <c r="M8" s="110">
         <f>V11</f>
         <v>0.95</v>
       </c>
-      <c r="N8" s="74"/>
-      <c r="Q8" s="42" t="s">
+      <c r="N8" s="115"/>
+      <c r="Q8" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="R8" s="43"/>
-      <c r="S8" s="43"/>
+      <c r="R8" s="83"/>
+      <c r="S8" s="83"/>
       <c r="T8" s="1">
         <v>0.7</v>
       </c>
@@ -1913,11 +2404,11 @@
         <f t="shared" si="1"/>
         <v>0.75</v>
       </c>
-      <c r="AC8" s="42" t="s">
+      <c r="AC8" s="87" t="s">
         <v>46</v>
       </c>
-      <c r="AD8" s="43"/>
-      <c r="AE8" s="43"/>
+      <c r="AD8" s="83"/>
+      <c r="AE8" s="83"/>
       <c r="AF8" s="1">
         <v>10</v>
       </c>
@@ -1942,31 +2433,31 @@
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="56"/>
-      <c r="C9" s="56"/>
-      <c r="D9" s="56"/>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="70"/>
-      <c r="I9" s="42" t="s">
+      <c r="B9" s="102"/>
+      <c r="C9" s="102"/>
+      <c r="D9" s="102"/>
+      <c r="E9" s="102"/>
+      <c r="F9" s="102"/>
+      <c r="G9" s="103"/>
+      <c r="I9" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="J9" s="43"/>
-      <c r="K9" s="43"/>
-      <c r="L9" s="43"/>
-      <c r="M9" s="58">
+      <c r="J9" s="83"/>
+      <c r="K9" s="83"/>
+      <c r="L9" s="83"/>
+      <c r="M9" s="80">
         <f>M7^K7*M6^K6*M8^K8</f>
         <v>0.94128803999999988</v>
       </c>
-      <c r="N9" s="59"/>
-      <c r="Q9" s="42" t="s">
+      <c r="N9" s="113"/>
+      <c r="Q9" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="R9" s="43"/>
-      <c r="S9" s="43"/>
+      <c r="R9" s="83"/>
+      <c r="S9" s="83"/>
       <c r="T9" s="1">
         <v>0.75</v>
       </c>
@@ -1977,11 +2468,11 @@
         <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="AC9" s="42" t="s">
+      <c r="AC9" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="AD9" s="43"/>
-      <c r="AE9" s="43"/>
+      <c r="AD9" s="83"/>
+      <c r="AE9" s="83"/>
       <c r="AF9" s="1">
         <v>8</v>
       </c>
@@ -2006,30 +2497,30 @@
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A10" s="71" t="s">
+      <c r="A10" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="72"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="73"/>
-      <c r="I10" s="42" t="s">
+      <c r="B10" s="105"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="106"/>
+      <c r="I10" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="J10" s="43"/>
-      <c r="K10" s="43"/>
-      <c r="L10" s="43"/>
-      <c r="M10" s="44">
+      <c r="J10" s="83"/>
+      <c r="K10" s="83"/>
+      <c r="L10" s="83"/>
+      <c r="M10" s="93">
         <v>0.97</v>
       </c>
-      <c r="N10" s="45"/>
-      <c r="Q10" s="42" t="s">
+      <c r="N10" s="94"/>
+      <c r="Q10" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="R10" s="43"/>
-      <c r="S10" s="43"/>
+      <c r="R10" s="83"/>
+      <c r="S10" s="83"/>
       <c r="T10" s="1">
         <v>0.8</v>
       </c>
@@ -2040,11 +2531,11 @@
         <f t="shared" si="1"/>
         <v>0.85000000000000009</v>
       </c>
-      <c r="AC10" s="46" t="s">
+      <c r="AC10" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="AD10" s="47"/>
-      <c r="AE10" s="47"/>
+      <c r="AD10" s="89"/>
+      <c r="AE10" s="89"/>
       <c r="AF10" s="4">
         <v>70</v>
       </c>
@@ -2069,31 +2560,31 @@
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A11" s="55" t="s">
+      <c r="A11" s="101" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="56"/>
-      <c r="C11" s="56"/>
-      <c r="D11" s="56"/>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="70"/>
-      <c r="I11" s="46" t="s">
+      <c r="B11" s="102"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="102"/>
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="103"/>
+      <c r="I11" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="J11" s="47"/>
-      <c r="K11" s="47"/>
-      <c r="L11" s="47"/>
-      <c r="M11" s="51">
+      <c r="J11" s="89"/>
+      <c r="K11" s="89"/>
+      <c r="L11" s="89"/>
+      <c r="M11" s="90">
         <f>M2/M10/M9</f>
         <v>7.0094783572623509</v>
       </c>
-      <c r="N11" s="52"/>
-      <c r="Q11" s="42" t="s">
+      <c r="N11" s="114"/>
+      <c r="Q11" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="R11" s="43"/>
-      <c r="S11" s="43"/>
+      <c r="R11" s="83"/>
+      <c r="S11" s="83"/>
       <c r="T11" s="1">
         <v>0.94</v>
       </c>
@@ -2112,22 +2603,22 @@
       <c r="AH11" s="1"/>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A12" s="48" t="s">
+      <c r="A12" s="92" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49" t="s">
+      <c r="B12" s="78"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="49"/>
-      <c r="G12" s="50"/>
-      <c r="Q12" s="46" t="s">
+      <c r="F12" s="78"/>
+      <c r="G12" s="100"/>
+      <c r="Q12" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="R12" s="47"/>
-      <c r="S12" s="47"/>
+      <c r="R12" s="89"/>
+      <c r="S12" s="89"/>
       <c r="T12" s="4">
         <v>0.92</v>
       </c>
@@ -2143,12 +2634,12 @@
       </c>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
+      <c r="B13" s="83"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="83"/>
       <c r="E13" s="21">
         <v>400</v>
       </c>
@@ -2163,12 +2654,12 @@
       </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
+      <c r="B14" s="83"/>
+      <c r="C14" s="83"/>
+      <c r="D14" s="83"/>
       <c r="E14" s="21">
         <v>400</v>
       </c>
@@ -2178,12 +2669,12 @@
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
+      <c r="B15" s="89"/>
+      <c r="C15" s="89"/>
+      <c r="D15" s="89"/>
       <c r="E15" s="22">
         <v>300</v>
       </c>
@@ -2193,40 +2684,40 @@
       <c r="G15" s="5"/>
     </row>
     <row r="19" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I19" s="48" t="s">
+      <c r="I19" s="92" t="s">
         <v>123</v>
       </c>
-      <c r="J19" s="50"/>
-      <c r="K19" s="48">
+      <c r="J19" s="100"/>
+      <c r="K19" s="92">
         <v>3000</v>
       </c>
-      <c r="L19" s="49"/>
-      <c r="M19" s="49"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="49">
+      <c r="L19" s="78"/>
+      <c r="M19" s="78"/>
+      <c r="N19" s="100"/>
+      <c r="O19" s="78">
         <v>1500</v>
       </c>
-      <c r="P19" s="49"/>
-      <c r="Q19" s="49"/>
-      <c r="R19" s="49"/>
-      <c r="S19" s="48">
+      <c r="P19" s="78"/>
+      <c r="Q19" s="78"/>
+      <c r="R19" s="78"/>
+      <c r="S19" s="92">
         <v>1000</v>
       </c>
-      <c r="T19" s="49"/>
-      <c r="U19" s="49"/>
-      <c r="V19" s="50"/>
-      <c r="W19" s="49">
+      <c r="T19" s="78"/>
+      <c r="U19" s="78"/>
+      <c r="V19" s="100"/>
+      <c r="W19" s="78">
         <v>750</v>
       </c>
-      <c r="X19" s="49"/>
-      <c r="Y19" s="49"/>
-      <c r="Z19" s="50"/>
+      <c r="X19" s="78"/>
+      <c r="Y19" s="78"/>
+      <c r="Z19" s="100"/>
     </row>
     <row r="20" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I20" s="46" t="s">
+      <c r="I20" s="88" t="s">
         <v>118</v>
       </c>
-      <c r="J20" s="54"/>
+      <c r="J20" s="112"/>
       <c r="K20" s="12" t="s">
         <v>72</v>
       </c>
@@ -2277,10 +2768,10 @@
       </c>
     </row>
     <row r="21" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I21" s="42">
+      <c r="I21" s="87">
         <v>0.37</v>
       </c>
-      <c r="J21" s="43"/>
+      <c r="J21" s="83"/>
       <c r="K21" s="26" t="s">
         <v>57</v>
       </c>
@@ -2315,10 +2806,10 @@
       <c r="Z21" s="3"/>
     </row>
     <row r="22" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I22" s="42">
+      <c r="I22" s="87">
         <v>0.55000000000000004</v>
       </c>
-      <c r="J22" s="43"/>
+      <c r="J22" s="83"/>
       <c r="K22" s="26" t="s">
         <v>57</v>
       </c>
@@ -2351,10 +2842,10 @@
       <c r="Z22" s="3"/>
     </row>
     <row r="23" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I23" s="42">
+      <c r="I23" s="87">
         <v>0.75</v>
       </c>
-      <c r="J23" s="43"/>
+      <c r="J23" s="83"/>
       <c r="K23" s="7" t="s">
         <v>58</v>
       </c>
@@ -2387,10 +2878,10 @@
       <c r="Z23" s="3"/>
     </row>
     <row r="24" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I24" s="42">
+      <c r="I24" s="87">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J24" s="43"/>
+      <c r="J24" s="83"/>
       <c r="K24" s="7" t="s">
         <v>59</v>
       </c>
@@ -2423,10 +2914,10 @@
       <c r="Z24" s="3"/>
     </row>
     <row r="25" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I25" s="42">
+      <c r="I25" s="87">
         <v>1.5</v>
       </c>
-      <c r="J25" s="43"/>
+      <c r="J25" s="83"/>
       <c r="K25" s="7" t="s">
         <v>60</v>
       </c>
@@ -2459,10 +2950,10 @@
       <c r="Z25" s="3"/>
     </row>
     <row r="26" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I26" s="42">
+      <c r="I26" s="87">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J26" s="43"/>
+      <c r="J26" s="83"/>
       <c r="K26" s="7" t="s">
         <v>87</v>
       </c>
@@ -2495,10 +2986,10 @@
       <c r="Z26" s="3"/>
     </row>
     <row r="27" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I27" s="42">
+      <c r="I27" s="87">
         <v>3</v>
       </c>
-      <c r="J27" s="43"/>
+      <c r="J27" s="83"/>
       <c r="K27" s="7" t="s">
         <v>61</v>
       </c>
@@ -2529,10 +3020,10 @@
       <c r="Z27" s="3"/>
     </row>
     <row r="28" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I28" s="42">
+      <c r="I28" s="87">
         <v>4</v>
       </c>
-      <c r="J28" s="43"/>
+      <c r="J28" s="83"/>
       <c r="K28" s="7" t="s">
         <v>62</v>
       </c>
@@ -2563,10 +3054,10 @@
       <c r="Z28" s="3"/>
     </row>
     <row r="29" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I29" s="42">
+      <c r="I29" s="87">
         <v>5.5</v>
       </c>
-      <c r="J29" s="43"/>
+      <c r="J29" s="83"/>
       <c r="K29" s="7" t="s">
         <v>63</v>
       </c>
@@ -2617,10 +3108,10 @@
       </c>
     </row>
     <row r="30" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I30" s="42">
+      <c r="I30" s="87">
         <v>7.5</v>
       </c>
-      <c r="J30" s="43"/>
+      <c r="J30" s="83"/>
       <c r="K30" s="7" t="s">
         <v>64</v>
       </c>
@@ -2671,10 +3162,10 @@
       </c>
     </row>
     <row r="31" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I31" s="42">
+      <c r="I31" s="87">
         <v>11</v>
       </c>
-      <c r="J31" s="43"/>
+      <c r="J31" s="83"/>
       <c r="K31" s="7" t="s">
         <v>65</v>
       </c>
@@ -2725,10 +3216,10 @@
       </c>
     </row>
     <row r="32" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I32" s="42">
+      <c r="I32" s="87">
         <v>15</v>
       </c>
-      <c r="J32" s="43"/>
+      <c r="J32" s="83"/>
       <c r="K32" s="7" t="s">
         <v>66</v>
       </c>
@@ -2759,10 +3250,10 @@
       <c r="Z32" s="3"/>
     </row>
     <row r="33" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="I33" s="42">
+      <c r="I33" s="87">
         <v>18.5</v>
       </c>
-      <c r="J33" s="43"/>
+      <c r="J33" s="83"/>
       <c r="K33" s="7" t="s">
         <v>67</v>
       </c>
@@ -2793,10 +3284,10 @@
       <c r="Z33" s="3"/>
     </row>
     <row r="34" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="I34" s="42">
+      <c r="I34" s="87">
         <v>22</v>
       </c>
-      <c r="J34" s="43"/>
+      <c r="J34" s="83"/>
       <c r="K34" s="7" t="s">
         <v>68</v>
       </c>
@@ -2827,10 +3318,10 @@
       <c r="Z34" s="3"/>
     </row>
     <row r="35" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="I35" s="46">
+      <c r="I35" s="88">
         <v>30</v>
       </c>
-      <c r="J35" s="47"/>
+      <c r="J35" s="89"/>
       <c r="K35" s="12" t="s">
         <v>69</v>
       </c>
@@ -2861,15 +3352,15 @@
       <c r="Z35" s="5"/>
     </row>
     <row r="36" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G36" s="61" t="s">
+      <c r="G36" s="111" t="s">
         <v>121</v>
       </c>
-      <c r="H36" s="61"/>
-      <c r="I36" s="55">
+      <c r="H36" s="111"/>
+      <c r="I36" s="101">
         <f>_xlfn.MINIFS(I21:J35,I21:J35,"&gt;="&amp;M11)</f>
         <v>7.5</v>
       </c>
-      <c r="J36" s="56"/>
+      <c r="J36" s="102"/>
       <c r="K36" s="9" t="str">
         <f>VLOOKUP($I$36,$I$21:$R$35,3)</f>
         <v>112M2</v>
@@ -2941,12 +3432,12 @@
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
       <c r="F38" s="16"/>
-      <c r="G38" s="48" t="s">
+      <c r="G38" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="H38" s="49"/>
-      <c r="I38" s="49"/>
-      <c r="J38" s="50"/>
+      <c r="H38" s="78"/>
+      <c r="I38" s="78"/>
+      <c r="J38" s="100"/>
       <c r="K38" s="11"/>
       <c r="L38" s="18"/>
       <c r="M38" s="18"/>
@@ -2970,12 +3461,12 @@
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
       <c r="F39" s="16"/>
-      <c r="G39" s="42" t="s">
+      <c r="G39" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="H39" s="43"/>
-      <c r="I39" s="43"/>
-      <c r="J39" s="53"/>
+      <c r="H39" s="83"/>
+      <c r="I39" s="83"/>
+      <c r="J39" s="95"/>
       <c r="K39" s="7"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -3011,14 +3502,14 @@
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
-      <c r="G40" s="42" t="s">
+      <c r="G40" s="87" t="s">
         <v>120</v>
       </c>
-      <c r="H40" s="43"/>
-      <c r="I40" s="43" t="s">
+      <c r="H40" s="83"/>
+      <c r="I40" s="83" t="s">
         <v>119</v>
       </c>
-      <c r="J40" s="53"/>
+      <c r="J40" s="95"/>
       <c r="K40" s="27" t="s">
         <v>122</v>
       </c>
@@ -3066,17 +3557,17 @@
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
-      <c r="G41" s="68">
+      <c r="G41" s="107">
         <v>160</v>
       </c>
-      <c r="H41" s="57"/>
-      <c r="I41" s="62">
-        <f>$E$3*60000/PI()/G41</f>
+      <c r="H41" s="108"/>
+      <c r="I41" s="96">
+        <f t="shared" ref="I41:I46" si="4">$E$3*60000/PI()/G41</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="J41" s="63"/>
+      <c r="J41" s="97"/>
       <c r="K41" s="15">
-        <f>IF($I41,L$36/$I41,"-")</f>
+        <f t="shared" ref="K41:K46" si="5">IF($I41,L$36/$I41,"-")</f>
         <v>15.15818455357075</v>
       </c>
       <c r="L41" s="8" t="str">
@@ -3084,15 +3575,15 @@
         <v>Прямозубая 2</v>
       </c>
       <c r="M41" s="31">
-        <f ca="1">IF(K41&lt;&gt;"-",SUMIF($AC:$AE,L41,$AJ:$AJ)-K41*SUMIF($AC:$AE,L41,$AK:$AK),0)</f>
+        <f t="shared" ref="M41:M46" ca="1" si="6">IF(K41&lt;&gt;"-",SUMIF($AC:$AE,L41,$AJ:$AJ)-K41*SUMIF($AC:$AE,L41,$AK:$AK),0)</f>
         <v>0.95497170733270809</v>
       </c>
       <c r="N41" s="8">
-        <f ca="1">M41*N$39</f>
+        <f t="shared" ref="N41:N46" ca="1" si="7">M41*N$39</f>
         <v>0.78204599858607271</v>
       </c>
       <c r="O41" s="38">
-        <f>IF($I41,P$36/$I41,"-")</f>
+        <f t="shared" ref="O41:O46" si="8">IF($I41,P$36/$I41,"-")</f>
         <v>7.5398223686155026</v>
       </c>
       <c r="P41" s="39" t="str">
@@ -3100,15 +3591,15 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="Q41" s="40">
-        <f ca="1">IF(O41&lt;&gt;"-",SUMIF($AC:$AE,P41,$AJ:$AJ)-O41*SUMIF($AC:$AE,P41,$AK:$AK),0)</f>
+        <f t="shared" ref="Q41:Q46" ca="1" si="9">IF(O41&lt;&gt;"-",SUMIF($AC:$AE,P41,$AJ:$AJ)-O41*SUMIF($AC:$AE,P41,$AK:$AK),0)</f>
         <v>0.96143805509807656</v>
       </c>
       <c r="R41" s="39">
-        <f ca="1">Q41*R$39</f>
+        <f t="shared" ref="R41:R46" ca="1" si="10">Q41*R$39</f>
         <v>0.78915140422920127</v>
       </c>
       <c r="S41" s="15">
-        <f>IF($I41,T$36/$I41,"-")</f>
+        <f t="shared" ref="S41:S46" si="11">IF($I41,T$36/$I41,"-")</f>
         <v>5.0265482457436681</v>
       </c>
       <c r="T41" s="8" t="str">
@@ -3116,15 +3607,15 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="U41" s="31">
-        <f ca="1">IF(S41&lt;&gt;"-",SUMIF($AC:$AE,T41,$AJ:$AJ)-S41*SUMIF($AC:$AE,T41,$AK:$AK),0)</f>
+        <f t="shared" ref="U41:U46" ca="1" si="12">IF(S41&lt;&gt;"-",SUMIF($AC:$AE,T41,$AJ:$AJ)-S41*SUMIF($AC:$AE,T41,$AK:$AK),0)</f>
         <v>0.969292036732051</v>
       </c>
       <c r="V41" s="8">
-        <f ca="1">U41*V$39</f>
+        <f t="shared" ref="V41:V46" ca="1" si="13">U41*V$39</f>
         <v>0.78464938124108341</v>
       </c>
       <c r="W41" s="15">
-        <f>IF($I41,X$36/$I41,"-")</f>
+        <f t="shared" ref="W41:W46" si="14">IF($I41,X$36/$I41,"-")</f>
         <v>3.8065630985996322</v>
       </c>
       <c r="X41" s="8" t="str">
@@ -3132,11 +3623,11 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="Y41" s="31">
-        <f ca="1">IF(W41&lt;&gt;"-",SUMIF($AC:$AE,X41,$AJ:$AJ)-W41*SUMIF($AC:$AE,X41,$AK:$AK),0)</f>
+        <f t="shared" ref="Y41:Y46" ca="1" si="15">IF(W41&lt;&gt;"-",SUMIF($AC:$AE,X41,$AJ:$AJ)-W41*SUMIF($AC:$AE,X41,$AK:$AK),0)</f>
         <v>0.97310449031687618</v>
       </c>
       <c r="Z41" s="6">
-        <f ca="1">Y41*Z$39</f>
+        <f t="shared" ref="Z41:Z46" ca="1" si="16">Y41*Z$39</f>
         <v>0.77857587564473563</v>
       </c>
     </row>
@@ -3146,17 +3637,17 @@
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-      <c r="G42" s="69">
+      <c r="G42" s="109">
         <v>200</v>
       </c>
-      <c r="H42" s="60"/>
-      <c r="I42" s="64">
-        <f>$E$3*60000/PI()/G42</f>
+      <c r="H42" s="110"/>
+      <c r="I42" s="81">
+        <f t="shared" si="4"/>
         <v>152.78874536821954</v>
       </c>
-      <c r="J42" s="65"/>
+      <c r="J42" s="98"/>
       <c r="K42" s="13">
-        <f>IF($I42,L$36/$I42,"-")</f>
+        <f t="shared" si="5"/>
         <v>18.947730691963439</v>
       </c>
       <c r="L42" s="1" t="str">
@@ -3164,28 +3655,28 @@
         <v>Прямозубая 2</v>
       </c>
       <c r="M42" s="30">
-        <f ca="1">IF(K42&lt;&gt;"-",SUMIF($AC:$AE,L42,$AJ:$AJ)-K42*SUMIF($AC:$AE,L42,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="6"/>
         <v>0.94723305521851664</v>
       </c>
       <c r="N42" s="1">
-        <f ca="1">M42*N$39</f>
+        <f t="shared" ca="1" si="7"/>
         <v>0.77570865699376879</v>
       </c>
       <c r="O42" s="34">
-        <f>IF($I42,P$36/$I42,"-")</f>
+        <f t="shared" si="8"/>
         <v>9.4247779607693793</v>
       </c>
       <c r="P42" s="25"/>
       <c r="Q42" s="35">
-        <f ca="1">IF(O42&lt;&gt;"-",SUMIF($AC:$AE,P42,$AJ:$AJ)-O42*SUMIF($AC:$AE,P42,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
       <c r="R42" s="25">
-        <f ca="1">Q42*R$39</f>
+        <f t="shared" ca="1" si="10"/>
         <v>0</v>
       </c>
       <c r="S42" s="13">
-        <f>IF($I42,T$36/$I42,"-")</f>
+        <f t="shared" si="11"/>
         <v>6.2831853071795862</v>
       </c>
       <c r="T42" s="1" t="str">
@@ -3193,15 +3684,15 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="U42" s="30">
-        <f ca="1">IF(S42&lt;&gt;"-",SUMIF($AC:$AE,T42,$AJ:$AJ)-S42*SUMIF($AC:$AE,T42,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="12"/>
         <v>0.96536504591506378</v>
       </c>
       <c r="V42" s="1">
-        <f ca="1">U42*V$39</f>
+        <f t="shared" ca="1" si="13"/>
         <v>0.78147045188035424</v>
       </c>
       <c r="W42" s="13">
-        <f>IF($I42,X$36/$I42,"-")</f>
+        <f t="shared" si="14"/>
         <v>4.7582038732495402</v>
       </c>
       <c r="X42" s="1" t="str">
@@ -3209,11 +3700,11 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="Y42" s="30">
-        <f ca="1">IF(W42&lt;&gt;"-",SUMIF($AC:$AE,X42,$AJ:$AJ)-W42*SUMIF($AC:$AE,X42,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="15"/>
         <v>0.97013061289609515</v>
       </c>
       <c r="Z42" s="3">
-        <f ca="1">Y42*Z$39</f>
+        <f t="shared" ca="1" si="16"/>
         <v>0.77619649168341942</v>
       </c>
     </row>
@@ -3223,17 +3714,17 @@
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
-      <c r="G43" s="42">
+      <c r="G43" s="87">
         <v>250</v>
       </c>
-      <c r="H43" s="43"/>
-      <c r="I43" s="64">
-        <f>$E$3*60000/PI()/G43</f>
+      <c r="H43" s="83"/>
+      <c r="I43" s="81">
+        <f t="shared" si="4"/>
         <v>122.23099629457563</v>
       </c>
-      <c r="J43" s="65"/>
+      <c r="J43" s="98"/>
       <c r="K43" s="13">
-        <f>IF($I43,L$36/$I43,"-")</f>
+        <f t="shared" si="5"/>
         <v>23.684663364954297</v>
       </c>
       <c r="L43" s="1" t="str">
@@ -3241,28 +3732,28 @@
         <v>Прямозубая 2</v>
       </c>
       <c r="M43" s="30">
-        <f ca="1">IF(K43&lt;&gt;"-",SUMIF($AC:$AE,L43,$AJ:$AJ)-K43*SUMIF($AC:$AE,L43,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="6"/>
         <v>0.93755974007577747</v>
       </c>
       <c r="N43" s="1">
-        <f ca="1">M43*N$39</f>
+        <f t="shared" ca="1" si="7"/>
         <v>0.76778698000338896</v>
       </c>
       <c r="O43" s="13">
-        <f>IF($I43,P$36/$I43,"-")</f>
+        <f t="shared" si="8"/>
         <v>11.780972450961723</v>
       </c>
       <c r="P43" s="1"/>
       <c r="Q43" s="30">
-        <f ca="1">IF(O43&lt;&gt;"-",SUMIF($AC:$AE,P43,$AJ:$AJ)-O43*SUMIF($AC:$AE,P43,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
       <c r="R43" s="1">
-        <f ca="1">Q43*R$39</f>
+        <f t="shared" ca="1" si="10"/>
         <v>0</v>
       </c>
       <c r="S43" s="13">
-        <f>IF($I43,T$36/$I43,"-")</f>
+        <f t="shared" si="11"/>
         <v>7.8539816339744819</v>
       </c>
       <c r="T43" s="1" t="str">
@@ -3270,15 +3761,15 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="U43" s="30">
-        <f ca="1">IF(S43&lt;&gt;"-",SUMIF($AC:$AE,T43,$AJ:$AJ)-S43*SUMIF($AC:$AE,T43,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="12"/>
         <v>0.9604563073938297</v>
       </c>
       <c r="V43" s="1">
-        <f ca="1">U43*V$39</f>
+        <f t="shared" ca="1" si="13"/>
         <v>0.77749679017944284</v>
       </c>
       <c r="W43" s="13">
-        <f>IF($I43,X$36/$I43,"-")</f>
+        <f t="shared" si="14"/>
         <v>5.9477548415619257</v>
       </c>
       <c r="X43" s="1" t="str">
@@ -3286,11 +3777,11 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="Y43" s="30">
-        <f ca="1">IF(W43&lt;&gt;"-",SUMIF($AC:$AE,X43,$AJ:$AJ)-W43*SUMIF($AC:$AE,X43,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="15"/>
         <v>0.96641326612011891</v>
       </c>
       <c r="Z43" s="3">
-        <f ca="1">Y43*Z$39</f>
+        <f t="shared" ca="1" si="16"/>
         <v>0.77322226173177433</v>
       </c>
     </row>
@@ -3300,17 +3791,17 @@
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
-      <c r="G44" s="42">
+      <c r="G44" s="87">
         <v>315</v>
       </c>
-      <c r="H44" s="43"/>
-      <c r="I44" s="64">
-        <f>$E$3*60000/PI()/G44</f>
+      <c r="H44" s="83"/>
+      <c r="I44" s="81">
+        <f t="shared" si="4"/>
         <v>97.008727217917169</v>
       </c>
-      <c r="J44" s="65"/>
+      <c r="J44" s="98"/>
       <c r="K44" s="13">
-        <f>IF($I44,L$36/$I44,"-")</f>
+        <f t="shared" si="5"/>
         <v>29.842675839842414</v>
       </c>
       <c r="L44" s="1" t="str">
@@ -3318,50 +3809,50 @@
         <v>Прямозубая 2</v>
       </c>
       <c r="M44" s="30">
-        <f ca="1">IF(K44&lt;&gt;"-",SUMIF($AC:$AE,L44,$AJ:$AJ)-K44*SUMIF($AC:$AE,L44,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="6"/>
         <v>0.92498443039021649</v>
       </c>
       <c r="N44" s="1">
-        <f ca="1">M44*N$39</f>
+        <f t="shared" ca="1" si="7"/>
         <v>0.75748879991589524</v>
       </c>
       <c r="O44" s="13">
-        <f>IF($I44,P$36/$I44,"-")</f>
+        <f t="shared" si="8"/>
         <v>14.844025288211771</v>
       </c>
       <c r="P44" s="1"/>
       <c r="Q44" s="30">
-        <f ca="1">IF(O44&lt;&gt;"-",SUMIF($AC:$AE,P44,$AJ:$AJ)-O44*SUMIF($AC:$AE,P44,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
       <c r="R44" s="1">
-        <f ca="1">Q44*R$39</f>
+        <f t="shared" ca="1" si="10"/>
         <v>0</v>
       </c>
       <c r="S44" s="13">
-        <f>IF($I44,T$36/$I44,"-")</f>
+        <f t="shared" si="11"/>
         <v>9.8960168588078474</v>
       </c>
       <c r="T44" s="1"/>
       <c r="U44" s="30">
-        <f ca="1">IF(S44&lt;&gt;"-",SUMIF($AC:$AE,T44,$AJ:$AJ)-S44*SUMIF($AC:$AE,T44,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="V44" s="1">
-        <f ca="1">U44*V$39</f>
+        <f t="shared" ca="1" si="13"/>
         <v>0</v>
       </c>
       <c r="W44" s="13">
-        <f>IF($I44,X$36/$I44,"-")</f>
+        <f t="shared" si="14"/>
         <v>7.4941711003680265</v>
       </c>
       <c r="X44" s="1"/>
       <c r="Y44" s="30">
-        <f ca="1">IF(W44&lt;&gt;"-",SUMIF($AC:$AE,X44,$AJ:$AJ)-W44*SUMIF($AC:$AE,X44,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="15"/>
         <v>0</v>
       </c>
       <c r="Z44" s="3">
-        <f ca="1">Y44*Z$39</f>
+        <f t="shared" ca="1" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -3371,65 +3862,65 @@
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="42">
+      <c r="G45" s="87">
         <v>400</v>
       </c>
-      <c r="H45" s="43"/>
-      <c r="I45" s="64">
-        <f>$E$3*60000/PI()/G45</f>
+      <c r="H45" s="83"/>
+      <c r="I45" s="81">
+        <f t="shared" si="4"/>
         <v>76.394372684109769</v>
       </c>
-      <c r="J45" s="65"/>
+      <c r="J45" s="98"/>
       <c r="K45" s="13">
-        <f>IF($I45,L$36/$I45,"-")</f>
+        <f t="shared" si="5"/>
         <v>37.895461383926879</v>
       </c>
       <c r="L45" s="1"/>
       <c r="M45" s="30">
-        <f ca="1">IF(K45&lt;&gt;"-",SUMIF($AC:$AE,L45,$AJ:$AJ)-K45*SUMIF($AC:$AE,L45,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="N45" s="1">
-        <f ca="1">M45*N$39</f>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="O45" s="13">
-        <f>IF($I45,P$36/$I45,"-")</f>
+        <f t="shared" si="8"/>
         <v>18.849555921538759</v>
       </c>
       <c r="P45" s="1"/>
       <c r="Q45" s="30">
-        <f ca="1">IF(O45&lt;&gt;"-",SUMIF($AC:$AE,P45,$AJ:$AJ)-O45*SUMIF($AC:$AE,P45,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
       <c r="R45" s="1">
-        <f ca="1">Q45*R$39</f>
+        <f t="shared" ca="1" si="10"/>
         <v>0</v>
       </c>
       <c r="S45" s="13">
-        <f>IF($I45,T$36/$I45,"-")</f>
+        <f t="shared" si="11"/>
         <v>12.566370614359172</v>
       </c>
       <c r="T45" s="1"/>
       <c r="U45" s="30">
-        <f ca="1">IF(S45&lt;&gt;"-",SUMIF($AC:$AE,T45,$AJ:$AJ)-S45*SUMIF($AC:$AE,T45,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="V45" s="1">
-        <f ca="1">U45*V$39</f>
+        <f t="shared" ca="1" si="13"/>
         <v>0</v>
       </c>
       <c r="W45" s="13">
-        <f>IF($I45,X$36/$I45,"-")</f>
+        <f t="shared" si="14"/>
         <v>9.5164077464990804</v>
       </c>
       <c r="X45" s="1"/>
       <c r="Y45" s="30">
-        <f ca="1">IF(W45&lt;&gt;"-",SUMIF($AC:$AE,X45,$AJ:$AJ)-W45*SUMIF($AC:$AE,X45,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="15"/>
         <v>0</v>
       </c>
       <c r="Z45" s="3">
-        <f ca="1">Y45*Z$39</f>
+        <f t="shared" ca="1" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -3439,32 +3930,32 @@
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-      <c r="G46" s="46">
+      <c r="G46" s="88">
         <v>500</v>
       </c>
-      <c r="H46" s="47"/>
-      <c r="I46" s="66">
-        <f>$E$3*60000/PI()/G46</f>
+      <c r="H46" s="89"/>
+      <c r="I46" s="91">
+        <f t="shared" si="4"/>
         <v>61.115498147287816</v>
       </c>
-      <c r="J46" s="67"/>
+      <c r="J46" s="99"/>
       <c r="K46" s="14">
-        <f>IF($I46,L$36/$I46,"-")</f>
+        <f t="shared" si="5"/>
         <v>47.369326729908593</v>
       </c>
       <c r="L46" s="4" t="s">
         <v>101</v>
       </c>
       <c r="M46" s="32">
-        <f ca="1">IF(K46&lt;&gt;"-",SUMIF($AC:$AE,L46,$AJ:$AJ)-K46*SUMIF($AC:$AE,L46,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="N46" s="4">
-        <f ca="1">M46*N$39</f>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="O46" s="14">
-        <f>IF($I46,P$36/$I46,"-")</f>
+        <f t="shared" si="8"/>
         <v>23.561944901923447</v>
       </c>
       <c r="P46" s="37" t="str">
@@ -3472,15 +3963,15 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="Q46" s="32">
-        <f ca="1">IF(O46&lt;&gt;"-",SUMIF($AC:$AE,P46,$AJ:$AJ)-O46*SUMIF($AC:$AE,P46,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="9"/>
         <v>0.91136892218148913</v>
       </c>
       <c r="R46" s="4">
-        <f ca="1">Q46*R$39</f>
+        <f t="shared" ca="1" si="10"/>
         <v>0.74805450116805416</v>
       </c>
       <c r="S46" s="14">
-        <f>IF($I46,T$36/$I46,"-")</f>
+        <f t="shared" si="11"/>
         <v>15.707963267948964</v>
       </c>
       <c r="T46" s="4" t="str">
@@ -3488,15 +3979,15 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="U46" s="32">
-        <f ca="1">IF(S46&lt;&gt;"-",SUMIF($AC:$AE,T46,$AJ:$AJ)-S46*SUMIF($AC:$AE,T46,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="12"/>
         <v>0.93591261478765941</v>
       </c>
       <c r="V46" s="4">
-        <f ca="1">U46*V$39</f>
+        <f t="shared" ca="1" si="13"/>
         <v>0.75762848167488572</v>
       </c>
       <c r="W46" s="14">
-        <f>IF($I46,X$36/$I46,"-")</f>
+        <f t="shared" si="14"/>
         <v>11.895509683123851</v>
       </c>
       <c r="X46" s="4" t="str">
@@ -3504,11 +3995,11 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="Y46" s="32">
-        <f ca="1">IF(W46&lt;&gt;"-",SUMIF($AC:$AE,X46,$AJ:$AJ)-W46*SUMIF($AC:$AE,X46,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="15"/>
         <v>0.94782653224023794</v>
       </c>
       <c r="Z46" s="5">
-        <f ca="1">Y46*Z$39</f>
+        <f t="shared" ca="1" si="16"/>
         <v>0.75835111197354876</v>
       </c>
     </row>
@@ -3540,25 +4031,25 @@
       <c r="Z47" s="1"/>
     </row>
     <row r="48" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B48" s="48" t="s">
+      <c r="B48" s="92" t="s">
         <v>110</v>
       </c>
-      <c r="C48" s="49"/>
-      <c r="D48" s="49"/>
-      <c r="E48" s="49"/>
-      <c r="F48" s="49" t="str">
+      <c r="C48" s="78"/>
+      <c r="D48" s="78"/>
+      <c r="E48" s="78"/>
+      <c r="F48" s="78" t="str">
         <f>P46</f>
         <v>Цилиндрическая 1</v>
       </c>
-      <c r="G48" s="50"/>
+      <c r="G48" s="100"/>
       <c r="H48" s="16"/>
       <c r="I48" s="16"/>
       <c r="J48" s="16"/>
       <c r="K48" s="36"/>
-      <c r="L48" s="43" t="s">
+      <c r="L48" s="83" t="s">
         <v>56</v>
       </c>
-      <c r="M48" s="43"/>
+      <c r="M48" s="83"/>
       <c r="N48" s="28">
         <f ca="1">MAX(Z41:Z46,V41:V46,R41:R46,N41:N46)</f>
         <v>0.78915140422920127</v>
@@ -3566,7 +4057,6 @@
       <c r="O48" s="36"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="30"/>
-      <c r="R48" s="1"/>
       <c r="S48" s="36"/>
       <c r="T48" s="1"/>
       <c r="U48" s="30"/>
@@ -3577,17 +4067,17 @@
       <c r="Z48" s="1"/>
     </row>
     <row r="49" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B49" s="42" t="s">
+      <c r="B49" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="43"/>
-      <c r="D49" s="43"/>
-      <c r="E49" s="43"/>
-      <c r="F49" s="87">
+      <c r="C49" s="83"/>
+      <c r="D49" s="83"/>
+      <c r="E49" s="83"/>
+      <c r="F49" s="46">
         <f>O41</f>
         <v>7.5398223686155026</v>
       </c>
-      <c r="G49" s="91"/>
+      <c r="G49" s="50"/>
       <c r="I49" s="16"/>
       <c r="J49" s="16"/>
       <c r="K49" s="36"/>
@@ -3600,7 +4090,6 @@
       <c r="R49" s="1"/>
       <c r="S49" s="36"/>
       <c r="T49" s="1"/>
-      <c r="U49" s="30"/>
       <c r="V49" s="1"/>
       <c r="W49" s="36"/>
       <c r="X49" s="1"/>
@@ -3608,497 +4097,582 @@
       <c r="Z49" s="1"/>
     </row>
     <row r="50" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B50" s="42" t="s">
+      <c r="B50" s="87" t="s">
         <v>96</v>
       </c>
-      <c r="C50" s="43"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="43"/>
+      <c r="C50" s="83"/>
+      <c r="D50" s="83"/>
+      <c r="E50" s="83"/>
       <c r="F50" s="16">
         <f>P36</f>
         <v>1440</v>
       </c>
-      <c r="G50" s="91" t="s">
+      <c r="G50" s="50" t="s">
         <v>105</v>
       </c>
       <c r="H50" s="16"/>
       <c r="P50" s="1"/>
       <c r="Q50" s="30"/>
+      <c r="V50" s="25"/>
       <c r="X50" s="1"/>
       <c r="Y50" s="30"/>
       <c r="Z50" s="1"/>
     </row>
     <row r="51" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B51" s="42" t="s">
+      <c r="B51" s="87" t="s">
         <v>104</v>
       </c>
-      <c r="C51" s="43"/>
-      <c r="D51" s="43"/>
-      <c r="E51" s="43"/>
+      <c r="C51" s="83"/>
+      <c r="D51" s="83"/>
+      <c r="E51" s="83"/>
       <c r="F51" s="1">
         <f>F50*PI()/30</f>
         <v>150.79644737231007</v>
       </c>
-      <c r="G51" s="91" t="s">
+      <c r="G51" s="50" t="s">
         <v>106</v>
       </c>
       <c r="H51" s="16"/>
-      <c r="I51" s="55" t="s">
+      <c r="I51" s="101" t="s">
         <v>114</v>
       </c>
-      <c r="J51" s="70"/>
+      <c r="J51" s="103"/>
       <c r="K51" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="L51" s="49" t="s">
+      <c r="L51" s="78" t="s">
         <v>122</v>
       </c>
-      <c r="M51" s="49"/>
-      <c r="N51" s="76" t="s">
+      <c r="M51" s="78"/>
+      <c r="N51" s="82" t="s">
         <v>115</v>
       </c>
-      <c r="O51" s="76"/>
-      <c r="P51" s="49" t="s">
+      <c r="O51" s="82"/>
+      <c r="P51" s="78" t="s">
         <v>116</v>
       </c>
-      <c r="Q51" s="49"/>
-      <c r="R51" s="76" t="s">
+      <c r="Q51" s="78"/>
+      <c r="R51" s="82" t="s">
         <v>118</v>
       </c>
-      <c r="S51" s="76"/>
-      <c r="T51" s="77" t="s">
-        <v>139</v>
-      </c>
-      <c r="U51" s="77"/>
-      <c r="V51" s="78"/>
+      <c r="S51" s="82"/>
+      <c r="T51" s="49"/>
+      <c r="U51" s="49"/>
+      <c r="V51" s="49"/>
       <c r="X51" s="1"/>
       <c r="Y51" s="30"/>
       <c r="Z51" s="1"/>
     </row>
     <row r="52" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B52" s="42" t="s">
+      <c r="B52" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="C52" s="43"/>
-      <c r="D52" s="43"/>
-      <c r="E52" s="43"/>
-      <c r="F52" s="86">
+      <c r="C52" s="83"/>
+      <c r="D52" s="83"/>
+      <c r="E52" s="83"/>
+      <c r="F52" s="45">
         <f>I41</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="G52" s="91" t="s">
+      <c r="G52" s="50" t="s">
         <v>105</v>
       </c>
       <c r="H52" s="16"/>
-      <c r="I52" s="42" t="s">
+      <c r="I52" s="87" t="s">
         <v>117</v>
       </c>
-      <c r="J52" s="43"/>
-      <c r="K52" s="80">
+      <c r="J52" s="83"/>
+      <c r="K52" s="42">
         <f>R36</f>
         <v>0.872</v>
       </c>
-      <c r="L52" s="49">
+      <c r="L52" s="78">
         <v>1</v>
       </c>
-      <c r="M52" s="49"/>
-      <c r="N52" s="83">
+      <c r="M52" s="78"/>
+      <c r="N52" s="84">
         <f>F50</f>
         <v>1440</v>
       </c>
-      <c r="O52" s="83"/>
-      <c r="P52" s="81">
+      <c r="O52" s="84"/>
+      <c r="P52" s="79">
         <f ca="1">F55</f>
         <v>46.89699496864425</v>
       </c>
-      <c r="Q52" s="81"/>
-      <c r="R52" s="76">
-        <f ca="1">P52*N52*PI()/1000/30</f>
+      <c r="Q52" s="79"/>
+      <c r="R52" s="82">
+        <f t="shared" ref="R52:R57" ca="1" si="17">P52*N52*PI()/1000/30</f>
         <v>7.0719002337086527</v>
       </c>
-      <c r="S52" s="76"/>
-      <c r="T52" s="49">
-        <f>F61</f>
-        <v>38</v>
-      </c>
-      <c r="U52" s="49"/>
-      <c r="V52" s="50"/>
+      <c r="S52" s="82"/>
+      <c r="T52" s="16"/>
+      <c r="U52" s="30"/>
       <c r="X52" s="1"/>
       <c r="Y52" s="30"/>
       <c r="Z52" s="1"/>
     </row>
     <row r="53" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B53" s="42" t="s">
+      <c r="B53" s="87" t="s">
         <v>107</v>
       </c>
-      <c r="C53" s="43"/>
-      <c r="D53" s="43"/>
-      <c r="E53" s="43"/>
+      <c r="C53" s="83"/>
+      <c r="D53" s="83"/>
+      <c r="E53" s="83"/>
       <c r="F53" s="16">
         <f>G41</f>
         <v>160</v>
       </c>
-      <c r="G53" s="91" t="s">
+      <c r="G53" s="50" t="s">
         <v>16</v>
       </c>
       <c r="H53" s="16"/>
-      <c r="I53" s="42" t="s">
+      <c r="I53" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="J53" s="43"/>
+      <c r="J53" s="83"/>
       <c r="K53" s="7">
         <f>M7</f>
         <v>0.98</v>
       </c>
-      <c r="L53" s="43">
+      <c r="L53" s="83">
         <v>1</v>
       </c>
-      <c r="M53" s="43"/>
-      <c r="N53" s="84">
+      <c r="M53" s="83"/>
+      <c r="N53" s="85">
         <f>N52/L53</f>
         <v>1440</v>
       </c>
-      <c r="O53" s="84"/>
-      <c r="P53" s="58">
+      <c r="O53" s="85"/>
+      <c r="P53" s="80">
         <f ca="1">P52*L53*K53</f>
         <v>45.959055069271365</v>
       </c>
-      <c r="Q53" s="58"/>
-      <c r="R53" s="75">
-        <f ca="1">P53*N53*PI()/1000/30</f>
+      <c r="Q53" s="80"/>
+      <c r="R53" s="86">
+        <f t="shared" ca="1" si="17"/>
         <v>6.9304622290344788</v>
       </c>
-      <c r="S53" s="75"/>
-      <c r="T53" s="1">
-        <f ca="1">$F$62*(P53)^(1/3)</f>
-        <v>25.073891195818355</v>
-      </c>
-      <c r="U53" s="75">
-        <f ca="1">MAX(T53:T54)</f>
-        <v>25.073891195818355</v>
-      </c>
-      <c r="V53" s="79">
-        <v>32</v>
-      </c>
-      <c r="W53" t="s">
-        <v>142</v>
-      </c>
-      <c r="X53" s="36">
-        <f>T52/V53</f>
-        <v>1.1875</v>
-      </c>
+      <c r="S53" s="86"/>
+      <c r="T53" s="1"/>
+      <c r="U53" s="73"/>
+      <c r="V53" s="74"/>
+      <c r="X53" s="36"/>
       <c r="Y53" s="30"/>
       <c r="Z53" s="1"/>
     </row>
     <row r="54" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B54" s="42" t="s">
+      <c r="B54" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="C54" s="43"/>
-      <c r="D54" s="43"/>
-      <c r="E54" s="43"/>
-      <c r="F54" s="85">
+      <c r="C54" s="83"/>
+      <c r="D54" s="83"/>
+      <c r="E54" s="83"/>
+      <c r="F54" s="44">
         <f>E2*F53/2</f>
         <v>320</v>
       </c>
-      <c r="G54" s="91" t="s">
+      <c r="G54" s="50" t="s">
         <v>100</v>
       </c>
       <c r="H54" s="16"/>
-      <c r="I54" s="42" t="s">
+      <c r="I54" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="J54" s="43"/>
+      <c r="J54" s="83"/>
       <c r="K54" s="7">
         <f>M6</f>
         <v>0.99</v>
       </c>
-      <c r="L54" s="43">
+      <c r="L54" s="83">
         <v>1</v>
       </c>
-      <c r="M54" s="43"/>
-      <c r="N54" s="84">
+      <c r="M54" s="83"/>
+      <c r="N54" s="85">
         <f>N53/L54</f>
         <v>1440</v>
       </c>
-      <c r="O54" s="84"/>
-      <c r="P54" s="58">
+      <c r="O54" s="85"/>
+      <c r="P54" s="80">
         <f ca="1">P53*L54*K54</f>
         <v>45.499464518578648</v>
       </c>
-      <c r="Q54" s="58"/>
-      <c r="R54" s="75">
-        <f ca="1">P54*N54*PI()/1000/30</f>
+      <c r="Q54" s="80"/>
+      <c r="R54" s="86">
+        <f t="shared" ca="1" si="17"/>
         <v>6.8611576067441344</v>
       </c>
-      <c r="S54" s="75"/>
-      <c r="T54" s="1">
-        <f ca="1">$F$62*(P54)^(1/3)</f>
-        <v>24.990031401542105</v>
-      </c>
-      <c r="U54" s="75"/>
-      <c r="V54" s="79"/>
-      <c r="W54" s="95" t="s">
-        <v>141</v>
-      </c>
+      <c r="S54" s="86"/>
+      <c r="T54" s="1"/>
+      <c r="U54" s="73"/>
+      <c r="V54" s="74"/>
+      <c r="W54" s="53"/>
       <c r="X54" s="1"/>
       <c r="Y54" s="30"/>
       <c r="Z54" s="1"/>
     </row>
     <row r="55" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B55" s="42" t="s">
+      <c r="B55" s="87" t="s">
         <v>98</v>
       </c>
-      <c r="C55" s="43"/>
-      <c r="D55" s="43"/>
-      <c r="E55" s="43"/>
+      <c r="C55" s="83"/>
+      <c r="D55" s="83"/>
+      <c r="E55" s="83"/>
       <c r="F55" s="1">
         <f ca="1">F54/F59/F49</f>
         <v>46.89699496864425</v>
       </c>
-      <c r="G55" s="91" t="s">
+      <c r="G55" s="50" t="s">
         <v>100</v>
       </c>
       <c r="H55" s="16"/>
-      <c r="I55" s="42" t="s">
+      <c r="I55" s="87" t="s">
         <v>94</v>
       </c>
-      <c r="J55" s="43"/>
-      <c r="K55" s="82">
+      <c r="J55" s="83"/>
+      <c r="K55" s="43">
         <f ca="1">Q41</f>
         <v>0.96143805509807656</v>
       </c>
-      <c r="L55" s="58">
+      <c r="L55" s="80">
         <f>F49</f>
         <v>7.5398223686155026</v>
       </c>
-      <c r="M55" s="58"/>
-      <c r="N55" s="58">
+      <c r="M55" s="80"/>
+      <c r="N55" s="80">
         <f>N54/L55</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O55" s="58"/>
-      <c r="P55" s="64">
+      <c r="O55" s="80"/>
+      <c r="P55" s="81">
         <f ca="1">P54*L55*K55</f>
         <v>329.82890125747264</v>
       </c>
-      <c r="Q55" s="64"/>
-      <c r="R55" s="75">
-        <f ca="1">P55*N55*PI()/1000/30</f>
+      <c r="Q55" s="81"/>
+      <c r="R55" s="86">
+        <f t="shared" ca="1" si="17"/>
         <v>6.5965780251494532</v>
       </c>
-      <c r="S55" s="75"/>
-      <c r="T55" s="1">
-        <f ca="1">$F$62*(P55)^(1/3)</f>
-        <v>48.364601010180287</v>
-      </c>
-      <c r="U55" s="75">
-        <f ca="1">MAX(T55:T57)</f>
-        <v>48.364601010180287</v>
-      </c>
-      <c r="V55" s="79">
-        <v>50</v>
-      </c>
+      <c r="S55" s="86"/>
+      <c r="T55" s="1"/>
+      <c r="U55" s="73"/>
+      <c r="V55" s="74"/>
       <c r="W55" s="36"/>
       <c r="X55" s="1"/>
       <c r="Y55" s="30"/>
       <c r="Z55" s="1"/>
     </row>
     <row r="56" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B56" s="42" t="s">
+      <c r="B56" s="87" t="s">
         <v>99</v>
       </c>
-      <c r="C56" s="43"/>
-      <c r="D56" s="43"/>
-      <c r="E56" s="43"/>
+      <c r="C56" s="83"/>
+      <c r="D56" s="83"/>
+      <c r="E56" s="83"/>
       <c r="F56" s="1">
         <f ca="1">F55*F51/1000</f>
         <v>7.0719002337086527</v>
       </c>
-      <c r="G56" s="91" t="s">
+      <c r="G56" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="I56" s="42" t="s">
+      <c r="I56" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="J56" s="43"/>
+      <c r="J56" s="83"/>
       <c r="K56" s="7">
         <f>M7</f>
         <v>0.98</v>
       </c>
-      <c r="L56" s="43">
+      <c r="L56" s="83">
         <v>1</v>
       </c>
-      <c r="M56" s="43"/>
-      <c r="N56" s="58">
+      <c r="M56" s="83"/>
+      <c r="N56" s="80">
         <f>N55/L56</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O56" s="58"/>
-      <c r="P56" s="64">
+      <c r="O56" s="80"/>
+      <c r="P56" s="81">
         <f ca="1">P55*L56*K56</f>
         <v>323.23232323232315</v>
       </c>
-      <c r="Q56" s="64"/>
-      <c r="R56" s="75">
-        <f ca="1">P56*N56*PI()/1000/30</f>
+      <c r="Q56" s="81"/>
+      <c r="R56" s="86">
+        <f t="shared" ca="1" si="17"/>
         <v>6.4646464646464636</v>
       </c>
-      <c r="S56" s="75"/>
-      <c r="T56" s="1">
-        <f t="shared" ref="T56:T57" ca="1" si="4">$F$62*(P56)^(1/3)</f>
-        <v>48.039996592008322</v>
-      </c>
-      <c r="U56" s="75"/>
-      <c r="V56" s="79"/>
+      <c r="S56" s="86"/>
+      <c r="T56" s="1"/>
+      <c r="U56" s="73"/>
+      <c r="V56" s="74"/>
     </row>
     <row r="57" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B57" s="42" t="s">
+      <c r="B57" s="87" t="s">
         <v>102</v>
       </c>
-      <c r="C57" s="43"/>
-      <c r="D57" s="43"/>
-      <c r="E57" s="43"/>
+      <c r="C57" s="83"/>
+      <c r="D57" s="83"/>
+      <c r="E57" s="83"/>
       <c r="F57" s="1">
         <f>Q36</f>
         <v>2.2000000000000002</v>
       </c>
-      <c r="G57" s="91"/>
-      <c r="I57" s="42" t="s">
+      <c r="G57" s="50"/>
+      <c r="I57" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="J57" s="43"/>
+      <c r="J57" s="83"/>
       <c r="K57" s="7">
         <f>M6</f>
         <v>0.99</v>
       </c>
-      <c r="L57" s="43">
+      <c r="L57" s="83">
         <v>1</v>
       </c>
-      <c r="M57" s="43"/>
-      <c r="N57" s="58">
+      <c r="M57" s="83"/>
+      <c r="N57" s="80">
         <f>N56/L57</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O57" s="58"/>
-      <c r="P57" s="64">
+      <c r="O57" s="80"/>
+      <c r="P57" s="81">
         <f ca="1">P56*L57*K57</f>
         <v>319.99999999999994</v>
       </c>
-      <c r="Q57" s="64"/>
-      <c r="R57" s="75">
-        <f ca="1">P57*N57*PI()/1000/30</f>
+      <c r="Q57" s="81"/>
+      <c r="R57" s="86">
+        <f t="shared" ca="1" si="17"/>
         <v>6.3999999999999995</v>
       </c>
-      <c r="S57" s="75"/>
-      <c r="T57" s="1">
-        <f t="shared" ca="1" si="4"/>
-        <v>47.879326506947514</v>
-      </c>
-      <c r="U57" s="75"/>
-      <c r="V57" s="79"/>
+      <c r="S57" s="86"/>
+      <c r="T57" s="1"/>
+      <c r="U57" s="73"/>
+      <c r="V57" s="74"/>
     </row>
     <row r="58" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B58" s="42" t="s">
+      <c r="B58" s="87" t="s">
         <v>103</v>
       </c>
-      <c r="C58" s="43"/>
-      <c r="D58" s="43"/>
-      <c r="E58" s="43"/>
-      <c r="F58" s="85">
+      <c r="C58" s="83"/>
+      <c r="D58" s="83"/>
+      <c r="E58" s="83"/>
+      <c r="F58" s="44">
         <f>MAX(F57,E8)</f>
         <v>2.2000000000000002</v>
       </c>
-      <c r="G58" s="91"/>
-      <c r="I58" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="J58" s="47"/>
+      <c r="G58" s="50"/>
+      <c r="I58" s="88" t="s">
+        <v>139</v>
+      </c>
+      <c r="J58" s="89"/>
       <c r="K58" s="12"/>
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
-      <c r="N58" s="51">
+      <c r="N58" s="90">
         <f>N57</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O58" s="51"/>
-      <c r="P58" s="66">
+      <c r="O58" s="90"/>
+      <c r="P58" s="91">
         <f ca="1">P57</f>
         <v>319.99999999999994</v>
       </c>
-      <c r="Q58" s="66"/>
+      <c r="Q58" s="91"/>
       <c r="R58" s="4"/>
       <c r="S58" s="4"/>
-      <c r="T58" s="47">
-        <f>F54</f>
-        <v>320</v>
-      </c>
-      <c r="U58" s="47"/>
-      <c r="V58" s="54"/>
+      <c r="T58" s="16"/>
+      <c r="U58" s="16"/>
+      <c r="V58" s="16"/>
     </row>
     <row r="59" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B59" s="42" t="s">
+      <c r="B59" s="87" t="s">
         <v>109</v>
       </c>
-      <c r="C59" s="43"/>
-      <c r="D59" s="43"/>
-      <c r="E59" s="43"/>
+      <c r="C59" s="83"/>
+      <c r="D59" s="83"/>
+      <c r="E59" s="83"/>
       <c r="F59" s="1">
         <f ca="1">K57*K55*K56*K54*K53</f>
         <v>0.90499014246468046</v>
       </c>
-      <c r="G59" s="91"/>
+      <c r="G59" s="50"/>
     </row>
     <row r="60" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B60" s="46" t="s">
+      <c r="B60" s="87" t="s">
         <v>111</v>
       </c>
-      <c r="C60" s="47"/>
-      <c r="D60" s="47"/>
-      <c r="E60" s="47"/>
-      <c r="F60" s="4">
+      <c r="C60" s="83"/>
+      <c r="D60" s="83"/>
+      <c r="E60" s="83"/>
+      <c r="F60" s="1">
         <f ca="1">F59*K52</f>
         <v>0.78915140422920138</v>
       </c>
-      <c r="G60" s="92"/>
+      <c r="G60" s="50"/>
     </row>
     <row r="61" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B61" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="C61" s="56"/>
-      <c r="D61" s="56"/>
-      <c r="E61" s="56"/>
-      <c r="F61" s="94">
+      <c r="B61" s="83" t="s">
+        <v>138</v>
+      </c>
+      <c r="C61" s="83"/>
+      <c r="D61" s="83"/>
+      <c r="E61" s="83"/>
+      <c r="F61" s="75">
         <v>38</v>
       </c>
-      <c r="G61" t="s">
+      <c r="G61" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="62" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B62" s="61" t="s">
-        <v>177</v>
-      </c>
-      <c r="C62" s="61"/>
-      <c r="D62" s="61"/>
-      <c r="E62" s="61"/>
-      <c r="F62" s="89">
-        <v>7</v>
-      </c>
+      <c r="B62" s="48"/>
+      <c r="C62" s="48"/>
+      <c r="D62" s="48"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="48"/>
     </row>
     <row r="63" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B63" s="89"/>
-      <c r="C63" s="89"/>
-      <c r="D63" s="89"/>
-      <c r="E63" s="89"/>
-      <c r="F63" s="89"/>
+      <c r="B63" s="48"/>
+      <c r="C63" s="48"/>
+      <c r="D63" s="48"/>
+      <c r="E63" s="48"/>
+      <c r="F63" s="48"/>
     </row>
     <row r="65" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G65" s="93"/>
+      <c r="G65" s="51"/>
     </row>
   </sheetData>
-  <mergeCells count="159">
+  <mergeCells count="151">
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="S19:V19"/>
+    <mergeCell ref="W19:Z19"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="AC8:AE8"/>
+    <mergeCell ref="AC6:AE6"/>
+    <mergeCell ref="K19:N19"/>
+    <mergeCell ref="AC2:AE2"/>
+    <mergeCell ref="AC3:AE3"/>
+    <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="AC5:AE5"/>
+    <mergeCell ref="AC7:AE7"/>
+    <mergeCell ref="AC10:AE10"/>
+    <mergeCell ref="AC9:AE9"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="Q6:S6"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="R53:S53"/>
+    <mergeCell ref="R54:S54"/>
+    <mergeCell ref="R55:S55"/>
+    <mergeCell ref="R56:S56"/>
+    <mergeCell ref="R57:S57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="I55:J55"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="I52:J52"/>
     <mergeCell ref="P51:Q51"/>
     <mergeCell ref="P52:Q52"/>
     <mergeCell ref="P53:Q53"/>
@@ -4120,144 +4694,6 @@
     <mergeCell ref="N55:O55"/>
     <mergeCell ref="N56:O56"/>
     <mergeCell ref="N57:O57"/>
-    <mergeCell ref="T51:V51"/>
-    <mergeCell ref="V55:V57"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="R53:S53"/>
-    <mergeCell ref="R54:S54"/>
-    <mergeCell ref="R55:S55"/>
-    <mergeCell ref="R56:S56"/>
-    <mergeCell ref="R57:S57"/>
-    <mergeCell ref="U53:U54"/>
-    <mergeCell ref="V53:V54"/>
-    <mergeCell ref="T52:V52"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="U55:U57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="I55:J55"/>
-    <mergeCell ref="I54:J54"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="I58:J58"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="T58:V58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="G39:J39"/>
-    <mergeCell ref="G38:J38"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="Q6:S6"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="I4:N4"/>
-    <mergeCell ref="I3:N3"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="AC2:AE2"/>
-    <mergeCell ref="AC3:AE3"/>
-    <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="AC5:AE5"/>
-    <mergeCell ref="AC7:AE7"/>
-    <mergeCell ref="AC10:AE10"/>
-    <mergeCell ref="AC9:AE9"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="S19:V19"/>
-    <mergeCell ref="W19:Z19"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="AC8:AE8"/>
-    <mergeCell ref="AC6:AE6"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="K19:N19"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="M11:N11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -4273,87 +4709,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
-        <v>144</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
+      <c r="A1" s="83" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="87" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43" t="str">
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83" t="str">
         <f>Электродвигатель!F48</f>
         <v>Цилиндрическая 1</v>
       </c>
-      <c r="F2" s="53"/>
-      <c r="K2" s="48" t="s">
-        <v>157</v>
-      </c>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="49"/>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="49"/>
+      <c r="F2" s="95"/>
+      <c r="K2" s="92" t="s">
+        <v>153</v>
+      </c>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
       <c r="R2" s="1"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="98">
-        <f>Электродвигатель!F49</f>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="56">
+        <f>Электродвигатель!$F$49</f>
         <v>7.5398223686155026</v>
       </c>
-      <c r="F3" s="91"/>
+      <c r="F3" s="50"/>
       <c r="K3" s="7" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="L3" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="R3" s="25" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="98">
-        <f>Электродвигатель!F52</f>
+      <c r="B4" s="83"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="56">
+        <f>Электродвигатель!$F$52</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="F4" s="91" t="s">
+      <c r="F4" s="50" t="s">
         <v>105</v>
       </c>
       <c r="K4" s="11">
@@ -4378,22 +4814,22 @@
         <v>78.900000000000006</v>
       </c>
       <c r="R4" s="1">
-        <f>IF(P4&gt;$E$15,1,0)</f>
+        <f ca="1">IF(P4&gt;$E$15,1,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
       <c r="E5" s="25">
-        <f>Электродвигатель!F54</f>
+        <f>Электродвигатель!$F$54</f>
         <v>320</v>
       </c>
-      <c r="F5" s="91" t="s">
+      <c r="F5" s="50" t="s">
         <v>100</v>
       </c>
       <c r="K5" s="7">
@@ -4418,19 +4854,19 @@
         <v>74.900000000000006</v>
       </c>
       <c r="R5" s="1">
-        <f t="shared" ref="R5:R15" si="0">IF(P5&gt;$E$15,1,0)</f>
+        <f t="shared" ref="R5:R15" ca="1" si="0">IF(P5&gt;$E$15,1,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="87" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
       <c r="E6" s="25">
-        <f>Электродвигатель!F58</f>
+        <f>Электродвигатель!$F$58</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="F6" s="3"/>
@@ -4456,19 +4892,19 @@
         <v>68.900000000000006</v>
       </c>
       <c r="R6" s="1">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A7" s="61" t="s">
-        <v>151</v>
-      </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
+      <c r="A7" s="111" t="s">
+        <v>147</v>
+      </c>
+      <c r="B7" s="111"/>
+      <c r="C7" s="111"/>
+      <c r="D7" s="111"/>
       <c r="E7">
-        <f>Электродвигатель!E5</f>
+        <f>Электродвигатель!$E$5</f>
         <v>10000</v>
       </c>
       <c r="F7" t="s">
@@ -4496,19 +4932,19 @@
         <v>70.8</v>
       </c>
       <c r="R7" s="1">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A8" s="61" t="s">
-        <v>145</v>
-      </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
+      <c r="A8" s="111" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8" s="111"/>
+      <c r="C8" s="111"/>
+      <c r="D8" s="111"/>
+      <c r="E8" s="111"/>
+      <c r="F8" s="111"/>
       <c r="K8" s="7">
         <v>5</v>
       </c>
@@ -4531,20 +4967,23 @@
         <v>64.599999999999994</v>
       </c>
       <c r="R8" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
       <c r="S8" s="1"/>
+      <c r="V8" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A9" s="61" t="s">
-        <v>150</v>
-      </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="61"/>
-      <c r="D9" s="61"/>
+      <c r="A9" s="111" t="s">
+        <v>146</v>
+      </c>
+      <c r="B9" s="111"/>
+      <c r="C9" s="111"/>
+      <c r="D9" s="111"/>
       <c r="E9">
-        <f>Электродвигатель!E15</f>
+        <f>Электродвигатель!$E$15</f>
         <v>300</v>
       </c>
       <c r="F9" t="s">
@@ -4568,108 +5007,117 @@
       <c r="P9" s="1">
         <v>49.35</v>
       </c>
-      <c r="Q9" s="90">
+      <c r="Q9" s="49">
         <v>69.400000000000006</v>
       </c>
       <c r="R9" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="S9" s="96"/>
+      <c r="S9" s="54"/>
+      <c r="V9" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="43"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
+      <c r="B10" s="83"/>
+      <c r="C10" s="83"/>
+      <c r="D10" s="83"/>
       <c r="E10" s="16">
-        <f>Электродвигатель!E7</f>
+        <f>Электродвигатель!$E$7</f>
         <v>3</v>
       </c>
-      <c r="F10" s="91" t="s">
-        <v>138</v>
-      </c>
-      <c r="K10" s="100">
+      <c r="F10" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="K10" s="58">
         <v>7</v>
       </c>
-      <c r="L10" s="85">
+      <c r="L10" s="44">
         <v>49</v>
       </c>
-      <c r="M10" s="85">
+      <c r="M10" s="44">
         <v>28.5</v>
       </c>
-      <c r="N10" s="85">
+      <c r="N10" s="44">
         <v>0.315</v>
       </c>
-      <c r="O10" s="85">
+      <c r="O10" s="44">
         <v>180</v>
       </c>
-      <c r="P10" s="85">
+      <c r="P10" s="44">
         <v>37.75</v>
       </c>
-      <c r="Q10" s="86">
+      <c r="Q10" s="45">
         <v>57.3</v>
       </c>
       <c r="R10" s="1">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S10" s="96"/>
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="54"/>
+      <c r="V10" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="87" t="s">
+        <v>217</v>
+      </c>
+      <c r="B11" s="83"/>
+      <c r="C11" s="83"/>
+      <c r="D11" s="83"/>
+      <c r="E11" s="47" t="s">
+        <v>101</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="K11" s="58">
+        <v>8</v>
+      </c>
+      <c r="L11" s="44">
+        <v>49</v>
+      </c>
+      <c r="M11" s="44">
+        <v>28.5</v>
+      </c>
+      <c r="N11" s="44">
+        <v>0.4</v>
+      </c>
+      <c r="O11" s="44">
+        <v>180</v>
+      </c>
+      <c r="P11" s="45">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="Q11" s="45">
+        <v>64.2</v>
+      </c>
+      <c r="R11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="54"/>
+      <c r="V11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A12" s="87" t="s">
         <v>130</v>
       </c>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="88" t="s">
+      <c r="B12" s="83"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="K11" s="7">
-        <v>8</v>
-      </c>
-      <c r="L11" s="1">
-        <v>49</v>
-      </c>
-      <c r="M11" s="1">
-        <v>28.5</v>
-      </c>
-      <c r="N11" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="O11" s="1">
-        <v>180</v>
-      </c>
-      <c r="P11" s="16">
-        <v>36.299999999999997</v>
-      </c>
-      <c r="Q11" s="90">
-        <v>64.2</v>
-      </c>
-      <c r="R11" s="1">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S11" s="96"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A12" s="42" t="s">
+      <c r="F12" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="97" t="s">
-        <v>101</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>132</v>
       </c>
       <c r="K12" s="7">
         <v>9</v>
@@ -4686,27 +5134,27 @@
       <c r="O12" s="1">
         <v>160</v>
       </c>
-      <c r="P12" s="90">
+      <c r="P12" s="49">
         <v>32.75</v>
       </c>
-      <c r="Q12" s="90">
+      <c r="Q12" s="49">
         <v>34.4</v>
       </c>
       <c r="R12" s="1">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S12" s="96"/>
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="54"/>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A13" s="61" t="s">
-        <v>146</v>
-      </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
+      <c r="A13" s="111" t="s">
+        <v>142</v>
+      </c>
+      <c r="B13" s="111"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="111"/>
+      <c r="E13" s="111"/>
+      <c r="F13" s="111"/>
       <c r="K13" s="7">
         <v>10</v>
       </c>
@@ -4722,27 +5170,27 @@
       <c r="O13" s="1">
         <v>140</v>
       </c>
-      <c r="P13" s="90">
+      <c r="P13" s="49">
         <v>28.75</v>
       </c>
-      <c r="Q13" s="90">
+      <c r="Q13" s="49">
         <v>31.8</v>
       </c>
       <c r="R13" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="S13" s="96"/>
+      <c r="S13" s="54"/>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A14" s="61" t="s">
-        <v>149</v>
-      </c>
-      <c r="B14" s="61"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
+      <c r="A14" s="111" t="s">
+        <v>145</v>
+      </c>
+      <c r="B14" s="111"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
       <c r="E14">
-        <f>Электродвигатель!T52</f>
+        <f>Вал!$D$6</f>
         <v>38</v>
       </c>
       <c r="F14" t="s">
@@ -4763,28 +5211,28 @@
       <c r="O14" s="25">
         <v>120</v>
       </c>
-      <c r="P14" s="90">
+      <c r="P14" s="49">
         <v>24.2</v>
       </c>
-      <c r="Q14" s="90">
+      <c r="Q14" s="49">
         <v>31.9</v>
       </c>
       <c r="R14" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="S14" s="96"/>
+      <c r="S14" s="54"/>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A15" s="43" t="s">
-        <v>147</v>
-      </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
+      <c r="A15" s="83" t="s">
+        <v>143</v>
+      </c>
+      <c r="B15" s="83"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="83"/>
       <c r="E15">
-        <f>Электродвигатель!V53</f>
-        <v>32</v>
+        <f ca="1">Вал!$K$19</f>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
@@ -4804,704 +5252,817 @@
       <c r="O15" s="37">
         <v>130</v>
       </c>
-      <c r="P15" s="99">
+      <c r="P15" s="57">
         <v>26.25</v>
       </c>
-      <c r="Q15" s="99">
+      <c r="Q15" s="57">
         <v>38.1</v>
       </c>
       <c r="R15" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A16" s="43" t="s">
-        <v>148</v>
-      </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
+      <c r="A16" s="83" t="s">
+        <v>144</v>
+      </c>
+      <c r="B16" s="83"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="83"/>
       <c r="E16">
-        <f>Электродвигатель!V55</f>
+        <f ca="1">Вал!$R$18</f>
         <v>50</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
       </c>
-      <c r="Z16" s="101"/>
+      <c r="Z16" s="59"/>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="Z17" s="101"/>
+      <c r="H17" s="125" t="s">
+        <v>156</v>
+      </c>
+      <c r="I17" s="126"/>
+      <c r="J17" s="126"/>
+      <c r="K17" s="126"/>
+      <c r="L17" s="60">
+        <v>7</v>
+      </c>
+      <c r="M17" s="61"/>
+      <c r="O17" s="125" t="s">
+        <v>156</v>
+      </c>
+      <c r="P17" s="126"/>
+      <c r="Q17" s="126"/>
+      <c r="R17" s="126"/>
+      <c r="S17" s="60">
+        <v>8</v>
+      </c>
+      <c r="T17" s="61"/>
+      <c r="Z17" s="59"/>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="Z18" s="101"/>
+      <c r="H18" s="123" t="s">
+        <v>152</v>
+      </c>
+      <c r="I18" s="124"/>
+      <c r="J18" s="124"/>
+      <c r="K18" s="124"/>
+      <c r="L18" s="64">
+        <v>57</v>
+      </c>
+      <c r="M18" s="62" t="s">
+        <v>159</v>
+      </c>
+      <c r="O18" s="123" t="s">
+        <v>152</v>
+      </c>
+      <c r="P18" s="124"/>
+      <c r="Q18" s="124"/>
+      <c r="R18" s="124"/>
+      <c r="S18" s="64">
+        <v>64</v>
+      </c>
+      <c r="T18" s="62" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z18" s="59"/>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z19" s="101"/>
+      <c r="H19" s="123" t="s">
+        <v>157</v>
+      </c>
+      <c r="I19" s="124"/>
+      <c r="J19" s="124"/>
+      <c r="K19" s="124"/>
+      <c r="L19" s="63">
+        <v>20</v>
+      </c>
+      <c r="M19" s="62" t="s">
+        <v>159</v>
+      </c>
+      <c r="O19" s="123" t="s">
+        <v>157</v>
+      </c>
+      <c r="P19" s="124"/>
+      <c r="Q19" s="124"/>
+      <c r="R19" s="124"/>
+      <c r="S19" s="63">
+        <v>25.3</v>
+      </c>
+      <c r="T19" s="62" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z19" s="59"/>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>137</v>
-      </c>
-      <c r="M20" s="111" t="s">
+      <c r="H20" s="123" t="s">
+        <v>149</v>
+      </c>
+      <c r="I20" s="124"/>
+      <c r="J20" s="124"/>
+      <c r="K20" s="124"/>
+      <c r="L20" s="63">
+        <v>180</v>
+      </c>
+      <c r="M20" s="62" t="s">
+        <v>16</v>
+      </c>
+      <c r="O20" s="123" t="s">
+        <v>149</v>
+      </c>
+      <c r="P20" s="124"/>
+      <c r="Q20" s="124"/>
+      <c r="R20" s="124"/>
+      <c r="S20" s="63">
+        <v>180</v>
+      </c>
+      <c r="T20" s="62" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z20" s="59"/>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="H21" s="123" t="s">
+        <v>158</v>
+      </c>
+      <c r="I21" s="124"/>
+      <c r="J21" s="124"/>
+      <c r="K21" s="124"/>
+      <c r="L21" s="63">
+        <v>2.5</v>
+      </c>
+      <c r="M21" s="62" t="s">
+        <v>16</v>
+      </c>
+      <c r="O21" s="123" t="s">
+        <v>158</v>
+      </c>
+      <c r="P21" s="124"/>
+      <c r="Q21" s="124"/>
+      <c r="R21" s="124"/>
+      <c r="S21" s="63">
+        <v>3</v>
+      </c>
+      <c r="T21" s="62" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z21" s="59"/>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="H22" s="123" t="s">
+        <v>0</v>
+      </c>
+      <c r="I22" s="124"/>
+      <c r="J22" s="124"/>
+      <c r="K22" s="124"/>
+      <c r="L22" s="63">
+        <v>2016</v>
+      </c>
+      <c r="M22" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="O22" s="123" t="s">
+        <v>0</v>
+      </c>
+      <c r="P22" s="124"/>
+      <c r="Q22" s="124"/>
+      <c r="R22" s="124"/>
+      <c r="S22" s="63">
+        <v>2013</v>
+      </c>
+      <c r="T22" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z22" s="59"/>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="H23" s="123" t="s">
         <v>160</v>
       </c>
-      <c r="N20" s="112"/>
-      <c r="O20" s="112"/>
-      <c r="P20" s="112"/>
-      <c r="Q20" s="102">
-        <v>7</v>
-      </c>
-      <c r="R20" s="103"/>
-      <c r="T20" s="111" t="s">
+      <c r="I23" s="124"/>
+      <c r="J23" s="124"/>
+      <c r="K23" s="124"/>
+      <c r="L23" s="63">
+        <v>734</v>
+      </c>
+      <c r="M23" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="O23" s="123" t="s">
         <v>160</v>
       </c>
-      <c r="U20" s="112"/>
-      <c r="V20" s="112"/>
-      <c r="W20" s="112"/>
-      <c r="X20" s="102">
-        <v>8</v>
-      </c>
-      <c r="Y20" s="103"/>
-      <c r="Z20" s="101"/>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="M21" s="113" t="s">
-        <v>156</v>
-      </c>
-      <c r="N21" s="114"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="114"/>
-      <c r="Q21" s="115">
+      <c r="P23" s="124"/>
+      <c r="Q23" s="124"/>
+      <c r="R23" s="124"/>
+      <c r="S23" s="63">
+        <v>733</v>
+      </c>
+      <c r="T23" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z23" s="59"/>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A24" s="92" t="s">
+        <v>180</v>
+      </c>
+      <c r="B24" s="78"/>
+      <c r="C24" s="78"/>
+      <c r="D24" s="78"/>
+      <c r="E24" s="100"/>
+      <c r="H24" s="116" t="s">
+        <v>161</v>
+      </c>
+      <c r="I24" s="117"/>
+      <c r="J24" s="117"/>
+      <c r="K24" s="117"/>
+      <c r="L24" s="65">
+        <v>0</v>
+      </c>
+      <c r="M24" s="66" t="s">
+        <v>162</v>
+      </c>
+      <c r="O24" s="116" t="s">
+        <v>161</v>
+      </c>
+      <c r="P24" s="117"/>
+      <c r="Q24" s="117"/>
+      <c r="R24" s="117"/>
+      <c r="S24" s="65">
+        <v>0</v>
+      </c>
+      <c r="T24" s="66" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z24" s="59"/>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A25" s="123" t="s">
+        <v>149</v>
+      </c>
+      <c r="B25" s="124"/>
+      <c r="C25" s="124"/>
+      <c r="D25" s="1">
+        <f>L20</f>
+        <v>180</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="64"/>
+      <c r="I25" s="64"/>
+      <c r="J25" s="64"/>
+      <c r="K25" s="64"/>
+      <c r="L25" s="64"/>
+      <c r="M25" s="64"/>
+      <c r="O25" s="64"/>
+      <c r="P25" s="64"/>
+      <c r="Q25" s="64"/>
+      <c r="R25" s="64"/>
+      <c r="S25" s="64"/>
+      <c r="T25" s="64"/>
+      <c r="Z25" s="59"/>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A26" s="111" t="s">
+        <v>158</v>
+      </c>
+      <c r="B26" s="111"/>
+      <c r="C26" s="111"/>
+      <c r="D26">
+        <f>L21</f>
+        <v>2.5</v>
+      </c>
+      <c r="E26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="125" t="s">
+        <v>163</v>
+      </c>
+      <c r="I26" s="126"/>
+      <c r="J26" s="127" t="s">
+        <v>164</v>
+      </c>
+      <c r="K26" s="127"/>
+      <c r="L26" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="M26" s="128"/>
+      <c r="O26" s="125" t="s">
+        <v>163</v>
+      </c>
+      <c r="P26" s="126"/>
+      <c r="Q26" s="127" t="s">
+        <v>164</v>
+      </c>
+      <c r="R26" s="127"/>
+      <c r="S26" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="T26" s="128"/>
+      <c r="Z26" s="59"/>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A27" s="111" t="s">
+        <v>234</v>
+      </c>
+      <c r="B27" s="111"/>
+      <c r="C27" s="111"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="111"/>
+      <c r="H27" s="123" t="s">
+        <v>165</v>
+      </c>
+      <c r="I27" s="124"/>
+      <c r="J27" s="121">
+        <v>17</v>
+      </c>
+      <c r="K27" s="121"/>
+      <c r="L27" s="121">
+        <v>127</v>
+      </c>
+      <c r="M27" s="122"/>
+      <c r="O27" s="123" t="s">
+        <v>165</v>
+      </c>
+      <c r="P27" s="124"/>
+      <c r="Q27" s="121">
+        <v>14</v>
+      </c>
+      <c r="R27" s="121"/>
+      <c r="S27" s="121">
+        <v>106</v>
+      </c>
+      <c r="T27" s="122"/>
+      <c r="Z27" s="59"/>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A28" s="123" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="124"/>
+      <c r="C28" s="124"/>
+      <c r="D28" s="64">
+        <f>L22</f>
+        <v>2016</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H28" s="120" t="s">
+        <v>172</v>
+      </c>
+      <c r="I28" s="121"/>
+      <c r="J28" s="121">
+        <v>-0.3</v>
+      </c>
+      <c r="K28" s="121"/>
+      <c r="L28" s="121">
+        <v>0.3</v>
+      </c>
+      <c r="M28" s="122"/>
+      <c r="O28" s="120" t="s">
+        <v>172</v>
+      </c>
+      <c r="P28" s="121"/>
+      <c r="Q28" s="121">
+        <v>0.3</v>
+      </c>
+      <c r="R28" s="121"/>
+      <c r="S28" s="121">
+        <v>-0.3</v>
+      </c>
+      <c r="T28" s="122"/>
+      <c r="Z28" s="59"/>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A29" s="123" t="s">
+        <v>160</v>
+      </c>
+      <c r="B29" s="124"/>
+      <c r="C29" s="124"/>
+      <c r="D29" s="64">
+        <f>L23</f>
+        <v>734</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H29" s="120" t="s">
+        <v>171</v>
+      </c>
+      <c r="I29" s="121"/>
+      <c r="J29" s="121">
+        <v>49</v>
+      </c>
+      <c r="K29" s="121"/>
+      <c r="L29" s="121">
+        <v>28.5</v>
+      </c>
+      <c r="M29" s="122"/>
+      <c r="O29" s="120" t="s">
+        <v>171</v>
+      </c>
+      <c r="P29" s="121"/>
+      <c r="Q29" s="121">
+        <v>49</v>
+      </c>
+      <c r="R29" s="121"/>
+      <c r="S29" s="121">
+        <v>28.5</v>
+      </c>
+      <c r="T29" s="122"/>
+      <c r="Z29" s="59"/>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A30" s="123" t="s">
+        <v>161</v>
+      </c>
+      <c r="B30" s="124"/>
+      <c r="C30" s="124"/>
+      <c r="D30" s="64">
+        <f>L24</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H30" s="87" t="s">
+        <v>174</v>
+      </c>
+      <c r="I30" s="83"/>
+      <c r="J30" s="83" t="s">
+        <v>175</v>
+      </c>
+      <c r="K30" s="83"/>
+      <c r="L30" s="83" t="s">
+        <v>176</v>
+      </c>
+      <c r="M30" s="95"/>
+      <c r="O30" s="87" t="s">
+        <v>174</v>
+      </c>
+      <c r="P30" s="83"/>
+      <c r="Q30" s="83" t="s">
+        <v>175</v>
+      </c>
+      <c r="R30" s="83"/>
+      <c r="S30" s="83" t="s">
+        <v>176</v>
+      </c>
+      <c r="T30" s="95"/>
+      <c r="Z30" s="59"/>
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A31" s="111" t="s">
+        <v>222</v>
+      </c>
+      <c r="B31" s="111"/>
+      <c r="C31" s="111"/>
+      <c r="D31" s="111"/>
+      <c r="E31" s="111"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="83"/>
+      <c r="K31" s="83"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="Z31" s="59"/>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A32" s="111" t="s">
+        <v>225</v>
+      </c>
+      <c r="B32" s="111"/>
+      <c r="C32" s="111"/>
+      <c r="D32">
+        <f>J33</f>
+        <v>42.5</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="120" t="s">
+        <v>167</v>
+      </c>
+      <c r="I32" s="121"/>
+      <c r="J32" s="121"/>
+      <c r="K32" s="121"/>
+      <c r="L32" s="121"/>
+      <c r="M32" s="122"/>
+      <c r="O32" s="120" t="s">
+        <v>167</v>
+      </c>
+      <c r="P32" s="121"/>
+      <c r="Q32" s="121"/>
+      <c r="R32" s="121"/>
+      <c r="S32" s="121"/>
+      <c r="T32" s="122"/>
+      <c r="Z32" s="59"/>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A33" s="83" t="s">
+        <v>223</v>
+      </c>
+      <c r="B33" s="83"/>
+      <c r="C33" s="83"/>
+      <c r="D33" s="1">
+        <f>J35</f>
+        <v>37.75</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" s="123" t="s">
+        <v>166</v>
+      </c>
+      <c r="I33" s="124"/>
+      <c r="J33" s="121">
+        <v>42.5</v>
+      </c>
+      <c r="K33" s="121"/>
+      <c r="L33" s="121">
+        <v>317.5</v>
+      </c>
+      <c r="M33" s="122"/>
+      <c r="O33" s="123" t="s">
+        <v>166</v>
+      </c>
+      <c r="P33" s="124"/>
+      <c r="Q33" s="121">
+        <v>42</v>
+      </c>
+      <c r="R33" s="121"/>
+      <c r="S33" s="121">
+        <v>318</v>
+      </c>
+      <c r="T33" s="122"/>
+      <c r="Z33" s="59"/>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A34" s="83" t="s">
+        <v>224</v>
+      </c>
+      <c r="B34" s="83"/>
+      <c r="C34" s="83"/>
+      <c r="D34" s="1">
+        <f>J34</f>
+        <v>49</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" s="123" t="s">
+        <v>169</v>
+      </c>
+      <c r="I34" s="124"/>
+      <c r="J34" s="121">
+        <v>49</v>
+      </c>
+      <c r="K34" s="121"/>
+      <c r="L34" s="121">
+        <v>321</v>
+      </c>
+      <c r="M34" s="122"/>
+      <c r="O34" s="123" t="s">
+        <v>169</v>
+      </c>
+      <c r="P34" s="124"/>
+      <c r="Q34" s="121">
+        <v>49.8</v>
+      </c>
+      <c r="R34" s="121"/>
+      <c r="S34" s="121">
+        <v>322</v>
+      </c>
+      <c r="T34" s="122"/>
+      <c r="Z34" s="59"/>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A35" s="83" t="s">
+        <v>170</v>
+      </c>
+      <c r="B35" s="83"/>
+      <c r="C35" s="83"/>
+      <c r="D35" s="1">
+        <f>J36</f>
+        <v>62</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="123" t="s">
+        <v>168</v>
+      </c>
+      <c r="I35" s="124"/>
+      <c r="J35" s="121">
+        <v>37.75</v>
+      </c>
+      <c r="K35" s="121"/>
+      <c r="L35" s="121">
+        <v>309.75</v>
+      </c>
+      <c r="M35" s="122"/>
+      <c r="O35" s="123" t="s">
+        <v>168</v>
+      </c>
+      <c r="P35" s="124"/>
+      <c r="Q35" s="121">
+        <v>36.6</v>
+      </c>
+      <c r="R35" s="121"/>
+      <c r="S35" s="121">
+        <v>308.7</v>
+      </c>
+      <c r="T35" s="122"/>
+      <c r="Z35" s="59"/>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A36" s="111" t="s">
+        <v>226</v>
+      </c>
+      <c r="B36" s="111"/>
+      <c r="C36" s="111"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="111"/>
+      <c r="H36" s="116" t="s">
+        <v>170</v>
+      </c>
+      <c r="I36" s="117"/>
+      <c r="J36" s="118">
+        <v>62</v>
+      </c>
+      <c r="K36" s="118"/>
+      <c r="L36" s="118">
         <v>57</v>
       </c>
-      <c r="R21" s="104" t="s">
-        <v>163</v>
-      </c>
-      <c r="T21" s="113" t="s">
-        <v>156</v>
-      </c>
-      <c r="U21" s="114"/>
-      <c r="V21" s="114"/>
-      <c r="W21" s="114"/>
-      <c r="X21" s="115">
-        <v>64</v>
-      </c>
-      <c r="Y21" s="104" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z21" s="101"/>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="M22" s="113" t="s">
-        <v>161</v>
-      </c>
-      <c r="N22" s="114"/>
-      <c r="O22" s="114"/>
-      <c r="P22" s="114"/>
-      <c r="Q22" s="105">
-        <v>20</v>
-      </c>
-      <c r="R22" s="104" t="s">
-        <v>163</v>
-      </c>
-      <c r="T22" s="113" t="s">
-        <v>161</v>
-      </c>
-      <c r="U22" s="114"/>
-      <c r="V22" s="114"/>
-      <c r="W22" s="114"/>
-      <c r="X22" s="105">
-        <v>25.3</v>
-      </c>
-      <c r="Y22" s="104" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z22" s="101"/>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="M23" s="113" t="s">
-        <v>153</v>
-      </c>
-      <c r="N23" s="114"/>
-      <c r="O23" s="114"/>
-      <c r="P23" s="114"/>
-      <c r="Q23" s="105">
-        <v>180</v>
-      </c>
-      <c r="R23" s="104" t="s">
+      <c r="M36" s="119"/>
+      <c r="O36" s="116" t="s">
+        <v>170</v>
+      </c>
+      <c r="P36" s="117"/>
+      <c r="Q36" s="118">
+        <v>79</v>
+      </c>
+      <c r="R36" s="118"/>
+      <c r="S36" s="118">
+        <v>72</v>
+      </c>
+      <c r="T36" s="119"/>
+      <c r="Z36" s="59"/>
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A37" s="111" t="s">
+        <v>225</v>
+      </c>
+      <c r="B37" s="111"/>
+      <c r="C37" s="111"/>
+      <c r="D37">
+        <f>L33</f>
+        <v>317.5</v>
+      </c>
+      <c r="E37" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="T23" s="113" t="s">
-        <v>153</v>
-      </c>
-      <c r="U23" s="114"/>
-      <c r="V23" s="114"/>
-      <c r="W23" s="114"/>
-      <c r="X23" s="105">
-        <v>180</v>
-      </c>
-      <c r="Y23" s="104" t="s">
+      <c r="H37" s="111" t="s">
+        <v>173</v>
+      </c>
+      <c r="I37" s="111"/>
+      <c r="J37" s="111" t="b">
+        <f ca="1">J35&gt;$E$15</f>
+        <v>0</v>
+      </c>
+      <c r="K37" s="111"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="48"/>
+      <c r="Q37" s="111" t="b">
+        <f ca="1">Q35&gt;$E$15</f>
+        <v>0</v>
+      </c>
+      <c r="R37" s="111"/>
+      <c r="S37" s="48"/>
+      <c r="T37" s="48"/>
+      <c r="Z37" s="59"/>
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A38" s="83" t="s">
+        <v>223</v>
+      </c>
+      <c r="B38" s="83"/>
+      <c r="C38" s="83"/>
+      <c r="D38" s="1">
+        <f>L35</f>
+        <v>309.75</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="Z23" s="101"/>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="M24" s="113" t="s">
-        <v>162</v>
-      </c>
-      <c r="N24" s="114"/>
-      <c r="O24" s="114"/>
-      <c r="P24" s="114"/>
-      <c r="Q24" s="105">
-        <v>2.5</v>
-      </c>
-      <c r="R24" s="104" t="s">
+      <c r="Z38" s="59"/>
+    </row>
+    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A39" s="83" t="s">
+        <v>224</v>
+      </c>
+      <c r="B39" s="83"/>
+      <c r="C39" s="83"/>
+      <c r="D39" s="1">
+        <f>L34</f>
+        <v>321</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="T24" s="113" t="s">
-        <v>162</v>
-      </c>
-      <c r="U24" s="114"/>
-      <c r="V24" s="114"/>
-      <c r="W24" s="114"/>
-      <c r="X24" s="105">
-        <v>3</v>
-      </c>
-      <c r="Y24" s="104" t="s">
+      <c r="Z39" s="59"/>
+    </row>
+    <row r="40" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A40" s="83" t="s">
+        <v>170</v>
+      </c>
+      <c r="B40" s="83"/>
+      <c r="C40" s="83"/>
+      <c r="D40" s="1">
+        <f>L36</f>
+        <v>57</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="Z24" s="101"/>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="M25" s="113" t="s">
-        <v>0</v>
-      </c>
-      <c r="N25" s="114"/>
-      <c r="O25" s="114"/>
-      <c r="P25" s="114"/>
-      <c r="Q25" s="105">
-        <v>2016</v>
-      </c>
-      <c r="R25" s="104" t="s">
-        <v>166</v>
-      </c>
-      <c r="T25" s="113" t="s">
-        <v>0</v>
-      </c>
-      <c r="U25" s="114"/>
-      <c r="V25" s="114"/>
-      <c r="W25" s="114"/>
-      <c r="X25" s="105">
-        <v>2013</v>
-      </c>
-      <c r="Y25" s="104" t="s">
-        <v>166</v>
-      </c>
-      <c r="Z25" s="101"/>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="M26" s="113" t="s">
-        <v>164</v>
-      </c>
-      <c r="N26" s="114"/>
-      <c r="O26" s="114"/>
-      <c r="P26" s="114"/>
-      <c r="Q26" s="105">
-        <v>734</v>
-      </c>
-      <c r="R26" s="104" t="s">
-        <v>166</v>
-      </c>
-      <c r="T26" s="113" t="s">
-        <v>164</v>
-      </c>
-      <c r="U26" s="114"/>
-      <c r="V26" s="114"/>
-      <c r="W26" s="114"/>
-      <c r="X26" s="105">
-        <v>733</v>
-      </c>
-      <c r="Y26" s="104" t="s">
-        <v>166</v>
-      </c>
-      <c r="Z26" s="101"/>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="M27" s="116" t="s">
-        <v>165</v>
-      </c>
-      <c r="N27" s="117"/>
-      <c r="O27" s="117"/>
-      <c r="P27" s="117"/>
-      <c r="Q27" s="120">
-        <v>0</v>
-      </c>
-      <c r="R27" s="121" t="s">
-        <v>166</v>
-      </c>
-      <c r="T27" s="116" t="s">
-        <v>165</v>
-      </c>
-      <c r="U27" s="117"/>
-      <c r="V27" s="117"/>
-      <c r="W27" s="117"/>
-      <c r="X27" s="120">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="121" t="s">
-        <v>166</v>
-      </c>
-      <c r="Z27" s="101"/>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="M28" s="115"/>
-      <c r="N28" s="115"/>
-      <c r="O28" s="115"/>
-      <c r="P28" s="115"/>
-      <c r="Q28" s="115"/>
-      <c r="R28" s="115"/>
-      <c r="T28" s="115"/>
-      <c r="U28" s="115"/>
-      <c r="V28" s="115"/>
-      <c r="W28" s="115"/>
-      <c r="X28" s="115"/>
-      <c r="Y28" s="115"/>
-      <c r="Z28" s="101"/>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="M29" s="111" t="s">
-        <v>167</v>
-      </c>
-      <c r="N29" s="112"/>
-      <c r="O29" s="118" t="s">
-        <v>168</v>
-      </c>
-      <c r="P29" s="118"/>
-      <c r="Q29" s="118" t="s">
-        <v>126</v>
-      </c>
-      <c r="R29" s="119"/>
-      <c r="T29" s="111" t="s">
-        <v>167</v>
-      </c>
-      <c r="U29" s="112"/>
-      <c r="V29" s="118" t="s">
-        <v>168</v>
-      </c>
-      <c r="W29" s="118"/>
-      <c r="X29" s="118" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y29" s="119"/>
-      <c r="Z29" s="101"/>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="M30" s="113" t="s">
-        <v>169</v>
-      </c>
-      <c r="N30" s="114"/>
-      <c r="O30" s="106">
-        <v>17</v>
-      </c>
-      <c r="P30" s="106"/>
-      <c r="Q30" s="106">
-        <v>127</v>
-      </c>
-      <c r="R30" s="107"/>
-      <c r="T30" s="113" t="s">
-        <v>169</v>
-      </c>
-      <c r="U30" s="114"/>
-      <c r="V30" s="106">
-        <v>14</v>
-      </c>
-      <c r="W30" s="106"/>
-      <c r="X30" s="106">
-        <v>106</v>
-      </c>
-      <c r="Y30" s="107"/>
-      <c r="Z30" s="101"/>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="M31" s="108" t="s">
-        <v>176</v>
-      </c>
-      <c r="N31" s="106"/>
-      <c r="O31" s="106">
-        <v>-0.3</v>
-      </c>
-      <c r="P31" s="106"/>
-      <c r="Q31" s="106">
-        <v>0.3</v>
-      </c>
-      <c r="R31" s="107"/>
-      <c r="T31" s="108" t="s">
-        <v>176</v>
-      </c>
-      <c r="U31" s="106"/>
-      <c r="V31" s="106">
-        <v>0.3</v>
-      </c>
-      <c r="W31" s="106"/>
-      <c r="X31" s="106">
-        <v>-0.3</v>
-      </c>
-      <c r="Y31" s="107"/>
-      <c r="Z31" s="101"/>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="M32" s="108" t="s">
-        <v>175</v>
-      </c>
-      <c r="N32" s="106"/>
-      <c r="O32" s="106">
-        <v>49</v>
-      </c>
-      <c r="P32" s="106"/>
-      <c r="Q32" s="106">
-        <v>28.5</v>
-      </c>
-      <c r="R32" s="107"/>
-      <c r="T32" s="108" t="s">
-        <v>175</v>
-      </c>
-      <c r="U32" s="106"/>
-      <c r="V32" s="106">
-        <v>49</v>
-      </c>
-      <c r="W32" s="106"/>
-      <c r="X32" s="106">
-        <v>28.5</v>
-      </c>
-      <c r="Y32" s="107"/>
-      <c r="Z32" s="101"/>
-    </row>
-    <row r="33" spans="11:26" x14ac:dyDescent="0.3">
-      <c r="M33" s="46" t="s">
-        <v>179</v>
-      </c>
-      <c r="N33" s="47"/>
-      <c r="O33" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="P33" s="47"/>
-      <c r="Q33" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="R33" s="54"/>
-      <c r="T33" s="46" t="s">
-        <v>179</v>
-      </c>
-      <c r="U33" s="47"/>
-      <c r="V33" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="W33" s="47"/>
-      <c r="X33" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y33" s="54"/>
-      <c r="Z33" s="101"/>
-    </row>
-    <row r="34" spans="11:26" x14ac:dyDescent="0.3">
-      <c r="L34" s="101"/>
-      <c r="M34" s="108" t="s">
-        <v>171</v>
-      </c>
-      <c r="N34" s="106"/>
-      <c r="O34" s="106"/>
-      <c r="P34" s="106"/>
-      <c r="Q34" s="106"/>
-      <c r="R34" s="107"/>
-      <c r="T34" s="108" t="s">
-        <v>171</v>
-      </c>
-      <c r="U34" s="106"/>
-      <c r="V34" s="106"/>
-      <c r="W34" s="106"/>
-      <c r="X34" s="106"/>
-      <c r="Y34" s="107"/>
-      <c r="Z34" s="101"/>
-    </row>
-    <row r="35" spans="11:26" x14ac:dyDescent="0.3">
-      <c r="M35" s="113" t="s">
-        <v>170</v>
-      </c>
-      <c r="N35" s="114"/>
-      <c r="O35" s="106">
-        <v>42.5</v>
-      </c>
-      <c r="P35" s="106"/>
-      <c r="Q35" s="106">
-        <v>317.5</v>
-      </c>
-      <c r="R35" s="107"/>
-      <c r="T35" s="113" t="s">
-        <v>170</v>
-      </c>
-      <c r="U35" s="114"/>
-      <c r="V35" s="106">
-        <v>42</v>
-      </c>
-      <c r="W35" s="106"/>
-      <c r="X35" s="106">
-        <v>318</v>
-      </c>
-      <c r="Y35" s="107"/>
-      <c r="Z35" s="101"/>
-    </row>
-    <row r="36" spans="11:26" x14ac:dyDescent="0.3">
-      <c r="M36" s="113" t="s">
-        <v>173</v>
-      </c>
-      <c r="N36" s="114"/>
-      <c r="O36" s="106">
-        <v>49</v>
-      </c>
-      <c r="P36" s="106"/>
-      <c r="Q36" s="106">
-        <v>321</v>
-      </c>
-      <c r="R36" s="107"/>
-      <c r="T36" s="113" t="s">
-        <v>173</v>
-      </c>
-      <c r="U36" s="114"/>
-      <c r="V36" s="106">
-        <v>49.8</v>
-      </c>
-      <c r="W36" s="106"/>
-      <c r="X36" s="106">
-        <v>322</v>
-      </c>
-      <c r="Y36" s="107"/>
-      <c r="Z36" s="101"/>
-    </row>
-    <row r="37" spans="11:26" x14ac:dyDescent="0.3">
-      <c r="M37" s="113" t="s">
-        <v>172</v>
-      </c>
-      <c r="N37" s="114"/>
-      <c r="O37" s="106">
-        <v>37.75</v>
-      </c>
-      <c r="P37" s="106"/>
-      <c r="Q37" s="106">
-        <v>309.75</v>
-      </c>
-      <c r="R37" s="107"/>
-      <c r="T37" s="113" t="s">
-        <v>172</v>
-      </c>
-      <c r="U37" s="114"/>
-      <c r="V37" s="106">
-        <v>36.6</v>
-      </c>
-      <c r="W37" s="106"/>
-      <c r="X37" s="106">
-        <v>308.7</v>
-      </c>
-      <c r="Y37" s="107"/>
-      <c r="Z37" s="101"/>
-    </row>
-    <row r="38" spans="11:26" x14ac:dyDescent="0.3">
-      <c r="M38" s="116" t="s">
-        <v>174</v>
-      </c>
-      <c r="N38" s="117"/>
-      <c r="O38" s="109">
-        <v>62</v>
-      </c>
-      <c r="P38" s="109"/>
-      <c r="Q38" s="109">
-        <v>57</v>
-      </c>
-      <c r="R38" s="110"/>
-      <c r="T38" s="116" t="s">
-        <v>174</v>
-      </c>
-      <c r="U38" s="117"/>
-      <c r="V38" s="109">
-        <v>79</v>
-      </c>
-      <c r="W38" s="109"/>
-      <c r="X38" s="109">
-        <v>72</v>
-      </c>
-      <c r="Y38" s="110"/>
-      <c r="Z38" s="101"/>
-    </row>
-    <row r="39" spans="11:26" x14ac:dyDescent="0.3">
-      <c r="Z39" s="101"/>
-    </row>
-    <row r="40" spans="11:26" x14ac:dyDescent="0.3">
-      <c r="K40" s="89"/>
-      <c r="L40" s="89"/>
-      <c r="M40" s="61" t="s">
-        <v>178</v>
-      </c>
-      <c r="N40" s="61"/>
-      <c r="O40" s="61" t="b">
-        <f>O37&gt;$E$15</f>
-        <v>1</v>
-      </c>
-      <c r="P40" s="61"/>
-      <c r="Q40" s="61" t="b">
-        <f>Q37&gt;$E$16</f>
-        <v>1</v>
-      </c>
-      <c r="R40" s="61"/>
-      <c r="V40" s="61" t="b">
-        <f>V37&gt;$E$15</f>
-        <v>1</v>
-      </c>
-      <c r="W40" s="61"/>
-      <c r="X40" s="61" t="b">
-        <f>X37&gt;$E$16</f>
-        <v>1</v>
-      </c>
-      <c r="Y40" s="61"/>
-      <c r="Z40" s="101"/>
-    </row>
-    <row r="41" spans="11:26" x14ac:dyDescent="0.3">
-      <c r="Z41" s="101"/>
-    </row>
-    <row r="42" spans="11:26" x14ac:dyDescent="0.3">
-      <c r="Z42" s="101"/>
-    </row>
-    <row r="43" spans="11:26" x14ac:dyDescent="0.3">
-      <c r="Z43" s="101"/>
-    </row>
-    <row r="44" spans="11:26" x14ac:dyDescent="0.3">
-      <c r="Z44" s="101"/>
-    </row>
-    <row r="45" spans="11:26" x14ac:dyDescent="0.3">
-      <c r="Z45" s="101"/>
-    </row>
-    <row r="46" spans="11:26" x14ac:dyDescent="0.3">
-      <c r="Z46" s="101"/>
-    </row>
-    <row r="47" spans="11:26" x14ac:dyDescent="0.3">
-      <c r="Z47" s="101"/>
-    </row>
-    <row r="48" spans="11:26" x14ac:dyDescent="0.3">
-      <c r="Z48" s="101"/>
+      <c r="Z40" s="59"/>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="Z41" s="59"/>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="Z42" s="59"/>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="Z43" s="59"/>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="Z44" s="59"/>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="Z45" s="59"/>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="Z46" s="59"/>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="Z47" s="59"/>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="Z48" s="59"/>
     </row>
     <row r="49" spans="26:26" x14ac:dyDescent="0.3">
-      <c r="Z49" s="101"/>
+      <c r="Z49" s="59"/>
     </row>
     <row r="50" spans="26:26" x14ac:dyDescent="0.3">
-      <c r="Z50" s="101"/>
+      <c r="Z50" s="59"/>
     </row>
     <row r="51" spans="26:26" x14ac:dyDescent="0.3">
-      <c r="Z51" s="101"/>
+      <c r="Z51" s="59"/>
     </row>
     <row r="52" spans="26:26" x14ac:dyDescent="0.3">
-      <c r="Z52" s="101"/>
+      <c r="Z52" s="59"/>
     </row>
     <row r="53" spans="26:26" x14ac:dyDescent="0.3">
-      <c r="Z53" s="101"/>
+      <c r="Z53" s="59"/>
     </row>
     <row r="54" spans="26:26" x14ac:dyDescent="0.3">
-      <c r="Z54" s="101"/>
+      <c r="Z54" s="59"/>
     </row>
     <row r="55" spans="26:26" x14ac:dyDescent="0.3">
-      <c r="Z55" s="101"/>
+      <c r="Z55" s="59"/>
     </row>
     <row r="56" spans="26:26" x14ac:dyDescent="0.3">
-      <c r="Z56" s="101"/>
+      <c r="Z56" s="59"/>
     </row>
     <row r="57" spans="26:26" x14ac:dyDescent="0.3">
-      <c r="Z57" s="101"/>
+      <c r="Z57" s="59"/>
     </row>
   </sheetData>
-  <mergeCells count="95">
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="T38:U38"/>
-    <mergeCell ref="V38:W38"/>
-    <mergeCell ref="X38:Y38"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="V40:W40"/>
-    <mergeCell ref="X40:Y40"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="V36:W36"/>
-    <mergeCell ref="X36:Y36"/>
-    <mergeCell ref="T37:U37"/>
-    <mergeCell ref="V37:W37"/>
-    <mergeCell ref="X37:Y37"/>
-    <mergeCell ref="T33:U33"/>
-    <mergeCell ref="V33:W33"/>
-    <mergeCell ref="X33:Y33"/>
-    <mergeCell ref="T34:Y34"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="V35:W35"/>
-    <mergeCell ref="X35:Y35"/>
-    <mergeCell ref="T31:U31"/>
-    <mergeCell ref="V31:W31"/>
-    <mergeCell ref="X31:Y31"/>
-    <mergeCell ref="T32:U32"/>
-    <mergeCell ref="V32:W32"/>
-    <mergeCell ref="X32:Y32"/>
-    <mergeCell ref="T26:W26"/>
-    <mergeCell ref="T27:W27"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="V29:W29"/>
-    <mergeCell ref="X29:Y29"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="V30:W30"/>
-    <mergeCell ref="X30:Y30"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="T20:W20"/>
-    <mergeCell ref="T21:W21"/>
-    <mergeCell ref="T22:W22"/>
-    <mergeCell ref="T23:W23"/>
-    <mergeCell ref="T24:W24"/>
-    <mergeCell ref="T25:W25"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="M34:R34"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="O37:P37"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="M22:P22"/>
-    <mergeCell ref="M23:P23"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="M25:P25"/>
-    <mergeCell ref="M26:P26"/>
-    <mergeCell ref="M27:P27"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="M20:P20"/>
-    <mergeCell ref="M21:P21"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
+  <mergeCells count="111">
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="J27:K27"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A13:F13"/>
@@ -5516,6 +6077,90 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="K2:Q2"/>
+    <mergeCell ref="H17:K17"/>
+    <mergeCell ref="H18:K18"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="H19:K19"/>
+    <mergeCell ref="H20:K20"/>
+    <mergeCell ref="H21:K21"/>
+    <mergeCell ref="H22:K22"/>
+    <mergeCell ref="O22:R22"/>
+    <mergeCell ref="O17:R17"/>
+    <mergeCell ref="O18:R18"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="O20:R20"/>
+    <mergeCell ref="O21:R21"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="H23:K23"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="S27:T27"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="O23:R23"/>
+    <mergeCell ref="O24:R24"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="S28:T28"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="S29:T29"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="S30:T30"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="H24:K24"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="O32:T32"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="S33:T33"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="S34:T34"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="S35:T35"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="S36:T36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A37:C37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5523,66 +6168,2531 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A416109-A6F9-42CB-B875-F300C0970630}">
-  <dimension ref="A1"/>
+  <dimension ref="A2:X29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="27" width="6.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A2" s="111" t="s">
+        <v>179</v>
+      </c>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="H2" s="111" t="s">
+        <v>192</v>
+      </c>
+      <c r="I2" s="111"/>
+      <c r="J2" s="111"/>
+      <c r="K2" s="111"/>
+      <c r="L2" s="111"/>
+      <c r="O2" s="111" t="s">
+        <v>191</v>
+      </c>
+      <c r="P2" s="111"/>
+      <c r="Q2" s="111"/>
+      <c r="R2" s="111"/>
+      <c r="S2" s="111"/>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A3" s="111" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" s="111"/>
+      <c r="D3" s="67">
+        <f ca="1">Электродвигатель!$P$53</f>
+        <v>45.959055069271365</v>
+      </c>
+      <c r="E3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H3" s="83" t="s">
+        <v>178</v>
+      </c>
+      <c r="I3" s="83"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="69">
+        <f ca="1">D3</f>
+        <v>45.959055069271365</v>
+      </c>
+      <c r="L3" t="s">
+        <v>100</v>
+      </c>
+      <c r="O3" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q3" s="16"/>
+      <c r="R3">
+        <f ca="1">Электродвигатель!P55</f>
+        <v>329.82890125747264</v>
+      </c>
+      <c r="S3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A4" s="111" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="111"/>
+      <c r="D4" s="68">
+        <f>Электродвигатель!$N$52</f>
+        <v>1440</v>
+      </c>
+      <c r="E4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" s="83" t="s">
+        <v>70</v>
+      </c>
+      <c r="I4" s="83"/>
+      <c r="J4" s="83"/>
+      <c r="K4" s="70">
+        <f>D4</f>
+        <v>1440</v>
+      </c>
+      <c r="L4" t="s">
+        <v>105</v>
+      </c>
+      <c r="O4" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="67">
+        <f>Электродвигатель!N55</f>
+        <v>190.98593171027443</v>
+      </c>
+      <c r="S4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="H5" s="111" t="s">
+        <v>182</v>
+      </c>
+      <c r="I5" s="111"/>
+      <c r="J5" s="111"/>
+      <c r="K5" s="111"/>
+      <c r="L5" s="111"/>
+      <c r="O5" s="111" t="s">
+        <v>126</v>
+      </c>
+      <c r="P5" s="111"/>
+      <c r="Q5" s="111"/>
+      <c r="R5" s="111"/>
+      <c r="S5" s="111"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A6" s="111" t="s">
+        <v>120</v>
+      </c>
+      <c r="B6" s="111"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="72">
+        <f>Электродвигатель!$F$61</f>
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="111" t="s">
+        <v>181</v>
+      </c>
+      <c r="I6" s="111"/>
+      <c r="J6" s="111"/>
+      <c r="K6">
+        <f>Передача!D33</f>
+        <v>37.75</v>
+      </c>
+      <c r="L6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O6" s="111" t="s">
+        <v>181</v>
+      </c>
+      <c r="P6" s="111"/>
+      <c r="Q6" s="111"/>
+      <c r="R6">
+        <f>Передача!D38</f>
+        <v>309.75</v>
+      </c>
+      <c r="S6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A7" s="129" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" s="129"/>
+      <c r="C7" s="129"/>
+      <c r="D7" s="52">
+        <v>0.8</v>
+      </c>
+      <c r="H7" s="111" t="s">
+        <v>190</v>
+      </c>
+      <c r="I7" s="111"/>
+      <c r="J7" s="111"/>
+      <c r="K7">
+        <f>Передача!D34</f>
+        <v>49</v>
+      </c>
+      <c r="L7" t="s">
+        <v>16</v>
+      </c>
+      <c r="O7" s="111" t="s">
+        <v>190</v>
+      </c>
+      <c r="P7" s="111"/>
+      <c r="Q7" s="111"/>
+      <c r="R7">
+        <f>Передача!D39</f>
+        <v>321</v>
+      </c>
+      <c r="S7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A8" s="111" t="s">
+        <v>201</v>
+      </c>
+      <c r="B8" s="111"/>
+      <c r="C8" s="111"/>
+      <c r="D8" s="77">
+        <v>1.2</v>
+      </c>
+      <c r="H8" s="111" t="s">
+        <v>170</v>
+      </c>
+      <c r="I8" s="111"/>
+      <c r="J8" s="111"/>
+      <c r="K8">
+        <f>Передача!D35</f>
+        <v>62</v>
+      </c>
+      <c r="L8" t="s">
+        <v>16</v>
+      </c>
+      <c r="O8" s="111" t="s">
+        <v>170</v>
+      </c>
+      <c r="P8" s="111"/>
+      <c r="Q8" s="111"/>
+      <c r="R8">
+        <f>Передача!D40</f>
+        <v>57</v>
+      </c>
+      <c r="S8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="H9" s="111" t="s">
+        <v>193</v>
+      </c>
+      <c r="I9" s="111"/>
+      <c r="J9" s="111"/>
+      <c r="K9" s="111"/>
+      <c r="L9" s="111"/>
+      <c r="O9" s="111" t="s">
+        <v>193</v>
+      </c>
+      <c r="P9" s="111"/>
+      <c r="Q9" s="111"/>
+      <c r="R9" s="111"/>
+      <c r="S9" s="111"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="H10" s="111" t="s">
+        <v>189</v>
+      </c>
+      <c r="I10" s="111"/>
+      <c r="J10" s="111"/>
+      <c r="K10">
+        <v>7.5</v>
+      </c>
+      <c r="L10" s="71" t="s">
+        <v>197</v>
+      </c>
+      <c r="O10" s="111" t="s">
+        <v>189</v>
+      </c>
+      <c r="P10" s="111"/>
+      <c r="R10">
+        <v>5.4</v>
+      </c>
+      <c r="S10" s="71" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="H11" s="111" t="s">
+        <v>202</v>
+      </c>
+      <c r="I11" s="111"/>
+      <c r="J11" s="111"/>
+      <c r="K11">
+        <f ca="1">K10*(K3)^(1/3)</f>
+        <v>26.864883424091097</v>
+      </c>
+      <c r="L11" t="s">
+        <v>16</v>
+      </c>
+      <c r="O11" s="111" t="s">
+        <v>202</v>
+      </c>
+      <c r="P11" s="111"/>
+      <c r="Q11" s="111"/>
+      <c r="R11">
+        <f ca="1">R10*(R3)^(1/3)</f>
+        <v>37.309835064996221</v>
+      </c>
+      <c r="S11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="H12" s="111" t="s">
+        <v>206</v>
+      </c>
+      <c r="I12" s="111"/>
+      <c r="J12" s="111"/>
+      <c r="K12">
+        <f ca="1">MIN(MAX(K11,D6/D8),D6/D7)</f>
+        <v>31.666666666666668</v>
+      </c>
+      <c r="O12" s="111" t="s">
+        <v>194</v>
+      </c>
+      <c r="P12" s="111"/>
+      <c r="Q12" s="111"/>
+      <c r="R12" s="72">
+        <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;R11)</f>
+        <v>38</v>
+      </c>
+      <c r="S12" t="s">
+        <v>16</v>
+      </c>
+      <c r="T12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="H13" s="111" t="s">
+        <v>194</v>
+      </c>
+      <c r="I13" s="111"/>
+      <c r="J13" s="111"/>
+      <c r="K13" s="72">
+        <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;K12)</f>
+        <v>32</v>
+      </c>
+      <c r="L13" t="s">
+        <v>16</v>
+      </c>
+      <c r="M13" t="s">
+        <v>204</v>
+      </c>
+      <c r="O13" s="111" t="s">
+        <v>203</v>
+      </c>
+      <c r="P13" s="111"/>
+      <c r="Q13" s="111"/>
+      <c r="R13">
+        <f ca="1">_xlfn.MINIFS($28:$28,$26:$26,"&gt;="&amp;R12)</f>
+        <v>3.5</v>
+      </c>
+      <c r="S13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="H14" s="111" t="s">
+        <v>203</v>
+      </c>
+      <c r="I14" s="111"/>
+      <c r="J14" s="111"/>
+      <c r="K14">
+        <f ca="1">_xlfn.MINIFS($28:$28,$26:$26,"&gt;="&amp;K13)</f>
+        <v>3.5</v>
+      </c>
+      <c r="L14" t="s">
+        <v>16</v>
+      </c>
+      <c r="O14" s="111" t="s">
+        <v>199</v>
+      </c>
+      <c r="P14" s="111"/>
+      <c r="Q14" s="111"/>
+      <c r="R14">
+        <f ca="1">R12+2*R13</f>
+        <v>45</v>
+      </c>
+      <c r="S14" t="s">
+        <v>16</v>
+      </c>
+      <c r="X14" s="48"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="H15" s="111" t="s">
+        <v>199</v>
+      </c>
+      <c r="I15" s="111"/>
+      <c r="J15" s="111"/>
+      <c r="K15">
+        <f ca="1">K13+2*K14</f>
+        <v>39</v>
+      </c>
+      <c r="L15" t="s">
+        <v>16</v>
+      </c>
+      <c r="O15" s="111" t="s">
+        <v>195</v>
+      </c>
+      <c r="P15" s="111"/>
+      <c r="Q15" s="111"/>
+      <c r="R15" s="72">
+        <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;R14)</f>
+        <v>45</v>
+      </c>
+      <c r="S15" t="s">
+        <v>16</v>
+      </c>
+      <c r="T15" t="s">
+        <v>204</v>
+      </c>
+      <c r="X15" s="48"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="H16" s="111" t="s">
+        <v>195</v>
+      </c>
+      <c r="I16" s="111"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="72">
+        <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;K15)</f>
+        <v>40</v>
+      </c>
+      <c r="L16" t="s">
+        <v>16</v>
+      </c>
+      <c r="M16" t="s">
+        <v>204</v>
+      </c>
+      <c r="O16" s="111" t="s">
+        <v>203</v>
+      </c>
+      <c r="P16" s="111"/>
+      <c r="Q16" s="111"/>
+      <c r="R16">
+        <f ca="1">_xlfn.MINIFS($29:$29,$26:$26,"&gt;="&amp;R12)</f>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="X16" s="48"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="H17" s="111" t="s">
+        <v>203</v>
+      </c>
+      <c r="I17" s="111"/>
+      <c r="J17" s="111"/>
+      <c r="K17">
+        <f ca="1">_xlfn.MINIFS($29:$29,$26:$26,"&gt;="&amp;K13)</f>
+        <v>2</v>
+      </c>
+      <c r="O17" s="111" t="s">
+        <v>200</v>
+      </c>
+      <c r="P17" s="111"/>
+      <c r="Q17" s="111"/>
+      <c r="R17">
+        <f ca="1">R15+2*R16</f>
+        <v>49.6</v>
+      </c>
+      <c r="S17" t="s">
+        <v>16</v>
+      </c>
+      <c r="X17" s="48"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="H18" s="111" t="s">
+        <v>200</v>
+      </c>
+      <c r="I18" s="111"/>
+      <c r="J18" s="111"/>
+      <c r="K18">
+        <f ca="1">K16+2*K17</f>
+        <v>44</v>
+      </c>
+      <c r="L18" t="s">
+        <v>16</v>
+      </c>
+      <c r="O18" s="111" t="s">
+        <v>196</v>
+      </c>
+      <c r="P18" s="111"/>
+      <c r="Q18" s="111"/>
+      <c r="R18" s="72">
+        <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;R17)</f>
+        <v>50</v>
+      </c>
+      <c r="S18" t="s">
+        <v>16</v>
+      </c>
+      <c r="T18" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="H19" s="111" t="s">
+        <v>196</v>
+      </c>
+      <c r="I19" s="111"/>
+      <c r="J19" s="111"/>
+      <c r="K19" s="72">
+        <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;K18)</f>
+        <v>45</v>
+      </c>
+      <c r="L19" t="s">
+        <v>16</v>
+      </c>
+      <c r="M19" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A26" s="111" t="s">
+        <v>187</v>
+      </c>
+      <c r="B26" s="111"/>
+      <c r="C26">
+        <v>17</v>
+      </c>
+      <c r="D26">
+        <v>24</v>
+      </c>
+      <c r="E26">
+        <v>32</v>
+      </c>
+      <c r="F26">
+        <v>40</v>
+      </c>
+      <c r="G26">
+        <v>45</v>
+      </c>
+      <c r="H26">
+        <v>52</v>
+      </c>
+      <c r="I26">
+        <v>60</v>
+      </c>
+      <c r="J26">
+        <v>67</v>
+      </c>
+      <c r="K26">
+        <v>80</v>
+      </c>
+      <c r="L26">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A27" s="111" t="s">
+        <v>188</v>
+      </c>
+      <c r="B27" s="111"/>
+      <c r="C27">
+        <v>22</v>
+      </c>
+      <c r="D27">
+        <v>30</v>
+      </c>
+      <c r="E27">
+        <v>38</v>
+      </c>
+      <c r="F27">
+        <v>44</v>
+      </c>
+      <c r="G27">
+        <v>50</v>
+      </c>
+      <c r="H27">
+        <v>58</v>
+      </c>
+      <c r="I27">
+        <v>65</v>
+      </c>
+      <c r="J27">
+        <v>75</v>
+      </c>
+      <c r="K27">
+        <v>85</v>
+      </c>
+      <c r="L27">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A28" s="111" t="s">
+        <v>185</v>
+      </c>
+      <c r="B28" s="111"/>
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28">
+        <v>3.5</v>
+      </c>
+      <c r="E28">
+        <v>3.5</v>
+      </c>
+      <c r="F28">
+        <v>3.5</v>
+      </c>
+      <c r="G28">
+        <v>4</v>
+      </c>
+      <c r="H28">
+        <v>4.5</v>
+      </c>
+      <c r="I28">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J28">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="K28">
+        <v>5.6</v>
+      </c>
+      <c r="L28">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A29" s="111" t="s">
+        <v>186</v>
+      </c>
+      <c r="B29" s="111"/>
+      <c r="C29">
+        <v>1.5</v>
+      </c>
+      <c r="D29">
+        <v>1.8</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G29">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="H29">
+        <v>2.5</v>
+      </c>
+      <c r="I29">
+        <v>2.7</v>
+      </c>
+      <c r="J29">
+        <v>2.7</v>
+      </c>
+      <c r="K29">
+        <v>2.7</v>
+      </c>
+      <c r="L29">
+        <v>2.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="43">
+    <mergeCell ref="O12:Q12"/>
+    <mergeCell ref="O13:Q13"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="O9:S9"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="O8:Q8"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="H9:L9"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="O11:Q11"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B080B891-BABE-48BC-B741-A9DC893B6424}">
-  <dimension ref="B4:G6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7BF09D0-EAD8-49BE-BC1A-C3CACFF128CD}">
+  <dimension ref="A2:A4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="17" width="6.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="1"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="61" t="s">
-        <v>129</v>
-      </c>
-      <c r="E4" s="61"/>
-      <c r="F4" s="43" t="s">
-        <v>125</v>
-      </c>
-      <c r="G4" s="43"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="75" t="s">
-        <v>124</v>
-      </c>
-      <c r="C5" s="75"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="75" t="s">
-        <v>126</v>
-      </c>
-      <c r="C6" s="75"/>
-      <c r="D6" s="43" t="s">
-        <v>127</v>
-      </c>
-      <c r="E6" s="43"/>
-      <c r="F6" s="58" t="s">
-        <v>128</v>
-      </c>
-      <c r="G6" s="58"/>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>238</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B5F8DC-2803-4E90-824A-7553AC4D2CA2}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="23" width="6.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="83" t="s">
+        <v>234</v>
+      </c>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="124" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="64">
+        <f>Передача!$D$28</f>
+        <v>2016</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="124" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" s="124"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="64">
+        <f>Передача!$D$29</f>
+        <v>734</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="124" t="s">
+        <v>161</v>
+      </c>
+      <c r="B5" s="124"/>
+      <c r="C5" s="124"/>
+      <c r="D5" s="64">
+        <f>Передача!$D$30</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC1D7275-A232-429A-A734-4E325D043F64}">
+  <dimension ref="A1:AA32"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="29" width="6.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A1" s="111" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="111"/>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A2" s="83" t="s">
+        <v>146</v>
+      </c>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="1">
+        <f>Передача!$E$9</f>
+        <v>300</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A3" s="83" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="16">
+        <f>Передача!$E$10</f>
+        <v>3</v>
+      </c>
+      <c r="F3" s="54" t="s">
+        <v>137</v>
+      </c>
+      <c r="J3" s="83" t="s">
+        <v>234</v>
+      </c>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="83"/>
+      <c r="N3" s="83"/>
+      <c r="T3" s="111" t="s">
+        <v>163</v>
+      </c>
+      <c r="U3" s="111"/>
+      <c r="V3" s="111"/>
+      <c r="W3" s="111"/>
+      <c r="X3" s="111" t="s">
+        <v>193</v>
+      </c>
+      <c r="Y3" s="111"/>
+      <c r="Z3" s="111" t="s">
+        <v>182</v>
+      </c>
+      <c r="AA3" s="111"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A4" s="83" t="s">
+        <v>217</v>
+      </c>
+      <c r="B4" s="83"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="47" t="str">
+        <f>Передача!$E$11</f>
+        <v>?</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="J4" s="124" t="s">
+        <v>0</v>
+      </c>
+      <c r="K4" s="124"/>
+      <c r="L4" s="124"/>
+      <c r="M4" s="64">
+        <f>Передача!$D$28</f>
+        <v>2016</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="T4" s="111" t="s">
+        <v>264</v>
+      </c>
+      <c r="U4" s="111"/>
+      <c r="V4" s="111"/>
+      <c r="W4" s="111"/>
+      <c r="X4" s="111">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="111"/>
+      <c r="Z4" s="111">
+        <f ca="1">M7</f>
+        <v>50</v>
+      </c>
+      <c r="AA4" s="111"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A5" s="110" t="s">
+        <v>219</v>
+      </c>
+      <c r="B5" s="110"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="76" t="s">
+        <v>218</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="J5" s="124" t="s">
+        <v>160</v>
+      </c>
+      <c r="K5" s="124"/>
+      <c r="L5" s="124"/>
+      <c r="M5" s="64">
+        <f>Передача!$D$29</f>
+        <v>734</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="T5" s="111" t="s">
+        <v>266</v>
+      </c>
+      <c r="U5" s="111"/>
+      <c r="V5" s="111"/>
+      <c r="W5" s="111"/>
+      <c r="X5" s="111">
+        <f ca="1">M7</f>
+        <v>50</v>
+      </c>
+      <c r="Y5" s="111"/>
+      <c r="Z5" s="111">
+        <f ca="1">E18</f>
+        <v>60</v>
+      </c>
+      <c r="AA5" s="111"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A6" s="111" t="s">
+        <v>158</v>
+      </c>
+      <c r="B6" s="111"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
+      <c r="E6">
+        <f>Передача!$D$26</f>
+        <v>2.5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="124" t="s">
+        <v>161</v>
+      </c>
+      <c r="K6" s="124"/>
+      <c r="L6" s="124"/>
+      <c r="M6" s="64">
+        <f>Передача!$D$30</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="T6" s="111" t="s">
+        <v>250</v>
+      </c>
+      <c r="U6" s="111"/>
+      <c r="V6" s="111"/>
+      <c r="W6" s="111"/>
+      <c r="X6" s="130">
+        <v>0.3</v>
+      </c>
+      <c r="Y6" s="130"/>
+      <c r="Z6" s="130">
+        <v>0.3</v>
+      </c>
+      <c r="AA6" s="130"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A7" s="111" t="s">
+        <v>221</v>
+      </c>
+      <c r="B7" s="111"/>
+      <c r="C7" s="111"/>
+      <c r="D7" s="111"/>
+      <c r="E7">
+        <f>Передача!$D$37</f>
+        <v>317.5</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="111" t="s">
+        <v>251</v>
+      </c>
+      <c r="K7" s="111"/>
+      <c r="L7" s="111"/>
+      <c r="M7">
+        <f ca="1">Вал!$R$18</f>
+        <v>50</v>
+      </c>
+      <c r="N7" t="s">
+        <v>16</v>
+      </c>
+      <c r="T7" s="111" t="s">
+        <v>261</v>
+      </c>
+      <c r="U7" s="111"/>
+      <c r="V7" s="111"/>
+      <c r="W7" s="111"/>
+      <c r="X7" s="130">
+        <f>2.1*10^5</f>
+        <v>210000</v>
+      </c>
+      <c r="Y7" s="130"/>
+      <c r="Z7" s="130">
+        <f>2.1*10^5</f>
+        <v>210000</v>
+      </c>
+      <c r="AA7" s="130"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A8" s="83" t="s">
+        <v>190</v>
+      </c>
+      <c r="B8" s="83"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="1">
+        <f>Передача!$D$39</f>
+        <v>321</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="111" t="s">
+        <v>267</v>
+      </c>
+      <c r="K8" s="111"/>
+      <c r="L8" s="111"/>
+      <c r="M8" s="111"/>
+      <c r="N8" s="111"/>
+      <c r="T8" s="111" t="s">
+        <v>260</v>
+      </c>
+      <c r="U8" s="111"/>
+      <c r="V8" s="111"/>
+      <c r="W8" s="111"/>
+      <c r="X8" s="130">
+        <v>330</v>
+      </c>
+      <c r="Y8" s="130"/>
+      <c r="Z8" s="130">
+        <v>330</v>
+      </c>
+      <c r="AA8" s="130"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A9" s="83" t="s">
+        <v>181</v>
+      </c>
+      <c r="B9" s="83"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="1">
+        <f>Передача!$D$38</f>
+        <v>309.75</v>
+      </c>
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="111" t="s">
+        <v>178</v>
+      </c>
+      <c r="K9" s="111"/>
+      <c r="L9" s="111"/>
+      <c r="M9">
+        <f>Передача!$E$5</f>
+        <v>320</v>
+      </c>
+      <c r="N9" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="T9" s="111" t="s">
+        <v>262</v>
+      </c>
+      <c r="U9" s="111"/>
+      <c r="V9" s="111"/>
+      <c r="W9" s="111"/>
+      <c r="X9" s="111">
+        <f ca="1">(X5*X5+X4*X4)/(X5*X5-X4*X4)-X6</f>
+        <v>0.7</v>
+      </c>
+      <c r="Y9" s="111"/>
+      <c r="Z9" s="111">
+        <f ca="1">(Z5*Z5+Z4*Z4)/(Z5*Z5-Z4*Z4)+Z6</f>
+        <v>5.8454545454545457</v>
+      </c>
+      <c r="AA9" s="111"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A10" s="111" t="s">
+        <v>170</v>
+      </c>
+      <c r="B10" s="111"/>
+      <c r="C10" s="111"/>
+      <c r="D10" s="111"/>
+      <c r="E10">
+        <f>Передача!$D$40</f>
+        <v>57</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="111" t="s">
+        <v>241</v>
+      </c>
+      <c r="K10" s="111"/>
+      <c r="L10" s="111"/>
+      <c r="M10" s="52">
+        <v>3</v>
+      </c>
+      <c r="N10" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="T10" s="111" t="s">
+        <v>263</v>
+      </c>
+      <c r="U10" s="111"/>
+      <c r="V10" s="111"/>
+      <c r="W10" s="111"/>
+      <c r="X10" s="111">
+        <f ca="1">0.5*X8*(1-(X4*X4/X5/X5))</f>
+        <v>165</v>
+      </c>
+      <c r="Y10" s="111"/>
+      <c r="Z10" s="111">
+        <f ca="1">0.5*Z8*(1-(Z4*Z4/Z5/Z5))</f>
+        <v>50.416666666666671</v>
+      </c>
+      <c r="AA10" s="111"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A11" s="111" t="s">
+        <v>227</v>
+      </c>
+      <c r="B11" s="111"/>
+      <c r="C11" s="111"/>
+      <c r="D11" s="111"/>
+      <c r="E11">
+        <f>_xlfn.MINIFS($32:$32,$31:$31,"&gt;="&amp;E7)</f>
+        <v>5</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="111" t="s">
+        <v>243</v>
+      </c>
+      <c r="K11" s="111"/>
+      <c r="L11" s="111"/>
+      <c r="M11" s="52">
+        <v>0.08</v>
+      </c>
+      <c r="O11" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A12" s="111" t="s">
+        <v>228</v>
+      </c>
+      <c r="B12" s="111"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" t="s">
+        <v>229</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="111" t="s">
+        <v>245</v>
+      </c>
+      <c r="K12" s="111"/>
+      <c r="L12" s="111"/>
+      <c r="M12" s="25">
+        <f>E17</f>
+        <v>57</v>
+      </c>
+      <c r="N12" t="s">
+        <v>16</v>
+      </c>
+      <c r="O12" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A13" s="131" t="s">
+        <v>230</v>
+      </c>
+      <c r="B13" s="111"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="111"/>
+      <c r="E13" t="s">
+        <v>232</v>
+      </c>
+      <c r="F13" t="s">
+        <v>231</v>
+      </c>
+      <c r="J13" s="111" t="s">
+        <v>242</v>
+      </c>
+      <c r="K13" s="111"/>
+      <c r="L13" s="111"/>
+      <c r="M13">
+        <f ca="1">2000*M10*M9/(PI()*M7*M7*M12*M11)</f>
+        <v>53.610086094112106</v>
+      </c>
+      <c r="N13" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A14" s="111" t="s">
+        <v>235</v>
+      </c>
+      <c r="B14" s="111"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14">
+        <f>2.2*E6+0.05*E10</f>
+        <v>8.35</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="111" t="s">
+        <v>249</v>
+      </c>
+      <c r="K14" s="111"/>
+      <c r="L14" s="111"/>
+      <c r="M14">
+        <f ca="1">1000*M13*M7*(X9/X7+Z9/Z7)</f>
+        <v>83.548186120694183</v>
+      </c>
+      <c r="N14" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A15" s="111" t="s">
+        <v>233</v>
+      </c>
+      <c r="B15" s="111"/>
+      <c r="C15" s="111"/>
+      <c r="D15" s="111"/>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="111" t="s">
+        <v>256</v>
+      </c>
+      <c r="K15" s="111"/>
+      <c r="L15" s="111"/>
+      <c r="N15" t="s">
+        <v>255</v>
+      </c>
+      <c r="O15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A16" s="111" t="s">
+        <v>254</v>
+      </c>
+      <c r="B16" s="111"/>
+      <c r="C16" s="111"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="52">
+        <v>1</v>
+      </c>
+      <c r="J16" s="111" t="s">
+        <v>257</v>
+      </c>
+      <c r="K16" s="111"/>
+      <c r="L16" s="111"/>
+      <c r="N16" t="s">
+        <v>255</v>
+      </c>
+      <c r="O16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A17" s="111" t="s">
+        <v>252</v>
+      </c>
+      <c r="B17" s="111"/>
+      <c r="C17" s="111"/>
+      <c r="D17" s="111"/>
+      <c r="E17">
+        <f>E10*E16</f>
+        <v>57</v>
+      </c>
+      <c r="F17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="111" t="s">
+        <v>258</v>
+      </c>
+      <c r="K17" s="111"/>
+      <c r="L17" s="111"/>
+      <c r="M17" s="52">
+        <f ca="1">SUM(M14:M16)</f>
+        <v>83.548186120694183</v>
+      </c>
+      <c r="N17" t="s">
+        <v>255</v>
+      </c>
+      <c r="P17" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A18" s="111" t="s">
+        <v>253</v>
+      </c>
+      <c r="B18" s="111"/>
+      <c r="C18" s="111"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="52">
+        <f ca="1">M7+10</f>
+        <v>60</v>
+      </c>
+      <c r="F18" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="111" t="s">
+        <v>265</v>
+      </c>
+      <c r="K18" s="111"/>
+      <c r="L18" s="111"/>
+      <c r="M18">
+        <f ca="1">MAX(X10:AA10)*M14/M13</f>
+        <v>257.14285714285711</v>
+      </c>
+      <c r="N18" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="J19" s="111" t="s">
+        <v>259</v>
+      </c>
+      <c r="K19" s="111"/>
+      <c r="L19" s="111"/>
+      <c r="M19" s="52">
+        <f ca="1">M18+M15</f>
+        <v>257.14285714285711</v>
+      </c>
+      <c r="N19" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="J20" s="111"/>
+      <c r="K20" s="111"/>
+      <c r="L20" s="111"/>
+      <c r="M20">
+        <v>90</v>
+      </c>
+      <c r="N20">
+        <v>154</v>
+      </c>
+      <c r="O20" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="J21" s="111" t="s">
+        <v>270</v>
+      </c>
+      <c r="K21" s="111"/>
+      <c r="L21" s="111"/>
+      <c r="M21">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="J22" s="111" t="s">
+        <v>269</v>
+      </c>
+      <c r="K22" s="111"/>
+      <c r="L22" s="111"/>
+      <c r="M22">
+        <f ca="1">PI()*M7*M12*(M20-M15)*M21/1000</f>
+        <v>161.1637031291564</v>
+      </c>
+      <c r="N22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A30" s="111" t="s">
+        <v>187</v>
+      </c>
+      <c r="B30" s="111"/>
+      <c r="C30">
+        <v>20</v>
+      </c>
+      <c r="D30">
+        <v>30</v>
+      </c>
+      <c r="E30">
+        <v>40</v>
+      </c>
+      <c r="F30">
+        <v>50</v>
+      </c>
+      <c r="G30">
+        <v>80</v>
+      </c>
+      <c r="H30">
+        <v>120</v>
+      </c>
+      <c r="I30">
+        <v>150</v>
+      </c>
+      <c r="J30">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A31" s="111" t="s">
+        <v>188</v>
+      </c>
+      <c r="B31" s="111"/>
+      <c r="C31">
+        <v>30</v>
+      </c>
+      <c r="D31">
+        <v>40</v>
+      </c>
+      <c r="E31">
+        <v>50</v>
+      </c>
+      <c r="F31">
+        <v>80</v>
+      </c>
+      <c r="G31">
+        <v>120</v>
+      </c>
+      <c r="H31">
+        <v>150</v>
+      </c>
+      <c r="I31">
+        <v>250</v>
+      </c>
+      <c r="J31">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A32" s="111" t="s">
+        <v>220</v>
+      </c>
+      <c r="B32" s="111"/>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>1.2</v>
+      </c>
+      <c r="E32">
+        <v>1.6</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
+      </c>
+      <c r="G32">
+        <v>2.5</v>
+      </c>
+      <c r="H32">
+        <v>3</v>
+      </c>
+      <c r="I32">
+        <v>4</v>
+      </c>
+      <c r="J32">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="65">
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="T3:W3"/>
+    <mergeCell ref="T4:W4"/>
+    <mergeCell ref="T5:W5"/>
+    <mergeCell ref="T6:W6"/>
+    <mergeCell ref="T7:W7"/>
+    <mergeCell ref="T8:W8"/>
+    <mergeCell ref="T9:W9"/>
+    <mergeCell ref="T10:W10"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="Z8:AA8"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="Z10:AA10"/>
+    <mergeCell ref="J8:N8"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="Z9:AA9"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="J19:L19"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20604C11-E2B8-4CC3-855A-FA5D156E5EA8}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B080B891-BABE-48BC-B741-A9DC893B6424}">
+  <dimension ref="A2:W22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="12" width="6.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="111" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2">
+        <f>Передача!$D$25</f>
+        <v>180</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="111" t="s">
+        <v>210</v>
+      </c>
+      <c r="B3" s="111"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+      <c r="E3">
+        <f>Передача!$D$34</f>
+        <v>49</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="111" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4" s="111"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4">
+        <f>Передача!$D$35</f>
+        <v>62</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="111" t="s">
+        <v>211</v>
+      </c>
+      <c r="B5" s="111"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="111"/>
+      <c r="E5">
+        <f>Передача!$D$39</f>
+        <v>321</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="111" t="s">
+        <v>184</v>
+      </c>
+      <c r="B6" s="111"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
+      <c r="E6">
+        <f>Передача!$D$40</f>
+        <v>57</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="111" t="s">
+        <v>209</v>
+      </c>
+      <c r="B7" s="111"/>
+      <c r="C7" s="111"/>
+      <c r="D7" s="111"/>
+      <c r="E7">
+        <f>E2+E3/2+E5/2</f>
+        <v>365</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="111" t="s">
+        <v>208</v>
+      </c>
+      <c r="B8" s="111"/>
+      <c r="C8" s="111"/>
+      <c r="D8" s="111"/>
+      <c r="E8">
+        <f>E7^(1/3)+3</f>
+        <v>10.146569498815023</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="111" t="s">
+        <v>212</v>
+      </c>
+      <c r="B9" s="111"/>
+      <c r="C9" s="111"/>
+      <c r="D9" s="111"/>
+      <c r="E9">
+        <f>E8*3</f>
+        <v>30.439708496445068</v>
+      </c>
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="111" t="s">
+        <v>213</v>
+      </c>
+      <c r="B10" s="111"/>
+      <c r="C10" s="111"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="52">
+        <v>4</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="111" t="s">
+        <v>214</v>
+      </c>
+      <c r="B11" s="111"/>
+      <c r="C11" s="111"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="52">
+        <v>20</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="111" t="s">
+        <v>216</v>
+      </c>
+      <c r="B12" s="111"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="111"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="111" t="s">
+        <v>215</v>
+      </c>
+      <c r="B13" s="111"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="111"/>
+      <c r="E13">
+        <f>E7+2*E8+E10*2+E11*2</f>
+        <v>433.29313899763002</v>
+      </c>
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="111" t="s">
+        <v>170</v>
+      </c>
+      <c r="B14" s="111"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14">
+        <f>E4+2*E8+2*E10</f>
+        <v>90.293138997630052</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="111" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="111"/>
+      <c r="C15" s="111"/>
+      <c r="D15" s="111"/>
+      <c r="E15">
+        <f>E5+E8+E9+2*E10</f>
+        <v>369.5862779952601</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="18:23" x14ac:dyDescent="0.3">
+      <c r="R20" s="1"/>
+      <c r="S20" s="36"/>
+      <c r="T20" s="111" t="s">
+        <v>129</v>
+      </c>
+      <c r="U20" s="111"/>
+      <c r="V20" s="83" t="s">
+        <v>125</v>
+      </c>
+      <c r="W20" s="83"/>
+    </row>
+    <row r="21" spans="18:23" x14ac:dyDescent="0.3">
+      <c r="R21" s="86" t="s">
+        <v>124</v>
+      </c>
+      <c r="S21" s="86"/>
+      <c r="T21" s="83"/>
+      <c r="U21" s="83"/>
+      <c r="V21" s="83"/>
+      <c r="W21" s="83"/>
+    </row>
+    <row r="22" spans="18:23" x14ac:dyDescent="0.3">
+      <c r="R22" s="86" t="s">
+        <v>126</v>
+      </c>
+      <c r="S22" s="86"/>
+      <c r="T22" s="83" t="s">
+        <v>127</v>
+      </c>
+      <c r="U22" s="83"/>
+      <c r="V22" s="80" t="s">
+        <v>128</v>
+      </c>
+      <c r="W22" s="80"/>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D8564D3-007A-4908-B584-B11BCC9DA655}">
+  <dimension ref="A1:E80"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="111">
+        <v>1</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="D1" s="48"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="111"/>
+      <c r="B2">
+        <v>1.05</v>
+      </c>
+      <c r="D2" s="48"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="111">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D3" s="48"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="111"/>
+      <c r="B4">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="D4" s="48"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="111">
+        <v>1.2</v>
+      </c>
+      <c r="B5">
+        <v>1.2</v>
+      </c>
+      <c r="D5" s="48"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="111"/>
+      <c r="B6">
+        <v>1.3</v>
+      </c>
+      <c r="D6" s="48"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="111">
+        <v>1.4</v>
+      </c>
+      <c r="B7">
+        <v>1.4</v>
+      </c>
+      <c r="D7" s="48"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="111"/>
+      <c r="B8">
+        <v>1.5</v>
+      </c>
+      <c r="D8" s="48"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="111">
+        <v>1.6</v>
+      </c>
+      <c r="B9">
+        <v>1.6</v>
+      </c>
+      <c r="D9" s="48"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="111"/>
+      <c r="B10">
+        <v>1.7</v>
+      </c>
+      <c r="D10" s="48"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="111">
+        <v>1.8</v>
+      </c>
+      <c r="B11">
+        <v>1.8</v>
+      </c>
+      <c r="D11" s="48"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="111"/>
+      <c r="B12">
+        <v>1.9</v>
+      </c>
+      <c r="D12" s="48"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="111">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="D13" s="48"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="111"/>
+      <c r="B14">
+        <v>2.1</v>
+      </c>
+      <c r="D14" s="48"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="111">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D15" s="48"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="111"/>
+      <c r="B16">
+        <v>2.4</v>
+      </c>
+      <c r="D16" s="48"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="111">
+        <v>2.5</v>
+      </c>
+      <c r="B17">
+        <v>2.5</v>
+      </c>
+      <c r="D17" s="48"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="111"/>
+      <c r="B18">
+        <v>2.6</v>
+      </c>
+      <c r="D18" s="48"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="111">
+        <v>2.8</v>
+      </c>
+      <c r="B19">
+        <v>2.8</v>
+      </c>
+      <c r="D19" s="48"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="111"/>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="D20" s="48"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="111">
+        <v>3.2</v>
+      </c>
+      <c r="B21">
+        <v>3.2</v>
+      </c>
+      <c r="D21" s="48"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="111"/>
+      <c r="B22">
+        <v>3.4</v>
+      </c>
+      <c r="D22" s="48"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="111">
+        <v>3.6</v>
+      </c>
+      <c r="B23">
+        <v>3.6</v>
+      </c>
+      <c r="D23" s="48"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="111"/>
+      <c r="B24">
+        <v>3.8</v>
+      </c>
+      <c r="D24" s="48"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="111">
+        <v>4</v>
+      </c>
+      <c r="B25">
+        <v>4</v>
+      </c>
+      <c r="D25" s="48"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="111"/>
+      <c r="B26">
+        <v>4.2</v>
+      </c>
+      <c r="D26" s="48"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="111">
+        <v>4.5</v>
+      </c>
+      <c r="B27">
+        <v>4.5</v>
+      </c>
+      <c r="D27" s="48"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="111"/>
+      <c r="B28">
+        <v>4.8</v>
+      </c>
+      <c r="D28" s="48"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="111">
+        <v>5</v>
+      </c>
+      <c r="B29">
+        <v>5</v>
+      </c>
+      <c r="D29" s="48"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="111"/>
+      <c r="B30">
+        <v>5.3</v>
+      </c>
+      <c r="D30" s="48"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="111">
+        <v>5.6</v>
+      </c>
+      <c r="B31">
+        <v>5.6</v>
+      </c>
+      <c r="D31" s="48"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="111"/>
+      <c r="B32">
+        <v>6</v>
+      </c>
+      <c r="D32" s="48"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="111">
+        <v>6.3</v>
+      </c>
+      <c r="B33">
+        <v>6.3</v>
+      </c>
+      <c r="D33" s="48"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="111"/>
+      <c r="B34">
+        <v>6.7</v>
+      </c>
+      <c r="D34" s="48"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="111">
+        <v>7.1</v>
+      </c>
+      <c r="B35">
+        <v>7.1</v>
+      </c>
+      <c r="D35" s="48"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="111"/>
+      <c r="B36">
+        <v>7.5</v>
+      </c>
+      <c r="D36" s="48"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="111">
+        <v>8</v>
+      </c>
+      <c r="B37">
+        <v>8</v>
+      </c>
+      <c r="D37" s="48"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="111"/>
+      <c r="B38">
+        <v>8.5</v>
+      </c>
+      <c r="D38" s="48"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="111">
+        <v>9</v>
+      </c>
+      <c r="B39">
+        <v>9</v>
+      </c>
+      <c r="D39" s="48"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="111"/>
+      <c r="B40" s="67">
+        <v>9.5</v>
+      </c>
+      <c r="D40" s="48"/>
+      <c r="E40" s="67"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="111">
+        <v>10</v>
+      </c>
+      <c r="B41" s="48">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="111"/>
+      <c r="B42" s="48">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="111">
+        <v>11</v>
+      </c>
+      <c r="B43" s="48">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="111"/>
+      <c r="B44" s="48">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="111">
+        <v>12</v>
+      </c>
+      <c r="B45" s="48">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="111"/>
+      <c r="B46" s="48">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="111">
+        <v>14</v>
+      </c>
+      <c r="B47" s="48">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="111"/>
+      <c r="B48" s="48">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="111">
+        <v>16</v>
+      </c>
+      <c r="B49" s="48">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="111"/>
+      <c r="B50" s="48">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="111">
+        <v>18</v>
+      </c>
+      <c r="B51" s="48">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="111"/>
+      <c r="B52" s="48">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="111">
+        <v>20</v>
+      </c>
+      <c r="B53" s="48">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="111"/>
+      <c r="B54" s="48">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="111">
+        <v>22</v>
+      </c>
+      <c r="B55" s="48">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="111"/>
+      <c r="B56" s="48">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="111">
+        <v>25</v>
+      </c>
+      <c r="B57" s="48">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="111"/>
+      <c r="B58" s="48">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="111">
+        <v>28</v>
+      </c>
+      <c r="B59" s="48">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="111"/>
+      <c r="B60" s="48">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="111">
+        <v>32</v>
+      </c>
+      <c r="B61" s="48">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="111"/>
+      <c r="B62" s="48">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="111">
+        <v>36</v>
+      </c>
+      <c r="B63" s="48">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="111"/>
+      <c r="B64" s="48">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="111">
+        <v>40</v>
+      </c>
+      <c r="B65" s="48">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="111"/>
+      <c r="B66" s="48">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="111">
+        <v>45</v>
+      </c>
+      <c r="B67" s="48">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="111"/>
+      <c r="B68" s="48">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="111">
+        <v>50</v>
+      </c>
+      <c r="B69" s="48">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" s="111"/>
+      <c r="B70" s="48">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="111">
+        <v>56</v>
+      </c>
+      <c r="B71" s="48">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="111"/>
+      <c r="B72" s="48">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="111">
+        <v>63</v>
+      </c>
+      <c r="B73" s="48">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="111"/>
+      <c r="B74" s="48">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="111">
+        <v>71</v>
+      </c>
+      <c r="B75" s="48">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="111"/>
+      <c r="B76" s="48">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="111">
+        <v>80</v>
+      </c>
+      <c r="B77" s="48">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="111"/>
+      <c r="B78" s="48">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="111">
+        <v>90</v>
+      </c>
+      <c r="B79" s="48">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="111"/>
+      <c r="B80" s="48">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="40">
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="A75:A76"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Расчёт.xlsx
+++ b/Расчёт.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Professional\Downloads\интститут\курсач детмаш\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEDC2F2-8B91-4C25-95AF-B0D24392336C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63BBD386-C827-42BD-954C-2E259E97C752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="671" activeTab="4" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
   </bookViews>
   <sheets>
     <sheet name="Электродвигатель" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="Вал-шестерня" sheetId="8" r:id="rId7"/>
     <sheet name="Корпус" sheetId="3" r:id="rId8"/>
     <sheet name="Ra40" sheetId="5" r:id="rId9"/>
+    <sheet name="Установ" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="276">
   <si>
     <t>Окружная сила</t>
   </si>
@@ -566,9 +567,6 @@
     <t>Смещение</t>
   </si>
   <si>
-    <t>Налазит на вал</t>
-  </si>
-  <si>
     <t>Обработка</t>
   </si>
   <si>
@@ -861,6 +859,21 @@
   </si>
   <si>
     <t>Ремень</t>
+  </si>
+  <si>
+    <t>Тип подшипника</t>
+  </si>
+  <si>
+    <t>Под подшипник</t>
+  </si>
+  <si>
+    <t>Быстроходный</t>
+  </si>
+  <si>
+    <t>Тихоходный</t>
+  </si>
+  <si>
+    <t>Шариковый однорядный</t>
   </si>
 </sst>
 </file>
@@ -1082,7 +1095,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -1197,34 +1210,25 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1233,37 +1237,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1293,22 +1285,70 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1323,42 +1363,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1964,23 +1980,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
       <c r="E2" s="19">
         <v>4</v>
       </c>
@@ -1988,22 +2004,22 @@
         <v>4</v>
       </c>
       <c r="G2" s="6"/>
-      <c r="I2" s="92" t="s">
+      <c r="I2" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78">
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="83">
         <f>E2*E3</f>
         <v>6.4</v>
       </c>
-      <c r="N2" s="100"/>
-      <c r="Q2" s="92" t="s">
+      <c r="N2" s="84"/>
+      <c r="Q2" s="82" t="s">
         <v>29</v>
       </c>
-      <c r="R2" s="78"/>
-      <c r="S2" s="78"/>
+      <c r="R2" s="83"/>
+      <c r="S2" s="83"/>
       <c r="T2" s="8" t="s">
         <v>30</v>
       </c>
@@ -2013,11 +2029,11 @@
       <c r="V2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AC2" s="92" t="s">
+      <c r="AC2" s="82" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="78"/>
-      <c r="AE2" s="78"/>
+      <c r="AD2" s="83"/>
+      <c r="AE2" s="83"/>
       <c r="AF2" s="8" t="s">
         <v>44</v>
       </c>
@@ -2036,12 +2052,12 @@
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
       <c r="E3" s="20">
         <v>1.6</v>
       </c>
@@ -2049,19 +2065,19 @@
         <v>5</v>
       </c>
       <c r="G3" s="3"/>
-      <c r="I3" s="87" t="s">
+      <c r="I3" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="83"/>
-      <c r="K3" s="83"/>
-      <c r="L3" s="83"/>
-      <c r="M3" s="83"/>
-      <c r="N3" s="95"/>
-      <c r="Q3" s="87" t="s">
+      <c r="J3" s="79"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="79"/>
+      <c r="N3" s="90"/>
+      <c r="Q3" s="78" t="s">
         <v>134</v>
       </c>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
+      <c r="R3" s="79"/>
+      <c r="S3" s="79"/>
       <c r="T3" s="1">
         <v>0.96</v>
       </c>
@@ -2072,11 +2088,11 @@
         <f>AVERAGE(T3:U3)</f>
         <v>0.97</v>
       </c>
-      <c r="AC3" s="87" t="s">
+      <c r="AC3" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="AD3" s="83"/>
-      <c r="AE3" s="83"/>
+      <c r="AD3" s="79"/>
+      <c r="AE3" s="79"/>
       <c r="AF3" s="1">
         <v>1.6</v>
       </c>
@@ -2101,30 +2117,30 @@
       </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A4" s="87" t="s">
+      <c r="A4" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="93" t="s">
+      <c r="B4" s="79"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="93"/>
-      <c r="G4" s="94"/>
-      <c r="I4" s="87" t="s">
+      <c r="F4" s="87"/>
+      <c r="G4" s="93"/>
+      <c r="I4" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="83"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="83"/>
-      <c r="M4" s="83"/>
-      <c r="N4" s="95"/>
-      <c r="Q4" s="87" t="s">
+      <c r="J4" s="79"/>
+      <c r="K4" s="79"/>
+      <c r="L4" s="79"/>
+      <c r="M4" s="79"/>
+      <c r="N4" s="90"/>
+      <c r="Q4" s="78" t="s">
         <v>49</v>
       </c>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
+      <c r="R4" s="79"/>
+      <c r="S4" s="79"/>
       <c r="T4" s="1">
         <v>0.95</v>
       </c>
@@ -2135,11 +2151,11 @@
         <f t="shared" ref="V4:V12" si="1">AVERAGE(T4:U4)</f>
         <v>0.96</v>
       </c>
-      <c r="AC4" s="87" t="s">
+      <c r="AC4" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="AD4" s="83"/>
-      <c r="AE4" s="83"/>
+      <c r="AD4" s="79"/>
+      <c r="AE4" s="79"/>
       <c r="AF4" s="1">
         <v>1</v>
       </c>
@@ -2164,12 +2180,12 @@
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A5" s="87" t="s">
+      <c r="A5" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="83"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="83"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
       <c r="E5" s="21">
         <v>10000</v>
       </c>
@@ -2179,19 +2195,19 @@
       <c r="G5" s="3"/>
       <c r="I5" s="7"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="83" t="s">
+      <c r="K5" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="83"/>
-      <c r="M5" s="83" t="s">
+      <c r="L5" s="79"/>
+      <c r="M5" s="79" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="95"/>
-      <c r="Q5" s="87" t="s">
+      <c r="N5" s="90"/>
+      <c r="Q5" s="78" t="s">
         <v>32</v>
       </c>
-      <c r="R5" s="83"/>
-      <c r="S5" s="83"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
       <c r="T5" s="1">
         <v>0.95</v>
       </c>
@@ -2202,11 +2218,11 @@
         <f t="shared" si="1"/>
         <v>0.96</v>
       </c>
-      <c r="AC5" s="87" t="s">
+      <c r="AC5" s="78" t="s">
         <v>32</v>
       </c>
-      <c r="AD5" s="83"/>
-      <c r="AE5" s="83"/>
+      <c r="AD5" s="79"/>
+      <c r="AE5" s="79"/>
       <c r="AF5" s="1">
         <v>3.15</v>
       </c>
@@ -2231,34 +2247,34 @@
       </c>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A6" s="87" t="s">
+      <c r="A6" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="83"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
       <c r="E6" s="21">
         <v>0.9</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="3"/>
-      <c r="I6" s="87" t="s">
+      <c r="I6" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="83"/>
-      <c r="K6" s="93">
+      <c r="J6" s="79"/>
+      <c r="K6" s="87">
         <v>2</v>
       </c>
-      <c r="L6" s="93"/>
-      <c r="M6" s="83">
+      <c r="L6" s="87"/>
+      <c r="M6" s="79">
         <v>0.99</v>
       </c>
-      <c r="N6" s="95"/>
-      <c r="Q6" s="87" t="s">
+      <c r="N6" s="90"/>
+      <c r="Q6" s="78" t="s">
         <v>33</v>
       </c>
-      <c r="R6" s="83"/>
-      <c r="S6" s="83"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79"/>
       <c r="T6" s="1">
         <v>0.92</v>
       </c>
@@ -2269,11 +2285,11 @@
         <f t="shared" si="1"/>
         <v>0.94</v>
       </c>
-      <c r="AC6" s="87" t="s">
+      <c r="AC6" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="AD6" s="83"/>
-      <c r="AE6" s="83"/>
+      <c r="AD6" s="79"/>
+      <c r="AE6" s="79"/>
       <c r="AF6" s="1">
         <v>12.5</v>
       </c>
@@ -2298,34 +2314,34 @@
       </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A7" s="87" t="s">
+      <c r="A7" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
+      <c r="B7" s="79"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="79"/>
       <c r="E7" s="21">
         <v>3</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="3"/>
-      <c r="I7" s="87" t="s">
+      <c r="I7" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="83"/>
-      <c r="K7" s="93">
+      <c r="J7" s="79"/>
+      <c r="K7" s="87">
         <v>2</v>
       </c>
-      <c r="L7" s="93"/>
-      <c r="M7" s="83">
+      <c r="L7" s="87"/>
+      <c r="M7" s="79">
         <v>0.98</v>
       </c>
-      <c r="N7" s="95"/>
-      <c r="Q7" s="87" t="s">
+      <c r="N7" s="90"/>
+      <c r="Q7" s="78" t="s">
         <v>34</v>
       </c>
-      <c r="R7" s="83"/>
-      <c r="S7" s="83"/>
+      <c r="R7" s="79"/>
+      <c r="S7" s="79"/>
       <c r="T7" s="1">
         <v>0.72</v>
       </c>
@@ -2336,11 +2352,11 @@
         <f t="shared" si="1"/>
         <v>0.77</v>
       </c>
-      <c r="AC7" s="87" t="s">
+      <c r="AC7" s="78" t="s">
         <v>33</v>
       </c>
-      <c r="AD7" s="83"/>
-      <c r="AE7" s="83"/>
+      <c r="AD7" s="79"/>
+      <c r="AE7" s="79"/>
       <c r="AF7" s="1">
         <v>16</v>
       </c>
@@ -2365,35 +2381,35 @@
       </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A8" s="88" t="s">
+      <c r="A8" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="89"/>
-      <c r="C8" s="89"/>
-      <c r="D8" s="89"/>
+      <c r="B8" s="86"/>
+      <c r="C8" s="86"/>
+      <c r="D8" s="86"/>
       <c r="E8" s="22">
         <v>2.2000000000000002</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="5"/>
-      <c r="I8" s="87" t="s">
-        <v>271</v>
-      </c>
-      <c r="J8" s="83"/>
-      <c r="K8" s="93">
+      <c r="I8" s="78" t="s">
+        <v>270</v>
+      </c>
+      <c r="J8" s="79"/>
+      <c r="K8" s="87">
         <v>0</v>
       </c>
-      <c r="L8" s="93"/>
-      <c r="M8" s="110">
+      <c r="L8" s="87"/>
+      <c r="M8" s="88">
         <f>V11</f>
         <v>0.95</v>
       </c>
-      <c r="N8" s="115"/>
-      <c r="Q8" s="87" t="s">
+      <c r="N8" s="89"/>
+      <c r="Q8" s="78" t="s">
         <v>35</v>
       </c>
-      <c r="R8" s="83"/>
-      <c r="S8" s="83"/>
+      <c r="R8" s="79"/>
+      <c r="S8" s="79"/>
       <c r="T8" s="1">
         <v>0.7</v>
       </c>
@@ -2404,11 +2420,11 @@
         <f t="shared" si="1"/>
         <v>0.75</v>
       </c>
-      <c r="AC8" s="87" t="s">
+      <c r="AC8" s="78" t="s">
         <v>46</v>
       </c>
-      <c r="AD8" s="83"/>
-      <c r="AE8" s="83"/>
+      <c r="AD8" s="79"/>
+      <c r="AE8" s="79"/>
       <c r="AF8" s="1">
         <v>10</v>
       </c>
@@ -2433,31 +2449,31 @@
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A9" s="101" t="s">
+      <c r="A9" s="94" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="102"/>
-      <c r="C9" s="102"/>
-      <c r="D9" s="102"/>
-      <c r="E9" s="102"/>
-      <c r="F9" s="102"/>
-      <c r="G9" s="103"/>
-      <c r="I9" s="87" t="s">
+      <c r="B9" s="95"/>
+      <c r="C9" s="95"/>
+      <c r="D9" s="95"/>
+      <c r="E9" s="95"/>
+      <c r="F9" s="95"/>
+      <c r="G9" s="96"/>
+      <c r="I9" s="78" t="s">
         <v>50</v>
       </c>
-      <c r="J9" s="83"/>
-      <c r="K9" s="83"/>
-      <c r="L9" s="83"/>
-      <c r="M9" s="80">
+      <c r="J9" s="79"/>
+      <c r="K9" s="79"/>
+      <c r="L9" s="79"/>
+      <c r="M9" s="91">
         <f>M7^K7*M6^K6*M8^K8</f>
         <v>0.94128803999999988</v>
       </c>
-      <c r="N9" s="113"/>
-      <c r="Q9" s="87" t="s">
+      <c r="N9" s="92"/>
+      <c r="Q9" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="R9" s="83"/>
-      <c r="S9" s="83"/>
+      <c r="R9" s="79"/>
+      <c r="S9" s="79"/>
       <c r="T9" s="1">
         <v>0.75</v>
       </c>
@@ -2468,11 +2484,11 @@
         <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="AC9" s="87" t="s">
+      <c r="AC9" s="78" t="s">
         <v>47</v>
       </c>
-      <c r="AD9" s="83"/>
-      <c r="AE9" s="83"/>
+      <c r="AD9" s="79"/>
+      <c r="AE9" s="79"/>
       <c r="AF9" s="1">
         <v>8</v>
       </c>
@@ -2497,30 +2513,30 @@
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A10" s="104" t="s">
+      <c r="A10" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="105"/>
-      <c r="C10" s="105"/>
-      <c r="D10" s="105"/>
-      <c r="E10" s="105"/>
-      <c r="F10" s="105"/>
-      <c r="G10" s="106"/>
-      <c r="I10" s="87" t="s">
+      <c r="B10" s="98"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="98"/>
+      <c r="E10" s="98"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="99"/>
+      <c r="I10" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="J10" s="83"/>
-      <c r="K10" s="83"/>
-      <c r="L10" s="83"/>
-      <c r="M10" s="93">
+      <c r="J10" s="79"/>
+      <c r="K10" s="79"/>
+      <c r="L10" s="79"/>
+      <c r="M10" s="87">
         <v>0.97</v>
       </c>
-      <c r="N10" s="94"/>
-      <c r="Q10" s="87" t="s">
+      <c r="N10" s="93"/>
+      <c r="Q10" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="R10" s="83"/>
-      <c r="S10" s="83"/>
+      <c r="R10" s="79"/>
+      <c r="S10" s="79"/>
       <c r="T10" s="1">
         <v>0.8</v>
       </c>
@@ -2531,11 +2547,11 @@
         <f t="shared" si="1"/>
         <v>0.85000000000000009</v>
       </c>
-      <c r="AC10" s="88" t="s">
+      <c r="AC10" s="85" t="s">
         <v>34</v>
       </c>
-      <c r="AD10" s="89"/>
-      <c r="AE10" s="89"/>
+      <c r="AD10" s="86"/>
+      <c r="AE10" s="86"/>
       <c r="AF10" s="4">
         <v>70</v>
       </c>
@@ -2560,31 +2576,31 @@
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A11" s="101" t="s">
+      <c r="A11" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="102"/>
-      <c r="C11" s="102"/>
-      <c r="D11" s="102"/>
-      <c r="E11" s="102"/>
-      <c r="F11" s="102"/>
-      <c r="G11" s="103"/>
-      <c r="I11" s="88" t="s">
+      <c r="B11" s="95"/>
+      <c r="C11" s="95"/>
+      <c r="D11" s="95"/>
+      <c r="E11" s="95"/>
+      <c r="F11" s="95"/>
+      <c r="G11" s="96"/>
+      <c r="I11" s="85" t="s">
         <v>55</v>
       </c>
-      <c r="J11" s="89"/>
-      <c r="K11" s="89"/>
-      <c r="L11" s="89"/>
-      <c r="M11" s="90">
+      <c r="J11" s="86"/>
+      <c r="K11" s="86"/>
+      <c r="L11" s="86"/>
+      <c r="M11" s="80">
         <f>M2/M10/M9</f>
         <v>7.0094783572623509</v>
       </c>
-      <c r="N11" s="114"/>
-      <c r="Q11" s="87" t="s">
+      <c r="N11" s="81"/>
+      <c r="Q11" s="78" t="s">
         <v>38</v>
       </c>
-      <c r="R11" s="83"/>
-      <c r="S11" s="83"/>
+      <c r="R11" s="79"/>
+      <c r="S11" s="79"/>
       <c r="T11" s="1">
         <v>0.94</v>
       </c>
@@ -2603,22 +2619,22 @@
       <c r="AH11" s="1"/>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A12" s="92" t="s">
+      <c r="A12" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78" t="s">
+      <c r="B12" s="83"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="78"/>
-      <c r="G12" s="100"/>
-      <c r="Q12" s="88" t="s">
+      <c r="F12" s="83"/>
+      <c r="G12" s="84"/>
+      <c r="Q12" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="R12" s="89"/>
-      <c r="S12" s="89"/>
+      <c r="R12" s="86"/>
+      <c r="S12" s="86"/>
       <c r="T12" s="4">
         <v>0.92</v>
       </c>
@@ -2634,12 +2650,12 @@
       </c>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A13" s="87" t="s">
+      <c r="A13" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="83"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
+      <c r="B13" s="79"/>
+      <c r="C13" s="79"/>
+      <c r="D13" s="79"/>
       <c r="E13" s="21">
         <v>400</v>
       </c>
@@ -2654,12 +2670,12 @@
       </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A14" s="87" t="s">
+      <c r="A14" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="83"/>
-      <c r="C14" s="83"/>
-      <c r="D14" s="83"/>
+      <c r="B14" s="79"/>
+      <c r="C14" s="79"/>
+      <c r="D14" s="79"/>
       <c r="E14" s="21">
         <v>400</v>
       </c>
@@ -2669,12 +2685,12 @@
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A15" s="88" t="s">
+      <c r="A15" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="89"/>
-      <c r="C15" s="89"/>
-      <c r="D15" s="89"/>
+      <c r="B15" s="86"/>
+      <c r="C15" s="86"/>
+      <c r="D15" s="86"/>
       <c r="E15" s="22">
         <v>300</v>
       </c>
@@ -2684,40 +2700,40 @@
       <c r="G15" s="5"/>
     </row>
     <row r="19" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I19" s="92" t="s">
+      <c r="I19" s="82" t="s">
         <v>123</v>
       </c>
-      <c r="J19" s="100"/>
-      <c r="K19" s="92">
+      <c r="J19" s="84"/>
+      <c r="K19" s="82">
         <v>3000</v>
       </c>
-      <c r="L19" s="78"/>
-      <c r="M19" s="78"/>
-      <c r="N19" s="100"/>
-      <c r="O19" s="78">
+      <c r="L19" s="83"/>
+      <c r="M19" s="83"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="83">
         <v>1500</v>
       </c>
-      <c r="P19" s="78"/>
-      <c r="Q19" s="78"/>
-      <c r="R19" s="78"/>
-      <c r="S19" s="92">
+      <c r="P19" s="83"/>
+      <c r="Q19" s="83"/>
+      <c r="R19" s="83"/>
+      <c r="S19" s="82">
         <v>1000</v>
       </c>
-      <c r="T19" s="78"/>
-      <c r="U19" s="78"/>
-      <c r="V19" s="100"/>
-      <c r="W19" s="78">
+      <c r="T19" s="83"/>
+      <c r="U19" s="83"/>
+      <c r="V19" s="84"/>
+      <c r="W19" s="83">
         <v>750</v>
       </c>
-      <c r="X19" s="78"/>
-      <c r="Y19" s="78"/>
-      <c r="Z19" s="100"/>
+      <c r="X19" s="83"/>
+      <c r="Y19" s="83"/>
+      <c r="Z19" s="84"/>
     </row>
     <row r="20" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I20" s="88" t="s">
+      <c r="I20" s="85" t="s">
         <v>118</v>
       </c>
-      <c r="J20" s="112"/>
+      <c r="J20" s="104"/>
       <c r="K20" s="12" t="s">
         <v>72</v>
       </c>
@@ -2768,10 +2784,10 @@
       </c>
     </row>
     <row r="21" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I21" s="87">
+      <c r="I21" s="78">
         <v>0.37</v>
       </c>
-      <c r="J21" s="83"/>
+      <c r="J21" s="79"/>
       <c r="K21" s="26" t="s">
         <v>57</v>
       </c>
@@ -2806,10 +2822,10 @@
       <c r="Z21" s="3"/>
     </row>
     <row r="22" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I22" s="87">
+      <c r="I22" s="78">
         <v>0.55000000000000004</v>
       </c>
-      <c r="J22" s="83"/>
+      <c r="J22" s="79"/>
       <c r="K22" s="26" t="s">
         <v>57</v>
       </c>
@@ -2842,10 +2858,10 @@
       <c r="Z22" s="3"/>
     </row>
     <row r="23" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I23" s="87">
+      <c r="I23" s="78">
         <v>0.75</v>
       </c>
-      <c r="J23" s="83"/>
+      <c r="J23" s="79"/>
       <c r="K23" s="7" t="s">
         <v>58</v>
       </c>
@@ -2878,10 +2894,10 @@
       <c r="Z23" s="3"/>
     </row>
     <row r="24" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I24" s="87">
+      <c r="I24" s="78">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J24" s="83"/>
+      <c r="J24" s="79"/>
       <c r="K24" s="7" t="s">
         <v>59</v>
       </c>
@@ -2914,10 +2930,10 @@
       <c r="Z24" s="3"/>
     </row>
     <row r="25" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I25" s="87">
+      <c r="I25" s="78">
         <v>1.5</v>
       </c>
-      <c r="J25" s="83"/>
+      <c r="J25" s="79"/>
       <c r="K25" s="7" t="s">
         <v>60</v>
       </c>
@@ -2950,10 +2966,10 @@
       <c r="Z25" s="3"/>
     </row>
     <row r="26" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I26" s="87">
+      <c r="I26" s="78">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J26" s="83"/>
+      <c r="J26" s="79"/>
       <c r="K26" s="7" t="s">
         <v>87</v>
       </c>
@@ -2986,10 +3002,10 @@
       <c r="Z26" s="3"/>
     </row>
     <row r="27" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I27" s="87">
+      <c r="I27" s="78">
         <v>3</v>
       </c>
-      <c r="J27" s="83"/>
+      <c r="J27" s="79"/>
       <c r="K27" s="7" t="s">
         <v>61</v>
       </c>
@@ -3020,10 +3036,10 @@
       <c r="Z27" s="3"/>
     </row>
     <row r="28" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I28" s="87">
+      <c r="I28" s="78">
         <v>4</v>
       </c>
-      <c r="J28" s="83"/>
+      <c r="J28" s="79"/>
       <c r="K28" s="7" t="s">
         <v>62</v>
       </c>
@@ -3054,10 +3070,10 @@
       <c r="Z28" s="3"/>
     </row>
     <row r="29" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I29" s="87">
+      <c r="I29" s="78">
         <v>5.5</v>
       </c>
-      <c r="J29" s="83"/>
+      <c r="J29" s="79"/>
       <c r="K29" s="7" t="s">
         <v>63</v>
       </c>
@@ -3108,10 +3124,10 @@
       </c>
     </row>
     <row r="30" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I30" s="87">
+      <c r="I30" s="78">
         <v>7.5</v>
       </c>
-      <c r="J30" s="83"/>
+      <c r="J30" s="79"/>
       <c r="K30" s="7" t="s">
         <v>64</v>
       </c>
@@ -3162,10 +3178,10 @@
       </c>
     </row>
     <row r="31" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I31" s="87">
+      <c r="I31" s="78">
         <v>11</v>
       </c>
-      <c r="J31" s="83"/>
+      <c r="J31" s="79"/>
       <c r="K31" s="7" t="s">
         <v>65</v>
       </c>
@@ -3216,10 +3232,10 @@
       </c>
     </row>
     <row r="32" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I32" s="87">
+      <c r="I32" s="78">
         <v>15</v>
       </c>
-      <c r="J32" s="83"/>
+      <c r="J32" s="79"/>
       <c r="K32" s="7" t="s">
         <v>66</v>
       </c>
@@ -3250,10 +3266,10 @@
       <c r="Z32" s="3"/>
     </row>
     <row r="33" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="I33" s="87">
+      <c r="I33" s="78">
         <v>18.5</v>
       </c>
-      <c r="J33" s="83"/>
+      <c r="J33" s="79"/>
       <c r="K33" s="7" t="s">
         <v>67</v>
       </c>
@@ -3284,10 +3300,10 @@
       <c r="Z33" s="3"/>
     </row>
     <row r="34" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="I34" s="87">
+      <c r="I34" s="78">
         <v>22</v>
       </c>
-      <c r="J34" s="83"/>
+      <c r="J34" s="79"/>
       <c r="K34" s="7" t="s">
         <v>68</v>
       </c>
@@ -3318,10 +3334,10 @@
       <c r="Z34" s="3"/>
     </row>
     <row r="35" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="I35" s="88">
+      <c r="I35" s="85">
         <v>30</v>
       </c>
-      <c r="J35" s="89"/>
+      <c r="J35" s="86"/>
       <c r="K35" s="12" t="s">
         <v>69</v>
       </c>
@@ -3352,15 +3368,15 @@
       <c r="Z35" s="5"/>
     </row>
     <row r="36" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G36" s="111" t="s">
+      <c r="G36" s="103" t="s">
         <v>121</v>
       </c>
-      <c r="H36" s="111"/>
-      <c r="I36" s="101">
+      <c r="H36" s="103"/>
+      <c r="I36" s="94">
         <f>_xlfn.MINIFS(I21:J35,I21:J35,"&gt;="&amp;M11)</f>
         <v>7.5</v>
       </c>
-      <c r="J36" s="102"/>
+      <c r="J36" s="95"/>
       <c r="K36" s="9" t="str">
         <f>VLOOKUP($I$36,$I$21:$R$35,3)</f>
         <v>112M2</v>
@@ -3432,12 +3448,12 @@
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
       <c r="F38" s="16"/>
-      <c r="G38" s="92" t="s">
+      <c r="G38" s="82" t="s">
         <v>40</v>
       </c>
-      <c r="H38" s="78"/>
-      <c r="I38" s="78"/>
-      <c r="J38" s="100"/>
+      <c r="H38" s="83"/>
+      <c r="I38" s="83"/>
+      <c r="J38" s="84"/>
       <c r="K38" s="11"/>
       <c r="L38" s="18"/>
       <c r="M38" s="18"/>
@@ -3461,12 +3477,12 @@
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
       <c r="F39" s="16"/>
-      <c r="G39" s="87" t="s">
+      <c r="G39" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="H39" s="83"/>
-      <c r="I39" s="83"/>
-      <c r="J39" s="95"/>
+      <c r="H39" s="79"/>
+      <c r="I39" s="79"/>
+      <c r="J39" s="90"/>
       <c r="K39" s="7"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -3502,14 +3518,14 @@
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
-      <c r="G40" s="87" t="s">
+      <c r="G40" s="78" t="s">
         <v>120</v>
       </c>
-      <c r="H40" s="83"/>
-      <c r="I40" s="83" t="s">
+      <c r="H40" s="79"/>
+      <c r="I40" s="79" t="s">
         <v>119</v>
       </c>
-      <c r="J40" s="95"/>
+      <c r="J40" s="90"/>
       <c r="K40" s="27" t="s">
         <v>122</v>
       </c>
@@ -3557,15 +3573,15 @@
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
-      <c r="G41" s="107">
+      <c r="G41" s="100">
         <v>160</v>
       </c>
-      <c r="H41" s="108"/>
-      <c r="I41" s="96">
+      <c r="H41" s="101"/>
+      <c r="I41" s="105">
         <f t="shared" ref="I41:I46" si="4">$E$3*60000/PI()/G41</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="J41" s="97"/>
+      <c r="J41" s="106"/>
       <c r="K41" s="15">
         <f t="shared" ref="K41:K46" si="5">IF($I41,L$36/$I41,"-")</f>
         <v>15.15818455357075</v>
@@ -3637,15 +3653,15 @@
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-      <c r="G42" s="109">
+      <c r="G42" s="102">
         <v>200</v>
       </c>
-      <c r="H42" s="110"/>
-      <c r="I42" s="81">
+      <c r="H42" s="88"/>
+      <c r="I42" s="107">
         <f t="shared" si="4"/>
         <v>152.78874536821954</v>
       </c>
-      <c r="J42" s="98"/>
+      <c r="J42" s="108"/>
       <c r="K42" s="13">
         <f t="shared" si="5"/>
         <v>18.947730691963439</v>
@@ -3714,15 +3730,15 @@
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
-      <c r="G43" s="87">
+      <c r="G43" s="78">
         <v>250</v>
       </c>
-      <c r="H43" s="83"/>
-      <c r="I43" s="81">
+      <c r="H43" s="79"/>
+      <c r="I43" s="107">
         <f t="shared" si="4"/>
         <v>122.23099629457563</v>
       </c>
-      <c r="J43" s="98"/>
+      <c r="J43" s="108"/>
       <c r="K43" s="13">
         <f t="shared" si="5"/>
         <v>23.684663364954297</v>
@@ -3791,15 +3807,15 @@
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
-      <c r="G44" s="87">
+      <c r="G44" s="78">
         <v>315</v>
       </c>
-      <c r="H44" s="83"/>
-      <c r="I44" s="81">
+      <c r="H44" s="79"/>
+      <c r="I44" s="107">
         <f t="shared" si="4"/>
         <v>97.008727217917169</v>
       </c>
-      <c r="J44" s="98"/>
+      <c r="J44" s="108"/>
       <c r="K44" s="13">
         <f t="shared" si="5"/>
         <v>29.842675839842414</v>
@@ -3862,15 +3878,15 @@
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="87">
+      <c r="G45" s="78">
         <v>400</v>
       </c>
-      <c r="H45" s="83"/>
-      <c r="I45" s="81">
+      <c r="H45" s="79"/>
+      <c r="I45" s="107">
         <f t="shared" si="4"/>
         <v>76.394372684109769</v>
       </c>
-      <c r="J45" s="98"/>
+      <c r="J45" s="108"/>
       <c r="K45" s="13">
         <f t="shared" si="5"/>
         <v>37.895461383926879</v>
@@ -3930,15 +3946,15 @@
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-      <c r="G46" s="88">
+      <c r="G46" s="85">
         <v>500</v>
       </c>
-      <c r="H46" s="89"/>
-      <c r="I46" s="91">
+      <c r="H46" s="86"/>
+      <c r="I46" s="109">
         <f t="shared" si="4"/>
         <v>61.115498147287816</v>
       </c>
-      <c r="J46" s="99"/>
+      <c r="J46" s="110"/>
       <c r="K46" s="14">
         <f t="shared" si="5"/>
         <v>47.369326729908593</v>
@@ -4031,25 +4047,25 @@
       <c r="Z47" s="1"/>
     </row>
     <row r="48" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B48" s="92" t="s">
+      <c r="B48" s="82" t="s">
         <v>110</v>
       </c>
-      <c r="C48" s="78"/>
-      <c r="D48" s="78"/>
-      <c r="E48" s="78"/>
-      <c r="F48" s="78" t="str">
+      <c r="C48" s="83"/>
+      <c r="D48" s="83"/>
+      <c r="E48" s="83"/>
+      <c r="F48" s="83" t="str">
         <f>P46</f>
         <v>Цилиндрическая 1</v>
       </c>
-      <c r="G48" s="100"/>
+      <c r="G48" s="84"/>
       <c r="H48" s="16"/>
       <c r="I48" s="16"/>
       <c r="J48" s="16"/>
       <c r="K48" s="36"/>
-      <c r="L48" s="83" t="s">
+      <c r="L48" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="M48" s="83"/>
+      <c r="M48" s="79"/>
       <c r="N48" s="28">
         <f ca="1">MAX(Z41:Z46,V41:V46,R41:R46,N41:N46)</f>
         <v>0.78915140422920127</v>
@@ -4067,12 +4083,12 @@
       <c r="Z48" s="1"/>
     </row>
     <row r="49" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B49" s="87" t="s">
+      <c r="B49" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="83"/>
-      <c r="D49" s="83"/>
-      <c r="E49" s="83"/>
+      <c r="C49" s="79"/>
+      <c r="D49" s="79"/>
+      <c r="E49" s="79"/>
       <c r="F49" s="46">
         <f>O41</f>
         <v>7.5398223686155026</v>
@@ -4097,12 +4113,12 @@
       <c r="Z49" s="1"/>
     </row>
     <row r="50" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B50" s="87" t="s">
+      <c r="B50" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="C50" s="83"/>
-      <c r="D50" s="83"/>
-      <c r="E50" s="83"/>
+      <c r="C50" s="79"/>
+      <c r="D50" s="79"/>
+      <c r="E50" s="79"/>
       <c r="F50" s="16">
         <f>P36</f>
         <v>1440</v>
@@ -4119,12 +4135,12 @@
       <c r="Z50" s="1"/>
     </row>
     <row r="51" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B51" s="87" t="s">
+      <c r="B51" s="78" t="s">
         <v>104</v>
       </c>
-      <c r="C51" s="83"/>
-      <c r="D51" s="83"/>
-      <c r="E51" s="83"/>
+      <c r="C51" s="79"/>
+      <c r="D51" s="79"/>
+      <c r="E51" s="79"/>
       <c r="F51" s="1">
         <f>F50*PI()/30</f>
         <v>150.79644737231007</v>
@@ -4133,29 +4149,29 @@
         <v>106</v>
       </c>
       <c r="H51" s="16"/>
-      <c r="I51" s="101" t="s">
+      <c r="I51" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="J51" s="103"/>
+      <c r="J51" s="96"/>
       <c r="K51" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="L51" s="78" t="s">
+      <c r="L51" s="83" t="s">
         <v>122</v>
       </c>
-      <c r="M51" s="78"/>
-      <c r="N51" s="82" t="s">
+      <c r="M51" s="83"/>
+      <c r="N51" s="111" t="s">
         <v>115</v>
       </c>
-      <c r="O51" s="82"/>
-      <c r="P51" s="78" t="s">
+      <c r="O51" s="111"/>
+      <c r="P51" s="83" t="s">
         <v>116</v>
       </c>
-      <c r="Q51" s="78"/>
-      <c r="R51" s="82" t="s">
+      <c r="Q51" s="83"/>
+      <c r="R51" s="111" t="s">
         <v>118</v>
       </c>
-      <c r="S51" s="82"/>
+      <c r="S51" s="111"/>
       <c r="T51" s="49"/>
       <c r="U51" s="49"/>
       <c r="V51" s="49"/>
@@ -4164,12 +4180,12 @@
       <c r="Z51" s="1"/>
     </row>
     <row r="52" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B52" s="87" t="s">
+      <c r="B52" s="78" t="s">
         <v>42</v>
       </c>
-      <c r="C52" s="83"/>
-      <c r="D52" s="83"/>
-      <c r="E52" s="83"/>
+      <c r="C52" s="79"/>
+      <c r="D52" s="79"/>
+      <c r="E52" s="79"/>
       <c r="F52" s="45">
         <f>I41</f>
         <v>190.98593171027443</v>
@@ -4178,33 +4194,33 @@
         <v>105</v>
       </c>
       <c r="H52" s="16"/>
-      <c r="I52" s="87" t="s">
+      <c r="I52" s="78" t="s">
         <v>117</v>
       </c>
-      <c r="J52" s="83"/>
+      <c r="J52" s="79"/>
       <c r="K52" s="42">
         <f>R36</f>
         <v>0.872</v>
       </c>
-      <c r="L52" s="78">
+      <c r="L52" s="83">
         <v>1</v>
       </c>
-      <c r="M52" s="78"/>
-      <c r="N52" s="84">
+      <c r="M52" s="83"/>
+      <c r="N52" s="114">
         <f>F50</f>
         <v>1440</v>
       </c>
-      <c r="O52" s="84"/>
-      <c r="P52" s="79">
+      <c r="O52" s="114"/>
+      <c r="P52" s="113">
         <f ca="1">F55</f>
         <v>46.89699496864425</v>
       </c>
-      <c r="Q52" s="79"/>
-      <c r="R52" s="82">
+      <c r="Q52" s="113"/>
+      <c r="R52" s="111">
         <f t="shared" ref="R52:R57" ca="1" si="17">P52*N52*PI()/1000/30</f>
         <v>7.0719002337086527</v>
       </c>
-      <c r="S52" s="82"/>
+      <c r="S52" s="111"/>
       <c r="T52" s="16"/>
       <c r="U52" s="30"/>
       <c r="X52" s="1"/>
@@ -4212,12 +4228,12 @@
       <c r="Z52" s="1"/>
     </row>
     <row r="53" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B53" s="87" t="s">
+      <c r="B53" s="78" t="s">
         <v>107</v>
       </c>
-      <c r="C53" s="83"/>
-      <c r="D53" s="83"/>
-      <c r="E53" s="83"/>
+      <c r="C53" s="79"/>
+      <c r="D53" s="79"/>
+      <c r="E53" s="79"/>
       <c r="F53" s="16">
         <f>G41</f>
         <v>160</v>
@@ -4226,33 +4242,33 @@
         <v>16</v>
       </c>
       <c r="H53" s="16"/>
-      <c r="I53" s="87" t="s">
+      <c r="I53" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="J53" s="83"/>
+      <c r="J53" s="79"/>
       <c r="K53" s="7">
         <f>M7</f>
         <v>0.98</v>
       </c>
-      <c r="L53" s="83">
+      <c r="L53" s="79">
         <v>1</v>
       </c>
-      <c r="M53" s="83"/>
-      <c r="N53" s="85">
+      <c r="M53" s="79"/>
+      <c r="N53" s="115">
         <f>N52/L53</f>
         <v>1440</v>
       </c>
-      <c r="O53" s="85"/>
-      <c r="P53" s="80">
+      <c r="O53" s="115"/>
+      <c r="P53" s="91">
         <f ca="1">P52*L53*K53</f>
         <v>45.959055069271365</v>
       </c>
-      <c r="Q53" s="80"/>
-      <c r="R53" s="86">
+      <c r="Q53" s="91"/>
+      <c r="R53" s="112">
         <f t="shared" ca="1" si="17"/>
         <v>6.9304622290344788</v>
       </c>
-      <c r="S53" s="86"/>
+      <c r="S53" s="112"/>
       <c r="T53" s="1"/>
       <c r="U53" s="73"/>
       <c r="V53" s="74"/>
@@ -4261,12 +4277,12 @@
       <c r="Z53" s="1"/>
     </row>
     <row r="54" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B54" s="87" t="s">
+      <c r="B54" s="78" t="s">
         <v>97</v>
       </c>
-      <c r="C54" s="83"/>
-      <c r="D54" s="83"/>
-      <c r="E54" s="83"/>
+      <c r="C54" s="79"/>
+      <c r="D54" s="79"/>
+      <c r="E54" s="79"/>
       <c r="F54" s="44">
         <f>E2*F53/2</f>
         <v>320</v>
@@ -4275,33 +4291,33 @@
         <v>100</v>
       </c>
       <c r="H54" s="16"/>
-      <c r="I54" s="87" t="s">
+      <c r="I54" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="J54" s="83"/>
+      <c r="J54" s="79"/>
       <c r="K54" s="7">
         <f>M6</f>
         <v>0.99</v>
       </c>
-      <c r="L54" s="83">
+      <c r="L54" s="79">
         <v>1</v>
       </c>
-      <c r="M54" s="83"/>
-      <c r="N54" s="85">
+      <c r="M54" s="79"/>
+      <c r="N54" s="115">
         <f>N53/L54</f>
         <v>1440</v>
       </c>
-      <c r="O54" s="85"/>
-      <c r="P54" s="80">
+      <c r="O54" s="115"/>
+      <c r="P54" s="91">
         <f ca="1">P53*L54*K54</f>
         <v>45.499464518578648</v>
       </c>
-      <c r="Q54" s="80"/>
-      <c r="R54" s="86">
+      <c r="Q54" s="91"/>
+      <c r="R54" s="112">
         <f t="shared" ca="1" si="17"/>
         <v>6.8611576067441344</v>
       </c>
-      <c r="S54" s="86"/>
+      <c r="S54" s="112"/>
       <c r="T54" s="1"/>
       <c r="U54" s="73"/>
       <c r="V54" s="74"/>
@@ -4311,12 +4327,12 @@
       <c r="Z54" s="1"/>
     </row>
     <row r="55" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B55" s="87" t="s">
+      <c r="B55" s="78" t="s">
         <v>98</v>
       </c>
-      <c r="C55" s="83"/>
-      <c r="D55" s="83"/>
-      <c r="E55" s="83"/>
+      <c r="C55" s="79"/>
+      <c r="D55" s="79"/>
+      <c r="E55" s="79"/>
       <c r="F55" s="1">
         <f ca="1">F54/F59/F49</f>
         <v>46.89699496864425</v>
@@ -4325,34 +4341,34 @@
         <v>100</v>
       </c>
       <c r="H55" s="16"/>
-      <c r="I55" s="87" t="s">
+      <c r="I55" s="78" t="s">
         <v>94</v>
       </c>
-      <c r="J55" s="83"/>
+      <c r="J55" s="79"/>
       <c r="K55" s="43">
         <f ca="1">Q41</f>
         <v>0.96143805509807656</v>
       </c>
-      <c r="L55" s="80">
+      <c r="L55" s="91">
         <f>F49</f>
         <v>7.5398223686155026</v>
       </c>
-      <c r="M55" s="80"/>
-      <c r="N55" s="80">
+      <c r="M55" s="91"/>
+      <c r="N55" s="91">
         <f>N54/L55</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O55" s="80"/>
-      <c r="P55" s="81">
+      <c r="O55" s="91"/>
+      <c r="P55" s="107">
         <f ca="1">P54*L55*K55</f>
         <v>329.82890125747264</v>
       </c>
-      <c r="Q55" s="81"/>
-      <c r="R55" s="86">
+      <c r="Q55" s="107"/>
+      <c r="R55" s="112">
         <f t="shared" ca="1" si="17"/>
         <v>6.5965780251494532</v>
       </c>
-      <c r="S55" s="86"/>
+      <c r="S55" s="112"/>
       <c r="T55" s="1"/>
       <c r="U55" s="73"/>
       <c r="V55" s="74"/>
@@ -4362,12 +4378,12 @@
       <c r="Z55" s="1"/>
     </row>
     <row r="56" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B56" s="87" t="s">
+      <c r="B56" s="78" t="s">
         <v>99</v>
       </c>
-      <c r="C56" s="83"/>
-      <c r="D56" s="83"/>
-      <c r="E56" s="83"/>
+      <c r="C56" s="79"/>
+      <c r="D56" s="79"/>
+      <c r="E56" s="79"/>
       <c r="F56" s="1">
         <f ca="1">F55*F51/1000</f>
         <v>7.0719002337086527</v>
@@ -4375,109 +4391,109 @@
       <c r="G56" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="I56" s="87" t="s">
+      <c r="I56" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="J56" s="83"/>
+      <c r="J56" s="79"/>
       <c r="K56" s="7">
         <f>M7</f>
         <v>0.98</v>
       </c>
-      <c r="L56" s="83">
+      <c r="L56" s="79">
         <v>1</v>
       </c>
-      <c r="M56" s="83"/>
-      <c r="N56" s="80">
+      <c r="M56" s="79"/>
+      <c r="N56" s="91">
         <f>N55/L56</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O56" s="80"/>
-      <c r="P56" s="81">
+      <c r="O56" s="91"/>
+      <c r="P56" s="107">
         <f ca="1">P55*L56*K56</f>
         <v>323.23232323232315</v>
       </c>
-      <c r="Q56" s="81"/>
-      <c r="R56" s="86">
+      <c r="Q56" s="107"/>
+      <c r="R56" s="112">
         <f t="shared" ca="1" si="17"/>
         <v>6.4646464646464636</v>
       </c>
-      <c r="S56" s="86"/>
+      <c r="S56" s="112"/>
       <c r="T56" s="1"/>
       <c r="U56" s="73"/>
       <c r="V56" s="74"/>
     </row>
     <row r="57" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B57" s="87" t="s">
+      <c r="B57" s="78" t="s">
         <v>102</v>
       </c>
-      <c r="C57" s="83"/>
-      <c r="D57" s="83"/>
-      <c r="E57" s="83"/>
+      <c r="C57" s="79"/>
+      <c r="D57" s="79"/>
+      <c r="E57" s="79"/>
       <c r="F57" s="1">
         <f>Q36</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="G57" s="50"/>
-      <c r="I57" s="87" t="s">
+      <c r="I57" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="J57" s="83"/>
+      <c r="J57" s="79"/>
       <c r="K57" s="7">
         <f>M6</f>
         <v>0.99</v>
       </c>
-      <c r="L57" s="83">
+      <c r="L57" s="79">
         <v>1</v>
       </c>
-      <c r="M57" s="83"/>
-      <c r="N57" s="80">
+      <c r="M57" s="79"/>
+      <c r="N57" s="91">
         <f>N56/L57</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O57" s="80"/>
-      <c r="P57" s="81">
+      <c r="O57" s="91"/>
+      <c r="P57" s="107">
         <f ca="1">P56*L57*K57</f>
         <v>319.99999999999994</v>
       </c>
-      <c r="Q57" s="81"/>
-      <c r="R57" s="86">
+      <c r="Q57" s="107"/>
+      <c r="R57" s="112">
         <f t="shared" ca="1" si="17"/>
         <v>6.3999999999999995</v>
       </c>
-      <c r="S57" s="86"/>
+      <c r="S57" s="112"/>
       <c r="T57" s="1"/>
       <c r="U57" s="73"/>
       <c r="V57" s="74"/>
     </row>
     <row r="58" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B58" s="87" t="s">
+      <c r="B58" s="78" t="s">
         <v>103</v>
       </c>
-      <c r="C58" s="83"/>
-      <c r="D58" s="83"/>
-      <c r="E58" s="83"/>
+      <c r="C58" s="79"/>
+      <c r="D58" s="79"/>
+      <c r="E58" s="79"/>
       <c r="F58" s="44">
         <f>MAX(F57,E8)</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="G58" s="50"/>
-      <c r="I58" s="88" t="s">
+      <c r="I58" s="85" t="s">
         <v>139</v>
       </c>
-      <c r="J58" s="89"/>
+      <c r="J58" s="86"/>
       <c r="K58" s="12"/>
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
-      <c r="N58" s="90">
+      <c r="N58" s="80">
         <f>N57</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O58" s="90"/>
-      <c r="P58" s="91">
+      <c r="O58" s="80"/>
+      <c r="P58" s="109">
         <f ca="1">P57</f>
         <v>319.99999999999994</v>
       </c>
-      <c r="Q58" s="91"/>
+      <c r="Q58" s="109"/>
       <c r="R58" s="4"/>
       <c r="S58" s="4"/>
       <c r="T58" s="16"/>
@@ -4485,12 +4501,12 @@
       <c r="V58" s="16"/>
     </row>
     <row r="59" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B59" s="87" t="s">
+      <c r="B59" s="78" t="s">
         <v>109</v>
       </c>
-      <c r="C59" s="83"/>
-      <c r="D59" s="83"/>
-      <c r="E59" s="83"/>
+      <c r="C59" s="79"/>
+      <c r="D59" s="79"/>
+      <c r="E59" s="79"/>
       <c r="F59" s="1">
         <f ca="1">K57*K55*K56*K54*K53</f>
         <v>0.90499014246468046</v>
@@ -4498,12 +4514,12 @@
       <c r="G59" s="50"/>
     </row>
     <row r="60" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B60" s="87" t="s">
+      <c r="B60" s="78" t="s">
         <v>111</v>
       </c>
-      <c r="C60" s="83"/>
-      <c r="D60" s="83"/>
-      <c r="E60" s="83"/>
+      <c r="C60" s="79"/>
+      <c r="D60" s="79"/>
+      <c r="E60" s="79"/>
       <c r="F60" s="1">
         <f ca="1">F59*K52</f>
         <v>0.78915140422920138</v>
@@ -4511,12 +4527,12 @@
       <c r="G60" s="50"/>
     </row>
     <row r="61" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B61" s="83" t="s">
+      <c r="B61" s="79" t="s">
         <v>138</v>
       </c>
-      <c r="C61" s="83"/>
-      <c r="D61" s="83"/>
-      <c r="E61" s="83"/>
+      <c r="C61" s="79"/>
+      <c r="D61" s="79"/>
+      <c r="E61" s="79"/>
       <c r="F61" s="75">
         <v>38</v>
       </c>
@@ -4543,57 +4559,82 @@
     </row>
   </sheetData>
   <mergeCells count="151">
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="S19:V19"/>
-    <mergeCell ref="W19:Z19"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="AC8:AE8"/>
-    <mergeCell ref="AC6:AE6"/>
-    <mergeCell ref="K19:N19"/>
-    <mergeCell ref="AC2:AE2"/>
-    <mergeCell ref="AC3:AE3"/>
-    <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="AC5:AE5"/>
-    <mergeCell ref="AC7:AE7"/>
-    <mergeCell ref="AC10:AE10"/>
-    <mergeCell ref="AC9:AE9"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="I4:N4"/>
-    <mergeCell ref="I3:N3"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="L54:M54"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="N56:O56"/>
+    <mergeCell ref="N57:O57"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="R53:S53"/>
+    <mergeCell ref="R54:S54"/>
+    <mergeCell ref="R55:S55"/>
+    <mergeCell ref="R56:S56"/>
+    <mergeCell ref="R57:S57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="I55:J55"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="P56:Q56"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="Q6:S6"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="G38:J38"/>
     <mergeCell ref="B55:E55"/>
     <mergeCell ref="B54:E54"/>
     <mergeCell ref="B53:E53"/>
@@ -4618,136 +4659,294 @@
     <mergeCell ref="B48:E48"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="I20:J20"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="Q6:S6"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="G39:J39"/>
-    <mergeCell ref="G38:J38"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="I58:J58"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="R53:S53"/>
-    <mergeCell ref="R54:S54"/>
-    <mergeCell ref="R55:S55"/>
-    <mergeCell ref="R56:S56"/>
-    <mergeCell ref="R57:S57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="I55:J55"/>
-    <mergeCell ref="I54:J54"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="P55:Q55"/>
-    <mergeCell ref="P56:Q56"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="L54:M54"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="L57:M57"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="N56:O56"/>
-    <mergeCell ref="N57:O57"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="AC8:AE8"/>
+    <mergeCell ref="AC6:AE6"/>
+    <mergeCell ref="K19:N19"/>
+    <mergeCell ref="AC2:AE2"/>
+    <mergeCell ref="AC3:AE3"/>
+    <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="AC5:AE5"/>
+    <mergeCell ref="AC7:AE7"/>
+    <mergeCell ref="AC10:AE10"/>
+    <mergeCell ref="AC9:AE9"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="S19:V19"/>
+    <mergeCell ref="W19:Z19"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D136A9F2-8845-4295-A8BD-25F04BE0EFA0}">
+  <dimension ref="A1:B34"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>130</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4C98D27-F275-4550-B7FB-3917876B2935}">
-  <dimension ref="A1:Z57"/>
+  <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="30" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="79" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="78" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83" t="str">
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79" t="str">
         <f>Электродвигатель!F48</f>
         <v>Цилиндрическая 1</v>
       </c>
-      <c r="F2" s="95"/>
-      <c r="K2" s="92" t="s">
+      <c r="F2" s="90"/>
+      <c r="K2" s="82" t="s">
         <v>153</v>
       </c>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
-      <c r="O2" s="78"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="78"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="83"/>
+      <c r="N2" s="83"/>
+      <c r="O2" s="83"/>
+      <c r="P2" s="83"/>
+      <c r="Q2" s="83"/>
       <c r="R2" s="1"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
       <c r="E3" s="56">
         <f>Электродвигатель!$F$49</f>
         <v>7.5398223686155026</v>
@@ -4775,16 +4974,16 @@
         <v>152</v>
       </c>
       <c r="R3" s="25" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A4" s="87" t="s">
+      <c r="A4" s="78" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
       <c r="E4" s="56">
         <f>Электродвигатель!$F$52</f>
         <v>190.98593171027443</v>
@@ -4819,12 +5018,12 @@
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A5" s="87" t="s">
+      <c r="A5" s="78" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="83"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="83"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
       <c r="E5" s="25">
         <f>Электродвигатель!$F$54</f>
         <v>320</v>
@@ -4859,12 +5058,12 @@
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A6" s="87" t="s">
+      <c r="A6" s="78" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="83"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
       <c r="E6" s="25">
         <f>Электродвигатель!$F$58</f>
         <v>2.2000000000000002</v>
@@ -4897,12 +5096,12 @@
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A7" s="111" t="s">
+      <c r="A7" s="103" t="s">
         <v>147</v>
       </c>
-      <c r="B7" s="111"/>
-      <c r="C7" s="111"/>
-      <c r="D7" s="111"/>
+      <c r="B7" s="103"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
       <c r="E7">
         <f>Электродвигатель!$E$5</f>
         <v>10000</v>
@@ -4937,14 +5136,14 @@
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A8" s="111" t="s">
+      <c r="A8" s="103" t="s">
         <v>141</v>
       </c>
-      <c r="B8" s="111"/>
-      <c r="C8" s="111"/>
-      <c r="D8" s="111"/>
-      <c r="E8" s="111"/>
-      <c r="F8" s="111"/>
+      <c r="B8" s="103"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="103"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="103"/>
       <c r="K8" s="7">
         <v>5</v>
       </c>
@@ -4976,12 +5175,12 @@
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A9" s="111" t="s">
+      <c r="A9" s="103" t="s">
         <v>146</v>
       </c>
-      <c r="B9" s="111"/>
-      <c r="C9" s="111"/>
-      <c r="D9" s="111"/>
+      <c r="B9" s="103"/>
+      <c r="C9" s="103"/>
+      <c r="D9" s="103"/>
       <c r="E9">
         <f>Электродвигатель!$E$15</f>
         <v>300</v>
@@ -4989,25 +5188,25 @@
       <c r="F9" t="s">
         <v>22</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="132">
         <v>6</v>
       </c>
-      <c r="L9" s="1">
+      <c r="L9" s="133">
         <v>49</v>
       </c>
-      <c r="M9" s="1">
+      <c r="M9" s="133">
         <v>28.5</v>
       </c>
-      <c r="N9" s="1">
+      <c r="N9" s="133">
         <v>0.15</v>
       </c>
-      <c r="O9" s="1">
+      <c r="O9" s="133">
         <v>240</v>
       </c>
-      <c r="P9" s="1">
+      <c r="P9" s="133">
         <v>49.35</v>
       </c>
-      <c r="Q9" s="49">
+      <c r="Q9" s="134">
         <v>69.400000000000006</v>
       </c>
       <c r="R9" s="1">
@@ -5020,12 +5219,12 @@
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A10" s="87" t="s">
+      <c r="A10" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="83"/>
-      <c r="C10" s="83"/>
-      <c r="D10" s="83"/>
+      <c r="B10" s="79"/>
+      <c r="C10" s="79"/>
+      <c r="D10" s="79"/>
       <c r="E10" s="16">
         <f>Электродвигатель!$E$7</f>
         <v>3</v>
@@ -5060,16 +5259,16 @@
       </c>
       <c r="S10" s="54"/>
       <c r="V10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A11" s="87" t="s">
-        <v>217</v>
-      </c>
-      <c r="B11" s="83"/>
-      <c r="C11" s="83"/>
-      <c r="D11" s="83"/>
+      <c r="A11" s="78" t="s">
+        <v>216</v>
+      </c>
+      <c r="B11" s="79"/>
+      <c r="C11" s="79"/>
+      <c r="D11" s="79"/>
       <c r="E11" s="47" t="s">
         <v>101</v>
       </c>
@@ -5103,16 +5302,16 @@
       </c>
       <c r="S11" s="54"/>
       <c r="V11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A12" s="87" t="s">
+      <c r="A12" s="78" t="s">
         <v>130</v>
       </c>
-      <c r="B12" s="83"/>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
+      <c r="B12" s="79"/>
+      <c r="C12" s="79"/>
+      <c r="D12" s="79"/>
       <c r="E12" s="55" t="s">
         <v>101</v>
       </c>
@@ -5147,14 +5346,14 @@
       <c r="S12" s="54"/>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A13" s="111" t="s">
+      <c r="A13" s="103" t="s">
         <v>142</v>
       </c>
-      <c r="B13" s="111"/>
-      <c r="C13" s="111"/>
-      <c r="D13" s="111"/>
-      <c r="E13" s="111"/>
-      <c r="F13" s="111"/>
+      <c r="B13" s="103"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="103"/>
+      <c r="F13" s="103"/>
       <c r="K13" s="7">
         <v>10</v>
       </c>
@@ -5183,12 +5382,12 @@
       <c r="S13" s="54"/>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A14" s="111" t="s">
+      <c r="A14" s="103" t="s">
         <v>145</v>
       </c>
-      <c r="B14" s="111"/>
-      <c r="C14" s="111"/>
-      <c r="D14" s="111"/>
+      <c r="B14" s="103"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="103"/>
       <c r="E14">
         <f>Вал!$D$6</f>
         <v>38</v>
@@ -5224,12 +5423,12 @@
       <c r="S14" s="54"/>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A15" s="83" t="s">
+      <c r="A15" s="79" t="s">
         <v>143</v>
       </c>
-      <c r="B15" s="83"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="83"/>
+      <c r="B15" s="79"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="79"/>
       <c r="E15">
         <f ca="1">Вал!$K$19</f>
         <v>45</v>
@@ -5264,12 +5463,12 @@
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A16" s="83" t="s">
+      <c r="A16" s="79" t="s">
         <v>144</v>
       </c>
-      <c r="B16" s="83"/>
-      <c r="C16" s="83"/>
-      <c r="D16" s="83"/>
+      <c r="B16" s="79"/>
+      <c r="C16" s="79"/>
+      <c r="D16" s="79"/>
       <c r="E16">
         <f ca="1">Вал!$R$18</f>
         <v>50</v>
@@ -5279,687 +5478,881 @@
       </c>
       <c r="Z16" s="59"/>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="H17" s="125" t="s">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="L17" s="119" t="s">
         <v>156</v>
       </c>
-      <c r="I17" s="126"/>
-      <c r="J17" s="126"/>
-      <c r="K17" s="126"/>
-      <c r="L17" s="60">
+      <c r="M17" s="120"/>
+      <c r="N17" s="120"/>
+      <c r="O17" s="120"/>
+      <c r="P17" s="60">
+        <v>6</v>
+      </c>
+      <c r="Q17" s="61"/>
+      <c r="V17" s="119" t="s">
+        <v>156</v>
+      </c>
+      <c r="W17" s="120"/>
+      <c r="X17" s="120"/>
+      <c r="Y17" s="120"/>
+      <c r="Z17" s="60">
         <v>7</v>
       </c>
-      <c r="M17" s="61"/>
-      <c r="O17" s="125" t="s">
+      <c r="AA17" s="61"/>
+      <c r="AC17" s="119" t="s">
         <v>156</v>
       </c>
-      <c r="P17" s="126"/>
-      <c r="Q17" s="126"/>
-      <c r="R17" s="126"/>
-      <c r="S17" s="60">
+      <c r="AD17" s="120"/>
+      <c r="AE17" s="120"/>
+      <c r="AF17" s="120"/>
+      <c r="AG17" s="60">
         <v>8</v>
       </c>
-      <c r="T17" s="61"/>
-      <c r="Z17" s="59"/>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="H18" s="123" t="s">
+      <c r="AH17" s="61"/>
+    </row>
+    <row r="18" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="L18" s="116" t="s">
         <v>152</v>
       </c>
-      <c r="I18" s="124"/>
-      <c r="J18" s="124"/>
-      <c r="K18" s="124"/>
-      <c r="L18" s="64">
+      <c r="M18" s="117"/>
+      <c r="N18" s="117"/>
+      <c r="O18" s="117"/>
+      <c r="P18" s="64">
+        <v>69</v>
+      </c>
+      <c r="Q18" s="62" t="s">
+        <v>159</v>
+      </c>
+      <c r="V18" s="116" t="s">
+        <v>152</v>
+      </c>
+      <c r="W18" s="117"/>
+      <c r="X18" s="117"/>
+      <c r="Y18" s="117"/>
+      <c r="Z18" s="64">
         <v>57</v>
       </c>
-      <c r="M18" s="62" t="s">
+      <c r="AA18" s="62" t="s">
         <v>159</v>
       </c>
-      <c r="O18" s="123" t="s">
+      <c r="AC18" s="116" t="s">
         <v>152</v>
       </c>
-      <c r="P18" s="124"/>
-      <c r="Q18" s="124"/>
-      <c r="R18" s="124"/>
-      <c r="S18" s="64">
+      <c r="AD18" s="117"/>
+      <c r="AE18" s="117"/>
+      <c r="AF18" s="117"/>
+      <c r="AG18" s="64">
         <v>64</v>
       </c>
-      <c r="T18" s="62" t="s">
+      <c r="AH18" s="62" t="s">
         <v>159</v>
       </c>
-      <c r="Z18" s="59"/>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="H19" s="123" t="s">
+    </row>
+    <row r="19" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="L19" s="116" t="s">
         <v>157</v>
       </c>
-      <c r="I19" s="124"/>
-      <c r="J19" s="124"/>
-      <c r="K19" s="124"/>
-      <c r="L19" s="63">
+      <c r="M19" s="117"/>
+      <c r="N19" s="117"/>
+      <c r="O19" s="117"/>
+      <c r="P19" s="63">
+        <v>22.3</v>
+      </c>
+      <c r="Q19" s="62" t="s">
+        <v>159</v>
+      </c>
+      <c r="V19" s="116" t="s">
+        <v>157</v>
+      </c>
+      <c r="W19" s="117"/>
+      <c r="X19" s="117"/>
+      <c r="Y19" s="117"/>
+      <c r="Z19" s="63">
         <v>20</v>
       </c>
-      <c r="M19" s="62" t="s">
+      <c r="AA19" s="62" t="s">
         <v>159</v>
       </c>
-      <c r="O19" s="123" t="s">
+      <c r="AC19" s="116" t="s">
         <v>157</v>
       </c>
-      <c r="P19" s="124"/>
-      <c r="Q19" s="124"/>
-      <c r="R19" s="124"/>
-      <c r="S19" s="63">
+      <c r="AD19" s="117"/>
+      <c r="AE19" s="117"/>
+      <c r="AF19" s="117"/>
+      <c r="AG19" s="63">
         <v>25.3</v>
       </c>
-      <c r="T19" s="62" t="s">
+      <c r="AH19" s="62" t="s">
         <v>159</v>
       </c>
-      <c r="Z19" s="59"/>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="H20" s="123" t="s">
+    </row>
+    <row r="20" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="L20" s="116" t="s">
         <v>149</v>
       </c>
-      <c r="I20" s="124"/>
-      <c r="J20" s="124"/>
-      <c r="K20" s="124"/>
-      <c r="L20" s="63">
+      <c r="M20" s="117"/>
+      <c r="N20" s="117"/>
+      <c r="O20" s="117"/>
+      <c r="P20" s="63">
+        <v>240</v>
+      </c>
+      <c r="Q20" s="62" t="s">
+        <v>16</v>
+      </c>
+      <c r="V20" s="116" t="s">
+        <v>149</v>
+      </c>
+      <c r="W20" s="117"/>
+      <c r="X20" s="117"/>
+      <c r="Y20" s="117"/>
+      <c r="Z20" s="63">
         <v>180</v>
       </c>
-      <c r="M20" s="62" t="s">
+      <c r="AA20" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="O20" s="123" t="s">
+      <c r="AC20" s="116" t="s">
         <v>149</v>
       </c>
-      <c r="P20" s="124"/>
-      <c r="Q20" s="124"/>
-      <c r="R20" s="124"/>
-      <c r="S20" s="63">
+      <c r="AD20" s="117"/>
+      <c r="AE20" s="117"/>
+      <c r="AF20" s="117"/>
+      <c r="AG20" s="63">
         <v>180</v>
       </c>
-      <c r="T20" s="62" t="s">
+      <c r="AH20" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="Z20" s="59"/>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="H21" s="123" t="s">
+    </row>
+    <row r="21" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="L21" s="116" t="s">
         <v>158</v>
       </c>
-      <c r="I21" s="124"/>
-      <c r="J21" s="124"/>
-      <c r="K21" s="124"/>
-      <c r="L21" s="63">
+      <c r="M21" s="117"/>
+      <c r="N21" s="117"/>
+      <c r="O21" s="117"/>
+      <c r="P21" s="63">
+        <v>3.5</v>
+      </c>
+      <c r="Q21" s="62" t="s">
+        <v>16</v>
+      </c>
+      <c r="V21" s="116" t="s">
+        <v>158</v>
+      </c>
+      <c r="W21" s="117"/>
+      <c r="X21" s="117"/>
+      <c r="Y21" s="117"/>
+      <c r="Z21" s="63">
         <v>2.5</v>
       </c>
-      <c r="M21" s="62" t="s">
+      <c r="AA21" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="O21" s="123" t="s">
+      <c r="AC21" s="116" t="s">
         <v>158</v>
       </c>
-      <c r="P21" s="124"/>
-      <c r="Q21" s="124"/>
-      <c r="R21" s="124"/>
-      <c r="S21" s="63">
+      <c r="AD21" s="117"/>
+      <c r="AE21" s="117"/>
+      <c r="AF21" s="117"/>
+      <c r="AG21" s="63">
         <v>3</v>
       </c>
-      <c r="T21" s="62" t="s">
+      <c r="AH21" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="Z21" s="59"/>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="H22" s="123" t="s">
+    </row>
+    <row r="22" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="L22" s="116" t="s">
         <v>0</v>
       </c>
-      <c r="I22" s="124"/>
-      <c r="J22" s="124"/>
-      <c r="K22" s="124"/>
-      <c r="L22" s="63">
+      <c r="M22" s="117"/>
+      <c r="N22" s="117"/>
+      <c r="O22" s="117"/>
+      <c r="P22" s="63">
+        <v>1510</v>
+      </c>
+      <c r="Q22" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="V22" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="W22" s="117"/>
+      <c r="X22" s="117"/>
+      <c r="Y22" s="117"/>
+      <c r="Z22" s="63">
         <v>2016</v>
       </c>
-      <c r="M22" s="62" t="s">
+      <c r="AA22" s="62" t="s">
         <v>162</v>
       </c>
-      <c r="O22" s="123" t="s">
+      <c r="AC22" s="116" t="s">
         <v>0</v>
       </c>
-      <c r="P22" s="124"/>
-      <c r="Q22" s="124"/>
-      <c r="R22" s="124"/>
-      <c r="S22" s="63">
+      <c r="AD22" s="117"/>
+      <c r="AE22" s="117"/>
+      <c r="AF22" s="117"/>
+      <c r="AG22" s="63">
         <v>2013</v>
       </c>
-      <c r="T22" s="62" t="s">
+      <c r="AH22" s="62" t="s">
         <v>162</v>
       </c>
-      <c r="Z22" s="59"/>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="H23" s="123" t="s">
+    </row>
+    <row r="23" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="L23" s="116" t="s">
         <v>160</v>
       </c>
-      <c r="I23" s="124"/>
-      <c r="J23" s="124"/>
-      <c r="K23" s="124"/>
-      <c r="L23" s="63">
+      <c r="M23" s="117"/>
+      <c r="N23" s="117"/>
+      <c r="O23" s="117"/>
+      <c r="P23" s="63">
+        <v>554</v>
+      </c>
+      <c r="Q23" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="V23" s="116" t="s">
+        <v>160</v>
+      </c>
+      <c r="W23" s="117"/>
+      <c r="X23" s="117"/>
+      <c r="Y23" s="117"/>
+      <c r="Z23" s="63">
         <v>734</v>
       </c>
-      <c r="M23" s="62" t="s">
+      <c r="AA23" s="62" t="s">
         <v>162</v>
       </c>
-      <c r="O23" s="123" t="s">
+      <c r="AC23" s="116" t="s">
         <v>160</v>
       </c>
-      <c r="P23" s="124"/>
-      <c r="Q23" s="124"/>
-      <c r="R23" s="124"/>
-      <c r="S23" s="63">
+      <c r="AD23" s="117"/>
+      <c r="AE23" s="117"/>
+      <c r="AF23" s="117"/>
+      <c r="AG23" s="63">
         <v>733</v>
       </c>
-      <c r="T23" s="62" t="s">
+      <c r="AH23" s="62" t="s">
         <v>162</v>
       </c>
-      <c r="Z23" s="59"/>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A24" s="92" t="s">
-        <v>180</v>
-      </c>
-      <c r="B24" s="78"/>
-      <c r="C24" s="78"/>
-      <c r="D24" s="78"/>
-      <c r="E24" s="100"/>
-      <c r="H24" s="116" t="s">
+    </row>
+    <row r="24" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A24" s="82" t="s">
+        <v>179</v>
+      </c>
+      <c r="B24" s="83"/>
+      <c r="C24" s="83"/>
+      <c r="D24" s="83"/>
+      <c r="E24" s="84"/>
+      <c r="L24" s="125" t="s">
         <v>161</v>
       </c>
-      <c r="I24" s="117"/>
-      <c r="J24" s="117"/>
-      <c r="K24" s="117"/>
-      <c r="L24" s="65">
+      <c r="M24" s="126"/>
+      <c r="N24" s="126"/>
+      <c r="O24" s="126"/>
+      <c r="P24" s="65">
         <v>0</v>
       </c>
-      <c r="M24" s="66" t="s">
+      <c r="Q24" s="66" t="s">
         <v>162</v>
       </c>
-      <c r="O24" s="116" t="s">
+      <c r="V24" s="125" t="s">
         <v>161</v>
       </c>
-      <c r="P24" s="117"/>
-      <c r="Q24" s="117"/>
-      <c r="R24" s="117"/>
-      <c r="S24" s="65">
+      <c r="W24" s="126"/>
+      <c r="X24" s="126"/>
+      <c r="Y24" s="126"/>
+      <c r="Z24" s="65">
         <v>0</v>
       </c>
-      <c r="T24" s="66" t="s">
+      <c r="AA24" s="66" t="s">
         <v>162</v>
       </c>
-      <c r="Z24" s="59"/>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A25" s="123" t="s">
+      <c r="AC24" s="125" t="s">
+        <v>161</v>
+      </c>
+      <c r="AD24" s="126"/>
+      <c r="AE24" s="126"/>
+      <c r="AF24" s="126"/>
+      <c r="AG24" s="65">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="66" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A25" s="116" t="s">
         <v>149</v>
       </c>
-      <c r="B25" s="124"/>
-      <c r="C25" s="124"/>
+      <c r="B25" s="117"/>
+      <c r="C25" s="117"/>
       <c r="D25" s="1">
-        <f>L20</f>
+        <f>Z20</f>
         <v>180</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H25" s="64"/>
-      <c r="I25" s="64"/>
-      <c r="J25" s="64"/>
-      <c r="K25" s="64"/>
       <c r="L25" s="64"/>
       <c r="M25" s="64"/>
+      <c r="N25" s="64"/>
       <c r="O25" s="64"/>
       <c r="P25" s="64"/>
       <c r="Q25" s="64"/>
-      <c r="R25" s="64"/>
-      <c r="S25" s="64"/>
-      <c r="T25" s="64"/>
-      <c r="Z25" s="59"/>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A26" s="111" t="s">
+      <c r="V25" s="64"/>
+      <c r="W25" s="64"/>
+      <c r="X25" s="64"/>
+      <c r="Y25" s="64"/>
+      <c r="Z25" s="64"/>
+      <c r="AA25" s="64"/>
+      <c r="AC25" s="64"/>
+      <c r="AD25" s="64"/>
+      <c r="AE25" s="64"/>
+      <c r="AF25" s="64"/>
+      <c r="AG25" s="64"/>
+      <c r="AH25" s="64"/>
+    </row>
+    <row r="26" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A26" s="103" t="s">
         <v>158</v>
       </c>
-      <c r="B26" s="111"/>
-      <c r="C26" s="111"/>
+      <c r="B26" s="103"/>
+      <c r="C26" s="103"/>
       <c r="D26">
-        <f>L21</f>
+        <f>Z21</f>
         <v>2.5</v>
       </c>
       <c r="E26" t="s">
         <v>16</v>
       </c>
-      <c r="H26" s="125" t="s">
+      <c r="L26" s="119" t="s">
         <v>163</v>
       </c>
-      <c r="I26" s="126"/>
-      <c r="J26" s="127" t="s">
+      <c r="M26" s="120"/>
+      <c r="N26" s="123" t="s">
         <v>164</v>
       </c>
-      <c r="K26" s="127"/>
-      <c r="L26" s="127" t="s">
+      <c r="O26" s="123"/>
+      <c r="P26" s="123" t="s">
         <v>126</v>
       </c>
-      <c r="M26" s="128"/>
-      <c r="O26" s="125" t="s">
+      <c r="Q26" s="124"/>
+      <c r="V26" s="119" t="s">
         <v>163</v>
       </c>
-      <c r="P26" s="126"/>
-      <c r="Q26" s="127" t="s">
+      <c r="W26" s="120"/>
+      <c r="X26" s="123" t="s">
         <v>164</v>
       </c>
-      <c r="R26" s="127"/>
-      <c r="S26" s="127" t="s">
+      <c r="Y26" s="123"/>
+      <c r="Z26" s="123" t="s">
         <v>126</v>
       </c>
-      <c r="T26" s="128"/>
-      <c r="Z26" s="59"/>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A27" s="111" t="s">
-        <v>234</v>
-      </c>
-      <c r="B27" s="111"/>
-      <c r="C27" s="111"/>
-      <c r="D27" s="111"/>
-      <c r="E27" s="111"/>
-      <c r="H27" s="123" t="s">
+      <c r="AA26" s="124"/>
+      <c r="AC26" s="119" t="s">
+        <v>163</v>
+      </c>
+      <c r="AD26" s="120"/>
+      <c r="AE26" s="123" t="s">
+        <v>164</v>
+      </c>
+      <c r="AF26" s="123"/>
+      <c r="AG26" s="123" t="s">
+        <v>126</v>
+      </c>
+      <c r="AH26" s="124"/>
+    </row>
+    <row r="27" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A27" s="103" t="s">
+        <v>233</v>
+      </c>
+      <c r="B27" s="103"/>
+      <c r="C27" s="103"/>
+      <c r="D27" s="103"/>
+      <c r="E27" s="103"/>
+      <c r="L27" s="116" t="s">
         <v>165</v>
       </c>
-      <c r="I27" s="124"/>
-      <c r="J27" s="121">
+      <c r="M27" s="117"/>
+      <c r="N27" s="118">
+        <v>16</v>
+      </c>
+      <c r="O27" s="118"/>
+      <c r="P27" s="118">
+        <v>121</v>
+      </c>
+      <c r="Q27" s="122"/>
+      <c r="V27" s="116" t="s">
+        <v>165</v>
+      </c>
+      <c r="W27" s="117"/>
+      <c r="X27" s="118">
         <v>17</v>
       </c>
-      <c r="K27" s="121"/>
-      <c r="L27" s="121">
+      <c r="Y27" s="118"/>
+      <c r="Z27" s="118">
         <v>127</v>
       </c>
-      <c r="M27" s="122"/>
-      <c r="O27" s="123" t="s">
+      <c r="AA27" s="122"/>
+      <c r="AC27" s="116" t="s">
         <v>165</v>
       </c>
-      <c r="P27" s="124"/>
-      <c r="Q27" s="121">
+      <c r="AD27" s="117"/>
+      <c r="AE27" s="118">
         <v>14</v>
       </c>
-      <c r="R27" s="121"/>
-      <c r="S27" s="121">
+      <c r="AF27" s="118"/>
+      <c r="AG27" s="118">
         <v>106</v>
       </c>
-      <c r="T27" s="122"/>
-      <c r="Z27" s="59"/>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A28" s="123" t="s">
+      <c r="AH27" s="122"/>
+    </row>
+    <row r="28" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A28" s="116" t="s">
         <v>0</v>
       </c>
-      <c r="B28" s="124"/>
-      <c r="C28" s="124"/>
+      <c r="B28" s="117"/>
+      <c r="C28" s="117"/>
       <c r="D28" s="64">
-        <f>L22</f>
+        <f>Z22</f>
         <v>2016</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="H28" s="120" t="s">
+      <c r="L28" s="121" t="s">
         <v>172</v>
       </c>
-      <c r="I28" s="121"/>
-      <c r="J28" s="121">
+      <c r="M28" s="118"/>
+      <c r="N28" s="118">
+        <v>0.3</v>
+      </c>
+      <c r="O28" s="118"/>
+      <c r="P28" s="118">
+        <v>-0.22800000000000001</v>
+      </c>
+      <c r="Q28" s="122"/>
+      <c r="V28" s="121" t="s">
+        <v>172</v>
+      </c>
+      <c r="W28" s="118"/>
+      <c r="X28" s="118">
         <v>-0.3</v>
       </c>
-      <c r="K28" s="121"/>
-      <c r="L28" s="121">
+      <c r="Y28" s="118"/>
+      <c r="Z28" s="118">
         <v>0.3</v>
       </c>
-      <c r="M28" s="122"/>
-      <c r="O28" s="120" t="s">
+      <c r="AA28" s="122"/>
+      <c r="AC28" s="121" t="s">
         <v>172</v>
       </c>
-      <c r="P28" s="121"/>
-      <c r="Q28" s="121">
+      <c r="AD28" s="118"/>
+      <c r="AE28" s="118">
         <v>0.3</v>
       </c>
-      <c r="R28" s="121"/>
-      <c r="S28" s="121">
+      <c r="AF28" s="118"/>
+      <c r="AG28" s="118">
         <v>-0.3</v>
       </c>
-      <c r="T28" s="122"/>
-      <c r="Z28" s="59"/>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A29" s="123" t="s">
+      <c r="AH28" s="122"/>
+    </row>
+    <row r="29" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A29" s="116" t="s">
         <v>160</v>
       </c>
-      <c r="B29" s="124"/>
-      <c r="C29" s="124"/>
+      <c r="B29" s="117"/>
+      <c r="C29" s="117"/>
       <c r="D29" s="64">
-        <f>L23</f>
+        <f>Z23</f>
         <v>734</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="H29" s="120" t="s">
+      <c r="L29" s="121" t="s">
         <v>171</v>
       </c>
-      <c r="I29" s="121"/>
-      <c r="J29" s="121">
+      <c r="M29" s="118"/>
+      <c r="N29" s="118">
         <v>49</v>
       </c>
-      <c r="K29" s="121"/>
-      <c r="L29" s="121">
+      <c r="O29" s="118"/>
+      <c r="P29" s="118">
         <v>28.5</v>
       </c>
-      <c r="M29" s="122"/>
-      <c r="O29" s="120" t="s">
+      <c r="Q29" s="122"/>
+      <c r="V29" s="121" t="s">
         <v>171</v>
       </c>
-      <c r="P29" s="121"/>
-      <c r="Q29" s="121">
+      <c r="W29" s="118"/>
+      <c r="X29" s="118">
         <v>49</v>
       </c>
-      <c r="R29" s="121"/>
-      <c r="S29" s="121">
+      <c r="Y29" s="118"/>
+      <c r="Z29" s="118">
         <v>28.5</v>
       </c>
-      <c r="T29" s="122"/>
-      <c r="Z29" s="59"/>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A30" s="123" t="s">
+      <c r="AA29" s="122"/>
+      <c r="AC29" s="121" t="s">
+        <v>171</v>
+      </c>
+      <c r="AD29" s="118"/>
+      <c r="AE29" s="118">
+        <v>49</v>
+      </c>
+      <c r="AF29" s="118"/>
+      <c r="AG29" s="118">
+        <v>28.5</v>
+      </c>
+      <c r="AH29" s="122"/>
+    </row>
+    <row r="30" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A30" s="116" t="s">
         <v>161</v>
       </c>
-      <c r="B30" s="124"/>
-      <c r="C30" s="124"/>
+      <c r="B30" s="117"/>
+      <c r="C30" s="117"/>
       <c r="D30" s="64">
-        <f>L24</f>
+        <f>Z24</f>
         <v>0</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="H30" s="87" t="s">
+      <c r="L30" s="78" t="s">
+        <v>173</v>
+      </c>
+      <c r="M30" s="79"/>
+      <c r="N30" s="79" t="s">
         <v>174</v>
       </c>
-      <c r="I30" s="83"/>
-      <c r="J30" s="83" t="s">
+      <c r="O30" s="79"/>
+      <c r="P30" s="79" t="s">
         <v>175</v>
       </c>
-      <c r="K30" s="83"/>
-      <c r="L30" s="83" t="s">
-        <v>176</v>
-      </c>
-      <c r="M30" s="95"/>
-      <c r="O30" s="87" t="s">
+      <c r="Q30" s="90"/>
+      <c r="V30" s="78" t="s">
+        <v>173</v>
+      </c>
+      <c r="W30" s="79"/>
+      <c r="X30" s="79" t="s">
         <v>174</v>
       </c>
-      <c r="P30" s="83"/>
-      <c r="Q30" s="83" t="s">
+      <c r="Y30" s="79"/>
+      <c r="Z30" s="79" t="s">
         <v>175</v>
       </c>
-      <c r="R30" s="83"/>
-      <c r="S30" s="83" t="s">
-        <v>176</v>
-      </c>
-      <c r="T30" s="95"/>
-      <c r="Z30" s="59"/>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A31" s="111" t="s">
-        <v>222</v>
-      </c>
-      <c r="B31" s="111"/>
-      <c r="C31" s="111"/>
-      <c r="D31" s="111"/>
-      <c r="E31" s="111"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="83"/>
-      <c r="K31" s="83"/>
+      <c r="AA30" s="90"/>
+      <c r="AC30" s="78" t="s">
+        <v>173</v>
+      </c>
+      <c r="AD30" s="79"/>
+      <c r="AE30" s="79" t="s">
+        <v>174</v>
+      </c>
+      <c r="AF30" s="79"/>
+      <c r="AG30" s="79" t="s">
+        <v>175</v>
+      </c>
+      <c r="AH30" s="90"/>
+    </row>
+    <row r="31" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A31" s="103" t="s">
+        <v>221</v>
+      </c>
+      <c r="B31" s="103"/>
+      <c r="C31" s="103"/>
+      <c r="D31" s="103"/>
+      <c r="E31" s="103"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
-      <c r="O31" s="1"/>
+      <c r="N31" s="79"/>
+      <c r="O31" s="79"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
-      <c r="R31" s="1"/>
-      <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
-      <c r="Z31" s="59"/>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A32" s="111" t="s">
-        <v>225</v>
-      </c>
-      <c r="B32" s="111"/>
-      <c r="C32" s="111"/>
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="79"/>
+      <c r="Y31" s="79"/>
+      <c r="Z31" s="1"/>
+      <c r="AA31" s="1"/>
+      <c r="AC31" s="1"/>
+      <c r="AD31" s="1"/>
+      <c r="AE31" s="1"/>
+      <c r="AF31" s="1"/>
+      <c r="AG31" s="1"/>
+      <c r="AH31" s="1"/>
+    </row>
+    <row r="32" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A32" s="103" t="s">
+        <v>224</v>
+      </c>
+      <c r="B32" s="103"/>
+      <c r="C32" s="103"/>
       <c r="D32">
-        <f>J33</f>
+        <f>X33</f>
         <v>42.5</v>
       </c>
       <c r="E32" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="H32" s="120" t="s">
+      <c r="L32" s="121" t="s">
         <v>167</v>
       </c>
-      <c r="I32" s="121"/>
-      <c r="J32" s="121"/>
-      <c r="K32" s="121"/>
-      <c r="L32" s="121"/>
-      <c r="M32" s="122"/>
-      <c r="O32" s="120" t="s">
+      <c r="M32" s="118"/>
+      <c r="N32" s="118"/>
+      <c r="O32" s="118"/>
+      <c r="P32" s="118"/>
+      <c r="Q32" s="122"/>
+      <c r="V32" s="121" t="s">
         <v>167</v>
       </c>
-      <c r="P32" s="121"/>
-      <c r="Q32" s="121"/>
-      <c r="R32" s="121"/>
-      <c r="S32" s="121"/>
-      <c r="T32" s="122"/>
-      <c r="Z32" s="59"/>
-    </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A33" s="83" t="s">
-        <v>223</v>
-      </c>
-      <c r="B33" s="83"/>
-      <c r="C33" s="83"/>
+      <c r="W32" s="118"/>
+      <c r="X32" s="118"/>
+      <c r="Y32" s="118"/>
+      <c r="Z32" s="118"/>
+      <c r="AA32" s="122"/>
+      <c r="AC32" s="121" t="s">
+        <v>167</v>
+      </c>
+      <c r="AD32" s="118"/>
+      <c r="AE32" s="118"/>
+      <c r="AF32" s="118"/>
+      <c r="AG32" s="118"/>
+      <c r="AH32" s="122"/>
+    </row>
+    <row r="33" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A33" s="79" t="s">
+        <v>222</v>
+      </c>
+      <c r="B33" s="79"/>
+      <c r="C33" s="79"/>
       <c r="D33" s="1">
-        <f>J35</f>
+        <f>X35</f>
         <v>37.75</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H33" s="123" t="s">
+      <c r="L33" s="116" t="s">
         <v>166</v>
       </c>
-      <c r="I33" s="124"/>
-      <c r="J33" s="121">
+      <c r="M33" s="117"/>
+      <c r="N33" s="118">
+        <v>56</v>
+      </c>
+      <c r="O33" s="118"/>
+      <c r="P33" s="118">
+        <v>423.5</v>
+      </c>
+      <c r="Q33" s="122"/>
+      <c r="V33" s="116" t="s">
+        <v>166</v>
+      </c>
+      <c r="W33" s="117"/>
+      <c r="X33" s="118">
         <v>42.5</v>
       </c>
-      <c r="K33" s="121"/>
-      <c r="L33" s="121">
+      <c r="Y33" s="118"/>
+      <c r="Z33" s="118">
         <v>317.5</v>
       </c>
-      <c r="M33" s="122"/>
-      <c r="O33" s="123" t="s">
+      <c r="AA33" s="122"/>
+      <c r="AC33" s="116" t="s">
         <v>166</v>
       </c>
-      <c r="P33" s="124"/>
-      <c r="Q33" s="121">
+      <c r="AD33" s="117"/>
+      <c r="AE33" s="118">
         <v>42</v>
       </c>
-      <c r="R33" s="121"/>
-      <c r="S33" s="121">
+      <c r="AF33" s="118"/>
+      <c r="AG33" s="118">
         <v>318</v>
       </c>
-      <c r="T33" s="122"/>
-      <c r="Z33" s="59"/>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A34" s="83" t="s">
-        <v>224</v>
-      </c>
-      <c r="B34" s="83"/>
-      <c r="C34" s="83"/>
+      <c r="AH33" s="122"/>
+    </row>
+    <row r="34" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A34" s="79" t="s">
+        <v>223</v>
+      </c>
+      <c r="B34" s="79"/>
+      <c r="C34" s="79"/>
       <c r="D34" s="1">
-        <f>J34</f>
+        <f>X34</f>
         <v>49</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H34" s="123" t="s">
+      <c r="L34" s="116" t="s">
         <v>169</v>
       </c>
-      <c r="I34" s="124"/>
-      <c r="J34" s="121">
+      <c r="M34" s="117"/>
+      <c r="N34" s="118">
+        <v>65</v>
+      </c>
+      <c r="O34" s="118"/>
+      <c r="P34" s="118">
+        <v>428.9</v>
+      </c>
+      <c r="Q34" s="122"/>
+      <c r="V34" s="116" t="s">
+        <v>169</v>
+      </c>
+      <c r="W34" s="117"/>
+      <c r="X34" s="118">
         <v>49</v>
       </c>
-      <c r="K34" s="121"/>
-      <c r="L34" s="121">
+      <c r="Y34" s="118"/>
+      <c r="Z34" s="118">
         <v>321</v>
       </c>
-      <c r="M34" s="122"/>
-      <c r="O34" s="123" t="s">
+      <c r="AA34" s="122"/>
+      <c r="AC34" s="116" t="s">
         <v>169</v>
       </c>
-      <c r="P34" s="124"/>
-      <c r="Q34" s="121">
+      <c r="AD34" s="117"/>
+      <c r="AE34" s="118">
         <v>49.8</v>
       </c>
-      <c r="R34" s="121"/>
-      <c r="S34" s="121">
+      <c r="AF34" s="118"/>
+      <c r="AG34" s="118">
         <v>322</v>
       </c>
-      <c r="T34" s="122"/>
-      <c r="Z34" s="59"/>
-    </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A35" s="83" t="s">
+      <c r="AH34" s="122"/>
+    </row>
+    <row r="35" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A35" s="79" t="s">
         <v>170</v>
       </c>
-      <c r="B35" s="83"/>
-      <c r="C35" s="83"/>
+      <c r="B35" s="79"/>
+      <c r="C35" s="79"/>
       <c r="D35" s="1">
-        <f>J36</f>
+        <f>X36</f>
         <v>62</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H35" s="123" t="s">
+      <c r="L35" s="116" t="s">
         <v>168</v>
       </c>
-      <c r="I35" s="124"/>
-      <c r="J35" s="121">
+      <c r="M35" s="117"/>
+      <c r="N35" s="118">
+        <v>49.35</v>
+      </c>
+      <c r="O35" s="118"/>
+      <c r="P35" s="118">
+        <v>413</v>
+      </c>
+      <c r="Q35" s="122"/>
+      <c r="V35" s="116" t="s">
+        <v>168</v>
+      </c>
+      <c r="W35" s="117"/>
+      <c r="X35" s="118">
         <v>37.75</v>
       </c>
-      <c r="K35" s="121"/>
-      <c r="L35" s="121">
+      <c r="Y35" s="118"/>
+      <c r="Z35" s="118">
         <v>309.75</v>
       </c>
-      <c r="M35" s="122"/>
-      <c r="O35" s="123" t="s">
+      <c r="AA35" s="122"/>
+      <c r="AC35" s="116" t="s">
         <v>168</v>
       </c>
-      <c r="P35" s="124"/>
-      <c r="Q35" s="121">
+      <c r="AD35" s="117"/>
+      <c r="AE35" s="118">
         <v>36.6</v>
       </c>
-      <c r="R35" s="121"/>
-      <c r="S35" s="121">
+      <c r="AF35" s="118"/>
+      <c r="AG35" s="118">
         <v>308.7</v>
       </c>
-      <c r="T35" s="122"/>
-      <c r="Z35" s="59"/>
-    </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A36" s="111" t="s">
-        <v>226</v>
-      </c>
-      <c r="B36" s="111"/>
-      <c r="C36" s="111"/>
-      <c r="D36" s="111"/>
-      <c r="E36" s="111"/>
-      <c r="H36" s="116" t="s">
+      <c r="AH35" s="122"/>
+    </row>
+    <row r="36" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A36" s="103" t="s">
+        <v>225</v>
+      </c>
+      <c r="B36" s="103"/>
+      <c r="C36" s="103"/>
+      <c r="D36" s="103"/>
+      <c r="E36" s="103"/>
+      <c r="L36" s="125" t="s">
         <v>170</v>
       </c>
-      <c r="I36" s="117"/>
-      <c r="J36" s="118">
+      <c r="M36" s="126"/>
+      <c r="N36" s="127">
+        <v>40</v>
+      </c>
+      <c r="O36" s="127"/>
+      <c r="P36" s="127">
+        <v>36</v>
+      </c>
+      <c r="Q36" s="128"/>
+      <c r="V36" s="125" t="s">
+        <v>170</v>
+      </c>
+      <c r="W36" s="126"/>
+      <c r="X36" s="127">
         <v>62</v>
       </c>
-      <c r="K36" s="118"/>
-      <c r="L36" s="118">
+      <c r="Y36" s="127"/>
+      <c r="Z36" s="127">
         <v>57</v>
       </c>
-      <c r="M36" s="119"/>
-      <c r="O36" s="116" t="s">
+      <c r="AA36" s="128"/>
+      <c r="AC36" s="125" t="s">
         <v>170</v>
       </c>
-      <c r="P36" s="117"/>
-      <c r="Q36" s="118">
+      <c r="AD36" s="126"/>
+      <c r="AE36" s="127">
         <v>79</v>
       </c>
-      <c r="R36" s="118"/>
-      <c r="S36" s="118">
+      <c r="AF36" s="127"/>
+      <c r="AG36" s="127">
         <v>72</v>
       </c>
-      <c r="T36" s="119"/>
-      <c r="Z36" s="59"/>
-    </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A37" s="111" t="s">
-        <v>225</v>
-      </c>
-      <c r="B37" s="111"/>
-      <c r="C37" s="111"/>
+      <c r="AH36" s="128"/>
+    </row>
+    <row r="37" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A37" s="103" t="s">
+        <v>224</v>
+      </c>
+      <c r="B37" s="103"/>
+      <c r="C37" s="103"/>
       <c r="D37">
-        <f>L33</f>
+        <f>Z33</f>
         <v>317.5</v>
       </c>
       <c r="E37" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="H37" s="111" t="s">
-        <v>173</v>
-      </c>
-      <c r="I37" s="111"/>
-      <c r="J37" s="111" t="b">
-        <f ca="1">J35&gt;$E$15</f>
-        <v>0</v>
-      </c>
-      <c r="K37" s="111"/>
+      <c r="H37" s="103"/>
+      <c r="I37" s="103"/>
+      <c r="J37" s="103"/>
+      <c r="K37" s="103"/>
       <c r="L37" s="48"/>
       <c r="M37" s="48"/>
-      <c r="Q37" s="111" t="b">
-        <f ca="1">Q35&gt;$E$15</f>
-        <v>0</v>
-      </c>
-      <c r="R37" s="111"/>
+      <c r="Q37" s="103"/>
+      <c r="R37" s="103"/>
       <c r="S37" s="48"/>
       <c r="T37" s="48"/>
       <c r="Z37" s="59"/>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A38" s="83" t="s">
-        <v>223</v>
-      </c>
-      <c r="B38" s="83"/>
-      <c r="C38" s="83"/>
+    <row r="38" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A38" s="79" t="s">
+        <v>222</v>
+      </c>
+      <c r="B38" s="79"/>
+      <c r="C38" s="79"/>
       <c r="D38" s="1">
-        <f>L35</f>
+        <f>Z35</f>
         <v>309.75</v>
       </c>
       <c r="E38" s="1" t="s">
@@ -5967,14 +6360,14 @@
       </c>
       <c r="Z38" s="59"/>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A39" s="83" t="s">
-        <v>224</v>
-      </c>
-      <c r="B39" s="83"/>
-      <c r="C39" s="83"/>
+    <row r="39" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A39" s="79" t="s">
+        <v>223</v>
+      </c>
+      <c r="B39" s="79"/>
+      <c r="C39" s="79"/>
       <c r="D39" s="1">
-        <f>L34</f>
+        <f>Z34</f>
         <v>321</v>
       </c>
       <c r="E39" s="1" t="s">
@@ -5982,14 +6375,14 @@
       </c>
       <c r="Z39" s="59"/>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A40" s="83" t="s">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A40" s="79" t="s">
         <v>170</v>
       </c>
-      <c r="B40" s="83"/>
-      <c r="C40" s="83"/>
+      <c r="B40" s="79"/>
+      <c r="C40" s="79"/>
       <c r="D40" s="1">
-        <f>L36</f>
+        <f>Z36</f>
         <v>57</v>
       </c>
       <c r="E40" s="1" t="s">
@@ -5997,28 +6390,28 @@
       </c>
       <c r="Z40" s="59"/>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:34" x14ac:dyDescent="0.3">
       <c r="Z41" s="59"/>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.3">
       <c r="Z42" s="59"/>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.3">
       <c r="Z43" s="59"/>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:34" x14ac:dyDescent="0.3">
       <c r="Z44" s="59"/>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:34" x14ac:dyDescent="0.3">
       <c r="Z45" s="59"/>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:34" x14ac:dyDescent="0.3">
       <c r="Z46" s="59"/>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:34" x14ac:dyDescent="0.3">
       <c r="Z47" s="59"/>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:34" x14ac:dyDescent="0.3">
       <c r="Z48" s="59"/>
     </row>
     <row r="49" spans="26:26" x14ac:dyDescent="0.3">
@@ -6049,20 +6442,126 @@
       <c r="Z57" s="59"/>
     </row>
   </sheetData>
-  <mergeCells count="111">
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="J27:K27"/>
+  <mergeCells count="148">
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="L32:Q32"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="V23:Y23"/>
+    <mergeCell ref="V24:Y24"/>
+    <mergeCell ref="Z27:AA27"/>
+    <mergeCell ref="Z30:AA30"/>
+    <mergeCell ref="X30:Y30"/>
+    <mergeCell ref="V30:W30"/>
+    <mergeCell ref="L17:O17"/>
+    <mergeCell ref="L18:O18"/>
+    <mergeCell ref="L19:O19"/>
+    <mergeCell ref="L20:O20"/>
+    <mergeCell ref="L21:O21"/>
+    <mergeCell ref="L22:O22"/>
+    <mergeCell ref="L23:O23"/>
+    <mergeCell ref="L24:O24"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="P27:Q27"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="X27:Y27"/>
+    <mergeCell ref="X31:Y31"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="Z26:AA26"/>
+    <mergeCell ref="X26:Y26"/>
+    <mergeCell ref="V26:W26"/>
+    <mergeCell ref="Z28:AA28"/>
+    <mergeCell ref="X28:Y28"/>
+    <mergeCell ref="V28:W28"/>
+    <mergeCell ref="V29:W29"/>
+    <mergeCell ref="Z29:AA29"/>
+    <mergeCell ref="X29:Y29"/>
+    <mergeCell ref="AC36:AD36"/>
+    <mergeCell ref="AE36:AF36"/>
+    <mergeCell ref="AG36:AH36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="X35:Y35"/>
+    <mergeCell ref="V35:W35"/>
+    <mergeCell ref="V32:AA32"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="P34:Q34"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="P36:Q36"/>
+    <mergeCell ref="Z35:AA35"/>
+    <mergeCell ref="V36:W36"/>
+    <mergeCell ref="X36:Y36"/>
+    <mergeCell ref="Z36:AA36"/>
+    <mergeCell ref="V33:W33"/>
+    <mergeCell ref="X33:Y33"/>
+    <mergeCell ref="Z33:AA33"/>
+    <mergeCell ref="V34:W34"/>
+    <mergeCell ref="X34:Y34"/>
+    <mergeCell ref="Z34:AA34"/>
+    <mergeCell ref="AC33:AD33"/>
+    <mergeCell ref="AE33:AF33"/>
+    <mergeCell ref="AG33:AH33"/>
+    <mergeCell ref="AC34:AD34"/>
+    <mergeCell ref="AE34:AF34"/>
+    <mergeCell ref="AG34:AH34"/>
+    <mergeCell ref="AC35:AD35"/>
+    <mergeCell ref="AE35:AF35"/>
+    <mergeCell ref="AG35:AH35"/>
+    <mergeCell ref="AG27:AH27"/>
+    <mergeCell ref="AC23:AF23"/>
+    <mergeCell ref="AC24:AF24"/>
+    <mergeCell ref="AC26:AD26"/>
+    <mergeCell ref="AE26:AF26"/>
+    <mergeCell ref="AG26:AH26"/>
+    <mergeCell ref="AC28:AD28"/>
+    <mergeCell ref="AE28:AF28"/>
+    <mergeCell ref="AG28:AH28"/>
+    <mergeCell ref="AC29:AD29"/>
+    <mergeCell ref="AE29:AF29"/>
+    <mergeCell ref="AG29:AH29"/>
+    <mergeCell ref="AC30:AD30"/>
+    <mergeCell ref="AE30:AF30"/>
+    <mergeCell ref="AG30:AH30"/>
+    <mergeCell ref="AC27:AD27"/>
+    <mergeCell ref="AE27:AF27"/>
+    <mergeCell ref="AC32:AH32"/>
+    <mergeCell ref="K2:Q2"/>
+    <mergeCell ref="V17:Y17"/>
+    <mergeCell ref="V18:Y18"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="V19:Y19"/>
+    <mergeCell ref="V20:Y20"/>
+    <mergeCell ref="V21:Y21"/>
+    <mergeCell ref="V22:Y22"/>
+    <mergeCell ref="AC22:AF22"/>
+    <mergeCell ref="AC17:AF17"/>
+    <mergeCell ref="AC18:AF18"/>
+    <mergeCell ref="AC19:AF19"/>
+    <mergeCell ref="AC20:AF20"/>
+    <mergeCell ref="AC21:AF21"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A13:F13"/>
@@ -6078,89 +6577,20 @@
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A7:D7"/>
-    <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="H17:K17"/>
-    <mergeCell ref="H18:K18"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="H19:K19"/>
-    <mergeCell ref="H20:K20"/>
-    <mergeCell ref="H21:K21"/>
-    <mergeCell ref="H22:K22"/>
-    <mergeCell ref="O22:R22"/>
-    <mergeCell ref="O17:R17"/>
-    <mergeCell ref="O18:R18"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="O20:R20"/>
-    <mergeCell ref="O21:R21"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="H23:K23"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="S27:T27"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="O23:R23"/>
-    <mergeCell ref="O24:R24"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="S26:T26"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="S28:T28"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="S29:T29"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="S30:T30"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="H24:K24"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A33:C33"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A39:C39"/>
-    <mergeCell ref="O32:T32"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="S33:T33"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="S34:T34"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="S35:T35"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="L34:M34"/>
     <mergeCell ref="H37:I37"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="S36:T36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A37:C37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6175,33 +6605,33 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A2" s="111" t="s">
-        <v>179</v>
-      </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="111"/>
-      <c r="H2" s="111" t="s">
-        <v>192</v>
-      </c>
-      <c r="I2" s="111"/>
-      <c r="J2" s="111"/>
-      <c r="K2" s="111"/>
-      <c r="L2" s="111"/>
-      <c r="O2" s="111" t="s">
+      <c r="A2" s="103" t="s">
+        <v>178</v>
+      </c>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="H2" s="103" t="s">
         <v>191</v>
       </c>
-      <c r="P2" s="111"/>
-      <c r="Q2" s="111"/>
-      <c r="R2" s="111"/>
-      <c r="S2" s="111"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="103"/>
+      <c r="L2" s="103"/>
+      <c r="O2" s="103" t="s">
+        <v>190</v>
+      </c>
+      <c r="P2" s="103"/>
+      <c r="Q2" s="103"/>
+      <c r="R2" s="103"/>
+      <c r="S2" s="103"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A3" s="111" t="s">
-        <v>178</v>
-      </c>
-      <c r="B3" s="111"/>
+      <c r="A3" s="103" t="s">
+        <v>177</v>
+      </c>
+      <c r="B3" s="103"/>
       <c r="D3" s="67">
         <f ca="1">Электродвигатель!$P$53</f>
         <v>45.959055069271365</v>
@@ -6209,11 +6639,11 @@
       <c r="E3" t="s">
         <v>100</v>
       </c>
-      <c r="H3" s="83" t="s">
-        <v>178</v>
-      </c>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
+      <c r="H3" s="79" t="s">
+        <v>177</v>
+      </c>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
       <c r="K3" s="69">
         <f ca="1">D3</f>
         <v>45.959055069271365</v>
@@ -6222,7 +6652,7 @@
         <v>100</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q3" s="16"/>
       <c r="R3">
@@ -6234,10 +6664,10 @@
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A4" s="111" t="s">
+      <c r="A4" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="111"/>
+      <c r="B4" s="103"/>
       <c r="D4" s="68">
         <f>Электродвигатель!$N$52</f>
         <v>1440</v>
@@ -6245,11 +6675,11 @@
       <c r="E4" t="s">
         <v>105</v>
       </c>
-      <c r="H4" s="83" t="s">
+      <c r="H4" s="79" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="79"/>
       <c r="K4" s="70">
         <f>D4</f>
         <v>1440</v>
@@ -6271,27 +6701,27 @@
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="H5" s="111" t="s">
-        <v>182</v>
-      </c>
-      <c r="I5" s="111"/>
-      <c r="J5" s="111"/>
-      <c r="K5" s="111"/>
-      <c r="L5" s="111"/>
-      <c r="O5" s="111" t="s">
+      <c r="H5" s="103" t="s">
+        <v>181</v>
+      </c>
+      <c r="I5" s="103"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="103"/>
+      <c r="L5" s="103"/>
+      <c r="O5" s="103" t="s">
         <v>126</v>
       </c>
-      <c r="P5" s="111"/>
-      <c r="Q5" s="111"/>
-      <c r="R5" s="111"/>
-      <c r="S5" s="111"/>
+      <c r="P5" s="103"/>
+      <c r="Q5" s="103"/>
+      <c r="R5" s="103"/>
+      <c r="S5" s="103"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A6" s="111" t="s">
+      <c r="A6" s="103" t="s">
         <v>120</v>
       </c>
-      <c r="B6" s="111"/>
-      <c r="C6" s="111"/>
+      <c r="B6" s="103"/>
+      <c r="C6" s="103"/>
       <c r="D6" s="72">
         <f>Электродвигатель!$F$61</f>
         <v>38</v>
@@ -6299,11 +6729,11 @@
       <c r="E6" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="111" t="s">
-        <v>181</v>
-      </c>
-      <c r="I6" s="111"/>
-      <c r="J6" s="111"/>
+      <c r="H6" s="103" t="s">
+        <v>180</v>
+      </c>
+      <c r="I6" s="103"/>
+      <c r="J6" s="103"/>
       <c r="K6">
         <f>Передача!D33</f>
         <v>37.75</v>
@@ -6311,11 +6741,11 @@
       <c r="L6" t="s">
         <v>16</v>
       </c>
-      <c r="O6" s="111" t="s">
-        <v>181</v>
-      </c>
-      <c r="P6" s="111"/>
-      <c r="Q6" s="111"/>
+      <c r="O6" s="103" t="s">
+        <v>180</v>
+      </c>
+      <c r="P6" s="103"/>
+      <c r="Q6" s="103"/>
       <c r="R6">
         <f>Передача!D38</f>
         <v>309.75</v>
@@ -6326,18 +6756,18 @@
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" s="129" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B7" s="129"/>
       <c r="C7" s="129"/>
       <c r="D7" s="52">
         <v>0.8</v>
       </c>
-      <c r="H7" s="111" t="s">
-        <v>190</v>
-      </c>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
+      <c r="H7" s="103" t="s">
+        <v>189</v>
+      </c>
+      <c r="I7" s="103"/>
+      <c r="J7" s="103"/>
       <c r="K7">
         <f>Передача!D34</f>
         <v>49</v>
@@ -6345,11 +6775,11 @@
       <c r="L7" t="s">
         <v>16</v>
       </c>
-      <c r="O7" s="111" t="s">
-        <v>190</v>
-      </c>
-      <c r="P7" s="111"/>
-      <c r="Q7" s="111"/>
+      <c r="O7" s="103" t="s">
+        <v>189</v>
+      </c>
+      <c r="P7" s="103"/>
+      <c r="Q7" s="103"/>
       <c r="R7">
         <f>Передача!D39</f>
         <v>321</v>
@@ -6359,19 +6789,19 @@
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A8" s="111" t="s">
-        <v>201</v>
-      </c>
-      <c r="B8" s="111"/>
-      <c r="C8" s="111"/>
+      <c r="A8" s="103" t="s">
+        <v>200</v>
+      </c>
+      <c r="B8" s="103"/>
+      <c r="C8" s="103"/>
       <c r="D8" s="77">
         <v>1.2</v>
       </c>
-      <c r="H8" s="111" t="s">
+      <c r="H8" s="103" t="s">
         <v>170</v>
       </c>
-      <c r="I8" s="111"/>
-      <c r="J8" s="111"/>
+      <c r="I8" s="103"/>
+      <c r="J8" s="103"/>
       <c r="K8">
         <f>Передача!D35</f>
         <v>62</v>
@@ -6379,11 +6809,11 @@
       <c r="L8" t="s">
         <v>16</v>
       </c>
-      <c r="O8" s="111" t="s">
+      <c r="O8" s="103" t="s">
         <v>170</v>
       </c>
-      <c r="P8" s="111"/>
-      <c r="Q8" s="111"/>
+      <c r="P8" s="103"/>
+      <c r="Q8" s="103"/>
       <c r="R8">
         <f>Передача!D40</f>
         <v>57</v>
@@ -6393,50 +6823,50 @@
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="H9" s="111" t="s">
-        <v>193</v>
-      </c>
-      <c r="I9" s="111"/>
-      <c r="J9" s="111"/>
-      <c r="K9" s="111"/>
-      <c r="L9" s="111"/>
-      <c r="O9" s="111" t="s">
-        <v>193</v>
-      </c>
-      <c r="P9" s="111"/>
-      <c r="Q9" s="111"/>
-      <c r="R9" s="111"/>
-      <c r="S9" s="111"/>
+      <c r="H9" s="103" t="s">
+        <v>192</v>
+      </c>
+      <c r="I9" s="103"/>
+      <c r="J9" s="103"/>
+      <c r="K9" s="103"/>
+      <c r="L9" s="103"/>
+      <c r="O9" s="103" t="s">
+        <v>192</v>
+      </c>
+      <c r="P9" s="103"/>
+      <c r="Q9" s="103"/>
+      <c r="R9" s="103"/>
+      <c r="S9" s="103"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="H10" s="111" t="s">
-        <v>189</v>
-      </c>
-      <c r="I10" s="111"/>
-      <c r="J10" s="111"/>
+      <c r="H10" s="103" t="s">
+        <v>188</v>
+      </c>
+      <c r="I10" s="103"/>
+      <c r="J10" s="103"/>
       <c r="K10">
         <v>7.5</v>
       </c>
       <c r="L10" s="71" t="s">
-        <v>197</v>
-      </c>
-      <c r="O10" s="111" t="s">
-        <v>189</v>
-      </c>
-      <c r="P10" s="111"/>
+        <v>196</v>
+      </c>
+      <c r="O10" s="103" t="s">
+        <v>188</v>
+      </c>
+      <c r="P10" s="103"/>
       <c r="R10">
         <v>5.4</v>
       </c>
       <c r="S10" s="71" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="H11" s="111" t="s">
-        <v>202</v>
-      </c>
-      <c r="I11" s="111"/>
-      <c r="J11" s="111"/>
+      <c r="H11" s="103" t="s">
+        <v>201</v>
+      </c>
+      <c r="I11" s="103"/>
+      <c r="J11" s="103"/>
       <c r="K11">
         <f ca="1">K10*(K3)^(1/3)</f>
         <v>26.864883424091097</v>
@@ -6444,11 +6874,11 @@
       <c r="L11" t="s">
         <v>16</v>
       </c>
-      <c r="O11" s="111" t="s">
-        <v>202</v>
-      </c>
-      <c r="P11" s="111"/>
-      <c r="Q11" s="111"/>
+      <c r="O11" s="103" t="s">
+        <v>201</v>
+      </c>
+      <c r="P11" s="103"/>
+      <c r="Q11" s="103"/>
       <c r="R11">
         <f ca="1">R10*(R3)^(1/3)</f>
         <v>37.309835064996221</v>
@@ -6458,20 +6888,20 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="H12" s="111" t="s">
-        <v>206</v>
-      </c>
-      <c r="I12" s="111"/>
-      <c r="J12" s="111"/>
+      <c r="H12" s="103" t="s">
+        <v>205</v>
+      </c>
+      <c r="I12" s="103"/>
+      <c r="J12" s="103"/>
       <c r="K12">
         <f ca="1">MIN(MAX(K11,D6/D8),D6/D7)</f>
         <v>31.666666666666668</v>
       </c>
-      <c r="O12" s="111" t="s">
-        <v>194</v>
-      </c>
-      <c r="P12" s="111"/>
-      <c r="Q12" s="111"/>
+      <c r="O12" s="103" t="s">
+        <v>193</v>
+      </c>
+      <c r="P12" s="103"/>
+      <c r="Q12" s="103"/>
       <c r="R12" s="72">
         <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;R11)</f>
         <v>38</v>
@@ -6480,15 +6910,15 @@
         <v>16</v>
       </c>
       <c r="T12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="H13" s="111" t="s">
-        <v>194</v>
-      </c>
-      <c r="I13" s="111"/>
-      <c r="J13" s="111"/>
+      <c r="H13" s="103" t="s">
+        <v>193</v>
+      </c>
+      <c r="I13" s="103"/>
+      <c r="J13" s="103"/>
       <c r="K13" s="72">
         <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;K12)</f>
         <v>32</v>
@@ -6497,13 +6927,13 @@
         <v>16</v>
       </c>
       <c r="M13" t="s">
-        <v>204</v>
-      </c>
-      <c r="O13" s="111" t="s">
         <v>203</v>
       </c>
-      <c r="P13" s="111"/>
-      <c r="Q13" s="111"/>
+      <c r="O13" s="103" t="s">
+        <v>202</v>
+      </c>
+      <c r="P13" s="103"/>
+      <c r="Q13" s="103"/>
       <c r="R13">
         <f ca="1">_xlfn.MINIFS($28:$28,$26:$26,"&gt;="&amp;R12)</f>
         <v>3.5</v>
@@ -6513,11 +6943,11 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="H14" s="111" t="s">
-        <v>203</v>
-      </c>
-      <c r="I14" s="111"/>
-      <c r="J14" s="111"/>
+      <c r="H14" s="103" t="s">
+        <v>202</v>
+      </c>
+      <c r="I14" s="103"/>
+      <c r="J14" s="103"/>
       <c r="K14">
         <f ca="1">_xlfn.MINIFS($28:$28,$26:$26,"&gt;="&amp;K13)</f>
         <v>3.5</v>
@@ -6525,11 +6955,11 @@
       <c r="L14" t="s">
         <v>16</v>
       </c>
-      <c r="O14" s="111" t="s">
-        <v>199</v>
-      </c>
-      <c r="P14" s="111"/>
-      <c r="Q14" s="111"/>
+      <c r="O14" s="103" t="s">
+        <v>198</v>
+      </c>
+      <c r="P14" s="103"/>
+      <c r="Q14" s="103"/>
       <c r="R14">
         <f ca="1">R12+2*R13</f>
         <v>45</v>
@@ -6540,11 +6970,11 @@
       <c r="X14" s="48"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="H15" s="111" t="s">
-        <v>199</v>
-      </c>
-      <c r="I15" s="111"/>
-      <c r="J15" s="111"/>
+      <c r="H15" s="103" t="s">
+        <v>198</v>
+      </c>
+      <c r="I15" s="103"/>
+      <c r="J15" s="103"/>
       <c r="K15">
         <f ca="1">K13+2*K14</f>
         <v>39</v>
@@ -6552,44 +6982,44 @@
       <c r="L15" t="s">
         <v>16</v>
       </c>
-      <c r="O15" s="111" t="s">
-        <v>195</v>
-      </c>
-      <c r="P15" s="111"/>
-      <c r="Q15" s="111"/>
+      <c r="O15" s="103" t="s">
+        <v>194</v>
+      </c>
+      <c r="P15" s="103"/>
+      <c r="Q15" s="103"/>
       <c r="R15" s="72">
-        <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;R14)</f>
+        <f ca="1">_xlfn.MINIFS(Установ!$A:$A,Установ!$A:$A,"&gt;="&amp;R14)</f>
         <v>45</v>
       </c>
       <c r="S15" t="s">
         <v>16</v>
       </c>
       <c r="T15" t="s">
-        <v>204</v>
+        <v>272</v>
       </c>
       <c r="X15" s="48"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="H16" s="111" t="s">
-        <v>195</v>
-      </c>
-      <c r="I16" s="111"/>
-      <c r="J16" s="111"/>
+      <c r="H16" s="103" t="s">
+        <v>194</v>
+      </c>
+      <c r="I16" s="103"/>
+      <c r="J16" s="103"/>
       <c r="K16" s="72">
-        <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;K15)</f>
+        <f ca="1">_xlfn.MINIFS(Установ!$A:$A,Установ!$A:$A,"&gt;="&amp;K15)</f>
         <v>40</v>
       </c>
       <c r="L16" t="s">
         <v>16</v>
       </c>
       <c r="M16" t="s">
-        <v>204</v>
-      </c>
-      <c r="O16" s="111" t="s">
-        <v>203</v>
-      </c>
-      <c r="P16" s="111"/>
-      <c r="Q16" s="111"/>
+        <v>272</v>
+      </c>
+      <c r="O16" s="103" t="s">
+        <v>202</v>
+      </c>
+      <c r="P16" s="103"/>
+      <c r="Q16" s="103"/>
       <c r="R16">
         <f ca="1">_xlfn.MINIFS($29:$29,$26:$26,"&gt;="&amp;R12)</f>
         <v>2.2999999999999998</v>
@@ -6597,20 +7027,20 @@
       <c r="X16" s="48"/>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="H17" s="111" t="s">
-        <v>203</v>
-      </c>
-      <c r="I17" s="111"/>
-      <c r="J17" s="111"/>
+      <c r="H17" s="103" t="s">
+        <v>202</v>
+      </c>
+      <c r="I17" s="103"/>
+      <c r="J17" s="103"/>
       <c r="K17">
         <f ca="1">_xlfn.MINIFS($29:$29,$26:$26,"&gt;="&amp;K13)</f>
         <v>2</v>
       </c>
-      <c r="O17" s="111" t="s">
-        <v>200</v>
-      </c>
-      <c r="P17" s="111"/>
-      <c r="Q17" s="111"/>
+      <c r="O17" s="103" t="s">
+        <v>199</v>
+      </c>
+      <c r="P17" s="103"/>
+      <c r="Q17" s="103"/>
       <c r="R17">
         <f ca="1">R15+2*R16</f>
         <v>49.6</v>
@@ -6621,11 +7051,11 @@
       <c r="X17" s="48"/>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="H18" s="111" t="s">
-        <v>200</v>
-      </c>
-      <c r="I18" s="111"/>
-      <c r="J18" s="111"/>
+      <c r="H18" s="103" t="s">
+        <v>199</v>
+      </c>
+      <c r="I18" s="103"/>
+      <c r="J18" s="103"/>
       <c r="K18">
         <f ca="1">K16+2*K17</f>
         <v>44</v>
@@ -6633,11 +7063,11 @@
       <c r="L18" t="s">
         <v>16</v>
       </c>
-      <c r="O18" s="111" t="s">
-        <v>196</v>
-      </c>
-      <c r="P18" s="111"/>
-      <c r="Q18" s="111"/>
+      <c r="O18" s="103" t="s">
+        <v>195</v>
+      </c>
+      <c r="P18" s="103"/>
+      <c r="Q18" s="103"/>
       <c r="R18" s="72">
         <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;R17)</f>
         <v>50</v>
@@ -6646,15 +7076,15 @@
         <v>16</v>
       </c>
       <c r="T18" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="H19" s="111" t="s">
-        <v>196</v>
-      </c>
-      <c r="I19" s="111"/>
-      <c r="J19" s="111"/>
+      <c r="H19" s="103" t="s">
+        <v>195</v>
+      </c>
+      <c r="I19" s="103"/>
+      <c r="J19" s="103"/>
       <c r="K19" s="72">
         <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;K18)</f>
         <v>45</v>
@@ -6663,14 +7093,14 @@
         <v>16</v>
       </c>
       <c r="M19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A26" s="111" t="s">
-        <v>187</v>
-      </c>
-      <c r="B26" s="111"/>
+      <c r="A26" s="103" t="s">
+        <v>186</v>
+      </c>
+      <c r="B26" s="103"/>
       <c r="C26">
         <v>17</v>
       </c>
@@ -6703,10 +7133,10 @@
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A27" s="111" t="s">
-        <v>188</v>
-      </c>
-      <c r="B27" s="111"/>
+      <c r="A27" s="103" t="s">
+        <v>187</v>
+      </c>
+      <c r="B27" s="103"/>
       <c r="C27">
         <v>22</v>
       </c>
@@ -6739,10 +7169,10 @@
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A28" s="111" t="s">
-        <v>185</v>
-      </c>
-      <c r="B28" s="111"/>
+      <c r="A28" s="103" t="s">
+        <v>184</v>
+      </c>
+      <c r="B28" s="103"/>
       <c r="C28">
         <v>3</v>
       </c>
@@ -6775,10 +7205,10 @@
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A29" s="111" t="s">
-        <v>186</v>
-      </c>
-      <c r="B29" s="111"/>
+      <c r="A29" s="103" t="s">
+        <v>185</v>
+      </c>
+      <c r="B29" s="103"/>
       <c r="C29">
         <v>1.5</v>
       </c>
@@ -6812,33 +7242,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="O12:Q12"/>
-    <mergeCell ref="O13:Q13"/>
-    <mergeCell ref="O14:Q14"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="O9:S9"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="O7:Q7"/>
-    <mergeCell ref="O8:Q8"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="H3:J3"/>
     <mergeCell ref="O16:Q16"/>
     <mergeCell ref="O17:Q17"/>
     <mergeCell ref="O18:Q18"/>
@@ -6855,6 +7258,33 @@
     <mergeCell ref="H9:L9"/>
     <mergeCell ref="H18:J18"/>
     <mergeCell ref="O11:Q11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="O12:Q12"/>
+    <mergeCell ref="O13:Q13"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="O9:S9"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="O8:Q8"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6871,17 +7301,17 @@
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -6892,34 +7322,48 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B5F8DC-2803-4E90-824A-7553AC4D2CA2}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="23" width="6.77734375" customWidth="1"/>
+    <col min="1" max="27" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="83" t="s">
-        <v>234</v>
-      </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="124" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" s="79" t="s">
+        <v>233</v>
+      </c>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="G2" s="103" t="s">
+        <v>273</v>
+      </c>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="103"/>
+      <c r="M2" s="103" t="s">
+        <v>274</v>
+      </c>
+      <c r="N2" s="103"/>
+      <c r="O2" s="103"/>
+      <c r="P2" s="103"/>
+      <c r="Q2" s="103"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="117" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="117"/>
       <c r="D3" s="64">
         <f>Передача!$D$28</f>
         <v>2016</v>
@@ -6927,13 +7371,25 @@
       <c r="E3" s="1" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="124" t="s">
+      <c r="G3" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" t="s">
+        <v>275</v>
+      </c>
+      <c r="M3" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="N3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="117" t="s">
         <v>160</v>
       </c>
-      <c r="B4" s="124"/>
-      <c r="C4" s="124"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="117"/>
       <c r="D4" s="64">
         <f>Передача!$D$29</f>
         <v>734</v>
@@ -6941,13 +7397,28 @@
       <c r="E4" s="1" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="124" t="s">
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" s="103" t="s">
+        <v>120</v>
+      </c>
+      <c r="N4" s="103"/>
+      <c r="O4" s="103"/>
+      <c r="P4">
+        <f ca="1">Вал!R15</f>
+        <v>45</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="117" t="s">
         <v>161</v>
       </c>
-      <c r="B5" s="124"/>
-      <c r="C5" s="124"/>
+      <c r="B5" s="117"/>
+      <c r="C5" s="117"/>
       <c r="D5" s="64">
         <f>Передача!$D$30</f>
         <v>0</v>
@@ -6955,8 +7426,20 @@
       <c r="E5" s="1" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G5" s="103" t="s">
+        <v>120</v>
+      </c>
+      <c r="H5" s="103"/>
+      <c r="I5" s="103"/>
+      <c r="J5">
+        <f ca="1">Вал!K16</f>
+        <v>40</v>
+      </c>
+      <c r="K5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -6964,11 +7447,15 @@
       <c r="E6" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
+    <mergeCell ref="M2:Q2"/>
+    <mergeCell ref="M4:O4"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="G2:K2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6983,22 +7470,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="103" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
-      <c r="F1" s="111"/>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="79" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
       <c r="E2" s="1">
         <f>Передача!$E$9</f>
         <v>300</v>
@@ -7007,16 +7494,16 @@
         <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
       <c r="E3" s="16">
         <f>Передача!$E$10</f>
         <v>3</v>
@@ -7024,45 +7511,45 @@
       <c r="F3" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="J3" s="83" t="s">
-        <v>234</v>
-      </c>
-      <c r="K3" s="83"/>
-      <c r="L3" s="83"/>
-      <c r="M3" s="83"/>
-      <c r="N3" s="83"/>
-      <c r="T3" s="111" t="s">
+      <c r="J3" s="79" t="s">
+        <v>233</v>
+      </c>
+      <c r="K3" s="79"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="79"/>
+      <c r="N3" s="79"/>
+      <c r="T3" s="103" t="s">
         <v>163</v>
       </c>
-      <c r="U3" s="111"/>
-      <c r="V3" s="111"/>
-      <c r="W3" s="111"/>
-      <c r="X3" s="111" t="s">
-        <v>193</v>
-      </c>
-      <c r="Y3" s="111"/>
-      <c r="Z3" s="111" t="s">
-        <v>182</v>
-      </c>
-      <c r="AA3" s="111"/>
+      <c r="U3" s="103"/>
+      <c r="V3" s="103"/>
+      <c r="W3" s="103"/>
+      <c r="X3" s="103" t="s">
+        <v>192</v>
+      </c>
+      <c r="Y3" s="103"/>
+      <c r="Z3" s="103" t="s">
+        <v>181</v>
+      </c>
+      <c r="AA3" s="103"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A4" s="83" t="s">
-        <v>217</v>
-      </c>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
+      <c r="A4" s="79" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" s="79"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
       <c r="E4" s="47" t="str">
         <f>Передача!$E$11</f>
         <v>?</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="J4" s="124" t="s">
+      <c r="J4" s="117" t="s">
         <v>0</v>
       </c>
-      <c r="K4" s="124"/>
-      <c r="L4" s="124"/>
+      <c r="K4" s="117"/>
+      <c r="L4" s="117"/>
       <c r="M4" s="64">
         <f>Передача!$D$28</f>
         <v>2016</v>
@@ -7070,38 +7557,38 @@
       <c r="N4" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="T4" s="111" t="s">
-        <v>264</v>
-      </c>
-      <c r="U4" s="111"/>
-      <c r="V4" s="111"/>
-      <c r="W4" s="111"/>
-      <c r="X4" s="111">
+      <c r="T4" s="103" t="s">
+        <v>263</v>
+      </c>
+      <c r="U4" s="103"/>
+      <c r="V4" s="103"/>
+      <c r="W4" s="103"/>
+      <c r="X4" s="103">
         <v>0</v>
       </c>
-      <c r="Y4" s="111"/>
-      <c r="Z4" s="111">
+      <c r="Y4" s="103"/>
+      <c r="Z4" s="103">
         <f ca="1">M7</f>
         <v>50</v>
       </c>
-      <c r="AA4" s="111"/>
+      <c r="AA4" s="103"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A5" s="110" t="s">
-        <v>219</v>
-      </c>
-      <c r="B5" s="110"/>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
+      <c r="A5" s="88" t="s">
+        <v>218</v>
+      </c>
+      <c r="B5" s="88"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="88"/>
       <c r="E5" s="76" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="J5" s="124" t="s">
+      <c r="J5" s="117" t="s">
         <v>160</v>
       </c>
-      <c r="K5" s="124"/>
-      <c r="L5" s="124"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="117"/>
       <c r="M5" s="64">
         <f>Передача!$D$29</f>
         <v>734</v>
@@ -7109,30 +7596,30 @@
       <c r="N5" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="T5" s="111" t="s">
-        <v>266</v>
-      </c>
-      <c r="U5" s="111"/>
-      <c r="V5" s="111"/>
-      <c r="W5" s="111"/>
-      <c r="X5" s="111">
+      <c r="T5" s="103" t="s">
+        <v>265</v>
+      </c>
+      <c r="U5" s="103"/>
+      <c r="V5" s="103"/>
+      <c r="W5" s="103"/>
+      <c r="X5" s="103">
         <f ca="1">M7</f>
         <v>50</v>
       </c>
-      <c r="Y5" s="111"/>
-      <c r="Z5" s="111">
+      <c r="Y5" s="103"/>
+      <c r="Z5" s="103">
         <f ca="1">E18</f>
         <v>60</v>
       </c>
-      <c r="AA5" s="111"/>
+      <c r="AA5" s="103"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A6" s="111" t="s">
+      <c r="A6" s="103" t="s">
         <v>158</v>
       </c>
-      <c r="B6" s="111"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
+      <c r="B6" s="103"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
       <c r="E6">
         <f>Передача!$D$26</f>
         <v>2.5</v>
@@ -7140,11 +7627,11 @@
       <c r="F6" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="124" t="s">
+      <c r="J6" s="117" t="s">
         <v>161</v>
       </c>
-      <c r="K6" s="124"/>
-      <c r="L6" s="124"/>
+      <c r="K6" s="117"/>
+      <c r="L6" s="117"/>
       <c r="M6" s="64">
         <f>Передача!$D$30</f>
         <v>0</v>
@@ -7152,28 +7639,28 @@
       <c r="N6" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="T6" s="111" t="s">
-        <v>250</v>
-      </c>
-      <c r="U6" s="111"/>
-      <c r="V6" s="111"/>
-      <c r="W6" s="111"/>
-      <c r="X6" s="130">
+      <c r="T6" s="103" t="s">
+        <v>249</v>
+      </c>
+      <c r="U6" s="103"/>
+      <c r="V6" s="103"/>
+      <c r="W6" s="103"/>
+      <c r="X6" s="131">
         <v>0.3</v>
       </c>
-      <c r="Y6" s="130"/>
-      <c r="Z6" s="130">
+      <c r="Y6" s="131"/>
+      <c r="Z6" s="131">
         <v>0.3</v>
       </c>
-      <c r="AA6" s="130"/>
+      <c r="AA6" s="131"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A7" s="111" t="s">
-        <v>221</v>
-      </c>
-      <c r="B7" s="111"/>
-      <c r="C7" s="111"/>
-      <c r="D7" s="111"/>
+      <c r="A7" s="103" t="s">
+        <v>220</v>
+      </c>
+      <c r="B7" s="103"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
       <c r="E7">
         <f>Передача!$D$37</f>
         <v>317.5</v>
@@ -7181,11 +7668,11 @@
       <c r="F7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="111" t="s">
-        <v>251</v>
-      </c>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
+      <c r="J7" s="103" t="s">
+        <v>250</v>
+      </c>
+      <c r="K7" s="103"/>
+      <c r="L7" s="103"/>
       <c r="M7">
         <f ca="1">Вал!$R$18</f>
         <v>50</v>
@@ -7193,30 +7680,30 @@
       <c r="N7" t="s">
         <v>16</v>
       </c>
-      <c r="T7" s="111" t="s">
-        <v>261</v>
-      </c>
-      <c r="U7" s="111"/>
-      <c r="V7" s="111"/>
-      <c r="W7" s="111"/>
-      <c r="X7" s="130">
+      <c r="T7" s="103" t="s">
+        <v>260</v>
+      </c>
+      <c r="U7" s="103"/>
+      <c r="V7" s="103"/>
+      <c r="W7" s="103"/>
+      <c r="X7" s="131">
         <f>2.1*10^5</f>
         <v>210000</v>
       </c>
-      <c r="Y7" s="130"/>
-      <c r="Z7" s="130">
+      <c r="Y7" s="131"/>
+      <c r="Z7" s="131">
         <f>2.1*10^5</f>
         <v>210000</v>
       </c>
-      <c r="AA7" s="130"/>
+      <c r="AA7" s="131"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A8" s="83" t="s">
-        <v>190</v>
-      </c>
-      <c r="B8" s="83"/>
-      <c r="C8" s="83"/>
-      <c r="D8" s="83"/>
+      <c r="A8" s="79" t="s">
+        <v>189</v>
+      </c>
+      <c r="B8" s="79"/>
+      <c r="C8" s="79"/>
+      <c r="D8" s="79"/>
       <c r="E8" s="1">
         <f>Передача!$D$39</f>
         <v>321</v>
@@ -7224,35 +7711,35 @@
       <c r="F8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="111" t="s">
-        <v>267</v>
-      </c>
-      <c r="K8" s="111"/>
-      <c r="L8" s="111"/>
-      <c r="M8" s="111"/>
-      <c r="N8" s="111"/>
-      <c r="T8" s="111" t="s">
-        <v>260</v>
-      </c>
-      <c r="U8" s="111"/>
-      <c r="V8" s="111"/>
-      <c r="W8" s="111"/>
-      <c r="X8" s="130">
+      <c r="J8" s="103" t="s">
+        <v>266</v>
+      </c>
+      <c r="K8" s="103"/>
+      <c r="L8" s="103"/>
+      <c r="M8" s="103"/>
+      <c r="N8" s="103"/>
+      <c r="T8" s="103" t="s">
+        <v>259</v>
+      </c>
+      <c r="U8" s="103"/>
+      <c r="V8" s="103"/>
+      <c r="W8" s="103"/>
+      <c r="X8" s="131">
         <v>330</v>
       </c>
-      <c r="Y8" s="130"/>
-      <c r="Z8" s="130">
+      <c r="Y8" s="131"/>
+      <c r="Z8" s="131">
         <v>330</v>
       </c>
-      <c r="AA8" s="130"/>
+      <c r="AA8" s="131"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A9" s="83" t="s">
-        <v>181</v>
-      </c>
-      <c r="B9" s="83"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
+      <c r="A9" s="79" t="s">
+        <v>180</v>
+      </c>
+      <c r="B9" s="79"/>
+      <c r="C9" s="79"/>
+      <c r="D9" s="79"/>
       <c r="E9" s="1">
         <f>Передача!$D$38</f>
         <v>309.75</v>
@@ -7260,11 +7747,11 @@
       <c r="F9" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="111" t="s">
-        <v>178</v>
-      </c>
-      <c r="K9" s="111"/>
-      <c r="L9" s="111"/>
+      <c r="J9" s="103" t="s">
+        <v>177</v>
+      </c>
+      <c r="K9" s="103"/>
+      <c r="L9" s="103"/>
       <c r="M9">
         <f>Передача!$E$5</f>
         <v>320</v>
@@ -7272,30 +7759,30 @@
       <c r="N9" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="T9" s="111" t="s">
-        <v>262</v>
-      </c>
-      <c r="U9" s="111"/>
-      <c r="V9" s="111"/>
-      <c r="W9" s="111"/>
-      <c r="X9" s="111">
+      <c r="T9" s="103" t="s">
+        <v>261</v>
+      </c>
+      <c r="U9" s="103"/>
+      <c r="V9" s="103"/>
+      <c r="W9" s="103"/>
+      <c r="X9" s="103">
         <f ca="1">(X5*X5+X4*X4)/(X5*X5-X4*X4)-X6</f>
         <v>0.7</v>
       </c>
-      <c r="Y9" s="111"/>
-      <c r="Z9" s="111">
+      <c r="Y9" s="103"/>
+      <c r="Z9" s="103">
         <f ca="1">(Z5*Z5+Z4*Z4)/(Z5*Z5-Z4*Z4)+Z6</f>
         <v>5.8454545454545457</v>
       </c>
-      <c r="AA9" s="111"/>
+      <c r="AA9" s="103"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A10" s="111" t="s">
+      <c r="A10" s="103" t="s">
         <v>170</v>
       </c>
-      <c r="B10" s="111"/>
-      <c r="C10" s="111"/>
-      <c r="D10" s="111"/>
+      <c r="B10" s="103"/>
+      <c r="C10" s="103"/>
+      <c r="D10" s="103"/>
       <c r="E10">
         <f>Передача!$D$40</f>
         <v>57</v>
@@ -7303,41 +7790,41 @@
       <c r="F10" t="s">
         <v>16</v>
       </c>
-      <c r="J10" s="111" t="s">
-        <v>241</v>
-      </c>
-      <c r="K10" s="111"/>
-      <c r="L10" s="111"/>
+      <c r="J10" s="103" t="s">
+        <v>240</v>
+      </c>
+      <c r="K10" s="103"/>
+      <c r="L10" s="103"/>
       <c r="M10" s="52">
         <v>3</v>
       </c>
       <c r="N10" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="T10" s="111" t="s">
-        <v>263</v>
-      </c>
-      <c r="U10" s="111"/>
-      <c r="V10" s="111"/>
-      <c r="W10" s="111"/>
-      <c r="X10" s="111">
+        <v>243</v>
+      </c>
+      <c r="T10" s="103" t="s">
+        <v>262</v>
+      </c>
+      <c r="U10" s="103"/>
+      <c r="V10" s="103"/>
+      <c r="W10" s="103"/>
+      <c r="X10" s="103">
         <f ca="1">0.5*X8*(1-(X4*X4/X5/X5))</f>
         <v>165</v>
       </c>
-      <c r="Y10" s="111"/>
-      <c r="Z10" s="111">
+      <c r="Y10" s="103"/>
+      <c r="Z10" s="103">
         <f ca="1">0.5*Z8*(1-(Z4*Z4/Z5/Z5))</f>
         <v>50.416666666666671</v>
       </c>
-      <c r="AA10" s="111"/>
+      <c r="AA10" s="103"/>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A11" s="111" t="s">
-        <v>227</v>
-      </c>
-      <c r="B11" s="111"/>
-      <c r="C11" s="111"/>
-      <c r="D11" s="111"/>
+      <c r="A11" s="103" t="s">
+        <v>226</v>
+      </c>
+      <c r="B11" s="103"/>
+      <c r="C11" s="103"/>
+      <c r="D11" s="103"/>
       <c r="E11">
         <f>_xlfn.MINIFS($32:$32,$31:$31,"&gt;="&amp;E7)</f>
         <v>5</v>
@@ -7345,36 +7832,36 @@
       <c r="F11" t="s">
         <v>16</v>
       </c>
-      <c r="J11" s="111" t="s">
-        <v>243</v>
-      </c>
-      <c r="K11" s="111"/>
-      <c r="L11" s="111"/>
+      <c r="J11" s="103" t="s">
+        <v>242</v>
+      </c>
+      <c r="K11" s="103"/>
+      <c r="L11" s="103"/>
       <c r="M11" s="52">
         <v>0.08</v>
       </c>
       <c r="O11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A12" s="111" t="s">
+      <c r="A12" s="103" t="s">
+        <v>227</v>
+      </c>
+      <c r="B12" s="103"/>
+      <c r="C12" s="103"/>
+      <c r="D12" s="103"/>
+      <c r="E12" t="s">
         <v>228</v>
-      </c>
-      <c r="B12" s="111"/>
-      <c r="C12" s="111"/>
-      <c r="D12" s="111"/>
-      <c r="E12" t="s">
-        <v>229</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
       </c>
-      <c r="J12" s="111" t="s">
-        <v>245</v>
-      </c>
-      <c r="K12" s="111"/>
-      <c r="L12" s="111"/>
+      <c r="J12" s="103" t="s">
+        <v>244</v>
+      </c>
+      <c r="K12" s="103"/>
+      <c r="L12" s="103"/>
       <c r="M12" s="25">
         <f>E17</f>
         <v>57</v>
@@ -7383,42 +7870,42 @@
         <v>16</v>
       </c>
       <c r="O12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A13" s="131" t="s">
+      <c r="A13" s="130" t="s">
+        <v>229</v>
+      </c>
+      <c r="B13" s="103"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="103"/>
+      <c r="E13" t="s">
+        <v>231</v>
+      </c>
+      <c r="F13" t="s">
         <v>230</v>
       </c>
-      <c r="B13" s="111"/>
-      <c r="C13" s="111"/>
-      <c r="D13" s="111"/>
-      <c r="E13" t="s">
-        <v>232</v>
-      </c>
-      <c r="F13" t="s">
-        <v>231</v>
-      </c>
-      <c r="J13" s="111" t="s">
-        <v>242</v>
-      </c>
-      <c r="K13" s="111"/>
-      <c r="L13" s="111"/>
+      <c r="J13" s="103" t="s">
+        <v>241</v>
+      </c>
+      <c r="K13" s="103"/>
+      <c r="L13" s="103"/>
       <c r="M13">
         <f ca="1">2000*M10*M9/(PI()*M7*M7*M12*M11)</f>
         <v>53.610086094112106</v>
       </c>
       <c r="N13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A14" s="111" t="s">
-        <v>235</v>
-      </c>
-      <c r="B14" s="111"/>
-      <c r="C14" s="111"/>
-      <c r="D14" s="111"/>
+      <c r="A14" s="103" t="s">
+        <v>234</v>
+      </c>
+      <c r="B14" s="103"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="103"/>
       <c r="E14">
         <f>2.2*E6+0.05*E10</f>
         <v>8.35</v>
@@ -7426,70 +7913,70 @@
       <c r="F14" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="111" t="s">
-        <v>249</v>
-      </c>
-      <c r="K14" s="111"/>
-      <c r="L14" s="111"/>
+      <c r="J14" s="103" t="s">
+        <v>248</v>
+      </c>
+      <c r="K14" s="103"/>
+      <c r="L14" s="103"/>
       <c r="M14">
         <f ca="1">1000*M13*M7*(X9/X7+Z9/Z7)</f>
         <v>83.548186120694183</v>
       </c>
       <c r="N14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A15" s="111" t="s">
-        <v>233</v>
-      </c>
-      <c r="B15" s="111"/>
-      <c r="C15" s="111"/>
-      <c r="D15" s="111"/>
+      <c r="A15" s="103" t="s">
+        <v>232</v>
+      </c>
+      <c r="B15" s="103"/>
+      <c r="C15" s="103"/>
+      <c r="D15" s="103"/>
       <c r="F15" t="s">
         <v>16</v>
       </c>
-      <c r="J15" s="111" t="s">
-        <v>256</v>
-      </c>
-      <c r="K15" s="111"/>
-      <c r="L15" s="111"/>
+      <c r="J15" s="103" t="s">
+        <v>255</v>
+      </c>
+      <c r="K15" s="103"/>
+      <c r="L15" s="103"/>
       <c r="N15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O15" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A16" s="111" t="s">
-        <v>254</v>
-      </c>
-      <c r="B16" s="111"/>
-      <c r="C16" s="111"/>
-      <c r="D16" s="111"/>
+      <c r="A16" s="103" t="s">
+        <v>253</v>
+      </c>
+      <c r="B16" s="103"/>
+      <c r="C16" s="103"/>
+      <c r="D16" s="103"/>
       <c r="E16" s="52">
         <v>1</v>
       </c>
-      <c r="J16" s="111" t="s">
-        <v>257</v>
-      </c>
-      <c r="K16" s="111"/>
-      <c r="L16" s="111"/>
+      <c r="J16" s="103" t="s">
+        <v>256</v>
+      </c>
+      <c r="K16" s="103"/>
+      <c r="L16" s="103"/>
       <c r="N16" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O16" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" s="111" t="s">
-        <v>252</v>
-      </c>
-      <c r="B17" s="111"/>
-      <c r="C17" s="111"/>
-      <c r="D17" s="111"/>
+      <c r="A17" s="103" t="s">
+        <v>251</v>
+      </c>
+      <c r="B17" s="103"/>
+      <c r="C17" s="103"/>
+      <c r="D17" s="103"/>
       <c r="E17">
         <f>E10*E16</f>
         <v>57</v>
@@ -7497,29 +7984,29 @@
       <c r="F17" t="s">
         <v>16</v>
       </c>
-      <c r="J17" s="111" t="s">
-        <v>258</v>
-      </c>
-      <c r="K17" s="111"/>
-      <c r="L17" s="111"/>
+      <c r="J17" s="103" t="s">
+        <v>257</v>
+      </c>
+      <c r="K17" s="103"/>
+      <c r="L17" s="103"/>
       <c r="M17" s="52">
         <f ca="1">SUM(M14:M16)</f>
         <v>83.548186120694183</v>
       </c>
       <c r="N17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P17" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="111" t="s">
-        <v>253</v>
-      </c>
-      <c r="B18" s="111"/>
-      <c r="C18" s="111"/>
-      <c r="D18" s="111"/>
+      <c r="A18" s="103" t="s">
+        <v>252</v>
+      </c>
+      <c r="B18" s="103"/>
+      <c r="C18" s="103"/>
+      <c r="D18" s="103"/>
       <c r="E18" s="52">
         <f ca="1">M7+10</f>
         <v>60</v>
@@ -7527,37 +8014,37 @@
       <c r="F18" t="s">
         <v>16</v>
       </c>
-      <c r="J18" s="111" t="s">
-        <v>265</v>
-      </c>
-      <c r="K18" s="111"/>
-      <c r="L18" s="111"/>
+      <c r="J18" s="103" t="s">
+        <v>264</v>
+      </c>
+      <c r="K18" s="103"/>
+      <c r="L18" s="103"/>
       <c r="M18">
         <f ca="1">MAX(X10:AA10)*M14/M13</f>
         <v>257.14285714285711</v>
       </c>
       <c r="N18" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="J19" s="111" t="s">
-        <v>259</v>
-      </c>
-      <c r="K19" s="111"/>
-      <c r="L19" s="111"/>
+      <c r="J19" s="103" t="s">
+        <v>258</v>
+      </c>
+      <c r="K19" s="103"/>
+      <c r="L19" s="103"/>
       <c r="M19" s="52">
         <f ca="1">M18+M15</f>
         <v>257.14285714285711</v>
       </c>
       <c r="N19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="J20" s="111"/>
-      <c r="K20" s="111"/>
-      <c r="L20" s="111"/>
+      <c r="J20" s="103"/>
+      <c r="K20" s="103"/>
+      <c r="L20" s="103"/>
       <c r="M20">
         <v>90</v>
       </c>
@@ -7565,25 +8052,25 @@
         <v>154</v>
       </c>
       <c r="O20" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="J21" s="111" t="s">
-        <v>270</v>
-      </c>
-      <c r="K21" s="111"/>
-      <c r="L21" s="111"/>
+      <c r="J21" s="103" t="s">
+        <v>269</v>
+      </c>
+      <c r="K21" s="103"/>
+      <c r="L21" s="103"/>
       <c r="M21">
         <v>0.2</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="J22" s="111" t="s">
-        <v>269</v>
-      </c>
-      <c r="K22" s="111"/>
-      <c r="L22" s="111"/>
+      <c r="J22" s="103" t="s">
+        <v>268</v>
+      </c>
+      <c r="K22" s="103"/>
+      <c r="L22" s="103"/>
       <c r="M22">
         <f ca="1">PI()*M7*M12*(M20-M15)*M21/1000</f>
         <v>161.1637031291564</v>
@@ -7593,10 +8080,10 @@
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A30" s="111" t="s">
-        <v>187</v>
-      </c>
-      <c r="B30" s="111"/>
+      <c r="A30" s="103" t="s">
+        <v>186</v>
+      </c>
+      <c r="B30" s="103"/>
       <c r="C30">
         <v>20</v>
       </c>
@@ -7623,10 +8110,10 @@
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A31" s="111" t="s">
-        <v>188</v>
-      </c>
-      <c r="B31" s="111"/>
+      <c r="A31" s="103" t="s">
+        <v>187</v>
+      </c>
+      <c r="B31" s="103"/>
       <c r="C31">
         <v>30</v>
       </c>
@@ -7653,10 +8140,10 @@
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A32" s="111" t="s">
-        <v>220</v>
-      </c>
-      <c r="B32" s="111"/>
+      <c r="A32" s="103" t="s">
+        <v>219</v>
+      </c>
+      <c r="B32" s="103"/>
       <c r="C32">
         <v>1</v>
       </c>
@@ -7684,59 +8171,6 @@
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="T3:W3"/>
-    <mergeCell ref="T4:W4"/>
-    <mergeCell ref="T5:W5"/>
-    <mergeCell ref="T6:W6"/>
-    <mergeCell ref="T7:W7"/>
-    <mergeCell ref="T8:W8"/>
-    <mergeCell ref="T9:W9"/>
-    <mergeCell ref="T10:W10"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="X5:Y5"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="Z5:AA5"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="Z8:AA8"/>
-    <mergeCell ref="X10:Y10"/>
     <mergeCell ref="Z10:AA10"/>
     <mergeCell ref="J8:N8"/>
     <mergeCell ref="J22:L22"/>
@@ -7749,6 +8183,59 @@
     <mergeCell ref="J16:L16"/>
     <mergeCell ref="J17:L17"/>
     <mergeCell ref="J19:L19"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="Z8:AA8"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="T3:W3"/>
+    <mergeCell ref="T4:W4"/>
+    <mergeCell ref="T5:W5"/>
+    <mergeCell ref="T6:W6"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="T7:W7"/>
+    <mergeCell ref="T8:W8"/>
+    <mergeCell ref="T9:W9"/>
+    <mergeCell ref="T10:W10"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7775,12 +8262,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="111" t="s">
+      <c r="A2" s="103" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
       <c r="E2">
         <f>Передача!$D$25</f>
         <v>180</v>
@@ -7790,12 +8277,12 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="111" t="s">
-        <v>210</v>
-      </c>
-      <c r="B3" s="111"/>
-      <c r="C3" s="111"/>
-      <c r="D3" s="111"/>
+      <c r="A3" s="103" t="s">
+        <v>209</v>
+      </c>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
       <c r="E3">
         <f>Передача!$D$34</f>
         <v>49</v>
@@ -7805,12 +8292,12 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="111" t="s">
-        <v>183</v>
-      </c>
-      <c r="B4" s="111"/>
-      <c r="C4" s="111"/>
-      <c r="D4" s="111"/>
+      <c r="A4" s="103" t="s">
+        <v>182</v>
+      </c>
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
       <c r="E4">
         <f>Передача!$D$35</f>
         <v>62</v>
@@ -7820,12 +8307,12 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="111" t="s">
-        <v>211</v>
-      </c>
-      <c r="B5" s="111"/>
-      <c r="C5" s="111"/>
-      <c r="D5" s="111"/>
+      <c r="A5" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="B5" s="103"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
       <c r="E5">
         <f>Передача!$D$39</f>
         <v>321</v>
@@ -7835,12 +8322,12 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="111" t="s">
-        <v>184</v>
-      </c>
-      <c r="B6" s="111"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
+      <c r="A6" s="103" t="s">
+        <v>183</v>
+      </c>
+      <c r="B6" s="103"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
       <c r="E6">
         <f>Передача!$D$40</f>
         <v>57</v>
@@ -7850,12 +8337,12 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="111" t="s">
-        <v>209</v>
-      </c>
-      <c r="B7" s="111"/>
-      <c r="C7" s="111"/>
-      <c r="D7" s="111"/>
+      <c r="A7" s="103" t="s">
+        <v>208</v>
+      </c>
+      <c r="B7" s="103"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
       <c r="E7">
         <f>E2+E3/2+E5/2</f>
         <v>365</v>
@@ -7865,12 +8352,12 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="111" t="s">
-        <v>208</v>
-      </c>
-      <c r="B8" s="111"/>
-      <c r="C8" s="111"/>
-      <c r="D8" s="111"/>
+      <c r="A8" s="103" t="s">
+        <v>207</v>
+      </c>
+      <c r="B8" s="103"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="103"/>
       <c r="E8">
         <f>E7^(1/3)+3</f>
         <v>10.146569498815023</v>
@@ -7880,12 +8367,12 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="111" t="s">
-        <v>212</v>
-      </c>
-      <c r="B9" s="111"/>
-      <c r="C9" s="111"/>
-      <c r="D9" s="111"/>
+      <c r="A9" s="103" t="s">
+        <v>211</v>
+      </c>
+      <c r="B9" s="103"/>
+      <c r="C9" s="103"/>
+      <c r="D9" s="103"/>
       <c r="E9">
         <f>E8*3</f>
         <v>30.439708496445068</v>
@@ -7895,12 +8382,12 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="111" t="s">
-        <v>213</v>
-      </c>
-      <c r="B10" s="111"/>
-      <c r="C10" s="111"/>
-      <c r="D10" s="111"/>
+      <c r="A10" s="103" t="s">
+        <v>212</v>
+      </c>
+      <c r="B10" s="103"/>
+      <c r="C10" s="103"/>
+      <c r="D10" s="103"/>
       <c r="E10" s="52">
         <v>4</v>
       </c>
@@ -7909,12 +8396,12 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="111" t="s">
-        <v>214</v>
-      </c>
-      <c r="B11" s="111"/>
-      <c r="C11" s="111"/>
-      <c r="D11" s="111"/>
+      <c r="A11" s="103" t="s">
+        <v>213</v>
+      </c>
+      <c r="B11" s="103"/>
+      <c r="C11" s="103"/>
+      <c r="D11" s="103"/>
       <c r="E11" s="52">
         <v>20</v>
       </c>
@@ -7923,22 +8410,22 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="111" t="s">
-        <v>216</v>
-      </c>
-      <c r="B12" s="111"/>
-      <c r="C12" s="111"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="111"/>
-      <c r="F12" s="111"/>
+      <c r="A12" s="103" t="s">
+        <v>215</v>
+      </c>
+      <c r="B12" s="103"/>
+      <c r="C12" s="103"/>
+      <c r="D12" s="103"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="103"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="111" t="s">
-        <v>215</v>
-      </c>
-      <c r="B13" s="111"/>
-      <c r="C13" s="111"/>
-      <c r="D13" s="111"/>
+      <c r="A13" s="103" t="s">
+        <v>214</v>
+      </c>
+      <c r="B13" s="103"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="103"/>
       <c r="E13">
         <f>E7+2*E8+E10*2+E11*2</f>
         <v>433.29313899763002</v>
@@ -7948,12 +8435,12 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="111" t="s">
+      <c r="A14" s="103" t="s">
         <v>170</v>
       </c>
-      <c r="B14" s="111"/>
-      <c r="C14" s="111"/>
-      <c r="D14" s="111"/>
+      <c r="B14" s="103"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="103"/>
       <c r="E14">
         <f>E4+2*E8+2*E10</f>
         <v>90.293138997630052</v>
@@ -7963,12 +8450,12 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="111" t="s">
+      <c r="A15" s="103" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="111"/>
-      <c r="C15" s="111"/>
-      <c r="D15" s="111"/>
+      <c r="B15" s="103"/>
+      <c r="C15" s="103"/>
+      <c r="D15" s="103"/>
       <c r="E15">
         <f>E5+E8+E9+2*E10</f>
         <v>369.5862779952601</v>
@@ -7980,41 +8467,55 @@
     <row r="20" spans="18:23" x14ac:dyDescent="0.3">
       <c r="R20" s="1"/>
       <c r="S20" s="36"/>
-      <c r="T20" s="111" t="s">
+      <c r="T20" s="103" t="s">
         <v>129</v>
       </c>
-      <c r="U20" s="111"/>
-      <c r="V20" s="83" t="s">
+      <c r="U20" s="103"/>
+      <c r="V20" s="79" t="s">
         <v>125</v>
       </c>
-      <c r="W20" s="83"/>
+      <c r="W20" s="79"/>
     </row>
     <row r="21" spans="18:23" x14ac:dyDescent="0.3">
-      <c r="R21" s="86" t="s">
+      <c r="R21" s="112" t="s">
         <v>124</v>
       </c>
-      <c r="S21" s="86"/>
-      <c r="T21" s="83"/>
-      <c r="U21" s="83"/>
-      <c r="V21" s="83"/>
-      <c r="W21" s="83"/>
+      <c r="S21" s="112"/>
+      <c r="T21" s="79"/>
+      <c r="U21" s="79"/>
+      <c r="V21" s="79"/>
+      <c r="W21" s="79"/>
     </row>
     <row r="22" spans="18:23" x14ac:dyDescent="0.3">
-      <c r="R22" s="86" t="s">
+      <c r="R22" s="112" t="s">
         <v>126</v>
       </c>
-      <c r="S22" s="86"/>
-      <c r="T22" s="83" t="s">
+      <c r="S22" s="112"/>
+      <c r="T22" s="79" t="s">
         <v>127</v>
       </c>
-      <c r="U22" s="83"/>
-      <c r="V22" s="80" t="s">
+      <c r="U22" s="79"/>
+      <c r="V22" s="91" t="s">
         <v>128</v>
       </c>
-      <c r="W22" s="80"/>
+      <c r="W22" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A3:D3"/>
     <mergeCell ref="V22:W22"/>
     <mergeCell ref="T22:U22"/>
     <mergeCell ref="R22:S22"/>
@@ -8023,20 +8524,6 @@
     <mergeCell ref="V20:W20"/>
     <mergeCell ref="T21:U21"/>
     <mergeCell ref="V21:W21"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -8050,7 +8537,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="111">
+      <c r="A1" s="103">
         <v>1</v>
       </c>
       <c r="B1">
@@ -8059,14 +8546,14 @@
       <c r="D1" s="48"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="111"/>
+      <c r="A2" s="103"/>
       <c r="B2">
         <v>1.05</v>
       </c>
       <c r="D2" s="48"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="111">
+      <c r="A3" s="103">
         <v>1.1000000000000001</v>
       </c>
       <c r="B3">
@@ -8075,14 +8562,14 @@
       <c r="D3" s="48"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="111"/>
+      <c r="A4" s="103"/>
       <c r="B4">
         <v>1.1499999999999999</v>
       </c>
       <c r="D4" s="48"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="111">
+      <c r="A5" s="103">
         <v>1.2</v>
       </c>
       <c r="B5">
@@ -8091,14 +8578,14 @@
       <c r="D5" s="48"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="111"/>
+      <c r="A6" s="103"/>
       <c r="B6">
         <v>1.3</v>
       </c>
       <c r="D6" s="48"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="111">
+      <c r="A7" s="103">
         <v>1.4</v>
       </c>
       <c r="B7">
@@ -8107,14 +8594,14 @@
       <c r="D7" s="48"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="111"/>
+      <c r="A8" s="103"/>
       <c r="B8">
         <v>1.5</v>
       </c>
       <c r="D8" s="48"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="111">
+      <c r="A9" s="103">
         <v>1.6</v>
       </c>
       <c r="B9">
@@ -8123,14 +8610,14 @@
       <c r="D9" s="48"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="111"/>
+      <c r="A10" s="103"/>
       <c r="B10">
         <v>1.7</v>
       </c>
       <c r="D10" s="48"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="111">
+      <c r="A11" s="103">
         <v>1.8</v>
       </c>
       <c r="B11">
@@ -8139,14 +8626,14 @@
       <c r="D11" s="48"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="111"/>
+      <c r="A12" s="103"/>
       <c r="B12">
         <v>1.9</v>
       </c>
       <c r="D12" s="48"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="111">
+      <c r="A13" s="103">
         <v>2</v>
       </c>
       <c r="B13">
@@ -8155,14 +8642,14 @@
       <c r="D13" s="48"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="111"/>
+      <c r="A14" s="103"/>
       <c r="B14">
         <v>2.1</v>
       </c>
       <c r="D14" s="48"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="111">
+      <c r="A15" s="103">
         <v>2.2000000000000002</v>
       </c>
       <c r="B15">
@@ -8171,14 +8658,14 @@
       <c r="D15" s="48"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="111"/>
+      <c r="A16" s="103"/>
       <c r="B16">
         <v>2.4</v>
       </c>
       <c r="D16" s="48"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="111">
+      <c r="A17" s="103">
         <v>2.5</v>
       </c>
       <c r="B17">
@@ -8187,14 +8674,14 @@
       <c r="D17" s="48"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="111"/>
+      <c r="A18" s="103"/>
       <c r="B18">
         <v>2.6</v>
       </c>
       <c r="D18" s="48"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="111">
+      <c r="A19" s="103">
         <v>2.8</v>
       </c>
       <c r="B19">
@@ -8203,14 +8690,14 @@
       <c r="D19" s="48"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="111"/>
+      <c r="A20" s="103"/>
       <c r="B20">
         <v>3</v>
       </c>
       <c r="D20" s="48"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="111">
+      <c r="A21" s="103">
         <v>3.2</v>
       </c>
       <c r="B21">
@@ -8219,14 +8706,14 @@
       <c r="D21" s="48"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="111"/>
+      <c r="A22" s="103"/>
       <c r="B22">
         <v>3.4</v>
       </c>
       <c r="D22" s="48"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="111">
+      <c r="A23" s="103">
         <v>3.6</v>
       </c>
       <c r="B23">
@@ -8235,14 +8722,14 @@
       <c r="D23" s="48"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="111"/>
+      <c r="A24" s="103"/>
       <c r="B24">
         <v>3.8</v>
       </c>
       <c r="D24" s="48"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="111">
+      <c r="A25" s="103">
         <v>4</v>
       </c>
       <c r="B25">
@@ -8251,14 +8738,14 @@
       <c r="D25" s="48"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="111"/>
+      <c r="A26" s="103"/>
       <c r="B26">
         <v>4.2</v>
       </c>
       <c r="D26" s="48"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="111">
+      <c r="A27" s="103">
         <v>4.5</v>
       </c>
       <c r="B27">
@@ -8267,14 +8754,14 @@
       <c r="D27" s="48"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="111"/>
+      <c r="A28" s="103"/>
       <c r="B28">
         <v>4.8</v>
       </c>
       <c r="D28" s="48"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="111">
+      <c r="A29" s="103">
         <v>5</v>
       </c>
       <c r="B29">
@@ -8283,14 +8770,14 @@
       <c r="D29" s="48"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="111"/>
+      <c r="A30" s="103"/>
       <c r="B30">
         <v>5.3</v>
       </c>
       <c r="D30" s="48"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="111">
+      <c r="A31" s="103">
         <v>5.6</v>
       </c>
       <c r="B31">
@@ -8299,14 +8786,14 @@
       <c r="D31" s="48"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="111"/>
+      <c r="A32" s="103"/>
       <c r="B32">
         <v>6</v>
       </c>
       <c r="D32" s="48"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="111">
+      <c r="A33" s="103">
         <v>6.3</v>
       </c>
       <c r="B33">
@@ -8315,14 +8802,14 @@
       <c r="D33" s="48"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="111"/>
+      <c r="A34" s="103"/>
       <c r="B34">
         <v>6.7</v>
       </c>
       <c r="D34" s="48"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="111">
+      <c r="A35" s="103">
         <v>7.1</v>
       </c>
       <c r="B35">
@@ -8331,14 +8818,14 @@
       <c r="D35" s="48"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="111"/>
+      <c r="A36" s="103"/>
       <c r="B36">
         <v>7.5</v>
       </c>
       <c r="D36" s="48"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="111">
+      <c r="A37" s="103">
         <v>8</v>
       </c>
       <c r="B37">
@@ -8347,14 +8834,14 @@
       <c r="D37" s="48"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="111"/>
+      <c r="A38" s="103"/>
       <c r="B38">
         <v>8.5</v>
       </c>
       <c r="D38" s="48"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="111">
+      <c r="A39" s="103">
         <v>9</v>
       </c>
       <c r="B39">
@@ -8363,7 +8850,7 @@
       <c r="D39" s="48"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="111"/>
+      <c r="A40" s="103"/>
       <c r="B40" s="67">
         <v>9.5</v>
       </c>
@@ -8371,7 +8858,7 @@
       <c r="E40" s="67"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="111">
+      <c r="A41" s="103">
         <v>10</v>
       </c>
       <c r="B41" s="48">
@@ -8379,13 +8866,13 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="111"/>
+      <c r="A42" s="103"/>
       <c r="B42" s="48">
         <v>10.5</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="111">
+      <c r="A43" s="103">
         <v>11</v>
       </c>
       <c r="B43" s="48">
@@ -8393,13 +8880,13 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="111"/>
+      <c r="A44" s="103"/>
       <c r="B44" s="48">
         <v>11.5</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="111">
+      <c r="A45" s="103">
         <v>12</v>
       </c>
       <c r="B45" s="48">
@@ -8407,13 +8894,13 @@
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="111"/>
+      <c r="A46" s="103"/>
       <c r="B46" s="48">
         <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="111">
+      <c r="A47" s="103">
         <v>14</v>
       </c>
       <c r="B47" s="48">
@@ -8421,13 +8908,13 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="111"/>
+      <c r="A48" s="103"/>
       <c r="B48" s="48">
         <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="111">
+      <c r="A49" s="103">
         <v>16</v>
       </c>
       <c r="B49" s="48">
@@ -8435,13 +8922,13 @@
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="111"/>
+      <c r="A50" s="103"/>
       <c r="B50" s="48">
         <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="111">
+      <c r="A51" s="103">
         <v>18</v>
       </c>
       <c r="B51" s="48">
@@ -8449,13 +8936,13 @@
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="111"/>
+      <c r="A52" s="103"/>
       <c r="B52" s="48">
         <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="111">
+      <c r="A53" s="103">
         <v>20</v>
       </c>
       <c r="B53" s="48">
@@ -8463,13 +8950,13 @@
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="111"/>
+      <c r="A54" s="103"/>
       <c r="B54" s="48">
         <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="111">
+      <c r="A55" s="103">
         <v>22</v>
       </c>
       <c r="B55" s="48">
@@ -8477,13 +8964,13 @@
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="111"/>
+      <c r="A56" s="103"/>
       <c r="B56" s="48">
         <v>24</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="111">
+      <c r="A57" s="103">
         <v>25</v>
       </c>
       <c r="B57" s="48">
@@ -8491,13 +8978,13 @@
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="111"/>
+      <c r="A58" s="103"/>
       <c r="B58" s="48">
         <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="111">
+      <c r="A59" s="103">
         <v>28</v>
       </c>
       <c r="B59" s="48">
@@ -8505,13 +8992,13 @@
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="111"/>
+      <c r="A60" s="103"/>
       <c r="B60" s="48">
         <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="111">
+      <c r="A61" s="103">
         <v>32</v>
       </c>
       <c r="B61" s="48">
@@ -8519,13 +9006,13 @@
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="111"/>
+      <c r="A62" s="103"/>
       <c r="B62" s="48">
         <v>34</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="111">
+      <c r="A63" s="103">
         <v>36</v>
       </c>
       <c r="B63" s="48">
@@ -8533,13 +9020,13 @@
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="111"/>
+      <c r="A64" s="103"/>
       <c r="B64" s="48">
         <v>38</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="111">
+      <c r="A65" s="103">
         <v>40</v>
       </c>
       <c r="B65" s="48">
@@ -8547,13 +9034,13 @@
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="111"/>
+      <c r="A66" s="103"/>
       <c r="B66" s="48">
         <v>42</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="111">
+      <c r="A67" s="103">
         <v>45</v>
       </c>
       <c r="B67" s="48">
@@ -8561,13 +9048,13 @@
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="111"/>
+      <c r="A68" s="103"/>
       <c r="B68" s="48">
         <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="111">
+      <c r="A69" s="103">
         <v>50</v>
       </c>
       <c r="B69" s="48">
@@ -8575,13 +9062,13 @@
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="111"/>
+      <c r="A70" s="103"/>
       <c r="B70" s="48">
         <v>53</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="111">
+      <c r="A71" s="103">
         <v>56</v>
       </c>
       <c r="B71" s="48">
@@ -8589,13 +9076,13 @@
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="111"/>
+      <c r="A72" s="103"/>
       <c r="B72" s="48">
         <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="111">
+      <c r="A73" s="103">
         <v>63</v>
       </c>
       <c r="B73" s="48">
@@ -8603,13 +9090,13 @@
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="111"/>
+      <c r="A74" s="103"/>
       <c r="B74" s="48">
         <v>67</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="111">
+      <c r="A75" s="103">
         <v>71</v>
       </c>
       <c r="B75" s="48">
@@ -8617,13 +9104,13 @@
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="111"/>
+      <c r="A76" s="103"/>
       <c r="B76" s="48">
         <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="111">
+      <c r="A77" s="103">
         <v>80</v>
       </c>
       <c r="B77" s="48">
@@ -8631,13 +9118,13 @@
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="111"/>
+      <c r="A78" s="103"/>
       <c r="B78" s="48">
         <v>85</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="111">
+      <c r="A79" s="103">
         <v>90</v>
       </c>
       <c r="B79" s="48">
@@ -8645,13 +9132,41 @@
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="111"/>
+      <c r="A80" s="103"/>
       <c r="B80" s="48">
         <v>95</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A35:A36"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="A3:A4"/>
@@ -8664,34 +9179,6 @@
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="A75:A76"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Расчёт.xlsx
+++ b/Расчёт.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Professional\Downloads\интститут\курсач детмаш\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47BA657E-D501-4226-8FA1-18493E15D140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE4C7D0-4789-4711-952D-24C01F6BAB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="812" activeTab="1" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="812" activeTab="2" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
   </bookViews>
   <sheets>
     <sheet name="Электродвигатель" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="321">
   <si>
     <t>Окружная сила</t>
   </si>
@@ -457,9 +457,6 @@
     <t>Вопросы:</t>
   </si>
   <si>
-    <t>Как определить квалитет от массовости производтсва?</t>
-  </si>
-  <si>
     <t>Нормальный</t>
   </si>
   <si>
@@ -751,9 +748,6 @@
     <t>Соединение с натягом</t>
   </si>
   <si>
-    <t>Как соединяется тихоходный вал с барабаном</t>
-  </si>
-  <si>
     <t>Установка - с натягом</t>
   </si>
   <si>
@@ -1004,6 +998,18 @@
   </si>
   <si>
     <t>Шероховатость вала Ra</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>страниа 178</t>
+  </si>
+  <si>
+    <t>фланец в приложении</t>
+  </si>
+  <si>
+    <t>манжетта</t>
   </si>
 </sst>
 </file>
@@ -1343,34 +1349,45 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1379,37 +1396,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1439,34 +1444,76 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1478,62 +1525,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1653,16 +1659,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>373380</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>46629</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>99709</xdr:rowOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>381909</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>8269</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1685,7 +1691,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8839200" y="2217420"/>
+          <a:off x="7345680" y="2308860"/>
           <a:ext cx="6516009" cy="4648849"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2138,23 +2144,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="97" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A2" s="89" t="s">
+      <c r="A2" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
       <c r="E2" s="19">
         <v>4</v>
       </c>
@@ -2162,22 +2168,22 @@
         <v>4</v>
       </c>
       <c r="G2" s="6"/>
-      <c r="I2" s="89" t="s">
+      <c r="I2" s="97" t="s">
         <v>54</v>
       </c>
-      <c r="J2" s="82"/>
-      <c r="K2" s="82"/>
-      <c r="L2" s="82"/>
-      <c r="M2" s="82">
+      <c r="J2" s="98"/>
+      <c r="K2" s="98"/>
+      <c r="L2" s="98"/>
+      <c r="M2" s="98">
         <f>E2*E3</f>
         <v>6.4</v>
       </c>
-      <c r="N2" s="97"/>
-      <c r="Q2" s="89" t="s">
+      <c r="N2" s="99"/>
+      <c r="Q2" s="97" t="s">
         <v>29</v>
       </c>
-      <c r="R2" s="82"/>
-      <c r="S2" s="82"/>
+      <c r="R2" s="98"/>
+      <c r="S2" s="98"/>
       <c r="T2" s="8" t="s">
         <v>30</v>
       </c>
@@ -2187,11 +2193,11 @@
       <c r="V2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AC2" s="89" t="s">
+      <c r="AC2" s="97" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="82"/>
-      <c r="AE2" s="82"/>
+      <c r="AD2" s="98"/>
+      <c r="AE2" s="98"/>
       <c r="AF2" s="8" t="s">
         <v>44</v>
       </c>
@@ -2210,12 +2216,12 @@
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
       <c r="E3" s="20">
         <v>1.6</v>
       </c>
@@ -2223,19 +2229,19 @@
         <v>5</v>
       </c>
       <c r="G3" s="3"/>
-      <c r="I3" s="81" t="s">
+      <c r="I3" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="75"/>
-      <c r="K3" s="75"/>
-      <c r="L3" s="75"/>
-      <c r="M3" s="75"/>
-      <c r="N3" s="92"/>
-      <c r="Q3" s="81" t="s">
+      <c r="J3" s="94"/>
+      <c r="K3" s="94"/>
+      <c r="L3" s="94"/>
+      <c r="M3" s="94"/>
+      <c r="N3" s="105"/>
+      <c r="Q3" s="93" t="s">
         <v>134</v>
       </c>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
+      <c r="R3" s="94"/>
+      <c r="S3" s="94"/>
       <c r="T3" s="1">
         <v>0.96</v>
       </c>
@@ -2246,11 +2252,11 @@
         <f>AVERAGE(T3:U3)</f>
         <v>0.97</v>
       </c>
-      <c r="AC3" s="81" t="s">
+      <c r="AC3" s="93" t="s">
         <v>133</v>
       </c>
-      <c r="AD3" s="75"/>
-      <c r="AE3" s="75"/>
+      <c r="AD3" s="94"/>
+      <c r="AE3" s="94"/>
       <c r="AF3" s="1">
         <v>1.6</v>
       </c>
@@ -2275,30 +2281,30 @@
       </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A4" s="81" t="s">
+      <c r="A4" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="90" t="s">
+      <c r="B4" s="94"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="90"/>
-      <c r="G4" s="91"/>
-      <c r="I4" s="81" t="s">
+      <c r="F4" s="102"/>
+      <c r="G4" s="108"/>
+      <c r="I4" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="75"/>
-      <c r="K4" s="75"/>
-      <c r="L4" s="75"/>
-      <c r="M4" s="75"/>
-      <c r="N4" s="92"/>
-      <c r="Q4" s="81" t="s">
+      <c r="J4" s="94"/>
+      <c r="K4" s="94"/>
+      <c r="L4" s="94"/>
+      <c r="M4" s="94"/>
+      <c r="N4" s="105"/>
+      <c r="Q4" s="93" t="s">
         <v>49</v>
       </c>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
+      <c r="R4" s="94"/>
+      <c r="S4" s="94"/>
       <c r="T4" s="1">
         <v>0.95</v>
       </c>
@@ -2309,11 +2315,11 @@
         <f t="shared" ref="V4:V12" si="1">AVERAGE(T4:U4)</f>
         <v>0.96</v>
       </c>
-      <c r="AC4" s="81" t="s">
+      <c r="AC4" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="AD4" s="75"/>
-      <c r="AE4" s="75"/>
+      <c r="AD4" s="94"/>
+      <c r="AE4" s="94"/>
       <c r="AF4" s="1">
         <v>1</v>
       </c>
@@ -2338,12 +2344,12 @@
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="75"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
       <c r="E5" s="21">
         <v>10000</v>
       </c>
@@ -2353,19 +2359,19 @@
       <c r="G5" s="3"/>
       <c r="I5" s="7"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="75" t="s">
+      <c r="K5" s="94" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="75"/>
-      <c r="M5" s="75" t="s">
+      <c r="L5" s="94"/>
+      <c r="M5" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="92"/>
-      <c r="Q5" s="81" t="s">
+      <c r="N5" s="105"/>
+      <c r="Q5" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="R5" s="75"/>
-      <c r="S5" s="75"/>
+      <c r="R5" s="94"/>
+      <c r="S5" s="94"/>
       <c r="T5" s="1">
         <v>0.95</v>
       </c>
@@ -2376,11 +2382,11 @@
         <f t="shared" si="1"/>
         <v>0.96</v>
       </c>
-      <c r="AC5" s="81" t="s">
+      <c r="AC5" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="AD5" s="75"/>
-      <c r="AE5" s="75"/>
+      <c r="AD5" s="94"/>
+      <c r="AE5" s="94"/>
       <c r="AF5" s="1">
         <v>3.15</v>
       </c>
@@ -2405,34 +2411,34 @@
       </c>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A6" s="81" t="s">
+      <c r="A6" s="93" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="75"/>
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
+      <c r="B6" s="94"/>
+      <c r="C6" s="94"/>
+      <c r="D6" s="94"/>
       <c r="E6" s="21">
         <v>0.9</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="3"/>
-      <c r="I6" s="81" t="s">
+      <c r="I6" s="93" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="75"/>
-      <c r="K6" s="90">
+      <c r="J6" s="94"/>
+      <c r="K6" s="102">
         <v>2</v>
       </c>
-      <c r="L6" s="90"/>
-      <c r="M6" s="75">
+      <c r="L6" s="102"/>
+      <c r="M6" s="94">
         <v>0.99</v>
       </c>
-      <c r="N6" s="92"/>
-      <c r="Q6" s="81" t="s">
+      <c r="N6" s="105"/>
+      <c r="Q6" s="93" t="s">
         <v>33</v>
       </c>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75"/>
+      <c r="R6" s="94"/>
+      <c r="S6" s="94"/>
       <c r="T6" s="1">
         <v>0.92</v>
       </c>
@@ -2443,11 +2449,11 @@
         <f t="shared" si="1"/>
         <v>0.94</v>
       </c>
-      <c r="AC6" s="81" t="s">
+      <c r="AC6" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="AD6" s="75"/>
-      <c r="AE6" s="75"/>
+      <c r="AD6" s="94"/>
+      <c r="AE6" s="94"/>
       <c r="AF6" s="1">
         <v>12.5</v>
       </c>
@@ -2472,34 +2478,34 @@
       </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A7" s="81" t="s">
+      <c r="A7" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="75"/>
-      <c r="C7" s="75"/>
-      <c r="D7" s="75"/>
+      <c r="B7" s="94"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
       <c r="E7" s="21">
         <v>3</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="3"/>
-      <c r="I7" s="81" t="s">
+      <c r="I7" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="75"/>
-      <c r="K7" s="90">
+      <c r="J7" s="94"/>
+      <c r="K7" s="102">
         <v>2</v>
       </c>
-      <c r="L7" s="90"/>
-      <c r="M7" s="75">
+      <c r="L7" s="102"/>
+      <c r="M7" s="94">
         <v>0.98</v>
       </c>
-      <c r="N7" s="92"/>
-      <c r="Q7" s="81" t="s">
+      <c r="N7" s="105"/>
+      <c r="Q7" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="R7" s="75"/>
-      <c r="S7" s="75"/>
+      <c r="R7" s="94"/>
+      <c r="S7" s="94"/>
       <c r="T7" s="1">
         <v>0.72</v>
       </c>
@@ -2510,11 +2516,11 @@
         <f t="shared" si="1"/>
         <v>0.77</v>
       </c>
-      <c r="AC7" s="81" t="s">
+      <c r="AC7" s="93" t="s">
         <v>33</v>
       </c>
-      <c r="AD7" s="75"/>
-      <c r="AE7" s="75"/>
+      <c r="AD7" s="94"/>
+      <c r="AE7" s="94"/>
       <c r="AF7" s="1">
         <v>16</v>
       </c>
@@ -2539,35 +2545,35 @@
       </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A8" s="85" t="s">
+      <c r="A8" s="100" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="86"/>
-      <c r="C8" s="86"/>
-      <c r="D8" s="86"/>
+      <c r="B8" s="101"/>
+      <c r="C8" s="101"/>
+      <c r="D8" s="101"/>
       <c r="E8" s="22">
         <v>2.2000000000000002</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="5"/>
-      <c r="I8" s="81" t="s">
-        <v>266</v>
-      </c>
-      <c r="J8" s="75"/>
-      <c r="K8" s="90">
+      <c r="I8" s="93" t="s">
+        <v>264</v>
+      </c>
+      <c r="J8" s="94"/>
+      <c r="K8" s="102">
         <v>0</v>
       </c>
-      <c r="L8" s="90"/>
-      <c r="M8" s="107">
+      <c r="L8" s="102"/>
+      <c r="M8" s="103">
         <f>V11</f>
         <v>0.95</v>
       </c>
-      <c r="N8" s="112"/>
-      <c r="Q8" s="81" t="s">
+      <c r="N8" s="104"/>
+      <c r="Q8" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="R8" s="75"/>
-      <c r="S8" s="75"/>
+      <c r="R8" s="94"/>
+      <c r="S8" s="94"/>
       <c r="T8" s="1">
         <v>0.7</v>
       </c>
@@ -2578,11 +2584,11 @@
         <f t="shared" si="1"/>
         <v>0.75</v>
       </c>
-      <c r="AC8" s="81" t="s">
+      <c r="AC8" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="AD8" s="75"/>
-      <c r="AE8" s="75"/>
+      <c r="AD8" s="94"/>
+      <c r="AE8" s="94"/>
       <c r="AF8" s="1">
         <v>10</v>
       </c>
@@ -2607,31 +2613,31 @@
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A9" s="98" t="s">
+      <c r="A9" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="99"/>
-      <c r="C9" s="99"/>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="99"/>
-      <c r="G9" s="100"/>
-      <c r="I9" s="81" t="s">
+      <c r="B9" s="110"/>
+      <c r="C9" s="110"/>
+      <c r="D9" s="110"/>
+      <c r="E9" s="110"/>
+      <c r="F9" s="110"/>
+      <c r="G9" s="111"/>
+      <c r="I9" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="J9" s="75"/>
-      <c r="K9" s="75"/>
-      <c r="L9" s="75"/>
-      <c r="M9" s="76">
+      <c r="J9" s="94"/>
+      <c r="K9" s="94"/>
+      <c r="L9" s="94"/>
+      <c r="M9" s="106">
         <f>M7^K7*M6^K6*M8^K8</f>
         <v>0.94128803999999988</v>
       </c>
-      <c r="N9" s="110"/>
-      <c r="Q9" s="81" t="s">
+      <c r="N9" s="107"/>
+      <c r="Q9" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="R9" s="75"/>
-      <c r="S9" s="75"/>
+      <c r="R9" s="94"/>
+      <c r="S9" s="94"/>
       <c r="T9" s="1">
         <v>0.75</v>
       </c>
@@ -2642,11 +2648,11 @@
         <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="AC9" s="81" t="s">
+      <c r="AC9" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="AD9" s="75"/>
-      <c r="AE9" s="75"/>
+      <c r="AD9" s="94"/>
+      <c r="AE9" s="94"/>
       <c r="AF9" s="1">
         <v>8</v>
       </c>
@@ -2671,30 +2677,30 @@
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A10" s="101" t="s">
+      <c r="A10" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="102"/>
-      <c r="C10" s="102"/>
-      <c r="D10" s="102"/>
-      <c r="E10" s="102"/>
-      <c r="F10" s="102"/>
-      <c r="G10" s="103"/>
-      <c r="I10" s="81" t="s">
+      <c r="B10" s="113"/>
+      <c r="C10" s="113"/>
+      <c r="D10" s="113"/>
+      <c r="E10" s="113"/>
+      <c r="F10" s="113"/>
+      <c r="G10" s="114"/>
+      <c r="I10" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="J10" s="75"/>
-      <c r="K10" s="75"/>
-      <c r="L10" s="75"/>
-      <c r="M10" s="90">
+      <c r="J10" s="94"/>
+      <c r="K10" s="94"/>
+      <c r="L10" s="94"/>
+      <c r="M10" s="102">
         <v>0.97</v>
       </c>
-      <c r="N10" s="91"/>
-      <c r="Q10" s="81" t="s">
+      <c r="N10" s="108"/>
+      <c r="Q10" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="R10" s="75"/>
-      <c r="S10" s="75"/>
+      <c r="R10" s="94"/>
+      <c r="S10" s="94"/>
       <c r="T10" s="1">
         <v>0.8</v>
       </c>
@@ -2705,11 +2711,11 @@
         <f t="shared" si="1"/>
         <v>0.85000000000000009</v>
       </c>
-      <c r="AC10" s="85" t="s">
+      <c r="AC10" s="100" t="s">
         <v>34</v>
       </c>
-      <c r="AD10" s="86"/>
-      <c r="AE10" s="86"/>
+      <c r="AD10" s="101"/>
+      <c r="AE10" s="101"/>
       <c r="AF10" s="4">
         <v>70</v>
       </c>
@@ -2734,31 +2740,31 @@
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A11" s="98" t="s">
+      <c r="A11" s="109" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="99"/>
-      <c r="C11" s="99"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="99"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="100"/>
-      <c r="I11" s="85" t="s">
+      <c r="B11" s="110"/>
+      <c r="C11" s="110"/>
+      <c r="D11" s="110"/>
+      <c r="E11" s="110"/>
+      <c r="F11" s="110"/>
+      <c r="G11" s="111"/>
+      <c r="I11" s="100" t="s">
         <v>55</v>
       </c>
-      <c r="J11" s="86"/>
-      <c r="K11" s="86"/>
-      <c r="L11" s="86"/>
-      <c r="M11" s="87">
+      <c r="J11" s="101"/>
+      <c r="K11" s="101"/>
+      <c r="L11" s="101"/>
+      <c r="M11" s="95">
         <f>M2/M10/M9</f>
         <v>7.0094783572623509</v>
       </c>
-      <c r="N11" s="111"/>
-      <c r="Q11" s="81" t="s">
+      <c r="N11" s="96"/>
+      <c r="Q11" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="R11" s="75"/>
-      <c r="S11" s="75"/>
+      <c r="R11" s="94"/>
+      <c r="S11" s="94"/>
       <c r="T11" s="1">
         <v>0.94</v>
       </c>
@@ -2777,22 +2783,22 @@
       <c r="AH11" s="1"/>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A12" s="89" t="s">
+      <c r="A12" s="97" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="82"/>
-      <c r="C12" s="82"/>
-      <c r="D12" s="82"/>
-      <c r="E12" s="82" t="s">
+      <c r="B12" s="98"/>
+      <c r="C12" s="98"/>
+      <c r="D12" s="98"/>
+      <c r="E12" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="82"/>
-      <c r="G12" s="97"/>
-      <c r="Q12" s="85" t="s">
+      <c r="F12" s="98"/>
+      <c r="G12" s="99"/>
+      <c r="Q12" s="100" t="s">
         <v>39</v>
       </c>
-      <c r="R12" s="86"/>
-      <c r="S12" s="86"/>
+      <c r="R12" s="101"/>
+      <c r="S12" s="101"/>
       <c r="T12" s="4">
         <v>0.92</v>
       </c>
@@ -2808,12 +2814,12 @@
       </c>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A13" s="81" t="s">
+      <c r="A13" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="75"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
+      <c r="B13" s="94"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="94"/>
       <c r="E13" s="21">
         <v>400</v>
       </c>
@@ -2828,12 +2834,12 @@
       </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A14" s="81" t="s">
+      <c r="A14" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="75"/>
-      <c r="C14" s="75"/>
-      <c r="D14" s="75"/>
+      <c r="B14" s="94"/>
+      <c r="C14" s="94"/>
+      <c r="D14" s="94"/>
       <c r="E14" s="21">
         <v>400</v>
       </c>
@@ -2843,12 +2849,12 @@
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A15" s="85" t="s">
+      <c r="A15" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="86"/>
-      <c r="C15" s="86"/>
-      <c r="D15" s="86"/>
+      <c r="B15" s="101"/>
+      <c r="C15" s="101"/>
+      <c r="D15" s="101"/>
       <c r="E15" s="22">
         <v>300</v>
       </c>
@@ -2858,40 +2864,40 @@
       <c r="G15" s="5"/>
     </row>
     <row r="19" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I19" s="89" t="s">
+      <c r="I19" s="97" t="s">
         <v>123</v>
       </c>
-      <c r="J19" s="97"/>
-      <c r="K19" s="89">
+      <c r="J19" s="99"/>
+      <c r="K19" s="97">
         <v>3000</v>
       </c>
-      <c r="L19" s="82"/>
-      <c r="M19" s="82"/>
-      <c r="N19" s="97"/>
-      <c r="O19" s="82">
+      <c r="L19" s="98"/>
+      <c r="M19" s="98"/>
+      <c r="N19" s="99"/>
+      <c r="O19" s="98">
         <v>1500</v>
       </c>
-      <c r="P19" s="82"/>
-      <c r="Q19" s="82"/>
-      <c r="R19" s="82"/>
-      <c r="S19" s="89">
+      <c r="P19" s="98"/>
+      <c r="Q19" s="98"/>
+      <c r="R19" s="98"/>
+      <c r="S19" s="97">
         <v>1000</v>
       </c>
-      <c r="T19" s="82"/>
-      <c r="U19" s="82"/>
-      <c r="V19" s="97"/>
-      <c r="W19" s="82">
+      <c r="T19" s="98"/>
+      <c r="U19" s="98"/>
+      <c r="V19" s="99"/>
+      <c r="W19" s="98">
         <v>750</v>
       </c>
-      <c r="X19" s="82"/>
-      <c r="Y19" s="82"/>
-      <c r="Z19" s="97"/>
+      <c r="X19" s="98"/>
+      <c r="Y19" s="98"/>
+      <c r="Z19" s="99"/>
     </row>
     <row r="20" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I20" s="85" t="s">
+      <c r="I20" s="100" t="s">
         <v>118</v>
       </c>
-      <c r="J20" s="109"/>
+      <c r="J20" s="119"/>
       <c r="K20" s="12" t="s">
         <v>72</v>
       </c>
@@ -2942,10 +2948,10 @@
       </c>
     </row>
     <row r="21" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I21" s="81">
+      <c r="I21" s="93">
         <v>0.37</v>
       </c>
-      <c r="J21" s="75"/>
+      <c r="J21" s="94"/>
       <c r="K21" s="26" t="s">
         <v>57</v>
       </c>
@@ -2980,10 +2986,10 @@
       <c r="Z21" s="3"/>
     </row>
     <row r="22" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I22" s="81">
+      <c r="I22" s="93">
         <v>0.55000000000000004</v>
       </c>
-      <c r="J22" s="75"/>
+      <c r="J22" s="94"/>
       <c r="K22" s="26" t="s">
         <v>57</v>
       </c>
@@ -3016,10 +3022,10 @@
       <c r="Z22" s="3"/>
     </row>
     <row r="23" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I23" s="81">
+      <c r="I23" s="93">
         <v>0.75</v>
       </c>
-      <c r="J23" s="75"/>
+      <c r="J23" s="94"/>
       <c r="K23" s="7" t="s">
         <v>58</v>
       </c>
@@ -3052,10 +3058,10 @@
       <c r="Z23" s="3"/>
     </row>
     <row r="24" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I24" s="81">
+      <c r="I24" s="93">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J24" s="75"/>
+      <c r="J24" s="94"/>
       <c r="K24" s="7" t="s">
         <v>59</v>
       </c>
@@ -3088,10 +3094,10 @@
       <c r="Z24" s="3"/>
     </row>
     <row r="25" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I25" s="81">
+      <c r="I25" s="93">
         <v>1.5</v>
       </c>
-      <c r="J25" s="75"/>
+      <c r="J25" s="94"/>
       <c r="K25" s="7" t="s">
         <v>60</v>
       </c>
@@ -3124,10 +3130,10 @@
       <c r="Z25" s="3"/>
     </row>
     <row r="26" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I26" s="81">
+      <c r="I26" s="93">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J26" s="75"/>
+      <c r="J26" s="94"/>
       <c r="K26" s="7" t="s">
         <v>87</v>
       </c>
@@ -3160,10 +3166,10 @@
       <c r="Z26" s="3"/>
     </row>
     <row r="27" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I27" s="81">
+      <c r="I27" s="93">
         <v>3</v>
       </c>
-      <c r="J27" s="75"/>
+      <c r="J27" s="94"/>
       <c r="K27" s="7" t="s">
         <v>61</v>
       </c>
@@ -3194,10 +3200,10 @@
       <c r="Z27" s="3"/>
     </row>
     <row r="28" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I28" s="81">
+      <c r="I28" s="93">
         <v>4</v>
       </c>
-      <c r="J28" s="75"/>
+      <c r="J28" s="94"/>
       <c r="K28" s="7" t="s">
         <v>62</v>
       </c>
@@ -3228,10 +3234,10 @@
       <c r="Z28" s="3"/>
     </row>
     <row r="29" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I29" s="81">
+      <c r="I29" s="93">
         <v>5.5</v>
       </c>
-      <c r="J29" s="75"/>
+      <c r="J29" s="94"/>
       <c r="K29" s="7" t="s">
         <v>63</v>
       </c>
@@ -3282,10 +3288,10 @@
       </c>
     </row>
     <row r="30" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I30" s="81">
+      <c r="I30" s="93">
         <v>7.5</v>
       </c>
-      <c r="J30" s="75"/>
+      <c r="J30" s="94"/>
       <c r="K30" s="7" t="s">
         <v>64</v>
       </c>
@@ -3336,10 +3342,10 @@
       </c>
     </row>
     <row r="31" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I31" s="81">
+      <c r="I31" s="93">
         <v>11</v>
       </c>
-      <c r="J31" s="75"/>
+      <c r="J31" s="94"/>
       <c r="K31" s="7" t="s">
         <v>65</v>
       </c>
@@ -3390,10 +3396,10 @@
       </c>
     </row>
     <row r="32" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I32" s="81">
+      <c r="I32" s="93">
         <v>15</v>
       </c>
-      <c r="J32" s="75"/>
+      <c r="J32" s="94"/>
       <c r="K32" s="7" t="s">
         <v>66</v>
       </c>
@@ -3424,10 +3430,10 @@
       <c r="Z32" s="3"/>
     </row>
     <row r="33" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="I33" s="81">
+      <c r="I33" s="93">
         <v>18.5</v>
       </c>
-      <c r="J33" s="75"/>
+      <c r="J33" s="94"/>
       <c r="K33" s="7" t="s">
         <v>67</v>
       </c>
@@ -3458,10 +3464,10 @@
       <c r="Z33" s="3"/>
     </row>
     <row r="34" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="I34" s="81">
+      <c r="I34" s="93">
         <v>22</v>
       </c>
-      <c r="J34" s="75"/>
+      <c r="J34" s="94"/>
       <c r="K34" s="7" t="s">
         <v>68</v>
       </c>
@@ -3492,10 +3498,10 @@
       <c r="Z34" s="3"/>
     </row>
     <row r="35" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="I35" s="85">
+      <c r="I35" s="100">
         <v>30</v>
       </c>
-      <c r="J35" s="86"/>
+      <c r="J35" s="101"/>
       <c r="K35" s="12" t="s">
         <v>69</v>
       </c>
@@ -3526,15 +3532,15 @@
       <c r="Z35" s="5"/>
     </row>
     <row r="36" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G36" s="108" t="s">
+      <c r="G36" s="118" t="s">
         <v>121</v>
       </c>
-      <c r="H36" s="108"/>
-      <c r="I36" s="98">
+      <c r="H36" s="118"/>
+      <c r="I36" s="109">
         <f>_xlfn.MINIFS(I21:J35,I21:J35,"&gt;="&amp;M11)</f>
         <v>7.5</v>
       </c>
-      <c r="J36" s="99"/>
+      <c r="J36" s="110"/>
       <c r="K36" s="9" t="str">
         <f>VLOOKUP($I$36,$I$21:$R$35,3)</f>
         <v>112M2</v>
@@ -3606,12 +3612,12 @@
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
       <c r="F38" s="16"/>
-      <c r="G38" s="89" t="s">
+      <c r="G38" s="97" t="s">
         <v>40</v>
       </c>
-      <c r="H38" s="82"/>
-      <c r="I38" s="82"/>
-      <c r="J38" s="97"/>
+      <c r="H38" s="98"/>
+      <c r="I38" s="98"/>
+      <c r="J38" s="99"/>
       <c r="K38" s="11"/>
       <c r="L38" s="18"/>
       <c r="M38" s="18"/>
@@ -3635,12 +3641,12 @@
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
       <c r="F39" s="16"/>
-      <c r="G39" s="81" t="s">
+      <c r="G39" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="H39" s="75"/>
-      <c r="I39" s="75"/>
-      <c r="J39" s="92"/>
+      <c r="H39" s="94"/>
+      <c r="I39" s="94"/>
+      <c r="J39" s="105"/>
       <c r="K39" s="7"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -3676,14 +3682,14 @@
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
-      <c r="G40" s="81" t="s">
+      <c r="G40" s="93" t="s">
         <v>120</v>
       </c>
-      <c r="H40" s="75"/>
-      <c r="I40" s="75" t="s">
+      <c r="H40" s="94"/>
+      <c r="I40" s="94" t="s">
         <v>119</v>
       </c>
-      <c r="J40" s="92"/>
+      <c r="J40" s="105"/>
       <c r="K40" s="27" t="s">
         <v>122</v>
       </c>
@@ -3731,15 +3737,15 @@
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
-      <c r="G41" s="104">
+      <c r="G41" s="115">
         <v>160</v>
       </c>
-      <c r="H41" s="105"/>
-      <c r="I41" s="93">
+      <c r="H41" s="116"/>
+      <c r="I41" s="120">
         <f t="shared" ref="I41:I46" si="4">$E$3*60000/PI()/G41</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="J41" s="94"/>
+      <c r="J41" s="121"/>
       <c r="K41" s="15">
         <f t="shared" ref="K41:K46" si="5">IF($I41,L$36/$I41,"-")</f>
         <v>15.15818455357075</v>
@@ -3811,15 +3817,15 @@
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-      <c r="G42" s="106">
+      <c r="G42" s="117">
         <v>200</v>
       </c>
-      <c r="H42" s="107"/>
-      <c r="I42" s="84">
+      <c r="H42" s="103"/>
+      <c r="I42" s="122">
         <f t="shared" si="4"/>
         <v>152.78874536821954</v>
       </c>
-      <c r="J42" s="95"/>
+      <c r="J42" s="123"/>
       <c r="K42" s="13">
         <f t="shared" si="5"/>
         <v>18.947730691963439</v>
@@ -3888,15 +3894,15 @@
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
-      <c r="G43" s="81">
+      <c r="G43" s="93">
         <v>250</v>
       </c>
-      <c r="H43" s="75"/>
-      <c r="I43" s="84">
+      <c r="H43" s="94"/>
+      <c r="I43" s="122">
         <f t="shared" si="4"/>
         <v>122.23099629457563</v>
       </c>
-      <c r="J43" s="95"/>
+      <c r="J43" s="123"/>
       <c r="K43" s="13">
         <f t="shared" si="5"/>
         <v>23.684663364954297</v>
@@ -3965,15 +3971,15 @@
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
-      <c r="G44" s="81">
+      <c r="G44" s="93">
         <v>315</v>
       </c>
-      <c r="H44" s="75"/>
-      <c r="I44" s="84">
+      <c r="H44" s="94"/>
+      <c r="I44" s="122">
         <f t="shared" si="4"/>
         <v>97.008727217917169</v>
       </c>
-      <c r="J44" s="95"/>
+      <c r="J44" s="123"/>
       <c r="K44" s="13">
         <f t="shared" si="5"/>
         <v>29.842675839842414</v>
@@ -4036,15 +4042,15 @@
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="81">
+      <c r="G45" s="93">
         <v>400</v>
       </c>
-      <c r="H45" s="75"/>
-      <c r="I45" s="84">
+      <c r="H45" s="94"/>
+      <c r="I45" s="122">
         <f t="shared" si="4"/>
         <v>76.394372684109769</v>
       </c>
-      <c r="J45" s="95"/>
+      <c r="J45" s="123"/>
       <c r="K45" s="13">
         <f t="shared" si="5"/>
         <v>37.895461383926879</v>
@@ -4104,15 +4110,15 @@
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-      <c r="G46" s="85">
+      <c r="G46" s="100">
         <v>500</v>
       </c>
-      <c r="H46" s="86"/>
-      <c r="I46" s="88">
+      <c r="H46" s="101"/>
+      <c r="I46" s="124">
         <f t="shared" si="4"/>
         <v>61.115498147287816</v>
       </c>
-      <c r="J46" s="96"/>
+      <c r="J46" s="125"/>
       <c r="K46" s="14">
         <f t="shared" si="5"/>
         <v>47.369326729908593</v>
@@ -4205,25 +4211,25 @@
       <c r="Z47" s="1"/>
     </row>
     <row r="48" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B48" s="89" t="s">
+      <c r="B48" s="97" t="s">
         <v>110</v>
       </c>
-      <c r="C48" s="82"/>
-      <c r="D48" s="82"/>
-      <c r="E48" s="82"/>
-      <c r="F48" s="82" t="str">
+      <c r="C48" s="98"/>
+      <c r="D48" s="98"/>
+      <c r="E48" s="98"/>
+      <c r="F48" s="98" t="str">
         <f>P46</f>
         <v>Цилиндрическая 1</v>
       </c>
-      <c r="G48" s="97"/>
+      <c r="G48" s="99"/>
       <c r="H48" s="16"/>
       <c r="I48" s="16"/>
       <c r="J48" s="16"/>
       <c r="K48" s="36"/>
-      <c r="L48" s="75" t="s">
+      <c r="L48" s="94" t="s">
         <v>56</v>
       </c>
-      <c r="M48" s="75"/>
+      <c r="M48" s="94"/>
       <c r="N48" s="28">
         <f ca="1">MAX(Z41:Z46,V41:V46,R41:R46,N41:N46)</f>
         <v>0.78915140422920127</v>
@@ -4241,12 +4247,12 @@
       <c r="Z48" s="1"/>
     </row>
     <row r="49" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B49" s="81" t="s">
+      <c r="B49" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="75"/>
-      <c r="D49" s="75"/>
-      <c r="E49" s="75"/>
+      <c r="C49" s="94"/>
+      <c r="D49" s="94"/>
+      <c r="E49" s="94"/>
       <c r="F49" s="46">
         <f>O41</f>
         <v>7.5398223686155026</v>
@@ -4271,12 +4277,12 @@
       <c r="Z49" s="1"/>
     </row>
     <row r="50" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B50" s="81" t="s">
+      <c r="B50" s="93" t="s">
         <v>96</v>
       </c>
-      <c r="C50" s="75"/>
-      <c r="D50" s="75"/>
-      <c r="E50" s="75"/>
+      <c r="C50" s="94"/>
+      <c r="D50" s="94"/>
+      <c r="E50" s="94"/>
       <c r="F50" s="16">
         <f>P36</f>
         <v>1440</v>
@@ -4293,12 +4299,12 @@
       <c r="Z50" s="1"/>
     </row>
     <row r="51" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B51" s="81" t="s">
+      <c r="B51" s="93" t="s">
         <v>104</v>
       </c>
-      <c r="C51" s="75"/>
-      <c r="D51" s="75"/>
-      <c r="E51" s="75"/>
+      <c r="C51" s="94"/>
+      <c r="D51" s="94"/>
+      <c r="E51" s="94"/>
       <c r="F51" s="1">
         <f>F50*PI()/30</f>
         <v>150.79644737231007</v>
@@ -4307,29 +4313,29 @@
         <v>106</v>
       </c>
       <c r="H51" s="16"/>
-      <c r="I51" s="98" t="s">
+      <c r="I51" s="109" t="s">
         <v>114</v>
       </c>
-      <c r="J51" s="100"/>
+      <c r="J51" s="111"/>
       <c r="K51" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="L51" s="82" t="s">
+      <c r="L51" s="98" t="s">
         <v>122</v>
       </c>
-      <c r="M51" s="82"/>
-      <c r="N51" s="79" t="s">
+      <c r="M51" s="98"/>
+      <c r="N51" s="126" t="s">
         <v>115</v>
       </c>
-      <c r="O51" s="79"/>
-      <c r="P51" s="82" t="s">
+      <c r="O51" s="126"/>
+      <c r="P51" s="98" t="s">
         <v>116</v>
       </c>
-      <c r="Q51" s="82"/>
-      <c r="R51" s="79" t="s">
+      <c r="Q51" s="98"/>
+      <c r="R51" s="126" t="s">
         <v>118</v>
       </c>
-      <c r="S51" s="79"/>
+      <c r="S51" s="126"/>
       <c r="T51" s="49"/>
       <c r="U51" s="49"/>
       <c r="V51" s="49"/>
@@ -4338,12 +4344,12 @@
       <c r="Z51" s="1"/>
     </row>
     <row r="52" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B52" s="81" t="s">
+      <c r="B52" s="93" t="s">
         <v>42</v>
       </c>
-      <c r="C52" s="75"/>
-      <c r="D52" s="75"/>
-      <c r="E52" s="75"/>
+      <c r="C52" s="94"/>
+      <c r="D52" s="94"/>
+      <c r="E52" s="94"/>
       <c r="F52" s="45">
         <f>I41</f>
         <v>190.98593171027443</v>
@@ -4352,33 +4358,33 @@
         <v>105</v>
       </c>
       <c r="H52" s="16"/>
-      <c r="I52" s="81" t="s">
+      <c r="I52" s="93" t="s">
         <v>117</v>
       </c>
-      <c r="J52" s="75"/>
+      <c r="J52" s="94"/>
       <c r="K52" s="42">
         <f>R36</f>
         <v>0.872</v>
       </c>
-      <c r="L52" s="82">
+      <c r="L52" s="98">
         <v>1</v>
       </c>
-      <c r="M52" s="82"/>
-      <c r="N52" s="77">
+      <c r="M52" s="98"/>
+      <c r="N52" s="129">
         <f>F50</f>
         <v>1440</v>
       </c>
-      <c r="O52" s="77"/>
-      <c r="P52" s="83">
+      <c r="O52" s="129"/>
+      <c r="P52" s="128">
         <f ca="1">F55</f>
         <v>46.89699496864425</v>
       </c>
-      <c r="Q52" s="83"/>
-      <c r="R52" s="79">
+      <c r="Q52" s="128"/>
+      <c r="R52" s="126">
         <f t="shared" ref="R52:R57" ca="1" si="17">P52*N52*PI()/1000/30</f>
         <v>7.0719002337086527</v>
       </c>
-      <c r="S52" s="79"/>
+      <c r="S52" s="126"/>
       <c r="T52" s="16"/>
       <c r="U52" s="30"/>
       <c r="X52" s="1"/>
@@ -4386,12 +4392,12 @@
       <c r="Z52" s="1"/>
     </row>
     <row r="53" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B53" s="81" t="s">
+      <c r="B53" s="93" t="s">
         <v>107</v>
       </c>
-      <c r="C53" s="75"/>
-      <c r="D53" s="75"/>
-      <c r="E53" s="75"/>
+      <c r="C53" s="94"/>
+      <c r="D53" s="94"/>
+      <c r="E53" s="94"/>
       <c r="F53" s="16">
         <f>G41</f>
         <v>160</v>
@@ -4400,33 +4406,33 @@
         <v>16</v>
       </c>
       <c r="H53" s="16"/>
-      <c r="I53" s="81" t="s">
+      <c r="I53" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="J53" s="75"/>
+      <c r="J53" s="94"/>
       <c r="K53" s="7">
         <f>M7</f>
         <v>0.98</v>
       </c>
-      <c r="L53" s="75">
+      <c r="L53" s="94">
         <v>1</v>
       </c>
-      <c r="M53" s="75"/>
-      <c r="N53" s="78">
+      <c r="M53" s="94"/>
+      <c r="N53" s="130">
         <f>N52/L53</f>
         <v>1440</v>
       </c>
-      <c r="O53" s="78"/>
-      <c r="P53" s="76">
+      <c r="O53" s="130"/>
+      <c r="P53" s="106">
         <f ca="1">P52*L53*K53</f>
         <v>45.959055069271365</v>
       </c>
-      <c r="Q53" s="76"/>
-      <c r="R53" s="80">
+      <c r="Q53" s="106"/>
+      <c r="R53" s="127">
         <f t="shared" ca="1" si="17"/>
         <v>6.9304622290344788</v>
       </c>
-      <c r="S53" s="80"/>
+      <c r="S53" s="127"/>
       <c r="T53" s="1"/>
       <c r="U53" s="67"/>
       <c r="V53" s="68"/>
@@ -4435,12 +4441,12 @@
       <c r="Z53" s="1"/>
     </row>
     <row r="54" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B54" s="81" t="s">
+      <c r="B54" s="93" t="s">
         <v>97</v>
       </c>
-      <c r="C54" s="75"/>
-      <c r="D54" s="75"/>
-      <c r="E54" s="75"/>
+      <c r="C54" s="94"/>
+      <c r="D54" s="94"/>
+      <c r="E54" s="94"/>
       <c r="F54" s="44">
         <f>E2*F53/2</f>
         <v>320</v>
@@ -4449,33 +4455,33 @@
         <v>100</v>
       </c>
       <c r="H54" s="16"/>
-      <c r="I54" s="81" t="s">
+      <c r="I54" s="93" t="s">
         <v>95</v>
       </c>
-      <c r="J54" s="75"/>
+      <c r="J54" s="94"/>
       <c r="K54" s="7">
         <f>M6</f>
         <v>0.99</v>
       </c>
-      <c r="L54" s="75">
+      <c r="L54" s="94">
         <v>1</v>
       </c>
-      <c r="M54" s="75"/>
-      <c r="N54" s="78">
+      <c r="M54" s="94"/>
+      <c r="N54" s="130">
         <f>N53/L54</f>
         <v>1440</v>
       </c>
-      <c r="O54" s="78"/>
-      <c r="P54" s="76">
+      <c r="O54" s="130"/>
+      <c r="P54" s="106">
         <f ca="1">P53*L54*K54</f>
         <v>45.499464518578648</v>
       </c>
-      <c r="Q54" s="76"/>
-      <c r="R54" s="80">
+      <c r="Q54" s="106"/>
+      <c r="R54" s="127">
         <f t="shared" ca="1" si="17"/>
         <v>6.8611576067441344</v>
       </c>
-      <c r="S54" s="80"/>
+      <c r="S54" s="127"/>
       <c r="T54" s="1"/>
       <c r="U54" s="67"/>
       <c r="V54" s="68"/>
@@ -4485,12 +4491,12 @@
       <c r="Z54" s="1"/>
     </row>
     <row r="55" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B55" s="81" t="s">
+      <c r="B55" s="93" t="s">
         <v>98</v>
       </c>
-      <c r="C55" s="75"/>
-      <c r="D55" s="75"/>
-      <c r="E55" s="75"/>
+      <c r="C55" s="94"/>
+      <c r="D55" s="94"/>
+      <c r="E55" s="94"/>
       <c r="F55" s="1">
         <f ca="1">F54/F59/F49</f>
         <v>46.89699496864425</v>
@@ -4499,34 +4505,34 @@
         <v>100</v>
       </c>
       <c r="H55" s="16"/>
-      <c r="I55" s="81" t="s">
+      <c r="I55" s="93" t="s">
         <v>94</v>
       </c>
-      <c r="J55" s="75"/>
+      <c r="J55" s="94"/>
       <c r="K55" s="43">
         <f ca="1">Q41</f>
         <v>0.96143805509807656</v>
       </c>
-      <c r="L55" s="76">
+      <c r="L55" s="106">
         <f>F49</f>
         <v>7.5398223686155026</v>
       </c>
-      <c r="M55" s="76"/>
-      <c r="N55" s="76">
+      <c r="M55" s="106"/>
+      <c r="N55" s="106">
         <f>N54/L55</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O55" s="76"/>
-      <c r="P55" s="84">
+      <c r="O55" s="106"/>
+      <c r="P55" s="122">
         <f ca="1">P54*L55*K55</f>
         <v>329.82890125747264</v>
       </c>
-      <c r="Q55" s="84"/>
-      <c r="R55" s="80">
+      <c r="Q55" s="122"/>
+      <c r="R55" s="127">
         <f t="shared" ca="1" si="17"/>
         <v>6.5965780251494532</v>
       </c>
-      <c r="S55" s="80"/>
+      <c r="S55" s="127"/>
       <c r="T55" s="1"/>
       <c r="U55" s="67"/>
       <c r="V55" s="68"/>
@@ -4536,12 +4542,12 @@
       <c r="Z55" s="1"/>
     </row>
     <row r="56" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B56" s="81" t="s">
+      <c r="B56" s="93" t="s">
         <v>99</v>
       </c>
-      <c r="C56" s="75"/>
-      <c r="D56" s="75"/>
-      <c r="E56" s="75"/>
+      <c r="C56" s="94"/>
+      <c r="D56" s="94"/>
+      <c r="E56" s="94"/>
       <c r="F56" s="1">
         <f ca="1">F55*F51/1000</f>
         <v>7.0719002337086527</v>
@@ -4549,109 +4555,109 @@
       <c r="G56" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="I56" s="81" t="s">
+      <c r="I56" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="J56" s="75"/>
+      <c r="J56" s="94"/>
       <c r="K56" s="7">
         <f>M7</f>
         <v>0.98</v>
       </c>
-      <c r="L56" s="75">
+      <c r="L56" s="94">
         <v>1</v>
       </c>
-      <c r="M56" s="75"/>
-      <c r="N56" s="76">
+      <c r="M56" s="94"/>
+      <c r="N56" s="106">
         <f>N55/L56</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O56" s="76"/>
-      <c r="P56" s="84">
+      <c r="O56" s="106"/>
+      <c r="P56" s="122">
         <f ca="1">P55*L56*K56</f>
         <v>323.23232323232315</v>
       </c>
-      <c r="Q56" s="84"/>
-      <c r="R56" s="80">
+      <c r="Q56" s="122"/>
+      <c r="R56" s="127">
         <f t="shared" ca="1" si="17"/>
         <v>6.4646464646464636</v>
       </c>
-      <c r="S56" s="80"/>
+      <c r="S56" s="127"/>
       <c r="T56" s="1"/>
       <c r="U56" s="67"/>
       <c r="V56" s="68"/>
     </row>
     <row r="57" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B57" s="81" t="s">
+      <c r="B57" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="C57" s="75"/>
-      <c r="D57" s="75"/>
-      <c r="E57" s="75"/>
+      <c r="C57" s="94"/>
+      <c r="D57" s="94"/>
+      <c r="E57" s="94"/>
       <c r="F57" s="1">
         <f>Q36</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="G57" s="50"/>
-      <c r="I57" s="81" t="s">
+      <c r="I57" s="93" t="s">
         <v>95</v>
       </c>
-      <c r="J57" s="75"/>
+      <c r="J57" s="94"/>
       <c r="K57" s="7">
         <f>M6</f>
         <v>0.99</v>
       </c>
-      <c r="L57" s="75">
+      <c r="L57" s="94">
         <v>1</v>
       </c>
-      <c r="M57" s="75"/>
-      <c r="N57" s="76">
+      <c r="M57" s="94"/>
+      <c r="N57" s="106">
         <f>N56/L57</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O57" s="76"/>
-      <c r="P57" s="84">
+      <c r="O57" s="106"/>
+      <c r="P57" s="122">
         <f ca="1">P56*L57*K57</f>
         <v>319.99999999999994</v>
       </c>
-      <c r="Q57" s="84"/>
-      <c r="R57" s="80">
+      <c r="Q57" s="122"/>
+      <c r="R57" s="127">
         <f t="shared" ca="1" si="17"/>
         <v>6.3999999999999995</v>
       </c>
-      <c r="S57" s="80"/>
+      <c r="S57" s="127"/>
       <c r="T57" s="1"/>
       <c r="U57" s="67"/>
       <c r="V57" s="68"/>
     </row>
     <row r="58" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B58" s="81" t="s">
+      <c r="B58" s="93" t="s">
         <v>103</v>
       </c>
-      <c r="C58" s="75"/>
-      <c r="D58" s="75"/>
-      <c r="E58" s="75"/>
+      <c r="C58" s="94"/>
+      <c r="D58" s="94"/>
+      <c r="E58" s="94"/>
       <c r="F58" s="44">
         <f>MAX(F57,E8)</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="G58" s="50"/>
-      <c r="I58" s="85" t="s">
-        <v>139</v>
-      </c>
-      <c r="J58" s="86"/>
+      <c r="I58" s="100" t="s">
+        <v>138</v>
+      </c>
+      <c r="J58" s="101"/>
       <c r="K58" s="12"/>
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
-      <c r="N58" s="87">
+      <c r="N58" s="95">
         <f>N57</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O58" s="87"/>
-      <c r="P58" s="88">
+      <c r="O58" s="95"/>
+      <c r="P58" s="124">
         <f ca="1">P57</f>
         <v>319.99999999999994</v>
       </c>
-      <c r="Q58" s="88"/>
+      <c r="Q58" s="124"/>
       <c r="R58" s="4"/>
       <c r="S58" s="4"/>
       <c r="T58" s="16"/>
@@ -4659,12 +4665,12 @@
       <c r="V58" s="16"/>
     </row>
     <row r="59" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B59" s="81" t="s">
+      <c r="B59" s="93" t="s">
         <v>109</v>
       </c>
-      <c r="C59" s="75"/>
-      <c r="D59" s="75"/>
-      <c r="E59" s="75"/>
+      <c r="C59" s="94"/>
+      <c r="D59" s="94"/>
+      <c r="E59" s="94"/>
       <c r="F59" s="1">
         <f ca="1">K57*K55*K56*K54*K53</f>
         <v>0.90499014246468046</v>
@@ -4672,12 +4678,12 @@
       <c r="G59" s="50"/>
     </row>
     <row r="60" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B60" s="81" t="s">
+      <c r="B60" s="93" t="s">
         <v>111</v>
       </c>
-      <c r="C60" s="75"/>
-      <c r="D60" s="75"/>
-      <c r="E60" s="75"/>
+      <c r="C60" s="94"/>
+      <c r="D60" s="94"/>
+      <c r="E60" s="94"/>
       <c r="F60" s="1">
         <f ca="1">F59*K52</f>
         <v>0.78915140422920138</v>
@@ -4685,12 +4691,12 @@
       <c r="G60" s="50"/>
     </row>
     <row r="61" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B61" s="75" t="s">
-        <v>138</v>
-      </c>
-      <c r="C61" s="75"/>
-      <c r="D61" s="75"/>
-      <c r="E61" s="75"/>
+      <c r="B61" s="94" t="s">
+        <v>137</v>
+      </c>
+      <c r="C61" s="94"/>
+      <c r="D61" s="94"/>
+      <c r="E61" s="94"/>
       <c r="F61" s="69">
         <v>38</v>
       </c>
@@ -4717,57 +4723,82 @@
     </row>
   </sheetData>
   <mergeCells count="151">
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="S19:V19"/>
-    <mergeCell ref="W19:Z19"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="AC8:AE8"/>
-    <mergeCell ref="AC6:AE6"/>
-    <mergeCell ref="K19:N19"/>
-    <mergeCell ref="AC2:AE2"/>
-    <mergeCell ref="AC3:AE3"/>
-    <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="AC5:AE5"/>
-    <mergeCell ref="AC7:AE7"/>
-    <mergeCell ref="AC10:AE10"/>
-    <mergeCell ref="AC9:AE9"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="I4:N4"/>
-    <mergeCell ref="I3:N3"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="L54:M54"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="N56:O56"/>
+    <mergeCell ref="N57:O57"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="R53:S53"/>
+    <mergeCell ref="R54:S54"/>
+    <mergeCell ref="R55:S55"/>
+    <mergeCell ref="R56:S56"/>
+    <mergeCell ref="R57:S57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="I55:J55"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="P56:Q56"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="Q6:S6"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="G38:J38"/>
     <mergeCell ref="B55:E55"/>
     <mergeCell ref="B54:E54"/>
     <mergeCell ref="B53:E53"/>
@@ -4792,82 +4823,57 @@
     <mergeCell ref="B48:E48"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="I20:J20"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="Q6:S6"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="G39:J39"/>
-    <mergeCell ref="G38:J38"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="I58:J58"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="R53:S53"/>
-    <mergeCell ref="R54:S54"/>
-    <mergeCell ref="R55:S55"/>
-    <mergeCell ref="R56:S56"/>
-    <mergeCell ref="R57:S57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="I55:J55"/>
-    <mergeCell ref="I54:J54"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="P55:Q55"/>
-    <mergeCell ref="P56:Q56"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="L54:M54"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="L57:M57"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="N56:O56"/>
-    <mergeCell ref="N57:O57"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="AC8:AE8"/>
+    <mergeCell ref="AC6:AE6"/>
+    <mergeCell ref="K19:N19"/>
+    <mergeCell ref="AC2:AE2"/>
+    <mergeCell ref="AC3:AE3"/>
+    <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="AC5:AE5"/>
+    <mergeCell ref="AC7:AE7"/>
+    <mergeCell ref="AC10:AE10"/>
+    <mergeCell ref="AC9:AE9"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="S19:V19"/>
+    <mergeCell ref="W19:Z19"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -4887,7 +4893,7 @@
         <v>120</v>
       </c>
       <c r="B1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
@@ -4896,81 +4902,81 @@
       <c r="A2">
         <v>4</v>
       </c>
-      <c r="E2" s="75" t="s">
-        <v>229</v>
-      </c>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="108" t="s">
-        <v>268</v>
-      </c>
-      <c r="K2" s="108"/>
-      <c r="L2" s="108"/>
-      <c r="M2" s="108"/>
-      <c r="N2" s="108"/>
-      <c r="P2" s="108" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q2" s="108"/>
-      <c r="R2" s="108"/>
-      <c r="S2" s="108"/>
-      <c r="T2" s="108"/>
+      <c r="E2" s="94" t="s">
+        <v>228</v>
+      </c>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="118" t="s">
+        <v>266</v>
+      </c>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
+      <c r="P2" s="118" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q2" s="118"/>
+      <c r="R2" s="118"/>
+      <c r="S2" s="118"/>
+      <c r="T2" s="118"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>5</v>
       </c>
-      <c r="E3" s="116" t="s">
+      <c r="E3" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="134"/>
       <c r="H3" s="60">
         <f>Передача!$D$49</f>
-        <v>1510</v>
+        <v>2016</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J3" s="48" t="s">
         <v>72</v>
       </c>
       <c r="K3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="P3" s="48" t="s">
         <v>72</v>
       </c>
       <c r="Q3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>6</v>
       </c>
-      <c r="E4" s="116" t="s">
-        <v>160</v>
-      </c>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
+      <c r="E4" s="134" t="s">
+        <v>159</v>
+      </c>
+      <c r="F4" s="134"/>
+      <c r="G4" s="134"/>
       <c r="H4" s="60">
         <f>Передача!$D$50</f>
-        <v>554</v>
+        <v>734</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J4" t="s">
         <v>23</v>
       </c>
-      <c r="P4" s="108" t="s">
+      <c r="P4" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="Q4" s="108"/>
-      <c r="R4" s="108"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118"/>
       <c r="S4">
         <f ca="1">Вал!S15</f>
         <v>45</v>
@@ -4983,23 +4989,23 @@
       <c r="A5">
         <v>7</v>
       </c>
-      <c r="E5" s="116" t="s">
-        <v>161</v>
-      </c>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
+      <c r="E5" s="134" t="s">
+        <v>160</v>
+      </c>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
       <c r="H5" s="60">
         <f>Передача!$D$51</f>
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="J5" s="108" t="s">
+        <v>161</v>
+      </c>
+      <c r="J5" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="K5" s="108"/>
-      <c r="L5" s="108"/>
+      <c r="K5" s="118"/>
+      <c r="L5" s="118"/>
       <c r="M5">
         <f ca="1">Вал!K16</f>
         <v>40</v>
@@ -5047,7 +5053,7 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="J10" s="48" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
@@ -5271,69 +5277,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="108" t="s">
-        <v>276</v>
-      </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108" t="s">
-        <v>185</v>
-      </c>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108" t="s">
+      <c r="A1" s="118" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118" t="s">
+        <v>184</v>
+      </c>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118" t="s">
+        <v>281</v>
+      </c>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118" t="s">
+        <v>284</v>
+      </c>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="118"/>
+      <c r="B2" s="118"/>
+      <c r="C2" s="118" t="s">
+        <v>282</v>
+      </c>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118" t="s">
         <v>283</v>
       </c>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108" t="s">
+      <c r="F2" s="118"/>
+      <c r="G2" s="91" t="s">
+        <v>285</v>
+      </c>
+      <c r="H2" s="91" t="s">
         <v>286</v>
       </c>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="108"/>
-      <c r="B2" s="108"/>
-      <c r="C2" s="108" t="s">
-        <v>284</v>
-      </c>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108" t="s">
-        <v>285</v>
-      </c>
-      <c r="F2" s="108"/>
-      <c r="G2" s="147" t="s">
+      <c r="I2" s="91" t="s">
         <v>287</v>
       </c>
-      <c r="H2" s="147" t="s">
+      <c r="J2" s="91" t="s">
         <v>288</v>
       </c>
-      <c r="I2" s="147" t="s">
+      <c r="K2" s="91" t="s">
         <v>289</v>
       </c>
-      <c r="J2" s="147" t="s">
+      <c r="L2" s="91" t="s">
         <v>290</v>
       </c>
-      <c r="K2" s="147" t="s">
-        <v>291</v>
-      </c>
-      <c r="L2" s="147" t="s">
-        <v>292</v>
-      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="108" t="s">
-        <v>277</v>
-      </c>
-      <c r="B3" s="108"/>
-      <c r="C3" s="108">
+      <c r="A3" s="118" t="s">
+        <v>275</v>
+      </c>
+      <c r="B3" s="118"/>
+      <c r="C3" s="118">
         <v>1000</v>
       </c>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108">
+      <c r="D3" s="118"/>
+      <c r="E3" s="118">
         <v>190</v>
       </c>
-      <c r="F3" s="108"/>
+      <c r="F3" s="118"/>
       <c r="G3">
         <v>520</v>
       </c>
@@ -5354,18 +5360,18 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="108">
+      <c r="A4" s="118">
         <v>45</v>
       </c>
-      <c r="B4" s="108"/>
-      <c r="C4" s="108">
+      <c r="B4" s="118"/>
+      <c r="C4" s="118">
         <v>120</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108">
+      <c r="D4" s="118"/>
+      <c r="E4" s="118">
         <v>227</v>
       </c>
-      <c r="F4" s="108"/>
+      <c r="F4" s="118"/>
       <c r="G4">
         <v>820</v>
       </c>
@@ -5386,18 +5392,18 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="108">
+      <c r="A5" s="118">
         <v>45</v>
       </c>
-      <c r="B5" s="108"/>
-      <c r="C5" s="108">
+      <c r="B5" s="118"/>
+      <c r="C5" s="118">
         <v>80</v>
       </c>
-      <c r="D5" s="108"/>
-      <c r="E5" s="108">
+      <c r="D5" s="118"/>
+      <c r="E5" s="118">
         <v>260</v>
       </c>
-      <c r="F5" s="108"/>
+      <c r="F5" s="118"/>
       <c r="G5">
         <v>900</v>
       </c>
@@ -5418,18 +5424,18 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="108" t="s">
-        <v>278</v>
-      </c>
-      <c r="B6" s="108"/>
-      <c r="C6" s="108">
+      <c r="A6" s="118" t="s">
+        <v>276</v>
+      </c>
+      <c r="B6" s="118"/>
+      <c r="C6" s="118">
         <v>200</v>
       </c>
-      <c r="D6" s="108"/>
-      <c r="E6" s="108">
+      <c r="D6" s="118"/>
+      <c r="E6" s="118">
         <v>240</v>
       </c>
-      <c r="F6" s="108"/>
+      <c r="F6" s="118"/>
       <c r="G6">
         <v>790</v>
       </c>
@@ -5450,18 +5456,18 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="108" t="s">
-        <v>278</v>
-      </c>
-      <c r="B7" s="108"/>
-      <c r="C7" s="108">
+      <c r="A7" s="118" t="s">
+        <v>276</v>
+      </c>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118">
         <v>120</v>
       </c>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108">
+      <c r="D7" s="118"/>
+      <c r="E7" s="118">
         <v>270</v>
       </c>
-      <c r="F7" s="108"/>
+      <c r="F7" s="118"/>
       <c r="G7">
         <v>980</v>
       </c>
@@ -5482,18 +5488,18 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="108" t="s">
-        <v>279</v>
-      </c>
-      <c r="B8" s="108"/>
-      <c r="C8" s="108">
+      <c r="A8" s="118" t="s">
+        <v>277</v>
+      </c>
+      <c r="B8" s="118"/>
+      <c r="C8" s="118">
         <v>200</v>
       </c>
-      <c r="D8" s="108"/>
-      <c r="E8" s="108">
+      <c r="D8" s="118"/>
+      <c r="E8" s="118">
         <v>270</v>
       </c>
-      <c r="F8" s="108"/>
+      <c r="F8" s="118"/>
       <c r="G8">
         <v>980</v>
       </c>
@@ -5514,18 +5520,18 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="108" t="s">
-        <v>280</v>
-      </c>
-      <c r="B9" s="108"/>
-      <c r="C9" s="108">
+      <c r="A9" s="118" t="s">
+        <v>278</v>
+      </c>
+      <c r="B9" s="118"/>
+      <c r="C9" s="118">
         <v>120</v>
       </c>
-      <c r="D9" s="108"/>
-      <c r="E9" s="108">
+      <c r="D9" s="118"/>
+      <c r="E9" s="118">
         <v>197</v>
       </c>
-      <c r="F9" s="108"/>
+      <c r="F9" s="118"/>
       <c r="G9">
         <v>650</v>
       </c>
@@ -5546,18 +5552,18 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="108" t="s">
-        <v>281</v>
-      </c>
-      <c r="B10" s="108"/>
-      <c r="C10" s="108">
+      <c r="A10" s="118" t="s">
+        <v>279</v>
+      </c>
+      <c r="B10" s="118"/>
+      <c r="C10" s="118">
         <v>120</v>
       </c>
-      <c r="D10" s="108"/>
-      <c r="E10" s="108">
+      <c r="D10" s="118"/>
+      <c r="E10" s="118">
         <v>260</v>
       </c>
-      <c r="F10" s="108"/>
+      <c r="F10" s="118"/>
       <c r="G10">
         <v>930</v>
       </c>
@@ -5578,18 +5584,18 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="108" t="s">
-        <v>282</v>
-      </c>
-      <c r="B11" s="108"/>
-      <c r="C11" s="108">
+      <c r="A11" s="118" t="s">
+        <v>280</v>
+      </c>
+      <c r="B11" s="118"/>
+      <c r="C11" s="118">
         <v>60</v>
       </c>
-      <c r="D11" s="108"/>
-      <c r="E11" s="108">
+      <c r="D11" s="118"/>
+      <c r="E11" s="118">
         <v>330</v>
       </c>
-      <c r="F11" s="108"/>
+      <c r="F11" s="118"/>
       <c r="G11">
         <v>1180</v>
       </c>
@@ -5623,11 +5629,9 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="G1:K1"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
@@ -5642,8 +5646,13 @@
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
@@ -5653,9 +5662,6 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5670,82 +5676,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A1" s="75" t="s">
-        <v>140</v>
-      </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
+      <c r="A1" s="94" t="s">
+        <v>139</v>
+      </c>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="93" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="75"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75" t="str">
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94" t="str">
         <f>Электродвигатель!F48</f>
         <v>Цилиндрическая 1</v>
       </c>
-      <c r="F2" s="92"/>
-      <c r="K2" s="89" t="s">
-        <v>153</v>
-      </c>
-      <c r="L2" s="82"/>
-      <c r="M2" s="82"/>
-      <c r="N2" s="82"/>
-      <c r="O2" s="82"/>
-      <c r="P2" s="82"/>
-      <c r="Q2" s="82"/>
+      <c r="F2" s="105"/>
+      <c r="K2" s="97" t="s">
+        <v>152</v>
+      </c>
+      <c r="L2" s="98"/>
+      <c r="M2" s="98"/>
+      <c r="N2" s="98"/>
+      <c r="O2" s="98"/>
+      <c r="P2" s="98"/>
+      <c r="Q2" s="98"/>
       <c r="R2" s="1"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
       <c r="E3" s="56">
         <f>Электродвигатель!$F$49</f>
         <v>7.5398223686155026</v>
       </c>
       <c r="F3" s="50"/>
       <c r="K3" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L3" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q3" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="R3" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A4" s="81" t="s">
+      <c r="A4" s="93" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
       <c r="E4" s="56">
         <f>Электродвигатель!$F$52</f>
         <v>190.98593171027443</v>
@@ -5780,12 +5786,12 @@
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="93" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="75"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
       <c r="E5" s="25">
         <f>Электродвигатель!$F$54</f>
         <v>320</v>
@@ -5820,12 +5826,12 @@
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A6" s="81" t="s">
+      <c r="A6" s="93" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="75"/>
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
+      <c r="B6" s="94"/>
+      <c r="C6" s="94"/>
+      <c r="D6" s="94"/>
       <c r="E6" s="25">
         <f>Электродвигатель!$F$58</f>
         <v>2.2000000000000002</v>
@@ -5858,12 +5864,12 @@
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A7" s="108" t="s">
-        <v>147</v>
-      </c>
-      <c r="B7" s="108"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
+      <c r="A7" s="118" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
       <c r="E7">
         <f>Электродвигатель!$E$5</f>
         <v>10000</v>
@@ -5898,14 +5904,14 @@
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A8" s="108" t="s">
-        <v>141</v>
-      </c>
-      <c r="B8" s="108"/>
-      <c r="C8" s="108"/>
-      <c r="D8" s="108"/>
-      <c r="E8" s="108"/>
-      <c r="F8" s="108"/>
+      <c r="A8" s="118" t="s">
+        <v>140</v>
+      </c>
+      <c r="B8" s="118"/>
+      <c r="C8" s="118"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="118"/>
       <c r="K8" s="7">
         <v>5</v>
       </c>
@@ -5937,12 +5943,12 @@
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A9" s="108" t="s">
-        <v>146</v>
-      </c>
-      <c r="B9" s="108"/>
-      <c r="C9" s="108"/>
-      <c r="D9" s="108"/>
+      <c r="A9" s="118" t="s">
+        <v>145</v>
+      </c>
+      <c r="B9" s="118"/>
+      <c r="C9" s="118"/>
+      <c r="D9" s="118"/>
       <c r="E9">
         <f>Электродвигатель!$E$15</f>
         <v>300</v>
@@ -5976,23 +5982,20 @@
         <v>1</v>
       </c>
       <c r="S9" s="54"/>
-      <c r="V9" t="s">
-        <v>136</v>
-      </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A10" s="81" t="s">
+      <c r="A10" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="75"/>
-      <c r="C10" s="75"/>
-      <c r="D10" s="75"/>
+      <c r="B10" s="94"/>
+      <c r="C10" s="94"/>
+      <c r="D10" s="94"/>
       <c r="E10" s="16">
         <f>Электродвигатель!$E$7</f>
         <v>3</v>
       </c>
       <c r="F10" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K10" s="58">
         <v>7</v>
@@ -6021,16 +6024,16 @@
       </c>
       <c r="S10" s="54"/>
       <c r="V10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A11" s="81" t="s">
-        <v>213</v>
-      </c>
-      <c r="B11" s="75"/>
-      <c r="C11" s="75"/>
-      <c r="D11" s="75"/>
+      <c r="A11" s="93" t="s">
+        <v>212</v>
+      </c>
+      <c r="B11" s="94"/>
+      <c r="C11" s="94"/>
+      <c r="D11" s="94"/>
       <c r="E11" s="47" t="s">
         <v>101</v>
       </c>
@@ -6063,17 +6066,14 @@
         <v>0</v>
       </c>
       <c r="S11" s="54"/>
-      <c r="V11" t="s">
-        <v>234</v>
-      </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A12" s="81" t="s">
+      <c r="A12" s="93" t="s">
         <v>130</v>
       </c>
-      <c r="B12" s="75"/>
-      <c r="C12" s="75"/>
-      <c r="D12" s="75"/>
+      <c r="B12" s="94"/>
+      <c r="C12" s="94"/>
+      <c r="D12" s="94"/>
       <c r="E12" s="55" t="s">
         <v>101</v>
       </c>
@@ -6108,14 +6108,14 @@
       <c r="S12" s="54"/>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A13" s="108" t="s">
-        <v>142</v>
-      </c>
-      <c r="B13" s="108"/>
-      <c r="C13" s="108"/>
-      <c r="D13" s="108"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="108"/>
+      <c r="A13" s="118" t="s">
+        <v>141</v>
+      </c>
+      <c r="B13" s="118"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="118"/>
+      <c r="F13" s="118"/>
       <c r="K13" s="7">
         <v>10</v>
       </c>
@@ -6144,12 +6144,12 @@
       <c r="S13" s="54"/>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A14" s="108" t="s">
-        <v>145</v>
-      </c>
-      <c r="B14" s="108"/>
-      <c r="C14" s="108"/>
-      <c r="D14" s="108"/>
+      <c r="A14" s="118" t="s">
+        <v>144</v>
+      </c>
+      <c r="B14" s="118"/>
+      <c r="C14" s="118"/>
+      <c r="D14" s="118"/>
       <c r="E14">
         <f>Вал!$D$6</f>
         <v>38</v>
@@ -6185,12 +6185,12 @@
       <c r="S14" s="54"/>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A15" s="75" t="s">
-        <v>143</v>
-      </c>
-      <c r="B15" s="75"/>
-      <c r="C15" s="75"/>
-      <c r="D15" s="75"/>
+      <c r="A15" s="94" t="s">
+        <v>142</v>
+      </c>
+      <c r="B15" s="94"/>
+      <c r="C15" s="94"/>
+      <c r="D15" s="94"/>
       <c r="E15">
         <f ca="1">Вал!$K$19</f>
         <v>45</v>
@@ -6225,12 +6225,12 @@
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A16" s="75" t="s">
-        <v>144</v>
-      </c>
-      <c r="B16" s="75"/>
-      <c r="C16" s="75"/>
-      <c r="D16" s="75"/>
+      <c r="A16" s="94" t="s">
+        <v>143</v>
+      </c>
+      <c r="B16" s="94"/>
+      <c r="C16" s="94"/>
+      <c r="D16" s="94"/>
       <c r="E16">
         <f ca="1">Вал!$S$18</f>
         <v>50</v>
@@ -6241,1260 +6241,1245 @@
       <c r="Z16" s="59"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G18" s="136" t="s">
+      <c r="G18" s="140" t="s">
+        <v>155</v>
+      </c>
+      <c r="H18" s="141"/>
+      <c r="I18" s="141"/>
+      <c r="J18" s="141"/>
+      <c r="K18" s="82">
+        <v>6</v>
+      </c>
+      <c r="L18" s="84"/>
+      <c r="M18" s="77"/>
+      <c r="N18" s="140" t="s">
+        <v>155</v>
+      </c>
+      <c r="O18" s="141"/>
+      <c r="P18" s="141"/>
+      <c r="Q18" s="141"/>
+      <c r="R18" s="82">
+        <v>7</v>
+      </c>
+      <c r="S18" s="84"/>
+      <c r="T18" s="77"/>
+      <c r="U18" s="140" t="s">
+        <v>155</v>
+      </c>
+      <c r="V18" s="141"/>
+      <c r="W18" s="141"/>
+      <c r="X18" s="141"/>
+      <c r="Y18" s="82">
+        <v>8</v>
+      </c>
+      <c r="Z18" s="84"/>
+    </row>
+    <row r="19" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="G19" s="133" t="s">
+        <v>151</v>
+      </c>
+      <c r="H19" s="134"/>
+      <c r="I19" s="134"/>
+      <c r="J19" s="134"/>
+      <c r="K19" s="78">
+        <v>69</v>
+      </c>
+      <c r="L19" s="76" t="s">
+        <v>158</v>
+      </c>
+      <c r="M19" s="77"/>
+      <c r="N19" s="133" t="s">
+        <v>151</v>
+      </c>
+      <c r="O19" s="134"/>
+      <c r="P19" s="134"/>
+      <c r="Q19" s="134"/>
+      <c r="R19" s="78">
+        <v>57</v>
+      </c>
+      <c r="S19" s="76" t="s">
+        <v>158</v>
+      </c>
+      <c r="T19" s="77"/>
+      <c r="U19" s="133" t="s">
+        <v>151</v>
+      </c>
+      <c r="V19" s="134"/>
+      <c r="W19" s="134"/>
+      <c r="X19" s="134"/>
+      <c r="Y19" s="78">
+        <v>64</v>
+      </c>
+      <c r="Z19" s="76" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="G20" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="H18" s="137"/>
-      <c r="I18" s="137"/>
-      <c r="J18" s="137"/>
-      <c r="K18" s="134">
-        <v>6</v>
-      </c>
-      <c r="L18" s="138"/>
-      <c r="M18" s="124"/>
-      <c r="N18" s="136" t="s">
+      <c r="H20" s="134"/>
+      <c r="I20" s="134"/>
+      <c r="J20" s="134"/>
+      <c r="K20" s="75">
+        <v>22.3</v>
+      </c>
+      <c r="L20" s="76" t="s">
+        <v>158</v>
+      </c>
+      <c r="M20" s="77"/>
+      <c r="N20" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="O18" s="137"/>
-      <c r="P18" s="137"/>
-      <c r="Q18" s="137"/>
-      <c r="R18" s="134">
+      <c r="O20" s="134"/>
+      <c r="P20" s="134"/>
+      <c r="Q20" s="134"/>
+      <c r="R20" s="75">
+        <v>20</v>
+      </c>
+      <c r="S20" s="76" t="s">
+        <v>158</v>
+      </c>
+      <c r="T20" s="77"/>
+      <c r="U20" s="133" t="s">
+        <v>156</v>
+      </c>
+      <c r="V20" s="134"/>
+      <c r="W20" s="134"/>
+      <c r="X20" s="134"/>
+      <c r="Y20" s="75">
+        <v>25.3</v>
+      </c>
+      <c r="Z20" s="76" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="G21" s="133" t="s">
+        <v>148</v>
+      </c>
+      <c r="H21" s="134"/>
+      <c r="I21" s="134"/>
+      <c r="J21" s="134"/>
+      <c r="K21" s="75">
+        <v>240</v>
+      </c>
+      <c r="L21" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="M21" s="77"/>
+      <c r="N21" s="133" t="s">
+        <v>148</v>
+      </c>
+      <c r="O21" s="134"/>
+      <c r="P21" s="134"/>
+      <c r="Q21" s="134"/>
+      <c r="R21" s="75">
+        <v>180</v>
+      </c>
+      <c r="S21" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="T21" s="77"/>
+      <c r="U21" s="133" t="s">
+        <v>148</v>
+      </c>
+      <c r="V21" s="134"/>
+      <c r="W21" s="134"/>
+      <c r="X21" s="134"/>
+      <c r="Y21" s="75">
+        <v>180</v>
+      </c>
+      <c r="Z21" s="76" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="G22" s="133" t="s">
+        <v>157</v>
+      </c>
+      <c r="H22" s="134"/>
+      <c r="I22" s="134"/>
+      <c r="J22" s="134"/>
+      <c r="K22" s="75">
+        <v>3.5</v>
+      </c>
+      <c r="L22" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="M22" s="77"/>
+      <c r="N22" s="133" t="s">
+        <v>157</v>
+      </c>
+      <c r="O22" s="134"/>
+      <c r="P22" s="134"/>
+      <c r="Q22" s="134"/>
+      <c r="R22" s="75">
+        <v>2.5</v>
+      </c>
+      <c r="S22" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="T22" s="77"/>
+      <c r="U22" s="133" t="s">
+        <v>157</v>
+      </c>
+      <c r="V22" s="134"/>
+      <c r="W22" s="134"/>
+      <c r="X22" s="134"/>
+      <c r="Y22" s="75">
+        <v>3</v>
+      </c>
+      <c r="Z22" s="76" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="G23" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="H23" s="134"/>
+      <c r="I23" s="134"/>
+      <c r="J23" s="134"/>
+      <c r="K23" s="75">
+        <v>1510</v>
+      </c>
+      <c r="L23" s="76" t="s">
+        <v>161</v>
+      </c>
+      <c r="M23" s="77"/>
+      <c r="N23" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="O23" s="134"/>
+      <c r="P23" s="134"/>
+      <c r="Q23" s="134"/>
+      <c r="R23" s="75">
+        <v>2016</v>
+      </c>
+      <c r="S23" s="76" t="s">
+        <v>161</v>
+      </c>
+      <c r="T23" s="77"/>
+      <c r="U23" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="V23" s="134"/>
+      <c r="W23" s="134"/>
+      <c r="X23" s="134"/>
+      <c r="Y23" s="75">
+        <v>2013</v>
+      </c>
+      <c r="Z23" s="76" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="24" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="G24" s="133" t="s">
+        <v>159</v>
+      </c>
+      <c r="H24" s="134"/>
+      <c r="I24" s="134"/>
+      <c r="J24" s="134"/>
+      <c r="K24" s="75">
+        <v>554</v>
+      </c>
+      <c r="L24" s="76" t="s">
+        <v>161</v>
+      </c>
+      <c r="M24" s="77"/>
+      <c r="N24" s="133" t="s">
+        <v>159</v>
+      </c>
+      <c r="O24" s="134"/>
+      <c r="P24" s="134"/>
+      <c r="Q24" s="134"/>
+      <c r="R24" s="75">
+        <v>734</v>
+      </c>
+      <c r="S24" s="76" t="s">
+        <v>161</v>
+      </c>
+      <c r="T24" s="77"/>
+      <c r="U24" s="133" t="s">
+        <v>159</v>
+      </c>
+      <c r="V24" s="134"/>
+      <c r="W24" s="134"/>
+      <c r="X24" s="134"/>
+      <c r="Y24" s="75">
+        <v>733</v>
+      </c>
+      <c r="Z24" s="76" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="25" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="G25" s="131" t="s">
+        <v>160</v>
+      </c>
+      <c r="H25" s="132"/>
+      <c r="I25" s="132"/>
+      <c r="J25" s="132"/>
+      <c r="K25" s="80">
+        <v>0</v>
+      </c>
+      <c r="L25" s="81" t="s">
+        <v>161</v>
+      </c>
+      <c r="M25" s="77"/>
+      <c r="N25" s="131" t="s">
+        <v>160</v>
+      </c>
+      <c r="O25" s="132"/>
+      <c r="P25" s="132"/>
+      <c r="Q25" s="132"/>
+      <c r="R25" s="80">
+        <v>0</v>
+      </c>
+      <c r="S25" s="81" t="s">
+        <v>161</v>
+      </c>
+      <c r="T25" s="77"/>
+      <c r="U25" s="131" t="s">
+        <v>160</v>
+      </c>
+      <c r="V25" s="132"/>
+      <c r="W25" s="132"/>
+      <c r="X25" s="132"/>
+      <c r="Y25" s="80">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="81" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="26" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="G26" s="142" t="s">
+        <v>163</v>
+      </c>
+      <c r="H26" s="143"/>
+      <c r="I26" s="143"/>
+      <c r="J26" s="143"/>
+      <c r="K26" s="143"/>
+      <c r="L26" s="144"/>
+      <c r="M26" s="77"/>
+      <c r="N26" s="142" t="s">
+        <v>163</v>
+      </c>
+      <c r="O26" s="143"/>
+      <c r="P26" s="143"/>
+      <c r="Q26" s="143"/>
+      <c r="R26" s="143"/>
+      <c r="S26" s="144"/>
+      <c r="T26" s="77"/>
+      <c r="U26" s="142" t="s">
+        <v>163</v>
+      </c>
+      <c r="V26" s="143"/>
+      <c r="W26" s="143"/>
+      <c r="X26" s="143"/>
+      <c r="Y26" s="143"/>
+      <c r="Z26" s="144"/>
+    </row>
+    <row r="27" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="G27" s="133" t="s">
+        <v>164</v>
+      </c>
+      <c r="H27" s="134"/>
+      <c r="I27" s="134"/>
+      <c r="J27" s="134"/>
+      <c r="K27" s="87">
+        <v>16</v>
+      </c>
+      <c r="L27" s="76"/>
+      <c r="M27" s="77"/>
+      <c r="N27" s="133" t="s">
+        <v>164</v>
+      </c>
+      <c r="O27" s="134"/>
+      <c r="P27" s="134"/>
+      <c r="Q27" s="134"/>
+      <c r="R27" s="87">
+        <v>17</v>
+      </c>
+      <c r="S27" s="76"/>
+      <c r="T27" s="77"/>
+      <c r="U27" s="133" t="s">
+        <v>164</v>
+      </c>
+      <c r="V27" s="134"/>
+      <c r="W27" s="134"/>
+      <c r="X27" s="134"/>
+      <c r="Y27" s="87">
+        <v>14</v>
+      </c>
+      <c r="Z27" s="76"/>
+    </row>
+    <row r="28" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="G28" s="135" t="s">
+        <v>169</v>
+      </c>
+      <c r="H28" s="136"/>
+      <c r="I28" s="136"/>
+      <c r="J28" s="136"/>
+      <c r="K28" s="87">
+        <v>0.3</v>
+      </c>
+      <c r="L28" s="79" t="s">
+        <v>16</v>
+      </c>
+      <c r="M28" s="77"/>
+      <c r="N28" s="135" t="s">
+        <v>169</v>
+      </c>
+      <c r="O28" s="136"/>
+      <c r="P28" s="136"/>
+      <c r="Q28" s="136"/>
+      <c r="R28" s="87">
+        <v>-0.3</v>
+      </c>
+      <c r="S28" s="79" t="s">
+        <v>16</v>
+      </c>
+      <c r="T28" s="77"/>
+      <c r="U28" s="135" t="s">
+        <v>169</v>
+      </c>
+      <c r="V28" s="136"/>
+      <c r="W28" s="136"/>
+      <c r="X28" s="136"/>
+      <c r="Y28" s="87">
+        <v>0.3</v>
+      </c>
+      <c r="Z28" s="79" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="G29" s="135" t="s">
+        <v>168</v>
+      </c>
+      <c r="H29" s="136"/>
+      <c r="I29" s="136"/>
+      <c r="J29" s="136"/>
+      <c r="K29" s="87">
+        <v>49</v>
+      </c>
+      <c r="L29" s="79" t="s">
+        <v>271</v>
+      </c>
+      <c r="M29" s="77"/>
+      <c r="N29" s="135" t="s">
+        <v>168</v>
+      </c>
+      <c r="O29" s="136"/>
+      <c r="P29" s="136"/>
+      <c r="Q29" s="136"/>
+      <c r="R29" s="87">
+        <v>49</v>
+      </c>
+      <c r="S29" s="79" t="s">
+        <v>271</v>
+      </c>
+      <c r="T29" s="77"/>
+      <c r="U29" s="135" t="s">
+        <v>168</v>
+      </c>
+      <c r="V29" s="136"/>
+      <c r="W29" s="136"/>
+      <c r="X29" s="136"/>
+      <c r="Y29" s="87">
+        <v>49</v>
+      </c>
+      <c r="Z29" s="79" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="30" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="G30" s="135" t="s">
+        <v>170</v>
+      </c>
+      <c r="H30" s="136"/>
+      <c r="I30" s="136"/>
+      <c r="J30" s="136"/>
+      <c r="K30" s="87" t="s">
+        <v>171</v>
+      </c>
+      <c r="L30" s="76"/>
+      <c r="M30" s="77"/>
+      <c r="N30" s="135" t="s">
+        <v>170</v>
+      </c>
+      <c r="O30" s="136"/>
+      <c r="P30" s="136"/>
+      <c r="Q30" s="136"/>
+      <c r="R30" s="87" t="s">
+        <v>171</v>
+      </c>
+      <c r="S30" s="76"/>
+      <c r="T30" s="77"/>
+      <c r="U30" s="135" t="s">
+        <v>170</v>
+      </c>
+      <c r="V30" s="136"/>
+      <c r="W30" s="136"/>
+      <c r="X30" s="136"/>
+      <c r="Y30" s="87" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z30" s="76"/>
+    </row>
+    <row r="31" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B31" s="86"/>
+      <c r="G31" s="133" t="s">
+        <v>216</v>
+      </c>
+      <c r="H31" s="134"/>
+      <c r="I31" s="134"/>
+      <c r="J31" s="134"/>
+      <c r="K31" s="87">
+        <v>56</v>
+      </c>
+      <c r="L31" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="M31" s="77"/>
+      <c r="N31" s="133" t="s">
+        <v>216</v>
+      </c>
+      <c r="O31" s="134"/>
+      <c r="P31" s="134"/>
+      <c r="Q31" s="134"/>
+      <c r="R31" s="87">
+        <v>42.5</v>
+      </c>
+      <c r="S31" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="T31" s="77"/>
+      <c r="U31" s="133" t="s">
+        <v>216</v>
+      </c>
+      <c r="V31" s="134"/>
+      <c r="W31" s="134"/>
+      <c r="X31" s="134"/>
+      <c r="Y31" s="87">
+        <v>42</v>
+      </c>
+      <c r="Z31" s="76" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="G32" s="133" t="s">
+        <v>186</v>
+      </c>
+      <c r="H32" s="134"/>
+      <c r="I32" s="134"/>
+      <c r="J32" s="134"/>
+      <c r="K32" s="87">
+        <v>65</v>
+      </c>
+      <c r="L32" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="M32" s="77"/>
+      <c r="N32" s="133" t="s">
+        <v>186</v>
+      </c>
+      <c r="O32" s="134"/>
+      <c r="P32" s="134"/>
+      <c r="Q32" s="134"/>
+      <c r="R32" s="87">
+        <v>49</v>
+      </c>
+      <c r="S32" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="T32" s="77"/>
+      <c r="U32" s="133" t="s">
+        <v>186</v>
+      </c>
+      <c r="V32" s="134"/>
+      <c r="W32" s="134"/>
+      <c r="X32" s="134"/>
+      <c r="Y32" s="87">
+        <v>49.8</v>
+      </c>
+      <c r="Z32" s="76" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="G33" s="133" t="s">
+        <v>177</v>
+      </c>
+      <c r="H33" s="134"/>
+      <c r="I33" s="134"/>
+      <c r="J33" s="134"/>
+      <c r="K33" s="87">
+        <v>49.35</v>
+      </c>
+      <c r="L33" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="M33" s="77"/>
+      <c r="N33" s="133" t="s">
+        <v>177</v>
+      </c>
+      <c r="O33" s="134"/>
+      <c r="P33" s="134"/>
+      <c r="Q33" s="134"/>
+      <c r="R33" s="87">
+        <v>37.75</v>
+      </c>
+      <c r="S33" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="T33" s="77"/>
+      <c r="U33" s="133" t="s">
+        <v>177</v>
+      </c>
+      <c r="V33" s="134"/>
+      <c r="W33" s="134"/>
+      <c r="X33" s="134"/>
+      <c r="Y33" s="87">
+        <v>36.6</v>
+      </c>
+      <c r="Z33" s="76" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="G34" s="133" t="s">
+        <v>167</v>
+      </c>
+      <c r="H34" s="134"/>
+      <c r="I34" s="134"/>
+      <c r="J34" s="134"/>
+      <c r="K34" s="87">
+        <v>40</v>
+      </c>
+      <c r="L34" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="M34" s="77"/>
+      <c r="N34" s="133" t="s">
+        <v>167</v>
+      </c>
+      <c r="O34" s="134"/>
+      <c r="P34" s="134"/>
+      <c r="Q34" s="134"/>
+      <c r="R34" s="87">
+        <v>62</v>
+      </c>
+      <c r="S34" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="T34" s="77"/>
+      <c r="U34" s="131" t="s">
+        <v>167</v>
+      </c>
+      <c r="V34" s="132"/>
+      <c r="W34" s="132"/>
+      <c r="X34" s="132"/>
+      <c r="Y34" s="87">
+        <v>79</v>
+      </c>
+      <c r="Z34" s="81" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="G35" s="142" t="s">
+        <v>126</v>
+      </c>
+      <c r="H35" s="143"/>
+      <c r="I35" s="143"/>
+      <c r="J35" s="143"/>
+      <c r="K35" s="143"/>
+      <c r="L35" s="144"/>
+      <c r="M35" s="77"/>
+      <c r="N35" s="142" t="s">
+        <v>126</v>
+      </c>
+      <c r="O35" s="143"/>
+      <c r="P35" s="143"/>
+      <c r="Q35" s="143"/>
+      <c r="R35" s="143"/>
+      <c r="S35" s="144"/>
+      <c r="T35" s="77"/>
+      <c r="U35" s="142" t="s">
+        <v>126</v>
+      </c>
+      <c r="V35" s="143"/>
+      <c r="W35" s="143"/>
+      <c r="X35" s="143"/>
+      <c r="Y35" s="143"/>
+      <c r="Z35" s="144"/>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="G36" s="133" t="s">
+        <v>164</v>
+      </c>
+      <c r="H36" s="134"/>
+      <c r="I36" s="134"/>
+      <c r="J36" s="134"/>
+      <c r="K36" s="87">
+        <v>121</v>
+      </c>
+      <c r="L36" s="76"/>
+      <c r="M36" s="77"/>
+      <c r="N36" s="133" t="s">
+        <v>164</v>
+      </c>
+      <c r="O36" s="134"/>
+      <c r="P36" s="134"/>
+      <c r="Q36" s="134"/>
+      <c r="R36" s="87">
+        <v>127</v>
+      </c>
+      <c r="S36" s="76"/>
+      <c r="T36" s="77"/>
+      <c r="U36" s="133" t="s">
+        <v>164</v>
+      </c>
+      <c r="V36" s="134"/>
+      <c r="W36" s="134"/>
+      <c r="X36" s="134"/>
+      <c r="Y36" s="87">
+        <v>106</v>
+      </c>
+      <c r="Z36" s="76"/>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="G37" s="135" t="s">
+        <v>169</v>
+      </c>
+      <c r="H37" s="136"/>
+      <c r="I37" s="136"/>
+      <c r="J37" s="136"/>
+      <c r="K37" s="87">
+        <v>-0.22800000000000001</v>
+      </c>
+      <c r="L37" s="79" t="s">
+        <v>16</v>
+      </c>
+      <c r="M37" s="88"/>
+      <c r="N37" s="135" t="s">
+        <v>169</v>
+      </c>
+      <c r="O37" s="136"/>
+      <c r="P37" s="136"/>
+      <c r="Q37" s="136"/>
+      <c r="R37" s="87">
+        <v>0.3</v>
+      </c>
+      <c r="S37" s="79" t="s">
+        <v>16</v>
+      </c>
+      <c r="T37" s="88"/>
+      <c r="U37" s="135" t="s">
+        <v>169</v>
+      </c>
+      <c r="V37" s="136"/>
+      <c r="W37" s="136"/>
+      <c r="X37" s="136"/>
+      <c r="Y37" s="87">
+        <v>-0.3</v>
+      </c>
+      <c r="Z37" s="79" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="G38" s="135" t="s">
+        <v>168</v>
+      </c>
+      <c r="H38" s="136"/>
+      <c r="I38" s="136"/>
+      <c r="J38" s="136"/>
+      <c r="K38" s="87">
+        <v>28.5</v>
+      </c>
+      <c r="L38" s="79" t="s">
+        <v>271</v>
+      </c>
+      <c r="M38" s="77"/>
+      <c r="N38" s="135" t="s">
+        <v>168</v>
+      </c>
+      <c r="O38" s="136"/>
+      <c r="P38" s="136"/>
+      <c r="Q38" s="136"/>
+      <c r="R38" s="87">
+        <v>28.5</v>
+      </c>
+      <c r="S38" s="79" t="s">
+        <v>271</v>
+      </c>
+      <c r="T38" s="77"/>
+      <c r="U38" s="135" t="s">
+        <v>168</v>
+      </c>
+      <c r="V38" s="136"/>
+      <c r="W38" s="136"/>
+      <c r="X38" s="136"/>
+      <c r="Y38" s="87">
+        <v>28.5</v>
+      </c>
+      <c r="Z38" s="79" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="G39" s="135" t="s">
+        <v>170</v>
+      </c>
+      <c r="H39" s="136"/>
+      <c r="I39" s="136"/>
+      <c r="J39" s="136"/>
+      <c r="K39" s="87" t="s">
+        <v>172</v>
+      </c>
+      <c r="L39" s="76"/>
+      <c r="M39" s="77"/>
+      <c r="N39" s="135" t="s">
+        <v>170</v>
+      </c>
+      <c r="O39" s="136"/>
+      <c r="P39" s="136"/>
+      <c r="Q39" s="136"/>
+      <c r="R39" s="87" t="s">
+        <v>172</v>
+      </c>
+      <c r="S39" s="76"/>
+      <c r="T39" s="77"/>
+      <c r="U39" s="135" t="s">
+        <v>170</v>
+      </c>
+      <c r="V39" s="136"/>
+      <c r="W39" s="136"/>
+      <c r="X39" s="136"/>
+      <c r="Y39" s="87" t="s">
+        <v>172</v>
+      </c>
+      <c r="Z39" s="76"/>
+      <c r="AA39" s="86"/>
+    </row>
+    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="G40" s="133" t="s">
+        <v>216</v>
+      </c>
+      <c r="H40" s="134"/>
+      <c r="I40" s="134"/>
+      <c r="J40" s="134"/>
+      <c r="K40" s="87">
+        <v>423.5</v>
+      </c>
+      <c r="L40" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="M40" s="77"/>
+      <c r="N40" s="133" t="s">
+        <v>216</v>
+      </c>
+      <c r="O40" s="134"/>
+      <c r="P40" s="134"/>
+      <c r="Q40" s="134"/>
+      <c r="R40" s="87">
+        <v>317.5</v>
+      </c>
+      <c r="S40" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="T40" s="77"/>
+      <c r="U40" s="133" t="s">
+        <v>216</v>
+      </c>
+      <c r="V40" s="134"/>
+      <c r="W40" s="134"/>
+      <c r="X40" s="134"/>
+      <c r="Y40" s="87">
+        <v>318</v>
+      </c>
+      <c r="Z40" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA40" s="86"/>
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="G41" s="133" t="s">
+        <v>186</v>
+      </c>
+      <c r="H41" s="134"/>
+      <c r="I41" s="134"/>
+      <c r="J41" s="134"/>
+      <c r="K41" s="87">
+        <v>428.9</v>
+      </c>
+      <c r="L41" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="M41" s="77"/>
+      <c r="N41" s="133" t="s">
+        <v>186</v>
+      </c>
+      <c r="O41" s="134"/>
+      <c r="P41" s="134"/>
+      <c r="Q41" s="134"/>
+      <c r="R41" s="87">
+        <v>321</v>
+      </c>
+      <c r="S41" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="T41" s="77"/>
+      <c r="U41" s="133" t="s">
+        <v>186</v>
+      </c>
+      <c r="V41" s="134"/>
+      <c r="W41" s="134"/>
+      <c r="X41" s="134"/>
+      <c r="Y41" s="87">
+        <v>322</v>
+      </c>
+      <c r="Z41" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA41" s="86"/>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="G42" s="133" t="s">
+        <v>177</v>
+      </c>
+      <c r="H42" s="134"/>
+      <c r="I42" s="134"/>
+      <c r="J42" s="134"/>
+      <c r="K42" s="87">
+        <v>413</v>
+      </c>
+      <c r="L42" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="M42" s="77"/>
+      <c r="N42" s="133" t="s">
+        <v>177</v>
+      </c>
+      <c r="O42" s="134"/>
+      <c r="P42" s="134"/>
+      <c r="Q42" s="134"/>
+      <c r="R42" s="87">
+        <v>309.75</v>
+      </c>
+      <c r="S42" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="T42" s="77"/>
+      <c r="U42" s="133" t="s">
+        <v>177</v>
+      </c>
+      <c r="V42" s="134"/>
+      <c r="W42" s="134"/>
+      <c r="X42" s="134"/>
+      <c r="Y42" s="87">
+        <v>308.7</v>
+      </c>
+      <c r="Z42" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA42" s="16"/>
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="G43" s="131" t="s">
+        <v>167</v>
+      </c>
+      <c r="H43" s="132"/>
+      <c r="I43" s="132"/>
+      <c r="J43" s="132"/>
+      <c r="K43" s="89">
+        <v>36</v>
+      </c>
+      <c r="L43" s="81" t="s">
+        <v>16</v>
+      </c>
+      <c r="M43" s="77"/>
+      <c r="N43" s="131" t="s">
+        <v>167</v>
+      </c>
+      <c r="O43" s="132"/>
+      <c r="P43" s="132"/>
+      <c r="Q43" s="132"/>
+      <c r="R43" s="89">
+        <v>57</v>
+      </c>
+      <c r="S43" s="81" t="s">
+        <v>16</v>
+      </c>
+      <c r="T43" s="77"/>
+      <c r="U43" s="131" t="s">
+        <v>167</v>
+      </c>
+      <c r="V43" s="132"/>
+      <c r="W43" s="132"/>
+      <c r="X43" s="132"/>
+      <c r="Y43" s="89">
+        <v>72</v>
+      </c>
+      <c r="Z43" s="81" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA43" s="86"/>
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="L44" s="86"/>
+      <c r="AA44" s="86"/>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A45" s="142" t="s">
+        <v>176</v>
+      </c>
+      <c r="B45" s="143"/>
+      <c r="C45" s="143"/>
+      <c r="D45" s="143"/>
+      <c r="E45" s="85">
         <v>7</v>
       </c>
-      <c r="S18" s="138"/>
-      <c r="T18" s="124"/>
-      <c r="U18" s="136" t="s">
-        <v>156</v>
-      </c>
-      <c r="V18" s="137"/>
-      <c r="W18" s="137"/>
-      <c r="X18" s="137"/>
-      <c r="Y18" s="134">
-        <v>8</v>
-      </c>
-      <c r="Z18" s="138"/>
-    </row>
-    <row r="19" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G19" s="120" t="s">
-        <v>152</v>
-      </c>
-      <c r="H19" s="116"/>
-      <c r="I19" s="116"/>
-      <c r="J19" s="116"/>
-      <c r="K19" s="125">
-        <v>69</v>
-      </c>
-      <c r="L19" s="122" t="s">
+      <c r="L45" s="86"/>
+      <c r="AA45" s="86"/>
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A46" s="133" t="s">
+        <v>148</v>
+      </c>
+      <c r="B46" s="134"/>
+      <c r="C46" s="134"/>
+      <c r="D46" s="75">
+        <f>HLOOKUP($E$45,$18:$43,4)</f>
+        <v>180</v>
+      </c>
+      <c r="E46" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="L46" s="86"/>
+      <c r="R46" s="86"/>
+      <c r="S46" s="86"/>
+      <c r="AA46" s="86"/>
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A47" s="137" t="s">
+        <v>157</v>
+      </c>
+      <c r="B47" s="138"/>
+      <c r="C47" s="138"/>
+      <c r="D47" s="80">
+        <f>HLOOKUP($E$45,$18:$43,5)</f>
+        <v>2.5</v>
+      </c>
+      <c r="E47" s="81" t="s">
+        <v>16</v>
+      </c>
+      <c r="L47" s="86"/>
+      <c r="AA47" s="86"/>
+    </row>
+    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A48" s="135" t="s">
+        <v>228</v>
+      </c>
+      <c r="B48" s="136"/>
+      <c r="C48" s="136"/>
+      <c r="D48" s="136"/>
+      <c r="E48" s="139"/>
+      <c r="L48" s="86"/>
+      <c r="Z48" s="59"/>
+    </row>
+    <row r="49" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A49" s="140" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49" s="141"/>
+      <c r="C49" s="141"/>
+      <c r="D49" s="82">
+        <f>HLOOKUP($E$45,$18:$43,6)</f>
+        <v>2016</v>
+      </c>
+      <c r="E49" s="84" t="s">
+        <v>161</v>
+      </c>
+      <c r="Z49" s="59"/>
+    </row>
+    <row r="50" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A50" s="133" t="s">
         <v>159</v>
       </c>
-      <c r="M19" s="124"/>
-      <c r="N19" s="120" t="s">
-        <v>152</v>
-      </c>
-      <c r="O19" s="116"/>
-      <c r="P19" s="116"/>
-      <c r="Q19" s="116"/>
-      <c r="R19" s="125">
-        <v>57</v>
-      </c>
-      <c r="S19" s="122" t="s">
-        <v>159</v>
-      </c>
-      <c r="T19" s="124"/>
-      <c r="U19" s="120" t="s">
-        <v>152</v>
-      </c>
-      <c r="V19" s="116"/>
-      <c r="W19" s="116"/>
-      <c r="X19" s="116"/>
-      <c r="Y19" s="125">
-        <v>64</v>
-      </c>
-      <c r="Z19" s="122" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="20" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G20" s="120" t="s">
-        <v>157</v>
-      </c>
-      <c r="H20" s="116"/>
-      <c r="I20" s="116"/>
-      <c r="J20" s="116"/>
-      <c r="K20" s="121">
-        <v>22.3</v>
-      </c>
-      <c r="L20" s="122" t="s">
-        <v>159</v>
-      </c>
-      <c r="M20" s="124"/>
-      <c r="N20" s="120" t="s">
-        <v>157</v>
-      </c>
-      <c r="O20" s="116"/>
-      <c r="P20" s="116"/>
-      <c r="Q20" s="116"/>
-      <c r="R20" s="121">
-        <v>20</v>
-      </c>
-      <c r="S20" s="122" t="s">
-        <v>159</v>
-      </c>
-      <c r="T20" s="124"/>
-      <c r="U20" s="120" t="s">
-        <v>157</v>
-      </c>
-      <c r="V20" s="116"/>
-      <c r="W20" s="116"/>
-      <c r="X20" s="116"/>
-      <c r="Y20" s="121">
-        <v>25.3</v>
-      </c>
-      <c r="Z20" s="122" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="21" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G21" s="120" t="s">
-        <v>149</v>
-      </c>
-      <c r="H21" s="116"/>
-      <c r="I21" s="116"/>
-      <c r="J21" s="116"/>
-      <c r="K21" s="121">
-        <v>240</v>
-      </c>
-      <c r="L21" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="M21" s="124"/>
-      <c r="N21" s="120" t="s">
-        <v>149</v>
-      </c>
-      <c r="O21" s="116"/>
-      <c r="P21" s="116"/>
-      <c r="Q21" s="116"/>
-      <c r="R21" s="121">
-        <v>180</v>
-      </c>
-      <c r="S21" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="T21" s="124"/>
-      <c r="U21" s="120" t="s">
-        <v>149</v>
-      </c>
-      <c r="V21" s="116"/>
-      <c r="W21" s="116"/>
-      <c r="X21" s="116"/>
-      <c r="Y21" s="121">
-        <v>180</v>
-      </c>
-      <c r="Z21" s="122" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G22" s="120" t="s">
-        <v>158</v>
-      </c>
-      <c r="H22" s="116"/>
-      <c r="I22" s="116"/>
-      <c r="J22" s="116"/>
-      <c r="K22" s="121">
-        <v>3.5</v>
-      </c>
-      <c r="L22" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="M22" s="124"/>
-      <c r="N22" s="120" t="s">
-        <v>158</v>
-      </c>
-      <c r="O22" s="116"/>
-      <c r="P22" s="116"/>
-      <c r="Q22" s="116"/>
-      <c r="R22" s="121">
-        <v>2.5</v>
-      </c>
-      <c r="S22" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="T22" s="124"/>
-      <c r="U22" s="120" t="s">
-        <v>158</v>
-      </c>
-      <c r="V22" s="116"/>
-      <c r="W22" s="116"/>
-      <c r="X22" s="116"/>
-      <c r="Y22" s="121">
-        <v>3</v>
-      </c>
-      <c r="Z22" s="122" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G23" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="H23" s="116"/>
-      <c r="I23" s="116"/>
-      <c r="J23" s="116"/>
-      <c r="K23" s="121">
-        <v>1510</v>
-      </c>
-      <c r="L23" s="122" t="s">
-        <v>162</v>
-      </c>
-      <c r="M23" s="124"/>
-      <c r="N23" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="O23" s="116"/>
-      <c r="P23" s="116"/>
-      <c r="Q23" s="116"/>
-      <c r="R23" s="121">
-        <v>2016</v>
-      </c>
-      <c r="S23" s="122" t="s">
-        <v>162</v>
-      </c>
-      <c r="T23" s="124"/>
-      <c r="U23" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="V23" s="116"/>
-      <c r="W23" s="116"/>
-      <c r="X23" s="116"/>
-      <c r="Y23" s="121">
-        <v>2013</v>
-      </c>
-      <c r="Z23" s="122" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="24" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G24" s="120" t="s">
+      <c r="B50" s="134"/>
+      <c r="C50" s="134"/>
+      <c r="D50" s="75">
+        <f>HLOOKUP($E$45,$18:$43,7)</f>
+        <v>734</v>
+      </c>
+      <c r="E50" s="76" t="s">
+        <v>161</v>
+      </c>
+      <c r="Z50" s="59"/>
+    </row>
+    <row r="51" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A51" s="131" t="s">
         <v>160</v>
       </c>
-      <c r="H24" s="116"/>
-      <c r="I24" s="116"/>
-      <c r="J24" s="116"/>
-      <c r="K24" s="121">
-        <v>554</v>
-      </c>
-      <c r="L24" s="122" t="s">
-        <v>162</v>
-      </c>
-      <c r="M24" s="124"/>
-      <c r="N24" s="120" t="s">
-        <v>160</v>
-      </c>
-      <c r="O24" s="116"/>
-      <c r="P24" s="116"/>
-      <c r="Q24" s="116"/>
-      <c r="R24" s="121">
-        <v>734</v>
-      </c>
-      <c r="S24" s="122" t="s">
-        <v>162</v>
-      </c>
-      <c r="T24" s="124"/>
-      <c r="U24" s="120" t="s">
-        <v>160</v>
-      </c>
-      <c r="V24" s="116"/>
-      <c r="W24" s="116"/>
-      <c r="X24" s="116"/>
-      <c r="Y24" s="121">
-        <v>733</v>
-      </c>
-      <c r="Z24" s="122" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="25" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G25" s="139" t="s">
-        <v>161</v>
-      </c>
-      <c r="H25" s="140"/>
-      <c r="I25" s="140"/>
-      <c r="J25" s="140"/>
-      <c r="K25" s="132">
-        <v>0</v>
-      </c>
-      <c r="L25" s="133" t="s">
-        <v>162</v>
-      </c>
-      <c r="M25" s="124"/>
-      <c r="N25" s="139" t="s">
-        <v>161</v>
-      </c>
-      <c r="O25" s="140"/>
-      <c r="P25" s="140"/>
-      <c r="Q25" s="140"/>
-      <c r="R25" s="132">
-        <v>0</v>
-      </c>
-      <c r="S25" s="133" t="s">
-        <v>162</v>
-      </c>
-      <c r="T25" s="124"/>
-      <c r="U25" s="139" t="s">
-        <v>161</v>
-      </c>
-      <c r="V25" s="140"/>
-      <c r="W25" s="140"/>
-      <c r="X25" s="140"/>
-      <c r="Y25" s="132">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="133" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="26" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G26" s="117" t="s">
-        <v>164</v>
-      </c>
-      <c r="H26" s="118"/>
-      <c r="I26" s="118"/>
-      <c r="J26" s="118"/>
-      <c r="K26" s="118"/>
-      <c r="L26" s="119"/>
-      <c r="M26" s="124"/>
-      <c r="N26" s="117" t="s">
-        <v>164</v>
-      </c>
-      <c r="O26" s="118"/>
-      <c r="P26" s="118"/>
-      <c r="Q26" s="118"/>
-      <c r="R26" s="118"/>
-      <c r="S26" s="119"/>
-      <c r="T26" s="124"/>
-      <c r="U26" s="117" t="s">
-        <v>164</v>
-      </c>
-      <c r="V26" s="118"/>
-      <c r="W26" s="118"/>
-      <c r="X26" s="118"/>
-      <c r="Y26" s="118"/>
-      <c r="Z26" s="119"/>
-    </row>
-    <row r="27" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G27" s="120" t="s">
-        <v>165</v>
-      </c>
-      <c r="H27" s="116"/>
-      <c r="I27" s="116"/>
-      <c r="J27" s="116"/>
-      <c r="K27" s="143">
-        <v>16</v>
-      </c>
-      <c r="L27" s="122"/>
-      <c r="M27" s="124"/>
-      <c r="N27" s="120" t="s">
-        <v>165</v>
-      </c>
-      <c r="O27" s="116"/>
-      <c r="P27" s="116"/>
-      <c r="Q27" s="116"/>
-      <c r="R27" s="143">
-        <v>17</v>
-      </c>
-      <c r="S27" s="122"/>
-      <c r="T27" s="124"/>
-      <c r="U27" s="120" t="s">
-        <v>165</v>
-      </c>
-      <c r="V27" s="116"/>
-      <c r="W27" s="116"/>
-      <c r="X27" s="116"/>
-      <c r="Y27" s="143">
-        <v>14</v>
-      </c>
-      <c r="Z27" s="122"/>
-    </row>
-    <row r="28" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G28" s="127" t="s">
-        <v>170</v>
-      </c>
-      <c r="H28" s="126"/>
-      <c r="I28" s="126"/>
-      <c r="J28" s="126"/>
-      <c r="K28" s="143">
-        <v>0.3</v>
-      </c>
-      <c r="L28" s="129" t="s">
-        <v>16</v>
-      </c>
-      <c r="M28" s="124"/>
-      <c r="N28" s="127" t="s">
-        <v>170</v>
-      </c>
-      <c r="O28" s="126"/>
-      <c r="P28" s="126"/>
-      <c r="Q28" s="126"/>
-      <c r="R28" s="143">
-        <v>-0.3</v>
-      </c>
-      <c r="S28" s="129" t="s">
-        <v>16</v>
-      </c>
-      <c r="T28" s="124"/>
-      <c r="U28" s="127" t="s">
-        <v>170</v>
-      </c>
-      <c r="V28" s="126"/>
-      <c r="W28" s="126"/>
-      <c r="X28" s="126"/>
-      <c r="Y28" s="143">
-        <v>0.3</v>
-      </c>
-      <c r="Z28" s="129" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G29" s="127" t="s">
-        <v>169</v>
-      </c>
-      <c r="H29" s="126"/>
-      <c r="I29" s="126"/>
-      <c r="J29" s="126"/>
-      <c r="K29" s="143">
-        <v>49</v>
-      </c>
-      <c r="L29" s="129" t="s">
-        <v>273</v>
-      </c>
-      <c r="M29" s="124"/>
-      <c r="N29" s="127" t="s">
-        <v>169</v>
-      </c>
-      <c r="O29" s="126"/>
-      <c r="P29" s="126"/>
-      <c r="Q29" s="126"/>
-      <c r="R29" s="143">
-        <v>49</v>
-      </c>
-      <c r="S29" s="129" t="s">
-        <v>273</v>
-      </c>
-      <c r="T29" s="124"/>
-      <c r="U29" s="127" t="s">
-        <v>169</v>
-      </c>
-      <c r="V29" s="126"/>
-      <c r="W29" s="126"/>
-      <c r="X29" s="126"/>
-      <c r="Y29" s="143">
-        <v>49</v>
-      </c>
-      <c r="Z29" s="129" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="30" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G30" s="127" t="s">
-        <v>171</v>
-      </c>
-      <c r="H30" s="126"/>
-      <c r="I30" s="126"/>
-      <c r="J30" s="126"/>
-      <c r="K30" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="L30" s="122"/>
-      <c r="M30" s="124"/>
-      <c r="N30" s="127" t="s">
-        <v>171</v>
-      </c>
-      <c r="O30" s="126"/>
-      <c r="P30" s="126"/>
-      <c r="Q30" s="126"/>
-      <c r="R30" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="S30" s="122"/>
-      <c r="T30" s="124"/>
-      <c r="U30" s="127" t="s">
-        <v>171</v>
-      </c>
-      <c r="V30" s="126"/>
-      <c r="W30" s="126"/>
-      <c r="X30" s="126"/>
-      <c r="Y30" s="143" t="s">
-        <v>172</v>
-      </c>
-      <c r="Z30" s="122"/>
-    </row>
-    <row r="31" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B31" s="142"/>
-      <c r="G31" s="120" t="s">
-        <v>217</v>
-      </c>
-      <c r="H31" s="116"/>
-      <c r="I31" s="116"/>
-      <c r="J31" s="116"/>
-      <c r="K31" s="143">
-        <v>56</v>
-      </c>
-      <c r="L31" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="M31" s="124"/>
-      <c r="N31" s="120" t="s">
-        <v>217</v>
-      </c>
-      <c r="O31" s="116"/>
-      <c r="P31" s="116"/>
-      <c r="Q31" s="116"/>
-      <c r="R31" s="143">
-        <v>42.5</v>
-      </c>
-      <c r="S31" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="T31" s="124"/>
-      <c r="U31" s="120" t="s">
-        <v>217</v>
-      </c>
-      <c r="V31" s="116"/>
-      <c r="W31" s="116"/>
-      <c r="X31" s="116"/>
-      <c r="Y31" s="143">
-        <v>42</v>
-      </c>
-      <c r="Z31" s="122" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G32" s="120" t="s">
-        <v>187</v>
-      </c>
-      <c r="H32" s="116"/>
-      <c r="I32" s="116"/>
-      <c r="J32" s="116"/>
-      <c r="K32" s="143">
-        <v>65</v>
-      </c>
-      <c r="L32" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="M32" s="124"/>
-      <c r="N32" s="120" t="s">
-        <v>187</v>
-      </c>
-      <c r="O32" s="116"/>
-      <c r="P32" s="116"/>
-      <c r="Q32" s="116"/>
-      <c r="R32" s="143">
-        <v>49</v>
-      </c>
-      <c r="S32" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="T32" s="124"/>
-      <c r="U32" s="120" t="s">
-        <v>187</v>
-      </c>
-      <c r="V32" s="116"/>
-      <c r="W32" s="116"/>
-      <c r="X32" s="116"/>
-      <c r="Y32" s="143">
-        <v>49.8</v>
-      </c>
-      <c r="Z32" s="122" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G33" s="120" t="s">
-        <v>178</v>
-      </c>
-      <c r="H33" s="116"/>
-      <c r="I33" s="116"/>
-      <c r="J33" s="116"/>
-      <c r="K33" s="143">
-        <v>49.35</v>
-      </c>
-      <c r="L33" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="M33" s="124"/>
-      <c r="N33" s="120" t="s">
-        <v>178</v>
-      </c>
-      <c r="O33" s="116"/>
-      <c r="P33" s="116"/>
-      <c r="Q33" s="116"/>
-      <c r="R33" s="143">
-        <v>37.75</v>
-      </c>
-      <c r="S33" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="T33" s="124"/>
-      <c r="U33" s="120" t="s">
-        <v>178</v>
-      </c>
-      <c r="V33" s="116"/>
-      <c r="W33" s="116"/>
-      <c r="X33" s="116"/>
-      <c r="Y33" s="143">
-        <v>36.6</v>
-      </c>
-      <c r="Z33" s="122" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G34" s="120" t="s">
-        <v>168</v>
-      </c>
-      <c r="H34" s="116"/>
-      <c r="I34" s="116"/>
-      <c r="J34" s="116"/>
-      <c r="K34" s="143">
-        <v>40</v>
-      </c>
-      <c r="L34" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="M34" s="124"/>
-      <c r="N34" s="120" t="s">
-        <v>168</v>
-      </c>
-      <c r="O34" s="116"/>
-      <c r="P34" s="116"/>
-      <c r="Q34" s="116"/>
-      <c r="R34" s="143">
-        <v>62</v>
-      </c>
-      <c r="S34" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="T34" s="124"/>
-      <c r="U34" s="139" t="s">
-        <v>168</v>
-      </c>
-      <c r="V34" s="140"/>
-      <c r="W34" s="140"/>
-      <c r="X34" s="140"/>
-      <c r="Y34" s="143">
-        <v>79</v>
-      </c>
-      <c r="Z34" s="133" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G35" s="117" t="s">
-        <v>126</v>
-      </c>
-      <c r="H35" s="118"/>
-      <c r="I35" s="118"/>
-      <c r="J35" s="118"/>
-      <c r="K35" s="118"/>
-      <c r="L35" s="119"/>
-      <c r="M35" s="124"/>
-      <c r="N35" s="117" t="s">
-        <v>126</v>
-      </c>
-      <c r="O35" s="118"/>
-      <c r="P35" s="118"/>
-      <c r="Q35" s="118"/>
-      <c r="R35" s="118"/>
-      <c r="S35" s="119"/>
-      <c r="T35" s="124"/>
-      <c r="U35" s="117" t="s">
-        <v>126</v>
-      </c>
-      <c r="V35" s="118"/>
-      <c r="W35" s="118"/>
-      <c r="X35" s="118"/>
-      <c r="Y35" s="118"/>
-      <c r="Z35" s="119"/>
-    </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G36" s="120" t="s">
-        <v>165</v>
-      </c>
-      <c r="H36" s="116"/>
-      <c r="I36" s="116"/>
-      <c r="J36" s="116"/>
-      <c r="K36" s="143">
-        <v>121</v>
-      </c>
-      <c r="L36" s="122"/>
-      <c r="M36" s="124"/>
-      <c r="N36" s="120" t="s">
-        <v>165</v>
-      </c>
-      <c r="O36" s="116"/>
-      <c r="P36" s="116"/>
-      <c r="Q36" s="116"/>
-      <c r="R36" s="143">
-        <v>127</v>
-      </c>
-      <c r="S36" s="122"/>
-      <c r="T36" s="124"/>
-      <c r="U36" s="120" t="s">
-        <v>165</v>
-      </c>
-      <c r="V36" s="116"/>
-      <c r="W36" s="116"/>
-      <c r="X36" s="116"/>
-      <c r="Y36" s="143">
-        <v>106</v>
-      </c>
-      <c r="Z36" s="122"/>
-    </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G37" s="127" t="s">
-        <v>170</v>
-      </c>
-      <c r="H37" s="126"/>
-      <c r="I37" s="126"/>
-      <c r="J37" s="126"/>
-      <c r="K37" s="143">
-        <v>-0.22800000000000001</v>
-      </c>
-      <c r="L37" s="129" t="s">
-        <v>16</v>
-      </c>
-      <c r="M37" s="144"/>
-      <c r="N37" s="127" t="s">
-        <v>170</v>
-      </c>
-      <c r="O37" s="126"/>
-      <c r="P37" s="126"/>
-      <c r="Q37" s="126"/>
-      <c r="R37" s="143">
-        <v>0.3</v>
-      </c>
-      <c r="S37" s="129" t="s">
-        <v>16</v>
-      </c>
-      <c r="T37" s="144"/>
-      <c r="U37" s="127" t="s">
-        <v>170</v>
-      </c>
-      <c r="V37" s="126"/>
-      <c r="W37" s="126"/>
-      <c r="X37" s="126"/>
-      <c r="Y37" s="143">
-        <v>-0.3</v>
-      </c>
-      <c r="Z37" s="129" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G38" s="127" t="s">
-        <v>169</v>
-      </c>
-      <c r="H38" s="126"/>
-      <c r="I38" s="126"/>
-      <c r="J38" s="126"/>
-      <c r="K38" s="143">
-        <v>28.5</v>
-      </c>
-      <c r="L38" s="129" t="s">
-        <v>273</v>
-      </c>
-      <c r="M38" s="124"/>
-      <c r="N38" s="127" t="s">
-        <v>169</v>
-      </c>
-      <c r="O38" s="126"/>
-      <c r="P38" s="126"/>
-      <c r="Q38" s="126"/>
-      <c r="R38" s="143">
-        <v>28.5</v>
-      </c>
-      <c r="S38" s="129" t="s">
-        <v>273</v>
-      </c>
-      <c r="T38" s="124"/>
-      <c r="U38" s="127" t="s">
-        <v>169</v>
-      </c>
-      <c r="V38" s="126"/>
-      <c r="W38" s="126"/>
-      <c r="X38" s="126"/>
-      <c r="Y38" s="143">
-        <v>28.5</v>
-      </c>
-      <c r="Z38" s="129" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G39" s="127" t="s">
-        <v>171</v>
-      </c>
-      <c r="H39" s="126"/>
-      <c r="I39" s="126"/>
-      <c r="J39" s="126"/>
-      <c r="K39" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="L39" s="122"/>
-      <c r="M39" s="124"/>
-      <c r="N39" s="127" t="s">
-        <v>171</v>
-      </c>
-      <c r="O39" s="126"/>
-      <c r="P39" s="126"/>
-      <c r="Q39" s="126"/>
-      <c r="R39" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="S39" s="122"/>
-      <c r="T39" s="124"/>
-      <c r="U39" s="127" t="s">
-        <v>171</v>
-      </c>
-      <c r="V39" s="126"/>
-      <c r="W39" s="126"/>
-      <c r="X39" s="126"/>
-      <c r="Y39" s="143" t="s">
-        <v>173</v>
-      </c>
-      <c r="Z39" s="122"/>
-      <c r="AA39" s="142"/>
-    </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G40" s="120" t="s">
-        <v>217</v>
-      </c>
-      <c r="H40" s="116"/>
-      <c r="I40" s="116"/>
-      <c r="J40" s="116"/>
-      <c r="K40" s="143">
-        <v>423.5</v>
-      </c>
-      <c r="L40" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="M40" s="124"/>
-      <c r="N40" s="120" t="s">
-        <v>217</v>
-      </c>
-      <c r="O40" s="116"/>
-      <c r="P40" s="116"/>
-      <c r="Q40" s="116"/>
-      <c r="R40" s="143">
-        <v>317.5</v>
-      </c>
-      <c r="S40" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="T40" s="124"/>
-      <c r="U40" s="120" t="s">
-        <v>217</v>
-      </c>
-      <c r="V40" s="116"/>
-      <c r="W40" s="116"/>
-      <c r="X40" s="116"/>
-      <c r="Y40" s="143">
-        <v>318</v>
-      </c>
-      <c r="Z40" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA40" s="142"/>
-    </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G41" s="120" t="s">
-        <v>187</v>
-      </c>
-      <c r="H41" s="116"/>
-      <c r="I41" s="116"/>
-      <c r="J41" s="116"/>
-      <c r="K41" s="143">
-        <v>428.9</v>
-      </c>
-      <c r="L41" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="M41" s="124"/>
-      <c r="N41" s="120" t="s">
-        <v>187</v>
-      </c>
-      <c r="O41" s="116"/>
-      <c r="P41" s="116"/>
-      <c r="Q41" s="116"/>
-      <c r="R41" s="143">
-        <v>321</v>
-      </c>
-      <c r="S41" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="T41" s="124"/>
-      <c r="U41" s="120" t="s">
-        <v>187</v>
-      </c>
-      <c r="V41" s="116"/>
-      <c r="W41" s="116"/>
-      <c r="X41" s="116"/>
-      <c r="Y41" s="143">
-        <v>322</v>
-      </c>
-      <c r="Z41" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA41" s="142"/>
-    </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G42" s="120" t="s">
-        <v>178</v>
-      </c>
-      <c r="H42" s="116"/>
-      <c r="I42" s="116"/>
-      <c r="J42" s="116"/>
-      <c r="K42" s="143">
-        <v>413</v>
-      </c>
-      <c r="L42" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="M42" s="124"/>
-      <c r="N42" s="120" t="s">
-        <v>178</v>
-      </c>
-      <c r="O42" s="116"/>
-      <c r="P42" s="116"/>
-      <c r="Q42" s="116"/>
-      <c r="R42" s="143">
-        <v>309.75</v>
-      </c>
-      <c r="S42" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="T42" s="124"/>
-      <c r="U42" s="120" t="s">
-        <v>178</v>
-      </c>
-      <c r="V42" s="116"/>
-      <c r="W42" s="116"/>
-      <c r="X42" s="116"/>
-      <c r="Y42" s="143">
-        <v>308.7</v>
-      </c>
-      <c r="Z42" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA42" s="16"/>
-    </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G43" s="139" t="s">
-        <v>168</v>
-      </c>
-      <c r="H43" s="140"/>
-      <c r="I43" s="140"/>
-      <c r="J43" s="140"/>
-      <c r="K43" s="145">
-        <v>36</v>
-      </c>
-      <c r="L43" s="133" t="s">
-        <v>16</v>
-      </c>
-      <c r="M43" s="124"/>
-      <c r="N43" s="139" t="s">
-        <v>168</v>
-      </c>
-      <c r="O43" s="140"/>
-      <c r="P43" s="140"/>
-      <c r="Q43" s="140"/>
-      <c r="R43" s="145">
-        <v>57</v>
-      </c>
-      <c r="S43" s="133" t="s">
-        <v>16</v>
-      </c>
-      <c r="T43" s="124"/>
-      <c r="U43" s="139" t="s">
-        <v>168</v>
-      </c>
-      <c r="V43" s="140"/>
-      <c r="W43" s="140"/>
-      <c r="X43" s="140"/>
-      <c r="Y43" s="145">
-        <v>72</v>
-      </c>
-      <c r="Z43" s="133" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA43" s="142"/>
-    </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="L44" s="142"/>
-      <c r="AA44" s="142"/>
-    </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A45" s="117" t="s">
-        <v>177</v>
-      </c>
-      <c r="B45" s="118"/>
-      <c r="C45" s="118"/>
-      <c r="D45" s="118"/>
-      <c r="E45" s="141">
-        <f>K18</f>
-        <v>6</v>
-      </c>
-      <c r="L45" s="142"/>
-      <c r="AA45" s="142"/>
-    </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A46" s="120" t="s">
-        <v>149</v>
-      </c>
-      <c r="B46" s="116"/>
-      <c r="C46" s="116"/>
-      <c r="D46" s="121">
-        <f>HLOOKUP($E$45,$18:$43,4)</f>
-        <v>240</v>
-      </c>
-      <c r="E46" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="L46" s="142"/>
-      <c r="R46" s="142"/>
-      <c r="S46" s="142"/>
-      <c r="AA46" s="142"/>
-    </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A47" s="130" t="s">
-        <v>158</v>
-      </c>
-      <c r="B47" s="131"/>
-      <c r="C47" s="131"/>
-      <c r="D47" s="132">
-        <f>HLOOKUP($E$45,$18:$43,5)</f>
-        <v>3.5</v>
-      </c>
-      <c r="E47" s="133" t="s">
-        <v>16</v>
-      </c>
-      <c r="L47" s="142"/>
-      <c r="AA47" s="142"/>
-    </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A48" s="127" t="s">
-        <v>229</v>
-      </c>
-      <c r="B48" s="126"/>
-      <c r="C48" s="126"/>
-      <c r="D48" s="126"/>
-      <c r="E48" s="128"/>
-      <c r="L48" s="142"/>
-      <c r="Z48" s="59"/>
-    </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A49" s="136" t="s">
-        <v>0</v>
-      </c>
-      <c r="B49" s="137"/>
-      <c r="C49" s="137"/>
-      <c r="D49" s="134">
-        <f>HLOOKUP($E$45,$18:$43,6)</f>
-        <v>1510</v>
-      </c>
-      <c r="E49" s="138" t="s">
-        <v>162</v>
-      </c>
-      <c r="Z49" s="59"/>
-    </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A50" s="120" t="s">
-        <v>160</v>
-      </c>
-      <c r="B50" s="116"/>
-      <c r="C50" s="116"/>
-      <c r="D50" s="121">
-        <f>HLOOKUP($E$45,$18:$43,7)</f>
-        <v>554</v>
-      </c>
-      <c r="E50" s="122" t="s">
-        <v>162</v>
-      </c>
-      <c r="Z50" s="59"/>
-    </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A51" s="139" t="s">
-        <v>161</v>
-      </c>
-      <c r="B51" s="140"/>
-      <c r="C51" s="140"/>
-      <c r="D51" s="132">
+      <c r="B51" s="132"/>
+      <c r="C51" s="132"/>
+      <c r="D51" s="80">
         <f>HLOOKUP($E$45,$18:$43,8)</f>
         <v>0</v>
       </c>
-      <c r="E51" s="133" t="s">
-        <v>162</v>
+      <c r="E51" s="81" t="s">
+        <v>161</v>
       </c>
       <c r="Z51" s="59"/>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A52" s="127" t="s">
-        <v>218</v>
-      </c>
-      <c r="B52" s="126"/>
-      <c r="C52" s="126"/>
-      <c r="D52" s="126"/>
-      <c r="E52" s="128"/>
+      <c r="A52" s="135" t="s">
+        <v>217</v>
+      </c>
+      <c r="B52" s="136"/>
+      <c r="C52" s="136"/>
+      <c r="D52" s="136"/>
+      <c r="E52" s="139"/>
       <c r="Z52" s="59"/>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A53" s="117" t="s">
+      <c r="A53" s="142" t="s">
+        <v>219</v>
+      </c>
+      <c r="B53" s="143"/>
+      <c r="C53" s="143"/>
+      <c r="D53" s="82">
+        <f>HLOOKUP($E$45,$18:$43,14)</f>
+        <v>42.5</v>
+      </c>
+      <c r="E53" s="83" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z53" s="59"/>
+    </row>
+    <row r="54" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A54" s="135" t="s">
+        <v>166</v>
+      </c>
+      <c r="B54" s="136"/>
+      <c r="C54" s="136"/>
+      <c r="D54" s="75">
+        <f>HLOOKUP($E$45,$18:$43,15)</f>
+        <v>49</v>
+      </c>
+      <c r="E54" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z54" s="59"/>
+    </row>
+    <row r="55" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A55" s="135" t="s">
+        <v>165</v>
+      </c>
+      <c r="B55" s="136"/>
+      <c r="C55" s="136"/>
+      <c r="D55" s="75">
+        <f>HLOOKUP($E$45,$18:$43,16)</f>
+        <v>37.75</v>
+      </c>
+      <c r="E55" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z55" s="59"/>
+    </row>
+    <row r="56" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A56" s="137" t="s">
+        <v>167</v>
+      </c>
+      <c r="B56" s="138"/>
+      <c r="C56" s="138"/>
+      <c r="D56" s="80">
+        <f>HLOOKUP($E$45,$18:$43,17)</f>
+        <v>62</v>
+      </c>
+      <c r="E56" s="81" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z56" s="59"/>
+    </row>
+    <row r="57" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A57" s="135" t="s">
         <v>220</v>
       </c>
-      <c r="B53" s="118"/>
-      <c r="C53" s="118"/>
-      <c r="D53" s="134">
-        <f>HLOOKUP($E$45,$18:$43,14)</f>
-        <v>56</v>
-      </c>
-      <c r="E53" s="135" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z53" s="59"/>
-    </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A54" s="127" t="s">
+      <c r="B57" s="136"/>
+      <c r="C57" s="136"/>
+      <c r="D57" s="136"/>
+      <c r="E57" s="139"/>
+      <c r="Z57" s="59"/>
+    </row>
+    <row r="58" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A58" s="142" t="s">
+        <v>219</v>
+      </c>
+      <c r="B58" s="143"/>
+      <c r="C58" s="143"/>
+      <c r="D58" s="82">
+        <f>HLOOKUP($E$45,$18:$43,23)</f>
+        <v>317.5</v>
+      </c>
+      <c r="E58" s="83" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A59" s="135" t="s">
+        <v>166</v>
+      </c>
+      <c r="B59" s="136"/>
+      <c r="C59" s="136"/>
+      <c r="D59" s="75">
+        <f>HLOOKUP($E$45,$18:$43,24)</f>
+        <v>321</v>
+      </c>
+      <c r="E59" s="76" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A60" s="135" t="s">
+        <v>305</v>
+      </c>
+      <c r="B60" s="136"/>
+      <c r="C60" s="136"/>
+      <c r="D60" s="75">
+        <f>HLOOKUP($E$45,$18:$43,25)</f>
+        <v>309.75</v>
+      </c>
+      <c r="E60" s="76" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A61" s="137" t="s">
         <v>167</v>
       </c>
-      <c r="B54" s="126"/>
-      <c r="C54" s="126"/>
-      <c r="D54" s="121">
-        <f>HLOOKUP($E$45,$18:$43,15)</f>
-        <v>65</v>
-      </c>
-      <c r="E54" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z54" s="59"/>
-    </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A55" s="127" t="s">
-        <v>166</v>
-      </c>
-      <c r="B55" s="126"/>
-      <c r="C55" s="126"/>
-      <c r="D55" s="121">
-        <f>HLOOKUP($E$45,$18:$43,16)</f>
-        <v>49.35</v>
-      </c>
-      <c r="E55" s="122" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z55" s="59"/>
-    </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A56" s="130" t="s">
-        <v>168</v>
-      </c>
-      <c r="B56" s="131"/>
-      <c r="C56" s="131"/>
-      <c r="D56" s="132">
-        <f>HLOOKUP($E$45,$18:$43,17)</f>
-        <v>40</v>
-      </c>
-      <c r="E56" s="133" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z56" s="59"/>
-    </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A57" s="127" t="s">
-        <v>221</v>
-      </c>
-      <c r="B57" s="126"/>
-      <c r="C57" s="126"/>
-      <c r="D57" s="126"/>
-      <c r="E57" s="128"/>
-      <c r="Z57" s="59"/>
-    </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A58" s="117" t="s">
-        <v>220</v>
-      </c>
-      <c r="B58" s="118"/>
-      <c r="C58" s="118"/>
-      <c r="D58" s="134">
-        <f>HLOOKUP($E$45,$18:$43,23)</f>
-        <v>423.5</v>
-      </c>
-      <c r="E58" s="135" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A59" s="127" t="s">
-        <v>167</v>
-      </c>
-      <c r="B59" s="126"/>
-      <c r="C59" s="126"/>
-      <c r="D59" s="121">
-        <f>HLOOKUP($E$45,$18:$43,24)</f>
-        <v>428.9</v>
-      </c>
-      <c r="E59" s="122" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A60" s="127" t="s">
-        <v>307</v>
-      </c>
-      <c r="B60" s="126"/>
-      <c r="C60" s="126"/>
-      <c r="D60" s="121">
-        <f>HLOOKUP($E$45,$18:$43,25)</f>
-        <v>413</v>
-      </c>
-      <c r="E60" s="122" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A61" s="130" t="s">
-        <v>168</v>
-      </c>
-      <c r="B61" s="131"/>
-      <c r="C61" s="131"/>
-      <c r="D61" s="132">
+      <c r="B61" s="138"/>
+      <c r="C61" s="138"/>
+      <c r="D61" s="80">
         <f>HLOOKUP($E$45,$18:$43,26)</f>
-        <v>36</v>
-      </c>
-      <c r="E61" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="E61" s="81" t="s">
         <v>16</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="113">
-    <mergeCell ref="U41:X41"/>
-    <mergeCell ref="U42:X42"/>
-    <mergeCell ref="U43:X43"/>
-    <mergeCell ref="U27:X27"/>
-    <mergeCell ref="U28:X28"/>
-    <mergeCell ref="U29:X29"/>
-    <mergeCell ref="U30:X30"/>
-    <mergeCell ref="U31:X31"/>
-    <mergeCell ref="U32:X32"/>
-    <mergeCell ref="U33:X33"/>
-    <mergeCell ref="U34:X34"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="G26:L26"/>
-    <mergeCell ref="G27:J27"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="N43:Q43"/>
     <mergeCell ref="G31:J31"/>
     <mergeCell ref="G32:J32"/>
     <mergeCell ref="G33:J33"/>
@@ -7504,25 +7489,52 @@
     <mergeCell ref="G40:J40"/>
     <mergeCell ref="G41:J41"/>
     <mergeCell ref="G42:J42"/>
-    <mergeCell ref="G43:J43"/>
-    <mergeCell ref="G36:J36"/>
-    <mergeCell ref="G37:J37"/>
-    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="N37:Q37"/>
+    <mergeCell ref="N38:Q38"/>
+    <mergeCell ref="N39:Q39"/>
+    <mergeCell ref="N40:Q40"/>
+    <mergeCell ref="N41:Q41"/>
+    <mergeCell ref="N42:Q42"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="G26:L26"/>
+    <mergeCell ref="G27:J27"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="N33:Q33"/>
+    <mergeCell ref="N34:Q34"/>
+    <mergeCell ref="U18:X18"/>
+    <mergeCell ref="U19:X19"/>
+    <mergeCell ref="U20:X20"/>
+    <mergeCell ref="U21:X21"/>
+    <mergeCell ref="U22:X22"/>
+    <mergeCell ref="N29:Q29"/>
+    <mergeCell ref="N30:Q30"/>
+    <mergeCell ref="N31:Q31"/>
+    <mergeCell ref="U26:Z26"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="U25:X25"/>
     <mergeCell ref="N26:S26"/>
     <mergeCell ref="N27:Q27"/>
     <mergeCell ref="N28:Q28"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="U23:X23"/>
+    <mergeCell ref="N24:Q24"/>
+    <mergeCell ref="N25:Q25"/>
+    <mergeCell ref="K2:Q2"/>
+    <mergeCell ref="N18:Q18"/>
+    <mergeCell ref="N19:Q19"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="N20:Q20"/>
+    <mergeCell ref="N21:Q21"/>
+    <mergeCell ref="N22:Q22"/>
+    <mergeCell ref="N23:Q23"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="G23:J23"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A13:F13"/>
@@ -7538,59 +7550,46 @@
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A7:D7"/>
-    <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="N18:Q18"/>
-    <mergeCell ref="N19:Q19"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="N20:Q20"/>
-    <mergeCell ref="N21:Q21"/>
-    <mergeCell ref="N22:Q22"/>
-    <mergeCell ref="N23:Q23"/>
-    <mergeCell ref="U23:X23"/>
-    <mergeCell ref="U18:X18"/>
-    <mergeCell ref="U19:X19"/>
-    <mergeCell ref="U20:X20"/>
-    <mergeCell ref="U21:X21"/>
-    <mergeCell ref="U22:X22"/>
-    <mergeCell ref="N29:Q29"/>
-    <mergeCell ref="N30:Q30"/>
-    <mergeCell ref="N31:Q31"/>
-    <mergeCell ref="N32:Q32"/>
-    <mergeCell ref="U26:Z26"/>
-    <mergeCell ref="U24:X24"/>
-    <mergeCell ref="U25:X25"/>
-    <mergeCell ref="N35:S35"/>
-    <mergeCell ref="N36:Q36"/>
-    <mergeCell ref="N37:Q37"/>
-    <mergeCell ref="N38:Q38"/>
-    <mergeCell ref="N39:Q39"/>
-    <mergeCell ref="N40:Q40"/>
-    <mergeCell ref="N41:Q41"/>
-    <mergeCell ref="N42:Q42"/>
-    <mergeCell ref="N43:Q43"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="G43:J43"/>
+    <mergeCell ref="G36:J36"/>
+    <mergeCell ref="G37:J37"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="U41:X41"/>
+    <mergeCell ref="U42:X42"/>
+    <mergeCell ref="U43:X43"/>
+    <mergeCell ref="U27:X27"/>
+    <mergeCell ref="U28:X28"/>
+    <mergeCell ref="U29:X29"/>
+    <mergeCell ref="U30:X30"/>
+    <mergeCell ref="U31:X31"/>
+    <mergeCell ref="U32:X32"/>
+    <mergeCell ref="U33:X33"/>
+    <mergeCell ref="U34:X34"/>
     <mergeCell ref="U35:Z35"/>
     <mergeCell ref="U36:X36"/>
     <mergeCell ref="U37:X37"/>
     <mergeCell ref="U38:X38"/>
     <mergeCell ref="U39:X39"/>
     <mergeCell ref="U40:X40"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="N33:Q33"/>
-    <mergeCell ref="N34:Q34"/>
-    <mergeCell ref="N24:Q24"/>
-    <mergeCell ref="N25:Q25"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="N32:Q32"/>
+    <mergeCell ref="N35:S35"/>
+    <mergeCell ref="N36:Q36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7605,33 +7604,33 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="108" t="s">
-        <v>176</v>
-      </c>
-      <c r="B2" s="108"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="H2" s="108" t="s">
-        <v>189</v>
-      </c>
-      <c r="I2" s="108"/>
-      <c r="J2" s="108"/>
-      <c r="K2" s="108"/>
-      <c r="L2" s="108"/>
-      <c r="P2" s="108" t="s">
+      <c r="A2" s="118" t="s">
+        <v>175</v>
+      </c>
+      <c r="B2" s="118"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="H2" s="118" t="s">
         <v>188</v>
       </c>
-      <c r="Q2" s="108"/>
-      <c r="R2" s="108"/>
-      <c r="S2" s="108"/>
-      <c r="T2" s="108"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="P2" s="118" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q2" s="118"/>
+      <c r="R2" s="118"/>
+      <c r="S2" s="118"/>
+      <c r="T2" s="118"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="108" t="s">
-        <v>175</v>
-      </c>
-      <c r="B3" s="108"/>
+      <c r="A3" s="118" t="s">
+        <v>174</v>
+      </c>
+      <c r="B3" s="118"/>
       <c r="D3" s="61">
         <f ca="1">Электродвигатель!$P$53</f>
         <v>45.959055069271365</v>
@@ -7639,11 +7638,11 @@
       <c r="E3" t="s">
         <v>100</v>
       </c>
-      <c r="H3" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
+      <c r="H3" s="94" t="s">
+        <v>174</v>
+      </c>
+      <c r="I3" s="94"/>
+      <c r="J3" s="94"/>
       <c r="K3" s="63">
         <f ca="1">D3</f>
         <v>45.959055069271365</v>
@@ -7652,7 +7651,7 @@
         <v>100</v>
       </c>
       <c r="P3" s="16" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R3" s="16"/>
       <c r="S3">
@@ -7664,10 +7663,10 @@
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="108" t="s">
+      <c r="A4" s="118" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="108"/>
+      <c r="B4" s="118"/>
       <c r="D4" s="62">
         <f>Электродвигатель!$N$52</f>
         <v>1440</v>
@@ -7675,11 +7674,11 @@
       <c r="E4" t="s">
         <v>105</v>
       </c>
-      <c r="H4" s="75" t="s">
+      <c r="H4" s="94" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
+      <c r="I4" s="94"/>
+      <c r="J4" s="94"/>
       <c r="K4" s="64">
         <f>D4</f>
         <v>1440</v>
@@ -7701,27 +7700,27 @@
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H5" s="108" t="s">
-        <v>179</v>
-      </c>
-      <c r="I5" s="108"/>
-      <c r="J5" s="108"/>
-      <c r="K5" s="108"/>
-      <c r="L5" s="108"/>
-      <c r="P5" s="108" t="s">
+      <c r="H5" s="118" t="s">
+        <v>178</v>
+      </c>
+      <c r="I5" s="118"/>
+      <c r="J5" s="118"/>
+      <c r="K5" s="118"/>
+      <c r="L5" s="118"/>
+      <c r="P5" s="118" t="s">
         <v>126</v>
       </c>
-      <c r="Q5" s="108"/>
-      <c r="R5" s="108"/>
-      <c r="S5" s="108"/>
-      <c r="T5" s="108"/>
+      <c r="Q5" s="118"/>
+      <c r="R5" s="118"/>
+      <c r="S5" s="118"/>
+      <c r="T5" s="118"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="108" t="s">
+      <c r="A6" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="B6" s="108"/>
-      <c r="C6" s="108"/>
+      <c r="B6" s="118"/>
+      <c r="C6" s="118"/>
       <c r="D6" s="66">
         <f>Электродвигатель!$F$61</f>
         <v>38</v>
@@ -7729,145 +7728,145 @@
       <c r="E6" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="108" t="s">
-        <v>178</v>
-      </c>
-      <c r="I6" s="108"/>
-      <c r="J6" s="108"/>
+      <c r="H6" s="118" t="s">
+        <v>177</v>
+      </c>
+      <c r="I6" s="118"/>
+      <c r="J6" s="118"/>
       <c r="K6">
         <f>Передача!D55</f>
-        <v>49.35</v>
+        <v>37.75</v>
       </c>
       <c r="L6" t="s">
         <v>16</v>
       </c>
-      <c r="P6" s="108" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q6" s="108"/>
-      <c r="R6" s="108"/>
+      <c r="P6" s="118" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q6" s="118"/>
+      <c r="R6" s="118"/>
       <c r="S6">
         <f>Передача!D60</f>
-        <v>413</v>
+        <v>309.75</v>
       </c>
       <c r="T6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="113" t="s">
-        <v>201</v>
-      </c>
-      <c r="B7" s="113"/>
-      <c r="C7" s="113"/>
+      <c r="A7" s="145" t="s">
+        <v>200</v>
+      </c>
+      <c r="B7" s="145"/>
+      <c r="C7" s="145"/>
       <c r="D7" s="52">
         <v>0.8</v>
       </c>
-      <c r="H7" s="108" t="s">
-        <v>187</v>
-      </c>
-      <c r="I7" s="108"/>
-      <c r="J7" s="108"/>
+      <c r="H7" s="118" t="s">
+        <v>186</v>
+      </c>
+      <c r="I7" s="118"/>
+      <c r="J7" s="118"/>
       <c r="K7">
         <f>Передача!D54</f>
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="L7" t="s">
         <v>16</v>
       </c>
-      <c r="P7" s="108" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q7" s="108"/>
-      <c r="R7" s="108"/>
+      <c r="P7" s="118" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q7" s="118"/>
+      <c r="R7" s="118"/>
       <c r="S7">
         <f>Передача!D59</f>
-        <v>428.9</v>
+        <v>321</v>
       </c>
       <c r="T7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="108" t="s">
-        <v>197</v>
-      </c>
-      <c r="B8" s="108"/>
-      <c r="C8" s="108"/>
+      <c r="A8" s="118" t="s">
+        <v>196</v>
+      </c>
+      <c r="B8" s="118"/>
+      <c r="C8" s="118"/>
       <c r="D8" s="71">
         <v>1.2</v>
       </c>
-      <c r="H8" s="108" t="s">
-        <v>168</v>
-      </c>
-      <c r="I8" s="108"/>
-      <c r="J8" s="108"/>
+      <c r="H8" s="118" t="s">
+        <v>167</v>
+      </c>
+      <c r="I8" s="118"/>
+      <c r="J8" s="118"/>
       <c r="K8">
         <f>Передача!D56</f>
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="L8" t="s">
         <v>16</v>
       </c>
-      <c r="P8" s="108" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q8" s="108"/>
-      <c r="R8" s="108"/>
+      <c r="P8" s="118" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q8" s="118"/>
+      <c r="R8" s="118"/>
       <c r="S8">
         <f>Передача!D61</f>
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="T8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H9" s="108" t="s">
-        <v>190</v>
-      </c>
-      <c r="I9" s="108"/>
-      <c r="J9" s="108"/>
-      <c r="K9" s="108"/>
-      <c r="L9" s="108"/>
-      <c r="P9" s="108" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q9" s="108"/>
-      <c r="R9" s="108"/>
-      <c r="S9" s="108"/>
-      <c r="T9" s="108"/>
+      <c r="H9" s="118" t="s">
+        <v>189</v>
+      </c>
+      <c r="I9" s="118"/>
+      <c r="J9" s="118"/>
+      <c r="K9" s="118"/>
+      <c r="L9" s="118"/>
+      <c r="P9" s="118" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q9" s="118"/>
+      <c r="R9" s="118"/>
+      <c r="S9" s="118"/>
+      <c r="T9" s="118"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H10" s="108" t="s">
-        <v>186</v>
-      </c>
-      <c r="I10" s="108"/>
-      <c r="J10" s="108"/>
+      <c r="H10" s="118" t="s">
+        <v>185</v>
+      </c>
+      <c r="I10" s="118"/>
+      <c r="J10" s="118"/>
       <c r="K10">
         <v>7.5</v>
       </c>
       <c r="L10" s="65" t="s">
-        <v>193</v>
-      </c>
-      <c r="P10" s="108" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q10" s="108"/>
-      <c r="R10" s="108"/>
+        <v>192</v>
+      </c>
+      <c r="P10" s="118" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q10" s="118"/>
+      <c r="R10" s="118"/>
       <c r="S10">
         <v>5.4</v>
       </c>
       <c r="T10" s="65" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H11" s="108" t="s">
-        <v>198</v>
-      </c>
-      <c r="I11" s="108"/>
-      <c r="J11" s="108"/>
+      <c r="H11" s="118" t="s">
+        <v>197</v>
+      </c>
+      <c r="I11" s="118"/>
+      <c r="J11" s="118"/>
       <c r="K11">
         <f ca="1">K10*(K3)^(1/3)</f>
         <v>26.864883424091097</v>
@@ -7875,11 +7874,11 @@
       <c r="L11" t="s">
         <v>16</v>
       </c>
-      <c r="P11" s="108" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q11" s="108"/>
-      <c r="R11" s="108"/>
+      <c r="P11" s="118" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q11" s="118"/>
+      <c r="R11" s="118"/>
       <c r="S11">
         <f ca="1">S10*(S3)^(1/3)</f>
         <v>37.309835064996221</v>
@@ -7889,11 +7888,11 @@
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H12" s="108" t="s">
-        <v>202</v>
-      </c>
-      <c r="I12" s="108"/>
-      <c r="J12" s="108"/>
+      <c r="H12" s="118" t="s">
+        <v>201</v>
+      </c>
+      <c r="I12" s="118"/>
+      <c r="J12" s="118"/>
       <c r="K12">
         <f ca="1">MIN(MAX(K11,D6/D8),D6/D7)</f>
         <v>31.666666666666668</v>
@@ -7901,11 +7900,11 @@
       <c r="L12" t="s">
         <v>16</v>
       </c>
-      <c r="P12" s="108" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q12" s="108"/>
-      <c r="R12" s="108"/>
+      <c r="P12" s="118" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q12" s="118"/>
+      <c r="R12" s="118"/>
       <c r="S12" s="66">
         <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;S11)</f>
         <v>38</v>
@@ -7914,15 +7913,15 @@
         <v>16</v>
       </c>
       <c r="U12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H13" s="108" t="s">
-        <v>191</v>
-      </c>
-      <c r="I13" s="108"/>
-      <c r="J13" s="108"/>
+      <c r="H13" s="118" t="s">
+        <v>190</v>
+      </c>
+      <c r="I13" s="118"/>
+      <c r="J13" s="118"/>
       <c r="K13" s="66">
         <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;K12)</f>
         <v>32</v>
@@ -7931,13 +7930,13 @@
         <v>16</v>
       </c>
       <c r="M13" t="s">
-        <v>200</v>
-      </c>
-      <c r="P13" s="108" t="s">
         <v>199</v>
       </c>
-      <c r="Q13" s="108"/>
-      <c r="R13" s="108"/>
+      <c r="P13" s="118" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q13" s="118"/>
+      <c r="R13" s="118"/>
       <c r="S13">
         <f ca="1">_xlfn.MINIFS($28:$28,$26:$26,"&gt;="&amp;S12)</f>
         <v>3.5</v>
@@ -7947,20 +7946,20 @@
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="108" t="s">
-        <v>294</v>
-      </c>
-      <c r="B14" s="108"/>
-      <c r="C14" s="108"/>
+      <c r="A14" s="118" t="s">
+        <v>292</v>
+      </c>
+      <c r="B14" s="118"/>
+      <c r="C14" s="118"/>
       <c r="D14">
         <f>Электродвигатель!$F$58</f>
         <v>2.2000000000000002</v>
       </c>
-      <c r="H14" s="108" t="s">
-        <v>199</v>
-      </c>
-      <c r="I14" s="108"/>
-      <c r="J14" s="108"/>
+      <c r="H14" s="118" t="s">
+        <v>198</v>
+      </c>
+      <c r="I14" s="118"/>
+      <c r="J14" s="118"/>
       <c r="K14">
         <f ca="1">_xlfn.MINIFS($28:$28,$26:$26,"&gt;="&amp;K13)</f>
         <v>3.5</v>
@@ -7968,11 +7967,11 @@
       <c r="L14" t="s">
         <v>16</v>
       </c>
-      <c r="P14" s="108" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q14" s="108"/>
-      <c r="R14" s="108"/>
+      <c r="P14" s="118" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q14" s="118"/>
+      <c r="R14" s="118"/>
       <c r="S14">
         <f ca="1">S12+2*S13</f>
         <v>45</v>
@@ -7982,11 +7981,11 @@
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H15" s="108" t="s">
-        <v>195</v>
-      </c>
-      <c r="I15" s="108"/>
-      <c r="J15" s="108"/>
+      <c r="H15" s="118" t="s">
+        <v>194</v>
+      </c>
+      <c r="I15" s="118"/>
+      <c r="J15" s="118"/>
       <c r="K15">
         <f ca="1">K13+2*K14</f>
         <v>39</v>
@@ -7994,11 +7993,11 @@
       <c r="L15" t="s">
         <v>16</v>
       </c>
-      <c r="P15" s="108" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q15" s="108"/>
-      <c r="R15" s="108"/>
+      <c r="P15" s="118" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q15" s="118"/>
+      <c r="R15" s="118"/>
       <c r="S15" s="66">
         <f ca="1">_xlfn.MINIFS(Подшипники!$A:$A,Подшипники!$A:$A,"&gt;="&amp;S14)</f>
         <v>45</v>
@@ -8008,11 +8007,11 @@
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H16" s="108" t="s">
-        <v>271</v>
-      </c>
-      <c r="I16" s="108"/>
-      <c r="J16" s="108"/>
+      <c r="H16" s="118" t="s">
+        <v>269</v>
+      </c>
+      <c r="I16" s="118"/>
+      <c r="J16" s="118"/>
       <c r="K16" s="66">
         <f ca="1">_xlfn.MINIFS(Подшипники!$A:$A,Подшипники!$A:$A,"&gt;="&amp;K15)</f>
         <v>40</v>
@@ -8020,11 +8019,11 @@
       <c r="L16" t="s">
         <v>16</v>
       </c>
-      <c r="P16" s="108" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q16" s="108"/>
-      <c r="R16" s="108"/>
+      <c r="P16" s="118" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q16" s="118"/>
+      <c r="R16" s="118"/>
       <c r="S16">
         <f ca="1">_xlfn.MINIFS($29:$29,$26:$26,"&gt;="&amp;S12)</f>
         <v>2.2999999999999998</v>
@@ -8034,11 +8033,11 @@
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H17" s="108" t="s">
-        <v>199</v>
-      </c>
-      <c r="I17" s="108"/>
-      <c r="J17" s="108"/>
+      <c r="H17" s="118" t="s">
+        <v>198</v>
+      </c>
+      <c r="I17" s="118"/>
+      <c r="J17" s="118"/>
       <c r="K17">
         <f ca="1">_xlfn.MINIFS($29:$29,$26:$26,"&gt;="&amp;K13)</f>
         <v>2</v>
@@ -8046,11 +8045,11 @@
       <c r="L17" t="s">
         <v>16</v>
       </c>
-      <c r="P17" s="108" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q17" s="108"/>
-      <c r="R17" s="108"/>
+      <c r="P17" s="118" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q17" s="118"/>
+      <c r="R17" s="118"/>
       <c r="S17">
         <f ca="1">S15+2*S16</f>
         <v>49.6</v>
@@ -8060,11 +8059,11 @@
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H18" s="108" t="s">
-        <v>196</v>
-      </c>
-      <c r="I18" s="108"/>
-      <c r="J18" s="108"/>
+      <c r="H18" s="118" t="s">
+        <v>195</v>
+      </c>
+      <c r="I18" s="118"/>
+      <c r="J18" s="118"/>
       <c r="K18">
         <f ca="1">K16+2*K17</f>
         <v>44</v>
@@ -8072,11 +8071,11 @@
       <c r="L18" t="s">
         <v>16</v>
       </c>
-      <c r="P18" s="108" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q18" s="108"/>
-      <c r="R18" s="108"/>
+      <c r="P18" s="118" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q18" s="118"/>
+      <c r="R18" s="118"/>
       <c r="S18" s="66">
         <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;S17)</f>
         <v>50</v>
@@ -8085,15 +8084,15 @@
         <v>16</v>
       </c>
       <c r="U18" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H19" s="108" t="s">
-        <v>192</v>
-      </c>
-      <c r="I19" s="108"/>
-      <c r="J19" s="108"/>
+      <c r="H19" s="118" t="s">
+        <v>191</v>
+      </c>
+      <c r="I19" s="118"/>
+      <c r="J19" s="118"/>
       <c r="K19" s="66">
         <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;K18)</f>
         <v>45</v>
@@ -8102,14 +8101,24 @@
         <v>16</v>
       </c>
       <c r="M19" t="s">
-        <v>200</v>
+        <v>199</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="S24" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="S25" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A26" s="108" t="s">
-        <v>184</v>
-      </c>
-      <c r="B26" s="108"/>
+      <c r="A26" s="118" t="s">
+        <v>183</v>
+      </c>
+      <c r="B26" s="118"/>
       <c r="C26">
         <v>17</v>
       </c>
@@ -8140,12 +8149,15 @@
       <c r="L26">
         <v>90</v>
       </c>
+      <c r="S26" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A27" s="108" t="s">
-        <v>185</v>
-      </c>
-      <c r="B27" s="108"/>
+      <c r="A27" s="118" t="s">
+        <v>184</v>
+      </c>
+      <c r="B27" s="118"/>
       <c r="C27">
         <v>22</v>
       </c>
@@ -8178,10 +8190,10 @@
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A28" s="108" t="s">
-        <v>182</v>
-      </c>
-      <c r="B28" s="108"/>
+      <c r="A28" s="118" t="s">
+        <v>181</v>
+      </c>
+      <c r="B28" s="118"/>
       <c r="C28">
         <v>3</v>
       </c>
@@ -8214,10 +8226,10 @@
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A29" s="108" t="s">
-        <v>183</v>
-      </c>
-      <c r="B29" s="108"/>
+      <c r="A29" s="118" t="s">
+        <v>182</v>
+      </c>
+      <c r="B29" s="118"/>
       <c r="C29">
         <v>1.5</v>
       </c>
@@ -8251,22 +8263,6 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="P12:R12"/>
-    <mergeCell ref="P13:R13"/>
-    <mergeCell ref="P14:R14"/>
-    <mergeCell ref="P15:R15"/>
-    <mergeCell ref="P5:T5"/>
-    <mergeCell ref="P9:T9"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="P10:R10"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="H19:J19"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="P2:T2"/>
@@ -8274,15 +8270,16 @@
     <mergeCell ref="H5:L5"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="P5:T5"/>
     <mergeCell ref="H6:J6"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="P16:R16"/>
     <mergeCell ref="P17:R17"/>
     <mergeCell ref="P18:R18"/>
-    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="P11:R11"/>
+    <mergeCell ref="P15:R15"/>
     <mergeCell ref="H12:J12"/>
     <mergeCell ref="H14:J14"/>
     <mergeCell ref="H17:J17"/>
@@ -8290,11 +8287,26 @@
     <mergeCell ref="H15:J15"/>
     <mergeCell ref="H11:J11"/>
     <mergeCell ref="H13:J13"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="P9:T9"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="P8:R8"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="P13:R13"/>
+    <mergeCell ref="P14:R14"/>
+    <mergeCell ref="P10:R10"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="A8:C8"/>
     <mergeCell ref="H10:J10"/>
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="H9:L9"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="P11:R11"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8311,17 +8323,17 @@
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -8339,58 +8351,58 @@
   </cols>
   <sheetData>
     <row r="5" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="D5" s="148" t="s">
-        <v>295</v>
-      </c>
-      <c r="E5" s="148"/>
-      <c r="F5" s="148" t="s">
+      <c r="D5" s="146" t="s">
+        <v>293</v>
+      </c>
+      <c r="E5" s="146"/>
+      <c r="F5" s="146" t="s">
+        <v>299</v>
+      </c>
+      <c r="G5" s="146"/>
+      <c r="H5" s="146" t="s">
+        <v>300</v>
+      </c>
+      <c r="I5" s="146"/>
+      <c r="J5" s="146" t="s">
+        <v>178</v>
+      </c>
+      <c r="K5" s="146"/>
+      <c r="L5" s="146" t="s">
         <v>301</v>
       </c>
-      <c r="G5" s="148"/>
-      <c r="H5" s="148" t="s">
+      <c r="M5" s="146"/>
+      <c r="N5" s="146" t="s">
         <v>302</v>
       </c>
-      <c r="I5" s="148"/>
-      <c r="J5" s="148" t="s">
-        <v>179</v>
-      </c>
-      <c r="K5" s="148"/>
-      <c r="L5" s="148" t="s">
+      <c r="O5" s="146"/>
+      <c r="P5" s="146" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q5" s="146"/>
+      <c r="R5" s="146" t="s">
         <v>303</v>
       </c>
-      <c r="M5" s="148"/>
-      <c r="N5" s="148" t="s">
-        <v>304</v>
-      </c>
-      <c r="O5" s="148"/>
-      <c r="P5" s="148" t="s">
-        <v>306</v>
-      </c>
-      <c r="Q5" s="148"/>
-      <c r="R5" s="148" t="s">
-        <v>305</v>
-      </c>
-      <c r="S5" s="148"/>
+      <c r="S5" s="146"/>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="B6" s="48"/>
       <c r="C6" s="48"/>
-      <c r="D6" s="148"/>
-      <c r="E6" s="148"/>
-      <c r="F6" s="148"/>
-      <c r="G6" s="148"/>
-      <c r="H6" s="148"/>
-      <c r="I6" s="148"/>
-      <c r="J6" s="148"/>
-      <c r="K6" s="148"/>
-      <c r="L6" s="148"/>
-      <c r="M6" s="148"/>
-      <c r="N6" s="148"/>
-      <c r="O6" s="148"/>
-      <c r="P6" s="148"/>
-      <c r="Q6" s="148"/>
-      <c r="R6" s="148"/>
-      <c r="S6" s="148"/>
+      <c r="D6" s="146"/>
+      <c r="E6" s="146"/>
+      <c r="F6" s="146"/>
+      <c r="G6" s="146"/>
+      <c r="H6" s="146"/>
+      <c r="I6" s="146"/>
+      <c r="J6" s="146"/>
+      <c r="K6" s="146"/>
+      <c r="L6" s="146"/>
+      <c r="M6" s="146"/>
+      <c r="N6" s="146"/>
+      <c r="O6" s="146"/>
+      <c r="P6" s="146"/>
+      <c r="Q6" s="146"/>
+      <c r="R6" s="146"/>
+      <c r="S6" s="146"/>
       <c r="T6" s="48"/>
       <c r="U6" s="48"/>
       <c r="V6" s="48"/>
@@ -8409,48 +8421,48 @@
       <c r="AI6" s="48"/>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A7" s="108" t="s">
-        <v>296</v>
-      </c>
-      <c r="B7" s="108"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108">
+      <c r="A7" s="118" t="s">
+        <v>294</v>
+      </c>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118">
         <f ca="1">Вал!$K$16</f>
         <v>40</v>
       </c>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="108"/>
-      <c r="H7" s="108">
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118">
         <f ca="1">Вал!$K$19</f>
         <v>45</v>
       </c>
-      <c r="I7" s="108"/>
-      <c r="J7" s="108">
+      <c r="I7" s="118"/>
+      <c r="J7" s="118">
         <f>Передача!D54</f>
-        <v>65</v>
-      </c>
-      <c r="K7" s="108"/>
-      <c r="L7" s="108">
+        <v>49</v>
+      </c>
+      <c r="K7" s="118"/>
+      <c r="L7" s="118">
         <f ca="1">H7</f>
         <v>45</v>
       </c>
-      <c r="M7" s="108"/>
-      <c r="N7" s="108">
+      <c r="M7" s="118"/>
+      <c r="N7" s="118">
         <f>F7</f>
         <v>0</v>
       </c>
-      <c r="O7" s="108"/>
-      <c r="P7" s="108">
+      <c r="O7" s="118"/>
+      <c r="P7" s="118">
         <f ca="1">D7</f>
         <v>40</v>
       </c>
-      <c r="Q7" s="108"/>
-      <c r="R7" s="108">
+      <c r="Q7" s="118"/>
+      <c r="R7" s="118">
         <f ca="1">Вал!K13</f>
         <v>32</v>
       </c>
-      <c r="S7" s="108"/>
+      <c r="S7" s="118"/>
       <c r="U7" s="48"/>
       <c r="V7" s="48"/>
       <c r="W7" s="48"/>
@@ -8462,30 +8474,30 @@
       <c r="AG7" s="48"/>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A8" s="108" t="s">
-        <v>272</v>
-      </c>
-      <c r="B8" s="108"/>
-      <c r="C8" s="108"/>
-      <c r="D8" s="108"/>
-      <c r="E8" s="108"/>
-      <c r="F8" s="108"/>
-      <c r="G8" s="108"/>
-      <c r="H8" s="108"/>
-      <c r="I8" s="108"/>
-      <c r="J8" s="108">
+      <c r="A8" s="118" t="s">
+        <v>270</v>
+      </c>
+      <c r="B8" s="118"/>
+      <c r="C8" s="118"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="118"/>
+      <c r="G8" s="118"/>
+      <c r="H8" s="118"/>
+      <c r="I8" s="118"/>
+      <c r="J8" s="118">
         <f>Передача!$D$56</f>
-        <v>40</v>
-      </c>
-      <c r="K8" s="108"/>
-      <c r="L8" s="108"/>
-      <c r="M8" s="108"/>
-      <c r="N8" s="108"/>
-      <c r="O8" s="108"/>
-      <c r="P8" s="108"/>
-      <c r="Q8" s="108"/>
-      <c r="R8" s="108"/>
-      <c r="S8" s="108"/>
+        <v>62</v>
+      </c>
+      <c r="K8" s="118"/>
+      <c r="L8" s="118"/>
+      <c r="M8" s="118"/>
+      <c r="N8" s="118"/>
+      <c r="O8" s="118"/>
+      <c r="P8" s="118"/>
+      <c r="Q8" s="118"/>
+      <c r="R8" s="118"/>
+      <c r="S8" s="118"/>
       <c r="U8" s="48"/>
       <c r="V8" s="48"/>
       <c r="W8" s="48"/>
@@ -8497,27 +8509,27 @@
       <c r="AG8" s="48"/>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A9" s="108" t="s">
-        <v>297</v>
-      </c>
-      <c r="B9" s="108"/>
-      <c r="C9" s="108"/>
-      <c r="D9" s="108"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="108"/>
-      <c r="H9" s="108"/>
-      <c r="I9" s="108"/>
-      <c r="J9" s="108"/>
-      <c r="K9" s="108"/>
-      <c r="L9" s="108"/>
-      <c r="M9" s="108"/>
-      <c r="N9" s="108"/>
-      <c r="O9" s="108"/>
-      <c r="P9" s="108"/>
-      <c r="Q9" s="108"/>
-      <c r="R9" s="108"/>
-      <c r="S9" s="108"/>
+      <c r="A9" s="118" t="s">
+        <v>295</v>
+      </c>
+      <c r="B9" s="118"/>
+      <c r="C9" s="118"/>
+      <c r="D9" s="118"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="118"/>
+      <c r="G9" s="118"/>
+      <c r="H9" s="118"/>
+      <c r="I9" s="118"/>
+      <c r="J9" s="118"/>
+      <c r="K9" s="118"/>
+      <c r="L9" s="118"/>
+      <c r="M9" s="118"/>
+      <c r="N9" s="118"/>
+      <c r="O9" s="118"/>
+      <c r="P9" s="118"/>
+      <c r="Q9" s="118"/>
+      <c r="R9" s="118"/>
+      <c r="S9" s="118"/>
       <c r="U9" s="48"/>
       <c r="V9" s="48"/>
       <c r="W9" s="48"/>
@@ -8529,27 +8541,27 @@
       <c r="AG9" s="48"/>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A10" s="108" t="s">
-        <v>213</v>
-      </c>
-      <c r="B10" s="108"/>
-      <c r="C10" s="108"/>
-      <c r="D10" s="108"/>
-      <c r="E10" s="108"/>
-      <c r="F10" s="108"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="108"/>
-      <c r="I10" s="108"/>
-      <c r="J10" s="108"/>
-      <c r="K10" s="108"/>
-      <c r="L10" s="108"/>
-      <c r="M10" s="108"/>
-      <c r="N10" s="108"/>
-      <c r="O10" s="108"/>
-      <c r="P10" s="108"/>
-      <c r="Q10" s="108"/>
-      <c r="R10" s="108"/>
-      <c r="S10" s="108"/>
+      <c r="A10" s="118" t="s">
+        <v>212</v>
+      </c>
+      <c r="B10" s="118"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="118"/>
+      <c r="F10" s="118"/>
+      <c r="G10" s="118"/>
+      <c r="H10" s="118"/>
+      <c r="I10" s="118"/>
+      <c r="J10" s="118"/>
+      <c r="K10" s="118"/>
+      <c r="L10" s="118"/>
+      <c r="M10" s="118"/>
+      <c r="N10" s="118"/>
+      <c r="O10" s="118"/>
+      <c r="P10" s="118"/>
+      <c r="Q10" s="118"/>
+      <c r="R10" s="118"/>
+      <c r="S10" s="118"/>
       <c r="U10" s="48"/>
       <c r="V10" s="48"/>
       <c r="W10" s="48"/>
@@ -8561,27 +8573,27 @@
       <c r="AG10" s="48"/>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A11" s="108" t="s">
-        <v>298</v>
-      </c>
-      <c r="B11" s="108"/>
-      <c r="C11" s="108"/>
-      <c r="D11" s="108"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="108"/>
-      <c r="K11" s="108"/>
-      <c r="L11" s="108"/>
-      <c r="M11" s="108"/>
-      <c r="N11" s="108"/>
-      <c r="O11" s="108"/>
-      <c r="P11" s="108"/>
-      <c r="Q11" s="108"/>
-      <c r="R11" s="108"/>
-      <c r="S11" s="108"/>
+      <c r="A11" s="118" t="s">
+        <v>296</v>
+      </c>
+      <c r="B11" s="118"/>
+      <c r="C11" s="118"/>
+      <c r="D11" s="118"/>
+      <c r="E11" s="118"/>
+      <c r="F11" s="118"/>
+      <c r="G11" s="118"/>
+      <c r="H11" s="118"/>
+      <c r="I11" s="118"/>
+      <c r="J11" s="118"/>
+      <c r="K11" s="118"/>
+      <c r="L11" s="118"/>
+      <c r="M11" s="118"/>
+      <c r="N11" s="118"/>
+      <c r="O11" s="118"/>
+      <c r="P11" s="118"/>
+      <c r="Q11" s="118"/>
+      <c r="R11" s="118"/>
+      <c r="S11" s="118"/>
       <c r="U11" s="48"/>
       <c r="V11" s="48"/>
       <c r="W11" s="48"/>
@@ -8590,64 +8602,121 @@
       <c r="AG11" s="48"/>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A12" s="108" t="s">
-        <v>299</v>
-      </c>
-      <c r="B12" s="108"/>
-      <c r="C12" s="108"/>
-      <c r="D12" s="108"/>
-      <c r="E12" s="108"/>
-      <c r="F12" s="108"/>
-      <c r="G12" s="108"/>
-      <c r="H12" s="108"/>
-      <c r="I12" s="108"/>
-      <c r="J12" s="108"/>
-      <c r="K12" s="108"/>
-      <c r="L12" s="108"/>
-      <c r="M12" s="108"/>
-      <c r="N12" s="108"/>
-      <c r="O12" s="108"/>
-      <c r="P12" s="108"/>
-      <c r="Q12" s="108"/>
-      <c r="R12" s="108"/>
-      <c r="S12" s="108"/>
+      <c r="A12" s="118" t="s">
+        <v>297</v>
+      </c>
+      <c r="B12" s="118"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="118"/>
+      <c r="F12" s="118"/>
+      <c r="G12" s="118"/>
+      <c r="H12" s="118"/>
+      <c r="I12" s="118"/>
+      <c r="J12" s="118"/>
+      <c r="K12" s="118"/>
+      <c r="L12" s="118"/>
+      <c r="M12" s="118"/>
+      <c r="N12" s="118"/>
+      <c r="O12" s="118"/>
+      <c r="P12" s="118"/>
+      <c r="Q12" s="118"/>
+      <c r="R12" s="118"/>
+      <c r="S12" s="118"/>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A13" s="108" t="s">
-        <v>300</v>
-      </c>
-      <c r="B13" s="108"/>
-      <c r="C13" s="108"/>
-      <c r="D13" s="108"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="108"/>
-      <c r="H13" s="108"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="108"/>
-      <c r="K13" s="108"/>
-      <c r="L13" s="108"/>
-      <c r="M13" s="108"/>
-      <c r="N13" s="108"/>
-      <c r="O13" s="108"/>
-      <c r="P13" s="108"/>
-      <c r="Q13" s="108"/>
-      <c r="R13" s="108"/>
-      <c r="S13" s="108"/>
+      <c r="A13" s="118" t="s">
+        <v>298</v>
+      </c>
+      <c r="B13" s="118"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="118"/>
+      <c r="F13" s="118"/>
+      <c r="G13" s="118"/>
+      <c r="H13" s="118"/>
+      <c r="I13" s="118"/>
+      <c r="J13" s="118"/>
+      <c r="K13" s="118"/>
+      <c r="L13" s="118"/>
+      <c r="M13" s="118"/>
+      <c r="N13" s="118"/>
+      <c r="O13" s="118"/>
+      <c r="P13" s="118"/>
+      <c r="Q13" s="118"/>
+      <c r="R13" s="118"/>
+      <c r="S13" s="118"/>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="H14" s="108" t="s">
-        <v>219</v>
-      </c>
-      <c r="I14" s="108"/>
-      <c r="J14" s="108">
+      <c r="H14" s="118" t="s">
+        <v>218</v>
+      </c>
+      <c r="I14" s="118"/>
+      <c r="J14" s="118">
         <f>Передача!D55</f>
-        <v>49.35</v>
-      </c>
-      <c r="K14" s="108"/>
+        <v>37.75</v>
+      </c>
+      <c r="K14" s="118"/>
     </row>
   </sheetData>
   <mergeCells count="73">
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D5:E6"/>
+    <mergeCell ref="F5:G6"/>
+    <mergeCell ref="H5:I6"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="R5:S6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="J5:K6"/>
+    <mergeCell ref="L5:M6"/>
+    <mergeCell ref="N5:O6"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="N13:O13"/>
     <mergeCell ref="J14:K14"/>
     <mergeCell ref="H14:I14"/>
     <mergeCell ref="R13:S13"/>
@@ -8664,63 +8733,6 @@
     <mergeCell ref="L12:M12"/>
     <mergeCell ref="N12:O12"/>
     <mergeCell ref="R12:S12"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="J5:K6"/>
-    <mergeCell ref="L5:M6"/>
-    <mergeCell ref="N5:O6"/>
-    <mergeCell ref="R5:S6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D5:E6"/>
-    <mergeCell ref="F5:G6"/>
-    <mergeCell ref="H5:I6"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -8736,22 +8748,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A1" s="108" t="s">
-        <v>141</v>
-      </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
+      <c r="A1" s="118" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A2" s="75" t="s">
-        <v>146</v>
-      </c>
-      <c r="B2" s="75"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
+      <c r="A2" s="94" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
       <c r="E2" s="1">
         <f>Передача!$E$9</f>
         <v>300</v>
@@ -8760,252 +8772,252 @@
         <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
       <c r="E3" s="16">
         <f>Передача!$E$10</f>
         <v>3</v>
       </c>
       <c r="F3" s="54" t="s">
-        <v>137</v>
-      </c>
-      <c r="J3" s="75" t="s">
-        <v>229</v>
-      </c>
-      <c r="K3" s="75"/>
-      <c r="L3" s="75"/>
-      <c r="M3" s="75"/>
-      <c r="N3" s="75"/>
-      <c r="T3" s="108" t="s">
-        <v>163</v>
-      </c>
-      <c r="U3" s="108"/>
-      <c r="V3" s="108"/>
-      <c r="W3" s="108"/>
-      <c r="X3" s="108" t="s">
-        <v>190</v>
-      </c>
-      <c r="Y3" s="108"/>
-      <c r="Z3" s="108" t="s">
-        <v>179</v>
-      </c>
-      <c r="AA3" s="108"/>
+        <v>136</v>
+      </c>
+      <c r="J3" s="94" t="s">
+        <v>228</v>
+      </c>
+      <c r="K3" s="94"/>
+      <c r="L3" s="94"/>
+      <c r="M3" s="94"/>
+      <c r="N3" s="94"/>
+      <c r="T3" s="118" t="s">
+        <v>162</v>
+      </c>
+      <c r="U3" s="118"/>
+      <c r="V3" s="118"/>
+      <c r="W3" s="118"/>
+      <c r="X3" s="118" t="s">
+        <v>189</v>
+      </c>
+      <c r="Y3" s="118"/>
+      <c r="Z3" s="118" t="s">
+        <v>178</v>
+      </c>
+      <c r="AA3" s="118"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A4" s="75" t="s">
-        <v>213</v>
-      </c>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
+      <c r="A4" s="94" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="94"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
       <c r="E4" s="47" t="str">
         <f>Передача!$E$11</f>
         <v>?</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="J4" s="116" t="s">
+      <c r="J4" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116"/>
-      <c r="M4" s="125">
+      <c r="K4" s="134"/>
+      <c r="L4" s="134"/>
+      <c r="M4" s="78">
         <f>Передача!$D$49</f>
-        <v>1510</v>
-      </c>
-      <c r="N4" s="121" t="s">
-        <v>162</v>
-      </c>
-      <c r="T4" s="108" t="s">
-        <v>259</v>
-      </c>
-      <c r="U4" s="108"/>
-      <c r="V4" s="108"/>
-      <c r="W4" s="108"/>
-      <c r="X4" s="108">
+        <v>2016</v>
+      </c>
+      <c r="N4" s="75" t="s">
+        <v>161</v>
+      </c>
+      <c r="T4" s="118" t="s">
+        <v>257</v>
+      </c>
+      <c r="U4" s="118"/>
+      <c r="V4" s="118"/>
+      <c r="W4" s="118"/>
+      <c r="X4" s="118">
         <v>0</v>
       </c>
-      <c r="Y4" s="108"/>
-      <c r="Z4" s="108">
+      <c r="Y4" s="118"/>
+      <c r="Z4" s="118">
         <f ca="1">E19</f>
         <v>50</v>
       </c>
-      <c r="AA4" s="108"/>
+      <c r="AA4" s="118"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A5" s="107" t="s">
-        <v>215</v>
-      </c>
-      <c r="B5" s="107"/>
-      <c r="C5" s="107"/>
-      <c r="D5" s="107"/>
+      <c r="A5" s="103" t="s">
+        <v>214</v>
+      </c>
+      <c r="B5" s="103"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
       <c r="E5" s="70" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="J5" s="116" t="s">
-        <v>160</v>
-      </c>
-      <c r="K5" s="116"/>
-      <c r="L5" s="116"/>
-      <c r="M5" s="125">
+      <c r="J5" s="134" t="s">
+        <v>159</v>
+      </c>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="78">
         <f>Передача!$D$50</f>
-        <v>554</v>
-      </c>
-      <c r="N5" s="121" t="s">
-        <v>162</v>
-      </c>
-      <c r="T5" s="108" t="s">
-        <v>261</v>
-      </c>
-      <c r="U5" s="108"/>
-      <c r="V5" s="108"/>
-      <c r="W5" s="108"/>
-      <c r="X5" s="108">
+        <v>734</v>
+      </c>
+      <c r="N5" s="75" t="s">
+        <v>161</v>
+      </c>
+      <c r="T5" s="118" t="s">
+        <v>259</v>
+      </c>
+      <c r="U5" s="118"/>
+      <c r="V5" s="118"/>
+      <c r="W5" s="118"/>
+      <c r="X5" s="118">
         <f ca="1">E19</f>
         <v>50</v>
       </c>
-      <c r="Y5" s="108"/>
-      <c r="Z5" s="108">
-        <f ca="1">E18</f>
-        <v>60</v>
-      </c>
-      <c r="AA5" s="108"/>
+      <c r="Y5" s="118"/>
+      <c r="Z5" s="118">
+        <f>E18</f>
+        <v>80</v>
+      </c>
+      <c r="AA5" s="118"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A6" s="108" t="s">
-        <v>158</v>
-      </c>
-      <c r="B6" s="108"/>
-      <c r="C6" s="108"/>
-      <c r="D6" s="108"/>
+      <c r="A6" s="118" t="s">
+        <v>157</v>
+      </c>
+      <c r="B6" s="118"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
       <c r="E6">
         <f>Передача!$D$47</f>
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="116" t="s">
-        <v>161</v>
-      </c>
-      <c r="K6" s="116"/>
-      <c r="L6" s="116"/>
-      <c r="M6" s="125">
+      <c r="J6" s="134" t="s">
+        <v>160</v>
+      </c>
+      <c r="K6" s="134"/>
+      <c r="L6" s="134"/>
+      <c r="M6" s="78">
         <f>Передача!$D$51</f>
         <v>0</v>
       </c>
-      <c r="N6" s="121" t="s">
-        <v>162</v>
-      </c>
-      <c r="T6" s="108" t="s">
-        <v>245</v>
-      </c>
-      <c r="U6" s="108"/>
-      <c r="V6" s="108"/>
-      <c r="W6" s="108"/>
-      <c r="X6" s="114">
+      <c r="N6" s="75" t="s">
+        <v>161</v>
+      </c>
+      <c r="T6" s="118" t="s">
+        <v>243</v>
+      </c>
+      <c r="U6" s="118"/>
+      <c r="V6" s="118"/>
+      <c r="W6" s="118"/>
+      <c r="X6" s="149">
         <v>0.3</v>
       </c>
-      <c r="Y6" s="114"/>
-      <c r="Z6" s="114">
+      <c r="Y6" s="149"/>
+      <c r="Z6" s="149">
         <v>0.3</v>
       </c>
-      <c r="AA6" s="114"/>
+      <c r="AA6" s="149"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A7" s="108" t="s">
-        <v>217</v>
-      </c>
-      <c r="B7" s="108"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
+      <c r="A7" s="118" t="s">
+        <v>216</v>
+      </c>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
       <c r="E7">
         <f>Передача!$D$58</f>
-        <v>423.5</v>
+        <v>317.5</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="T7" s="108" t="s">
-        <v>256</v>
-      </c>
-      <c r="U7" s="108"/>
-      <c r="V7" s="108"/>
-      <c r="W7" s="108"/>
-      <c r="X7" s="114">
+      <c r="T7" s="118" t="s">
+        <v>254</v>
+      </c>
+      <c r="U7" s="118"/>
+      <c r="V7" s="118"/>
+      <c r="W7" s="118"/>
+      <c r="X7" s="149">
         <f>2.1*10^5</f>
         <v>210000</v>
       </c>
-      <c r="Y7" s="114"/>
-      <c r="Z7" s="114">
+      <c r="Y7" s="149"/>
+      <c r="Z7" s="149">
         <f>2.1*10^5</f>
         <v>210000</v>
       </c>
-      <c r="AA7" s="114"/>
+      <c r="AA7" s="149"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A8" s="75" t="s">
-        <v>187</v>
-      </c>
-      <c r="B8" s="75"/>
-      <c r="C8" s="75"/>
-      <c r="D8" s="75"/>
+      <c r="A8" s="94" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" s="94"/>
+      <c r="C8" s="94"/>
+      <c r="D8" s="94"/>
       <c r="E8" s="1">
+        <f>Передача!$D$59</f>
+        <v>321</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="148" t="s">
+        <v>260</v>
+      </c>
+      <c r="K8" s="148"/>
+      <c r="L8" s="148"/>
+      <c r="M8" s="148"/>
+      <c r="N8" s="148"/>
+      <c r="T8" s="118" t="s">
+        <v>253</v>
+      </c>
+      <c r="U8" s="118"/>
+      <c r="V8" s="118"/>
+      <c r="W8" s="118"/>
+      <c r="X8" s="149">
+        <v>330</v>
+      </c>
+      <c r="Y8" s="149"/>
+      <c r="Z8" s="149">
+        <v>330</v>
+      </c>
+      <c r="AA8" s="149"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A9" s="94" t="s">
+        <v>177</v>
+      </c>
+      <c r="B9" s="94"/>
+      <c r="C9" s="94"/>
+      <c r="D9" s="94"/>
+      <c r="E9" s="1">
         <f>Передача!$D$60</f>
-        <v>413</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="123" t="s">
-        <v>262</v>
-      </c>
-      <c r="K8" s="123"/>
-      <c r="L8" s="123"/>
-      <c r="M8" s="123"/>
-      <c r="N8" s="123"/>
-      <c r="T8" s="108" t="s">
-        <v>255</v>
-      </c>
-      <c r="U8" s="108"/>
-      <c r="V8" s="108"/>
-      <c r="W8" s="108"/>
-      <c r="X8" s="114">
-        <v>330</v>
-      </c>
-      <c r="Y8" s="114"/>
-      <c r="Z8" s="114">
-        <v>330</v>
-      </c>
-      <c r="AA8" s="114"/>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A9" s="75" t="s">
-        <v>178</v>
-      </c>
-      <c r="B9" s="75"/>
-      <c r="C9" s="75"/>
-      <c r="D9" s="75"/>
-      <c r="E9" s="1">
-        <f>Передача!$D$59</f>
-        <v>428.9</v>
+        <v>309.75</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="108" t="s">
-        <v>175</v>
-      </c>
-      <c r="K9" s="108"/>
-      <c r="L9" s="108"/>
+      <c r="J9" s="118" t="s">
+        <v>174</v>
+      </c>
+      <c r="K9" s="118"/>
+      <c r="L9" s="118"/>
       <c r="M9">
         <f>Передача!$E$5</f>
         <v>320</v>
@@ -9013,72 +9025,72 @@
       <c r="N9" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="T9" s="108" t="s">
-        <v>257</v>
-      </c>
-      <c r="U9" s="108"/>
-      <c r="V9" s="108"/>
-      <c r="W9" s="108"/>
-      <c r="X9" s="108">
+      <c r="T9" s="118" t="s">
+        <v>255</v>
+      </c>
+      <c r="U9" s="118"/>
+      <c r="V9" s="118"/>
+      <c r="W9" s="118"/>
+      <c r="X9" s="118">
         <f ca="1">(X5*X5+X4*X4)/(X5*X5-X4*X4)-X6</f>
         <v>0.7</v>
       </c>
-      <c r="Y9" s="108"/>
-      <c r="Z9" s="108">
+      <c r="Y9" s="118"/>
+      <c r="Z9" s="118">
         <f ca="1">(Z5*Z5+Z4*Z4)/(Z5*Z5-Z4*Z4)+Z6</f>
-        <v>5.8454545454545457</v>
-      </c>
-      <c r="AA9" s="108"/>
+        <v>2.5820512820512818</v>
+      </c>
+      <c r="AA9" s="118"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A10" s="108" t="s">
-        <v>168</v>
-      </c>
-      <c r="B10" s="108"/>
-      <c r="C10" s="108"/>
-      <c r="D10" s="108"/>
+      <c r="A10" s="118" t="s">
+        <v>167</v>
+      </c>
+      <c r="B10" s="118"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="118"/>
       <c r="E10">
         <f>Передача!$D$61</f>
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
       </c>
-      <c r="J10" s="108" t="s">
-        <v>236</v>
-      </c>
-      <c r="K10" s="108"/>
-      <c r="L10" s="108"/>
+      <c r="J10" s="118" t="s">
+        <v>234</v>
+      </c>
+      <c r="K10" s="118"/>
+      <c r="L10" s="118"/>
       <c r="M10" s="52">
         <v>3</v>
       </c>
       <c r="N10" s="25" t="s">
-        <v>239</v>
-      </c>
-      <c r="T10" s="108" t="s">
-        <v>258</v>
-      </c>
-      <c r="U10" s="108"/>
-      <c r="V10" s="108"/>
-      <c r="W10" s="108"/>
-      <c r="X10" s="108">
+        <v>237</v>
+      </c>
+      <c r="T10" s="118" t="s">
+        <v>256</v>
+      </c>
+      <c r="U10" s="118"/>
+      <c r="V10" s="118"/>
+      <c r="W10" s="118"/>
+      <c r="X10" s="118">
         <f ca="1">0.5*X8*(1-(X4*X4/X5/X5))</f>
         <v>165</v>
       </c>
-      <c r="Y10" s="108"/>
-      <c r="Z10" s="108">
+      <c r="Y10" s="118"/>
+      <c r="Z10" s="118">
         <f ca="1">0.5*Z8*(1-(Z4*Z4/Z5/Z5))</f>
-        <v>50.416666666666671</v>
-      </c>
-      <c r="AA10" s="108"/>
+        <v>100.546875</v>
+      </c>
+      <c r="AA10" s="118"/>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A11" s="108" t="s">
-        <v>222</v>
-      </c>
-      <c r="B11" s="108"/>
-      <c r="C11" s="108"/>
-      <c r="D11" s="108"/>
+      <c r="A11" s="118" t="s">
+        <v>221</v>
+      </c>
+      <c r="B11" s="118"/>
+      <c r="C11" s="118"/>
+      <c r="D11" s="118"/>
       <c r="E11">
         <f>_xlfn.MINIFS($32:$32,$31:$31,"&gt;="&amp;E7)</f>
         <v>5</v>
@@ -9086,263 +9098,266 @@
       <c r="F11" t="s">
         <v>16</v>
       </c>
-      <c r="J11" s="108" t="s">
-        <v>238</v>
-      </c>
-      <c r="K11" s="108"/>
-      <c r="L11" s="108"/>
+      <c r="J11" s="118" t="s">
+        <v>236</v>
+      </c>
+      <c r="K11" s="118"/>
+      <c r="L11" s="118"/>
       <c r="M11" s="52">
         <f>E35</f>
         <v>0.08</v>
       </c>
       <c r="O11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A12" s="108" t="s">
+      <c r="A12" s="118" t="s">
+        <v>222</v>
+      </c>
+      <c r="B12" s="118"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="118"/>
+      <c r="E12" t="s">
         <v>223</v>
       </c>
-      <c r="B12" s="108"/>
-      <c r="C12" s="108"/>
-      <c r="D12" s="108"/>
-      <c r="E12" t="s">
-        <v>224</v>
-      </c>
       <c r="F12" t="s">
         <v>16</v>
       </c>
-      <c r="J12" s="108" t="s">
-        <v>240</v>
-      </c>
-      <c r="K12" s="108"/>
-      <c r="L12" s="108"/>
+      <c r="J12" s="118" t="s">
+        <v>238</v>
+      </c>
+      <c r="K12" s="118"/>
+      <c r="L12" s="118"/>
       <c r="M12" s="25">
         <f>E17</f>
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="N12" t="s">
         <v>16</v>
       </c>
       <c r="O12" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A13" s="115" t="s">
+      <c r="A13" s="147" t="s">
+        <v>224</v>
+      </c>
+      <c r="B13" s="118"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="118"/>
+      <c r="E13" t="s">
+        <v>226</v>
+      </c>
+      <c r="F13" t="s">
         <v>225</v>
       </c>
-      <c r="B13" s="108"/>
-      <c r="C13" s="108"/>
-      <c r="D13" s="108"/>
-      <c r="E13" t="s">
-        <v>227</v>
-      </c>
-      <c r="F13" t="s">
-        <v>226</v>
-      </c>
-      <c r="J13" s="108" t="s">
-        <v>237</v>
-      </c>
-      <c r="K13" s="108"/>
-      <c r="L13" s="108"/>
+      <c r="J13" s="118" t="s">
+        <v>235</v>
+      </c>
+      <c r="K13" s="118"/>
+      <c r="L13" s="118"/>
       <c r="M13">
         <f ca="1">2000*M10*M9/(PI()*E19*E19*M12*M11)</f>
-        <v>84.882636315677502</v>
+        <v>53.610086094112106</v>
       </c>
       <c r="N13" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A14" s="108" t="s">
-        <v>230</v>
-      </c>
-      <c r="B14" s="108"/>
-      <c r="C14" s="108"/>
-      <c r="D14" s="108"/>
+      <c r="A14" s="118" t="s">
+        <v>229</v>
+      </c>
+      <c r="B14" s="118"/>
+      <c r="C14" s="118"/>
+      <c r="D14" s="118"/>
       <c r="E14">
         <f>2.2*E6+0.05*E10</f>
-        <v>9.5000000000000018</v>
+        <v>8.35</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="108" t="s">
-        <v>244</v>
-      </c>
-      <c r="K14" s="108"/>
-      <c r="L14" s="108"/>
+      <c r="J14" s="118" t="s">
+        <v>242</v>
+      </c>
+      <c r="K14" s="118"/>
+      <c r="L14" s="118"/>
       <c r="M14">
         <f ca="1">1000*M13*E19*(X9/X7+Z9/Z7)</f>
-        <v>132.28462802443246</v>
+        <v>41.893107570490528</v>
       </c>
       <c r="N14" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A15" s="108" t="s">
-        <v>228</v>
-      </c>
-      <c r="B15" s="108"/>
-      <c r="C15" s="108"/>
-      <c r="D15" s="108"/>
+      <c r="A15" s="118" t="s">
+        <v>227</v>
+      </c>
+      <c r="B15" s="118"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="118"/>
+      <c r="E15">
+        <f ca="1">(E18-E19)/2</f>
+        <v>15</v>
+      </c>
       <c r="F15" t="s">
         <v>16</v>
       </c>
-      <c r="J15" s="108" t="s">
-        <v>251</v>
-      </c>
-      <c r="K15" s="108"/>
-      <c r="L15" s="108"/>
+      <c r="J15" s="118" t="s">
+        <v>249</v>
+      </c>
+      <c r="K15" s="118"/>
+      <c r="L15" s="118"/>
       <c r="M15">
         <f>5.5*(E20+E22)</f>
         <v>0</v>
       </c>
       <c r="N15" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="O15" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A16" s="108" t="s">
-        <v>249</v>
-      </c>
-      <c r="B16" s="108"/>
-      <c r="C16" s="108"/>
-      <c r="D16" s="108"/>
+      <c r="A16" s="118" t="s">
+        <v>247</v>
+      </c>
+      <c r="B16" s="118"/>
+      <c r="C16" s="118"/>
+      <c r="D16" s="118"/>
       <c r="E16" s="52">
         <v>1</v>
       </c>
-      <c r="J16" s="108" t="s">
-        <v>252</v>
-      </c>
-      <c r="K16" s="108"/>
-      <c r="L16" s="108"/>
+      <c r="J16" s="118" t="s">
+        <v>250</v>
+      </c>
+      <c r="K16" s="118"/>
+      <c r="L16" s="118"/>
       <c r="N16" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="O16" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="108" t="s">
-        <v>247</v>
-      </c>
-      <c r="B17" s="108"/>
-      <c r="C17" s="108"/>
-      <c r="D17" s="108"/>
+      <c r="A17" s="118" t="s">
+        <v>245</v>
+      </c>
+      <c r="B17" s="118"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="118"/>
       <c r="E17">
         <f>E10*E16</f>
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F17" t="s">
         <v>16</v>
       </c>
-      <c r="J17" s="108" t="s">
-        <v>253</v>
-      </c>
-      <c r="K17" s="108"/>
-      <c r="L17" s="108"/>
+      <c r="J17" s="118" t="s">
+        <v>251</v>
+      </c>
+      <c r="K17" s="118"/>
+      <c r="L17" s="118"/>
       <c r="M17" s="25">
         <f ca="1">SUM(M14:M16)</f>
-        <v>132.28462802443246</v>
+        <v>41.893107570490528</v>
       </c>
       <c r="N17" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="108" t="s">
-        <v>248</v>
-      </c>
-      <c r="B18" s="108"/>
-      <c r="C18" s="108"/>
-      <c r="D18" s="108"/>
+      <c r="A18" s="118" t="s">
+        <v>246</v>
+      </c>
+      <c r="B18" s="118"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="118"/>
       <c r="E18" s="52">
-        <f ca="1">E19+10</f>
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
       </c>
-      <c r="J18" s="108" t="s">
-        <v>260</v>
-      </c>
-      <c r="K18" s="108"/>
-      <c r="L18" s="108"/>
+      <c r="J18" s="118" t="s">
+        <v>258</v>
+      </c>
+      <c r="K18" s="118"/>
+      <c r="L18" s="118"/>
       <c r="M18">
         <f ca="1">MAX(X10:AA10)*M14/M13</f>
-        <v>257.14285714285711</v>
+        <v>128.93772893772891</v>
       </c>
       <c r="N18" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="123" t="s">
-        <v>246</v>
-      </c>
-      <c r="B19" s="123"/>
-      <c r="C19" s="123"/>
-      <c r="D19" s="123"/>
-      <c r="E19" s="124">
+      <c r="A19" s="148" t="s">
+        <v>244</v>
+      </c>
+      <c r="B19" s="148"/>
+      <c r="C19" s="148"/>
+      <c r="D19" s="148"/>
+      <c r="E19" s="77">
         <f ca="1">Вал!$S$18</f>
         <v>50</v>
       </c>
-      <c r="F19" s="124" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="108" t="s">
-        <v>254</v>
-      </c>
-      <c r="K19" s="108"/>
-      <c r="L19" s="108"/>
-      <c r="M19" s="146">
+      <c r="F19" s="77" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="118" t="s">
+        <v>252</v>
+      </c>
+      <c r="K19" s="118"/>
+      <c r="L19" s="118"/>
+      <c r="M19" s="90">
         <f ca="1">M18+M15</f>
-        <v>257.14285714285711</v>
+        <v>128.93772893772891</v>
       </c>
       <c r="N19" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="108" t="s">
+      <c r="A20" s="118" t="s">
+        <v>313</v>
+      </c>
+      <c r="B20" s="118"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="77" t="s">
+        <v>248</v>
+      </c>
+      <c r="M20" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" s="118" t="s">
+        <v>314</v>
+      </c>
+      <c r="B21" s="118"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="118"/>
+      <c r="E21" s="92" t="s">
         <v>315</v>
       </c>
-      <c r="B20" s="108"/>
-      <c r="C20" s="108"/>
-      <c r="D20" s="108"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="124" t="s">
-        <v>250</v>
-      </c>
-      <c r="M20" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="108" t="s">
-        <v>316</v>
-      </c>
-      <c r="B21" s="108"/>
-      <c r="C21" s="108"/>
-      <c r="D21" s="108"/>
-      <c r="E21" s="149" t="s">
-        <v>317</v>
-      </c>
       <c r="F21" t="s">
         <v>16</v>
       </c>
-      <c r="J21" s="108" t="s">
-        <v>274</v>
-      </c>
-      <c r="K21" s="108"/>
-      <c r="L21" s="108"/>
+      <c r="J21" s="118" t="s">
+        <v>272</v>
+      </c>
+      <c r="K21" s="118"/>
+      <c r="L21" s="118"/>
       <c r="M21">
         <v>90</v>
       </c>
@@ -9350,48 +9365,61 @@
         <v>154</v>
       </c>
       <c r="O21" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="108" t="s">
-        <v>318</v>
-      </c>
-      <c r="B22" s="108"/>
-      <c r="C22" s="108"/>
-      <c r="D22" s="108"/>
+      <c r="A22" s="118" t="s">
+        <v>316</v>
+      </c>
+      <c r="B22" s="118"/>
+      <c r="C22" s="118"/>
+      <c r="D22" s="118"/>
       <c r="E22" s="52"/>
       <c r="F22" t="s">
-        <v>250</v>
-      </c>
-      <c r="J22" s="108" t="s">
-        <v>265</v>
-      </c>
-      <c r="K22" s="108"/>
-      <c r="L22" s="108"/>
+        <v>248</v>
+      </c>
+      <c r="J22" s="118" t="s">
+        <v>263</v>
+      </c>
+      <c r="K22" s="118"/>
+      <c r="L22" s="118"/>
       <c r="M22">
         <v>0.2</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="J23" s="108" t="s">
-        <v>264</v>
-      </c>
-      <c r="K23" s="108"/>
-      <c r="L23" s="108"/>
+      <c r="A23" s="118" t="s">
+        <v>317</v>
+      </c>
+      <c r="B23" s="118"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="118"/>
+      <c r="E23">
+        <f ca="1">MAX(E10/4,(E15+E14)/2)</f>
+        <v>14.25</v>
+      </c>
+      <c r="F23" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="118" t="s">
+        <v>262</v>
+      </c>
+      <c r="K23" s="118"/>
+      <c r="L23" s="118"/>
       <c r="M23">
         <f ca="1">PI()*E19*M12*(M21-M15)*M22/1000</f>
-        <v>101.7876019763093</v>
+        <v>161.1637031291564</v>
       </c>
       <c r="N23" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="108" t="s">
-        <v>184</v>
-      </c>
-      <c r="B30" s="108"/>
+      <c r="A30" s="118" t="s">
+        <v>183</v>
+      </c>
+      <c r="B30" s="118"/>
       <c r="C30">
         <v>20</v>
       </c>
@@ -9418,10 +9446,10 @@
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="108" t="s">
-        <v>185</v>
-      </c>
-      <c r="B31" s="108"/>
+      <c r="A31" s="118" t="s">
+        <v>184</v>
+      </c>
+      <c r="B31" s="118"/>
       <c r="C31">
         <v>30</v>
       </c>
@@ -9448,10 +9476,10 @@
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="108" t="s">
-        <v>216</v>
-      </c>
-      <c r="B32" s="108"/>
+      <c r="A32" s="118" t="s">
+        <v>215</v>
+      </c>
+      <c r="B32" s="118"/>
       <c r="C32">
         <v>1</v>
       </c>
@@ -9478,169 +9506,97 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="108" t="s">
+      <c r="A34" s="118" t="s">
+        <v>306</v>
+      </c>
+      <c r="B34" s="118"/>
+      <c r="C34" s="118" t="s">
+        <v>307</v>
+      </c>
+      <c r="D34" s="118"/>
+      <c r="E34" s="118" t="s">
+        <v>311</v>
+      </c>
+      <c r="F34" s="118"/>
+      <c r="G34" s="118" t="s">
+        <v>312</v>
+      </c>
+      <c r="H34" s="118"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="118" t="s">
         <v>308</v>
       </c>
-      <c r="B34" s="108"/>
-      <c r="C34" s="108" t="s">
+      <c r="B35" s="118"/>
+      <c r="C35" s="118" t="s">
         <v>309</v>
       </c>
-      <c r="D34" s="108"/>
-      <c r="E34" s="108" t="s">
-        <v>313</v>
-      </c>
-      <c r="F34" s="108"/>
-      <c r="G34" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="H34" s="108"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="108" t="s">
+      <c r="D35" s="118"/>
+      <c r="E35" s="118">
+        <v>0.08</v>
+      </c>
+      <c r="F35" s="118"/>
+      <c r="G35" s="118">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H35" s="118"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="118" t="s">
+        <v>308</v>
+      </c>
+      <c r="B36" s="118"/>
+      <c r="C36" s="118" t="s">
+        <v>308</v>
+      </c>
+      <c r="D36" s="118"/>
+      <c r="E36" s="118">
+        <v>0.08</v>
+      </c>
+      <c r="F36" s="118"/>
+      <c r="G36" s="118">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H36" s="118"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="118" t="s">
+        <v>308</v>
+      </c>
+      <c r="B37" s="118"/>
+      <c r="C37" s="118" t="s">
         <v>310</v>
       </c>
-      <c r="B35" s="108"/>
-      <c r="C35" s="108" t="s">
-        <v>311</v>
-      </c>
-      <c r="D35" s="108"/>
-      <c r="E35" s="108">
-        <v>0.08</v>
-      </c>
-      <c r="F35" s="108"/>
-      <c r="G35" s="108">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="H35" s="108"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="108" t="s">
+      <c r="D37" s="118"/>
+      <c r="E37" s="118">
+        <v>0.05</v>
+      </c>
+      <c r="F37" s="118"/>
+      <c r="G37" s="118">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H37" s="118"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="118" t="s">
+        <v>309</v>
+      </c>
+      <c r="B38" s="118"/>
+      <c r="C38" s="118" t="s">
         <v>310</v>
       </c>
-      <c r="B36" s="108"/>
-      <c r="C36" s="108" t="s">
-        <v>310</v>
-      </c>
-      <c r="D36" s="108"/>
-      <c r="E36" s="108">
-        <v>0.08</v>
-      </c>
-      <c r="F36" s="108"/>
-      <c r="G36" s="108">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="H36" s="108"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="108" t="s">
-        <v>310</v>
-      </c>
-      <c r="B37" s="108"/>
-      <c r="C37" s="108" t="s">
-        <v>312</v>
-      </c>
-      <c r="D37" s="108"/>
-      <c r="E37" s="108">
+      <c r="D38" s="118"/>
+      <c r="E38" s="118">
         <v>0.05</v>
       </c>
-      <c r="F37" s="108"/>
-      <c r="G37" s="108">
+      <c r="F38" s="118"/>
+      <c r="G38" s="118">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="H37" s="108"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="108" t="s">
-        <v>311</v>
-      </c>
-      <c r="B38" s="108"/>
-      <c r="C38" s="108" t="s">
-        <v>312</v>
-      </c>
-      <c r="D38" s="108"/>
-      <c r="E38" s="108">
-        <v>0.05</v>
-      </c>
-      <c r="F38" s="108"/>
-      <c r="G38" s="108">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="H38" s="108"/>
+      <c r="H38" s="118"/>
     </row>
   </sheetData>
-  <mergeCells count="88">
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="T7:W7"/>
-    <mergeCell ref="T8:W8"/>
-    <mergeCell ref="T9:W9"/>
-    <mergeCell ref="T10:W10"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="X10:Y10"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="T3:W3"/>
-    <mergeCell ref="T4:W4"/>
-    <mergeCell ref="T5:W5"/>
-    <mergeCell ref="T6:W6"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="X5:Y5"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="Z5:AA5"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="Z8:AA8"/>
+  <mergeCells count="89">
     <mergeCell ref="Z10:AA10"/>
     <mergeCell ref="J8:N8"/>
     <mergeCell ref="J23:L23"/>
@@ -9657,6 +9613,79 @@
     <mergeCell ref="J13:L13"/>
     <mergeCell ref="J11:L11"/>
     <mergeCell ref="J12:L12"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="Z8:AA8"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="T3:W3"/>
+    <mergeCell ref="T4:W4"/>
+    <mergeCell ref="T5:W5"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="T6:W6"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="T7:W7"/>
+    <mergeCell ref="T8:W8"/>
+    <mergeCell ref="T9:W9"/>
+    <mergeCell ref="T10:W10"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="G38:H38"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9682,132 +9711,132 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="108" t="s">
-        <v>149</v>
-      </c>
-      <c r="B2" s="108"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
+      <c r="A2" s="118" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="118"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
       <c r="E2">
         <f>Передача!$D$46</f>
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="108" t="s">
-        <v>206</v>
-      </c>
-      <c r="B3" s="108"/>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
+      <c r="A3" s="118" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3" s="118"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3">
         <f>Передача!$D$55</f>
-        <v>49.35</v>
+        <v>37.75</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="108" t="s">
-        <v>180</v>
-      </c>
-      <c r="B4" s="108"/>
-      <c r="C4" s="108"/>
-      <c r="D4" s="108"/>
+      <c r="A4" s="118" t="s">
+        <v>179</v>
+      </c>
+      <c r="B4" s="118"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="118"/>
       <c r="E4">
         <f>Передача!$D$56</f>
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="108" t="s">
-        <v>207</v>
-      </c>
-      <c r="B5" s="108"/>
-      <c r="C5" s="108"/>
-      <c r="D5" s="108"/>
+      <c r="A5" s="118" t="s">
+        <v>206</v>
+      </c>
+      <c r="B5" s="118"/>
+      <c r="C5" s="118"/>
+      <c r="D5" s="118"/>
       <c r="E5">
         <f>Передача!$D$60</f>
-        <v>413</v>
+        <v>309.75</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="108" t="s">
-        <v>181</v>
-      </c>
-      <c r="B6" s="108"/>
-      <c r="C6" s="108"/>
-      <c r="D6" s="108"/>
+      <c r="A6" s="118" t="s">
+        <v>180</v>
+      </c>
+      <c r="B6" s="118"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
       <c r="E6">
         <f>Передача!$D$61</f>
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="108" t="s">
-        <v>205</v>
-      </c>
-      <c r="B7" s="108"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
+      <c r="A7" s="118" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
       <c r="E7">
         <f>E2+E3/2+E5/2</f>
-        <v>471.17500000000001</v>
+        <v>353.75</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="108" t="s">
-        <v>204</v>
-      </c>
-      <c r="B8" s="108"/>
-      <c r="C8" s="108"/>
-      <c r="D8" s="108"/>
+      <c r="A8" s="118" t="s">
+        <v>203</v>
+      </c>
+      <c r="B8" s="118"/>
+      <c r="C8" s="118"/>
+      <c r="D8" s="118"/>
       <c r="E8">
         <f>E7^(1/3)+3</f>
-        <v>10.781453855618512</v>
+        <v>10.072378298355165</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="108" t="s">
-        <v>208</v>
-      </c>
-      <c r="B9" s="108"/>
-      <c r="C9" s="108"/>
-      <c r="D9" s="108"/>
+      <c r="A9" s="118" t="s">
+        <v>207</v>
+      </c>
+      <c r="B9" s="118"/>
+      <c r="C9" s="118"/>
+      <c r="D9" s="118"/>
       <c r="E9">
         <f>E8*3</f>
-        <v>32.34436156685554</v>
+        <v>30.217134895065495</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="108" t="s">
-        <v>209</v>
-      </c>
-      <c r="B10" s="108"/>
-      <c r="C10" s="108"/>
-      <c r="D10" s="108"/>
+      <c r="A10" s="118" t="s">
+        <v>208</v>
+      </c>
+      <c r="B10" s="118"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="118"/>
       <c r="E10" s="52">
         <v>4</v>
       </c>
@@ -9816,12 +9845,12 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="108" t="s">
-        <v>210</v>
-      </c>
-      <c r="B11" s="108"/>
-      <c r="C11" s="108"/>
-      <c r="D11" s="108"/>
+      <c r="A11" s="118" t="s">
+        <v>209</v>
+      </c>
+      <c r="B11" s="118"/>
+      <c r="C11" s="118"/>
+      <c r="D11" s="118"/>
       <c r="E11" s="52">
         <v>20</v>
       </c>
@@ -9830,55 +9859,55 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="108" t="s">
-        <v>212</v>
-      </c>
-      <c r="B12" s="108"/>
-      <c r="C12" s="108"/>
-      <c r="D12" s="108"/>
-      <c r="E12" s="108"/>
-      <c r="F12" s="108"/>
+      <c r="A12" s="118" t="s">
+        <v>211</v>
+      </c>
+      <c r="B12" s="118"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="118"/>
+      <c r="F12" s="118"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="108" t="s">
-        <v>211</v>
-      </c>
-      <c r="B13" s="108"/>
-      <c r="C13" s="108"/>
-      <c r="D13" s="108"/>
+      <c r="A13" s="118" t="s">
+        <v>210</v>
+      </c>
+      <c r="B13" s="118"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="118"/>
       <c r="E13">
         <f>E7+2*E8+E10*2+E11*2</f>
-        <v>540.73790771123709</v>
+        <v>421.89475659671035</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="108" t="s">
-        <v>168</v>
-      </c>
-      <c r="B14" s="108"/>
-      <c r="C14" s="108"/>
-      <c r="D14" s="108"/>
+      <c r="A14" s="118" t="s">
+        <v>167</v>
+      </c>
+      <c r="B14" s="118"/>
+      <c r="C14" s="118"/>
+      <c r="D14" s="118"/>
       <c r="E14">
         <f>E4+2*E8+2*E10</f>
-        <v>69.562907711237017</v>
+        <v>90.144756596710323</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="108" t="s">
+      <c r="A15" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="108"/>
-      <c r="C15" s="108"/>
-      <c r="D15" s="108"/>
+      <c r="B15" s="118"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="118"/>
       <c r="E15">
         <f>E5+E8+E9+2*E10</f>
-        <v>464.12581542247403</v>
+        <v>358.03951319342065</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
@@ -9887,41 +9916,55 @@
     <row r="20" spans="18:23" x14ac:dyDescent="0.3">
       <c r="R20" s="1"/>
       <c r="S20" s="36"/>
-      <c r="T20" s="108" t="s">
+      <c r="T20" s="118" t="s">
         <v>129</v>
       </c>
-      <c r="U20" s="108"/>
-      <c r="V20" s="75" t="s">
+      <c r="U20" s="118"/>
+      <c r="V20" s="94" t="s">
         <v>125</v>
       </c>
-      <c r="W20" s="75"/>
+      <c r="W20" s="94"/>
     </row>
     <row r="21" spans="18:23" x14ac:dyDescent="0.3">
-      <c r="R21" s="80" t="s">
+      <c r="R21" s="127" t="s">
         <v>124</v>
       </c>
-      <c r="S21" s="80"/>
-      <c r="T21" s="75"/>
-      <c r="U21" s="75"/>
-      <c r="V21" s="75"/>
-      <c r="W21" s="75"/>
+      <c r="S21" s="127"/>
+      <c r="T21" s="94"/>
+      <c r="U21" s="94"/>
+      <c r="V21" s="94"/>
+      <c r="W21" s="94"/>
     </row>
     <row r="22" spans="18:23" x14ac:dyDescent="0.3">
-      <c r="R22" s="80" t="s">
+      <c r="R22" s="127" t="s">
         <v>126</v>
       </c>
-      <c r="S22" s="80"/>
-      <c r="T22" s="75" t="s">
+      <c r="S22" s="127"/>
+      <c r="T22" s="94" t="s">
         <v>127</v>
       </c>
-      <c r="U22" s="75"/>
-      <c r="V22" s="76" t="s">
+      <c r="U22" s="94"/>
+      <c r="V22" s="106" t="s">
         <v>128</v>
       </c>
-      <c r="W22" s="76"/>
+      <c r="W22" s="106"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A3:D3"/>
     <mergeCell ref="V22:W22"/>
     <mergeCell ref="T22:U22"/>
     <mergeCell ref="R22:S22"/>
@@ -9930,20 +9973,6 @@
     <mergeCell ref="V20:W20"/>
     <mergeCell ref="T21:U21"/>
     <mergeCell ref="V21:W21"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -9957,7 +9986,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="108">
+      <c r="A1" s="118">
         <v>1</v>
       </c>
       <c r="B1">
@@ -9966,14 +9995,14 @@
       <c r="D1" s="48"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="108"/>
+      <c r="A2" s="118"/>
       <c r="B2">
         <v>1.05</v>
       </c>
       <c r="D2" s="48"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="108">
+      <c r="A3" s="118">
         <v>1.1000000000000001</v>
       </c>
       <c r="B3">
@@ -9982,14 +10011,14 @@
       <c r="D3" s="48"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="108"/>
+      <c r="A4" s="118"/>
       <c r="B4">
         <v>1.1499999999999999</v>
       </c>
       <c r="D4" s="48"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="108">
+      <c r="A5" s="118">
         <v>1.2</v>
       </c>
       <c r="B5">
@@ -9998,14 +10027,14 @@
       <c r="D5" s="48"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="108"/>
+      <c r="A6" s="118"/>
       <c r="B6">
         <v>1.3</v>
       </c>
       <c r="D6" s="48"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="108">
+      <c r="A7" s="118">
         <v>1.4</v>
       </c>
       <c r="B7">
@@ -10014,14 +10043,14 @@
       <c r="D7" s="48"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="108"/>
+      <c r="A8" s="118"/>
       <c r="B8">
         <v>1.5</v>
       </c>
       <c r="D8" s="48"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="108">
+      <c r="A9" s="118">
         <v>1.6</v>
       </c>
       <c r="B9">
@@ -10030,14 +10059,14 @@
       <c r="D9" s="48"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="108"/>
+      <c r="A10" s="118"/>
       <c r="B10">
         <v>1.7</v>
       </c>
       <c r="D10" s="48"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="108">
+      <c r="A11" s="118">
         <v>1.8</v>
       </c>
       <c r="B11">
@@ -10046,14 +10075,14 @@
       <c r="D11" s="48"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="108"/>
+      <c r="A12" s="118"/>
       <c r="B12">
         <v>1.9</v>
       </c>
       <c r="D12" s="48"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="108">
+      <c r="A13" s="118">
         <v>2</v>
       </c>
       <c r="B13">
@@ -10062,14 +10091,14 @@
       <c r="D13" s="48"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="108"/>
+      <c r="A14" s="118"/>
       <c r="B14">
         <v>2.1</v>
       </c>
       <c r="D14" s="48"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="108">
+      <c r="A15" s="118">
         <v>2.2000000000000002</v>
       </c>
       <c r="B15">
@@ -10078,14 +10107,14 @@
       <c r="D15" s="48"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="108"/>
+      <c r="A16" s="118"/>
       <c r="B16">
         <v>2.4</v>
       </c>
       <c r="D16" s="48"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="108">
+      <c r="A17" s="118">
         <v>2.5</v>
       </c>
       <c r="B17">
@@ -10094,14 +10123,14 @@
       <c r="D17" s="48"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="108"/>
+      <c r="A18" s="118"/>
       <c r="B18">
         <v>2.6</v>
       </c>
       <c r="D18" s="48"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="108">
+      <c r="A19" s="118">
         <v>2.8</v>
       </c>
       <c r="B19">
@@ -10110,14 +10139,14 @@
       <c r="D19" s="48"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="108"/>
+      <c r="A20" s="118"/>
       <c r="B20">
         <v>3</v>
       </c>
       <c r="D20" s="48"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="108">
+      <c r="A21" s="118">
         <v>3.2</v>
       </c>
       <c r="B21">
@@ -10126,14 +10155,14 @@
       <c r="D21" s="48"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="108"/>
+      <c r="A22" s="118"/>
       <c r="B22">
         <v>3.4</v>
       </c>
       <c r="D22" s="48"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="108">
+      <c r="A23" s="118">
         <v>3.6</v>
       </c>
       <c r="B23">
@@ -10142,14 +10171,14 @@
       <c r="D23" s="48"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="108"/>
+      <c r="A24" s="118"/>
       <c r="B24">
         <v>3.8</v>
       </c>
       <c r="D24" s="48"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="108">
+      <c r="A25" s="118">
         <v>4</v>
       </c>
       <c r="B25">
@@ -10158,14 +10187,14 @@
       <c r="D25" s="48"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="108"/>
+      <c r="A26" s="118"/>
       <c r="B26">
         <v>4.2</v>
       </c>
       <c r="D26" s="48"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="108">
+      <c r="A27" s="118">
         <v>4.5</v>
       </c>
       <c r="B27">
@@ -10174,14 +10203,14 @@
       <c r="D27" s="48"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="108"/>
+      <c r="A28" s="118"/>
       <c r="B28">
         <v>4.8</v>
       </c>
       <c r="D28" s="48"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="108">
+      <c r="A29" s="118">
         <v>5</v>
       </c>
       <c r="B29">
@@ -10190,14 +10219,14 @@
       <c r="D29" s="48"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="108"/>
+      <c r="A30" s="118"/>
       <c r="B30">
         <v>5.3</v>
       </c>
       <c r="D30" s="48"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="108">
+      <c r="A31" s="118">
         <v>5.6</v>
       </c>
       <c r="B31">
@@ -10206,14 +10235,14 @@
       <c r="D31" s="48"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="108"/>
+      <c r="A32" s="118"/>
       <c r="B32">
         <v>6</v>
       </c>
       <c r="D32" s="48"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="108">
+      <c r="A33" s="118">
         <v>6.3</v>
       </c>
       <c r="B33">
@@ -10222,14 +10251,14 @@
       <c r="D33" s="48"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="108"/>
+      <c r="A34" s="118"/>
       <c r="B34">
         <v>6.7</v>
       </c>
       <c r="D34" s="48"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="108">
+      <c r="A35" s="118">
         <v>7.1</v>
       </c>
       <c r="B35">
@@ -10238,14 +10267,14 @@
       <c r="D35" s="48"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="108"/>
+      <c r="A36" s="118"/>
       <c r="B36">
         <v>7.5</v>
       </c>
       <c r="D36" s="48"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="108">
+      <c r="A37" s="118">
         <v>8</v>
       </c>
       <c r="B37">
@@ -10254,14 +10283,14 @@
       <c r="D37" s="48"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="108"/>
+      <c r="A38" s="118"/>
       <c r="B38">
         <v>8.5</v>
       </c>
       <c r="D38" s="48"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="108">
+      <c r="A39" s="118">
         <v>9</v>
       </c>
       <c r="B39">
@@ -10270,7 +10299,7 @@
       <c r="D39" s="48"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="108"/>
+      <c r="A40" s="118"/>
       <c r="B40" s="61">
         <v>9.5</v>
       </c>
@@ -10278,7 +10307,7 @@
       <c r="E40" s="61"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="108">
+      <c r="A41" s="118">
         <v>10</v>
       </c>
       <c r="B41" s="48">
@@ -10286,13 +10315,13 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="108"/>
+      <c r="A42" s="118"/>
       <c r="B42" s="48">
         <v>10.5</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="108">
+      <c r="A43" s="118">
         <v>11</v>
       </c>
       <c r="B43" s="48">
@@ -10300,13 +10329,13 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="108"/>
+      <c r="A44" s="118"/>
       <c r="B44" s="48">
         <v>11.5</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="108">
+      <c r="A45" s="118">
         <v>12</v>
       </c>
       <c r="B45" s="48">
@@ -10314,13 +10343,13 @@
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="108"/>
+      <c r="A46" s="118"/>
       <c r="B46" s="48">
         <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="108">
+      <c r="A47" s="118">
         <v>14</v>
       </c>
       <c r="B47" s="48">
@@ -10328,13 +10357,13 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="108"/>
+      <c r="A48" s="118"/>
       <c r="B48" s="48">
         <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="108">
+      <c r="A49" s="118">
         <v>16</v>
       </c>
       <c r="B49" s="48">
@@ -10342,13 +10371,13 @@
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="108"/>
+      <c r="A50" s="118"/>
       <c r="B50" s="48">
         <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="108">
+      <c r="A51" s="118">
         <v>18</v>
       </c>
       <c r="B51" s="48">
@@ -10356,13 +10385,13 @@
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="108"/>
+      <c r="A52" s="118"/>
       <c r="B52" s="48">
         <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="108">
+      <c r="A53" s="118">
         <v>20</v>
       </c>
       <c r="B53" s="48">
@@ -10370,13 +10399,13 @@
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="108"/>
+      <c r="A54" s="118"/>
       <c r="B54" s="48">
         <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="108">
+      <c r="A55" s="118">
         <v>22</v>
       </c>
       <c r="B55" s="48">
@@ -10384,13 +10413,13 @@
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="108"/>
+      <c r="A56" s="118"/>
       <c r="B56" s="48">
         <v>24</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="108">
+      <c r="A57" s="118">
         <v>25</v>
       </c>
       <c r="B57" s="48">
@@ -10398,13 +10427,13 @@
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="108"/>
+      <c r="A58" s="118"/>
       <c r="B58" s="48">
         <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="108">
+      <c r="A59" s="118">
         <v>28</v>
       </c>
       <c r="B59" s="48">
@@ -10412,13 +10441,13 @@
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="108"/>
+      <c r="A60" s="118"/>
       <c r="B60" s="48">
         <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="108">
+      <c r="A61" s="118">
         <v>32</v>
       </c>
       <c r="B61" s="48">
@@ -10426,13 +10455,13 @@
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="108"/>
+      <c r="A62" s="118"/>
       <c r="B62" s="48">
         <v>34</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="108">
+      <c r="A63" s="118">
         <v>36</v>
       </c>
       <c r="B63" s="48">
@@ -10440,13 +10469,13 @@
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="108"/>
+      <c r="A64" s="118"/>
       <c r="B64" s="48">
         <v>38</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="108">
+      <c r="A65" s="118">
         <v>40</v>
       </c>
       <c r="B65" s="48">
@@ -10454,13 +10483,13 @@
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="108"/>
+      <c r="A66" s="118"/>
       <c r="B66" s="48">
         <v>42</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="108">
+      <c r="A67" s="118">
         <v>45</v>
       </c>
       <c r="B67" s="48">
@@ -10468,13 +10497,13 @@
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="108"/>
+      <c r="A68" s="118"/>
       <c r="B68" s="48">
         <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="108">
+      <c r="A69" s="118">
         <v>50</v>
       </c>
       <c r="B69" s="48">
@@ -10482,13 +10511,13 @@
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="108"/>
+      <c r="A70" s="118"/>
       <c r="B70" s="48">
         <v>53</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="108">
+      <c r="A71" s="118">
         <v>56</v>
       </c>
       <c r="B71" s="48">
@@ -10496,13 +10525,13 @@
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="108"/>
+      <c r="A72" s="118"/>
       <c r="B72" s="48">
         <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="108">
+      <c r="A73" s="118">
         <v>63</v>
       </c>
       <c r="B73" s="48">
@@ -10510,13 +10539,13 @@
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="108"/>
+      <c r="A74" s="118"/>
       <c r="B74" s="48">
         <v>67</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="108">
+      <c r="A75" s="118">
         <v>71</v>
       </c>
       <c r="B75" s="48">
@@ -10524,13 +10553,13 @@
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="108"/>
+      <c r="A76" s="118"/>
       <c r="B76" s="48">
         <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="108">
+      <c r="A77" s="118">
         <v>80</v>
       </c>
       <c r="B77" s="48">
@@ -10538,13 +10567,13 @@
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="108"/>
+      <c r="A78" s="118"/>
       <c r="B78" s="48">
         <v>85</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="108">
+      <c r="A79" s="118">
         <v>90</v>
       </c>
       <c r="B79" s="48">
@@ -10552,13 +10581,41 @@
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="108"/>
+      <c r="A80" s="118"/>
       <c r="B80" s="48">
         <v>95</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A35:A36"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="A3:A4"/>
@@ -10571,34 +10628,6 @@
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="A75:A76"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Расчёт.xlsx
+++ b/Расчёт.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Professional\Downloads\интститут\курсач детмаш\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE4C7D0-4789-4711-952D-24C01F6BAB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A578623C-539C-44BE-AF24-FAA696F6196F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="812" activeTab="2" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
   </bookViews>
@@ -1369,25 +1369,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1396,25 +1405,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1444,50 +1465,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1495,25 +1489,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1525,19 +1504,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2144,23 +2144,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A2" s="97" t="s">
+      <c r="A2" s="107" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
       <c r="E2" s="19">
         <v>4</v>
       </c>
@@ -2168,22 +2168,22 @@
         <v>4</v>
       </c>
       <c r="G2" s="6"/>
-      <c r="I2" s="97" t="s">
+      <c r="I2" s="107" t="s">
         <v>54</v>
       </c>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98">
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100">
         <f>E2*E3</f>
         <v>6.4</v>
       </c>
-      <c r="N2" s="99"/>
-      <c r="Q2" s="97" t="s">
+      <c r="N2" s="115"/>
+      <c r="Q2" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="R2" s="98"/>
-      <c r="S2" s="98"/>
+      <c r="R2" s="100"/>
+      <c r="S2" s="100"/>
       <c r="T2" s="8" t="s">
         <v>30</v>
       </c>
@@ -2193,11 +2193,11 @@
       <c r="V2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AC2" s="97" t="s">
+      <c r="AC2" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="98"/>
-      <c r="AE2" s="98"/>
+      <c r="AD2" s="100"/>
+      <c r="AE2" s="100"/>
       <c r="AF2" s="8" t="s">
         <v>44</v>
       </c>
@@ -2216,12 +2216,12 @@
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="94"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
       <c r="E3" s="20">
         <v>1.6</v>
       </c>
@@ -2229,19 +2229,19 @@
         <v>5</v>
       </c>
       <c r="G3" s="3"/>
-      <c r="I3" s="93" t="s">
+      <c r="I3" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="94"/>
-      <c r="K3" s="94"/>
-      <c r="L3" s="94"/>
-      <c r="M3" s="94"/>
-      <c r="N3" s="105"/>
-      <c r="Q3" s="93" t="s">
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="110"/>
+      <c r="Q3" s="99" t="s">
         <v>134</v>
       </c>
-      <c r="R3" s="94"/>
-      <c r="S3" s="94"/>
+      <c r="R3" s="93"/>
+      <c r="S3" s="93"/>
       <c r="T3" s="1">
         <v>0.96</v>
       </c>
@@ -2252,11 +2252,11 @@
         <f>AVERAGE(T3:U3)</f>
         <v>0.97</v>
       </c>
-      <c r="AC3" s="93" t="s">
+      <c r="AC3" s="99" t="s">
         <v>133</v>
       </c>
-      <c r="AD3" s="94"/>
-      <c r="AE3" s="94"/>
+      <c r="AD3" s="93"/>
+      <c r="AE3" s="93"/>
       <c r="AF3" s="1">
         <v>1.6</v>
       </c>
@@ -2281,30 +2281,30 @@
       </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A4" s="93" t="s">
+      <c r="A4" s="99" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="94"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="102" t="s">
+      <c r="B4" s="93"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="102"/>
-      <c r="G4" s="108"/>
-      <c r="I4" s="93" t="s">
+      <c r="F4" s="108"/>
+      <c r="G4" s="109"/>
+      <c r="I4" s="99" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="94"/>
-      <c r="K4" s="94"/>
-      <c r="L4" s="94"/>
-      <c r="M4" s="94"/>
-      <c r="N4" s="105"/>
-      <c r="Q4" s="93" t="s">
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93"/>
+      <c r="M4" s="93"/>
+      <c r="N4" s="110"/>
+      <c r="Q4" s="99" t="s">
         <v>49</v>
       </c>
-      <c r="R4" s="94"/>
-      <c r="S4" s="94"/>
+      <c r="R4" s="93"/>
+      <c r="S4" s="93"/>
       <c r="T4" s="1">
         <v>0.95</v>
       </c>
@@ -2315,11 +2315,11 @@
         <f t="shared" ref="V4:V12" si="1">AVERAGE(T4:U4)</f>
         <v>0.96</v>
       </c>
-      <c r="AC4" s="93" t="s">
+      <c r="AC4" s="99" t="s">
         <v>48</v>
       </c>
-      <c r="AD4" s="94"/>
-      <c r="AE4" s="94"/>
+      <c r="AD4" s="93"/>
+      <c r="AE4" s="93"/>
       <c r="AF4" s="1">
         <v>1</v>
       </c>
@@ -2344,12 +2344,12 @@
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="94"/>
-      <c r="D5" s="94"/>
+      <c r="B5" s="93"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
       <c r="E5" s="21">
         <v>10000</v>
       </c>
@@ -2359,19 +2359,19 @@
       <c r="G5" s="3"/>
       <c r="I5" s="7"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="94" t="s">
+      <c r="K5" s="93" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="94"/>
-      <c r="M5" s="94" t="s">
+      <c r="L5" s="93"/>
+      <c r="M5" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="105"/>
-      <c r="Q5" s="93" t="s">
+      <c r="N5" s="110"/>
+      <c r="Q5" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="R5" s="94"/>
-      <c r="S5" s="94"/>
+      <c r="R5" s="93"/>
+      <c r="S5" s="93"/>
       <c r="T5" s="1">
         <v>0.95</v>
       </c>
@@ -2382,11 +2382,11 @@
         <f t="shared" si="1"/>
         <v>0.96</v>
       </c>
-      <c r="AC5" s="93" t="s">
+      <c r="AC5" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="AD5" s="94"/>
-      <c r="AE5" s="94"/>
+      <c r="AD5" s="93"/>
+      <c r="AE5" s="93"/>
       <c r="AF5" s="1">
         <v>3.15</v>
       </c>
@@ -2411,34 +2411,34 @@
       </c>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A6" s="93" t="s">
+      <c r="A6" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="94"/>
-      <c r="C6" s="94"/>
-      <c r="D6" s="94"/>
+      <c r="B6" s="93"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="93"/>
       <c r="E6" s="21">
         <v>0.9</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="3"/>
-      <c r="I6" s="93" t="s">
+      <c r="I6" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="94"/>
-      <c r="K6" s="102">
+      <c r="J6" s="93"/>
+      <c r="K6" s="108">
         <v>2</v>
       </c>
-      <c r="L6" s="102"/>
-      <c r="M6" s="94">
+      <c r="L6" s="108"/>
+      <c r="M6" s="93">
         <v>0.99</v>
       </c>
-      <c r="N6" s="105"/>
-      <c r="Q6" s="93" t="s">
+      <c r="N6" s="110"/>
+      <c r="Q6" s="99" t="s">
         <v>33</v>
       </c>
-      <c r="R6" s="94"/>
-      <c r="S6" s="94"/>
+      <c r="R6" s="93"/>
+      <c r="S6" s="93"/>
       <c r="T6" s="1">
         <v>0.92</v>
       </c>
@@ -2449,11 +2449,11 @@
         <f t="shared" si="1"/>
         <v>0.94</v>
       </c>
-      <c r="AC6" s="93" t="s">
+      <c r="AC6" s="99" t="s">
         <v>45</v>
       </c>
-      <c r="AD6" s="94"/>
-      <c r="AE6" s="94"/>
+      <c r="AD6" s="93"/>
+      <c r="AE6" s="93"/>
       <c r="AF6" s="1">
         <v>12.5</v>
       </c>
@@ -2478,34 +2478,34 @@
       </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A7" s="93" t="s">
+      <c r="A7" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="94"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
+      <c r="B7" s="93"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="93"/>
       <c r="E7" s="21">
         <v>3</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="3"/>
-      <c r="I7" s="93" t="s">
+      <c r="I7" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="94"/>
-      <c r="K7" s="102">
+      <c r="J7" s="93"/>
+      <c r="K7" s="108">
         <v>2</v>
       </c>
-      <c r="L7" s="102"/>
-      <c r="M7" s="94">
+      <c r="L7" s="108"/>
+      <c r="M7" s="93">
         <v>0.98</v>
       </c>
-      <c r="N7" s="105"/>
-      <c r="Q7" s="93" t="s">
+      <c r="N7" s="110"/>
+      <c r="Q7" s="99" t="s">
         <v>34</v>
       </c>
-      <c r="R7" s="94"/>
-      <c r="S7" s="94"/>
+      <c r="R7" s="93"/>
+      <c r="S7" s="93"/>
       <c r="T7" s="1">
         <v>0.72</v>
       </c>
@@ -2516,11 +2516,11 @@
         <f t="shared" si="1"/>
         <v>0.77</v>
       </c>
-      <c r="AC7" s="93" t="s">
+      <c r="AC7" s="99" t="s">
         <v>33</v>
       </c>
-      <c r="AD7" s="94"/>
-      <c r="AE7" s="94"/>
+      <c r="AD7" s="93"/>
+      <c r="AE7" s="93"/>
       <c r="AF7" s="1">
         <v>16</v>
       </c>
@@ -2545,35 +2545,35 @@
       </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A8" s="100" t="s">
+      <c r="A8" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="101"/>
-      <c r="C8" s="101"/>
-      <c r="D8" s="101"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="104"/>
       <c r="E8" s="22">
         <v>2.2000000000000002</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="5"/>
-      <c r="I8" s="93" t="s">
+      <c r="I8" s="99" t="s">
         <v>264</v>
       </c>
-      <c r="J8" s="94"/>
-      <c r="K8" s="102">
+      <c r="J8" s="93"/>
+      <c r="K8" s="108">
         <v>0</v>
       </c>
-      <c r="L8" s="102"/>
-      <c r="M8" s="103">
+      <c r="L8" s="108"/>
+      <c r="M8" s="125">
         <f>V11</f>
         <v>0.95</v>
       </c>
-      <c r="N8" s="104"/>
-      <c r="Q8" s="93" t="s">
+      <c r="N8" s="130"/>
+      <c r="Q8" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="R8" s="94"/>
-      <c r="S8" s="94"/>
+      <c r="R8" s="93"/>
+      <c r="S8" s="93"/>
       <c r="T8" s="1">
         <v>0.7</v>
       </c>
@@ -2584,11 +2584,11 @@
         <f t="shared" si="1"/>
         <v>0.75</v>
       </c>
-      <c r="AC8" s="93" t="s">
+      <c r="AC8" s="99" t="s">
         <v>46</v>
       </c>
-      <c r="AD8" s="94"/>
-      <c r="AE8" s="94"/>
+      <c r="AD8" s="93"/>
+      <c r="AE8" s="93"/>
       <c r="AF8" s="1">
         <v>10</v>
       </c>
@@ -2613,31 +2613,31 @@
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A9" s="109" t="s">
+      <c r="A9" s="116" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="110"/>
-      <c r="C9" s="110"/>
-      <c r="D9" s="110"/>
-      <c r="E9" s="110"/>
-      <c r="F9" s="110"/>
-      <c r="G9" s="111"/>
-      <c r="I9" s="93" t="s">
+      <c r="B9" s="117"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="117"/>
+      <c r="G9" s="118"/>
+      <c r="I9" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="J9" s="94"/>
-      <c r="K9" s="94"/>
-      <c r="L9" s="94"/>
-      <c r="M9" s="106">
+      <c r="J9" s="93"/>
+      <c r="K9" s="93"/>
+      <c r="L9" s="93"/>
+      <c r="M9" s="94">
         <f>M7^K7*M6^K6*M8^K8</f>
         <v>0.94128803999999988</v>
       </c>
-      <c r="N9" s="107"/>
-      <c r="Q9" s="93" t="s">
+      <c r="N9" s="128"/>
+      <c r="Q9" s="99" t="s">
         <v>36</v>
       </c>
-      <c r="R9" s="94"/>
-      <c r="S9" s="94"/>
+      <c r="R9" s="93"/>
+      <c r="S9" s="93"/>
       <c r="T9" s="1">
         <v>0.75</v>
       </c>
@@ -2648,11 +2648,11 @@
         <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="AC9" s="93" t="s">
+      <c r="AC9" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="AD9" s="94"/>
-      <c r="AE9" s="94"/>
+      <c r="AD9" s="93"/>
+      <c r="AE9" s="93"/>
       <c r="AF9" s="1">
         <v>8</v>
       </c>
@@ -2677,30 +2677,30 @@
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A10" s="112" t="s">
+      <c r="A10" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="113"/>
-      <c r="C10" s="113"/>
-      <c r="D10" s="113"/>
-      <c r="E10" s="113"/>
-      <c r="F10" s="113"/>
-      <c r="G10" s="114"/>
-      <c r="I10" s="93" t="s">
+      <c r="B10" s="120"/>
+      <c r="C10" s="120"/>
+      <c r="D10" s="120"/>
+      <c r="E10" s="120"/>
+      <c r="F10" s="120"/>
+      <c r="G10" s="121"/>
+      <c r="I10" s="99" t="s">
         <v>51</v>
       </c>
-      <c r="J10" s="94"/>
-      <c r="K10" s="94"/>
-      <c r="L10" s="94"/>
-      <c r="M10" s="102">
+      <c r="J10" s="93"/>
+      <c r="K10" s="93"/>
+      <c r="L10" s="93"/>
+      <c r="M10" s="108">
         <v>0.97</v>
       </c>
-      <c r="N10" s="108"/>
-      <c r="Q10" s="93" t="s">
+      <c r="N10" s="109"/>
+      <c r="Q10" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="R10" s="94"/>
-      <c r="S10" s="94"/>
+      <c r="R10" s="93"/>
+      <c r="S10" s="93"/>
       <c r="T10" s="1">
         <v>0.8</v>
       </c>
@@ -2711,11 +2711,11 @@
         <f t="shared" si="1"/>
         <v>0.85000000000000009</v>
       </c>
-      <c r="AC10" s="100" t="s">
+      <c r="AC10" s="103" t="s">
         <v>34</v>
       </c>
-      <c r="AD10" s="101"/>
-      <c r="AE10" s="101"/>
+      <c r="AD10" s="104"/>
+      <c r="AE10" s="104"/>
       <c r="AF10" s="4">
         <v>70</v>
       </c>
@@ -2740,31 +2740,31 @@
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A11" s="109" t="s">
+      <c r="A11" s="116" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="110"/>
-      <c r="C11" s="110"/>
-      <c r="D11" s="110"/>
-      <c r="E11" s="110"/>
-      <c r="F11" s="110"/>
-      <c r="G11" s="111"/>
-      <c r="I11" s="100" t="s">
+      <c r="B11" s="117"/>
+      <c r="C11" s="117"/>
+      <c r="D11" s="117"/>
+      <c r="E11" s="117"/>
+      <c r="F11" s="117"/>
+      <c r="G11" s="118"/>
+      <c r="I11" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="J11" s="101"/>
-      <c r="K11" s="101"/>
-      <c r="L11" s="101"/>
-      <c r="M11" s="95">
+      <c r="J11" s="104"/>
+      <c r="K11" s="104"/>
+      <c r="L11" s="104"/>
+      <c r="M11" s="105">
         <f>M2/M10/M9</f>
         <v>7.0094783572623509</v>
       </c>
-      <c r="N11" s="96"/>
-      <c r="Q11" s="93" t="s">
+      <c r="N11" s="129"/>
+      <c r="Q11" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="R11" s="94"/>
-      <c r="S11" s="94"/>
+      <c r="R11" s="93"/>
+      <c r="S11" s="93"/>
       <c r="T11" s="1">
         <v>0.94</v>
       </c>
@@ -2783,22 +2783,22 @@
       <c r="AH11" s="1"/>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A12" s="97" t="s">
+      <c r="A12" s="107" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="98"/>
-      <c r="C12" s="98"/>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98" t="s">
+      <c r="B12" s="100"/>
+      <c r="C12" s="100"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="100" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="98"/>
-      <c r="G12" s="99"/>
-      <c r="Q12" s="100" t="s">
+      <c r="F12" s="100"/>
+      <c r="G12" s="115"/>
+      <c r="Q12" s="103" t="s">
         <v>39</v>
       </c>
-      <c r="R12" s="101"/>
-      <c r="S12" s="101"/>
+      <c r="R12" s="104"/>
+      <c r="S12" s="104"/>
       <c r="T12" s="4">
         <v>0.92</v>
       </c>
@@ -2814,12 +2814,12 @@
       </c>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A13" s="93" t="s">
+      <c r="A13" s="99" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="94"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="94"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="93"/>
       <c r="E13" s="21">
         <v>400</v>
       </c>
@@ -2834,12 +2834,12 @@
       </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A14" s="93" t="s">
+      <c r="A14" s="99" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="94"/>
-      <c r="C14" s="94"/>
-      <c r="D14" s="94"/>
+      <c r="B14" s="93"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="93"/>
       <c r="E14" s="21">
         <v>400</v>
       </c>
@@ -2849,12 +2849,12 @@
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A15" s="100" t="s">
+      <c r="A15" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="101"/>
-      <c r="C15" s="101"/>
-      <c r="D15" s="101"/>
+      <c r="B15" s="104"/>
+      <c r="C15" s="104"/>
+      <c r="D15" s="104"/>
       <c r="E15" s="22">
         <v>300</v>
       </c>
@@ -2864,40 +2864,40 @@
       <c r="G15" s="5"/>
     </row>
     <row r="19" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I19" s="97" t="s">
+      <c r="I19" s="107" t="s">
         <v>123</v>
       </c>
-      <c r="J19" s="99"/>
-      <c r="K19" s="97">
+      <c r="J19" s="115"/>
+      <c r="K19" s="107">
         <v>3000</v>
       </c>
-      <c r="L19" s="98"/>
-      <c r="M19" s="98"/>
-      <c r="N19" s="99"/>
-      <c r="O19" s="98">
+      <c r="L19" s="100"/>
+      <c r="M19" s="100"/>
+      <c r="N19" s="115"/>
+      <c r="O19" s="100">
         <v>1500</v>
       </c>
-      <c r="P19" s="98"/>
-      <c r="Q19" s="98"/>
-      <c r="R19" s="98"/>
-      <c r="S19" s="97">
+      <c r="P19" s="100"/>
+      <c r="Q19" s="100"/>
+      <c r="R19" s="100"/>
+      <c r="S19" s="107">
         <v>1000</v>
       </c>
-      <c r="T19" s="98"/>
-      <c r="U19" s="98"/>
-      <c r="V19" s="99"/>
-      <c r="W19" s="98">
+      <c r="T19" s="100"/>
+      <c r="U19" s="100"/>
+      <c r="V19" s="115"/>
+      <c r="W19" s="100">
         <v>750</v>
       </c>
-      <c r="X19" s="98"/>
-      <c r="Y19" s="98"/>
-      <c r="Z19" s="99"/>
+      <c r="X19" s="100"/>
+      <c r="Y19" s="100"/>
+      <c r="Z19" s="115"/>
     </row>
     <row r="20" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I20" s="100" t="s">
+      <c r="I20" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="J20" s="119"/>
+      <c r="J20" s="127"/>
       <c r="K20" s="12" t="s">
         <v>72</v>
       </c>
@@ -2948,10 +2948,10 @@
       </c>
     </row>
     <row r="21" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I21" s="93">
+      <c r="I21" s="99">
         <v>0.37</v>
       </c>
-      <c r="J21" s="94"/>
+      <c r="J21" s="93"/>
       <c r="K21" s="26" t="s">
         <v>57</v>
       </c>
@@ -2986,10 +2986,10 @@
       <c r="Z21" s="3"/>
     </row>
     <row r="22" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I22" s="93">
+      <c r="I22" s="99">
         <v>0.55000000000000004</v>
       </c>
-      <c r="J22" s="94"/>
+      <c r="J22" s="93"/>
       <c r="K22" s="26" t="s">
         <v>57</v>
       </c>
@@ -3022,10 +3022,10 @@
       <c r="Z22" s="3"/>
     </row>
     <row r="23" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I23" s="93">
+      <c r="I23" s="99">
         <v>0.75</v>
       </c>
-      <c r="J23" s="94"/>
+      <c r="J23" s="93"/>
       <c r="K23" s="7" t="s">
         <v>58</v>
       </c>
@@ -3058,10 +3058,10 @@
       <c r="Z23" s="3"/>
     </row>
     <row r="24" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I24" s="93">
+      <c r="I24" s="99">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J24" s="94"/>
+      <c r="J24" s="93"/>
       <c r="K24" s="7" t="s">
         <v>59</v>
       </c>
@@ -3094,10 +3094,10 @@
       <c r="Z24" s="3"/>
     </row>
     <row r="25" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I25" s="93">
+      <c r="I25" s="99">
         <v>1.5</v>
       </c>
-      <c r="J25" s="94"/>
+      <c r="J25" s="93"/>
       <c r="K25" s="7" t="s">
         <v>60</v>
       </c>
@@ -3130,10 +3130,10 @@
       <c r="Z25" s="3"/>
     </row>
     <row r="26" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I26" s="93">
+      <c r="I26" s="99">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J26" s="94"/>
+      <c r="J26" s="93"/>
       <c r="K26" s="7" t="s">
         <v>87</v>
       </c>
@@ -3166,10 +3166,10 @@
       <c r="Z26" s="3"/>
     </row>
     <row r="27" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I27" s="93">
+      <c r="I27" s="99">
         <v>3</v>
       </c>
-      <c r="J27" s="94"/>
+      <c r="J27" s="93"/>
       <c r="K27" s="7" t="s">
         <v>61</v>
       </c>
@@ -3200,10 +3200,10 @@
       <c r="Z27" s="3"/>
     </row>
     <row r="28" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I28" s="93">
+      <c r="I28" s="99">
         <v>4</v>
       </c>
-      <c r="J28" s="94"/>
+      <c r="J28" s="93"/>
       <c r="K28" s="7" t="s">
         <v>62</v>
       </c>
@@ -3234,10 +3234,10 @@
       <c r="Z28" s="3"/>
     </row>
     <row r="29" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I29" s="93">
+      <c r="I29" s="99">
         <v>5.5</v>
       </c>
-      <c r="J29" s="94"/>
+      <c r="J29" s="93"/>
       <c r="K29" s="7" t="s">
         <v>63</v>
       </c>
@@ -3288,10 +3288,10 @@
       </c>
     </row>
     <row r="30" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I30" s="93">
+      <c r="I30" s="99">
         <v>7.5</v>
       </c>
-      <c r="J30" s="94"/>
+      <c r="J30" s="93"/>
       <c r="K30" s="7" t="s">
         <v>64</v>
       </c>
@@ -3342,10 +3342,10 @@
       </c>
     </row>
     <row r="31" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I31" s="93">
+      <c r="I31" s="99">
         <v>11</v>
       </c>
-      <c r="J31" s="94"/>
+      <c r="J31" s="93"/>
       <c r="K31" s="7" t="s">
         <v>65</v>
       </c>
@@ -3396,10 +3396,10 @@
       </c>
     </row>
     <row r="32" spans="9:26" x14ac:dyDescent="0.3">
-      <c r="I32" s="93">
+      <c r="I32" s="99">
         <v>15</v>
       </c>
-      <c r="J32" s="94"/>
+      <c r="J32" s="93"/>
       <c r="K32" s="7" t="s">
         <v>66</v>
       </c>
@@ -3430,10 +3430,10 @@
       <c r="Z32" s="3"/>
     </row>
     <row r="33" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="I33" s="93">
+      <c r="I33" s="99">
         <v>18.5</v>
       </c>
-      <c r="J33" s="94"/>
+      <c r="J33" s="93"/>
       <c r="K33" s="7" t="s">
         <v>67</v>
       </c>
@@ -3464,10 +3464,10 @@
       <c r="Z33" s="3"/>
     </row>
     <row r="34" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="I34" s="93">
+      <c r="I34" s="99">
         <v>22</v>
       </c>
-      <c r="J34" s="94"/>
+      <c r="J34" s="93"/>
       <c r="K34" s="7" t="s">
         <v>68</v>
       </c>
@@ -3498,10 +3498,10 @@
       <c r="Z34" s="3"/>
     </row>
     <row r="35" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="I35" s="100">
+      <c r="I35" s="103">
         <v>30</v>
       </c>
-      <c r="J35" s="101"/>
+      <c r="J35" s="104"/>
       <c r="K35" s="12" t="s">
         <v>69</v>
       </c>
@@ -3532,15 +3532,15 @@
       <c r="Z35" s="5"/>
     </row>
     <row r="36" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G36" s="118" t="s">
+      <c r="G36" s="126" t="s">
         <v>121</v>
       </c>
-      <c r="H36" s="118"/>
-      <c r="I36" s="109">
+      <c r="H36" s="126"/>
+      <c r="I36" s="116">
         <f>_xlfn.MINIFS(I21:J35,I21:J35,"&gt;="&amp;M11)</f>
         <v>7.5</v>
       </c>
-      <c r="J36" s="110"/>
+      <c r="J36" s="117"/>
       <c r="K36" s="9" t="str">
         <f>VLOOKUP($I$36,$I$21:$R$35,3)</f>
         <v>112M2</v>
@@ -3612,12 +3612,12 @@
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
       <c r="F38" s="16"/>
-      <c r="G38" s="97" t="s">
+      <c r="G38" s="107" t="s">
         <v>40</v>
       </c>
-      <c r="H38" s="98"/>
-      <c r="I38" s="98"/>
-      <c r="J38" s="99"/>
+      <c r="H38" s="100"/>
+      <c r="I38" s="100"/>
+      <c r="J38" s="115"/>
       <c r="K38" s="11"/>
       <c r="L38" s="18"/>
       <c r="M38" s="18"/>
@@ -3641,12 +3641,12 @@
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
       <c r="F39" s="16"/>
-      <c r="G39" s="93" t="s">
+      <c r="G39" s="99" t="s">
         <v>43</v>
       </c>
-      <c r="H39" s="94"/>
-      <c r="I39" s="94"/>
-      <c r="J39" s="105"/>
+      <c r="H39" s="93"/>
+      <c r="I39" s="93"/>
+      <c r="J39" s="110"/>
       <c r="K39" s="7"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -3682,14 +3682,14 @@
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
-      <c r="G40" s="93" t="s">
+      <c r="G40" s="99" t="s">
         <v>120</v>
       </c>
-      <c r="H40" s="94"/>
-      <c r="I40" s="94" t="s">
+      <c r="H40" s="93"/>
+      <c r="I40" s="93" t="s">
         <v>119</v>
       </c>
-      <c r="J40" s="105"/>
+      <c r="J40" s="110"/>
       <c r="K40" s="27" t="s">
         <v>122</v>
       </c>
@@ -3737,15 +3737,15 @@
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
-      <c r="G41" s="115">
+      <c r="G41" s="122">
         <v>160</v>
       </c>
-      <c r="H41" s="116"/>
-      <c r="I41" s="120">
+      <c r="H41" s="123"/>
+      <c r="I41" s="111">
         <f t="shared" ref="I41:I46" si="4">$E$3*60000/PI()/G41</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="J41" s="121"/>
+      <c r="J41" s="112"/>
       <c r="K41" s="15">
         <f t="shared" ref="K41:K46" si="5">IF($I41,L$36/$I41,"-")</f>
         <v>15.15818455357075</v>
@@ -3817,15 +3817,15 @@
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-      <c r="G42" s="117">
+      <c r="G42" s="124">
         <v>200</v>
       </c>
-      <c r="H42" s="103"/>
-      <c r="I42" s="122">
+      <c r="H42" s="125"/>
+      <c r="I42" s="102">
         <f t="shared" si="4"/>
         <v>152.78874536821954</v>
       </c>
-      <c r="J42" s="123"/>
+      <c r="J42" s="113"/>
       <c r="K42" s="13">
         <f t="shared" si="5"/>
         <v>18.947730691963439</v>
@@ -3894,15 +3894,15 @@
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
-      <c r="G43" s="93">
+      <c r="G43" s="99">
         <v>250</v>
       </c>
-      <c r="H43" s="94"/>
-      <c r="I43" s="122">
+      <c r="H43" s="93"/>
+      <c r="I43" s="102">
         <f t="shared" si="4"/>
         <v>122.23099629457563</v>
       </c>
-      <c r="J43" s="123"/>
+      <c r="J43" s="113"/>
       <c r="K43" s="13">
         <f t="shared" si="5"/>
         <v>23.684663364954297</v>
@@ -3971,15 +3971,15 @@
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
-      <c r="G44" s="93">
+      <c r="G44" s="99">
         <v>315</v>
       </c>
-      <c r="H44" s="94"/>
-      <c r="I44" s="122">
+      <c r="H44" s="93"/>
+      <c r="I44" s="102">
         <f t="shared" si="4"/>
         <v>97.008727217917169</v>
       </c>
-      <c r="J44" s="123"/>
+      <c r="J44" s="113"/>
       <c r="K44" s="13">
         <f t="shared" si="5"/>
         <v>29.842675839842414</v>
@@ -4042,15 +4042,15 @@
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="93">
+      <c r="G45" s="99">
         <v>400</v>
       </c>
-      <c r="H45" s="94"/>
-      <c r="I45" s="122">
+      <c r="H45" s="93"/>
+      <c r="I45" s="102">
         <f t="shared" si="4"/>
         <v>76.394372684109769</v>
       </c>
-      <c r="J45" s="123"/>
+      <c r="J45" s="113"/>
       <c r="K45" s="13">
         <f t="shared" si="5"/>
         <v>37.895461383926879</v>
@@ -4110,15 +4110,15 @@
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-      <c r="G46" s="100">
+      <c r="G46" s="103">
         <v>500</v>
       </c>
-      <c r="H46" s="101"/>
-      <c r="I46" s="124">
+      <c r="H46" s="104"/>
+      <c r="I46" s="106">
         <f t="shared" si="4"/>
         <v>61.115498147287816</v>
       </c>
-      <c r="J46" s="125"/>
+      <c r="J46" s="114"/>
       <c r="K46" s="14">
         <f t="shared" si="5"/>
         <v>47.369326729908593</v>
@@ -4211,25 +4211,25 @@
       <c r="Z47" s="1"/>
     </row>
     <row r="48" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B48" s="97" t="s">
+      <c r="B48" s="107" t="s">
         <v>110</v>
       </c>
-      <c r="C48" s="98"/>
-      <c r="D48" s="98"/>
-      <c r="E48" s="98"/>
-      <c r="F48" s="98" t="str">
+      <c r="C48" s="100"/>
+      <c r="D48" s="100"/>
+      <c r="E48" s="100"/>
+      <c r="F48" s="100" t="str">
         <f>P46</f>
         <v>Цилиндрическая 1</v>
       </c>
-      <c r="G48" s="99"/>
+      <c r="G48" s="115"/>
       <c r="H48" s="16"/>
       <c r="I48" s="16"/>
       <c r="J48" s="16"/>
       <c r="K48" s="36"/>
-      <c r="L48" s="94" t="s">
+      <c r="L48" s="93" t="s">
         <v>56</v>
       </c>
-      <c r="M48" s="94"/>
+      <c r="M48" s="93"/>
       <c r="N48" s="28">
         <f ca="1">MAX(Z41:Z46,V41:V46,R41:R46,N41:N46)</f>
         <v>0.78915140422920127</v>
@@ -4247,12 +4247,12 @@
       <c r="Z48" s="1"/>
     </row>
     <row r="49" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B49" s="93" t="s">
+      <c r="B49" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="94"/>
-      <c r="D49" s="94"/>
-      <c r="E49" s="94"/>
+      <c r="C49" s="93"/>
+      <c r="D49" s="93"/>
+      <c r="E49" s="93"/>
       <c r="F49" s="46">
         <f>O41</f>
         <v>7.5398223686155026</v>
@@ -4277,12 +4277,12 @@
       <c r="Z49" s="1"/>
     </row>
     <row r="50" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B50" s="93" t="s">
+      <c r="B50" s="99" t="s">
         <v>96</v>
       </c>
-      <c r="C50" s="94"/>
-      <c r="D50" s="94"/>
-      <c r="E50" s="94"/>
+      <c r="C50" s="93"/>
+      <c r="D50" s="93"/>
+      <c r="E50" s="93"/>
       <c r="F50" s="16">
         <f>P36</f>
         <v>1440</v>
@@ -4299,12 +4299,12 @@
       <c r="Z50" s="1"/>
     </row>
     <row r="51" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B51" s="93" t="s">
+      <c r="B51" s="99" t="s">
         <v>104</v>
       </c>
-      <c r="C51" s="94"/>
-      <c r="D51" s="94"/>
-      <c r="E51" s="94"/>
+      <c r="C51" s="93"/>
+      <c r="D51" s="93"/>
+      <c r="E51" s="93"/>
       <c r="F51" s="1">
         <f>F50*PI()/30</f>
         <v>150.79644737231007</v>
@@ -4313,29 +4313,29 @@
         <v>106</v>
       </c>
       <c r="H51" s="16"/>
-      <c r="I51" s="109" t="s">
+      <c r="I51" s="116" t="s">
         <v>114</v>
       </c>
-      <c r="J51" s="111"/>
+      <c r="J51" s="118"/>
       <c r="K51" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="L51" s="98" t="s">
+      <c r="L51" s="100" t="s">
         <v>122</v>
       </c>
-      <c r="M51" s="98"/>
-      <c r="N51" s="126" t="s">
+      <c r="M51" s="100"/>
+      <c r="N51" s="97" t="s">
         <v>115</v>
       </c>
-      <c r="O51" s="126"/>
-      <c r="P51" s="98" t="s">
+      <c r="O51" s="97"/>
+      <c r="P51" s="100" t="s">
         <v>116</v>
       </c>
-      <c r="Q51" s="98"/>
-      <c r="R51" s="126" t="s">
+      <c r="Q51" s="100"/>
+      <c r="R51" s="97" t="s">
         <v>118</v>
       </c>
-      <c r="S51" s="126"/>
+      <c r="S51" s="97"/>
       <c r="T51" s="49"/>
       <c r="U51" s="49"/>
       <c r="V51" s="49"/>
@@ -4344,12 +4344,12 @@
       <c r="Z51" s="1"/>
     </row>
     <row r="52" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B52" s="93" t="s">
+      <c r="B52" s="99" t="s">
         <v>42</v>
       </c>
-      <c r="C52" s="94"/>
-      <c r="D52" s="94"/>
-      <c r="E52" s="94"/>
+      <c r="C52" s="93"/>
+      <c r="D52" s="93"/>
+      <c r="E52" s="93"/>
       <c r="F52" s="45">
         <f>I41</f>
         <v>190.98593171027443</v>
@@ -4358,33 +4358,33 @@
         <v>105</v>
       </c>
       <c r="H52" s="16"/>
-      <c r="I52" s="93" t="s">
+      <c r="I52" s="99" t="s">
         <v>117</v>
       </c>
-      <c r="J52" s="94"/>
+      <c r="J52" s="93"/>
       <c r="K52" s="42">
         <f>R36</f>
         <v>0.872</v>
       </c>
-      <c r="L52" s="98">
+      <c r="L52" s="100">
         <v>1</v>
       </c>
-      <c r="M52" s="98"/>
-      <c r="N52" s="129">
+      <c r="M52" s="100"/>
+      <c r="N52" s="95">
         <f>F50</f>
         <v>1440</v>
       </c>
-      <c r="O52" s="129"/>
-      <c r="P52" s="128">
+      <c r="O52" s="95"/>
+      <c r="P52" s="101">
         <f ca="1">F55</f>
         <v>46.89699496864425</v>
       </c>
-      <c r="Q52" s="128"/>
-      <c r="R52" s="126">
+      <c r="Q52" s="101"/>
+      <c r="R52" s="97">
         <f t="shared" ref="R52:R57" ca="1" si="17">P52*N52*PI()/1000/30</f>
         <v>7.0719002337086527</v>
       </c>
-      <c r="S52" s="126"/>
+      <c r="S52" s="97"/>
       <c r="T52" s="16"/>
       <c r="U52" s="30"/>
       <c r="X52" s="1"/>
@@ -4392,12 +4392,12 @@
       <c r="Z52" s="1"/>
     </row>
     <row r="53" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B53" s="93" t="s">
+      <c r="B53" s="99" t="s">
         <v>107</v>
       </c>
-      <c r="C53" s="94"/>
-      <c r="D53" s="94"/>
-      <c r="E53" s="94"/>
+      <c r="C53" s="93"/>
+      <c r="D53" s="93"/>
+      <c r="E53" s="93"/>
       <c r="F53" s="16">
         <f>G41</f>
         <v>160</v>
@@ -4406,33 +4406,33 @@
         <v>16</v>
       </c>
       <c r="H53" s="16"/>
-      <c r="I53" s="93" t="s">
+      <c r="I53" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="J53" s="94"/>
+      <c r="J53" s="93"/>
       <c r="K53" s="7">
         <f>M7</f>
         <v>0.98</v>
       </c>
-      <c r="L53" s="94">
+      <c r="L53" s="93">
         <v>1</v>
       </c>
-      <c r="M53" s="94"/>
-      <c r="N53" s="130">
+      <c r="M53" s="93"/>
+      <c r="N53" s="96">
         <f>N52/L53</f>
         <v>1440</v>
       </c>
-      <c r="O53" s="130"/>
-      <c r="P53" s="106">
+      <c r="O53" s="96"/>
+      <c r="P53" s="94">
         <f ca="1">P52*L53*K53</f>
         <v>45.959055069271365</v>
       </c>
-      <c r="Q53" s="106"/>
-      <c r="R53" s="127">
+      <c r="Q53" s="94"/>
+      <c r="R53" s="98">
         <f t="shared" ca="1" si="17"/>
         <v>6.9304622290344788</v>
       </c>
-      <c r="S53" s="127"/>
+      <c r="S53" s="98"/>
       <c r="T53" s="1"/>
       <c r="U53" s="67"/>
       <c r="V53" s="68"/>
@@ -4441,12 +4441,12 @@
       <c r="Z53" s="1"/>
     </row>
     <row r="54" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B54" s="93" t="s">
+      <c r="B54" s="99" t="s">
         <v>97</v>
       </c>
-      <c r="C54" s="94"/>
-      <c r="D54" s="94"/>
-      <c r="E54" s="94"/>
+      <c r="C54" s="93"/>
+      <c r="D54" s="93"/>
+      <c r="E54" s="93"/>
       <c r="F54" s="44">
         <f>E2*F53/2</f>
         <v>320</v>
@@ -4455,33 +4455,33 @@
         <v>100</v>
       </c>
       <c r="H54" s="16"/>
-      <c r="I54" s="93" t="s">
+      <c r="I54" s="99" t="s">
         <v>95</v>
       </c>
-      <c r="J54" s="94"/>
+      <c r="J54" s="93"/>
       <c r="K54" s="7">
         <f>M6</f>
         <v>0.99</v>
       </c>
-      <c r="L54" s="94">
+      <c r="L54" s="93">
         <v>1</v>
       </c>
-      <c r="M54" s="94"/>
-      <c r="N54" s="130">
+      <c r="M54" s="93"/>
+      <c r="N54" s="96">
         <f>N53/L54</f>
         <v>1440</v>
       </c>
-      <c r="O54" s="130"/>
-      <c r="P54" s="106">
+      <c r="O54" s="96"/>
+      <c r="P54" s="94">
         <f ca="1">P53*L54*K54</f>
         <v>45.499464518578648</v>
       </c>
-      <c r="Q54" s="106"/>
-      <c r="R54" s="127">
+      <c r="Q54" s="94"/>
+      <c r="R54" s="98">
         <f t="shared" ca="1" si="17"/>
         <v>6.8611576067441344</v>
       </c>
-      <c r="S54" s="127"/>
+      <c r="S54" s="98"/>
       <c r="T54" s="1"/>
       <c r="U54" s="67"/>
       <c r="V54" s="68"/>
@@ -4491,12 +4491,12 @@
       <c r="Z54" s="1"/>
     </row>
     <row r="55" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B55" s="93" t="s">
+      <c r="B55" s="99" t="s">
         <v>98</v>
       </c>
-      <c r="C55" s="94"/>
-      <c r="D55" s="94"/>
-      <c r="E55" s="94"/>
+      <c r="C55" s="93"/>
+      <c r="D55" s="93"/>
+      <c r="E55" s="93"/>
       <c r="F55" s="1">
         <f ca="1">F54/F59/F49</f>
         <v>46.89699496864425</v>
@@ -4505,34 +4505,34 @@
         <v>100</v>
       </c>
       <c r="H55" s="16"/>
-      <c r="I55" s="93" t="s">
+      <c r="I55" s="99" t="s">
         <v>94</v>
       </c>
-      <c r="J55" s="94"/>
+      <c r="J55" s="93"/>
       <c r="K55" s="43">
         <f ca="1">Q41</f>
         <v>0.96143805509807656</v>
       </c>
-      <c r="L55" s="106">
+      <c r="L55" s="94">
         <f>F49</f>
         <v>7.5398223686155026</v>
       </c>
-      <c r="M55" s="106"/>
-      <c r="N55" s="106">
+      <c r="M55" s="94"/>
+      <c r="N55" s="94">
         <f>N54/L55</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O55" s="106"/>
-      <c r="P55" s="122">
+      <c r="O55" s="94"/>
+      <c r="P55" s="102">
         <f ca="1">P54*L55*K55</f>
         <v>329.82890125747264</v>
       </c>
-      <c r="Q55" s="122"/>
-      <c r="R55" s="127">
+      <c r="Q55" s="102"/>
+      <c r="R55" s="98">
         <f t="shared" ca="1" si="17"/>
         <v>6.5965780251494532</v>
       </c>
-      <c r="S55" s="127"/>
+      <c r="S55" s="98"/>
       <c r="T55" s="1"/>
       <c r="U55" s="67"/>
       <c r="V55" s="68"/>
@@ -4542,12 +4542,12 @@
       <c r="Z55" s="1"/>
     </row>
     <row r="56" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B56" s="93" t="s">
+      <c r="B56" s="99" t="s">
         <v>99</v>
       </c>
-      <c r="C56" s="94"/>
-      <c r="D56" s="94"/>
-      <c r="E56" s="94"/>
+      <c r="C56" s="93"/>
+      <c r="D56" s="93"/>
+      <c r="E56" s="93"/>
       <c r="F56" s="1">
         <f ca="1">F55*F51/1000</f>
         <v>7.0719002337086527</v>
@@ -4555,109 +4555,109 @@
       <c r="G56" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="I56" s="93" t="s">
+      <c r="I56" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="J56" s="94"/>
+      <c r="J56" s="93"/>
       <c r="K56" s="7">
         <f>M7</f>
         <v>0.98</v>
       </c>
-      <c r="L56" s="94">
+      <c r="L56" s="93">
         <v>1</v>
       </c>
-      <c r="M56" s="94"/>
-      <c r="N56" s="106">
+      <c r="M56" s="93"/>
+      <c r="N56" s="94">
         <f>N55/L56</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O56" s="106"/>
-      <c r="P56" s="122">
+      <c r="O56" s="94"/>
+      <c r="P56" s="102">
         <f ca="1">P55*L56*K56</f>
         <v>323.23232323232315</v>
       </c>
-      <c r="Q56" s="122"/>
-      <c r="R56" s="127">
+      <c r="Q56" s="102"/>
+      <c r="R56" s="98">
         <f t="shared" ca="1" si="17"/>
         <v>6.4646464646464636</v>
       </c>
-      <c r="S56" s="127"/>
+      <c r="S56" s="98"/>
       <c r="T56" s="1"/>
       <c r="U56" s="67"/>
       <c r="V56" s="68"/>
     </row>
     <row r="57" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B57" s="93" t="s">
+      <c r="B57" s="99" t="s">
         <v>102</v>
       </c>
-      <c r="C57" s="94"/>
-      <c r="D57" s="94"/>
-      <c r="E57" s="94"/>
+      <c r="C57" s="93"/>
+      <c r="D57" s="93"/>
+      <c r="E57" s="93"/>
       <c r="F57" s="1">
         <f>Q36</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="G57" s="50"/>
-      <c r="I57" s="93" t="s">
+      <c r="I57" s="99" t="s">
         <v>95</v>
       </c>
-      <c r="J57" s="94"/>
+      <c r="J57" s="93"/>
       <c r="K57" s="7">
         <f>M6</f>
         <v>0.99</v>
       </c>
-      <c r="L57" s="94">
+      <c r="L57" s="93">
         <v>1</v>
       </c>
-      <c r="M57" s="94"/>
-      <c r="N57" s="106">
+      <c r="M57" s="93"/>
+      <c r="N57" s="94">
         <f>N56/L57</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O57" s="106"/>
-      <c r="P57" s="122">
+      <c r="O57" s="94"/>
+      <c r="P57" s="102">
         <f ca="1">P56*L57*K57</f>
         <v>319.99999999999994</v>
       </c>
-      <c r="Q57" s="122"/>
-      <c r="R57" s="127">
+      <c r="Q57" s="102"/>
+      <c r="R57" s="98">
         <f t="shared" ca="1" si="17"/>
         <v>6.3999999999999995</v>
       </c>
-      <c r="S57" s="127"/>
+      <c r="S57" s="98"/>
       <c r="T57" s="1"/>
       <c r="U57" s="67"/>
       <c r="V57" s="68"/>
     </row>
     <row r="58" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B58" s="93" t="s">
+      <c r="B58" s="99" t="s">
         <v>103</v>
       </c>
-      <c r="C58" s="94"/>
-      <c r="D58" s="94"/>
-      <c r="E58" s="94"/>
+      <c r="C58" s="93"/>
+      <c r="D58" s="93"/>
+      <c r="E58" s="93"/>
       <c r="F58" s="44">
         <f>MAX(F57,E8)</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="G58" s="50"/>
-      <c r="I58" s="100" t="s">
+      <c r="I58" s="103" t="s">
         <v>138</v>
       </c>
-      <c r="J58" s="101"/>
+      <c r="J58" s="104"/>
       <c r="K58" s="12"/>
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
-      <c r="N58" s="95">
+      <c r="N58" s="105">
         <f>N57</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O58" s="95"/>
-      <c r="P58" s="124">
+      <c r="O58" s="105"/>
+      <c r="P58" s="106">
         <f ca="1">P57</f>
         <v>319.99999999999994</v>
       </c>
-      <c r="Q58" s="124"/>
+      <c r="Q58" s="106"/>
       <c r="R58" s="4"/>
       <c r="S58" s="4"/>
       <c r="T58" s="16"/>
@@ -4665,12 +4665,12 @@
       <c r="V58" s="16"/>
     </row>
     <row r="59" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B59" s="93" t="s">
+      <c r="B59" s="99" t="s">
         <v>109</v>
       </c>
-      <c r="C59" s="94"/>
-      <c r="D59" s="94"/>
-      <c r="E59" s="94"/>
+      <c r="C59" s="93"/>
+      <c r="D59" s="93"/>
+      <c r="E59" s="93"/>
       <c r="F59" s="1">
         <f ca="1">K57*K55*K56*K54*K53</f>
         <v>0.90499014246468046</v>
@@ -4678,12 +4678,12 @@
       <c r="G59" s="50"/>
     </row>
     <row r="60" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B60" s="93" t="s">
+      <c r="B60" s="99" t="s">
         <v>111</v>
       </c>
-      <c r="C60" s="94"/>
-      <c r="D60" s="94"/>
-      <c r="E60" s="94"/>
+      <c r="C60" s="93"/>
+      <c r="D60" s="93"/>
+      <c r="E60" s="93"/>
       <c r="F60" s="1">
         <f ca="1">F59*K52</f>
         <v>0.78915140422920138</v>
@@ -4691,12 +4691,12 @@
       <c r="G60" s="50"/>
     </row>
     <row r="61" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B61" s="94" t="s">
+      <c r="B61" s="93" t="s">
         <v>137</v>
       </c>
-      <c r="C61" s="94"/>
-      <c r="D61" s="94"/>
-      <c r="E61" s="94"/>
+      <c r="C61" s="93"/>
+      <c r="D61" s="93"/>
+      <c r="E61" s="93"/>
       <c r="F61" s="69">
         <v>38</v>
       </c>
@@ -4723,16 +4723,123 @@
     </row>
   </sheetData>
   <mergeCells count="151">
-    <mergeCell ref="L54:M54"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="L57:M57"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="N56:O56"/>
-    <mergeCell ref="N57:O57"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="S19:V19"/>
+    <mergeCell ref="W19:Z19"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="AC8:AE8"/>
+    <mergeCell ref="AC6:AE6"/>
+    <mergeCell ref="K19:N19"/>
+    <mergeCell ref="AC2:AE2"/>
+    <mergeCell ref="AC3:AE3"/>
+    <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="AC5:AE5"/>
+    <mergeCell ref="AC7:AE7"/>
+    <mergeCell ref="AC10:AE10"/>
+    <mergeCell ref="AC9:AE9"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="Q6:S6"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B56:E56"/>
     <mergeCell ref="R51:S51"/>
     <mergeCell ref="R52:S52"/>
     <mergeCell ref="R53:S53"/>
@@ -4757,123 +4864,16 @@
     <mergeCell ref="L51:M51"/>
     <mergeCell ref="L52:M52"/>
     <mergeCell ref="L53:M53"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="I58:J58"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="Q6:S6"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="G39:J39"/>
-    <mergeCell ref="G38:J38"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="AC8:AE8"/>
-    <mergeCell ref="AC6:AE6"/>
-    <mergeCell ref="K19:N19"/>
-    <mergeCell ref="AC2:AE2"/>
-    <mergeCell ref="AC3:AE3"/>
-    <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="AC5:AE5"/>
-    <mergeCell ref="AC7:AE7"/>
-    <mergeCell ref="AC10:AE10"/>
-    <mergeCell ref="AC9:AE9"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="I4:N4"/>
-    <mergeCell ref="I3:N3"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="S19:V19"/>
-    <mergeCell ref="W19:Z19"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="L54:M54"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="N56:O56"/>
+    <mergeCell ref="N57:O57"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -4902,37 +4902,37 @@
       <c r="A2">
         <v>4</v>
       </c>
-      <c r="E2" s="94" t="s">
+      <c r="E2" s="93" t="s">
         <v>228</v>
       </c>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="118" t="s">
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="126" t="s">
         <v>266</v>
       </c>
-      <c r="K2" s="118"/>
-      <c r="L2" s="118"/>
-      <c r="M2" s="118"/>
-      <c r="N2" s="118"/>
-      <c r="P2" s="118" t="s">
+      <c r="K2" s="126"/>
+      <c r="L2" s="126"/>
+      <c r="M2" s="126"/>
+      <c r="N2" s="126"/>
+      <c r="P2" s="126" t="s">
         <v>267</v>
       </c>
-      <c r="Q2" s="118"/>
-      <c r="R2" s="118"/>
-      <c r="S2" s="118"/>
-      <c r="T2" s="118"/>
+      <c r="Q2" s="126"/>
+      <c r="R2" s="126"/>
+      <c r="S2" s="126"/>
+      <c r="T2" s="126"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>5</v>
       </c>
-      <c r="E3" s="134" t="s">
+      <c r="E3" s="132" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="134"/>
-      <c r="G3" s="134"/>
+      <c r="F3" s="132"/>
+      <c r="G3" s="132"/>
       <c r="H3" s="60">
         <f>Передача!$D$49</f>
         <v>2016</v>
@@ -4957,11 +4957,11 @@
       <c r="A4">
         <v>6</v>
       </c>
-      <c r="E4" s="134" t="s">
+      <c r="E4" s="132" t="s">
         <v>159</v>
       </c>
-      <c r="F4" s="134"/>
-      <c r="G4" s="134"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="132"/>
       <c r="H4" s="60">
         <f>Передача!$D$50</f>
         <v>734</v>
@@ -4972,11 +4972,11 @@
       <c r="J4" t="s">
         <v>23</v>
       </c>
-      <c r="P4" s="118" t="s">
+      <c r="P4" s="126" t="s">
         <v>120</v>
       </c>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118"/>
+      <c r="Q4" s="126"/>
+      <c r="R4" s="126"/>
       <c r="S4">
         <f ca="1">Вал!S15</f>
         <v>45</v>
@@ -4989,11 +4989,11 @@
       <c r="A5">
         <v>7</v>
       </c>
-      <c r="E5" s="134" t="s">
+      <c r="E5" s="132" t="s">
         <v>160</v>
       </c>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
+      <c r="F5" s="132"/>
+      <c r="G5" s="132"/>
       <c r="H5" s="60">
         <f>Передача!$D$51</f>
         <v>0</v>
@@ -5001,11 +5001,11 @@
       <c r="I5" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="126" t="s">
         <v>120</v>
       </c>
-      <c r="K5" s="118"/>
-      <c r="L5" s="118"/>
+      <c r="K5" s="126"/>
+      <c r="L5" s="126"/>
       <c r="M5">
         <f ca="1">Вал!K16</f>
         <v>40</v>
@@ -5277,37 +5277,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="126" t="s">
         <v>274</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118" t="s">
+      <c r="B1" s="126"/>
+      <c r="C1" s="126" t="s">
         <v>184</v>
       </c>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118" t="s">
+      <c r="D1" s="126"/>
+      <c r="E1" s="126" t="s">
         <v>281</v>
       </c>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118" t="s">
+      <c r="F1" s="126"/>
+      <c r="G1" s="126" t="s">
         <v>284</v>
       </c>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
+      <c r="H1" s="126"/>
+      <c r="I1" s="126"/>
+      <c r="J1" s="126"/>
+      <c r="K1" s="126"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="118"/>
-      <c r="B2" s="118"/>
-      <c r="C2" s="118" t="s">
+      <c r="A2" s="126"/>
+      <c r="B2" s="126"/>
+      <c r="C2" s="126" t="s">
         <v>282</v>
       </c>
-      <c r="D2" s="118"/>
-      <c r="E2" s="118" t="s">
+      <c r="D2" s="126"/>
+      <c r="E2" s="126" t="s">
         <v>283</v>
       </c>
-      <c r="F2" s="118"/>
+      <c r="F2" s="126"/>
       <c r="G2" s="91" t="s">
         <v>285</v>
       </c>
@@ -5328,18 +5328,18 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="118" t="s">
+      <c r="A3" s="126" t="s">
         <v>275</v>
       </c>
-      <c r="B3" s="118"/>
-      <c r="C3" s="118">
+      <c r="B3" s="126"/>
+      <c r="C3" s="126">
         <v>1000</v>
       </c>
-      <c r="D3" s="118"/>
-      <c r="E3" s="118">
+      <c r="D3" s="126"/>
+      <c r="E3" s="126">
         <v>190</v>
       </c>
-      <c r="F3" s="118"/>
+      <c r="F3" s="126"/>
       <c r="G3">
         <v>520</v>
       </c>
@@ -5360,18 +5360,18 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="118">
+      <c r="A4" s="126">
         <v>45</v>
       </c>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118">
+      <c r="B4" s="126"/>
+      <c r="C4" s="126">
         <v>120</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118">
+      <c r="D4" s="126"/>
+      <c r="E4" s="126">
         <v>227</v>
       </c>
-      <c r="F4" s="118"/>
+      <c r="F4" s="126"/>
       <c r="G4">
         <v>820</v>
       </c>
@@ -5392,18 +5392,18 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="118">
+      <c r="A5" s="126">
         <v>45</v>
       </c>
-      <c r="B5" s="118"/>
-      <c r="C5" s="118">
+      <c r="B5" s="126"/>
+      <c r="C5" s="126">
         <v>80</v>
       </c>
-      <c r="D5" s="118"/>
-      <c r="E5" s="118">
+      <c r="D5" s="126"/>
+      <c r="E5" s="126">
         <v>260</v>
       </c>
-      <c r="F5" s="118"/>
+      <c r="F5" s="126"/>
       <c r="G5">
         <v>900</v>
       </c>
@@ -5424,18 +5424,18 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="118" t="s">
+      <c r="A6" s="126" t="s">
         <v>276</v>
       </c>
-      <c r="B6" s="118"/>
-      <c r="C6" s="118">
+      <c r="B6" s="126"/>
+      <c r="C6" s="126">
         <v>200</v>
       </c>
-      <c r="D6" s="118"/>
-      <c r="E6" s="118">
+      <c r="D6" s="126"/>
+      <c r="E6" s="126">
         <v>240</v>
       </c>
-      <c r="F6" s="118"/>
+      <c r="F6" s="126"/>
       <c r="G6">
         <v>790</v>
       </c>
@@ -5456,18 +5456,18 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="118" t="s">
+      <c r="A7" s="126" t="s">
         <v>276</v>
       </c>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118">
+      <c r="B7" s="126"/>
+      <c r="C7" s="126">
         <v>120</v>
       </c>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118">
+      <c r="D7" s="126"/>
+      <c r="E7" s="126">
         <v>270</v>
       </c>
-      <c r="F7" s="118"/>
+      <c r="F7" s="126"/>
       <c r="G7">
         <v>980</v>
       </c>
@@ -5488,18 +5488,18 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="118" t="s">
+      <c r="A8" s="126" t="s">
         <v>277</v>
       </c>
-      <c r="B8" s="118"/>
-      <c r="C8" s="118">
+      <c r="B8" s="126"/>
+      <c r="C8" s="126">
         <v>200</v>
       </c>
-      <c r="D8" s="118"/>
-      <c r="E8" s="118">
+      <c r="D8" s="126"/>
+      <c r="E8" s="126">
         <v>270</v>
       </c>
-      <c r="F8" s="118"/>
+      <c r="F8" s="126"/>
       <c r="G8">
         <v>980</v>
       </c>
@@ -5520,18 +5520,18 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="118" t="s">
+      <c r="A9" s="126" t="s">
         <v>278</v>
       </c>
-      <c r="B9" s="118"/>
-      <c r="C9" s="118">
+      <c r="B9" s="126"/>
+      <c r="C9" s="126">
         <v>120</v>
       </c>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118">
+      <c r="D9" s="126"/>
+      <c r="E9" s="126">
         <v>197</v>
       </c>
-      <c r="F9" s="118"/>
+      <c r="F9" s="126"/>
       <c r="G9">
         <v>650</v>
       </c>
@@ -5552,18 +5552,18 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="118" t="s">
+      <c r="A10" s="126" t="s">
         <v>279</v>
       </c>
-      <c r="B10" s="118"/>
-      <c r="C10" s="118">
+      <c r="B10" s="126"/>
+      <c r="C10" s="126">
         <v>120</v>
       </c>
-      <c r="D10" s="118"/>
-      <c r="E10" s="118">
+      <c r="D10" s="126"/>
+      <c r="E10" s="126">
         <v>260</v>
       </c>
-      <c r="F10" s="118"/>
+      <c r="F10" s="126"/>
       <c r="G10">
         <v>930</v>
       </c>
@@ -5584,18 +5584,18 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="118" t="s">
+      <c r="A11" s="126" t="s">
         <v>280</v>
       </c>
-      <c r="B11" s="118"/>
-      <c r="C11" s="118">
+      <c r="B11" s="126"/>
+      <c r="C11" s="126">
         <v>60</v>
       </c>
-      <c r="D11" s="118"/>
-      <c r="E11" s="118">
+      <c r="D11" s="126"/>
+      <c r="E11" s="126">
         <v>330</v>
       </c>
-      <c r="F11" s="118"/>
+      <c r="F11" s="126"/>
       <c r="G11">
         <v>1180</v>
       </c>
@@ -5629,11 +5629,9 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="E3:F3"/>
@@ -5646,12 +5644,17 @@
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="E11:F11"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G1:K1"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C2:D2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
@@ -5659,9 +5662,6 @@
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5676,45 +5676,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="93" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A2" s="93" t="s">
+      <c r="A2" s="99" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94" t="str">
+      <c r="B2" s="93"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93" t="str">
         <f>Электродвигатель!F48</f>
         <v>Цилиндрическая 1</v>
       </c>
-      <c r="F2" s="105"/>
-      <c r="K2" s="97" t="s">
+      <c r="F2" s="110"/>
+      <c r="K2" s="107" t="s">
         <v>152</v>
       </c>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
+      <c r="O2" s="100"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="100"/>
       <c r="R2" s="1"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="94"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
       <c r="E3" s="56">
         <f>Электродвигатель!$F$49</f>
         <v>7.5398223686155026</v>
@@ -5746,12 +5746,12 @@
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A4" s="93" t="s">
+      <c r="A4" s="99" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="94"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="94"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="93"/>
       <c r="E4" s="56">
         <f>Электродвигатель!$F$52</f>
         <v>190.98593171027443</v>
@@ -5786,12 +5786,12 @@
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="99" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="94"/>
-      <c r="D5" s="94"/>
+      <c r="B5" s="93"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
       <c r="E5" s="25">
         <f>Электродвигатель!$F$54</f>
         <v>320</v>
@@ -5826,12 +5826,12 @@
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A6" s="93" t="s">
+      <c r="A6" s="99" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="94"/>
-      <c r="C6" s="94"/>
-      <c r="D6" s="94"/>
+      <c r="B6" s="93"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="93"/>
       <c r="E6" s="25">
         <f>Электродвигатель!$F$58</f>
         <v>2.2000000000000002</v>
@@ -5864,12 +5864,12 @@
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A7" s="118" t="s">
+      <c r="A7" s="126" t="s">
         <v>146</v>
       </c>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
+      <c r="B7" s="126"/>
+      <c r="C7" s="126"/>
+      <c r="D7" s="126"/>
       <c r="E7">
         <f>Электродвигатель!$E$5</f>
         <v>10000</v>
@@ -5904,14 +5904,14 @@
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A8" s="118" t="s">
+      <c r="A8" s="126" t="s">
         <v>140</v>
       </c>
-      <c r="B8" s="118"/>
-      <c r="C8" s="118"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="118"/>
-      <c r="F8" s="118"/>
+      <c r="B8" s="126"/>
+      <c r="C8" s="126"/>
+      <c r="D8" s="126"/>
+      <c r="E8" s="126"/>
+      <c r="F8" s="126"/>
       <c r="K8" s="7">
         <v>5</v>
       </c>
@@ -5943,12 +5943,12 @@
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A9" s="118" t="s">
+      <c r="A9" s="126" t="s">
         <v>145</v>
       </c>
-      <c r="B9" s="118"/>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
+      <c r="B9" s="126"/>
+      <c r="C9" s="126"/>
+      <c r="D9" s="126"/>
       <c r="E9">
         <f>Электродвигатель!$E$15</f>
         <v>300</v>
@@ -5984,12 +5984,12 @@
       <c r="S9" s="54"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A10" s="93" t="s">
+      <c r="A10" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="94"/>
-      <c r="C10" s="94"/>
-      <c r="D10" s="94"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
       <c r="E10" s="16">
         <f>Электродвигатель!$E$7</f>
         <v>3</v>
@@ -6028,12 +6028,12 @@
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A11" s="93" t="s">
+      <c r="A11" s="99" t="s">
         <v>212</v>
       </c>
-      <c r="B11" s="94"/>
-      <c r="C11" s="94"/>
-      <c r="D11" s="94"/>
+      <c r="B11" s="93"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
       <c r="E11" s="47" t="s">
         <v>101</v>
       </c>
@@ -6068,12 +6068,12 @@
       <c r="S11" s="54"/>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A12" s="93" t="s">
+      <c r="A12" s="99" t="s">
         <v>130</v>
       </c>
-      <c r="B12" s="94"/>
-      <c r="C12" s="94"/>
-      <c r="D12" s="94"/>
+      <c r="B12" s="93"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
       <c r="E12" s="55" t="s">
         <v>101</v>
       </c>
@@ -6108,14 +6108,14 @@
       <c r="S12" s="54"/>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A13" s="118" t="s">
+      <c r="A13" s="126" t="s">
         <v>141</v>
       </c>
-      <c r="B13" s="118"/>
-      <c r="C13" s="118"/>
-      <c r="D13" s="118"/>
-      <c r="E13" s="118"/>
-      <c r="F13" s="118"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="126"/>
       <c r="K13" s="7">
         <v>10</v>
       </c>
@@ -6144,12 +6144,12 @@
       <c r="S13" s="54"/>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A14" s="118" t="s">
+      <c r="A14" s="126" t="s">
         <v>144</v>
       </c>
-      <c r="B14" s="118"/>
-      <c r="C14" s="118"/>
-      <c r="D14" s="118"/>
+      <c r="B14" s="126"/>
+      <c r="C14" s="126"/>
+      <c r="D14" s="126"/>
       <c r="E14">
         <f>Вал!$D$6</f>
         <v>38</v>
@@ -6185,12 +6185,12 @@
       <c r="S14" s="54"/>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A15" s="94" t="s">
+      <c r="A15" s="93" t="s">
         <v>142</v>
       </c>
-      <c r="B15" s="94"/>
-      <c r="C15" s="94"/>
-      <c r="D15" s="94"/>
+      <c r="B15" s="93"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="93"/>
       <c r="E15">
         <f ca="1">Вал!$K$19</f>
         <v>45</v>
@@ -6225,12 +6225,12 @@
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A16" s="94" t="s">
+      <c r="A16" s="93" t="s">
         <v>143</v>
       </c>
-      <c r="B16" s="94"/>
-      <c r="C16" s="94"/>
-      <c r="D16" s="94"/>
+      <c r="B16" s="93"/>
+      <c r="C16" s="93"/>
+      <c r="D16" s="93"/>
       <c r="E16">
         <f ca="1">Вал!$S$18</f>
         <v>50</v>
@@ -6275,12 +6275,12 @@
       <c r="Z18" s="84"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G19" s="133" t="s">
+      <c r="G19" s="131" t="s">
         <v>151</v>
       </c>
-      <c r="H19" s="134"/>
-      <c r="I19" s="134"/>
-      <c r="J19" s="134"/>
+      <c r="H19" s="132"/>
+      <c r="I19" s="132"/>
+      <c r="J19" s="132"/>
       <c r="K19" s="78">
         <v>69</v>
       </c>
@@ -6288,12 +6288,12 @@
         <v>158</v>
       </c>
       <c r="M19" s="77"/>
-      <c r="N19" s="133" t="s">
+      <c r="N19" s="131" t="s">
         <v>151</v>
       </c>
-      <c r="O19" s="134"/>
-      <c r="P19" s="134"/>
-      <c r="Q19" s="134"/>
+      <c r="O19" s="132"/>
+      <c r="P19" s="132"/>
+      <c r="Q19" s="132"/>
       <c r="R19" s="78">
         <v>57</v>
       </c>
@@ -6301,12 +6301,12 @@
         <v>158</v>
       </c>
       <c r="T19" s="77"/>
-      <c r="U19" s="133" t="s">
+      <c r="U19" s="131" t="s">
         <v>151</v>
       </c>
-      <c r="V19" s="134"/>
-      <c r="W19" s="134"/>
-      <c r="X19" s="134"/>
+      <c r="V19" s="132"/>
+      <c r="W19" s="132"/>
+      <c r="X19" s="132"/>
       <c r="Y19" s="78">
         <v>64</v>
       </c>
@@ -6315,12 +6315,12 @@
       </c>
     </row>
     <row r="20" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G20" s="133" t="s">
+      <c r="G20" s="131" t="s">
         <v>156</v>
       </c>
-      <c r="H20" s="134"/>
-      <c r="I20" s="134"/>
-      <c r="J20" s="134"/>
+      <c r="H20" s="132"/>
+      <c r="I20" s="132"/>
+      <c r="J20" s="132"/>
       <c r="K20" s="75">
         <v>22.3</v>
       </c>
@@ -6328,12 +6328,12 @@
         <v>158</v>
       </c>
       <c r="M20" s="77"/>
-      <c r="N20" s="133" t="s">
+      <c r="N20" s="131" t="s">
         <v>156</v>
       </c>
-      <c r="O20" s="134"/>
-      <c r="P20" s="134"/>
-      <c r="Q20" s="134"/>
+      <c r="O20" s="132"/>
+      <c r="P20" s="132"/>
+      <c r="Q20" s="132"/>
       <c r="R20" s="75">
         <v>20</v>
       </c>
@@ -6341,12 +6341,12 @@
         <v>158</v>
       </c>
       <c r="T20" s="77"/>
-      <c r="U20" s="133" t="s">
+      <c r="U20" s="131" t="s">
         <v>156</v>
       </c>
-      <c r="V20" s="134"/>
-      <c r="W20" s="134"/>
-      <c r="X20" s="134"/>
+      <c r="V20" s="132"/>
+      <c r="W20" s="132"/>
+      <c r="X20" s="132"/>
       <c r="Y20" s="75">
         <v>25.3</v>
       </c>
@@ -6355,12 +6355,12 @@
       </c>
     </row>
     <row r="21" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G21" s="133" t="s">
+      <c r="G21" s="131" t="s">
         <v>148</v>
       </c>
-      <c r="H21" s="134"/>
-      <c r="I21" s="134"/>
-      <c r="J21" s="134"/>
+      <c r="H21" s="132"/>
+      <c r="I21" s="132"/>
+      <c r="J21" s="132"/>
       <c r="K21" s="75">
         <v>240</v>
       </c>
@@ -6368,12 +6368,12 @@
         <v>16</v>
       </c>
       <c r="M21" s="77"/>
-      <c r="N21" s="133" t="s">
+      <c r="N21" s="131" t="s">
         <v>148</v>
       </c>
-      <c r="O21" s="134"/>
-      <c r="P21" s="134"/>
-      <c r="Q21" s="134"/>
+      <c r="O21" s="132"/>
+      <c r="P21" s="132"/>
+      <c r="Q21" s="132"/>
       <c r="R21" s="75">
         <v>180</v>
       </c>
@@ -6381,12 +6381,12 @@
         <v>16</v>
       </c>
       <c r="T21" s="77"/>
-      <c r="U21" s="133" t="s">
+      <c r="U21" s="131" t="s">
         <v>148</v>
       </c>
-      <c r="V21" s="134"/>
-      <c r="W21" s="134"/>
-      <c r="X21" s="134"/>
+      <c r="V21" s="132"/>
+      <c r="W21" s="132"/>
+      <c r="X21" s="132"/>
       <c r="Y21" s="75">
         <v>180</v>
       </c>
@@ -6395,12 +6395,12 @@
       </c>
     </row>
     <row r="22" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G22" s="133" t="s">
+      <c r="G22" s="131" t="s">
         <v>157</v>
       </c>
-      <c r="H22" s="134"/>
-      <c r="I22" s="134"/>
-      <c r="J22" s="134"/>
+      <c r="H22" s="132"/>
+      <c r="I22" s="132"/>
+      <c r="J22" s="132"/>
       <c r="K22" s="75">
         <v>3.5</v>
       </c>
@@ -6408,12 +6408,12 @@
         <v>16</v>
       </c>
       <c r="M22" s="77"/>
-      <c r="N22" s="133" t="s">
+      <c r="N22" s="131" t="s">
         <v>157</v>
       </c>
-      <c r="O22" s="134"/>
-      <c r="P22" s="134"/>
-      <c r="Q22" s="134"/>
+      <c r="O22" s="132"/>
+      <c r="P22" s="132"/>
+      <c r="Q22" s="132"/>
       <c r="R22" s="75">
         <v>2.5</v>
       </c>
@@ -6421,12 +6421,12 @@
         <v>16</v>
       </c>
       <c r="T22" s="77"/>
-      <c r="U22" s="133" t="s">
+      <c r="U22" s="131" t="s">
         <v>157</v>
       </c>
-      <c r="V22" s="134"/>
-      <c r="W22" s="134"/>
-      <c r="X22" s="134"/>
+      <c r="V22" s="132"/>
+      <c r="W22" s="132"/>
+      <c r="X22" s="132"/>
       <c r="Y22" s="75">
         <v>3</v>
       </c>
@@ -6435,12 +6435,12 @@
       </c>
     </row>
     <row r="23" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G23" s="133" t="s">
+      <c r="G23" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="H23" s="134"/>
-      <c r="I23" s="134"/>
-      <c r="J23" s="134"/>
+      <c r="H23" s="132"/>
+      <c r="I23" s="132"/>
+      <c r="J23" s="132"/>
       <c r="K23" s="75">
         <v>1510</v>
       </c>
@@ -6448,12 +6448,12 @@
         <v>161</v>
       </c>
       <c r="M23" s="77"/>
-      <c r="N23" s="133" t="s">
+      <c r="N23" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="O23" s="134"/>
-      <c r="P23" s="134"/>
-      <c r="Q23" s="134"/>
+      <c r="O23" s="132"/>
+      <c r="P23" s="132"/>
+      <c r="Q23" s="132"/>
       <c r="R23" s="75">
         <v>2016</v>
       </c>
@@ -6461,12 +6461,12 @@
         <v>161</v>
       </c>
       <c r="T23" s="77"/>
-      <c r="U23" s="133" t="s">
+      <c r="U23" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="V23" s="134"/>
-      <c r="W23" s="134"/>
-      <c r="X23" s="134"/>
+      <c r="V23" s="132"/>
+      <c r="W23" s="132"/>
+      <c r="X23" s="132"/>
       <c r="Y23" s="75">
         <v>2013</v>
       </c>
@@ -6475,12 +6475,12 @@
       </c>
     </row>
     <row r="24" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G24" s="133" t="s">
+      <c r="G24" s="131" t="s">
         <v>159</v>
       </c>
-      <c r="H24" s="134"/>
-      <c r="I24" s="134"/>
-      <c r="J24" s="134"/>
+      <c r="H24" s="132"/>
+      <c r="I24" s="132"/>
+      <c r="J24" s="132"/>
       <c r="K24" s="75">
         <v>554</v>
       </c>
@@ -6488,12 +6488,12 @@
         <v>161</v>
       </c>
       <c r="M24" s="77"/>
-      <c r="N24" s="133" t="s">
+      <c r="N24" s="131" t="s">
         <v>159</v>
       </c>
-      <c r="O24" s="134"/>
-      <c r="P24" s="134"/>
-      <c r="Q24" s="134"/>
+      <c r="O24" s="132"/>
+      <c r="P24" s="132"/>
+      <c r="Q24" s="132"/>
       <c r="R24" s="75">
         <v>734</v>
       </c>
@@ -6501,12 +6501,12 @@
         <v>161</v>
       </c>
       <c r="T24" s="77"/>
-      <c r="U24" s="133" t="s">
+      <c r="U24" s="131" t="s">
         <v>159</v>
       </c>
-      <c r="V24" s="134"/>
-      <c r="W24" s="134"/>
-      <c r="X24" s="134"/>
+      <c r="V24" s="132"/>
+      <c r="W24" s="132"/>
+      <c r="X24" s="132"/>
       <c r="Y24" s="75">
         <v>733</v>
       </c>
@@ -6515,12 +6515,12 @@
       </c>
     </row>
     <row r="25" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G25" s="131" t="s">
+      <c r="G25" s="133" t="s">
         <v>160</v>
       </c>
-      <c r="H25" s="132"/>
-      <c r="I25" s="132"/>
-      <c r="J25" s="132"/>
+      <c r="H25" s="134"/>
+      <c r="I25" s="134"/>
+      <c r="J25" s="134"/>
       <c r="K25" s="80">
         <v>0</v>
       </c>
@@ -6528,12 +6528,12 @@
         <v>161</v>
       </c>
       <c r="M25" s="77"/>
-      <c r="N25" s="131" t="s">
+      <c r="N25" s="133" t="s">
         <v>160</v>
       </c>
-      <c r="O25" s="132"/>
-      <c r="P25" s="132"/>
-      <c r="Q25" s="132"/>
+      <c r="O25" s="134"/>
+      <c r="P25" s="134"/>
+      <c r="Q25" s="134"/>
       <c r="R25" s="80">
         <v>0</v>
       </c>
@@ -6541,12 +6541,12 @@
         <v>161</v>
       </c>
       <c r="T25" s="77"/>
-      <c r="U25" s="131" t="s">
+      <c r="U25" s="133" t="s">
         <v>160</v>
       </c>
-      <c r="V25" s="132"/>
-      <c r="W25" s="132"/>
-      <c r="X25" s="132"/>
+      <c r="V25" s="134"/>
+      <c r="W25" s="134"/>
+      <c r="X25" s="134"/>
       <c r="Y25" s="80">
         <v>0</v>
       </c>
@@ -6555,74 +6555,74 @@
       </c>
     </row>
     <row r="26" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G26" s="142" t="s">
+      <c r="G26" s="135" t="s">
         <v>163</v>
       </c>
-      <c r="H26" s="143"/>
-      <c r="I26" s="143"/>
-      <c r="J26" s="143"/>
-      <c r="K26" s="143"/>
-      <c r="L26" s="144"/>
+      <c r="H26" s="136"/>
+      <c r="I26" s="136"/>
+      <c r="J26" s="136"/>
+      <c r="K26" s="136"/>
+      <c r="L26" s="137"/>
       <c r="M26" s="77"/>
-      <c r="N26" s="142" t="s">
+      <c r="N26" s="135" t="s">
         <v>163</v>
       </c>
-      <c r="O26" s="143"/>
-      <c r="P26" s="143"/>
-      <c r="Q26" s="143"/>
-      <c r="R26" s="143"/>
-      <c r="S26" s="144"/>
+      <c r="O26" s="136"/>
+      <c r="P26" s="136"/>
+      <c r="Q26" s="136"/>
+      <c r="R26" s="136"/>
+      <c r="S26" s="137"/>
       <c r="T26" s="77"/>
-      <c r="U26" s="142" t="s">
+      <c r="U26" s="135" t="s">
         <v>163</v>
       </c>
-      <c r="V26" s="143"/>
-      <c r="W26" s="143"/>
-      <c r="X26" s="143"/>
-      <c r="Y26" s="143"/>
-      <c r="Z26" s="144"/>
+      <c r="V26" s="136"/>
+      <c r="W26" s="136"/>
+      <c r="X26" s="136"/>
+      <c r="Y26" s="136"/>
+      <c r="Z26" s="137"/>
     </row>
     <row r="27" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G27" s="133" t="s">
+      <c r="G27" s="131" t="s">
         <v>164</v>
       </c>
-      <c r="H27" s="134"/>
-      <c r="I27" s="134"/>
-      <c r="J27" s="134"/>
+      <c r="H27" s="132"/>
+      <c r="I27" s="132"/>
+      <c r="J27" s="132"/>
       <c r="K27" s="87">
         <v>16</v>
       </c>
       <c r="L27" s="76"/>
       <c r="M27" s="77"/>
-      <c r="N27" s="133" t="s">
+      <c r="N27" s="131" t="s">
         <v>164</v>
       </c>
-      <c r="O27" s="134"/>
-      <c r="P27" s="134"/>
-      <c r="Q27" s="134"/>
+      <c r="O27" s="132"/>
+      <c r="P27" s="132"/>
+      <c r="Q27" s="132"/>
       <c r="R27" s="87">
         <v>17</v>
       </c>
       <c r="S27" s="76"/>
       <c r="T27" s="77"/>
-      <c r="U27" s="133" t="s">
+      <c r="U27" s="131" t="s">
         <v>164</v>
       </c>
-      <c r="V27" s="134"/>
-      <c r="W27" s="134"/>
-      <c r="X27" s="134"/>
+      <c r="V27" s="132"/>
+      <c r="W27" s="132"/>
+      <c r="X27" s="132"/>
       <c r="Y27" s="87">
         <v>14</v>
       </c>
       <c r="Z27" s="76"/>
     </row>
     <row r="28" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G28" s="135" t="s">
+      <c r="G28" s="138" t="s">
         <v>169</v>
       </c>
-      <c r="H28" s="136"/>
-      <c r="I28" s="136"/>
-      <c r="J28" s="136"/>
+      <c r="H28" s="139"/>
+      <c r="I28" s="139"/>
+      <c r="J28" s="139"/>
       <c r="K28" s="87">
         <v>0.3</v>
       </c>
@@ -6630,12 +6630,12 @@
         <v>16</v>
       </c>
       <c r="M28" s="77"/>
-      <c r="N28" s="135" t="s">
+      <c r="N28" s="138" t="s">
         <v>169</v>
       </c>
-      <c r="O28" s="136"/>
-      <c r="P28" s="136"/>
-      <c r="Q28" s="136"/>
+      <c r="O28" s="139"/>
+      <c r="P28" s="139"/>
+      <c r="Q28" s="139"/>
       <c r="R28" s="87">
         <v>-0.3</v>
       </c>
@@ -6643,12 +6643,12 @@
         <v>16</v>
       </c>
       <c r="T28" s="77"/>
-      <c r="U28" s="135" t="s">
+      <c r="U28" s="138" t="s">
         <v>169</v>
       </c>
-      <c r="V28" s="136"/>
-      <c r="W28" s="136"/>
-      <c r="X28" s="136"/>
+      <c r="V28" s="139"/>
+      <c r="W28" s="139"/>
+      <c r="X28" s="139"/>
       <c r="Y28" s="87">
         <v>0.3</v>
       </c>
@@ -6657,12 +6657,12 @@
       </c>
     </row>
     <row r="29" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G29" s="135" t="s">
+      <c r="G29" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="H29" s="136"/>
-      <c r="I29" s="136"/>
-      <c r="J29" s="136"/>
+      <c r="H29" s="139"/>
+      <c r="I29" s="139"/>
+      <c r="J29" s="139"/>
       <c r="K29" s="87">
         <v>49</v>
       </c>
@@ -6670,12 +6670,12 @@
         <v>271</v>
       </c>
       <c r="M29" s="77"/>
-      <c r="N29" s="135" t="s">
+      <c r="N29" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="O29" s="136"/>
-      <c r="P29" s="136"/>
-      <c r="Q29" s="136"/>
+      <c r="O29" s="139"/>
+      <c r="P29" s="139"/>
+      <c r="Q29" s="139"/>
       <c r="R29" s="87">
         <v>49</v>
       </c>
@@ -6683,12 +6683,12 @@
         <v>271</v>
       </c>
       <c r="T29" s="77"/>
-      <c r="U29" s="135" t="s">
+      <c r="U29" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="V29" s="136"/>
-      <c r="W29" s="136"/>
-      <c r="X29" s="136"/>
+      <c r="V29" s="139"/>
+      <c r="W29" s="139"/>
+      <c r="X29" s="139"/>
       <c r="Y29" s="87">
         <v>49</v>
       </c>
@@ -6697,34 +6697,34 @@
       </c>
     </row>
     <row r="30" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G30" s="135" t="s">
+      <c r="G30" s="138" t="s">
         <v>170</v>
       </c>
-      <c r="H30" s="136"/>
-      <c r="I30" s="136"/>
-      <c r="J30" s="136"/>
+      <c r="H30" s="139"/>
+      <c r="I30" s="139"/>
+      <c r="J30" s="139"/>
       <c r="K30" s="87" t="s">
         <v>171</v>
       </c>
       <c r="L30" s="76"/>
       <c r="M30" s="77"/>
-      <c r="N30" s="135" t="s">
+      <c r="N30" s="138" t="s">
         <v>170</v>
       </c>
-      <c r="O30" s="136"/>
-      <c r="P30" s="136"/>
-      <c r="Q30" s="136"/>
+      <c r="O30" s="139"/>
+      <c r="P30" s="139"/>
+      <c r="Q30" s="139"/>
       <c r="R30" s="87" t="s">
         <v>171</v>
       </c>
       <c r="S30" s="76"/>
       <c r="T30" s="77"/>
-      <c r="U30" s="135" t="s">
+      <c r="U30" s="138" t="s">
         <v>170</v>
       </c>
-      <c r="V30" s="136"/>
-      <c r="W30" s="136"/>
-      <c r="X30" s="136"/>
+      <c r="V30" s="139"/>
+      <c r="W30" s="139"/>
+      <c r="X30" s="139"/>
       <c r="Y30" s="87" t="s">
         <v>171</v>
       </c>
@@ -6732,12 +6732,12 @@
     </row>
     <row r="31" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B31" s="86"/>
-      <c r="G31" s="133" t="s">
+      <c r="G31" s="131" t="s">
         <v>216</v>
       </c>
-      <c r="H31" s="134"/>
-      <c r="I31" s="134"/>
-      <c r="J31" s="134"/>
+      <c r="H31" s="132"/>
+      <c r="I31" s="132"/>
+      <c r="J31" s="132"/>
       <c r="K31" s="87">
         <v>56</v>
       </c>
@@ -6745,12 +6745,12 @@
         <v>16</v>
       </c>
       <c r="M31" s="77"/>
-      <c r="N31" s="133" t="s">
+      <c r="N31" s="131" t="s">
         <v>216</v>
       </c>
-      <c r="O31" s="134"/>
-      <c r="P31" s="134"/>
-      <c r="Q31" s="134"/>
+      <c r="O31" s="132"/>
+      <c r="P31" s="132"/>
+      <c r="Q31" s="132"/>
       <c r="R31" s="87">
         <v>42.5</v>
       </c>
@@ -6758,12 +6758,12 @@
         <v>16</v>
       </c>
       <c r="T31" s="77"/>
-      <c r="U31" s="133" t="s">
+      <c r="U31" s="131" t="s">
         <v>216</v>
       </c>
-      <c r="V31" s="134"/>
-      <c r="W31" s="134"/>
-      <c r="X31" s="134"/>
+      <c r="V31" s="132"/>
+      <c r="W31" s="132"/>
+      <c r="X31" s="132"/>
       <c r="Y31" s="87">
         <v>42</v>
       </c>
@@ -6772,12 +6772,12 @@
       </c>
     </row>
     <row r="32" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G32" s="133" t="s">
+      <c r="G32" s="131" t="s">
         <v>186</v>
       </c>
-      <c r="H32" s="134"/>
-      <c r="I32" s="134"/>
-      <c r="J32" s="134"/>
+      <c r="H32" s="132"/>
+      <c r="I32" s="132"/>
+      <c r="J32" s="132"/>
       <c r="K32" s="87">
         <v>65</v>
       </c>
@@ -6785,12 +6785,12 @@
         <v>16</v>
       </c>
       <c r="M32" s="77"/>
-      <c r="N32" s="133" t="s">
+      <c r="N32" s="131" t="s">
         <v>186</v>
       </c>
-      <c r="O32" s="134"/>
-      <c r="P32" s="134"/>
-      <c r="Q32" s="134"/>
+      <c r="O32" s="132"/>
+      <c r="P32" s="132"/>
+      <c r="Q32" s="132"/>
       <c r="R32" s="87">
         <v>49</v>
       </c>
@@ -6798,12 +6798,12 @@
         <v>16</v>
       </c>
       <c r="T32" s="77"/>
-      <c r="U32" s="133" t="s">
+      <c r="U32" s="131" t="s">
         <v>186</v>
       </c>
-      <c r="V32" s="134"/>
-      <c r="W32" s="134"/>
-      <c r="X32" s="134"/>
+      <c r="V32" s="132"/>
+      <c r="W32" s="132"/>
+      <c r="X32" s="132"/>
       <c r="Y32" s="87">
         <v>49.8</v>
       </c>
@@ -6812,12 +6812,12 @@
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G33" s="133" t="s">
+      <c r="G33" s="131" t="s">
         <v>177</v>
       </c>
-      <c r="H33" s="134"/>
-      <c r="I33" s="134"/>
-      <c r="J33" s="134"/>
+      <c r="H33" s="132"/>
+      <c r="I33" s="132"/>
+      <c r="J33" s="132"/>
       <c r="K33" s="87">
         <v>49.35</v>
       </c>
@@ -6825,12 +6825,12 @@
         <v>16</v>
       </c>
       <c r="M33" s="77"/>
-      <c r="N33" s="133" t="s">
+      <c r="N33" s="131" t="s">
         <v>177</v>
       </c>
-      <c r="O33" s="134"/>
-      <c r="P33" s="134"/>
-      <c r="Q33" s="134"/>
+      <c r="O33" s="132"/>
+      <c r="P33" s="132"/>
+      <c r="Q33" s="132"/>
       <c r="R33" s="87">
         <v>37.75</v>
       </c>
@@ -6838,12 +6838,12 @@
         <v>16</v>
       </c>
       <c r="T33" s="77"/>
-      <c r="U33" s="133" t="s">
+      <c r="U33" s="131" t="s">
         <v>177</v>
       </c>
-      <c r="V33" s="134"/>
-      <c r="W33" s="134"/>
-      <c r="X33" s="134"/>
+      <c r="V33" s="132"/>
+      <c r="W33" s="132"/>
+      <c r="X33" s="132"/>
       <c r="Y33" s="87">
         <v>36.6</v>
       </c>
@@ -6852,12 +6852,12 @@
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G34" s="133" t="s">
+      <c r="G34" s="131" t="s">
         <v>167</v>
       </c>
-      <c r="H34" s="134"/>
-      <c r="I34" s="134"/>
-      <c r="J34" s="134"/>
+      <c r="H34" s="132"/>
+      <c r="I34" s="132"/>
+      <c r="J34" s="132"/>
       <c r="K34" s="87">
         <v>40</v>
       </c>
@@ -6865,12 +6865,12 @@
         <v>16</v>
       </c>
       <c r="M34" s="77"/>
-      <c r="N34" s="133" t="s">
+      <c r="N34" s="131" t="s">
         <v>167</v>
       </c>
-      <c r="O34" s="134"/>
-      <c r="P34" s="134"/>
-      <c r="Q34" s="134"/>
+      <c r="O34" s="132"/>
+      <c r="P34" s="132"/>
+      <c r="Q34" s="132"/>
       <c r="R34" s="87">
         <v>62</v>
       </c>
@@ -6878,12 +6878,12 @@
         <v>16</v>
       </c>
       <c r="T34" s="77"/>
-      <c r="U34" s="131" t="s">
+      <c r="U34" s="133" t="s">
         <v>167</v>
       </c>
-      <c r="V34" s="132"/>
-      <c r="W34" s="132"/>
-      <c r="X34" s="132"/>
+      <c r="V34" s="134"/>
+      <c r="W34" s="134"/>
+      <c r="X34" s="134"/>
       <c r="Y34" s="87">
         <v>79</v>
       </c>
@@ -6892,74 +6892,74 @@
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G35" s="142" t="s">
+      <c r="G35" s="135" t="s">
         <v>126</v>
       </c>
-      <c r="H35" s="143"/>
-      <c r="I35" s="143"/>
-      <c r="J35" s="143"/>
-      <c r="K35" s="143"/>
-      <c r="L35" s="144"/>
+      <c r="H35" s="136"/>
+      <c r="I35" s="136"/>
+      <c r="J35" s="136"/>
+      <c r="K35" s="136"/>
+      <c r="L35" s="137"/>
       <c r="M35" s="77"/>
-      <c r="N35" s="142" t="s">
+      <c r="N35" s="135" t="s">
         <v>126</v>
       </c>
-      <c r="O35" s="143"/>
-      <c r="P35" s="143"/>
-      <c r="Q35" s="143"/>
-      <c r="R35" s="143"/>
-      <c r="S35" s="144"/>
+      <c r="O35" s="136"/>
+      <c r="P35" s="136"/>
+      <c r="Q35" s="136"/>
+      <c r="R35" s="136"/>
+      <c r="S35" s="137"/>
       <c r="T35" s="77"/>
-      <c r="U35" s="142" t="s">
+      <c r="U35" s="135" t="s">
         <v>126</v>
       </c>
-      <c r="V35" s="143"/>
-      <c r="W35" s="143"/>
-      <c r="X35" s="143"/>
-      <c r="Y35" s="143"/>
-      <c r="Z35" s="144"/>
+      <c r="V35" s="136"/>
+      <c r="W35" s="136"/>
+      <c r="X35" s="136"/>
+      <c r="Y35" s="136"/>
+      <c r="Z35" s="137"/>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G36" s="133" t="s">
+      <c r="G36" s="131" t="s">
         <v>164</v>
       </c>
-      <c r="H36" s="134"/>
-      <c r="I36" s="134"/>
-      <c r="J36" s="134"/>
+      <c r="H36" s="132"/>
+      <c r="I36" s="132"/>
+      <c r="J36" s="132"/>
       <c r="K36" s="87">
         <v>121</v>
       </c>
       <c r="L36" s="76"/>
       <c r="M36" s="77"/>
-      <c r="N36" s="133" t="s">
+      <c r="N36" s="131" t="s">
         <v>164</v>
       </c>
-      <c r="O36" s="134"/>
-      <c r="P36" s="134"/>
-      <c r="Q36" s="134"/>
+      <c r="O36" s="132"/>
+      <c r="P36" s="132"/>
+      <c r="Q36" s="132"/>
       <c r="R36" s="87">
         <v>127</v>
       </c>
       <c r="S36" s="76"/>
       <c r="T36" s="77"/>
-      <c r="U36" s="133" t="s">
+      <c r="U36" s="131" t="s">
         <v>164</v>
       </c>
-      <c r="V36" s="134"/>
-      <c r="W36" s="134"/>
-      <c r="X36" s="134"/>
+      <c r="V36" s="132"/>
+      <c r="W36" s="132"/>
+      <c r="X36" s="132"/>
       <c r="Y36" s="87">
         <v>106</v>
       </c>
       <c r="Z36" s="76"/>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G37" s="135" t="s">
+      <c r="G37" s="138" t="s">
         <v>169</v>
       </c>
-      <c r="H37" s="136"/>
-      <c r="I37" s="136"/>
-      <c r="J37" s="136"/>
+      <c r="H37" s="139"/>
+      <c r="I37" s="139"/>
+      <c r="J37" s="139"/>
       <c r="K37" s="87">
         <v>-0.22800000000000001</v>
       </c>
@@ -6967,12 +6967,12 @@
         <v>16</v>
       </c>
       <c r="M37" s="88"/>
-      <c r="N37" s="135" t="s">
+      <c r="N37" s="138" t="s">
         <v>169</v>
       </c>
-      <c r="O37" s="136"/>
-      <c r="P37" s="136"/>
-      <c r="Q37" s="136"/>
+      <c r="O37" s="139"/>
+      <c r="P37" s="139"/>
+      <c r="Q37" s="139"/>
       <c r="R37" s="87">
         <v>0.3</v>
       </c>
@@ -6980,12 +6980,12 @@
         <v>16</v>
       </c>
       <c r="T37" s="88"/>
-      <c r="U37" s="135" t="s">
+      <c r="U37" s="138" t="s">
         <v>169</v>
       </c>
-      <c r="V37" s="136"/>
-      <c r="W37" s="136"/>
-      <c r="X37" s="136"/>
+      <c r="V37" s="139"/>
+      <c r="W37" s="139"/>
+      <c r="X37" s="139"/>
       <c r="Y37" s="87">
         <v>-0.3</v>
       </c>
@@ -6994,12 +6994,12 @@
       </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G38" s="135" t="s">
+      <c r="G38" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="H38" s="136"/>
-      <c r="I38" s="136"/>
-      <c r="J38" s="136"/>
+      <c r="H38" s="139"/>
+      <c r="I38" s="139"/>
+      <c r="J38" s="139"/>
       <c r="K38" s="87">
         <v>28.5</v>
       </c>
@@ -7007,12 +7007,12 @@
         <v>271</v>
       </c>
       <c r="M38" s="77"/>
-      <c r="N38" s="135" t="s">
+      <c r="N38" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="O38" s="136"/>
-      <c r="P38" s="136"/>
-      <c r="Q38" s="136"/>
+      <c r="O38" s="139"/>
+      <c r="P38" s="139"/>
+      <c r="Q38" s="139"/>
       <c r="R38" s="87">
         <v>28.5</v>
       </c>
@@ -7020,12 +7020,12 @@
         <v>271</v>
       </c>
       <c r="T38" s="77"/>
-      <c r="U38" s="135" t="s">
+      <c r="U38" s="138" t="s">
         <v>168</v>
       </c>
-      <c r="V38" s="136"/>
-      <c r="W38" s="136"/>
-      <c r="X38" s="136"/>
+      <c r="V38" s="139"/>
+      <c r="W38" s="139"/>
+      <c r="X38" s="139"/>
       <c r="Y38" s="87">
         <v>28.5</v>
       </c>
@@ -7034,34 +7034,34 @@
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G39" s="135" t="s">
+      <c r="G39" s="138" t="s">
         <v>170</v>
       </c>
-      <c r="H39" s="136"/>
-      <c r="I39" s="136"/>
-      <c r="J39" s="136"/>
+      <c r="H39" s="139"/>
+      <c r="I39" s="139"/>
+      <c r="J39" s="139"/>
       <c r="K39" s="87" t="s">
         <v>172</v>
       </c>
       <c r="L39" s="76"/>
       <c r="M39" s="77"/>
-      <c r="N39" s="135" t="s">
+      <c r="N39" s="138" t="s">
         <v>170</v>
       </c>
-      <c r="O39" s="136"/>
-      <c r="P39" s="136"/>
-      <c r="Q39" s="136"/>
+      <c r="O39" s="139"/>
+      <c r="P39" s="139"/>
+      <c r="Q39" s="139"/>
       <c r="R39" s="87" t="s">
         <v>172</v>
       </c>
       <c r="S39" s="76"/>
       <c r="T39" s="77"/>
-      <c r="U39" s="135" t="s">
+      <c r="U39" s="138" t="s">
         <v>170</v>
       </c>
-      <c r="V39" s="136"/>
-      <c r="W39" s="136"/>
-      <c r="X39" s="136"/>
+      <c r="V39" s="139"/>
+      <c r="W39" s="139"/>
+      <c r="X39" s="139"/>
       <c r="Y39" s="87" t="s">
         <v>172</v>
       </c>
@@ -7069,12 +7069,12 @@
       <c r="AA39" s="86"/>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G40" s="133" t="s">
+      <c r="G40" s="131" t="s">
         <v>216</v>
       </c>
-      <c r="H40" s="134"/>
-      <c r="I40" s="134"/>
-      <c r="J40" s="134"/>
+      <c r="H40" s="132"/>
+      <c r="I40" s="132"/>
+      <c r="J40" s="132"/>
       <c r="K40" s="87">
         <v>423.5</v>
       </c>
@@ -7082,12 +7082,12 @@
         <v>16</v>
       </c>
       <c r="M40" s="77"/>
-      <c r="N40" s="133" t="s">
+      <c r="N40" s="131" t="s">
         <v>216</v>
       </c>
-      <c r="O40" s="134"/>
-      <c r="P40" s="134"/>
-      <c r="Q40" s="134"/>
+      <c r="O40" s="132"/>
+      <c r="P40" s="132"/>
+      <c r="Q40" s="132"/>
       <c r="R40" s="87">
         <v>317.5</v>
       </c>
@@ -7095,12 +7095,12 @@
         <v>16</v>
       </c>
       <c r="T40" s="77"/>
-      <c r="U40" s="133" t="s">
+      <c r="U40" s="131" t="s">
         <v>216</v>
       </c>
-      <c r="V40" s="134"/>
-      <c r="W40" s="134"/>
-      <c r="X40" s="134"/>
+      <c r="V40" s="132"/>
+      <c r="W40" s="132"/>
+      <c r="X40" s="132"/>
       <c r="Y40" s="87">
         <v>318</v>
       </c>
@@ -7110,12 +7110,12 @@
       <c r="AA40" s="86"/>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G41" s="133" t="s">
+      <c r="G41" s="131" t="s">
         <v>186</v>
       </c>
-      <c r="H41" s="134"/>
-      <c r="I41" s="134"/>
-      <c r="J41" s="134"/>
+      <c r="H41" s="132"/>
+      <c r="I41" s="132"/>
+      <c r="J41" s="132"/>
       <c r="K41" s="87">
         <v>428.9</v>
       </c>
@@ -7123,12 +7123,12 @@
         <v>16</v>
       </c>
       <c r="M41" s="77"/>
-      <c r="N41" s="133" t="s">
+      <c r="N41" s="131" t="s">
         <v>186</v>
       </c>
-      <c r="O41" s="134"/>
-      <c r="P41" s="134"/>
-      <c r="Q41" s="134"/>
+      <c r="O41" s="132"/>
+      <c r="P41" s="132"/>
+      <c r="Q41" s="132"/>
       <c r="R41" s="87">
         <v>321</v>
       </c>
@@ -7136,12 +7136,12 @@
         <v>16</v>
       </c>
       <c r="T41" s="77"/>
-      <c r="U41" s="133" t="s">
+      <c r="U41" s="131" t="s">
         <v>186</v>
       </c>
-      <c r="V41" s="134"/>
-      <c r="W41" s="134"/>
-      <c r="X41" s="134"/>
+      <c r="V41" s="132"/>
+      <c r="W41" s="132"/>
+      <c r="X41" s="132"/>
       <c r="Y41" s="87">
         <v>322</v>
       </c>
@@ -7151,12 +7151,12 @@
       <c r="AA41" s="86"/>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G42" s="133" t="s">
+      <c r="G42" s="131" t="s">
         <v>177</v>
       </c>
-      <c r="H42" s="134"/>
-      <c r="I42" s="134"/>
-      <c r="J42" s="134"/>
+      <c r="H42" s="132"/>
+      <c r="I42" s="132"/>
+      <c r="J42" s="132"/>
       <c r="K42" s="87">
         <v>413</v>
       </c>
@@ -7164,12 +7164,12 @@
         <v>16</v>
       </c>
       <c r="M42" s="77"/>
-      <c r="N42" s="133" t="s">
+      <c r="N42" s="131" t="s">
         <v>177</v>
       </c>
-      <c r="O42" s="134"/>
-      <c r="P42" s="134"/>
-      <c r="Q42" s="134"/>
+      <c r="O42" s="132"/>
+      <c r="P42" s="132"/>
+      <c r="Q42" s="132"/>
       <c r="R42" s="87">
         <v>309.75</v>
       </c>
@@ -7177,12 +7177,12 @@
         <v>16</v>
       </c>
       <c r="T42" s="77"/>
-      <c r="U42" s="133" t="s">
+      <c r="U42" s="131" t="s">
         <v>177</v>
       </c>
-      <c r="V42" s="134"/>
-      <c r="W42" s="134"/>
-      <c r="X42" s="134"/>
+      <c r="V42" s="132"/>
+      <c r="W42" s="132"/>
+      <c r="X42" s="132"/>
       <c r="Y42" s="87">
         <v>308.7</v>
       </c>
@@ -7192,12 +7192,12 @@
       <c r="AA42" s="16"/>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G43" s="131" t="s">
+      <c r="G43" s="133" t="s">
         <v>167</v>
       </c>
-      <c r="H43" s="132"/>
-      <c r="I43" s="132"/>
-      <c r="J43" s="132"/>
+      <c r="H43" s="134"/>
+      <c r="I43" s="134"/>
+      <c r="J43" s="134"/>
       <c r="K43" s="89">
         <v>36</v>
       </c>
@@ -7205,12 +7205,12 @@
         <v>16</v>
       </c>
       <c r="M43" s="77"/>
-      <c r="N43" s="131" t="s">
+      <c r="N43" s="133" t="s">
         <v>167</v>
       </c>
-      <c r="O43" s="132"/>
-      <c r="P43" s="132"/>
-      <c r="Q43" s="132"/>
+      <c r="O43" s="134"/>
+      <c r="P43" s="134"/>
+      <c r="Q43" s="134"/>
       <c r="R43" s="89">
         <v>57</v>
       </c>
@@ -7218,12 +7218,12 @@
         <v>16</v>
       </c>
       <c r="T43" s="77"/>
-      <c r="U43" s="131" t="s">
+      <c r="U43" s="133" t="s">
         <v>167</v>
       </c>
-      <c r="V43" s="132"/>
-      <c r="W43" s="132"/>
-      <c r="X43" s="132"/>
+      <c r="V43" s="134"/>
+      <c r="W43" s="134"/>
+      <c r="X43" s="134"/>
       <c r="Y43" s="89">
         <v>72</v>
       </c>
@@ -7237,12 +7237,12 @@
       <c r="AA44" s="86"/>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A45" s="142" t="s">
+      <c r="A45" s="135" t="s">
         <v>176</v>
       </c>
-      <c r="B45" s="143"/>
-      <c r="C45" s="143"/>
-      <c r="D45" s="143"/>
+      <c r="B45" s="136"/>
+      <c r="C45" s="136"/>
+      <c r="D45" s="136"/>
       <c r="E45" s="85">
         <v>7</v>
       </c>
@@ -7250,11 +7250,11 @@
       <c r="AA45" s="86"/>
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A46" s="133" t="s">
+      <c r="A46" s="131" t="s">
         <v>148</v>
       </c>
-      <c r="B46" s="134"/>
-      <c r="C46" s="134"/>
+      <c r="B46" s="132"/>
+      <c r="C46" s="132"/>
       <c r="D46" s="75">
         <f>HLOOKUP($E$45,$18:$43,4)</f>
         <v>180</v>
@@ -7268,11 +7268,11 @@
       <c r="AA46" s="86"/>
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A47" s="137" t="s">
+      <c r="A47" s="142" t="s">
         <v>157</v>
       </c>
-      <c r="B47" s="138"/>
-      <c r="C47" s="138"/>
+      <c r="B47" s="143"/>
+      <c r="C47" s="143"/>
       <c r="D47" s="80">
         <f>HLOOKUP($E$45,$18:$43,5)</f>
         <v>2.5</v>
@@ -7284,13 +7284,13 @@
       <c r="AA47" s="86"/>
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A48" s="135" t="s">
+      <c r="A48" s="138" t="s">
         <v>228</v>
       </c>
-      <c r="B48" s="136"/>
-      <c r="C48" s="136"/>
-      <c r="D48" s="136"/>
-      <c r="E48" s="139"/>
+      <c r="B48" s="139"/>
+      <c r="C48" s="139"/>
+      <c r="D48" s="139"/>
+      <c r="E48" s="144"/>
       <c r="L48" s="86"/>
       <c r="Z48" s="59"/>
     </row>
@@ -7310,11 +7310,11 @@
       <c r="Z49" s="59"/>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A50" s="133" t="s">
+      <c r="A50" s="131" t="s">
         <v>159</v>
       </c>
-      <c r="B50" s="134"/>
-      <c r="C50" s="134"/>
+      <c r="B50" s="132"/>
+      <c r="C50" s="132"/>
       <c r="D50" s="75">
         <f>HLOOKUP($E$45,$18:$43,7)</f>
         <v>734</v>
@@ -7325,11 +7325,11 @@
       <c r="Z50" s="59"/>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A51" s="131" t="s">
+      <c r="A51" s="133" t="s">
         <v>160</v>
       </c>
-      <c r="B51" s="132"/>
-      <c r="C51" s="132"/>
+      <c r="B51" s="134"/>
+      <c r="C51" s="134"/>
       <c r="D51" s="80">
         <f>HLOOKUP($E$45,$18:$43,8)</f>
         <v>0</v>
@@ -7340,21 +7340,21 @@
       <c r="Z51" s="59"/>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A52" s="135" t="s">
+      <c r="A52" s="138" t="s">
         <v>217</v>
       </c>
-      <c r="B52" s="136"/>
-      <c r="C52" s="136"/>
-      <c r="D52" s="136"/>
-      <c r="E52" s="139"/>
+      <c r="B52" s="139"/>
+      <c r="C52" s="139"/>
+      <c r="D52" s="139"/>
+      <c r="E52" s="144"/>
       <c r="Z52" s="59"/>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A53" s="142" t="s">
+      <c r="A53" s="135" t="s">
         <v>219</v>
       </c>
-      <c r="B53" s="143"/>
-      <c r="C53" s="143"/>
+      <c r="B53" s="136"/>
+      <c r="C53" s="136"/>
       <c r="D53" s="82">
         <f>HLOOKUP($E$45,$18:$43,14)</f>
         <v>42.5</v>
@@ -7365,11 +7365,11 @@
       <c r="Z53" s="59"/>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A54" s="135" t="s">
+      <c r="A54" s="138" t="s">
         <v>166</v>
       </c>
-      <c r="B54" s="136"/>
-      <c r="C54" s="136"/>
+      <c r="B54" s="139"/>
+      <c r="C54" s="139"/>
       <c r="D54" s="75">
         <f>HLOOKUP($E$45,$18:$43,15)</f>
         <v>49</v>
@@ -7380,11 +7380,11 @@
       <c r="Z54" s="59"/>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A55" s="135" t="s">
+      <c r="A55" s="138" t="s">
         <v>165</v>
       </c>
-      <c r="B55" s="136"/>
-      <c r="C55" s="136"/>
+      <c r="B55" s="139"/>
+      <c r="C55" s="139"/>
       <c r="D55" s="75">
         <f>HLOOKUP($E$45,$18:$43,16)</f>
         <v>37.75</v>
@@ -7395,11 +7395,11 @@
       <c r="Z55" s="59"/>
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A56" s="137" t="s">
+      <c r="A56" s="142" t="s">
         <v>167</v>
       </c>
-      <c r="B56" s="138"/>
-      <c r="C56" s="138"/>
+      <c r="B56" s="143"/>
+      <c r="C56" s="143"/>
       <c r="D56" s="80">
         <f>HLOOKUP($E$45,$18:$43,17)</f>
         <v>62</v>
@@ -7410,21 +7410,21 @@
       <c r="Z56" s="59"/>
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A57" s="135" t="s">
+      <c r="A57" s="138" t="s">
         <v>220</v>
       </c>
-      <c r="B57" s="136"/>
-      <c r="C57" s="136"/>
-      <c r="D57" s="136"/>
-      <c r="E57" s="139"/>
+      <c r="B57" s="139"/>
+      <c r="C57" s="139"/>
+      <c r="D57" s="139"/>
+      <c r="E57" s="144"/>
       <c r="Z57" s="59"/>
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A58" s="142" t="s">
+      <c r="A58" s="135" t="s">
         <v>219</v>
       </c>
-      <c r="B58" s="143"/>
-      <c r="C58" s="143"/>
+      <c r="B58" s="136"/>
+      <c r="C58" s="136"/>
       <c r="D58" s="82">
         <f>HLOOKUP($E$45,$18:$43,23)</f>
         <v>317.5</v>
@@ -7434,11 +7434,11 @@
       </c>
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A59" s="135" t="s">
+      <c r="A59" s="138" t="s">
         <v>166</v>
       </c>
-      <c r="B59" s="136"/>
-      <c r="C59" s="136"/>
+      <c r="B59" s="139"/>
+      <c r="C59" s="139"/>
       <c r="D59" s="75">
         <f>HLOOKUP($E$45,$18:$43,24)</f>
         <v>321</v>
@@ -7448,11 +7448,11 @@
       </c>
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A60" s="135" t="s">
+      <c r="A60" s="138" t="s">
         <v>305</v>
       </c>
-      <c r="B60" s="136"/>
-      <c r="C60" s="136"/>
+      <c r="B60" s="139"/>
+      <c r="C60" s="139"/>
       <c r="D60" s="75">
         <f>HLOOKUP($E$45,$18:$43,25)</f>
         <v>309.75</v>
@@ -7462,11 +7462,11 @@
       </c>
     </row>
     <row r="61" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A61" s="137" t="s">
+      <c r="A61" s="142" t="s">
         <v>167</v>
       </c>
-      <c r="B61" s="138"/>
-      <c r="C61" s="138"/>
+      <c r="B61" s="143"/>
+      <c r="C61" s="143"/>
       <c r="D61" s="80">
         <f>HLOOKUP($E$45,$18:$43,26)</f>
         <v>57</v>
@@ -7477,24 +7477,71 @@
     </row>
   </sheetData>
   <mergeCells count="113">
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="N43:Q43"/>
-    <mergeCell ref="G31:J31"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="G33:J33"/>
-    <mergeCell ref="G34:J34"/>
-    <mergeCell ref="G35:L35"/>
-    <mergeCell ref="G39:J39"/>
-    <mergeCell ref="G40:J40"/>
-    <mergeCell ref="G41:J41"/>
-    <mergeCell ref="G42:J42"/>
-    <mergeCell ref="N37:Q37"/>
-    <mergeCell ref="N38:Q38"/>
-    <mergeCell ref="N39:Q39"/>
-    <mergeCell ref="N40:Q40"/>
-    <mergeCell ref="N41:Q41"/>
-    <mergeCell ref="N42:Q42"/>
+    <mergeCell ref="N35:S35"/>
+    <mergeCell ref="N36:Q36"/>
+    <mergeCell ref="U41:X41"/>
+    <mergeCell ref="U42:X42"/>
+    <mergeCell ref="U43:X43"/>
+    <mergeCell ref="U27:X27"/>
+    <mergeCell ref="U28:X28"/>
+    <mergeCell ref="U29:X29"/>
+    <mergeCell ref="U30:X30"/>
+    <mergeCell ref="U31:X31"/>
+    <mergeCell ref="U32:X32"/>
+    <mergeCell ref="U33:X33"/>
+    <mergeCell ref="U34:X34"/>
+    <mergeCell ref="U35:Z35"/>
+    <mergeCell ref="U36:X36"/>
+    <mergeCell ref="U37:X37"/>
+    <mergeCell ref="U38:X38"/>
+    <mergeCell ref="U39:X39"/>
+    <mergeCell ref="U40:X40"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="K2:Q2"/>
+    <mergeCell ref="N18:Q18"/>
+    <mergeCell ref="N19:Q19"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="N20:Q20"/>
+    <mergeCell ref="N21:Q21"/>
+    <mergeCell ref="N22:Q22"/>
+    <mergeCell ref="N23:Q23"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="G23:J23"/>
     <mergeCell ref="A45:D45"/>
     <mergeCell ref="G26:L26"/>
     <mergeCell ref="G27:J27"/>
@@ -7519,77 +7566,30 @@
     <mergeCell ref="N28:Q28"/>
     <mergeCell ref="U23:X23"/>
     <mergeCell ref="N24:Q24"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="N43:Q43"/>
+    <mergeCell ref="G31:J31"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="G34:J34"/>
+    <mergeCell ref="G35:L35"/>
+    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="G40:J40"/>
+    <mergeCell ref="G41:J41"/>
+    <mergeCell ref="G42:J42"/>
+    <mergeCell ref="N37:Q37"/>
+    <mergeCell ref="N38:Q38"/>
+    <mergeCell ref="N39:Q39"/>
+    <mergeCell ref="N40:Q40"/>
+    <mergeCell ref="N41:Q41"/>
+    <mergeCell ref="N42:Q42"/>
     <mergeCell ref="N25:Q25"/>
-    <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="N18:Q18"/>
-    <mergeCell ref="N19:Q19"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="N20:Q20"/>
-    <mergeCell ref="N21:Q21"/>
-    <mergeCell ref="N22:Q22"/>
-    <mergeCell ref="N23:Q23"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="A58:C58"/>
     <mergeCell ref="G43:J43"/>
     <mergeCell ref="G36:J36"/>
     <mergeCell ref="G37:J37"/>
     <mergeCell ref="G38:J38"/>
-    <mergeCell ref="U41:X41"/>
-    <mergeCell ref="U42:X42"/>
-    <mergeCell ref="U43:X43"/>
-    <mergeCell ref="U27:X27"/>
-    <mergeCell ref="U28:X28"/>
-    <mergeCell ref="U29:X29"/>
-    <mergeCell ref="U30:X30"/>
-    <mergeCell ref="U31:X31"/>
-    <mergeCell ref="U32:X32"/>
-    <mergeCell ref="U33:X33"/>
-    <mergeCell ref="U34:X34"/>
-    <mergeCell ref="U35:Z35"/>
-    <mergeCell ref="U36:X36"/>
-    <mergeCell ref="U37:X37"/>
-    <mergeCell ref="U38:X38"/>
-    <mergeCell ref="U39:X39"/>
-    <mergeCell ref="U40:X40"/>
     <mergeCell ref="N32:Q32"/>
-    <mergeCell ref="N35:S35"/>
-    <mergeCell ref="N36:Q36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7604,33 +7604,33 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="118" t="s">
+      <c r="A2" s="126" t="s">
         <v>175</v>
       </c>
-      <c r="B2" s="118"/>
-      <c r="C2" s="118"/>
-      <c r="D2" s="118"/>
-      <c r="E2" s="118"/>
-      <c r="H2" s="118" t="s">
+      <c r="B2" s="126"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="126"/>
+      <c r="H2" s="126" t="s">
         <v>188</v>
       </c>
-      <c r="I2" s="118"/>
-      <c r="J2" s="118"/>
-      <c r="K2" s="118"/>
-      <c r="L2" s="118"/>
-      <c r="P2" s="118" t="s">
+      <c r="I2" s="126"/>
+      <c r="J2" s="126"/>
+      <c r="K2" s="126"/>
+      <c r="L2" s="126"/>
+      <c r="P2" s="126" t="s">
         <v>187</v>
       </c>
-      <c r="Q2" s="118"/>
-      <c r="R2" s="118"/>
-      <c r="S2" s="118"/>
-      <c r="T2" s="118"/>
+      <c r="Q2" s="126"/>
+      <c r="R2" s="126"/>
+      <c r="S2" s="126"/>
+      <c r="T2" s="126"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="118" t="s">
+      <c r="A3" s="126" t="s">
         <v>174</v>
       </c>
-      <c r="B3" s="118"/>
+      <c r="B3" s="126"/>
       <c r="D3" s="61">
         <f ca="1">Электродвигатель!$P$53</f>
         <v>45.959055069271365</v>
@@ -7638,11 +7638,11 @@
       <c r="E3" t="s">
         <v>100</v>
       </c>
-      <c r="H3" s="94" t="s">
+      <c r="H3" s="93" t="s">
         <v>174</v>
       </c>
-      <c r="I3" s="94"/>
-      <c r="J3" s="94"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
       <c r="K3" s="63">
         <f ca="1">D3</f>
         <v>45.959055069271365</v>
@@ -7663,10 +7663,10 @@
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="118" t="s">
+      <c r="A4" s="126" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="118"/>
+      <c r="B4" s="126"/>
       <c r="D4" s="62">
         <f>Электродвигатель!$N$52</f>
         <v>1440</v>
@@ -7674,11 +7674,11 @@
       <c r="E4" t="s">
         <v>105</v>
       </c>
-      <c r="H4" s="94" t="s">
+      <c r="H4" s="93" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="94"/>
-      <c r="J4" s="94"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
       <c r="K4" s="64">
         <f>D4</f>
         <v>1440</v>
@@ -7700,27 +7700,27 @@
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H5" s="118" t="s">
+      <c r="H5" s="126" t="s">
         <v>178</v>
       </c>
-      <c r="I5" s="118"/>
-      <c r="J5" s="118"/>
-      <c r="K5" s="118"/>
-      <c r="L5" s="118"/>
-      <c r="P5" s="118" t="s">
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
+      <c r="L5" s="126"/>
+      <c r="P5" s="126" t="s">
         <v>126</v>
       </c>
-      <c r="Q5" s="118"/>
-      <c r="R5" s="118"/>
-      <c r="S5" s="118"/>
-      <c r="T5" s="118"/>
+      <c r="Q5" s="126"/>
+      <c r="R5" s="126"/>
+      <c r="S5" s="126"/>
+      <c r="T5" s="126"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="118" t="s">
+      <c r="A6" s="126" t="s">
         <v>120</v>
       </c>
-      <c r="B6" s="118"/>
-      <c r="C6" s="118"/>
+      <c r="B6" s="126"/>
+      <c r="C6" s="126"/>
       <c r="D6" s="66">
         <f>Электродвигатель!$F$61</f>
         <v>38</v>
@@ -7728,11 +7728,11 @@
       <c r="E6" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="118" t="s">
+      <c r="H6" s="126" t="s">
         <v>177</v>
       </c>
-      <c r="I6" s="118"/>
-      <c r="J6" s="118"/>
+      <c r="I6" s="126"/>
+      <c r="J6" s="126"/>
       <c r="K6">
         <f>Передача!D55</f>
         <v>37.75</v>
@@ -7740,11 +7740,11 @@
       <c r="L6" t="s">
         <v>16</v>
       </c>
-      <c r="P6" s="118" t="s">
+      <c r="P6" s="126" t="s">
         <v>177</v>
       </c>
-      <c r="Q6" s="118"/>
-      <c r="R6" s="118"/>
+      <c r="Q6" s="126"/>
+      <c r="R6" s="126"/>
       <c r="S6">
         <f>Передача!D60</f>
         <v>309.75</v>
@@ -7762,11 +7762,11 @@
       <c r="D7" s="52">
         <v>0.8</v>
       </c>
-      <c r="H7" s="118" t="s">
+      <c r="H7" s="126" t="s">
         <v>186</v>
       </c>
-      <c r="I7" s="118"/>
-      <c r="J7" s="118"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="126"/>
       <c r="K7">
         <f>Передача!D54</f>
         <v>49</v>
@@ -7774,11 +7774,11 @@
       <c r="L7" t="s">
         <v>16</v>
       </c>
-      <c r="P7" s="118" t="s">
+      <c r="P7" s="126" t="s">
         <v>186</v>
       </c>
-      <c r="Q7" s="118"/>
-      <c r="R7" s="118"/>
+      <c r="Q7" s="126"/>
+      <c r="R7" s="126"/>
       <c r="S7">
         <f>Передача!D59</f>
         <v>321</v>
@@ -7788,19 +7788,19 @@
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="118" t="s">
+      <c r="A8" s="126" t="s">
         <v>196</v>
       </c>
-      <c r="B8" s="118"/>
-      <c r="C8" s="118"/>
+      <c r="B8" s="126"/>
+      <c r="C8" s="126"/>
       <c r="D8" s="71">
         <v>1.2</v>
       </c>
-      <c r="H8" s="118" t="s">
+      <c r="H8" s="126" t="s">
         <v>167</v>
       </c>
-      <c r="I8" s="118"/>
-      <c r="J8" s="118"/>
+      <c r="I8" s="126"/>
+      <c r="J8" s="126"/>
       <c r="K8">
         <f>Передача!D56</f>
         <v>62</v>
@@ -7808,11 +7808,11 @@
       <c r="L8" t="s">
         <v>16</v>
       </c>
-      <c r="P8" s="118" t="s">
+      <c r="P8" s="126" t="s">
         <v>167</v>
       </c>
-      <c r="Q8" s="118"/>
-      <c r="R8" s="118"/>
+      <c r="Q8" s="126"/>
+      <c r="R8" s="126"/>
       <c r="S8">
         <f>Передача!D61</f>
         <v>57</v>
@@ -7822,38 +7822,38 @@
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H9" s="118" t="s">
+      <c r="H9" s="126" t="s">
         <v>189</v>
       </c>
-      <c r="I9" s="118"/>
-      <c r="J9" s="118"/>
-      <c r="K9" s="118"/>
-      <c r="L9" s="118"/>
-      <c r="P9" s="118" t="s">
+      <c r="I9" s="126"/>
+      <c r="J9" s="126"/>
+      <c r="K9" s="126"/>
+      <c r="L9" s="126"/>
+      <c r="P9" s="126" t="s">
         <v>189</v>
       </c>
-      <c r="Q9" s="118"/>
-      <c r="R9" s="118"/>
-      <c r="S9" s="118"/>
-      <c r="T9" s="118"/>
+      <c r="Q9" s="126"/>
+      <c r="R9" s="126"/>
+      <c r="S9" s="126"/>
+      <c r="T9" s="126"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H10" s="118" t="s">
+      <c r="H10" s="126" t="s">
         <v>185</v>
       </c>
-      <c r="I10" s="118"/>
-      <c r="J10" s="118"/>
+      <c r="I10" s="126"/>
+      <c r="J10" s="126"/>
       <c r="K10">
         <v>7.5</v>
       </c>
       <c r="L10" s="65" t="s">
         <v>192</v>
       </c>
-      <c r="P10" s="118" t="s">
+      <c r="P10" s="126" t="s">
         <v>185</v>
       </c>
-      <c r="Q10" s="118"/>
-      <c r="R10" s="118"/>
+      <c r="Q10" s="126"/>
+      <c r="R10" s="126"/>
       <c r="S10">
         <v>5.4</v>
       </c>
@@ -7862,11 +7862,11 @@
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H11" s="118" t="s">
+      <c r="H11" s="126" t="s">
         <v>197</v>
       </c>
-      <c r="I11" s="118"/>
-      <c r="J11" s="118"/>
+      <c r="I11" s="126"/>
+      <c r="J11" s="126"/>
       <c r="K11">
         <f ca="1">K10*(K3)^(1/3)</f>
         <v>26.864883424091097</v>
@@ -7874,11 +7874,11 @@
       <c r="L11" t="s">
         <v>16</v>
       </c>
-      <c r="P11" s="118" t="s">
+      <c r="P11" s="126" t="s">
         <v>197</v>
       </c>
-      <c r="Q11" s="118"/>
-      <c r="R11" s="118"/>
+      <c r="Q11" s="126"/>
+      <c r="R11" s="126"/>
       <c r="S11">
         <f ca="1">S10*(S3)^(1/3)</f>
         <v>37.309835064996221</v>
@@ -7888,11 +7888,11 @@
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H12" s="118" t="s">
+      <c r="H12" s="126" t="s">
         <v>201</v>
       </c>
-      <c r="I12" s="118"/>
-      <c r="J12" s="118"/>
+      <c r="I12" s="126"/>
+      <c r="J12" s="126"/>
       <c r="K12">
         <f ca="1">MIN(MAX(K11,D6/D8),D6/D7)</f>
         <v>31.666666666666668</v>
@@ -7900,11 +7900,11 @@
       <c r="L12" t="s">
         <v>16</v>
       </c>
-      <c r="P12" s="118" t="s">
+      <c r="P12" s="126" t="s">
         <v>190</v>
       </c>
-      <c r="Q12" s="118"/>
-      <c r="R12" s="118"/>
+      <c r="Q12" s="126"/>
+      <c r="R12" s="126"/>
       <c r="S12" s="66">
         <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;S11)</f>
         <v>38</v>
@@ -7917,11 +7917,11 @@
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H13" s="118" t="s">
+      <c r="H13" s="126" t="s">
         <v>190</v>
       </c>
-      <c r="I13" s="118"/>
-      <c r="J13" s="118"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="126"/>
       <c r="K13" s="66">
         <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;K12)</f>
         <v>32</v>
@@ -7932,11 +7932,11 @@
       <c r="M13" t="s">
         <v>199</v>
       </c>
-      <c r="P13" s="118" t="s">
+      <c r="P13" s="126" t="s">
         <v>198</v>
       </c>
-      <c r="Q13" s="118"/>
-      <c r="R13" s="118"/>
+      <c r="Q13" s="126"/>
+      <c r="R13" s="126"/>
       <c r="S13">
         <f ca="1">_xlfn.MINIFS($28:$28,$26:$26,"&gt;="&amp;S12)</f>
         <v>3.5</v>
@@ -7946,20 +7946,20 @@
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="118" t="s">
+      <c r="A14" s="126" t="s">
         <v>292</v>
       </c>
-      <c r="B14" s="118"/>
-      <c r="C14" s="118"/>
+      <c r="B14" s="126"/>
+      <c r="C14" s="126"/>
       <c r="D14">
         <f>Электродвигатель!$F$58</f>
         <v>2.2000000000000002</v>
       </c>
-      <c r="H14" s="118" t="s">
+      <c r="H14" s="126" t="s">
         <v>198</v>
       </c>
-      <c r="I14" s="118"/>
-      <c r="J14" s="118"/>
+      <c r="I14" s="126"/>
+      <c r="J14" s="126"/>
       <c r="K14">
         <f ca="1">_xlfn.MINIFS($28:$28,$26:$26,"&gt;="&amp;K13)</f>
         <v>3.5</v>
@@ -7967,11 +7967,11 @@
       <c r="L14" t="s">
         <v>16</v>
       </c>
-      <c r="P14" s="118" t="s">
+      <c r="P14" s="126" t="s">
         <v>194</v>
       </c>
-      <c r="Q14" s="118"/>
-      <c r="R14" s="118"/>
+      <c r="Q14" s="126"/>
+      <c r="R14" s="126"/>
       <c r="S14">
         <f ca="1">S12+2*S13</f>
         <v>45</v>
@@ -7981,11 +7981,11 @@
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H15" s="118" t="s">
+      <c r="H15" s="126" t="s">
         <v>194</v>
       </c>
-      <c r="I15" s="118"/>
-      <c r="J15" s="118"/>
+      <c r="I15" s="126"/>
+      <c r="J15" s="126"/>
       <c r="K15">
         <f ca="1">K13+2*K14</f>
         <v>39</v>
@@ -7993,11 +7993,11 @@
       <c r="L15" t="s">
         <v>16</v>
       </c>
-      <c r="P15" s="118" t="s">
+      <c r="P15" s="126" t="s">
         <v>269</v>
       </c>
-      <c r="Q15" s="118"/>
-      <c r="R15" s="118"/>
+      <c r="Q15" s="126"/>
+      <c r="R15" s="126"/>
       <c r="S15" s="66">
         <f ca="1">_xlfn.MINIFS(Подшипники!$A:$A,Подшипники!$A:$A,"&gt;="&amp;S14)</f>
         <v>45</v>
@@ -8007,11 +8007,11 @@
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H16" s="118" t="s">
+      <c r="H16" s="126" t="s">
         <v>269</v>
       </c>
-      <c r="I16" s="118"/>
-      <c r="J16" s="118"/>
+      <c r="I16" s="126"/>
+      <c r="J16" s="126"/>
       <c r="K16" s="66">
         <f ca="1">_xlfn.MINIFS(Подшипники!$A:$A,Подшипники!$A:$A,"&gt;="&amp;K15)</f>
         <v>40</v>
@@ -8019,11 +8019,11 @@
       <c r="L16" t="s">
         <v>16</v>
       </c>
-      <c r="P16" s="118" t="s">
+      <c r="P16" s="126" t="s">
         <v>198</v>
       </c>
-      <c r="Q16" s="118"/>
-      <c r="R16" s="118"/>
+      <c r="Q16" s="126"/>
+      <c r="R16" s="126"/>
       <c r="S16">
         <f ca="1">_xlfn.MINIFS($29:$29,$26:$26,"&gt;="&amp;S12)</f>
         <v>2.2999999999999998</v>
@@ -8033,11 +8033,11 @@
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H17" s="118" t="s">
+      <c r="H17" s="126" t="s">
         <v>198</v>
       </c>
-      <c r="I17" s="118"/>
-      <c r="J17" s="118"/>
+      <c r="I17" s="126"/>
+      <c r="J17" s="126"/>
       <c r="K17">
         <f ca="1">_xlfn.MINIFS($29:$29,$26:$26,"&gt;="&amp;K13)</f>
         <v>2</v>
@@ -8045,11 +8045,11 @@
       <c r="L17" t="s">
         <v>16</v>
       </c>
-      <c r="P17" s="118" t="s">
+      <c r="P17" s="126" t="s">
         <v>195</v>
       </c>
-      <c r="Q17" s="118"/>
-      <c r="R17" s="118"/>
+      <c r="Q17" s="126"/>
+      <c r="R17" s="126"/>
       <c r="S17">
         <f ca="1">S15+2*S16</f>
         <v>49.6</v>
@@ -8059,11 +8059,11 @@
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H18" s="118" t="s">
+      <c r="H18" s="126" t="s">
         <v>195</v>
       </c>
-      <c r="I18" s="118"/>
-      <c r="J18" s="118"/>
+      <c r="I18" s="126"/>
+      <c r="J18" s="126"/>
       <c r="K18">
         <f ca="1">K16+2*K17</f>
         <v>44</v>
@@ -8071,11 +8071,11 @@
       <c r="L18" t="s">
         <v>16</v>
       </c>
-      <c r="P18" s="118" t="s">
+      <c r="P18" s="126" t="s">
         <v>273</v>
       </c>
-      <c r="Q18" s="118"/>
-      <c r="R18" s="118"/>
+      <c r="Q18" s="126"/>
+      <c r="R18" s="126"/>
       <c r="S18" s="66">
         <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;S17)</f>
         <v>50</v>
@@ -8088,11 +8088,11 @@
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H19" s="118" t="s">
+      <c r="H19" s="126" t="s">
         <v>191</v>
       </c>
-      <c r="I19" s="118"/>
-      <c r="J19" s="118"/>
+      <c r="I19" s="126"/>
+      <c r="J19" s="126"/>
       <c r="K19" s="66">
         <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;K18)</f>
         <v>45</v>
@@ -8115,10 +8115,10 @@
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A26" s="118" t="s">
+      <c r="A26" s="126" t="s">
         <v>183</v>
       </c>
-      <c r="B26" s="118"/>
+      <c r="B26" s="126"/>
       <c r="C26">
         <v>17</v>
       </c>
@@ -8154,10 +8154,10 @@
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A27" s="118" t="s">
+      <c r="A27" s="126" t="s">
         <v>184</v>
       </c>
-      <c r="B27" s="118"/>
+      <c r="B27" s="126"/>
       <c r="C27">
         <v>22</v>
       </c>
@@ -8190,10 +8190,10 @@
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A28" s="118" t="s">
+      <c r="A28" s="126" t="s">
         <v>181</v>
       </c>
-      <c r="B28" s="118"/>
+      <c r="B28" s="126"/>
       <c r="C28">
         <v>3</v>
       </c>
@@ -8226,10 +8226,10 @@
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A29" s="118" t="s">
+      <c r="A29" s="126" t="s">
         <v>182</v>
       </c>
-      <c r="B29" s="118"/>
+      <c r="B29" s="126"/>
       <c r="C29">
         <v>1.5</v>
       </c>
@@ -8263,35 +8263,6 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="P2:T2"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="P5:T5"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="P16:R16"/>
-    <mergeCell ref="P17:R17"/>
-    <mergeCell ref="P18:R18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="P11:R11"/>
-    <mergeCell ref="P15:R15"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="H19:J19"/>
     <mergeCell ref="P9:T9"/>
     <mergeCell ref="P6:R6"/>
     <mergeCell ref="P7:R7"/>
@@ -8307,6 +8278,35 @@
     <mergeCell ref="H10:J10"/>
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="H9:L9"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="P16:R16"/>
+    <mergeCell ref="P17:R17"/>
+    <mergeCell ref="P18:R18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="P11:R11"/>
+    <mergeCell ref="P15:R15"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="P5:T5"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8421,48 +8421,48 @@
       <c r="AI6" s="48"/>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A7" s="118" t="s">
+      <c r="A7" s="126" t="s">
         <v>294</v>
       </c>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118">
+      <c r="B7" s="126"/>
+      <c r="C7" s="126"/>
+      <c r="D7" s="126">
         <f ca="1">Вал!$K$16</f>
         <v>40</v>
       </c>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118">
+      <c r="E7" s="126"/>
+      <c r="F7" s="126"/>
+      <c r="G7" s="126"/>
+      <c r="H7" s="126">
         <f ca="1">Вал!$K$19</f>
         <v>45</v>
       </c>
-      <c r="I7" s="118"/>
-      <c r="J7" s="118">
+      <c r="I7" s="126"/>
+      <c r="J7" s="126">
         <f>Передача!D54</f>
         <v>49</v>
       </c>
-      <c r="K7" s="118"/>
-      <c r="L7" s="118">
+      <c r="K7" s="126"/>
+      <c r="L7" s="126">
         <f ca="1">H7</f>
         <v>45</v>
       </c>
-      <c r="M7" s="118"/>
-      <c r="N7" s="118">
+      <c r="M7" s="126"/>
+      <c r="N7" s="126">
         <f>F7</f>
         <v>0</v>
       </c>
-      <c r="O7" s="118"/>
-      <c r="P7" s="118">
+      <c r="O7" s="126"/>
+      <c r="P7" s="126">
         <f ca="1">D7</f>
         <v>40</v>
       </c>
-      <c r="Q7" s="118"/>
-      <c r="R7" s="118">
+      <c r="Q7" s="126"/>
+      <c r="R7" s="126">
         <f ca="1">Вал!K13</f>
         <v>32</v>
       </c>
-      <c r="S7" s="118"/>
+      <c r="S7" s="126"/>
       <c r="U7" s="48"/>
       <c r="V7" s="48"/>
       <c r="W7" s="48"/>
@@ -8474,30 +8474,30 @@
       <c r="AG7" s="48"/>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A8" s="118" t="s">
+      <c r="A8" s="126" t="s">
         <v>270</v>
       </c>
-      <c r="B8" s="118"/>
-      <c r="C8" s="118"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="118"/>
-      <c r="F8" s="118"/>
-      <c r="G8" s="118"/>
-      <c r="H8" s="118"/>
-      <c r="I8" s="118"/>
-      <c r="J8" s="118">
+      <c r="B8" s="126"/>
+      <c r="C8" s="126"/>
+      <c r="D8" s="126"/>
+      <c r="E8" s="126"/>
+      <c r="F8" s="126"/>
+      <c r="G8" s="126"/>
+      <c r="H8" s="126"/>
+      <c r="I8" s="126"/>
+      <c r="J8" s="126">
         <f>Передача!$D$56</f>
         <v>62</v>
       </c>
-      <c r="K8" s="118"/>
-      <c r="L8" s="118"/>
-      <c r="M8" s="118"/>
-      <c r="N8" s="118"/>
-      <c r="O8" s="118"/>
-      <c r="P8" s="118"/>
-      <c r="Q8" s="118"/>
-      <c r="R8" s="118"/>
-      <c r="S8" s="118"/>
+      <c r="K8" s="126"/>
+      <c r="L8" s="126"/>
+      <c r="M8" s="126"/>
+      <c r="N8" s="126"/>
+      <c r="O8" s="126"/>
+      <c r="P8" s="126"/>
+      <c r="Q8" s="126"/>
+      <c r="R8" s="126"/>
+      <c r="S8" s="126"/>
       <c r="U8" s="48"/>
       <c r="V8" s="48"/>
       <c r="W8" s="48"/>
@@ -8509,27 +8509,27 @@
       <c r="AG8" s="48"/>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A9" s="118" t="s">
+      <c r="A9" s="126" t="s">
         <v>295</v>
       </c>
-      <c r="B9" s="118"/>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="118"/>
-      <c r="G9" s="118"/>
-      <c r="H9" s="118"/>
-      <c r="I9" s="118"/>
-      <c r="J9" s="118"/>
-      <c r="K9" s="118"/>
-      <c r="L9" s="118"/>
-      <c r="M9" s="118"/>
-      <c r="N9" s="118"/>
-      <c r="O9" s="118"/>
-      <c r="P9" s="118"/>
-      <c r="Q9" s="118"/>
-      <c r="R9" s="118"/>
-      <c r="S9" s="118"/>
+      <c r="B9" s="126"/>
+      <c r="C9" s="126"/>
+      <c r="D9" s="126"/>
+      <c r="E9" s="126"/>
+      <c r="F9" s="126"/>
+      <c r="G9" s="126"/>
+      <c r="H9" s="126"/>
+      <c r="I9" s="126"/>
+      <c r="J9" s="126"/>
+      <c r="K9" s="126"/>
+      <c r="L9" s="126"/>
+      <c r="M9" s="126"/>
+      <c r="N9" s="126"/>
+      <c r="O9" s="126"/>
+      <c r="P9" s="126"/>
+      <c r="Q9" s="126"/>
+      <c r="R9" s="126"/>
+      <c r="S9" s="126"/>
       <c r="U9" s="48"/>
       <c r="V9" s="48"/>
       <c r="W9" s="48"/>
@@ -8541,27 +8541,27 @@
       <c r="AG9" s="48"/>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A10" s="118" t="s">
+      <c r="A10" s="126" t="s">
         <v>212</v>
       </c>
-      <c r="B10" s="118"/>
-      <c r="C10" s="118"/>
-      <c r="D10" s="118"/>
-      <c r="E10" s="118"/>
-      <c r="F10" s="118"/>
-      <c r="G10" s="118"/>
-      <c r="H10" s="118"/>
-      <c r="I10" s="118"/>
-      <c r="J10" s="118"/>
-      <c r="K10" s="118"/>
-      <c r="L10" s="118"/>
-      <c r="M10" s="118"/>
-      <c r="N10" s="118"/>
-      <c r="O10" s="118"/>
-      <c r="P10" s="118"/>
-      <c r="Q10" s="118"/>
-      <c r="R10" s="118"/>
-      <c r="S10" s="118"/>
+      <c r="B10" s="126"/>
+      <c r="C10" s="126"/>
+      <c r="D10" s="126"/>
+      <c r="E10" s="126"/>
+      <c r="F10" s="126"/>
+      <c r="G10" s="126"/>
+      <c r="H10" s="126"/>
+      <c r="I10" s="126"/>
+      <c r="J10" s="126"/>
+      <c r="K10" s="126"/>
+      <c r="L10" s="126"/>
+      <c r="M10" s="126"/>
+      <c r="N10" s="126"/>
+      <c r="O10" s="126"/>
+      <c r="P10" s="126"/>
+      <c r="Q10" s="126"/>
+      <c r="R10" s="126"/>
+      <c r="S10" s="126"/>
       <c r="U10" s="48"/>
       <c r="V10" s="48"/>
       <c r="W10" s="48"/>
@@ -8573,27 +8573,27 @@
       <c r="AG10" s="48"/>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A11" s="118" t="s">
+      <c r="A11" s="126" t="s">
         <v>296</v>
       </c>
-      <c r="B11" s="118"/>
-      <c r="C11" s="118"/>
-      <c r="D11" s="118"/>
-      <c r="E11" s="118"/>
-      <c r="F11" s="118"/>
-      <c r="G11" s="118"/>
-      <c r="H11" s="118"/>
-      <c r="I11" s="118"/>
-      <c r="J11" s="118"/>
-      <c r="K11" s="118"/>
-      <c r="L11" s="118"/>
-      <c r="M11" s="118"/>
-      <c r="N11" s="118"/>
-      <c r="O11" s="118"/>
-      <c r="P11" s="118"/>
-      <c r="Q11" s="118"/>
-      <c r="R11" s="118"/>
-      <c r="S11" s="118"/>
+      <c r="B11" s="126"/>
+      <c r="C11" s="126"/>
+      <c r="D11" s="126"/>
+      <c r="E11" s="126"/>
+      <c r="F11" s="126"/>
+      <c r="G11" s="126"/>
+      <c r="H11" s="126"/>
+      <c r="I11" s="126"/>
+      <c r="J11" s="126"/>
+      <c r="K11" s="126"/>
+      <c r="L11" s="126"/>
+      <c r="M11" s="126"/>
+      <c r="N11" s="126"/>
+      <c r="O11" s="126"/>
+      <c r="P11" s="126"/>
+      <c r="Q11" s="126"/>
+      <c r="R11" s="126"/>
+      <c r="S11" s="126"/>
       <c r="U11" s="48"/>
       <c r="V11" s="48"/>
       <c r="W11" s="48"/>
@@ -8602,64 +8602,121 @@
       <c r="AG11" s="48"/>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A12" s="118" t="s">
+      <c r="A12" s="126" t="s">
         <v>297</v>
       </c>
-      <c r="B12" s="118"/>
-      <c r="C12" s="118"/>
-      <c r="D12" s="118"/>
-      <c r="E12" s="118"/>
-      <c r="F12" s="118"/>
-      <c r="G12" s="118"/>
-      <c r="H12" s="118"/>
-      <c r="I12" s="118"/>
-      <c r="J12" s="118"/>
-      <c r="K12" s="118"/>
-      <c r="L12" s="118"/>
-      <c r="M12" s="118"/>
-      <c r="N12" s="118"/>
-      <c r="O12" s="118"/>
-      <c r="P12" s="118"/>
-      <c r="Q12" s="118"/>
-      <c r="R12" s="118"/>
-      <c r="S12" s="118"/>
+      <c r="B12" s="126"/>
+      <c r="C12" s="126"/>
+      <c r="D12" s="126"/>
+      <c r="E12" s="126"/>
+      <c r="F12" s="126"/>
+      <c r="G12" s="126"/>
+      <c r="H12" s="126"/>
+      <c r="I12" s="126"/>
+      <c r="J12" s="126"/>
+      <c r="K12" s="126"/>
+      <c r="L12" s="126"/>
+      <c r="M12" s="126"/>
+      <c r="N12" s="126"/>
+      <c r="O12" s="126"/>
+      <c r="P12" s="126"/>
+      <c r="Q12" s="126"/>
+      <c r="R12" s="126"/>
+      <c r="S12" s="126"/>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A13" s="118" t="s">
+      <c r="A13" s="126" t="s">
         <v>298</v>
       </c>
-      <c r="B13" s="118"/>
-      <c r="C13" s="118"/>
-      <c r="D13" s="118"/>
-      <c r="E13" s="118"/>
-      <c r="F13" s="118"/>
-      <c r="G13" s="118"/>
-      <c r="H13" s="118"/>
-      <c r="I13" s="118"/>
-      <c r="J13" s="118"/>
-      <c r="K13" s="118"/>
-      <c r="L13" s="118"/>
-      <c r="M13" s="118"/>
-      <c r="N13" s="118"/>
-      <c r="O13" s="118"/>
-      <c r="P13" s="118"/>
-      <c r="Q13" s="118"/>
-      <c r="R13" s="118"/>
-      <c r="S13" s="118"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="126"/>
+      <c r="L13" s="126"/>
+      <c r="M13" s="126"/>
+      <c r="N13" s="126"/>
+      <c r="O13" s="126"/>
+      <c r="P13" s="126"/>
+      <c r="Q13" s="126"/>
+      <c r="R13" s="126"/>
+      <c r="S13" s="126"/>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="H14" s="118" t="s">
+      <c r="H14" s="126" t="s">
         <v>218</v>
       </c>
-      <c r="I14" s="118"/>
-      <c r="J14" s="118">
+      <c r="I14" s="126"/>
+      <c r="J14" s="126">
         <f>Передача!D55</f>
         <v>37.75</v>
       </c>
-      <c r="K14" s="118"/>
+      <c r="K14" s="126"/>
     </row>
   </sheetData>
   <mergeCells count="73">
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="P5:Q6"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="R5:S6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="J5:K6"/>
+    <mergeCell ref="L5:M6"/>
+    <mergeCell ref="N5:O6"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="D5:E6"/>
@@ -8676,63 +8733,6 @@
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="D12:E12"/>
-    <mergeCell ref="R5:S6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="J5:K6"/>
-    <mergeCell ref="L5:M6"/>
-    <mergeCell ref="N5:O6"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="P5:Q6"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="R12:S12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -8748,22 +8748,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="126" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A2" s="94" t="s">
+      <c r="A2" s="93" t="s">
         <v>145</v>
       </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
       <c r="E2" s="1">
         <f>Передача!$E$9</f>
         <v>300</v>
@@ -8776,12 +8776,12 @@
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A3" s="94" t="s">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="94"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
       <c r="E3" s="16">
         <f>Передача!$E$10</f>
         <v>3</v>
@@ -8789,45 +8789,45 @@
       <c r="F3" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="J3" s="94" t="s">
+      <c r="J3" s="93" t="s">
         <v>228</v>
       </c>
-      <c r="K3" s="94"/>
-      <c r="L3" s="94"/>
-      <c r="M3" s="94"/>
-      <c r="N3" s="94"/>
-      <c r="T3" s="118" t="s">
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="93"/>
+      <c r="T3" s="126" t="s">
         <v>162</v>
       </c>
-      <c r="U3" s="118"/>
-      <c r="V3" s="118"/>
-      <c r="W3" s="118"/>
-      <c r="X3" s="118" t="s">
+      <c r="U3" s="126"/>
+      <c r="V3" s="126"/>
+      <c r="W3" s="126"/>
+      <c r="X3" s="126" t="s">
         <v>189</v>
       </c>
-      <c r="Y3" s="118"/>
-      <c r="Z3" s="118" t="s">
+      <c r="Y3" s="126"/>
+      <c r="Z3" s="126" t="s">
         <v>178</v>
       </c>
-      <c r="AA3" s="118"/>
+      <c r="AA3" s="126"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="93" t="s">
         <v>212</v>
       </c>
-      <c r="B4" s="94"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="94"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="93"/>
       <c r="E4" s="47" t="str">
         <f>Передача!$E$11</f>
         <v>?</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="J4" s="134" t="s">
+      <c r="J4" s="132" t="s">
         <v>0</v>
       </c>
-      <c r="K4" s="134"/>
-      <c r="L4" s="134"/>
+      <c r="K4" s="132"/>
+      <c r="L4" s="132"/>
       <c r="M4" s="78">
         <f>Передача!$D$49</f>
         <v>2016</v>
@@ -8835,38 +8835,38 @@
       <c r="N4" s="75" t="s">
         <v>161</v>
       </c>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="126" t="s">
         <v>257</v>
       </c>
-      <c r="U4" s="118"/>
-      <c r="V4" s="118"/>
-      <c r="W4" s="118"/>
-      <c r="X4" s="118">
+      <c r="U4" s="126"/>
+      <c r="V4" s="126"/>
+      <c r="W4" s="126"/>
+      <c r="X4" s="126">
         <v>0</v>
       </c>
-      <c r="Y4" s="118"/>
-      <c r="Z4" s="118">
+      <c r="Y4" s="126"/>
+      <c r="Z4" s="126">
         <f ca="1">E19</f>
         <v>50</v>
       </c>
-      <c r="AA4" s="118"/>
+      <c r="AA4" s="126"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A5" s="103" t="s">
+      <c r="A5" s="125" t="s">
         <v>214</v>
       </c>
-      <c r="B5" s="103"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
+      <c r="B5" s="125"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="125"/>
       <c r="E5" s="70" t="s">
         <v>213</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="J5" s="134" t="s">
+      <c r="J5" s="132" t="s">
         <v>159</v>
       </c>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
+      <c r="K5" s="132"/>
+      <c r="L5" s="132"/>
       <c r="M5" s="78">
         <f>Передача!$D$50</f>
         <v>734</v>
@@ -8874,30 +8874,30 @@
       <c r="N5" s="75" t="s">
         <v>161</v>
       </c>
-      <c r="T5" s="118" t="s">
+      <c r="T5" s="126" t="s">
         <v>259</v>
       </c>
-      <c r="U5" s="118"/>
-      <c r="V5" s="118"/>
-      <c r="W5" s="118"/>
-      <c r="X5" s="118">
+      <c r="U5" s="126"/>
+      <c r="V5" s="126"/>
+      <c r="W5" s="126"/>
+      <c r="X5" s="126">
         <f ca="1">E19</f>
         <v>50</v>
       </c>
-      <c r="Y5" s="118"/>
-      <c r="Z5" s="118">
+      <c r="Y5" s="126"/>
+      <c r="Z5" s="126">
         <f>E18</f>
         <v>80</v>
       </c>
-      <c r="AA5" s="118"/>
+      <c r="AA5" s="126"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A6" s="118" t="s">
+      <c r="A6" s="126" t="s">
         <v>157</v>
       </c>
-      <c r="B6" s="118"/>
-      <c r="C6" s="118"/>
-      <c r="D6" s="118"/>
+      <c r="B6" s="126"/>
+      <c r="C6" s="126"/>
+      <c r="D6" s="126"/>
       <c r="E6">
         <f>Передача!$D$47</f>
         <v>2.5</v>
@@ -8905,11 +8905,11 @@
       <c r="F6" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="134" t="s">
+      <c r="J6" s="132" t="s">
         <v>160</v>
       </c>
-      <c r="K6" s="134"/>
-      <c r="L6" s="134"/>
+      <c r="K6" s="132"/>
+      <c r="L6" s="132"/>
       <c r="M6" s="78">
         <f>Передача!$D$51</f>
         <v>0</v>
@@ -8917,28 +8917,28 @@
       <c r="N6" s="75" t="s">
         <v>161</v>
       </c>
-      <c r="T6" s="118" t="s">
+      <c r="T6" s="126" t="s">
         <v>243</v>
       </c>
-      <c r="U6" s="118"/>
-      <c r="V6" s="118"/>
-      <c r="W6" s="118"/>
-      <c r="X6" s="149">
+      <c r="U6" s="126"/>
+      <c r="V6" s="126"/>
+      <c r="W6" s="126"/>
+      <c r="X6" s="148">
         <v>0.3</v>
       </c>
-      <c r="Y6" s="149"/>
-      <c r="Z6" s="149">
+      <c r="Y6" s="148"/>
+      <c r="Z6" s="148">
         <v>0.3</v>
       </c>
-      <c r="AA6" s="149"/>
+      <c r="AA6" s="148"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A7" s="118" t="s">
+      <c r="A7" s="126" t="s">
         <v>216</v>
       </c>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
+      <c r="B7" s="126"/>
+      <c r="C7" s="126"/>
+      <c r="D7" s="126"/>
       <c r="E7">
         <f>Передача!$D$58</f>
         <v>317.5</v>
@@ -8946,30 +8946,30 @@
       <c r="F7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="T7" s="118" t="s">
+      <c r="T7" s="126" t="s">
         <v>254</v>
       </c>
-      <c r="U7" s="118"/>
-      <c r="V7" s="118"/>
-      <c r="W7" s="118"/>
-      <c r="X7" s="149">
+      <c r="U7" s="126"/>
+      <c r="V7" s="126"/>
+      <c r="W7" s="126"/>
+      <c r="X7" s="148">
         <f>2.1*10^5</f>
         <v>210000</v>
       </c>
-      <c r="Y7" s="149"/>
-      <c r="Z7" s="149">
+      <c r="Y7" s="148"/>
+      <c r="Z7" s="148">
         <f>2.1*10^5</f>
         <v>210000</v>
       </c>
-      <c r="AA7" s="149"/>
+      <c r="AA7" s="148"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A8" s="94" t="s">
+      <c r="A8" s="93" t="s">
         <v>186</v>
       </c>
-      <c r="B8" s="94"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="94"/>
+      <c r="B8" s="93"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="93"/>
       <c r="E8" s="1">
         <f>Передача!$D$59</f>
         <v>321</v>
@@ -8977,35 +8977,35 @@
       <c r="F8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="148" t="s">
+      <c r="J8" s="147" t="s">
         <v>260</v>
       </c>
-      <c r="K8" s="148"/>
-      <c r="L8" s="148"/>
-      <c r="M8" s="148"/>
-      <c r="N8" s="148"/>
-      <c r="T8" s="118" t="s">
+      <c r="K8" s="147"/>
+      <c r="L8" s="147"/>
+      <c r="M8" s="147"/>
+      <c r="N8" s="147"/>
+      <c r="T8" s="126" t="s">
         <v>253</v>
       </c>
-      <c r="U8" s="118"/>
-      <c r="V8" s="118"/>
-      <c r="W8" s="118"/>
-      <c r="X8" s="149">
+      <c r="U8" s="126"/>
+      <c r="V8" s="126"/>
+      <c r="W8" s="126"/>
+      <c r="X8" s="148">
         <v>330</v>
       </c>
-      <c r="Y8" s="149"/>
-      <c r="Z8" s="149">
+      <c r="Y8" s="148"/>
+      <c r="Z8" s="148">
         <v>330</v>
       </c>
-      <c r="AA8" s="149"/>
+      <c r="AA8" s="148"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A9" s="94" t="s">
+      <c r="A9" s="93" t="s">
         <v>177</v>
       </c>
-      <c r="B9" s="94"/>
-      <c r="C9" s="94"/>
-      <c r="D9" s="94"/>
+      <c r="B9" s="93"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="93"/>
       <c r="E9" s="1">
         <f>Передача!$D$60</f>
         <v>309.75</v>
@@ -9013,11 +9013,11 @@
       <c r="F9" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="118" t="s">
+      <c r="J9" s="126" t="s">
         <v>174</v>
       </c>
-      <c r="K9" s="118"/>
-      <c r="L9" s="118"/>
+      <c r="K9" s="126"/>
+      <c r="L9" s="126"/>
       <c r="M9">
         <f>Передача!$E$5</f>
         <v>320</v>
@@ -9025,30 +9025,30 @@
       <c r="N9" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="T9" s="118" t="s">
+      <c r="T9" s="126" t="s">
         <v>255</v>
       </c>
-      <c r="U9" s="118"/>
-      <c r="V9" s="118"/>
-      <c r="W9" s="118"/>
-      <c r="X9" s="118">
+      <c r="U9" s="126"/>
+      <c r="V9" s="126"/>
+      <c r="W9" s="126"/>
+      <c r="X9" s="126">
         <f ca="1">(X5*X5+X4*X4)/(X5*X5-X4*X4)-X6</f>
         <v>0.7</v>
       </c>
-      <c r="Y9" s="118"/>
-      <c r="Z9" s="118">
+      <c r="Y9" s="126"/>
+      <c r="Z9" s="126">
         <f ca="1">(Z5*Z5+Z4*Z4)/(Z5*Z5-Z4*Z4)+Z6</f>
         <v>2.5820512820512818</v>
       </c>
-      <c r="AA9" s="118"/>
+      <c r="AA9" s="126"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A10" s="118" t="s">
+      <c r="A10" s="126" t="s">
         <v>167</v>
       </c>
-      <c r="B10" s="118"/>
-      <c r="C10" s="118"/>
-      <c r="D10" s="118"/>
+      <c r="B10" s="126"/>
+      <c r="C10" s="126"/>
+      <c r="D10" s="126"/>
       <c r="E10">
         <f>Передача!$D$61</f>
         <v>57</v>
@@ -9056,41 +9056,41 @@
       <c r="F10" t="s">
         <v>16</v>
       </c>
-      <c r="J10" s="118" t="s">
+      <c r="J10" s="126" t="s">
         <v>234</v>
       </c>
-      <c r="K10" s="118"/>
-      <c r="L10" s="118"/>
+      <c r="K10" s="126"/>
+      <c r="L10" s="126"/>
       <c r="M10" s="52">
         <v>3</v>
       </c>
       <c r="N10" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="T10" s="118" t="s">
+      <c r="T10" s="126" t="s">
         <v>256</v>
       </c>
-      <c r="U10" s="118"/>
-      <c r="V10" s="118"/>
-      <c r="W10" s="118"/>
-      <c r="X10" s="118">
+      <c r="U10" s="126"/>
+      <c r="V10" s="126"/>
+      <c r="W10" s="126"/>
+      <c r="X10" s="126">
         <f ca="1">0.5*X8*(1-(X4*X4/X5/X5))</f>
         <v>165</v>
       </c>
-      <c r="Y10" s="118"/>
-      <c r="Z10" s="118">
+      <c r="Y10" s="126"/>
+      <c r="Z10" s="126">
         <f ca="1">0.5*Z8*(1-(Z4*Z4/Z5/Z5))</f>
         <v>100.546875</v>
       </c>
-      <c r="AA10" s="118"/>
+      <c r="AA10" s="126"/>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A11" s="118" t="s">
+      <c r="A11" s="126" t="s">
         <v>221</v>
       </c>
-      <c r="B11" s="118"/>
-      <c r="C11" s="118"/>
-      <c r="D11" s="118"/>
+      <c r="B11" s="126"/>
+      <c r="C11" s="126"/>
+      <c r="D11" s="126"/>
       <c r="E11">
         <f>_xlfn.MINIFS($32:$32,$31:$31,"&gt;="&amp;E7)</f>
         <v>5</v>
@@ -9098,11 +9098,11 @@
       <c r="F11" t="s">
         <v>16</v>
       </c>
-      <c r="J11" s="118" t="s">
+      <c r="J11" s="126" t="s">
         <v>236</v>
       </c>
-      <c r="K11" s="118"/>
-      <c r="L11" s="118"/>
+      <c r="K11" s="126"/>
+      <c r="L11" s="126"/>
       <c r="M11" s="52">
         <f>E35</f>
         <v>0.08</v>
@@ -9112,23 +9112,23 @@
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A12" s="118" t="s">
+      <c r="A12" s="126" t="s">
         <v>222</v>
       </c>
-      <c r="B12" s="118"/>
-      <c r="C12" s="118"/>
-      <c r="D12" s="118"/>
+      <c r="B12" s="126"/>
+      <c r="C12" s="126"/>
+      <c r="D12" s="126"/>
       <c r="E12" t="s">
         <v>223</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
       </c>
-      <c r="J12" s="118" t="s">
+      <c r="J12" s="126" t="s">
         <v>238</v>
       </c>
-      <c r="K12" s="118"/>
-      <c r="L12" s="118"/>
+      <c r="K12" s="126"/>
+      <c r="L12" s="126"/>
       <c r="M12" s="25">
         <f>E17</f>
         <v>57</v>
@@ -9141,23 +9141,23 @@
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A13" s="147" t="s">
+      <c r="A13" s="149" t="s">
         <v>224</v>
       </c>
-      <c r="B13" s="118"/>
-      <c r="C13" s="118"/>
-      <c r="D13" s="118"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
       <c r="E13" t="s">
         <v>226</v>
       </c>
       <c r="F13" t="s">
         <v>225</v>
       </c>
-      <c r="J13" s="118" t="s">
+      <c r="J13" s="126" t="s">
         <v>235</v>
       </c>
-      <c r="K13" s="118"/>
-      <c r="L13" s="118"/>
+      <c r="K13" s="126"/>
+      <c r="L13" s="126"/>
       <c r="M13">
         <f ca="1">2000*M10*M9/(PI()*E19*E19*M12*M11)</f>
         <v>53.610086094112106</v>
@@ -9167,12 +9167,12 @@
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A14" s="118" t="s">
+      <c r="A14" s="126" t="s">
         <v>229</v>
       </c>
-      <c r="B14" s="118"/>
-      <c r="C14" s="118"/>
-      <c r="D14" s="118"/>
+      <c r="B14" s="126"/>
+      <c r="C14" s="126"/>
+      <c r="D14" s="126"/>
       <c r="E14">
         <f>2.2*E6+0.05*E10</f>
         <v>8.35</v>
@@ -9180,11 +9180,11 @@
       <c r="F14" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="118" t="s">
+      <c r="J14" s="126" t="s">
         <v>242</v>
       </c>
-      <c r="K14" s="118"/>
-      <c r="L14" s="118"/>
+      <c r="K14" s="126"/>
+      <c r="L14" s="126"/>
       <c r="M14">
         <f ca="1">1000*M13*E19*(X9/X7+Z9/Z7)</f>
         <v>41.893107570490528</v>
@@ -9194,12 +9194,12 @@
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A15" s="118" t="s">
+      <c r="A15" s="126" t="s">
         <v>227</v>
       </c>
-      <c r="B15" s="118"/>
-      <c r="C15" s="118"/>
-      <c r="D15" s="118"/>
+      <c r="B15" s="126"/>
+      <c r="C15" s="126"/>
+      <c r="D15" s="126"/>
       <c r="E15">
         <f ca="1">(E18-E19)/2</f>
         <v>15</v>
@@ -9207,11 +9207,11 @@
       <c r="F15" t="s">
         <v>16</v>
       </c>
-      <c r="J15" s="118" t="s">
+      <c r="J15" s="126" t="s">
         <v>249</v>
       </c>
-      <c r="K15" s="118"/>
-      <c r="L15" s="118"/>
+      <c r="K15" s="126"/>
+      <c r="L15" s="126"/>
       <c r="M15">
         <f>5.5*(E20+E22)</f>
         <v>0</v>
@@ -9224,20 +9224,20 @@
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A16" s="118" t="s">
+      <c r="A16" s="126" t="s">
         <v>247</v>
       </c>
-      <c r="B16" s="118"/>
-      <c r="C16" s="118"/>
-      <c r="D16" s="118"/>
+      <c r="B16" s="126"/>
+      <c r="C16" s="126"/>
+      <c r="D16" s="126"/>
       <c r="E16" s="52">
         <v>1</v>
       </c>
-      <c r="J16" s="118" t="s">
+      <c r="J16" s="126" t="s">
         <v>250</v>
       </c>
-      <c r="K16" s="118"/>
-      <c r="L16" s="118"/>
+      <c r="K16" s="126"/>
+      <c r="L16" s="126"/>
       <c r="N16" t="s">
         <v>248</v>
       </c>
@@ -9246,12 +9246,12 @@
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="118" t="s">
+      <c r="A17" s="126" t="s">
         <v>245</v>
       </c>
-      <c r="B17" s="118"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="118"/>
+      <c r="B17" s="126"/>
+      <c r="C17" s="126"/>
+      <c r="D17" s="126"/>
       <c r="E17">
         <f>E10*E16</f>
         <v>57</v>
@@ -9259,11 +9259,11 @@
       <c r="F17" t="s">
         <v>16</v>
       </c>
-      <c r="J17" s="118" t="s">
+      <c r="J17" s="126" t="s">
         <v>251</v>
       </c>
-      <c r="K17" s="118"/>
-      <c r="L17" s="118"/>
+      <c r="K17" s="126"/>
+      <c r="L17" s="126"/>
       <c r="M17" s="25">
         <f ca="1">SUM(M14:M16)</f>
         <v>41.893107570490528</v>
@@ -9273,23 +9273,23 @@
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="118" t="s">
+      <c r="A18" s="126" t="s">
         <v>246</v>
       </c>
-      <c r="B18" s="118"/>
-      <c r="C18" s="118"/>
-      <c r="D18" s="118"/>
+      <c r="B18" s="126"/>
+      <c r="C18" s="126"/>
+      <c r="D18" s="126"/>
       <c r="E18" s="52">
         <v>80</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
       </c>
-      <c r="J18" s="118" t="s">
+      <c r="J18" s="126" t="s">
         <v>258</v>
       </c>
-      <c r="K18" s="118"/>
-      <c r="L18" s="118"/>
+      <c r="K18" s="126"/>
+      <c r="L18" s="126"/>
       <c r="M18">
         <f ca="1">MAX(X10:AA10)*M14/M13</f>
         <v>128.93772893772891</v>
@@ -9299,12 +9299,12 @@
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="148" t="s">
+      <c r="A19" s="147" t="s">
         <v>244</v>
       </c>
-      <c r="B19" s="148"/>
-      <c r="C19" s="148"/>
-      <c r="D19" s="148"/>
+      <c r="B19" s="147"/>
+      <c r="C19" s="147"/>
+      <c r="D19" s="147"/>
       <c r="E19" s="77">
         <f ca="1">Вал!$S$18</f>
         <v>50</v>
@@ -9312,11 +9312,11 @@
       <c r="F19" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="J19" s="118" t="s">
+      <c r="J19" s="126" t="s">
         <v>252</v>
       </c>
-      <c r="K19" s="118"/>
-      <c r="L19" s="118"/>
+      <c r="K19" s="126"/>
+      <c r="L19" s="126"/>
       <c r="M19" s="90">
         <f ca="1">M18+M15</f>
         <v>128.93772893772891</v>
@@ -9326,12 +9326,12 @@
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="118" t="s">
+      <c r="A20" s="126" t="s">
         <v>313</v>
       </c>
-      <c r="B20" s="118"/>
-      <c r="C20" s="118"/>
-      <c r="D20" s="118"/>
+      <c r="B20" s="126"/>
+      <c r="C20" s="126"/>
+      <c r="D20" s="126"/>
       <c r="E20" s="52"/>
       <c r="F20" s="77" t="s">
         <v>248</v>
@@ -9341,23 +9341,23 @@
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="118" t="s">
+      <c r="A21" s="126" t="s">
         <v>314</v>
       </c>
-      <c r="B21" s="118"/>
-      <c r="C21" s="118"/>
-      <c r="D21" s="118"/>
+      <c r="B21" s="126"/>
+      <c r="C21" s="126"/>
+      <c r="D21" s="126"/>
       <c r="E21" s="92" t="s">
         <v>315</v>
       </c>
       <c r="F21" t="s">
         <v>16</v>
       </c>
-      <c r="J21" s="118" t="s">
+      <c r="J21" s="126" t="s">
         <v>272</v>
       </c>
-      <c r="K21" s="118"/>
-      <c r="L21" s="118"/>
+      <c r="K21" s="126"/>
+      <c r="L21" s="126"/>
       <c r="M21">
         <v>90</v>
       </c>
@@ -9369,32 +9369,32 @@
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="118" t="s">
+      <c r="A22" s="126" t="s">
         <v>316</v>
       </c>
-      <c r="B22" s="118"/>
-      <c r="C22" s="118"/>
-      <c r="D22" s="118"/>
+      <c r="B22" s="126"/>
+      <c r="C22" s="126"/>
+      <c r="D22" s="126"/>
       <c r="E22" s="52"/>
       <c r="F22" t="s">
         <v>248</v>
       </c>
-      <c r="J22" s="118" t="s">
+      <c r="J22" s="126" t="s">
         <v>263</v>
       </c>
-      <c r="K22" s="118"/>
-      <c r="L22" s="118"/>
+      <c r="K22" s="126"/>
+      <c r="L22" s="126"/>
       <c r="M22">
         <v>0.2</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="118" t="s">
+      <c r="A23" s="126" t="s">
         <v>317</v>
       </c>
-      <c r="B23" s="118"/>
-      <c r="C23" s="118"/>
-      <c r="D23" s="118"/>
+      <c r="B23" s="126"/>
+      <c r="C23" s="126"/>
+      <c r="D23" s="126"/>
       <c r="E23">
         <f ca="1">MAX(E10/4,(E15+E14)/2)</f>
         <v>14.25</v>
@@ -9402,11 +9402,11 @@
       <c r="F23" t="s">
         <v>16</v>
       </c>
-      <c r="J23" s="118" t="s">
+      <c r="J23" s="126" t="s">
         <v>262</v>
       </c>
-      <c r="K23" s="118"/>
-      <c r="L23" s="118"/>
+      <c r="K23" s="126"/>
+      <c r="L23" s="126"/>
       <c r="M23">
         <f ca="1">PI()*E19*M12*(M21-M15)*M22/1000</f>
         <v>161.1637031291564</v>
@@ -9416,10 +9416,10 @@
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="118" t="s">
+      <c r="A30" s="126" t="s">
         <v>183</v>
       </c>
-      <c r="B30" s="118"/>
+      <c r="B30" s="126"/>
       <c r="C30">
         <v>20</v>
       </c>
@@ -9446,10 +9446,10 @@
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="118" t="s">
+      <c r="A31" s="126" t="s">
         <v>184</v>
       </c>
-      <c r="B31" s="118"/>
+      <c r="B31" s="126"/>
       <c r="C31">
         <v>30</v>
       </c>
@@ -9476,10 +9476,10 @@
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="118" t="s">
+      <c r="A32" s="126" t="s">
         <v>215</v>
       </c>
-      <c r="B32" s="118"/>
+      <c r="B32" s="126"/>
       <c r="C32">
         <v>1</v>
       </c>
@@ -9506,97 +9506,170 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="118" t="s">
+      <c r="A34" s="126" t="s">
         <v>306</v>
       </c>
-      <c r="B34" s="118"/>
-      <c r="C34" s="118" t="s">
+      <c r="B34" s="126"/>
+      <c r="C34" s="126" t="s">
         <v>307</v>
       </c>
-      <c r="D34" s="118"/>
-      <c r="E34" s="118" t="s">
+      <c r="D34" s="126"/>
+      <c r="E34" s="126" t="s">
         <v>311</v>
       </c>
-      <c r="F34" s="118"/>
-      <c r="G34" s="118" t="s">
+      <c r="F34" s="126"/>
+      <c r="G34" s="126" t="s">
         <v>312</v>
       </c>
-      <c r="H34" s="118"/>
+      <c r="H34" s="126"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="118" t="s">
+      <c r="A35" s="126" t="s">
         <v>308</v>
       </c>
-      <c r="B35" s="118"/>
-      <c r="C35" s="118" t="s">
+      <c r="B35" s="126"/>
+      <c r="C35" s="126" t="s">
         <v>309</v>
       </c>
-      <c r="D35" s="118"/>
-      <c r="E35" s="118">
+      <c r="D35" s="126"/>
+      <c r="E35" s="126">
         <v>0.08</v>
       </c>
-      <c r="F35" s="118"/>
-      <c r="G35" s="118">
+      <c r="F35" s="126"/>
+      <c r="G35" s="126">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H35" s="118"/>
+      <c r="H35" s="126"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="118" t="s">
+      <c r="A36" s="126" t="s">
         <v>308</v>
       </c>
-      <c r="B36" s="118"/>
-      <c r="C36" s="118" t="s">
+      <c r="B36" s="126"/>
+      <c r="C36" s="126" t="s">
         <v>308</v>
       </c>
-      <c r="D36" s="118"/>
-      <c r="E36" s="118">
+      <c r="D36" s="126"/>
+      <c r="E36" s="126">
         <v>0.08</v>
       </c>
-      <c r="F36" s="118"/>
-      <c r="G36" s="118">
+      <c r="F36" s="126"/>
+      <c r="G36" s="126">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H36" s="118"/>
+      <c r="H36" s="126"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="118" t="s">
+      <c r="A37" s="126" t="s">
         <v>308</v>
       </c>
-      <c r="B37" s="118"/>
-      <c r="C37" s="118" t="s">
+      <c r="B37" s="126"/>
+      <c r="C37" s="126" t="s">
         <v>310</v>
       </c>
-      <c r="D37" s="118"/>
-      <c r="E37" s="118">
+      <c r="D37" s="126"/>
+      <c r="E37" s="126">
         <v>0.05</v>
       </c>
-      <c r="F37" s="118"/>
-      <c r="G37" s="118">
+      <c r="F37" s="126"/>
+      <c r="G37" s="126">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="H37" s="118"/>
+      <c r="H37" s="126"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="118" t="s">
+      <c r="A38" s="126" t="s">
         <v>309</v>
       </c>
-      <c r="B38" s="118"/>
-      <c r="C38" s="118" t="s">
+      <c r="B38" s="126"/>
+      <c r="C38" s="126" t="s">
         <v>310</v>
       </c>
-      <c r="D38" s="118"/>
-      <c r="E38" s="118">
+      <c r="D38" s="126"/>
+      <c r="E38" s="126">
         <v>0.05</v>
       </c>
-      <c r="F38" s="118"/>
-      <c r="G38" s="118">
+      <c r="F38" s="126"/>
+      <c r="G38" s="126">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="H38" s="118"/>
+      <c r="H38" s="126"/>
     </row>
   </sheetData>
   <mergeCells count="89">
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="T6:W6"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="T7:W7"/>
+    <mergeCell ref="T8:W8"/>
+    <mergeCell ref="T9:W9"/>
+    <mergeCell ref="T10:W10"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="T3:W3"/>
+    <mergeCell ref="T4:W4"/>
+    <mergeCell ref="T5:W5"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="Z8:AA8"/>
     <mergeCell ref="Z10:AA10"/>
     <mergeCell ref="J8:N8"/>
     <mergeCell ref="J23:L23"/>
@@ -9613,79 +9686,6 @@
     <mergeCell ref="J13:L13"/>
     <mergeCell ref="J11:L11"/>
     <mergeCell ref="J12:L12"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="Z5:AA5"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="Z8:AA8"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="T3:W3"/>
-    <mergeCell ref="T4:W4"/>
-    <mergeCell ref="T5:W5"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="X5:Y5"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="T6:W6"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="T7:W7"/>
-    <mergeCell ref="T8:W8"/>
-    <mergeCell ref="T9:W9"/>
-    <mergeCell ref="T10:W10"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="X10:Y10"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="G38:H38"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9711,12 +9711,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="118" t="s">
+      <c r="A2" s="126" t="s">
         <v>148</v>
       </c>
-      <c r="B2" s="118"/>
-      <c r="C2" s="118"/>
-      <c r="D2" s="118"/>
+      <c r="B2" s="126"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="126"/>
       <c r="E2">
         <f>Передача!$D$46</f>
         <v>180</v>
@@ -9726,12 +9726,12 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="118" t="s">
+      <c r="A3" s="126" t="s">
         <v>205</v>
       </c>
-      <c r="B3" s="118"/>
-      <c r="C3" s="118"/>
-      <c r="D3" s="118"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="126"/>
       <c r="E3">
         <f>Передача!$D$55</f>
         <v>37.75</v>
@@ -9741,12 +9741,12 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="118" t="s">
+      <c r="A4" s="126" t="s">
         <v>179</v>
       </c>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
+      <c r="B4" s="126"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="126"/>
       <c r="E4">
         <f>Передача!$D$56</f>
         <v>62</v>
@@ -9756,12 +9756,12 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="118" t="s">
+      <c r="A5" s="126" t="s">
         <v>206</v>
       </c>
-      <c r="B5" s="118"/>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
+      <c r="B5" s="126"/>
+      <c r="C5" s="126"/>
+      <c r="D5" s="126"/>
       <c r="E5">
         <f>Передача!$D$60</f>
         <v>309.75</v>
@@ -9771,12 +9771,12 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="118" t="s">
+      <c r="A6" s="126" t="s">
         <v>180</v>
       </c>
-      <c r="B6" s="118"/>
-      <c r="C6" s="118"/>
-      <c r="D6" s="118"/>
+      <c r="B6" s="126"/>
+      <c r="C6" s="126"/>
+      <c r="D6" s="126"/>
       <c r="E6">
         <f>Передача!$D$61</f>
         <v>57</v>
@@ -9786,12 +9786,12 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="118" t="s">
+      <c r="A7" s="126" t="s">
         <v>204</v>
       </c>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
+      <c r="B7" s="126"/>
+      <c r="C7" s="126"/>
+      <c r="D7" s="126"/>
       <c r="E7">
         <f>E2+E3/2+E5/2</f>
         <v>353.75</v>
@@ -9801,12 +9801,12 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="118" t="s">
+      <c r="A8" s="126" t="s">
         <v>203</v>
       </c>
-      <c r="B8" s="118"/>
-      <c r="C8" s="118"/>
-      <c r="D8" s="118"/>
+      <c r="B8" s="126"/>
+      <c r="C8" s="126"/>
+      <c r="D8" s="126"/>
       <c r="E8">
         <f>E7^(1/3)+3</f>
         <v>10.072378298355165</v>
@@ -9816,12 +9816,12 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="118" t="s">
+      <c r="A9" s="126" t="s">
         <v>207</v>
       </c>
-      <c r="B9" s="118"/>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
+      <c r="B9" s="126"/>
+      <c r="C9" s="126"/>
+      <c r="D9" s="126"/>
       <c r="E9">
         <f>E8*3</f>
         <v>30.217134895065495</v>
@@ -9831,12 +9831,12 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="118" t="s">
+      <c r="A10" s="126" t="s">
         <v>208</v>
       </c>
-      <c r="B10" s="118"/>
-      <c r="C10" s="118"/>
-      <c r="D10" s="118"/>
+      <c r="B10" s="126"/>
+      <c r="C10" s="126"/>
+      <c r="D10" s="126"/>
       <c r="E10" s="52">
         <v>4</v>
       </c>
@@ -9845,12 +9845,12 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="118" t="s">
+      <c r="A11" s="126" t="s">
         <v>209</v>
       </c>
-      <c r="B11" s="118"/>
-      <c r="C11" s="118"/>
-      <c r="D11" s="118"/>
+      <c r="B11" s="126"/>
+      <c r="C11" s="126"/>
+      <c r="D11" s="126"/>
       <c r="E11" s="52">
         <v>20</v>
       </c>
@@ -9859,22 +9859,22 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="118" t="s">
+      <c r="A12" s="126" t="s">
         <v>211</v>
       </c>
-      <c r="B12" s="118"/>
-      <c r="C12" s="118"/>
-      <c r="D12" s="118"/>
-      <c r="E12" s="118"/>
-      <c r="F12" s="118"/>
+      <c r="B12" s="126"/>
+      <c r="C12" s="126"/>
+      <c r="D12" s="126"/>
+      <c r="E12" s="126"/>
+      <c r="F12" s="126"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="118" t="s">
+      <c r="A13" s="126" t="s">
         <v>210</v>
       </c>
-      <c r="B13" s="118"/>
-      <c r="C13" s="118"/>
-      <c r="D13" s="118"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
       <c r="E13">
         <f>E7+2*E8+E10*2+E11*2</f>
         <v>421.89475659671035</v>
@@ -9884,12 +9884,12 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="118" t="s">
+      <c r="A14" s="126" t="s">
         <v>167</v>
       </c>
-      <c r="B14" s="118"/>
-      <c r="C14" s="118"/>
-      <c r="D14" s="118"/>
+      <c r="B14" s="126"/>
+      <c r="C14" s="126"/>
+      <c r="D14" s="126"/>
       <c r="E14">
         <f>E4+2*E8+2*E10</f>
         <v>90.144756596710323</v>
@@ -9899,12 +9899,12 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="118" t="s">
+      <c r="A15" s="126" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="118"/>
-      <c r="C15" s="118"/>
-      <c r="D15" s="118"/>
+      <c r="B15" s="126"/>
+      <c r="C15" s="126"/>
+      <c r="D15" s="126"/>
       <c r="E15">
         <f>E5+E8+E9+2*E10</f>
         <v>358.03951319342065</v>
@@ -9916,47 +9916,49 @@
     <row r="20" spans="18:23" x14ac:dyDescent="0.3">
       <c r="R20" s="1"/>
       <c r="S20" s="36"/>
-      <c r="T20" s="118" t="s">
+      <c r="T20" s="126" t="s">
         <v>129</v>
       </c>
-      <c r="U20" s="118"/>
-      <c r="V20" s="94" t="s">
+      <c r="U20" s="126"/>
+      <c r="V20" s="93" t="s">
         <v>125</v>
       </c>
-      <c r="W20" s="94"/>
+      <c r="W20" s="93"/>
     </row>
     <row r="21" spans="18:23" x14ac:dyDescent="0.3">
-      <c r="R21" s="127" t="s">
+      <c r="R21" s="98" t="s">
         <v>124</v>
       </c>
-      <c r="S21" s="127"/>
-      <c r="T21" s="94"/>
-      <c r="U21" s="94"/>
-      <c r="V21" s="94"/>
-      <c r="W21" s="94"/>
+      <c r="S21" s="98"/>
+      <c r="T21" s="93"/>
+      <c r="U21" s="93"/>
+      <c r="V21" s="93"/>
+      <c r="W21" s="93"/>
     </row>
     <row r="22" spans="18:23" x14ac:dyDescent="0.3">
-      <c r="R22" s="127" t="s">
+      <c r="R22" s="98" t="s">
         <v>126</v>
       </c>
-      <c r="S22" s="127"/>
-      <c r="T22" s="94" t="s">
+      <c r="S22" s="98"/>
+      <c r="T22" s="93" t="s">
         <v>127</v>
       </c>
-      <c r="U22" s="94"/>
-      <c r="V22" s="106" t="s">
+      <c r="U22" s="93"/>
+      <c r="V22" s="94" t="s">
         <v>128</v>
       </c>
-      <c r="W22" s="106"/>
+      <c r="W22" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="V21:W21"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A12:F12"/>
@@ -9965,14 +9967,12 @@
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -9986,7 +9986,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="118">
+      <c r="A1" s="126">
         <v>1</v>
       </c>
       <c r="B1">
@@ -9995,14 +9995,14 @@
       <c r="D1" s="48"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="118"/>
+      <c r="A2" s="126"/>
       <c r="B2">
         <v>1.05</v>
       </c>
       <c r="D2" s="48"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="118">
+      <c r="A3" s="126">
         <v>1.1000000000000001</v>
       </c>
       <c r="B3">
@@ -10011,14 +10011,14 @@
       <c r="D3" s="48"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="118"/>
+      <c r="A4" s="126"/>
       <c r="B4">
         <v>1.1499999999999999</v>
       </c>
       <c r="D4" s="48"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="118">
+      <c r="A5" s="126">
         <v>1.2</v>
       </c>
       <c r="B5">
@@ -10027,14 +10027,14 @@
       <c r="D5" s="48"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="118"/>
+      <c r="A6" s="126"/>
       <c r="B6">
         <v>1.3</v>
       </c>
       <c r="D6" s="48"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="118">
+      <c r="A7" s="126">
         <v>1.4</v>
       </c>
       <c r="B7">
@@ -10043,14 +10043,14 @@
       <c r="D7" s="48"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="118"/>
+      <c r="A8" s="126"/>
       <c r="B8">
         <v>1.5</v>
       </c>
       <c r="D8" s="48"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="118">
+      <c r="A9" s="126">
         <v>1.6</v>
       </c>
       <c r="B9">
@@ -10059,14 +10059,14 @@
       <c r="D9" s="48"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="118"/>
+      <c r="A10" s="126"/>
       <c r="B10">
         <v>1.7</v>
       </c>
       <c r="D10" s="48"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="118">
+      <c r="A11" s="126">
         <v>1.8</v>
       </c>
       <c r="B11">
@@ -10075,14 +10075,14 @@
       <c r="D11" s="48"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="118"/>
+      <c r="A12" s="126"/>
       <c r="B12">
         <v>1.9</v>
       </c>
       <c r="D12" s="48"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="118">
+      <c r="A13" s="126">
         <v>2</v>
       </c>
       <c r="B13">
@@ -10091,14 +10091,14 @@
       <c r="D13" s="48"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="118"/>
+      <c r="A14" s="126"/>
       <c r="B14">
         <v>2.1</v>
       </c>
       <c r="D14" s="48"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="118">
+      <c r="A15" s="126">
         <v>2.2000000000000002</v>
       </c>
       <c r="B15">
@@ -10107,14 +10107,14 @@
       <c r="D15" s="48"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="118"/>
+      <c r="A16" s="126"/>
       <c r="B16">
         <v>2.4</v>
       </c>
       <c r="D16" s="48"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="118">
+      <c r="A17" s="126">
         <v>2.5</v>
       </c>
       <c r="B17">
@@ -10123,14 +10123,14 @@
       <c r="D17" s="48"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="118"/>
+      <c r="A18" s="126"/>
       <c r="B18">
         <v>2.6</v>
       </c>
       <c r="D18" s="48"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="118">
+      <c r="A19" s="126">
         <v>2.8</v>
       </c>
       <c r="B19">
@@ -10139,14 +10139,14 @@
       <c r="D19" s="48"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="118"/>
+      <c r="A20" s="126"/>
       <c r="B20">
         <v>3</v>
       </c>
       <c r="D20" s="48"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="118">
+      <c r="A21" s="126">
         <v>3.2</v>
       </c>
       <c r="B21">
@@ -10155,14 +10155,14 @@
       <c r="D21" s="48"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="118"/>
+      <c r="A22" s="126"/>
       <c r="B22">
         <v>3.4</v>
       </c>
       <c r="D22" s="48"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="118">
+      <c r="A23" s="126">
         <v>3.6</v>
       </c>
       <c r="B23">
@@ -10171,14 +10171,14 @@
       <c r="D23" s="48"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="118"/>
+      <c r="A24" s="126"/>
       <c r="B24">
         <v>3.8</v>
       </c>
       <c r="D24" s="48"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="118">
+      <c r="A25" s="126">
         <v>4</v>
       </c>
       <c r="B25">
@@ -10187,14 +10187,14 @@
       <c r="D25" s="48"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="118"/>
+      <c r="A26" s="126"/>
       <c r="B26">
         <v>4.2</v>
       </c>
       <c r="D26" s="48"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="118">
+      <c r="A27" s="126">
         <v>4.5</v>
       </c>
       <c r="B27">
@@ -10203,14 +10203,14 @@
       <c r="D27" s="48"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="118"/>
+      <c r="A28" s="126"/>
       <c r="B28">
         <v>4.8</v>
       </c>
       <c r="D28" s="48"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="118">
+      <c r="A29" s="126">
         <v>5</v>
       </c>
       <c r="B29">
@@ -10219,14 +10219,14 @@
       <c r="D29" s="48"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="118"/>
+      <c r="A30" s="126"/>
       <c r="B30">
         <v>5.3</v>
       </c>
       <c r="D30" s="48"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="118">
+      <c r="A31" s="126">
         <v>5.6</v>
       </c>
       <c r="B31">
@@ -10235,14 +10235,14 @@
       <c r="D31" s="48"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="118"/>
+      <c r="A32" s="126"/>
       <c r="B32">
         <v>6</v>
       </c>
       <c r="D32" s="48"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="118">
+      <c r="A33" s="126">
         <v>6.3</v>
       </c>
       <c r="B33">
@@ -10251,14 +10251,14 @@
       <c r="D33" s="48"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="118"/>
+      <c r="A34" s="126"/>
       <c r="B34">
         <v>6.7</v>
       </c>
       <c r="D34" s="48"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="118">
+      <c r="A35" s="126">
         <v>7.1</v>
       </c>
       <c r="B35">
@@ -10267,14 +10267,14 @@
       <c r="D35" s="48"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="118"/>
+      <c r="A36" s="126"/>
       <c r="B36">
         <v>7.5</v>
       </c>
       <c r="D36" s="48"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="118">
+      <c r="A37" s="126">
         <v>8</v>
       </c>
       <c r="B37">
@@ -10283,14 +10283,14 @@
       <c r="D37" s="48"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="118"/>
+      <c r="A38" s="126"/>
       <c r="B38">
         <v>8.5</v>
       </c>
       <c r="D38" s="48"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="118">
+      <c r="A39" s="126">
         <v>9</v>
       </c>
       <c r="B39">
@@ -10299,7 +10299,7 @@
       <c r="D39" s="48"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="118"/>
+      <c r="A40" s="126"/>
       <c r="B40" s="61">
         <v>9.5</v>
       </c>
@@ -10307,7 +10307,7 @@
       <c r="E40" s="61"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="118">
+      <c r="A41" s="126">
         <v>10</v>
       </c>
       <c r="B41" s="48">
@@ -10315,13 +10315,13 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="118"/>
+      <c r="A42" s="126"/>
       <c r="B42" s="48">
         <v>10.5</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="118">
+      <c r="A43" s="126">
         <v>11</v>
       </c>
       <c r="B43" s="48">
@@ -10329,13 +10329,13 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="118"/>
+      <c r="A44" s="126"/>
       <c r="B44" s="48">
         <v>11.5</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="118">
+      <c r="A45" s="126">
         <v>12</v>
       </c>
       <c r="B45" s="48">
@@ -10343,13 +10343,13 @@
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="118"/>
+      <c r="A46" s="126"/>
       <c r="B46" s="48">
         <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="118">
+      <c r="A47" s="126">
         <v>14</v>
       </c>
       <c r="B47" s="48">
@@ -10357,13 +10357,13 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="118"/>
+      <c r="A48" s="126"/>
       <c r="B48" s="48">
         <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="118">
+      <c r="A49" s="126">
         <v>16</v>
       </c>
       <c r="B49" s="48">
@@ -10371,13 +10371,13 @@
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="118"/>
+      <c r="A50" s="126"/>
       <c r="B50" s="48">
         <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="118">
+      <c r="A51" s="126">
         <v>18</v>
       </c>
       <c r="B51" s="48">
@@ -10385,13 +10385,13 @@
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="118"/>
+      <c r="A52" s="126"/>
       <c r="B52" s="48">
         <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="118">
+      <c r="A53" s="126">
         <v>20</v>
       </c>
       <c r="B53" s="48">
@@ -10399,13 +10399,13 @@
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="118"/>
+      <c r="A54" s="126"/>
       <c r="B54" s="48">
         <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="118">
+      <c r="A55" s="126">
         <v>22</v>
       </c>
       <c r="B55" s="48">
@@ -10413,13 +10413,13 @@
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="118"/>
+      <c r="A56" s="126"/>
       <c r="B56" s="48">
         <v>24</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="118">
+      <c r="A57" s="126">
         <v>25</v>
       </c>
       <c r="B57" s="48">
@@ -10427,13 +10427,13 @@
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="118"/>
+      <c r="A58" s="126"/>
       <c r="B58" s="48">
         <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="118">
+      <c r="A59" s="126">
         <v>28</v>
       </c>
       <c r="B59" s="48">
@@ -10441,13 +10441,13 @@
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="118"/>
+      <c r="A60" s="126"/>
       <c r="B60" s="48">
         <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="118">
+      <c r="A61" s="126">
         <v>32</v>
       </c>
       <c r="B61" s="48">
@@ -10455,13 +10455,13 @@
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="118"/>
+      <c r="A62" s="126"/>
       <c r="B62" s="48">
         <v>34</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="118">
+      <c r="A63" s="126">
         <v>36</v>
       </c>
       <c r="B63" s="48">
@@ -10469,13 +10469,13 @@
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="118"/>
+      <c r="A64" s="126"/>
       <c r="B64" s="48">
         <v>38</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="118">
+      <c r="A65" s="126">
         <v>40</v>
       </c>
       <c r="B65" s="48">
@@ -10483,13 +10483,13 @@
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="118"/>
+      <c r="A66" s="126"/>
       <c r="B66" s="48">
         <v>42</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="118">
+      <c r="A67" s="126">
         <v>45</v>
       </c>
       <c r="B67" s="48">
@@ -10497,13 +10497,13 @@
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="118"/>
+      <c r="A68" s="126"/>
       <c r="B68" s="48">
         <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="118">
+      <c r="A69" s="126">
         <v>50</v>
       </c>
       <c r="B69" s="48">
@@ -10511,13 +10511,13 @@
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="118"/>
+      <c r="A70" s="126"/>
       <c r="B70" s="48">
         <v>53</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="118">
+      <c r="A71" s="126">
         <v>56</v>
       </c>
       <c r="B71" s="48">
@@ -10525,13 +10525,13 @@
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="118"/>
+      <c r="A72" s="126"/>
       <c r="B72" s="48">
         <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="118">
+      <c r="A73" s="126">
         <v>63</v>
       </c>
       <c r="B73" s="48">
@@ -10539,13 +10539,13 @@
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="118"/>
+      <c r="A74" s="126"/>
       <c r="B74" s="48">
         <v>67</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="118">
+      <c r="A75" s="126">
         <v>71</v>
       </c>
       <c r="B75" s="48">
@@ -10553,13 +10553,13 @@
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="118"/>
+      <c r="A76" s="126"/>
       <c r="B76" s="48">
         <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="118">
+      <c r="A77" s="126">
         <v>80</v>
       </c>
       <c r="B77" s="48">
@@ -10567,13 +10567,13 @@
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="118"/>
+      <c r="A78" s="126"/>
       <c r="B78" s="48">
         <v>85</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="118">
+      <c r="A79" s="126">
         <v>90</v>
       </c>
       <c r="B79" s="48">
@@ -10581,21 +10581,33 @@
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="118"/>
+      <c r="A80" s="126"/>
       <c r="B80" s="48">
         <v>95</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A35:A36"/>
     <mergeCell ref="A63:A64"/>
     <mergeCell ref="A41:A42"/>
     <mergeCell ref="A43:A44"/>
@@ -10608,26 +10620,14 @@
     <mergeCell ref="A57:A58"/>
     <mergeCell ref="A59:A60"/>
     <mergeCell ref="A61:A62"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="A75:A76"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Расчёт.xlsx
+++ b/Расчёт.xlsx
@@ -8,22 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Professional\Downloads\интститут\курсач детмаш\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A578623C-539C-44BE-AF24-FAA696F6196F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C47ED9DA-5D3A-4102-96FE-EE27852628FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="812" activeTab="2" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="812" activeTab="4" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
   </bookViews>
   <sheets>
     <sheet name="Электродвигатель" sheetId="1" r:id="rId1"/>
-    <sheet name="Передача" sheetId="2" r:id="rId2"/>
-    <sheet name="Вал" sheetId="4" r:id="rId3"/>
-    <sheet name="Установка" sheetId="9" r:id="rId4"/>
-    <sheet name="Вал-шестерня" sheetId="8" r:id="rId5"/>
-    <sheet name="Колесо" sheetId="7" r:id="rId6"/>
-    <sheet name="Вал колеса" sheetId="12" r:id="rId7"/>
-    <sheet name="Корпус" sheetId="3" r:id="rId8"/>
-    <sheet name="Ra40" sheetId="5" r:id="rId9"/>
-    <sheet name="Подшипники" sheetId="10" r:id="rId10"/>
-    <sheet name="Материалы" sheetId="11" r:id="rId11"/>
+    <sheet name="Вал" sheetId="4" r:id="rId2"/>
+    <sheet name="Передача" sheetId="2" r:id="rId3"/>
+    <sheet name="Колесо" sheetId="7" r:id="rId4"/>
+    <sheet name="Корпус" sheetId="3" r:id="rId5"/>
+    <sheet name="Ra40" sheetId="5" r:id="rId6"/>
+    <sheet name="Подшипники" sheetId="10" r:id="rId7"/>
+    <sheet name="Материалы" sheetId="11" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="345">
   <si>
     <t>Окружная сила</t>
   </si>
@@ -346,9 +343,6 @@
     <t>Момент двигателя</t>
   </si>
   <si>
-    <t>Мощность требуемая</t>
-  </si>
-  <si>
     <t>Н*м</t>
   </si>
   <si>
@@ -367,9 +361,6 @@
     <t>1/мин</t>
   </si>
   <si>
-    <t>об/с</t>
-  </si>
-  <si>
     <t>Диаметр барабана</t>
   </si>
   <si>
@@ -655,9 +646,6 @@
     <t>Диаметр от электродвигателя</t>
   </si>
   <si>
-    <t>Берём по Ra40 для всех диаметровв валов?</t>
-  </si>
-  <si>
     <t>a</t>
   </si>
   <si>
@@ -703,9 +691,6 @@
     <t>Шестерня (меньшая)</t>
   </si>
   <si>
-    <t>Вершины</t>
-  </si>
-  <si>
     <t>Дельтельный</t>
   </si>
   <si>
@@ -739,15 +724,6 @@
     <t>S</t>
   </si>
   <si>
-    <t>Шпонка не подходит из-за массовости</t>
-  </si>
-  <si>
-    <t>Шлицы</t>
-  </si>
-  <si>
-    <t>Соединение с натягом</t>
-  </si>
-  <si>
     <t>Установка - с натягом</t>
   </si>
   <si>
@@ -859,9 +835,6 @@
     <t>Диаметр подшипниковый</t>
   </si>
   <si>
-    <t>Ширина [мм]</t>
-  </si>
-  <si>
     <t>HRC</t>
   </si>
   <si>
@@ -922,48 +895,9 @@
     <t>ψт</t>
   </si>
   <si>
-    <t>Обозначение</t>
-  </si>
-  <si>
     <t>Перегрузка</t>
   </si>
   <si>
-    <t>Подшипник левый</t>
-  </si>
-  <si>
-    <t>Диаметр [мм]</t>
-  </si>
-  <si>
-    <t>Шероховатость [Ra]</t>
-  </si>
-  <si>
-    <t>Фаска [мм]</t>
-  </si>
-  <si>
-    <t>r [мм]</t>
-  </si>
-  <si>
-    <t>r1 [мм]</t>
-  </si>
-  <si>
-    <t>Проточка левая</t>
-  </si>
-  <si>
-    <t>Вал левый</t>
-  </si>
-  <si>
-    <t>Вал правый</t>
-  </si>
-  <si>
-    <t>Проточка правая</t>
-  </si>
-  <si>
-    <t>Вал установочный</t>
-  </si>
-  <si>
-    <t>Подшипник правый</t>
-  </si>
-  <si>
     <t>Врадин</t>
   </si>
   <si>
@@ -1003,13 +937,148 @@
     <t>C</t>
   </si>
   <si>
-    <t>страниа 178</t>
-  </si>
-  <si>
-    <t>фланец в приложении</t>
-  </si>
-  <si>
     <t>манжетта</t>
+  </si>
+  <si>
+    <t>Мощность электродвигателя</t>
+  </si>
+  <si>
+    <t>Номер</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Шариковый радиальный подшипник</t>
+  </si>
+  <si>
+    <t>Схема установки</t>
+  </si>
+  <si>
+    <t>Порядко расчёта:</t>
+  </si>
+  <si>
+    <t>Выбор схемы установки</t>
+  </si>
+  <si>
+    <t>Выбор линейки электродвигателей</t>
+  </si>
+  <si>
+    <t>Подбор схем редукторов</t>
+  </si>
+  <si>
+    <t>Выбор линейки выходных частот</t>
+  </si>
+  <si>
+    <t>Выбор из схем оптимальной</t>
+  </si>
+  <si>
+    <t>Получение параметров её ступеней</t>
+  </si>
+  <si>
+    <t>Расчёт необходимых диаметров валов</t>
+  </si>
+  <si>
+    <t>Выбор оптимальной передачи</t>
+  </si>
+  <si>
+    <t>Расчёт параметров передачи</t>
+  </si>
+  <si>
+    <t>Оценка длинн валов</t>
+  </si>
+  <si>
+    <t>Оценка расстояний внутри редуктора</t>
+  </si>
+  <si>
+    <t>Предварительный выбор типов подшипников</t>
+  </si>
+  <si>
+    <t>Построение предварительной схемы редуктора</t>
+  </si>
+  <si>
+    <t>Выбор шпонок для соединения с муфтами</t>
+  </si>
+  <si>
+    <t>Построение чертежей</t>
+  </si>
+  <si>
+    <t>Выбор и расчёт схемы установки колеса на вал</t>
+  </si>
+  <si>
+    <t>какая сталь на валы/колесо</t>
+  </si>
+  <si>
+    <t>Поверочный расчёт статическую прочность вала</t>
+  </si>
+  <si>
+    <t>Поверочный расчёт динамическую прочность вала</t>
+  </si>
+  <si>
+    <t>Поверочный расчёт на статическую нагрузку подшипников</t>
+  </si>
+  <si>
+    <t>Поверочный расчёт на динамическую нагрузку подшипников</t>
+  </si>
+  <si>
+    <t>Выбор маслянных крышек</t>
+  </si>
+  <si>
+    <t>Выбор фланцев валов</t>
+  </si>
+  <si>
+    <t>Выбор способа упора подшипников</t>
+  </si>
+  <si>
+    <t>об/мин</t>
+  </si>
+  <si>
+    <t>рад/с</t>
+  </si>
+  <si>
+    <t>Угловая скорость</t>
+  </si>
+  <si>
+    <t>Скорость максимальная</t>
+  </si>
+  <si>
+    <t>Выбор способа крепления к полу</t>
+  </si>
+  <si>
+    <t>Выбор базирования</t>
+  </si>
+  <si>
+    <t>Смазывание</t>
+  </si>
+  <si>
+    <t>Контактные напряжения</t>
+  </si>
+  <si>
+    <t>мм^2/с</t>
+  </si>
+  <si>
+    <t>Кинематическая вязкость</t>
+  </si>
+  <si>
+    <t>Марка масла</t>
+  </si>
+  <si>
+    <t>И-Л-А-22</t>
+  </si>
+  <si>
+    <t>Уровень погружения в масла</t>
+  </si>
+  <si>
+    <t>пластины с разводными концами</t>
+  </si>
+  <si>
+    <t>закладные пластины</t>
+  </si>
+  <si>
+    <t>Гидроизоляция?</t>
   </si>
 </sst>
 </file>
@@ -1237,7 +1306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -1528,9 +1597,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1558,104 +1624,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>167640</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>197527</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>75277</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Рисунок 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{835CBBC7-233D-4AED-93FF-512452705E27}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6621780" y="350520"/>
-          <a:ext cx="9402487" cy="7039957"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>274320</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>99060</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>59905</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>97436</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Рисунок 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DE2E17A-B778-4EDE-BCF9-B7ACBC0E7AAE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7246620" y="2842260"/>
-          <a:ext cx="6087325" cy="2010056"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1701,30 +1669,25 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
-      <xdr:colOff>567440</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>177879</xdr:rowOff>
+      <xdr:colOff>509485</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>181256</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Рисунок 1">
+        <xdr:cNvPr id="3" name="Рисунок 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C86946C7-18E7-4C53-9483-5AB1F1EDAB0D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EB75198-180E-4A11-98DA-449428551F1F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1733,15 +1696,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4648200" y="4206240"/>
-          <a:ext cx="11860280" cy="5115639"/>
+          <a:off x="7901940" y="7498080"/>
+          <a:ext cx="6087325" cy="2010056"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1750,6 +1713,11 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>16</xdr:col>
@@ -1777,7 +1745,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1798,14 +1766,14 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>234782</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1821,14 +1789,102 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:srcRect t="7827" b="38720"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4297680" y="289560"/>
+          <a:off x="4297680" y="114300"/>
           <a:ext cx="3343742" cy="2133600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>26838</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>127862</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Рисунок 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF972123-2ADA-4892-BA70-8980D338D121}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6233160" y="2339340"/>
+          <a:ext cx="1200318" cy="1629002"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>236220</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>392582</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>64959</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Рисунок 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89E0590C-E1AA-4409-868E-03578C912CFC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4884420" y="3284220"/>
+          <a:ext cx="1086002" cy="1352739"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2209,10 +2265,10 @@
         <v>31</v>
       </c>
       <c r="AJ2" s="8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AK2" s="29" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.3">
@@ -2238,7 +2294,7 @@
       <c r="M3" s="93"/>
       <c r="N3" s="110"/>
       <c r="Q3" s="99" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="R3" s="93"/>
       <c r="S3" s="93"/>
@@ -2253,7 +2309,7 @@
         <v>0.97</v>
       </c>
       <c r="AC3" s="99" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AD3" s="93"/>
       <c r="AE3" s="93"/>
@@ -2557,7 +2613,7 @@
       <c r="F8" s="4"/>
       <c r="G8" s="5"/>
       <c r="I8" s="99" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="J8" s="93"/>
       <c r="K8" s="108">
@@ -2863,9 +2919,22 @@
       </c>
       <c r="G15" s="5"/>
     </row>
-    <row r="19" spans="9:26" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B18" s="66" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B19" s="66" t="s">
+        <v>306</v>
+      </c>
       <c r="I19" s="107" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J19" s="115"/>
       <c r="K19" s="107">
@@ -2893,9 +2962,12 @@
       <c r="Y19" s="100"/>
       <c r="Z19" s="115"/>
     </row>
-    <row r="20" spans="9:26" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B20" s="66" t="s">
+        <v>308</v>
+      </c>
       <c r="I20" s="103" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J20" s="127"/>
       <c r="K20" s="12" t="s">
@@ -2947,7 +3019,10 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="9:26" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B21" s="66" t="s">
+        <v>307</v>
+      </c>
       <c r="I21" s="99">
         <v>0.37</v>
       </c>
@@ -2985,7 +3060,10 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="3"/>
     </row>
-    <row r="22" spans="9:26" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B22" s="66" t="s">
+        <v>309</v>
+      </c>
       <c r="I22" s="99">
         <v>0.55000000000000004</v>
       </c>
@@ -3021,7 +3099,10 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="3"/>
     </row>
-    <row r="23" spans="9:26" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B23" s="66" t="s">
+        <v>310</v>
+      </c>
       <c r="I23" s="99">
         <v>0.75</v>
       </c>
@@ -3057,7 +3138,10 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="3"/>
     </row>
-    <row r="24" spans="9:26" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B24" s="66" t="s">
+        <v>311</v>
+      </c>
       <c r="I24" s="99">
         <v>1.1000000000000001</v>
       </c>
@@ -3093,7 +3177,10 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="3"/>
     </row>
-    <row r="25" spans="9:26" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B25" s="66" t="s">
+        <v>313</v>
+      </c>
       <c r="I25" s="99">
         <v>1.5</v>
       </c>
@@ -3129,7 +3216,10 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="3"/>
     </row>
-    <row r="26" spans="9:26" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B26" s="66" t="s">
+        <v>312</v>
+      </c>
       <c r="I26" s="99">
         <v>2.2000000000000002</v>
       </c>
@@ -3165,7 +3255,10 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="3"/>
     </row>
-    <row r="27" spans="9:26" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B27" s="66" t="s">
+        <v>315</v>
+      </c>
       <c r="I27" s="99">
         <v>3</v>
       </c>
@@ -3199,7 +3292,10 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="3"/>
     </row>
-    <row r="28" spans="9:26" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B28" s="66" t="s">
+        <v>316</v>
+      </c>
       <c r="I28" s="99">
         <v>4</v>
       </c>
@@ -3233,7 +3329,13 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="3"/>
     </row>
-    <row r="29" spans="9:26" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>135</v>
+      </c>
+      <c r="B29" t="s">
+        <v>328</v>
+      </c>
       <c r="I29" s="99">
         <v>5.5</v>
       </c>
@@ -3287,7 +3389,10 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="30" spans="9:26" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>327</v>
+      </c>
       <c r="I30" s="99">
         <v>7.5</v>
       </c>
@@ -3341,7 +3446,10 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="31" spans="9:26" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>314</v>
+      </c>
       <c r="I31" s="99">
         <v>11</v>
       </c>
@@ -3395,7 +3503,10 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="32" spans="9:26" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>317</v>
+      </c>
       <c r="I32" s="99">
         <v>15</v>
       </c>
@@ -3464,6 +3575,9 @@
       <c r="Z33" s="3"/>
     </row>
     <row r="34" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>320</v>
+      </c>
       <c r="I34" s="99">
         <v>22</v>
       </c>
@@ -3532,8 +3646,11 @@
       <c r="Z35" s="5"/>
     </row>
     <row r="36" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>318</v>
+      </c>
       <c r="G36" s="126" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H36" s="126"/>
       <c r="I36" s="116">
@@ -3606,8 +3723,15 @@
         <v>0.85</v>
       </c>
     </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>322</v>
+      </c>
+    </row>
     <row r="38" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B38" s="1"/>
+      <c r="B38" t="s">
+        <v>323</v>
+      </c>
       <c r="C38" s="16"/>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
@@ -3636,7 +3760,9 @@
       <c r="Z38" s="6"/>
     </row>
     <row r="39" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B39" s="16"/>
+      <c r="B39" s="1" t="s">
+        <v>324</v>
+      </c>
       <c r="C39" s="16"/>
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
@@ -3677,21 +3803,23 @@
       </c>
     </row>
     <row r="40" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B40" s="16"/>
+      <c r="B40" s="1" t="s">
+        <v>325</v>
+      </c>
       <c r="C40" s="16"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="99" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H40" s="93"/>
       <c r="I40" s="93" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J40" s="110"/>
       <c r="K40" s="27" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="L40" s="4" t="s">
         <v>72</v>
@@ -3701,7 +3829,7 @@
         <v>27</v>
       </c>
       <c r="O40" s="27" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="P40" s="4" t="s">
         <v>72</v>
@@ -3711,7 +3839,7 @@
         <v>27</v>
       </c>
       <c r="S40" s="27" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="T40" s="4" t="s">
         <v>72</v>
@@ -3721,7 +3849,7 @@
         <v>27</v>
       </c>
       <c r="W40" s="27" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="X40" s="4" t="s">
         <v>72</v>
@@ -3732,7 +3860,6 @@
       </c>
     </row>
     <row r="41" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -3755,15 +3882,15 @@
         <v>Прямозубая 2</v>
       </c>
       <c r="M41" s="31">
-        <f t="shared" ref="M41:M46" ca="1" si="6">IF(K41&lt;&gt;"-",SUMIF($AC:$AE,L41,$AJ:$AJ)-K41*SUMIF($AC:$AE,L41,$AK:$AK),0)</f>
+        <f ca="1">IF(K41&lt;&gt;"-",SUMIF($AC:$AE,L41,$AJ:$AJ)-K41*SUMIF($AC:$AE,L41,$AK:$AK),0)</f>
         <v>0.95497170733270809</v>
       </c>
       <c r="N41" s="8">
-        <f t="shared" ref="N41:N46" ca="1" si="7">M41*N$39</f>
+        <f ca="1">M41*N$39</f>
         <v>0.78204599858607271</v>
       </c>
       <c r="O41" s="38">
-        <f t="shared" ref="O41:O46" si="8">IF($I41,P$36/$I41,"-")</f>
+        <f t="shared" ref="O41:O46" si="6">IF($I41,P$36/$I41,"-")</f>
         <v>7.5398223686155026</v>
       </c>
       <c r="P41" s="39" t="str">
@@ -3771,15 +3898,15 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="Q41" s="40">
-        <f t="shared" ref="Q41:Q46" ca="1" si="9">IF(O41&lt;&gt;"-",SUMIF($AC:$AE,P41,$AJ:$AJ)-O41*SUMIF($AC:$AE,P41,$AK:$AK),0)</f>
+        <f ca="1">IF(O41&lt;&gt;"-",SUMIF($AC:$AE,P41,$AJ:$AJ)-O41*SUMIF($AC:$AE,P41,$AK:$AK),0)</f>
         <v>0.96143805509807656</v>
       </c>
       <c r="R41" s="39">
-        <f t="shared" ref="R41:R46" ca="1" si="10">Q41*R$39</f>
+        <f ca="1">Q41*R$39</f>
         <v>0.78915140422920127</v>
       </c>
       <c r="S41" s="15">
-        <f t="shared" ref="S41:S46" si="11">IF($I41,T$36/$I41,"-")</f>
+        <f t="shared" ref="S41:S46" si="7">IF($I41,T$36/$I41,"-")</f>
         <v>5.0265482457436681</v>
       </c>
       <c r="T41" s="8" t="str">
@@ -3787,15 +3914,15 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="U41" s="31">
-        <f t="shared" ref="U41:U46" ca="1" si="12">IF(S41&lt;&gt;"-",SUMIF($AC:$AE,T41,$AJ:$AJ)-S41*SUMIF($AC:$AE,T41,$AK:$AK),0)</f>
+        <f ca="1">IF(S41&lt;&gt;"-",SUMIF($AC:$AE,T41,$AJ:$AJ)-S41*SUMIF($AC:$AE,T41,$AK:$AK),0)</f>
         <v>0.969292036732051</v>
       </c>
       <c r="V41" s="8">
-        <f t="shared" ref="V41:V46" ca="1" si="13">U41*V$39</f>
+        <f ca="1">U41*V$39</f>
         <v>0.78464938124108341</v>
       </c>
       <c r="W41" s="15">
-        <f t="shared" ref="W41:W46" si="14">IF($I41,X$36/$I41,"-")</f>
+        <f t="shared" ref="W41:W46" si="8">IF($I41,X$36/$I41,"-")</f>
         <v>3.8065630985996322</v>
       </c>
       <c r="X41" s="8" t="str">
@@ -3803,16 +3930,18 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="Y41" s="31">
-        <f t="shared" ref="Y41:Y46" ca="1" si="15">IF(W41&lt;&gt;"-",SUMIF($AC:$AE,X41,$AJ:$AJ)-W41*SUMIF($AC:$AE,X41,$AK:$AK),0)</f>
+        <f ca="1">IF(W41&lt;&gt;"-",SUMIF($AC:$AE,X41,$AJ:$AJ)-W41*SUMIF($AC:$AE,X41,$AK:$AK),0)</f>
         <v>0.97310449031687618</v>
       </c>
       <c r="Z41" s="6">
-        <f t="shared" ref="Z41:Z46" ca="1" si="16">Y41*Z$39</f>
+        <f ca="1">Y41*Z$39</f>
         <v>0.77857587564473563</v>
       </c>
     </row>
     <row r="42" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B42" s="1"/>
+      <c r="B42" s="25" t="s">
+        <v>333</v>
+      </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -3835,28 +3964,28 @@
         <v>Прямозубая 2</v>
       </c>
       <c r="M42" s="30">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(K42&lt;&gt;"-",SUMIF($AC:$AE,L42,$AJ:$AJ)-K42*SUMIF($AC:$AE,L42,$AK:$AK),0)</f>
         <v>0.94723305521851664</v>
       </c>
       <c r="N42" s="1">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">M42*N$39</f>
         <v>0.77570865699376879</v>
       </c>
       <c r="O42" s="34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>9.4247779607693793</v>
       </c>
       <c r="P42" s="25"/>
       <c r="Q42" s="35">
-        <f t="shared" ca="1" si="9"/>
+        <f ca="1">IF(O42&lt;&gt;"-",SUMIF($AC:$AE,P42,$AJ:$AJ)-O42*SUMIF($AC:$AE,P42,$AK:$AK),0)</f>
         <v>0</v>
       </c>
       <c r="R42" s="25">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">Q42*R$39</f>
         <v>0</v>
       </c>
       <c r="S42" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>6.2831853071795862</v>
       </c>
       <c r="T42" s="1" t="str">
@@ -3864,15 +3993,15 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="U42" s="30">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(S42&lt;&gt;"-",SUMIF($AC:$AE,T42,$AJ:$AJ)-S42*SUMIF($AC:$AE,T42,$AK:$AK),0)</f>
         <v>0.96536504591506378</v>
       </c>
       <c r="V42" s="1">
-        <f t="shared" ca="1" si="13"/>
+        <f ca="1">U42*V$39</f>
         <v>0.78147045188035424</v>
       </c>
       <c r="W42" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="8"/>
         <v>4.7582038732495402</v>
       </c>
       <c r="X42" s="1" t="str">
@@ -3880,16 +4009,18 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="Y42" s="30">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(W42&lt;&gt;"-",SUMIF($AC:$AE,X42,$AJ:$AJ)-W42*SUMIF($AC:$AE,X42,$AK:$AK),0)</f>
         <v>0.97013061289609515</v>
       </c>
       <c r="Z42" s="3">
-        <f t="shared" ca="1" si="16"/>
+        <f ca="1">Y42*Z$39</f>
         <v>0.77619649168341942</v>
       </c>
     </row>
     <row r="43" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B43" s="1"/>
+      <c r="B43" s="25" t="s">
+        <v>326</v>
+      </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -3912,28 +4043,28 @@
         <v>Прямозубая 2</v>
       </c>
       <c r="M43" s="30">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(K43&lt;&gt;"-",SUMIF($AC:$AE,L43,$AJ:$AJ)-K43*SUMIF($AC:$AE,L43,$AK:$AK),0)</f>
         <v>0.93755974007577747</v>
       </c>
       <c r="N43" s="1">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">M43*N$39</f>
         <v>0.76778698000338896</v>
       </c>
       <c r="O43" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>11.780972450961723</v>
       </c>
       <c r="P43" s="1"/>
       <c r="Q43" s="30">
-        <f t="shared" ca="1" si="9"/>
+        <f ca="1">IF(O43&lt;&gt;"-",SUMIF($AC:$AE,P43,$AJ:$AJ)-O43*SUMIF($AC:$AE,P43,$AK:$AK),0)</f>
         <v>0</v>
       </c>
       <c r="R43" s="1">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">Q43*R$39</f>
         <v>0</v>
       </c>
       <c r="S43" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>7.8539816339744819</v>
       </c>
       <c r="T43" s="1" t="str">
@@ -3941,15 +4072,15 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="U43" s="30">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(S43&lt;&gt;"-",SUMIF($AC:$AE,T43,$AJ:$AJ)-S43*SUMIF($AC:$AE,T43,$AK:$AK),0)</f>
         <v>0.9604563073938297</v>
       </c>
       <c r="V43" s="1">
-        <f t="shared" ca="1" si="13"/>
+        <f ca="1">U43*V$39</f>
         <v>0.77749679017944284</v>
       </c>
       <c r="W43" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="8"/>
         <v>5.9477548415619257</v>
       </c>
       <c r="X43" s="1" t="str">
@@ -3957,16 +4088,15 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="Y43" s="30">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(W43&lt;&gt;"-",SUMIF($AC:$AE,X43,$AJ:$AJ)-W43*SUMIF($AC:$AE,X43,$AK:$AK),0)</f>
         <v>0.96641326612011891</v>
       </c>
       <c r="Z43" s="3">
-        <f t="shared" ca="1" si="16"/>
+        <f ca="1">Y43*Z$39</f>
         <v>0.77322226173177433</v>
       </c>
     </row>
     <row r="44" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -3989,55 +4119,57 @@
         <v>Прямозубая 2</v>
       </c>
       <c r="M44" s="30">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(K44&lt;&gt;"-",SUMIF($AC:$AE,L44,$AJ:$AJ)-K44*SUMIF($AC:$AE,L44,$AK:$AK),0)</f>
         <v>0.92498443039021649</v>
       </c>
       <c r="N44" s="1">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">M44*N$39</f>
         <v>0.75748879991589524</v>
       </c>
       <c r="O44" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>14.844025288211771</v>
       </c>
       <c r="P44" s="1"/>
       <c r="Q44" s="30">
-        <f t="shared" ca="1" si="9"/>
+        <f ca="1">IF(O44&lt;&gt;"-",SUMIF($AC:$AE,P44,$AJ:$AJ)-O44*SUMIF($AC:$AE,P44,$AK:$AK),0)</f>
         <v>0</v>
       </c>
       <c r="R44" s="1">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">Q44*R$39</f>
         <v>0</v>
       </c>
       <c r="S44" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>9.8960168588078474</v>
       </c>
       <c r="T44" s="1"/>
       <c r="U44" s="30">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(S44&lt;&gt;"-",SUMIF($AC:$AE,T44,$AJ:$AJ)-S44*SUMIF($AC:$AE,T44,$AK:$AK),0)</f>
         <v>0</v>
       </c>
       <c r="V44" s="1">
-        <f t="shared" ca="1" si="13"/>
+        <f ca="1">U44*V$39</f>
         <v>0</v>
       </c>
       <c r="W44" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="8"/>
         <v>7.4941711003680265</v>
       </c>
       <c r="X44" s="1"/>
       <c r="Y44" s="30">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(W44&lt;&gt;"-",SUMIF($AC:$AE,X44,$AJ:$AJ)-W44*SUMIF($AC:$AE,X44,$AK:$AK),0)</f>
         <v>0</v>
       </c>
       <c r="Z44" s="3">
-        <f t="shared" ca="1" si="16"/>
+        <f ca="1">Y44*Z$39</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B45" s="1"/>
+      <c r="B45" s="1" t="s">
+        <v>334</v>
+      </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -4057,55 +4189,57 @@
       </c>
       <c r="L45" s="1"/>
       <c r="M45" s="30">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(K45&lt;&gt;"-",SUMIF($AC:$AE,L45,$AJ:$AJ)-K45*SUMIF($AC:$AE,L45,$AK:$AK),0)</f>
         <v>0</v>
       </c>
       <c r="N45" s="1">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">M45*N$39</f>
         <v>0</v>
       </c>
       <c r="O45" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>18.849555921538759</v>
       </c>
       <c r="P45" s="1"/>
       <c r="Q45" s="30">
-        <f t="shared" ca="1" si="9"/>
+        <f ca="1">IF(O45&lt;&gt;"-",SUMIF($AC:$AE,P45,$AJ:$AJ)-O45*SUMIF($AC:$AE,P45,$AK:$AK),0)</f>
         <v>0</v>
       </c>
       <c r="R45" s="1">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">Q45*R$39</f>
         <v>0</v>
       </c>
       <c r="S45" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>12.566370614359172</v>
       </c>
       <c r="T45" s="1"/>
       <c r="U45" s="30">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(S45&lt;&gt;"-",SUMIF($AC:$AE,T45,$AJ:$AJ)-S45*SUMIF($AC:$AE,T45,$AK:$AK),0)</f>
         <v>0</v>
       </c>
       <c r="V45" s="1">
-        <f t="shared" ca="1" si="13"/>
+        <f ca="1">U45*V$39</f>
         <v>0</v>
       </c>
       <c r="W45" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="8"/>
         <v>9.5164077464990804</v>
       </c>
       <c r="X45" s="1"/>
       <c r="Y45" s="30">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(W45&lt;&gt;"-",SUMIF($AC:$AE,X45,$AJ:$AJ)-W45*SUMIF($AC:$AE,X45,$AK:$AK),0)</f>
         <v>0</v>
       </c>
       <c r="Z45" s="3">
-        <f t="shared" ca="1" si="16"/>
+        <f ca="1">Y45*Z$39</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B46" s="1"/>
+      <c r="B46" s="49" t="s">
+        <v>319</v>
+      </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -4124,18 +4258,18 @@
         <v>47.369326729908593</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M46" s="32">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">IF(K46&lt;&gt;"-",SUMIF($AC:$AE,L46,$AJ:$AJ)-K46*SUMIF($AC:$AE,L46,$AK:$AK),0)</f>
         <v>0</v>
       </c>
       <c r="N46" s="4">
-        <f t="shared" ca="1" si="7"/>
+        <f ca="1">M46*N$39</f>
         <v>0</v>
       </c>
       <c r="O46" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>23.561944901923447</v>
       </c>
       <c r="P46" s="37" t="str">
@@ -4143,15 +4277,15 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="Q46" s="32">
-        <f t="shared" ca="1" si="9"/>
+        <f ca="1">IF(O46&lt;&gt;"-",SUMIF($AC:$AE,P46,$AJ:$AJ)-O46*SUMIF($AC:$AE,P46,$AK:$AK),0)</f>
         <v>0.91136892218148913</v>
       </c>
       <c r="R46" s="4">
-        <f t="shared" ca="1" si="10"/>
+        <f ca="1">Q46*R$39</f>
         <v>0.74805450116805416</v>
       </c>
       <c r="S46" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>15.707963267948964</v>
       </c>
       <c r="T46" s="4" t="str">
@@ -4159,15 +4293,15 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="U46" s="32">
-        <f t="shared" ca="1" si="12"/>
+        <f ca="1">IF(S46&lt;&gt;"-",SUMIF($AC:$AE,T46,$AJ:$AJ)-S46*SUMIF($AC:$AE,T46,$AK:$AK),0)</f>
         <v>0.93591261478765941</v>
       </c>
       <c r="V46" s="4">
-        <f t="shared" ca="1" si="13"/>
+        <f ca="1">U46*V$39</f>
         <v>0.75762848167488572</v>
       </c>
       <c r="W46" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="8"/>
         <v>11.895509683123851</v>
       </c>
       <c r="X46" s="4" t="str">
@@ -4175,11 +4309,11 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="Y46" s="32">
-        <f t="shared" ca="1" si="15"/>
+        <f ca="1">IF(W46&lt;&gt;"-",SUMIF($AC:$AE,X46,$AJ:$AJ)-W46*SUMIF($AC:$AE,X46,$AK:$AK),0)</f>
         <v>0.94782653224023794</v>
       </c>
       <c r="Z46" s="5">
-        <f t="shared" ca="1" si="16"/>
+        <f ca="1">Y46*Z$39</f>
         <v>0.75835111197354876</v>
       </c>
     </row>
@@ -4212,7 +4346,7 @@
     </row>
     <row r="48" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B48" s="107" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C48" s="100"/>
       <c r="D48" s="100"/>
@@ -4288,7 +4422,7 @@
         <v>1440</v>
       </c>
       <c r="G50" s="50" t="s">
-        <v>105</v>
+        <v>329</v>
       </c>
       <c r="H50" s="16"/>
       <c r="P50" s="1"/>
@@ -4300,7 +4434,7 @@
     </row>
     <row r="51" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B51" s="99" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C51" s="93"/>
       <c r="D51" s="93"/>
@@ -4310,30 +4444,30 @@
         <v>150.79644737231007</v>
       </c>
       <c r="G51" s="50" t="s">
-        <v>106</v>
+        <v>330</v>
       </c>
       <c r="H51" s="16"/>
       <c r="I51" s="116" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J51" s="118"/>
       <c r="K51" s="33" t="s">
         <v>27</v>
       </c>
       <c r="L51" s="100" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M51" s="100"/>
       <c r="N51" s="97" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="O51" s="97"/>
       <c r="P51" s="100" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Q51" s="100"/>
       <c r="R51" s="97" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="S51" s="97"/>
       <c r="T51" s="49"/>
@@ -4355,11 +4489,11 @@
         <v>190.98593171027443</v>
       </c>
       <c r="G52" s="50" t="s">
-        <v>105</v>
+        <v>329</v>
       </c>
       <c r="H52" s="16"/>
       <c r="I52" s="99" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J52" s="93"/>
       <c r="K52" s="42">
@@ -4376,13 +4510,13 @@
       </c>
       <c r="O52" s="95"/>
       <c r="P52" s="101">
-        <f ca="1">F55</f>
-        <v>46.89699496864425</v>
+        <f>F55</f>
+        <v>49.735919716217296</v>
       </c>
       <c r="Q52" s="101"/>
       <c r="R52" s="97">
-        <f t="shared" ref="R52:R57" ca="1" si="17">P52*N52*PI()/1000/30</f>
-        <v>7.0719002337086527</v>
+        <f t="shared" ref="R52:R57" si="9">P52*N52*PI()/1000/30</f>
+        <v>7.5000000000000009</v>
       </c>
       <c r="S52" s="97"/>
       <c r="T52" s="16"/>
@@ -4393,7 +4527,7 @@
     </row>
     <row r="53" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B53" s="99" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C53" s="93"/>
       <c r="D53" s="93"/>
@@ -4424,13 +4558,13 @@
       </c>
       <c r="O53" s="96"/>
       <c r="P53" s="94">
-        <f ca="1">P52*L53*K53</f>
-        <v>45.959055069271365</v>
+        <f>P52*L53*K53</f>
+        <v>48.741201321892952</v>
       </c>
       <c r="Q53" s="94"/>
       <c r="R53" s="98">
-        <f t="shared" ca="1" si="17"/>
-        <v>6.9304622290344788</v>
+        <f t="shared" si="9"/>
+        <v>7.3500000000000005</v>
       </c>
       <c r="S53" s="98"/>
       <c r="T53" s="1"/>
@@ -4448,11 +4582,11 @@
       <c r="D54" s="93"/>
       <c r="E54" s="93"/>
       <c r="F54" s="44">
-        <f>E2*F53/2</f>
-        <v>320</v>
+        <f ca="1">F55*F49*PRODUCT(K53:K57)</f>
+        <v>339.37130342425513</v>
       </c>
       <c r="G54" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H54" s="16"/>
       <c r="I54" s="99" t="s">
@@ -4473,13 +4607,13 @@
       </c>
       <c r="O54" s="96"/>
       <c r="P54" s="94">
-        <f ca="1">P53*L54*K54</f>
-        <v>45.499464518578648</v>
+        <f>P53*L54*K54</f>
+        <v>48.253789308674023</v>
       </c>
       <c r="Q54" s="94"/>
       <c r="R54" s="98">
-        <f t="shared" ca="1" si="17"/>
-        <v>6.8611576067441344</v>
+        <f t="shared" si="9"/>
+        <v>7.2765000000000004</v>
       </c>
       <c r="S54" s="98"/>
       <c r="T54" s="1"/>
@@ -4498,11 +4632,11 @@
       <c r="D55" s="93"/>
       <c r="E55" s="93"/>
       <c r="F55" s="1">
-        <f ca="1">F54/F59/F49</f>
-        <v>46.89699496864425</v>
+        <f>F56/F51*1000</f>
+        <v>49.735919716217296</v>
       </c>
       <c r="G55" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H55" s="16"/>
       <c r="I55" s="99" t="s">
@@ -4525,12 +4659,12 @@
       <c r="O55" s="94"/>
       <c r="P55" s="102">
         <f ca="1">P54*L55*K55</f>
-        <v>329.82890125747264</v>
+        <v>349.79520039605768</v>
       </c>
       <c r="Q55" s="102"/>
       <c r="R55" s="98">
-        <f t="shared" ca="1" si="17"/>
-        <v>6.5965780251494532</v>
+        <f ca="1">P55*N55*PI()/1000/30</f>
+        <v>6.9959040079211547</v>
       </c>
       <c r="S55" s="98"/>
       <c r="T55" s="1"/>
@@ -4543,17 +4677,17 @@
     </row>
     <row r="56" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B56" s="99" t="s">
-        <v>99</v>
+        <v>298</v>
       </c>
       <c r="C56" s="93"/>
       <c r="D56" s="93"/>
       <c r="E56" s="93"/>
       <c r="F56" s="1">
-        <f ca="1">F55*F51/1000</f>
-        <v>7.0719002337086527</v>
+        <f>I36</f>
+        <v>7.5</v>
       </c>
       <c r="G56" s="50" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I56" s="99" t="s">
         <v>28</v>
@@ -4574,12 +4708,12 @@
       <c r="O56" s="94"/>
       <c r="P56" s="102">
         <f ca="1">P55*L56*K56</f>
-        <v>323.23232323232315</v>
+        <v>342.7992963881365</v>
       </c>
       <c r="Q56" s="102"/>
       <c r="R56" s="98">
-        <f t="shared" ca="1" si="17"/>
-        <v>6.4646464646464636</v>
+        <f ca="1">P56*N56*PI()/1000/30</f>
+        <v>6.8559859277627302</v>
       </c>
       <c r="S56" s="98"/>
       <c r="T56" s="1"/>
@@ -4588,7 +4722,7 @@
     </row>
     <row r="57" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B57" s="99" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C57" s="93"/>
       <c r="D57" s="93"/>
@@ -4617,12 +4751,12 @@
       <c r="O57" s="94"/>
       <c r="P57" s="102">
         <f ca="1">P56*L57*K57</f>
-        <v>319.99999999999994</v>
+        <v>339.37130342425513</v>
       </c>
       <c r="Q57" s="102"/>
       <c r="R57" s="98">
-        <f t="shared" ca="1" si="17"/>
-        <v>6.3999999999999995</v>
+        <f ca="1">P57*N57*PI()/1000/30</f>
+        <v>6.7874260684851038</v>
       </c>
       <c r="S57" s="98"/>
       <c r="T57" s="1"/>
@@ -4631,7 +4765,7 @@
     </row>
     <row r="58" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B58" s="99" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C58" s="93"/>
       <c r="D58" s="93"/>
@@ -4642,7 +4776,7 @@
       </c>
       <c r="G58" s="50"/>
       <c r="I58" s="103" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J58" s="104"/>
       <c r="K58" s="12"/>
@@ -4655,7 +4789,7 @@
       <c r="O58" s="105"/>
       <c r="P58" s="106">
         <f ca="1">P57</f>
-        <v>319.99999999999994</v>
+        <v>339.37130342425513</v>
       </c>
       <c r="Q58" s="106"/>
       <c r="R58" s="4"/>
@@ -4666,7 +4800,7 @@
     </row>
     <row r="59" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B59" s="99" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C59" s="93"/>
       <c r="D59" s="93"/>
@@ -4679,7 +4813,7 @@
     </row>
     <row r="60" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B60" s="99" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C60" s="93"/>
       <c r="D60" s="93"/>
@@ -4692,7 +4826,7 @@
     </row>
     <row r="61" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B61" s="93" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C61" s="93"/>
       <c r="D61" s="93"/>
@@ -4880,794 +5014,715 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D136A9F2-8845-4295-A8BD-25F04BE0EFA0}">
-  <dimension ref="A1:T34"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A416109-A6F9-42CB-B875-F300C0970630}">
+  <dimension ref="A2:U29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="23" width="6.77734375" customWidth="1"/>
+    <col min="1" max="27" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>4</v>
-      </c>
-      <c r="E2" s="93" t="s">
-        <v>228</v>
-      </c>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="126" t="s">
-        <v>266</v>
-      </c>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="126" t="s">
+        <v>173</v>
+      </c>
+      <c r="B2" s="126"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="126"/>
+      <c r="H2" s="126" t="s">
+        <v>186</v>
+      </c>
+      <c r="I2" s="126"/>
+      <c r="J2" s="126"/>
       <c r="K2" s="126"/>
       <c r="L2" s="126"/>
-      <c r="M2" s="126"/>
-      <c r="N2" s="126"/>
       <c r="P2" s="126" t="s">
-        <v>267</v>
+        <v>185</v>
       </c>
       <c r="Q2" s="126"/>
       <c r="R2" s="126"/>
       <c r="S2" s="126"/>
       <c r="T2" s="126"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>5</v>
-      </c>
-      <c r="E3" s="132" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="132"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="60">
-        <f>Передача!$D$49</f>
-        <v>2016</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="J3" s="48" t="s">
-        <v>72</v>
-      </c>
-      <c r="K3" t="s">
-        <v>268</v>
-      </c>
-      <c r="P3" s="48" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>6</v>
-      </c>
-      <c r="E4" s="132" t="s">
-        <v>159</v>
-      </c>
-      <c r="F4" s="132"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="60">
-        <f>Передача!$D$50</f>
-        <v>734</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="J4" t="s">
-        <v>23</v>
-      </c>
-      <c r="P4" s="126" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q4" s="126"/>
-      <c r="R4" s="126"/>
-      <c r="S4">
-        <f ca="1">Вал!S15</f>
-        <v>45</v>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="126" t="s">
+        <v>172</v>
+      </c>
+      <c r="B3" s="126"/>
+      <c r="D3" s="61">
+        <f>Электродвигатель!$P$53</f>
+        <v>48.741201321892952</v>
+      </c>
+      <c r="E3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3" s="93" t="s">
+        <v>172</v>
+      </c>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="63">
+        <f>D3</f>
+        <v>48.741201321892952</v>
+      </c>
+      <c r="L3" t="s">
+        <v>99</v>
+      </c>
+      <c r="P3" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="R3" s="16"/>
+      <c r="S3">
+        <f ca="1">Электродвигатель!P55</f>
+        <v>349.79520039605768</v>
+      </c>
+      <c r="T3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="126" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="126"/>
+      <c r="D4" s="62">
+        <f>Электродвигатель!$N$52</f>
+        <v>1440</v>
+      </c>
+      <c r="E4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H4" s="93" t="s">
+        <v>70</v>
+      </c>
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="64">
+        <f>D4</f>
+        <v>1440</v>
+      </c>
+      <c r="L4" t="s">
+        <v>329</v>
+      </c>
+      <c r="P4" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="61">
+        <f>Электродвигатель!N55</f>
+        <v>190.98593171027443</v>
       </c>
       <c r="T4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>7</v>
-      </c>
-      <c r="E5" s="132" t="s">
-        <v>160</v>
-      </c>
-      <c r="F5" s="132"/>
-      <c r="G5" s="132"/>
-      <c r="H5" s="60">
-        <f>Передача!$D$51</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="J5" s="126" t="s">
-        <v>120</v>
-      </c>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="H5" s="126" t="s">
+        <v>176</v>
+      </c>
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
       <c r="K5" s="126"/>
       <c r="L5" s="126"/>
-      <c r="M5">
-        <f ca="1">Вал!K16</f>
+      <c r="P5" s="126" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q5" s="126"/>
+      <c r="R5" s="126"/>
+      <c r="S5" s="126"/>
+      <c r="T5" s="126"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="126" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" s="126"/>
+      <c r="C6" s="126"/>
+      <c r="D6" s="66">
+        <f>Электродвигатель!$F$61</f>
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="126" t="s">
+        <v>175</v>
+      </c>
+      <c r="I6" s="126"/>
+      <c r="J6" s="126"/>
+      <c r="K6">
+        <f>Передача!D55</f>
+        <v>37.75</v>
+      </c>
+      <c r="L6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P6" s="126" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q6" s="126"/>
+      <c r="R6" s="126"/>
+      <c r="S6">
+        <f>Передача!D60</f>
+        <v>309.75</v>
+      </c>
+      <c r="T6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="145" t="s">
+        <v>198</v>
+      </c>
+      <c r="B7" s="145"/>
+      <c r="C7" s="145"/>
+      <c r="D7" s="52">
+        <v>0.8</v>
+      </c>
+      <c r="H7" s="126" t="s">
+        <v>184</v>
+      </c>
+      <c r="I7" s="126"/>
+      <c r="J7" s="126"/>
+      <c r="K7">
+        <f>Передача!D54</f>
+        <v>49</v>
+      </c>
+      <c r="L7" t="s">
+        <v>16</v>
+      </c>
+      <c r="P7" s="126" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q7" s="126"/>
+      <c r="R7" s="126"/>
+      <c r="S7">
+        <f>Передача!D59</f>
+        <v>321</v>
+      </c>
+      <c r="T7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="126" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="126"/>
+      <c r="C8" s="126"/>
+      <c r="D8" s="71">
+        <v>1.2</v>
+      </c>
+      <c r="H8" s="126" t="s">
+        <v>165</v>
+      </c>
+      <c r="I8" s="126"/>
+      <c r="J8" s="126"/>
+      <c r="K8">
+        <f>Передача!D56</f>
+        <v>62</v>
+      </c>
+      <c r="L8" t="s">
+        <v>16</v>
+      </c>
+      <c r="P8" s="126" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q8" s="126"/>
+      <c r="R8" s="126"/>
+      <c r="S8">
+        <f>Передача!D61</f>
+        <v>57</v>
+      </c>
+      <c r="T8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="H9" s="126" t="s">
+        <v>187</v>
+      </c>
+      <c r="I9" s="126"/>
+      <c r="J9" s="126"/>
+      <c r="K9" s="126"/>
+      <c r="L9" s="126"/>
+      <c r="P9" s="126" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q9" s="126"/>
+      <c r="R9" s="126"/>
+      <c r="S9" s="126"/>
+      <c r="T9" s="126"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="H10" s="126" t="s">
+        <v>183</v>
+      </c>
+      <c r="I10" s="126"/>
+      <c r="J10" s="126"/>
+      <c r="K10">
+        <v>7.5</v>
+      </c>
+      <c r="L10" s="65" t="s">
+        <v>190</v>
+      </c>
+      <c r="P10" s="126" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q10" s="126"/>
+      <c r="R10" s="126"/>
+      <c r="S10">
+        <v>5.4</v>
+      </c>
+      <c r="T10" s="65" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="H11" s="126" t="s">
+        <v>195</v>
+      </c>
+      <c r="I11" s="126"/>
+      <c r="J11" s="126"/>
+      <c r="K11">
+        <f>K10*(K3)^(1/3)</f>
+        <v>27.396389985469561</v>
+      </c>
+      <c r="L11" t="s">
+        <v>16</v>
+      </c>
+      <c r="P11" s="126" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q11" s="126"/>
+      <c r="R11" s="126"/>
+      <c r="S11">
+        <f ca="1">S10*(S3)^(1/3)</f>
+        <v>38.047989101548296</v>
+      </c>
+      <c r="T11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="H12" s="126" t="s">
+        <v>199</v>
+      </c>
+      <c r="I12" s="126"/>
+      <c r="J12" s="126"/>
+      <c r="K12">
+        <f>MIN(MAX(K11,D6/D8),D6/D7)</f>
+        <v>31.666666666666668</v>
+      </c>
+      <c r="L12" t="s">
+        <v>16</v>
+      </c>
+      <c r="P12" s="126" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q12" s="126"/>
+      <c r="R12" s="126"/>
+      <c r="S12" s="66">
+        <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;S11)</f>
         <v>40</v>
       </c>
-      <c r="N5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>13</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>15</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="T12" t="s">
+        <v>16</v>
+      </c>
+      <c r="U12" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="H13" s="126" t="s">
+        <v>188</v>
+      </c>
+      <c r="I13" s="126"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="66">
+        <f>_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;K12)</f>
+        <v>32</v>
+      </c>
+      <c r="L13" t="s">
+        <v>16</v>
+      </c>
+      <c r="M13" t="s">
+        <v>197</v>
+      </c>
+      <c r="P13" s="126" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q13" s="126"/>
+      <c r="R13" s="126"/>
+      <c r="S13">
+        <f ca="1">_xlfn.MINIFS($28:$28,$26:$26,"&gt;="&amp;S12)</f>
+        <v>3.5</v>
+      </c>
+      <c r="T13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="126" t="s">
+        <v>283</v>
+      </c>
+      <c r="B14" s="126"/>
+      <c r="C14" s="126"/>
+      <c r="D14">
+        <f>Электродвигатель!$F$58</f>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H14" s="126" t="s">
+        <v>196</v>
+      </c>
+      <c r="I14" s="126"/>
+      <c r="J14" s="126"/>
+      <c r="K14">
+        <f>_xlfn.MINIFS($28:$28,$26:$26,"&gt;="&amp;K13)</f>
+        <v>3.5</v>
+      </c>
+      <c r="L14" t="s">
+        <v>16</v>
+      </c>
+      <c r="P14" s="126" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q14" s="126"/>
+      <c r="R14" s="126"/>
+      <c r="S14">
+        <f ca="1">S12+2*S13</f>
+        <v>47</v>
+      </c>
+      <c r="T14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="H15" s="126" t="s">
+        <v>192</v>
+      </c>
+      <c r="I15" s="126"/>
+      <c r="J15" s="126"/>
+      <c r="K15">
+        <f>K13+2*K14</f>
+        <v>39</v>
+      </c>
+      <c r="L15" t="s">
+        <v>16</v>
+      </c>
+      <c r="P15" s="126" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q15" s="126"/>
+      <c r="R15" s="126"/>
+      <c r="S15" s="66">
+        <f ca="1">_xlfn.MINIFS(Подшипники!$A:$A,Подшипники!$A:$A,"&gt;="&amp;S14)</f>
+        <v>50</v>
+      </c>
+      <c r="T15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="H16" s="126" t="s">
+        <v>262</v>
+      </c>
+      <c r="I16" s="126"/>
+      <c r="J16" s="126"/>
+      <c r="K16" s="66">
+        <f>_xlfn.MINIFS(Подшипники!$A:$A,Подшипники!$A:$A,"&gt;="&amp;K15)</f>
+        <v>40</v>
+      </c>
+      <c r="L16" t="s">
+        <v>16</v>
+      </c>
+      <c r="P16" s="126" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q16" s="126"/>
+      <c r="R16" s="126"/>
+      <c r="S16">
+        <f ca="1">_xlfn.MINIFS($29:$29,$26:$26,"&gt;="&amp;S12)</f>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="T16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="H17" s="126" t="s">
+        <v>196</v>
+      </c>
+      <c r="I17" s="126"/>
+      <c r="J17" s="126"/>
+      <c r="K17">
+        <f>_xlfn.MINIFS($29:$29,$26:$26,"&gt;="&amp;K13)</f>
+        <v>2</v>
+      </c>
+      <c r="L17" t="s">
+        <v>16</v>
+      </c>
+      <c r="P17" s="126" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q17" s="126"/>
+      <c r="R17" s="126"/>
+      <c r="S17">
+        <f ca="1">S15+2*S16</f>
+        <v>54.6</v>
+      </c>
+      <c r="T17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="H18" s="126" t="s">
+        <v>193</v>
+      </c>
+      <c r="I18" s="126"/>
+      <c r="J18" s="126"/>
+      <c r="K18">
+        <f>K16+2*K17</f>
+        <v>44</v>
+      </c>
+      <c r="L18" t="s">
+        <v>16</v>
+      </c>
+      <c r="P18" s="126" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q18" s="126"/>
+      <c r="R18" s="126"/>
+      <c r="S18" s="66">
+        <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;S17)</f>
+        <v>56</v>
+      </c>
+      <c r="T18" t="s">
+        <v>16</v>
+      </c>
+      <c r="U18" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="H19" s="126" t="s">
+        <v>189</v>
+      </c>
+      <c r="I19" s="126"/>
+      <c r="J19" s="126"/>
+      <c r="K19" s="66">
+        <f>_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;K18)</f>
+        <v>45</v>
+      </c>
+      <c r="L19" t="s">
+        <v>16</v>
+      </c>
+      <c r="M19" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A26" s="126" t="s">
+        <v>181</v>
+      </c>
+      <c r="B26" s="126"/>
+      <c r="C26">
         <v>17</v>
       </c>
-      <c r="B10">
+      <c r="D26">
+        <v>24</v>
+      </c>
+      <c r="E26">
+        <v>32</v>
+      </c>
+      <c r="F26">
+        <v>40</v>
+      </c>
+      <c r="G26">
+        <v>45</v>
+      </c>
+      <c r="H26">
+        <v>52</v>
+      </c>
+      <c r="I26">
+        <v>60</v>
+      </c>
+      <c r="J26">
+        <v>67</v>
+      </c>
+      <c r="K26">
+        <v>80</v>
+      </c>
+      <c r="L26">
+        <v>90</v>
+      </c>
+      <c r="S26" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A27" s="126" t="s">
+        <v>182</v>
+      </c>
+      <c r="B27" s="126"/>
+      <c r="C27">
+        <v>22</v>
+      </c>
+      <c r="D27">
+        <v>30</v>
+      </c>
+      <c r="E27">
+        <v>38</v>
+      </c>
+      <c r="F27">
+        <v>44</v>
+      </c>
+      <c r="G27">
+        <v>50</v>
+      </c>
+      <c r="H27">
+        <v>58</v>
+      </c>
+      <c r="I27">
+        <v>65</v>
+      </c>
+      <c r="J27">
+        <v>75</v>
+      </c>
+      <c r="K27">
+        <v>85</v>
+      </c>
+      <c r="L27">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A28" s="126" t="s">
+        <v>179</v>
+      </c>
+      <c r="B28" s="126"/>
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28">
+        <v>3.5</v>
+      </c>
+      <c r="E28">
+        <v>3.5</v>
+      </c>
+      <c r="F28">
+        <v>3.5</v>
+      </c>
+      <c r="G28">
+        <v>4</v>
+      </c>
+      <c r="H28">
+        <v>4.5</v>
+      </c>
+      <c r="I28">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J28">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="K28">
+        <v>5.6</v>
+      </c>
+      <c r="L28">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A29" s="126" t="s">
+        <v>180</v>
+      </c>
+      <c r="B29" s="126"/>
+      <c r="C29">
+        <v>1.5</v>
+      </c>
+      <c r="D29">
+        <v>1.8</v>
+      </c>
+      <c r="E29">
         <v>2</v>
       </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="J10" s="48" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>19</v>
-      </c>
-      <c r="B11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>20</v>
-      </c>
-      <c r="B12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>25</v>
-      </c>
-      <c r="B13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>30</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>35</v>
-      </c>
-      <c r="B15">
-        <v>7</v>
-      </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>40</v>
-      </c>
-      <c r="B16">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>45</v>
-      </c>
-      <c r="B17">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>50</v>
-      </c>
-      <c r="B18">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>55</v>
-      </c>
-      <c r="B19">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>60</v>
-      </c>
-      <c r="B20">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>65</v>
-      </c>
-      <c r="B21">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>70</v>
-      </c>
-      <c r="B22">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>75</v>
-      </c>
-      <c r="B23">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>80</v>
-      </c>
-      <c r="B24">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>85</v>
-      </c>
-      <c r="B25">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>90</v>
-      </c>
-      <c r="B26">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>95</v>
-      </c>
-      <c r="B27">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>100</v>
-      </c>
-      <c r="B28">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>105</v>
-      </c>
-      <c r="B29">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>110</v>
-      </c>
-      <c r="B30">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>115</v>
-      </c>
-      <c r="B31">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>120</v>
-      </c>
-      <c r="B32">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>125</v>
-      </c>
-      <c r="B33">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>130</v>
-      </c>
-      <c r="B34">
-        <v>26</v>
+      <c r="F29">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G29">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="H29">
+        <v>2.5</v>
+      </c>
+      <c r="I29">
+        <v>2.7</v>
+      </c>
+      <c r="J29">
+        <v>2.7</v>
+      </c>
+      <c r="K29">
+        <v>2.7</v>
+      </c>
+      <c r="L29">
+        <v>2.9</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="J2:N2"/>
+  <mergeCells count="44">
+    <mergeCell ref="P9:T9"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="P8:R8"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="P13:R13"/>
+    <mergeCell ref="P14:R14"/>
+    <mergeCell ref="P10:R10"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="H9:L9"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="P16:R16"/>
+    <mergeCell ref="P17:R17"/>
+    <mergeCell ref="P18:R18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="P11:R11"/>
+    <mergeCell ref="P15:R15"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="H2:L2"/>
     <mergeCell ref="P2:T2"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="E2:I2"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="P5:T5"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="H3:J3"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32704C68-B145-4DB6-B0E3-AE1BF65D15BC}">
-  <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="18" width="6.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
-        <v>274</v>
-      </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126" t="s">
-        <v>184</v>
-      </c>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126" t="s">
-        <v>281</v>
-      </c>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126" t="s">
-        <v>284</v>
-      </c>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
-      <c r="J1" s="126"/>
-      <c r="K1" s="126"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="126"/>
-      <c r="B2" s="126"/>
-      <c r="C2" s="126" t="s">
-        <v>282</v>
-      </c>
-      <c r="D2" s="126"/>
-      <c r="E2" s="126" t="s">
-        <v>283</v>
-      </c>
-      <c r="F2" s="126"/>
-      <c r="G2" s="91" t="s">
-        <v>285</v>
-      </c>
-      <c r="H2" s="91" t="s">
-        <v>286</v>
-      </c>
-      <c r="I2" s="91" t="s">
-        <v>287</v>
-      </c>
-      <c r="J2" s="91" t="s">
-        <v>288</v>
-      </c>
-      <c r="K2" s="91" t="s">
-        <v>289</v>
-      </c>
-      <c r="L2" s="91" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="126" t="s">
-        <v>275</v>
-      </c>
-      <c r="B3" s="126"/>
-      <c r="C3" s="126">
-        <v>1000</v>
-      </c>
-      <c r="D3" s="126"/>
-      <c r="E3" s="126">
-        <v>190</v>
-      </c>
-      <c r="F3" s="126"/>
-      <c r="G3">
-        <v>520</v>
-      </c>
-      <c r="H3">
-        <v>280</v>
-      </c>
-      <c r="I3">
-        <v>150</v>
-      </c>
-      <c r="J3">
-        <v>220</v>
-      </c>
-      <c r="K3">
-        <v>130</v>
-      </c>
-      <c r="L3">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="126">
-        <v>45</v>
-      </c>
-      <c r="B4" s="126"/>
-      <c r="C4" s="126">
-        <v>120</v>
-      </c>
-      <c r="D4" s="126"/>
-      <c r="E4" s="126">
-        <v>227</v>
-      </c>
-      <c r="F4" s="126"/>
-      <c r="G4">
-        <v>820</v>
-      </c>
-      <c r="H4">
-        <v>640</v>
-      </c>
-      <c r="I4">
-        <v>290</v>
-      </c>
-      <c r="J4">
-        <v>360</v>
-      </c>
-      <c r="K4">
-        <v>200</v>
-      </c>
-      <c r="L4">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="126">
-        <v>45</v>
-      </c>
-      <c r="B5" s="126"/>
-      <c r="C5" s="126">
-        <v>80</v>
-      </c>
-      <c r="D5" s="126"/>
-      <c r="E5" s="126">
-        <v>260</v>
-      </c>
-      <c r="F5" s="126"/>
-      <c r="G5">
-        <v>900</v>
-      </c>
-      <c r="H5">
-        <v>650</v>
-      </c>
-      <c r="I5">
-        <v>390</v>
-      </c>
-      <c r="J5">
-        <v>410</v>
-      </c>
-      <c r="K5">
-        <v>230</v>
-      </c>
-      <c r="L5">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="126" t="s">
-        <v>276</v>
-      </c>
-      <c r="B6" s="126"/>
-      <c r="C6" s="126">
-        <v>200</v>
-      </c>
-      <c r="D6" s="126"/>
-      <c r="E6" s="126">
-        <v>240</v>
-      </c>
-      <c r="F6" s="126"/>
-      <c r="G6">
-        <v>790</v>
-      </c>
-      <c r="H6">
-        <v>640</v>
-      </c>
-      <c r="I6">
-        <v>380</v>
-      </c>
-      <c r="J6">
-        <v>370</v>
-      </c>
-      <c r="K6">
-        <v>210</v>
-      </c>
-      <c r="L6">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="126" t="s">
-        <v>276</v>
-      </c>
-      <c r="B7" s="126"/>
-      <c r="C7" s="126">
-        <v>120</v>
-      </c>
-      <c r="D7" s="126"/>
-      <c r="E7" s="126">
-        <v>270</v>
-      </c>
-      <c r="F7" s="126"/>
-      <c r="G7">
-        <v>980</v>
-      </c>
-      <c r="H7">
-        <v>780</v>
-      </c>
-      <c r="I7">
-        <v>450</v>
-      </c>
-      <c r="J7">
-        <v>410</v>
-      </c>
-      <c r="K7">
-        <v>240</v>
-      </c>
-      <c r="L7">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="126" t="s">
-        <v>277</v>
-      </c>
-      <c r="B8" s="126"/>
-      <c r="C8" s="126">
-        <v>200</v>
-      </c>
-      <c r="D8" s="126"/>
-      <c r="E8" s="126">
-        <v>270</v>
-      </c>
-      <c r="F8" s="126"/>
-      <c r="G8">
-        <v>980</v>
-      </c>
-      <c r="H8">
-        <v>750</v>
-      </c>
-      <c r="I8">
-        <v>450</v>
-      </c>
-      <c r="J8">
-        <v>420</v>
-      </c>
-      <c r="K8">
-        <v>2300</v>
-      </c>
-      <c r="L8">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="126" t="s">
-        <v>278</v>
-      </c>
-      <c r="B9" s="126"/>
-      <c r="C9" s="126">
-        <v>120</v>
-      </c>
-      <c r="D9" s="126"/>
-      <c r="E9" s="126">
-        <v>197</v>
-      </c>
-      <c r="F9" s="126"/>
-      <c r="G9">
-        <v>650</v>
-      </c>
-      <c r="H9">
-        <v>400</v>
-      </c>
-      <c r="I9">
-        <v>240</v>
-      </c>
-      <c r="J9">
-        <v>310</v>
-      </c>
-      <c r="K9">
-        <v>170</v>
-      </c>
-      <c r="L9">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="126" t="s">
-        <v>279</v>
-      </c>
-      <c r="B10" s="126"/>
-      <c r="C10" s="126">
-        <v>120</v>
-      </c>
-      <c r="D10" s="126"/>
-      <c r="E10" s="126">
-        <v>260</v>
-      </c>
-      <c r="F10" s="126"/>
-      <c r="G10">
-        <v>930</v>
-      </c>
-      <c r="H10">
-        <v>685</v>
-      </c>
-      <c r="I10">
-        <v>490</v>
-      </c>
-      <c r="J10">
-        <v>430</v>
-      </c>
-      <c r="K10">
-        <v>240</v>
-      </c>
-      <c r="L10">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="126" t="s">
-        <v>280</v>
-      </c>
-      <c r="B11" s="126"/>
-      <c r="C11" s="126">
-        <v>60</v>
-      </c>
-      <c r="D11" s="126"/>
-      <c r="E11" s="126">
-        <v>330</v>
-      </c>
-      <c r="F11" s="126"/>
-      <c r="G11">
-        <v>1180</v>
-      </c>
-      <c r="H11">
-        <v>930</v>
-      </c>
-      <c r="I11">
-        <v>660</v>
-      </c>
-      <c r="J11">
-        <v>500</v>
-      </c>
-      <c r="K11">
-        <v>280</v>
-      </c>
-      <c r="L11">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="48"/>
-      <c r="B12" s="48"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="48"/>
-      <c r="B13" s="48"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="48"/>
-      <c r="B14" s="48"/>
-    </row>
-  </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4C98D27-F275-4550-B7FB-3917876B2935}">
   <dimension ref="A1:AA61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5677,7 +5732,7 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" s="93" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B1" s="93"/>
       <c r="C1" s="93"/>
@@ -5687,7 +5742,7 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" s="99" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B2" s="93"/>
       <c r="C2" s="93"/>
@@ -5698,7 +5753,7 @@
       </c>
       <c r="F2" s="110"/>
       <c r="K2" s="107" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L2" s="100"/>
       <c r="M2" s="100"/>
@@ -5721,28 +5776,28 @@
       </c>
       <c r="F3" s="50"/>
       <c r="K3" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="L3" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q3" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="R3" s="25" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.3">
@@ -5757,7 +5812,7 @@
         <v>190.98593171027443</v>
       </c>
       <c r="F4" s="50" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K4" s="11">
         <v>1</v>
@@ -5781,7 +5836,7 @@
         <v>78.900000000000006</v>
       </c>
       <c r="R4" s="1">
-        <f ca="1">IF(P4&gt;$E$15,1,0)</f>
+        <f>IF(P4&gt;$E$15,1,0)</f>
         <v>1</v>
       </c>
     </row>
@@ -5793,11 +5848,11 @@
       <c r="C5" s="93"/>
       <c r="D5" s="93"/>
       <c r="E5" s="25">
-        <f>Электродвигатель!$F$54</f>
-        <v>320</v>
+        <f ca="1">Электродвигатель!$F$54</f>
+        <v>339.37130342425513</v>
       </c>
       <c r="F5" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K5" s="7">
         <v>2</v>
@@ -5821,13 +5876,13 @@
         <v>74.900000000000006</v>
       </c>
       <c r="R5" s="1">
-        <f t="shared" ref="R5:R15" ca="1" si="0">IF(P5&gt;$E$15,1,0)</f>
+        <f t="shared" ref="R5:R15" si="0">IF(P5&gt;$E$15,1,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" s="99" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B6" s="93"/>
       <c r="C6" s="93"/>
@@ -5859,13 +5914,13 @@
         <v>68.900000000000006</v>
       </c>
       <c r="R6" s="1">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" s="126" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B7" s="126"/>
       <c r="C7" s="126"/>
@@ -5899,13 +5954,13 @@
         <v>70.8</v>
       </c>
       <c r="R7" s="1">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" s="126" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B8" s="126"/>
       <c r="C8" s="126"/>
@@ -5934,17 +5989,14 @@
         <v>64.599999999999994</v>
       </c>
       <c r="R8" s="1">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S8" s="1"/>
-      <c r="V8" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A9" s="126" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B9" s="126"/>
       <c r="C9" s="126"/>
@@ -5978,7 +6030,7 @@
         <v>69.400000000000006</v>
       </c>
       <c r="R9" s="1">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S9" s="54"/>
@@ -5995,7 +6047,7 @@
         <v>3</v>
       </c>
       <c r="F10" s="50" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K10" s="58">
         <v>7</v>
@@ -6019,26 +6071,23 @@
         <v>57.3</v>
       </c>
       <c r="R10" s="1">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S10" s="54"/>
-      <c r="V10" t="s">
-        <v>202</v>
-      </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A11" s="99" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B11" s="93"/>
       <c r="C11" s="93"/>
       <c r="D11" s="93"/>
       <c r="E11" s="47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K11" s="58">
         <v>8</v>
@@ -6062,23 +6111,23 @@
         <v>64.2</v>
       </c>
       <c r="R11" s="1">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S11" s="54"/>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A12" s="99" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B12" s="93"/>
       <c r="C12" s="93"/>
       <c r="D12" s="93"/>
       <c r="E12" s="55" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K12" s="7">
         <v>9</v>
@@ -6102,14 +6151,14 @@
         <v>34.4</v>
       </c>
       <c r="R12" s="1">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S12" s="54"/>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A13" s="126" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B13" s="126"/>
       <c r="C13" s="126"/>
@@ -6138,14 +6187,14 @@
         <v>31.8</v>
       </c>
       <c r="R13" s="1">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S13" s="54"/>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A14" s="126" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B14" s="126"/>
       <c r="C14" s="126"/>
@@ -6179,20 +6228,20 @@
         <v>31.9</v>
       </c>
       <c r="R14" s="1">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S14" s="54"/>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A15" s="93" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B15" s="93"/>
       <c r="C15" s="93"/>
       <c r="D15" s="93"/>
       <c r="E15">
-        <f ca="1">Вал!$K$19</f>
+        <f>Вал!$K$19</f>
         <v>45</v>
       </c>
       <c r="F15" t="s">
@@ -6220,20 +6269,20 @@
         <v>38.1</v>
       </c>
       <c r="R15" s="1">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A16" s="93" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B16" s="93"/>
       <c r="C16" s="93"/>
       <c r="D16" s="93"/>
       <c r="E16">
         <f ca="1">Вал!$S$18</f>
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
@@ -6242,7 +6291,7 @@
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.3">
       <c r="G18" s="140" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H18" s="141"/>
       <c r="I18" s="141"/>
@@ -6253,7 +6302,7 @@
       <c r="L18" s="84"/>
       <c r="M18" s="77"/>
       <c r="N18" s="140" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="O18" s="141"/>
       <c r="P18" s="141"/>
@@ -6264,7 +6313,7 @@
       <c r="S18" s="84"/>
       <c r="T18" s="77"/>
       <c r="U18" s="140" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="V18" s="141"/>
       <c r="W18" s="141"/>
@@ -6276,7 +6325,7 @@
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.3">
       <c r="G19" s="131" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H19" s="132"/>
       <c r="I19" s="132"/>
@@ -6285,11 +6334,11 @@
         <v>69</v>
       </c>
       <c r="L19" s="76" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="M19" s="77"/>
       <c r="N19" s="131" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O19" s="132"/>
       <c r="P19" s="132"/>
@@ -6298,11 +6347,11 @@
         <v>57</v>
       </c>
       <c r="S19" s="76" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="T19" s="77"/>
       <c r="U19" s="131" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="V19" s="132"/>
       <c r="W19" s="132"/>
@@ -6311,12 +6360,12 @@
         <v>64</v>
       </c>
       <c r="Z19" s="76" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="2:26" x14ac:dyDescent="0.3">
       <c r="G20" s="131" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H20" s="132"/>
       <c r="I20" s="132"/>
@@ -6325,11 +6374,11 @@
         <v>22.3</v>
       </c>
       <c r="L20" s="76" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="M20" s="77"/>
       <c r="N20" s="131" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="O20" s="132"/>
       <c r="P20" s="132"/>
@@ -6338,11 +6387,11 @@
         <v>20</v>
       </c>
       <c r="S20" s="76" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="T20" s="77"/>
       <c r="U20" s="131" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="V20" s="132"/>
       <c r="W20" s="132"/>
@@ -6351,12 +6400,12 @@
         <v>25.3</v>
       </c>
       <c r="Z20" s="76" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="2:26" x14ac:dyDescent="0.3">
       <c r="G21" s="131" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H21" s="132"/>
       <c r="I21" s="132"/>
@@ -6369,7 +6418,7 @@
       </c>
       <c r="M21" s="77"/>
       <c r="N21" s="131" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="O21" s="132"/>
       <c r="P21" s="132"/>
@@ -6382,7 +6431,7 @@
       </c>
       <c r="T21" s="77"/>
       <c r="U21" s="131" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="V21" s="132"/>
       <c r="W21" s="132"/>
@@ -6396,7 +6445,7 @@
     </row>
     <row r="22" spans="2:26" x14ac:dyDescent="0.3">
       <c r="G22" s="131" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H22" s="132"/>
       <c r="I22" s="132"/>
@@ -6409,7 +6458,7 @@
       </c>
       <c r="M22" s="77"/>
       <c r="N22" s="131" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O22" s="132"/>
       <c r="P22" s="132"/>
@@ -6422,7 +6471,7 @@
       </c>
       <c r="T22" s="77"/>
       <c r="U22" s="131" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="V22" s="132"/>
       <c r="W22" s="132"/>
@@ -6445,7 +6494,7 @@
         <v>1510</v>
       </c>
       <c r="L23" s="76" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M23" s="77"/>
       <c r="N23" s="131" t="s">
@@ -6458,7 +6507,7 @@
         <v>2016</v>
       </c>
       <c r="S23" s="76" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="T23" s="77"/>
       <c r="U23" s="131" t="s">
@@ -6471,12 +6520,12 @@
         <v>2013</v>
       </c>
       <c r="Z23" s="76" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="2:26" x14ac:dyDescent="0.3">
       <c r="G24" s="131" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H24" s="132"/>
       <c r="I24" s="132"/>
@@ -6485,11 +6534,11 @@
         <v>554</v>
       </c>
       <c r="L24" s="76" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M24" s="77"/>
       <c r="N24" s="131" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="O24" s="132"/>
       <c r="P24" s="132"/>
@@ -6498,11 +6547,11 @@
         <v>734</v>
       </c>
       <c r="S24" s="76" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="T24" s="77"/>
       <c r="U24" s="131" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="V24" s="132"/>
       <c r="W24" s="132"/>
@@ -6511,12 +6560,12 @@
         <v>733</v>
       </c>
       <c r="Z24" s="76" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="2:26" x14ac:dyDescent="0.3">
       <c r="G25" s="133" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H25" s="134"/>
       <c r="I25" s="134"/>
@@ -6525,11 +6574,11 @@
         <v>0</v>
       </c>
       <c r="L25" s="81" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M25" s="77"/>
       <c r="N25" s="133" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="O25" s="134"/>
       <c r="P25" s="134"/>
@@ -6538,11 +6587,11 @@
         <v>0</v>
       </c>
       <c r="S25" s="81" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="T25" s="77"/>
       <c r="U25" s="133" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="V25" s="134"/>
       <c r="W25" s="134"/>
@@ -6551,12 +6600,12 @@
         <v>0</v>
       </c>
       <c r="Z25" s="81" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="2:26" x14ac:dyDescent="0.3">
       <c r="G26" s="135" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H26" s="136"/>
       <c r="I26" s="136"/>
@@ -6565,7 +6614,7 @@
       <c r="L26" s="137"/>
       <c r="M26" s="77"/>
       <c r="N26" s="135" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O26" s="136"/>
       <c r="P26" s="136"/>
@@ -6574,7 +6623,7 @@
       <c r="S26" s="137"/>
       <c r="T26" s="77"/>
       <c r="U26" s="135" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="V26" s="136"/>
       <c r="W26" s="136"/>
@@ -6584,7 +6633,7 @@
     </row>
     <row r="27" spans="2:26" x14ac:dyDescent="0.3">
       <c r="G27" s="131" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H27" s="132"/>
       <c r="I27" s="132"/>
@@ -6595,7 +6644,7 @@
       <c r="L27" s="76"/>
       <c r="M27" s="77"/>
       <c r="N27" s="131" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="O27" s="132"/>
       <c r="P27" s="132"/>
@@ -6606,7 +6655,7 @@
       <c r="S27" s="76"/>
       <c r="T27" s="77"/>
       <c r="U27" s="131" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="V27" s="132"/>
       <c r="W27" s="132"/>
@@ -6618,7 +6667,7 @@
     </row>
     <row r="28" spans="2:26" x14ac:dyDescent="0.3">
       <c r="G28" s="138" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H28" s="139"/>
       <c r="I28" s="139"/>
@@ -6631,7 +6680,7 @@
       </c>
       <c r="M28" s="77"/>
       <c r="N28" s="138" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="O28" s="139"/>
       <c r="P28" s="139"/>
@@ -6644,7 +6693,7 @@
       </c>
       <c r="T28" s="77"/>
       <c r="U28" s="138" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="V28" s="139"/>
       <c r="W28" s="139"/>
@@ -6658,7 +6707,7 @@
     </row>
     <row r="29" spans="2:26" x14ac:dyDescent="0.3">
       <c r="G29" s="138" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H29" s="139"/>
       <c r="I29" s="139"/>
@@ -6667,11 +6716,11 @@
         <v>49</v>
       </c>
       <c r="L29" s="79" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="M29" s="77"/>
       <c r="N29" s="138" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="O29" s="139"/>
       <c r="P29" s="139"/>
@@ -6680,11 +6729,11 @@
         <v>49</v>
       </c>
       <c r="S29" s="79" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="T29" s="77"/>
       <c r="U29" s="138" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="V29" s="139"/>
       <c r="W29" s="139"/>
@@ -6693,47 +6742,47 @@
         <v>49</v>
       </c>
       <c r="Z29" s="79" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
     </row>
     <row r="30" spans="2:26" x14ac:dyDescent="0.3">
       <c r="G30" s="138" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H30" s="139"/>
       <c r="I30" s="139"/>
       <c r="J30" s="139"/>
       <c r="K30" s="87" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L30" s="76"/>
       <c r="M30" s="77"/>
       <c r="N30" s="138" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O30" s="139"/>
       <c r="P30" s="139"/>
       <c r="Q30" s="139"/>
       <c r="R30" s="87" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="S30" s="76"/>
       <c r="T30" s="77"/>
       <c r="U30" s="138" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="V30" s="139"/>
       <c r="W30" s="139"/>
       <c r="X30" s="139"/>
       <c r="Y30" s="87" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Z30" s="76"/>
     </row>
     <row r="31" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B31" s="86"/>
       <c r="G31" s="131" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H31" s="132"/>
       <c r="I31" s="132"/>
@@ -6746,7 +6795,7 @@
       </c>
       <c r="M31" s="77"/>
       <c r="N31" s="131" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="O31" s="132"/>
       <c r="P31" s="132"/>
@@ -6759,7 +6808,7 @@
       </c>
       <c r="T31" s="77"/>
       <c r="U31" s="131" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="V31" s="132"/>
       <c r="W31" s="132"/>
@@ -6773,7 +6822,7 @@
     </row>
     <row r="32" spans="2:26" x14ac:dyDescent="0.3">
       <c r="G32" s="131" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H32" s="132"/>
       <c r="I32" s="132"/>
@@ -6786,7 +6835,7 @@
       </c>
       <c r="M32" s="77"/>
       <c r="N32" s="131" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="O32" s="132"/>
       <c r="P32" s="132"/>
@@ -6799,7 +6848,7 @@
       </c>
       <c r="T32" s="77"/>
       <c r="U32" s="131" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="V32" s="132"/>
       <c r="W32" s="132"/>
@@ -6813,7 +6862,7 @@
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.3">
       <c r="G33" s="131" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H33" s="132"/>
       <c r="I33" s="132"/>
@@ -6826,7 +6875,7 @@
       </c>
       <c r="M33" s="77"/>
       <c r="N33" s="131" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O33" s="132"/>
       <c r="P33" s="132"/>
@@ -6839,7 +6888,7 @@
       </c>
       <c r="T33" s="77"/>
       <c r="U33" s="131" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="V33" s="132"/>
       <c r="W33" s="132"/>
@@ -6853,7 +6902,7 @@
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.3">
       <c r="G34" s="131" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H34" s="132"/>
       <c r="I34" s="132"/>
@@ -6866,7 +6915,7 @@
       </c>
       <c r="M34" s="77"/>
       <c r="N34" s="131" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O34" s="132"/>
       <c r="P34" s="132"/>
@@ -6879,7 +6928,7 @@
       </c>
       <c r="T34" s="77"/>
       <c r="U34" s="133" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="V34" s="134"/>
       <c r="W34" s="134"/>
@@ -6893,7 +6942,7 @@
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.3">
       <c r="G35" s="135" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H35" s="136"/>
       <c r="I35" s="136"/>
@@ -6902,7 +6951,7 @@
       <c r="L35" s="137"/>
       <c r="M35" s="77"/>
       <c r="N35" s="135" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="O35" s="136"/>
       <c r="P35" s="136"/>
@@ -6911,7 +6960,7 @@
       <c r="S35" s="137"/>
       <c r="T35" s="77"/>
       <c r="U35" s="135" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V35" s="136"/>
       <c r="W35" s="136"/>
@@ -6921,7 +6970,7 @@
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.3">
       <c r="G36" s="131" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H36" s="132"/>
       <c r="I36" s="132"/>
@@ -6932,7 +6981,7 @@
       <c r="L36" s="76"/>
       <c r="M36" s="77"/>
       <c r="N36" s="131" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="O36" s="132"/>
       <c r="P36" s="132"/>
@@ -6943,7 +6992,7 @@
       <c r="S36" s="76"/>
       <c r="T36" s="77"/>
       <c r="U36" s="131" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="V36" s="132"/>
       <c r="W36" s="132"/>
@@ -6955,7 +7004,7 @@
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.3">
       <c r="G37" s="138" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H37" s="139"/>
       <c r="I37" s="139"/>
@@ -6968,7 +7017,7 @@
       </c>
       <c r="M37" s="88"/>
       <c r="N37" s="138" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="O37" s="139"/>
       <c r="P37" s="139"/>
@@ -6981,7 +7030,7 @@
       </c>
       <c r="T37" s="88"/>
       <c r="U37" s="138" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="V37" s="139"/>
       <c r="W37" s="139"/>
@@ -6995,7 +7044,7 @@
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.3">
       <c r="G38" s="138" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H38" s="139"/>
       <c r="I38" s="139"/>
@@ -7004,11 +7053,11 @@
         <v>28.5</v>
       </c>
       <c r="L38" s="79" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="M38" s="77"/>
       <c r="N38" s="138" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="O38" s="139"/>
       <c r="P38" s="139"/>
@@ -7017,11 +7066,11 @@
         <v>28.5</v>
       </c>
       <c r="S38" s="79" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="T38" s="77"/>
       <c r="U38" s="138" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="V38" s="139"/>
       <c r="W38" s="139"/>
@@ -7030,47 +7079,47 @@
         <v>28.5</v>
       </c>
       <c r="Z38" s="79" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.3">
       <c r="G39" s="138" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H39" s="139"/>
       <c r="I39" s="139"/>
       <c r="J39" s="139"/>
       <c r="K39" s="87" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L39" s="76"/>
       <c r="M39" s="77"/>
       <c r="N39" s="138" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O39" s="139"/>
       <c r="P39" s="139"/>
       <c r="Q39" s="139"/>
       <c r="R39" s="87" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="S39" s="76"/>
       <c r="T39" s="77"/>
       <c r="U39" s="138" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="V39" s="139"/>
       <c r="W39" s="139"/>
       <c r="X39" s="139"/>
       <c r="Y39" s="87" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Z39" s="76"/>
       <c r="AA39" s="86"/>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.3">
       <c r="G40" s="131" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H40" s="132"/>
       <c r="I40" s="132"/>
@@ -7083,7 +7132,7 @@
       </c>
       <c r="M40" s="77"/>
       <c r="N40" s="131" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="O40" s="132"/>
       <c r="P40" s="132"/>
@@ -7096,7 +7145,7 @@
       </c>
       <c r="T40" s="77"/>
       <c r="U40" s="131" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="V40" s="132"/>
       <c r="W40" s="132"/>
@@ -7111,7 +7160,7 @@
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.3">
       <c r="G41" s="131" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H41" s="132"/>
       <c r="I41" s="132"/>
@@ -7124,7 +7173,7 @@
       </c>
       <c r="M41" s="77"/>
       <c r="N41" s="131" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="O41" s="132"/>
       <c r="P41" s="132"/>
@@ -7137,7 +7186,7 @@
       </c>
       <c r="T41" s="77"/>
       <c r="U41" s="131" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="V41" s="132"/>
       <c r="W41" s="132"/>
@@ -7152,7 +7201,7 @@
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.3">
       <c r="G42" s="131" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H42" s="132"/>
       <c r="I42" s="132"/>
@@ -7165,7 +7214,7 @@
       </c>
       <c r="M42" s="77"/>
       <c r="N42" s="131" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O42" s="132"/>
       <c r="P42" s="132"/>
@@ -7178,7 +7227,7 @@
       </c>
       <c r="T42" s="77"/>
       <c r="U42" s="131" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="V42" s="132"/>
       <c r="W42" s="132"/>
@@ -7193,7 +7242,7 @@
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.3">
       <c r="G43" s="133" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H43" s="134"/>
       <c r="I43" s="134"/>
@@ -7206,7 +7255,7 @@
       </c>
       <c r="M43" s="77"/>
       <c r="N43" s="133" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O43" s="134"/>
       <c r="P43" s="134"/>
@@ -7219,7 +7268,7 @@
       </c>
       <c r="T43" s="77"/>
       <c r="U43" s="133" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="V43" s="134"/>
       <c r="W43" s="134"/>
@@ -7238,7 +7287,7 @@
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A45" s="135" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B45" s="136"/>
       <c r="C45" s="136"/>
@@ -7251,7 +7300,7 @@
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A46" s="131" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B46" s="132"/>
       <c r="C46" s="132"/>
@@ -7269,7 +7318,7 @@
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A47" s="142" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B47" s="143"/>
       <c r="C47" s="143"/>
@@ -7285,7 +7334,7 @@
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A48" s="138" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B48" s="139"/>
       <c r="C48" s="139"/>
@@ -7305,13 +7354,13 @@
         <v>2016</v>
       </c>
       <c r="E49" s="84" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Z49" s="59"/>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A50" s="131" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B50" s="132"/>
       <c r="C50" s="132"/>
@@ -7320,13 +7369,13 @@
         <v>734</v>
       </c>
       <c r="E50" s="76" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Z50" s="59"/>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A51" s="133" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B51" s="134"/>
       <c r="C51" s="134"/>
@@ -7335,13 +7384,13 @@
         <v>0</v>
       </c>
       <c r="E51" s="81" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Z51" s="59"/>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A52" s="138" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B52" s="139"/>
       <c r="C52" s="139"/>
@@ -7351,7 +7400,7 @@
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A53" s="135" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B53" s="136"/>
       <c r="C53" s="136"/>
@@ -7366,7 +7415,7 @@
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A54" s="138" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B54" s="139"/>
       <c r="C54" s="139"/>
@@ -7381,7 +7430,7 @@
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A55" s="138" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B55" s="139"/>
       <c r="C55" s="139"/>
@@ -7396,7 +7445,7 @@
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A56" s="142" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B56" s="143"/>
       <c r="C56" s="143"/>
@@ -7411,7 +7460,7 @@
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A57" s="138" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B57" s="139"/>
       <c r="C57" s="139"/>
@@ -7421,7 +7470,7 @@
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A58" s="135" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B58" s="136"/>
       <c r="C58" s="136"/>
@@ -7435,7 +7484,7 @@
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A59" s="138" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B59" s="139"/>
       <c r="C59" s="139"/>
@@ -7449,7 +7498,7 @@
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A60" s="138" t="s">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="B60" s="139"/>
       <c r="C60" s="139"/>
@@ -7463,7 +7512,7 @@
     </row>
     <row r="61" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A61" s="142" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B61" s="143"/>
       <c r="C61" s="143"/>
@@ -7595,1151 +7644,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A416109-A6F9-42CB-B875-F300C0970630}">
-  <dimension ref="A2:U29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="27" width="6.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="126" t="s">
-        <v>175</v>
-      </c>
-      <c r="B2" s="126"/>
-      <c r="C2" s="126"/>
-      <c r="D2" s="126"/>
-      <c r="E2" s="126"/>
-      <c r="H2" s="126" t="s">
-        <v>188</v>
-      </c>
-      <c r="I2" s="126"/>
-      <c r="J2" s="126"/>
-      <c r="K2" s="126"/>
-      <c r="L2" s="126"/>
-      <c r="P2" s="126" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q2" s="126"/>
-      <c r="R2" s="126"/>
-      <c r="S2" s="126"/>
-      <c r="T2" s="126"/>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="126" t="s">
-        <v>174</v>
-      </c>
-      <c r="B3" s="126"/>
-      <c r="D3" s="61">
-        <f ca="1">Электродвигатель!$P$53</f>
-        <v>45.959055069271365</v>
-      </c>
-      <c r="E3" t="s">
-        <v>100</v>
-      </c>
-      <c r="H3" s="93" t="s">
-        <v>174</v>
-      </c>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="63">
-        <f ca="1">D3</f>
-        <v>45.959055069271365</v>
-      </c>
-      <c r="L3" t="s">
-        <v>100</v>
-      </c>
-      <c r="P3" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="R3" s="16"/>
-      <c r="S3">
-        <f ca="1">Электродвигатель!P55</f>
-        <v>329.82890125747264</v>
-      </c>
-      <c r="T3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="126" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="126"/>
-      <c r="D4" s="62">
-        <f>Электродвигатель!$N$52</f>
-        <v>1440</v>
-      </c>
-      <c r="E4" t="s">
-        <v>105</v>
-      </c>
-      <c r="H4" s="93" t="s">
-        <v>70</v>
-      </c>
-      <c r="I4" s="93"/>
-      <c r="J4" s="93"/>
-      <c r="K4" s="64">
-        <f>D4</f>
-        <v>1440</v>
-      </c>
-      <c r="L4" t="s">
-        <v>105</v>
-      </c>
-      <c r="P4" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
-      <c r="S4" s="61">
-        <f>Электродвигатель!N55</f>
-        <v>190.98593171027443</v>
-      </c>
-      <c r="T4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H5" s="126" t="s">
-        <v>178</v>
-      </c>
-      <c r="I5" s="126"/>
-      <c r="J5" s="126"/>
-      <c r="K5" s="126"/>
-      <c r="L5" s="126"/>
-      <c r="P5" s="126" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q5" s="126"/>
-      <c r="R5" s="126"/>
-      <c r="S5" s="126"/>
-      <c r="T5" s="126"/>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="126" t="s">
-        <v>120</v>
-      </c>
-      <c r="B6" s="126"/>
-      <c r="C6" s="126"/>
-      <c r="D6" s="66">
-        <f>Электродвигатель!$F$61</f>
-        <v>38</v>
-      </c>
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="126" t="s">
-        <v>177</v>
-      </c>
-      <c r="I6" s="126"/>
-      <c r="J6" s="126"/>
-      <c r="K6">
-        <f>Передача!D55</f>
-        <v>37.75</v>
-      </c>
-      <c r="L6" t="s">
-        <v>16</v>
-      </c>
-      <c r="P6" s="126" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q6" s="126"/>
-      <c r="R6" s="126"/>
-      <c r="S6">
-        <f>Передача!D60</f>
-        <v>309.75</v>
-      </c>
-      <c r="T6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="145" t="s">
-        <v>200</v>
-      </c>
-      <c r="B7" s="145"/>
-      <c r="C7" s="145"/>
-      <c r="D7" s="52">
-        <v>0.8</v>
-      </c>
-      <c r="H7" s="126" t="s">
-        <v>186</v>
-      </c>
-      <c r="I7" s="126"/>
-      <c r="J7" s="126"/>
-      <c r="K7">
-        <f>Передача!D54</f>
-        <v>49</v>
-      </c>
-      <c r="L7" t="s">
-        <v>16</v>
-      </c>
-      <c r="P7" s="126" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q7" s="126"/>
-      <c r="R7" s="126"/>
-      <c r="S7">
-        <f>Передача!D59</f>
-        <v>321</v>
-      </c>
-      <c r="T7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="126" t="s">
-        <v>196</v>
-      </c>
-      <c r="B8" s="126"/>
-      <c r="C8" s="126"/>
-      <c r="D8" s="71">
-        <v>1.2</v>
-      </c>
-      <c r="H8" s="126" t="s">
-        <v>167</v>
-      </c>
-      <c r="I8" s="126"/>
-      <c r="J8" s="126"/>
-      <c r="K8">
-        <f>Передача!D56</f>
-        <v>62</v>
-      </c>
-      <c r="L8" t="s">
-        <v>16</v>
-      </c>
-      <c r="P8" s="126" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q8" s="126"/>
-      <c r="R8" s="126"/>
-      <c r="S8">
-        <f>Передача!D61</f>
-        <v>57</v>
-      </c>
-      <c r="T8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H9" s="126" t="s">
-        <v>189</v>
-      </c>
-      <c r="I9" s="126"/>
-      <c r="J9" s="126"/>
-      <c r="K9" s="126"/>
-      <c r="L9" s="126"/>
-      <c r="P9" s="126" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q9" s="126"/>
-      <c r="R9" s="126"/>
-      <c r="S9" s="126"/>
-      <c r="T9" s="126"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H10" s="126" t="s">
-        <v>185</v>
-      </c>
-      <c r="I10" s="126"/>
-      <c r="J10" s="126"/>
-      <c r="K10">
-        <v>7.5</v>
-      </c>
-      <c r="L10" s="65" t="s">
-        <v>192</v>
-      </c>
-      <c r="P10" s="126" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q10" s="126"/>
-      <c r="R10" s="126"/>
-      <c r="S10">
-        <v>5.4</v>
-      </c>
-      <c r="T10" s="65" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H11" s="126" t="s">
-        <v>197</v>
-      </c>
-      <c r="I11" s="126"/>
-      <c r="J11" s="126"/>
-      <c r="K11">
-        <f ca="1">K10*(K3)^(1/3)</f>
-        <v>26.864883424091097</v>
-      </c>
-      <c r="L11" t="s">
-        <v>16</v>
-      </c>
-      <c r="P11" s="126" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q11" s="126"/>
-      <c r="R11" s="126"/>
-      <c r="S11">
-        <f ca="1">S10*(S3)^(1/3)</f>
-        <v>37.309835064996221</v>
-      </c>
-      <c r="T11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H12" s="126" t="s">
-        <v>201</v>
-      </c>
-      <c r="I12" s="126"/>
-      <c r="J12" s="126"/>
-      <c r="K12">
-        <f ca="1">MIN(MAX(K11,D6/D8),D6/D7)</f>
-        <v>31.666666666666668</v>
-      </c>
-      <c r="L12" t="s">
-        <v>16</v>
-      </c>
-      <c r="P12" s="126" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q12" s="126"/>
-      <c r="R12" s="126"/>
-      <c r="S12" s="66">
-        <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;S11)</f>
-        <v>38</v>
-      </c>
-      <c r="T12" t="s">
-        <v>16</v>
-      </c>
-      <c r="U12" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H13" s="126" t="s">
-        <v>190</v>
-      </c>
-      <c r="I13" s="126"/>
-      <c r="J13" s="126"/>
-      <c r="K13" s="66">
-        <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;K12)</f>
-        <v>32</v>
-      </c>
-      <c r="L13" t="s">
-        <v>16</v>
-      </c>
-      <c r="M13" t="s">
-        <v>199</v>
-      </c>
-      <c r="P13" s="126" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q13" s="126"/>
-      <c r="R13" s="126"/>
-      <c r="S13">
-        <f ca="1">_xlfn.MINIFS($28:$28,$26:$26,"&gt;="&amp;S12)</f>
-        <v>3.5</v>
-      </c>
-      <c r="T13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="126" t="s">
-        <v>292</v>
-      </c>
-      <c r="B14" s="126"/>
-      <c r="C14" s="126"/>
-      <c r="D14">
-        <f>Электродвигатель!$F$58</f>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="H14" s="126" t="s">
-        <v>198</v>
-      </c>
-      <c r="I14" s="126"/>
-      <c r="J14" s="126"/>
-      <c r="K14">
-        <f ca="1">_xlfn.MINIFS($28:$28,$26:$26,"&gt;="&amp;K13)</f>
-        <v>3.5</v>
-      </c>
-      <c r="L14" t="s">
-        <v>16</v>
-      </c>
-      <c r="P14" s="126" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q14" s="126"/>
-      <c r="R14" s="126"/>
-      <c r="S14">
-        <f ca="1">S12+2*S13</f>
-        <v>45</v>
-      </c>
-      <c r="T14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H15" s="126" t="s">
-        <v>194</v>
-      </c>
-      <c r="I15" s="126"/>
-      <c r="J15" s="126"/>
-      <c r="K15">
-        <f ca="1">K13+2*K14</f>
-        <v>39</v>
-      </c>
-      <c r="L15" t="s">
-        <v>16</v>
-      </c>
-      <c r="P15" s="126" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q15" s="126"/>
-      <c r="R15" s="126"/>
-      <c r="S15" s="66">
-        <f ca="1">_xlfn.MINIFS(Подшипники!$A:$A,Подшипники!$A:$A,"&gt;="&amp;S14)</f>
-        <v>45</v>
-      </c>
-      <c r="T15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H16" s="126" t="s">
-        <v>269</v>
-      </c>
-      <c r="I16" s="126"/>
-      <c r="J16" s="126"/>
-      <c r="K16" s="66">
-        <f ca="1">_xlfn.MINIFS(Подшипники!$A:$A,Подшипники!$A:$A,"&gt;="&amp;K15)</f>
-        <v>40</v>
-      </c>
-      <c r="L16" t="s">
-        <v>16</v>
-      </c>
-      <c r="P16" s="126" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q16" s="126"/>
-      <c r="R16" s="126"/>
-      <c r="S16">
-        <f ca="1">_xlfn.MINIFS($29:$29,$26:$26,"&gt;="&amp;S12)</f>
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="T16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H17" s="126" t="s">
-        <v>198</v>
-      </c>
-      <c r="I17" s="126"/>
-      <c r="J17" s="126"/>
-      <c r="K17">
-        <f ca="1">_xlfn.MINIFS($29:$29,$26:$26,"&gt;="&amp;K13)</f>
-        <v>2</v>
-      </c>
-      <c r="L17" t="s">
-        <v>16</v>
-      </c>
-      <c r="P17" s="126" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q17" s="126"/>
-      <c r="R17" s="126"/>
-      <c r="S17">
-        <f ca="1">S15+2*S16</f>
-        <v>49.6</v>
-      </c>
-      <c r="T17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H18" s="126" t="s">
-        <v>195</v>
-      </c>
-      <c r="I18" s="126"/>
-      <c r="J18" s="126"/>
-      <c r="K18">
-        <f ca="1">K16+2*K17</f>
-        <v>44</v>
-      </c>
-      <c r="L18" t="s">
-        <v>16</v>
-      </c>
-      <c r="P18" s="126" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q18" s="126"/>
-      <c r="R18" s="126"/>
-      <c r="S18" s="66">
-        <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;S17)</f>
-        <v>50</v>
-      </c>
-      <c r="T18" t="s">
-        <v>16</v>
-      </c>
-      <c r="U18" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H19" s="126" t="s">
-        <v>191</v>
-      </c>
-      <c r="I19" s="126"/>
-      <c r="J19" s="126"/>
-      <c r="K19" s="66">
-        <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;K18)</f>
-        <v>45</v>
-      </c>
-      <c r="L19" t="s">
-        <v>16</v>
-      </c>
-      <c r="M19" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="S24" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="S25" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A26" s="126" t="s">
-        <v>183</v>
-      </c>
-      <c r="B26" s="126"/>
-      <c r="C26">
-        <v>17</v>
-      </c>
-      <c r="D26">
-        <v>24</v>
-      </c>
-      <c r="E26">
-        <v>32</v>
-      </c>
-      <c r="F26">
-        <v>40</v>
-      </c>
-      <c r="G26">
-        <v>45</v>
-      </c>
-      <c r="H26">
-        <v>52</v>
-      </c>
-      <c r="I26">
-        <v>60</v>
-      </c>
-      <c r="J26">
-        <v>67</v>
-      </c>
-      <c r="K26">
-        <v>80</v>
-      </c>
-      <c r="L26">
-        <v>90</v>
-      </c>
-      <c r="S26" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A27" s="126" t="s">
-        <v>184</v>
-      </c>
-      <c r="B27" s="126"/>
-      <c r="C27">
-        <v>22</v>
-      </c>
-      <c r="D27">
-        <v>30</v>
-      </c>
-      <c r="E27">
-        <v>38</v>
-      </c>
-      <c r="F27">
-        <v>44</v>
-      </c>
-      <c r="G27">
-        <v>50</v>
-      </c>
-      <c r="H27">
-        <v>58</v>
-      </c>
-      <c r="I27">
-        <v>65</v>
-      </c>
-      <c r="J27">
-        <v>75</v>
-      </c>
-      <c r="K27">
-        <v>85</v>
-      </c>
-      <c r="L27">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A28" s="126" t="s">
-        <v>181</v>
-      </c>
-      <c r="B28" s="126"/>
-      <c r="C28">
-        <v>3</v>
-      </c>
-      <c r="D28">
-        <v>3.5</v>
-      </c>
-      <c r="E28">
-        <v>3.5</v>
-      </c>
-      <c r="F28">
-        <v>3.5</v>
-      </c>
-      <c r="G28">
-        <v>4</v>
-      </c>
-      <c r="H28">
-        <v>4.5</v>
-      </c>
-      <c r="I28">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="J28">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="K28">
-        <v>5.6</v>
-      </c>
-      <c r="L28">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A29" s="126" t="s">
-        <v>182</v>
-      </c>
-      <c r="B29" s="126"/>
-      <c r="C29">
-        <v>1.5</v>
-      </c>
-      <c r="D29">
-        <v>1.8</v>
-      </c>
-      <c r="E29">
-        <v>2</v>
-      </c>
-      <c r="F29">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="G29">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="H29">
-        <v>2.5</v>
-      </c>
-      <c r="I29">
-        <v>2.7</v>
-      </c>
-      <c r="J29">
-        <v>2.7</v>
-      </c>
-      <c r="K29">
-        <v>2.7</v>
-      </c>
-      <c r="L29">
-        <v>2.9</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="44">
-    <mergeCell ref="P9:T9"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="P12:R12"/>
-    <mergeCell ref="P13:R13"/>
-    <mergeCell ref="P14:R14"/>
-    <mergeCell ref="P10:R10"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="H9:L9"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="P16:R16"/>
-    <mergeCell ref="P17:R17"/>
-    <mergeCell ref="P18:R18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="P11:R11"/>
-    <mergeCell ref="P15:R15"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="P2:T2"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="P5:T5"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="H3:J3"/>
-  </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7BF09D0-EAD8-49BE-BC1A-C3CACFF128CD}">
-  <dimension ref="A2:A4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="17" width="6.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20604C11-E2B8-4CC3-855A-FA5D156E5EA8}">
-  <dimension ref="A5:AI14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="22" width="6.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="D5" s="146" t="s">
-        <v>293</v>
-      </c>
-      <c r="E5" s="146"/>
-      <c r="F5" s="146" t="s">
-        <v>299</v>
-      </c>
-      <c r="G5" s="146"/>
-      <c r="H5" s="146" t="s">
-        <v>300</v>
-      </c>
-      <c r="I5" s="146"/>
-      <c r="J5" s="146" t="s">
-        <v>178</v>
-      </c>
-      <c r="K5" s="146"/>
-      <c r="L5" s="146" t="s">
-        <v>301</v>
-      </c>
-      <c r="M5" s="146"/>
-      <c r="N5" s="146" t="s">
-        <v>302</v>
-      </c>
-      <c r="O5" s="146"/>
-      <c r="P5" s="146" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q5" s="146"/>
-      <c r="R5" s="146" t="s">
-        <v>303</v>
-      </c>
-      <c r="S5" s="146"/>
-    </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="146"/>
-      <c r="E6" s="146"/>
-      <c r="F6" s="146"/>
-      <c r="G6" s="146"/>
-      <c r="H6" s="146"/>
-      <c r="I6" s="146"/>
-      <c r="J6" s="146"/>
-      <c r="K6" s="146"/>
-      <c r="L6" s="146"/>
-      <c r="M6" s="146"/>
-      <c r="N6" s="146"/>
-      <c r="O6" s="146"/>
-      <c r="P6" s="146"/>
-      <c r="Q6" s="146"/>
-      <c r="R6" s="146"/>
-      <c r="S6" s="146"/>
-      <c r="T6" s="48"/>
-      <c r="U6" s="48"/>
-      <c r="V6" s="48"/>
-      <c r="W6" s="48"/>
-      <c r="X6" s="48"/>
-      <c r="Y6" s="48"/>
-      <c r="Z6" s="48"/>
-      <c r="AA6" s="48"/>
-      <c r="AB6" s="48"/>
-      <c r="AC6" s="48"/>
-      <c r="AD6" s="48"/>
-      <c r="AE6" s="48"/>
-      <c r="AF6" s="48"/>
-      <c r="AG6" s="48"/>
-      <c r="AH6" s="48"/>
-      <c r="AI6" s="48"/>
-    </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A7" s="126" t="s">
-        <v>294</v>
-      </c>
-      <c r="B7" s="126"/>
-      <c r="C7" s="126"/>
-      <c r="D7" s="126">
-        <f ca="1">Вал!$K$16</f>
-        <v>40</v>
-      </c>
-      <c r="E7" s="126"/>
-      <c r="F7" s="126"/>
-      <c r="G7" s="126"/>
-      <c r="H7" s="126">
-        <f ca="1">Вал!$K$19</f>
-        <v>45</v>
-      </c>
-      <c r="I7" s="126"/>
-      <c r="J7" s="126">
-        <f>Передача!D54</f>
-        <v>49</v>
-      </c>
-      <c r="K7" s="126"/>
-      <c r="L7" s="126">
-        <f ca="1">H7</f>
-        <v>45</v>
-      </c>
-      <c r="M7" s="126"/>
-      <c r="N7" s="126">
-        <f>F7</f>
-        <v>0</v>
-      </c>
-      <c r="O7" s="126"/>
-      <c r="P7" s="126">
-        <f ca="1">D7</f>
-        <v>40</v>
-      </c>
-      <c r="Q7" s="126"/>
-      <c r="R7" s="126">
-        <f ca="1">Вал!K13</f>
-        <v>32</v>
-      </c>
-      <c r="S7" s="126"/>
-      <c r="U7" s="48"/>
-      <c r="V7" s="48"/>
-      <c r="W7" s="48"/>
-      <c r="Z7" s="48"/>
-      <c r="AA7" s="48"/>
-      <c r="AB7" s="48"/>
-      <c r="AE7" s="48"/>
-      <c r="AF7" s="48"/>
-      <c r="AG7" s="48"/>
-    </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A8" s="126" t="s">
-        <v>270</v>
-      </c>
-      <c r="B8" s="126"/>
-      <c r="C8" s="126"/>
-      <c r="D8" s="126"/>
-      <c r="E8" s="126"/>
-      <c r="F8" s="126"/>
-      <c r="G8" s="126"/>
-      <c r="H8" s="126"/>
-      <c r="I8" s="126"/>
-      <c r="J8" s="126">
-        <f>Передача!$D$56</f>
-        <v>62</v>
-      </c>
-      <c r="K8" s="126"/>
-      <c r="L8" s="126"/>
-      <c r="M8" s="126"/>
-      <c r="N8" s="126"/>
-      <c r="O8" s="126"/>
-      <c r="P8" s="126"/>
-      <c r="Q8" s="126"/>
-      <c r="R8" s="126"/>
-      <c r="S8" s="126"/>
-      <c r="U8" s="48"/>
-      <c r="V8" s="48"/>
-      <c r="W8" s="48"/>
-      <c r="Z8" s="48"/>
-      <c r="AA8" s="48"/>
-      <c r="AB8" s="48"/>
-      <c r="AE8" s="48"/>
-      <c r="AF8" s="48"/>
-      <c r="AG8" s="48"/>
-    </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A9" s="126" t="s">
-        <v>295</v>
-      </c>
-      <c r="B9" s="126"/>
-      <c r="C9" s="126"/>
-      <c r="D9" s="126"/>
-      <c r="E9" s="126"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="126"/>
-      <c r="H9" s="126"/>
-      <c r="I9" s="126"/>
-      <c r="J9" s="126"/>
-      <c r="K9" s="126"/>
-      <c r="L9" s="126"/>
-      <c r="M9" s="126"/>
-      <c r="N9" s="126"/>
-      <c r="O9" s="126"/>
-      <c r="P9" s="126"/>
-      <c r="Q9" s="126"/>
-      <c r="R9" s="126"/>
-      <c r="S9" s="126"/>
-      <c r="U9" s="48"/>
-      <c r="V9" s="48"/>
-      <c r="W9" s="48"/>
-      <c r="Z9" s="48"/>
-      <c r="AA9" s="48"/>
-      <c r="AB9" s="48"/>
-      <c r="AE9" s="48"/>
-      <c r="AF9" s="48"/>
-      <c r="AG9" s="48"/>
-    </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A10" s="126" t="s">
-        <v>212</v>
-      </c>
-      <c r="B10" s="126"/>
-      <c r="C10" s="126"/>
-      <c r="D10" s="126"/>
-      <c r="E10" s="126"/>
-      <c r="F10" s="126"/>
-      <c r="G10" s="126"/>
-      <c r="H10" s="126"/>
-      <c r="I10" s="126"/>
-      <c r="J10" s="126"/>
-      <c r="K10" s="126"/>
-      <c r="L10" s="126"/>
-      <c r="M10" s="126"/>
-      <c r="N10" s="126"/>
-      <c r="O10" s="126"/>
-      <c r="P10" s="126"/>
-      <c r="Q10" s="126"/>
-      <c r="R10" s="126"/>
-      <c r="S10" s="126"/>
-      <c r="U10" s="48"/>
-      <c r="V10" s="48"/>
-      <c r="W10" s="48"/>
-      <c r="Z10" s="48"/>
-      <c r="AA10" s="48"/>
-      <c r="AB10" s="48"/>
-      <c r="AE10" s="48"/>
-      <c r="AF10" s="48"/>
-      <c r="AG10" s="48"/>
-    </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A11" s="126" t="s">
-        <v>296</v>
-      </c>
-      <c r="B11" s="126"/>
-      <c r="C11" s="126"/>
-      <c r="D11" s="126"/>
-      <c r="E11" s="126"/>
-      <c r="F11" s="126"/>
-      <c r="G11" s="126"/>
-      <c r="H11" s="126"/>
-      <c r="I11" s="126"/>
-      <c r="J11" s="126"/>
-      <c r="K11" s="126"/>
-      <c r="L11" s="126"/>
-      <c r="M11" s="126"/>
-      <c r="N11" s="126"/>
-      <c r="O11" s="126"/>
-      <c r="P11" s="126"/>
-      <c r="Q11" s="126"/>
-      <c r="R11" s="126"/>
-      <c r="S11" s="126"/>
-      <c r="U11" s="48"/>
-      <c r="V11" s="48"/>
-      <c r="W11" s="48"/>
-      <c r="AE11" s="48"/>
-      <c r="AF11" s="48"/>
-      <c r="AG11" s="48"/>
-    </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A12" s="126" t="s">
-        <v>297</v>
-      </c>
-      <c r="B12" s="126"/>
-      <c r="C12" s="126"/>
-      <c r="D12" s="126"/>
-      <c r="E12" s="126"/>
-      <c r="F12" s="126"/>
-      <c r="G12" s="126"/>
-      <c r="H12" s="126"/>
-      <c r="I12" s="126"/>
-      <c r="J12" s="126"/>
-      <c r="K12" s="126"/>
-      <c r="L12" s="126"/>
-      <c r="M12" s="126"/>
-      <c r="N12" s="126"/>
-      <c r="O12" s="126"/>
-      <c r="P12" s="126"/>
-      <c r="Q12" s="126"/>
-      <c r="R12" s="126"/>
-      <c r="S12" s="126"/>
-    </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A13" s="126" t="s">
-        <v>298</v>
-      </c>
-      <c r="B13" s="126"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="126"/>
-      <c r="E13" s="126"/>
-      <c r="F13" s="126"/>
-      <c r="G13" s="126"/>
-      <c r="H13" s="126"/>
-      <c r="I13" s="126"/>
-      <c r="J13" s="126"/>
-      <c r="K13" s="126"/>
-      <c r="L13" s="126"/>
-      <c r="M13" s="126"/>
-      <c r="N13" s="126"/>
-      <c r="O13" s="126"/>
-      <c r="P13" s="126"/>
-      <c r="Q13" s="126"/>
-      <c r="R13" s="126"/>
-      <c r="S13" s="126"/>
-    </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="H14" s="126" t="s">
-        <v>218</v>
-      </c>
-      <c r="I14" s="126"/>
-      <c r="J14" s="126">
-        <f>Передача!D55</f>
-        <v>37.75</v>
-      </c>
-      <c r="K14" s="126"/>
-    </row>
-  </sheetData>
-  <mergeCells count="73">
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="P5:Q6"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="R5:S6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="J5:K6"/>
-    <mergeCell ref="L5:M6"/>
-    <mergeCell ref="N5:O6"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D5:E6"/>
-    <mergeCell ref="F5:G6"/>
-    <mergeCell ref="H5:I6"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC1D7275-A232-429A-A734-4E325D043F64}">
   <dimension ref="A1:AA38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8749,7 +7654,7 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="126" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B1" s="126"/>
       <c r="C1" s="126"/>
@@ -8759,7 +7664,7 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="93" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B2" s="93"/>
       <c r="C2" s="93"/>
@@ -8772,7 +7677,7 @@
         <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
@@ -8787,33 +7692,33 @@
         <v>3</v>
       </c>
       <c r="F3" s="54" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J3" s="93" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="K3" s="93"/>
       <c r="L3" s="93"/>
       <c r="M3" s="93"/>
       <c r="N3" s="93"/>
       <c r="T3" s="126" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="U3" s="126"/>
       <c r="V3" s="126"/>
       <c r="W3" s="126"/>
       <c r="X3" s="126" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="Y3" s="126"/>
       <c r="Z3" s="126" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AA3" s="126"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="93" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B4" s="93"/>
       <c r="C4" s="93"/>
@@ -8833,10 +7738,10 @@
         <v>2016</v>
       </c>
       <c r="N4" s="75" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="T4" s="126" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="U4" s="126"/>
       <c r="V4" s="126"/>
@@ -8847,23 +7752,23 @@
       <c r="Y4" s="126"/>
       <c r="Z4" s="126">
         <f ca="1">E19</f>
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AA4" s="126"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="125" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B5" s="125"/>
       <c r="C5" s="125"/>
       <c r="D5" s="125"/>
       <c r="E5" s="70" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F5" s="1"/>
       <c r="J5" s="132" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K5" s="132"/>
       <c r="L5" s="132"/>
@@ -8872,17 +7777,17 @@
         <v>734</v>
       </c>
       <c r="N5" s="75" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="T5" s="126" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="U5" s="126"/>
       <c r="V5" s="126"/>
       <c r="W5" s="126"/>
       <c r="X5" s="126">
         <f ca="1">E19</f>
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="Y5" s="126"/>
       <c r="Z5" s="126">
@@ -8893,7 +7798,7 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="126" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B6" s="126"/>
       <c r="C6" s="126"/>
@@ -8906,7 +7811,7 @@
         <v>16</v>
       </c>
       <c r="J6" s="132" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K6" s="132"/>
       <c r="L6" s="132"/>
@@ -8915,26 +7820,26 @@
         <v>0</v>
       </c>
       <c r="N6" s="75" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="T6" s="126" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="U6" s="126"/>
       <c r="V6" s="126"/>
       <c r="W6" s="126"/>
-      <c r="X6" s="148">
+      <c r="X6" s="147">
         <v>0.3</v>
       </c>
-      <c r="Y6" s="148"/>
-      <c r="Z6" s="148">
+      <c r="Y6" s="147"/>
+      <c r="Z6" s="147">
         <v>0.3</v>
       </c>
-      <c r="AA6" s="148"/>
+      <c r="AA6" s="147"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="126" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B7" s="126"/>
       <c r="C7" s="126"/>
@@ -8947,25 +7852,25 @@
         <v>16</v>
       </c>
       <c r="T7" s="126" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="U7" s="126"/>
       <c r="V7" s="126"/>
       <c r="W7" s="126"/>
-      <c r="X7" s="148">
+      <c r="X7" s="147">
         <f>2.1*10^5</f>
         <v>210000</v>
       </c>
-      <c r="Y7" s="148"/>
-      <c r="Z7" s="148">
+      <c r="Y7" s="147"/>
+      <c r="Z7" s="147">
         <f>2.1*10^5</f>
         <v>210000</v>
       </c>
-      <c r="AA7" s="148"/>
+      <c r="AA7" s="147"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="93" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B8" s="93"/>
       <c r="C8" s="93"/>
@@ -8977,31 +7882,31 @@
       <c r="F8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="147" t="s">
-        <v>260</v>
-      </c>
-      <c r="K8" s="147"/>
-      <c r="L8" s="147"/>
-      <c r="M8" s="147"/>
-      <c r="N8" s="147"/>
+      <c r="J8" s="146" t="s">
+        <v>253</v>
+      </c>
+      <c r="K8" s="146"/>
+      <c r="L8" s="146"/>
+      <c r="M8" s="146"/>
+      <c r="N8" s="146"/>
       <c r="T8" s="126" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="U8" s="126"/>
       <c r="V8" s="126"/>
       <c r="W8" s="126"/>
-      <c r="X8" s="148">
+      <c r="X8" s="147">
         <v>330</v>
       </c>
-      <c r="Y8" s="148"/>
-      <c r="Z8" s="148">
+      <c r="Y8" s="147"/>
+      <c r="Z8" s="147">
         <v>330</v>
       </c>
-      <c r="AA8" s="148"/>
+      <c r="AA8" s="147"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="93" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B9" s="93"/>
       <c r="C9" s="93"/>
@@ -9014,19 +7919,19 @@
         <v>16</v>
       </c>
       <c r="J9" s="126" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K9" s="126"/>
       <c r="L9" s="126"/>
       <c r="M9">
-        <f>Передача!$E$5</f>
-        <v>320</v>
+        <f ca="1">Передача!$E$5</f>
+        <v>339.37130342425513</v>
       </c>
       <c r="N9" s="25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T9" s="126" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="U9" s="126"/>
       <c r="V9" s="126"/>
@@ -9038,13 +7943,13 @@
       <c r="Y9" s="126"/>
       <c r="Z9" s="126">
         <f ca="1">(Z5*Z5+Z4*Z4)/(Z5*Z5-Z4*Z4)+Z6</f>
-        <v>2.5820512820512818</v>
+        <v>3.22156862745098</v>
       </c>
       <c r="AA9" s="126"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="126" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B10" s="126"/>
       <c r="C10" s="126"/>
@@ -9057,7 +7962,7 @@
         <v>16</v>
       </c>
       <c r="J10" s="126" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K10" s="126"/>
       <c r="L10" s="126"/>
@@ -9065,10 +7970,10 @@
         <v>3</v>
       </c>
       <c r="N10" s="25" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="T10" s="126" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="U10" s="126"/>
       <c r="V10" s="126"/>
@@ -9080,13 +7985,13 @@
       <c r="Y10" s="126"/>
       <c r="Z10" s="126">
         <f ca="1">0.5*Z8*(1-(Z4*Z4/Z5/Z5))</f>
-        <v>100.546875</v>
+        <v>84.15</v>
       </c>
       <c r="AA10" s="126"/>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" s="126" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B11" s="126"/>
       <c r="C11" s="126"/>
@@ -9099,7 +8004,7 @@
         <v>16</v>
       </c>
       <c r="J11" s="126" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="K11" s="126"/>
       <c r="L11" s="126"/>
@@ -9108,24 +8013,24 @@
         <v>0.08</v>
       </c>
       <c r="O11" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="126" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B12" s="126"/>
       <c r="C12" s="126"/>
       <c r="D12" s="126"/>
       <c r="E12" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
       </c>
       <c r="J12" s="126" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="K12" s="126"/>
       <c r="L12" s="126"/>
@@ -9137,38 +8042,38 @@
         <v>16</v>
       </c>
       <c r="O12" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A13" s="149" t="s">
-        <v>224</v>
+      <c r="A13" s="148" t="s">
+        <v>220</v>
       </c>
       <c r="B13" s="126"/>
       <c r="C13" s="126"/>
       <c r="D13" s="126"/>
       <c r="E13" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F13" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="J13" s="126" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="K13" s="126"/>
       <c r="L13" s="126"/>
       <c r="M13">
         <f ca="1">2000*M10*M9/(PI()*E19*E19*M12*M11)</f>
-        <v>53.610086094112106</v>
+        <v>45.324768799937637</v>
       </c>
       <c r="N13" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="126" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B14" s="126"/>
       <c r="C14" s="126"/>
@@ -9181,34 +8086,34 @@
         <v>16</v>
       </c>
       <c r="J14" s="126" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="K14" s="126"/>
       <c r="L14" s="126"/>
       <c r="M14">
         <f ca="1">1000*M13*E19*(X9/X7+Z9/Z7)</f>
-        <v>41.893107570490528</v>
+        <v>47.398451032614524</v>
       </c>
       <c r="N14" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="126" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B15" s="126"/>
       <c r="C15" s="126"/>
       <c r="D15" s="126"/>
       <c r="E15">
         <f ca="1">(E18-E19)/2</f>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
       </c>
       <c r="J15" s="126" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="K15" s="126"/>
       <c r="L15" s="126"/>
@@ -9217,15 +8122,15 @@
         <v>0</v>
       </c>
       <c r="N15" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="O15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="126" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B16" s="126"/>
       <c r="C16" s="126"/>
@@ -9234,20 +8139,20 @@
         <v>1</v>
       </c>
       <c r="J16" s="126" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="K16" s="126"/>
       <c r="L16" s="126"/>
       <c r="N16" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="O16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="126" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B17" s="126"/>
       <c r="C17" s="126"/>
@@ -9260,21 +8165,21 @@
         <v>16</v>
       </c>
       <c r="J17" s="126" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="K17" s="126"/>
       <c r="L17" s="126"/>
       <c r="M17" s="25">
         <f ca="1">SUM(M14:M16)</f>
-        <v>41.893107570490528</v>
+        <v>47.398451032614524</v>
       </c>
       <c r="N17" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="126" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B18" s="126"/>
       <c r="C18" s="126"/>
@@ -9286,75 +8191,75 @@
         <v>16</v>
       </c>
       <c r="J18" s="126" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="K18" s="126"/>
       <c r="L18" s="126"/>
       <c r="M18">
         <f ca="1">MAX(X10:AA10)*M14/M13</f>
-        <v>128.93772893772891</v>
+        <v>172.54901960784315</v>
       </c>
       <c r="N18" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="147" t="s">
-        <v>244</v>
-      </c>
-      <c r="B19" s="147"/>
-      <c r="C19" s="147"/>
-      <c r="D19" s="147"/>
+      <c r="A19" s="146" t="s">
+        <v>237</v>
+      </c>
+      <c r="B19" s="146"/>
+      <c r="C19" s="146"/>
+      <c r="D19" s="146"/>
       <c r="E19" s="77">
         <f ca="1">Вал!$S$18</f>
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F19" s="77" t="s">
         <v>16</v>
       </c>
       <c r="J19" s="126" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="K19" s="126"/>
       <c r="L19" s="126"/>
       <c r="M19" s="90">
         <f ca="1">M18+M15</f>
-        <v>128.93772893772891</v>
+        <v>172.54901960784315</v>
       </c>
       <c r="N19" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="126" t="s">
-        <v>313</v>
+        <v>292</v>
       </c>
       <c r="B20" s="126"/>
       <c r="C20" s="126"/>
       <c r="D20" s="126"/>
       <c r="E20" s="52"/>
       <c r="F20" s="77" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="M20" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="126" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="B21" s="126"/>
       <c r="C21" s="126"/>
       <c r="D21" s="126"/>
       <c r="E21" s="92" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="F21" t="s">
         <v>16</v>
       </c>
       <c r="J21" s="126" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="K21" s="126"/>
       <c r="L21" s="126"/>
@@ -9365,22 +8270,22 @@
         <v>154</v>
       </c>
       <c r="O21" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="126" t="s">
-        <v>316</v>
+        <v>295</v>
       </c>
       <c r="B22" s="126"/>
       <c r="C22" s="126"/>
       <c r="D22" s="126"/>
       <c r="E22" s="52"/>
       <c r="F22" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="J22" s="126" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="K22" s="126"/>
       <c r="L22" s="126"/>
@@ -9390,7 +8295,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="126" t="s">
-        <v>317</v>
+        <v>296</v>
       </c>
       <c r="B23" s="126"/>
       <c r="C23" s="126"/>
@@ -9403,13 +8308,13 @@
         <v>16</v>
       </c>
       <c r="J23" s="126" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="K23" s="126"/>
       <c r="L23" s="126"/>
       <c r="M23">
         <f ca="1">PI()*E19*M12*(M21-M15)*M22/1000</f>
-        <v>161.1637031291564</v>
+        <v>180.50334750465515</v>
       </c>
       <c r="N23" t="s">
         <v>4</v>
@@ -9417,7 +8322,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="126" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B30" s="126"/>
       <c r="C30">
@@ -9447,7 +8352,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="126" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B31" s="126"/>
       <c r="C31">
@@ -9477,7 +8382,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="126" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B32" s="126"/>
       <c r="C32">
@@ -9507,29 +8412,29 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="126" t="s">
-        <v>306</v>
+        <v>285</v>
       </c>
       <c r="B34" s="126"/>
       <c r="C34" s="126" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="D34" s="126"/>
       <c r="E34" s="126" t="s">
-        <v>311</v>
+        <v>290</v>
       </c>
       <c r="F34" s="126"/>
       <c r="G34" s="126" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="H34" s="126"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="126" t="s">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="B35" s="126"/>
       <c r="C35" s="126" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
       <c r="D35" s="126"/>
       <c r="E35" s="126">
@@ -9543,11 +8448,11 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="126" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="B36" s="126"/>
       <c r="C36" s="126" t="s">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="D36" s="126"/>
       <c r="E36" s="126">
@@ -9561,11 +8466,11 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="126" t="s">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="B37" s="126"/>
       <c r="C37" s="126" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="D37" s="126"/>
       <c r="E37" s="126">
@@ -9579,11 +8484,11 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="126" t="s">
-        <v>309</v>
+        <v>288</v>
       </c>
       <c r="B38" s="126"/>
       <c r="C38" s="126" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="D38" s="126"/>
       <c r="E38" s="126">
@@ -9607,24 +8512,23 @@
     <mergeCell ref="E35:F35"/>
     <mergeCell ref="E36:F36"/>
     <mergeCell ref="E37:F37"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="C38:D38"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A7:D7"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A31:B31"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A7:D7"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
@@ -9639,6 +8543,7 @@
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A31:B31"/>
     <mergeCell ref="T6:W6"/>
     <mergeCell ref="X6:Y6"/>
     <mergeCell ref="J6:L6"/>
@@ -9693,26 +8598,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9158992-A036-481A-AB16-1E7B3E1F9E72}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B080B891-BABE-48BC-B741-A9DC893B6424}">
-  <dimension ref="A2:W22"/>
+  <dimension ref="A2:W29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="12" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="126" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B2" s="126"/>
       <c r="C2" s="126"/>
@@ -9725,9 +8621,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="126" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B3" s="126"/>
       <c r="C3" s="126"/>
@@ -9740,9 +8636,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="126" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B4" s="126"/>
       <c r="C4" s="126"/>
@@ -9755,9 +8651,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="126" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B5" s="126"/>
       <c r="C5" s="126"/>
@@ -9770,9 +8666,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="126" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B6" s="126"/>
       <c r="C6" s="126"/>
@@ -9785,9 +8681,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="126" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B7" s="126"/>
       <c r="C7" s="126"/>
@@ -9800,9 +8696,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="126" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B8" s="126"/>
       <c r="C8" s="126"/>
@@ -9815,9 +8711,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="126" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B9" s="126"/>
       <c r="C9" s="126"/>
@@ -9830,9 +8726,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="126" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B10" s="126"/>
       <c r="C10" s="126"/>
@@ -9844,9 +8740,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="126" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B11" s="126"/>
       <c r="C11" s="126"/>
@@ -9858,9 +8754,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="126" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B12" s="126"/>
       <c r="C12" s="126"/>
@@ -9868,9 +8764,9 @@
       <c r="E12" s="126"/>
       <c r="F12" s="126"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="126" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B13" s="126"/>
       <c r="C13" s="126"/>
@@ -9883,9 +8779,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="126" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B14" s="126"/>
       <c r="C14" s="126"/>
@@ -9898,7 +8794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="126" t="s">
         <v>19</v>
       </c>
@@ -9913,21 +8809,88 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="18:23" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K16" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A17" s="126" t="s">
+        <v>335</v>
+      </c>
+      <c r="B17" s="126"/>
+      <c r="C17" s="126"/>
+      <c r="D17" s="126"/>
+      <c r="E17" s="126"/>
+      <c r="F17" s="126"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A18" s="126" t="s">
+        <v>331</v>
+      </c>
+      <c r="B18" s="126"/>
+      <c r="C18" s="126"/>
+      <c r="D18" s="126"/>
+      <c r="E18">
+        <f>Вал!$K$4*PI()/30</f>
+        <v>150.79644737231007</v>
+      </c>
+      <c r="F18" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A19" s="126" t="s">
+        <v>332</v>
+      </c>
+      <c r="B19" s="126"/>
+      <c r="C19" s="126"/>
+      <c r="D19" s="126"/>
+      <c r="E19">
+        <f>Корпус!$E$18*MAX(Вал!$K$19,Вал!$K$7)/1000</f>
+        <v>7.3890259212431939</v>
+      </c>
+      <c r="F19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A20" s="126" t="s">
+        <v>336</v>
+      </c>
+      <c r="B20" s="126"/>
+      <c r="C20" s="126"/>
+      <c r="D20" s="126"/>
+      <c r="E20" s="52">
+        <v>504</v>
+      </c>
+      <c r="F20" t="s">
+        <v>232</v>
+      </c>
       <c r="R20" s="1"/>
       <c r="S20" s="36"/>
       <c r="T20" s="126" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="U20" s="126"/>
       <c r="V20" s="93" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="W20" s="93"/>
     </row>
-    <row r="21" spans="18:23" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A21" s="126" t="s">
+        <v>338</v>
+      </c>
+      <c r="B21" s="126"/>
+      <c r="C21" s="126"/>
+      <c r="D21" s="126"/>
+      <c r="E21" s="52"/>
+      <c r="F21" t="s">
+        <v>337</v>
+      </c>
       <c r="R21" s="98" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="S21" s="98"/>
       <c r="T21" s="93"/>
@@ -9935,22 +8898,75 @@
       <c r="V21" s="93"/>
       <c r="W21" s="93"/>
     </row>
-    <row r="22" spans="18:23" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A22" s="126" t="s">
+        <v>339</v>
+      </c>
+      <c r="B22" s="126"/>
+      <c r="C22" s="126"/>
+      <c r="D22" s="126"/>
+      <c r="E22" t="s">
+        <v>340</v>
+      </c>
       <c r="R22" s="98" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="S22" s="98"/>
       <c r="T22" s="93" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="U22" s="93"/>
       <c r="V22" s="94" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="W22" s="94"/>
     </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A23" s="126" t="s">
+        <v>341</v>
+      </c>
+      <c r="B23" s="126"/>
+      <c r="C23" s="126"/>
+      <c r="D23" s="126"/>
+      <c r="E23">
+        <f>MAX(4*Передача!$D$47,10)</f>
+        <v>10</v>
+      </c>
+      <c r="F23">
+        <f>MAX(Передача!$D$58/4,10)</f>
+        <v>79.375</v>
+      </c>
+      <c r="G23" t="s">
+        <v>16</v>
+      </c>
+      <c r="N23" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="K27" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="I28" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="I29" t="s">
+        <v>321</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="29">
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="V22:W22"/>
     <mergeCell ref="T22:U22"/>
     <mergeCell ref="R22:S22"/>
@@ -9980,7 +8996,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D8564D3-007A-4908-B584-B11BCC9DA655}">
   <dimension ref="A1:E80"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10631,4 +9647,1118 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D136A9F2-8845-4295-A8BD-25F04BE0EFA0}">
+  <dimension ref="A1:T34"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="23" width="6.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>4</v>
+      </c>
+      <c r="E2" s="93" t="s">
+        <v>224</v>
+      </c>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="126" t="s">
+        <v>259</v>
+      </c>
+      <c r="K2" s="126"/>
+      <c r="L2" s="126"/>
+      <c r="M2" s="126"/>
+      <c r="N2" s="126"/>
+      <c r="P2" s="126" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q2" s="126"/>
+      <c r="R2" s="126"/>
+      <c r="S2" s="126"/>
+      <c r="T2" s="126"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>5</v>
+      </c>
+      <c r="E3" s="132" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="132"/>
+      <c r="G3" s="132"/>
+      <c r="H3" s="60">
+        <f>Передача!$D$49</f>
+        <v>2016</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J3" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="K3" t="s">
+        <v>261</v>
+      </c>
+      <c r="P3" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>6</v>
+      </c>
+      <c r="E4" s="132" t="s">
+        <v>157</v>
+      </c>
+      <c r="F4" s="132"/>
+      <c r="G4" s="132"/>
+      <c r="H4" s="60">
+        <f>Передача!$D$50</f>
+        <v>734</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J4" s="126" t="s">
+        <v>303</v>
+      </c>
+      <c r="K4" s="126"/>
+      <c r="L4" s="126"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>7</v>
+      </c>
+      <c r="E5" s="132" t="s">
+        <v>158</v>
+      </c>
+      <c r="F5" s="132"/>
+      <c r="G5" s="132"/>
+      <c r="H5" s="60">
+        <f>Передача!$D$51</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J5" s="126" t="s">
+        <v>118</v>
+      </c>
+      <c r="K5" s="126"/>
+      <c r="L5" s="126"/>
+      <c r="M5">
+        <f>Вал!K16</f>
+        <v>40</v>
+      </c>
+      <c r="N5" t="s">
+        <v>16</v>
+      </c>
+      <c r="P5" s="126" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q5" s="126"/>
+      <c r="R5" s="126"/>
+      <c r="S5">
+        <f ca="1">Вал!S15</f>
+        <v>50</v>
+      </c>
+      <c r="T5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>8</v>
+      </c>
+      <c r="J6" s="126" t="s">
+        <v>258</v>
+      </c>
+      <c r="K6" s="126"/>
+      <c r="L6" s="126"/>
+      <c r="M6" s="52">
+        <f>E16</f>
+        <v>208</v>
+      </c>
+      <c r="P6" s="126" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q6" s="126"/>
+      <c r="R6" s="126"/>
+      <c r="S6" s="52">
+        <f>E18</f>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>15</v>
+      </c>
+      <c r="E9" s="126" t="s">
+        <v>302</v>
+      </c>
+      <c r="F9" s="126"/>
+      <c r="G9" s="126"/>
+      <c r="H9" s="126"/>
+      <c r="I9" s="126"/>
+      <c r="J9" s="126"/>
+      <c r="K9" s="126"/>
+      <c r="L9" s="126"/>
+      <c r="M9" s="126"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>17</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="126">
+        <v>200</v>
+      </c>
+      <c r="F10" s="126"/>
+      <c r="G10" s="126"/>
+      <c r="H10" s="126">
+        <v>300</v>
+      </c>
+      <c r="I10" s="126"/>
+      <c r="J10" s="126"/>
+      <c r="K10" s="126">
+        <v>400</v>
+      </c>
+      <c r="L10" s="126"/>
+      <c r="M10" s="126"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>19</v>
+      </c>
+      <c r="E11" t="s">
+        <v>299</v>
+      </c>
+      <c r="F11" t="s">
+        <v>300</v>
+      </c>
+      <c r="G11" t="s">
+        <v>301</v>
+      </c>
+      <c r="H11" t="s">
+        <v>299</v>
+      </c>
+      <c r="I11" t="s">
+        <v>300</v>
+      </c>
+      <c r="J11" t="s">
+        <v>301</v>
+      </c>
+      <c r="K11" t="s">
+        <v>299</v>
+      </c>
+      <c r="L11" t="s">
+        <v>300</v>
+      </c>
+      <c r="M11" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>20</v>
+      </c>
+      <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="E12">
+        <v>204</v>
+      </c>
+      <c r="F12">
+        <v>47</v>
+      </c>
+      <c r="G12">
+        <v>14</v>
+      </c>
+      <c r="H12">
+        <v>304</v>
+      </c>
+      <c r="I12">
+        <v>52</v>
+      </c>
+      <c r="J12">
+        <v>15</v>
+      </c>
+      <c r="K12">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>25</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <v>205</v>
+      </c>
+      <c r="F13">
+        <v>52</v>
+      </c>
+      <c r="G13">
+        <v>15</v>
+      </c>
+      <c r="H13">
+        <v>305</v>
+      </c>
+      <c r="I13">
+        <v>62</v>
+      </c>
+      <c r="J13">
+        <v>17</v>
+      </c>
+      <c r="K13">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>30</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="E14">
+        <v>206</v>
+      </c>
+      <c r="F14">
+        <v>62</v>
+      </c>
+      <c r="G14">
+        <v>16</v>
+      </c>
+      <c r="H14">
+        <v>306</v>
+      </c>
+      <c r="I14">
+        <v>72</v>
+      </c>
+      <c r="J14">
+        <v>19</v>
+      </c>
+      <c r="K14">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>35</v>
+      </c>
+      <c r="B15">
+        <v>7</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15">
+        <v>207</v>
+      </c>
+      <c r="F15">
+        <v>72</v>
+      </c>
+      <c r="G15">
+        <v>17</v>
+      </c>
+      <c r="H15">
+        <v>307</v>
+      </c>
+      <c r="I15">
+        <v>80</v>
+      </c>
+      <c r="J15">
+        <v>21</v>
+      </c>
+      <c r="K15">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>40</v>
+      </c>
+      <c r="B16">
+        <v>8</v>
+      </c>
+      <c r="E16">
+        <v>208</v>
+      </c>
+      <c r="F16">
+        <v>80</v>
+      </c>
+      <c r="G16">
+        <v>18</v>
+      </c>
+      <c r="H16">
+        <v>308</v>
+      </c>
+      <c r="I16">
+        <v>90</v>
+      </c>
+      <c r="J16">
+        <v>23</v>
+      </c>
+      <c r="K16">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>45</v>
+      </c>
+      <c r="B17">
+        <v>9</v>
+      </c>
+      <c r="E17">
+        <v>209</v>
+      </c>
+      <c r="F17">
+        <v>85</v>
+      </c>
+      <c r="G17">
+        <v>19</v>
+      </c>
+      <c r="H17">
+        <v>309</v>
+      </c>
+      <c r="I17">
+        <v>100</v>
+      </c>
+      <c r="J17">
+        <v>25</v>
+      </c>
+      <c r="K17">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>50</v>
+      </c>
+      <c r="B18">
+        <v>10</v>
+      </c>
+      <c r="E18">
+        <v>210</v>
+      </c>
+      <c r="F18">
+        <v>90</v>
+      </c>
+      <c r="G18">
+        <v>20</v>
+      </c>
+      <c r="H18">
+        <v>310</v>
+      </c>
+      <c r="I18">
+        <v>110</v>
+      </c>
+      <c r="J18">
+        <v>27</v>
+      </c>
+      <c r="K18">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>55</v>
+      </c>
+      <c r="B19">
+        <v>11</v>
+      </c>
+      <c r="E19">
+        <v>211</v>
+      </c>
+      <c r="F19">
+        <v>100</v>
+      </c>
+      <c r="G19">
+        <v>21</v>
+      </c>
+      <c r="H19">
+        <v>311</v>
+      </c>
+      <c r="I19">
+        <v>120</v>
+      </c>
+      <c r="J19">
+        <v>29</v>
+      </c>
+      <c r="K19">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>60</v>
+      </c>
+      <c r="B20">
+        <v>12</v>
+      </c>
+      <c r="E20">
+        <v>212</v>
+      </c>
+      <c r="F20">
+        <v>110</v>
+      </c>
+      <c r="G20">
+        <v>22</v>
+      </c>
+      <c r="H20">
+        <v>312</v>
+      </c>
+      <c r="I20">
+        <v>130</v>
+      </c>
+      <c r="J20">
+        <v>31</v>
+      </c>
+      <c r="K20">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>65</v>
+      </c>
+      <c r="B21">
+        <v>13</v>
+      </c>
+      <c r="E21">
+        <v>213</v>
+      </c>
+      <c r="F21">
+        <v>120</v>
+      </c>
+      <c r="G21">
+        <v>23</v>
+      </c>
+      <c r="H21">
+        <v>313</v>
+      </c>
+      <c r="I21">
+        <v>140</v>
+      </c>
+      <c r="J21">
+        <v>33</v>
+      </c>
+      <c r="K21">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>70</v>
+      </c>
+      <c r="B22">
+        <v>14</v>
+      </c>
+      <c r="E22">
+        <v>214</v>
+      </c>
+      <c r="F22">
+        <v>125</v>
+      </c>
+      <c r="G22">
+        <v>24</v>
+      </c>
+      <c r="H22">
+        <v>314</v>
+      </c>
+      <c r="I22">
+        <v>150</v>
+      </c>
+      <c r="J22">
+        <v>35</v>
+      </c>
+      <c r="K22">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>75</v>
+      </c>
+      <c r="B23">
+        <v>15</v>
+      </c>
+      <c r="E23">
+        <v>215</v>
+      </c>
+      <c r="F23">
+        <v>130</v>
+      </c>
+      <c r="G23">
+        <v>25</v>
+      </c>
+      <c r="H23">
+        <v>315</v>
+      </c>
+      <c r="I23">
+        <v>160</v>
+      </c>
+      <c r="J23">
+        <v>37</v>
+      </c>
+      <c r="K23">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>80</v>
+      </c>
+      <c r="B24">
+        <v>16</v>
+      </c>
+      <c r="E24">
+        <v>216</v>
+      </c>
+      <c r="F24">
+        <v>140</v>
+      </c>
+      <c r="G24">
+        <v>26</v>
+      </c>
+      <c r="H24">
+        <v>316</v>
+      </c>
+      <c r="I24">
+        <v>170</v>
+      </c>
+      <c r="J24">
+        <v>39</v>
+      </c>
+      <c r="K24">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>85</v>
+      </c>
+      <c r="B25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>90</v>
+      </c>
+      <c r="B26">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>95</v>
+      </c>
+      <c r="B27">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>100</v>
+      </c>
+      <c r="B28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>105</v>
+      </c>
+      <c r="B29">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>110</v>
+      </c>
+      <c r="B30">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>115</v>
+      </c>
+      <c r="B31">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>120</v>
+      </c>
+      <c r="B32">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>125</v>
+      </c>
+      <c r="B33">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>130</v>
+      </c>
+      <c r="B34">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="E9:M9"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="J2:N2"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="E2:I2"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="E4:G4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32704C68-B145-4DB6-B0E3-AE1BF65D15BC}">
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="18" width="6.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="126" t="s">
+        <v>266</v>
+      </c>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126" t="s">
+        <v>182</v>
+      </c>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126" t="s">
+        <v>273</v>
+      </c>
+      <c r="F1" s="126"/>
+      <c r="G1" s="126" t="s">
+        <v>276</v>
+      </c>
+      <c r="H1" s="126"/>
+      <c r="I1" s="126"/>
+      <c r="J1" s="126"/>
+      <c r="K1" s="126"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="126"/>
+      <c r="B2" s="126"/>
+      <c r="C2" s="126" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2" s="126"/>
+      <c r="E2" s="126" t="s">
+        <v>275</v>
+      </c>
+      <c r="F2" s="126"/>
+      <c r="G2" s="91" t="s">
+        <v>277</v>
+      </c>
+      <c r="H2" s="91" t="s">
+        <v>278</v>
+      </c>
+      <c r="I2" s="91" t="s">
+        <v>279</v>
+      </c>
+      <c r="J2" s="91" t="s">
+        <v>280</v>
+      </c>
+      <c r="K2" s="91" t="s">
+        <v>281</v>
+      </c>
+      <c r="L2" s="91" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="126" t="s">
+        <v>267</v>
+      </c>
+      <c r="B3" s="126"/>
+      <c r="C3" s="126">
+        <v>1000</v>
+      </c>
+      <c r="D3" s="126"/>
+      <c r="E3" s="126">
+        <v>190</v>
+      </c>
+      <c r="F3" s="126"/>
+      <c r="G3">
+        <v>520</v>
+      </c>
+      <c r="H3">
+        <v>280</v>
+      </c>
+      <c r="I3">
+        <v>150</v>
+      </c>
+      <c r="J3">
+        <v>220</v>
+      </c>
+      <c r="K3">
+        <v>130</v>
+      </c>
+      <c r="L3">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="126">
+        <v>45</v>
+      </c>
+      <c r="B4" s="126"/>
+      <c r="C4" s="126">
+        <v>120</v>
+      </c>
+      <c r="D4" s="126"/>
+      <c r="E4" s="126">
+        <v>227</v>
+      </c>
+      <c r="F4" s="126"/>
+      <c r="G4">
+        <v>820</v>
+      </c>
+      <c r="H4">
+        <v>640</v>
+      </c>
+      <c r="I4">
+        <v>290</v>
+      </c>
+      <c r="J4">
+        <v>360</v>
+      </c>
+      <c r="K4">
+        <v>200</v>
+      </c>
+      <c r="L4">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="126">
+        <v>45</v>
+      </c>
+      <c r="B5" s="126"/>
+      <c r="C5" s="126">
+        <v>80</v>
+      </c>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126">
+        <v>260</v>
+      </c>
+      <c r="F5" s="126"/>
+      <c r="G5">
+        <v>900</v>
+      </c>
+      <c r="H5">
+        <v>650</v>
+      </c>
+      <c r="I5">
+        <v>390</v>
+      </c>
+      <c r="J5">
+        <v>410</v>
+      </c>
+      <c r="K5">
+        <v>230</v>
+      </c>
+      <c r="L5">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="126" t="s">
+        <v>268</v>
+      </c>
+      <c r="B6" s="126"/>
+      <c r="C6" s="126">
+        <v>200</v>
+      </c>
+      <c r="D6" s="126"/>
+      <c r="E6" s="126">
+        <v>240</v>
+      </c>
+      <c r="F6" s="126"/>
+      <c r="G6">
+        <v>790</v>
+      </c>
+      <c r="H6">
+        <v>640</v>
+      </c>
+      <c r="I6">
+        <v>380</v>
+      </c>
+      <c r="J6">
+        <v>370</v>
+      </c>
+      <c r="K6">
+        <v>210</v>
+      </c>
+      <c r="L6">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="126" t="s">
+        <v>268</v>
+      </c>
+      <c r="B7" s="126"/>
+      <c r="C7" s="126">
+        <v>120</v>
+      </c>
+      <c r="D7" s="126"/>
+      <c r="E7" s="126">
+        <v>270</v>
+      </c>
+      <c r="F7" s="126"/>
+      <c r="G7">
+        <v>980</v>
+      </c>
+      <c r="H7">
+        <v>780</v>
+      </c>
+      <c r="I7">
+        <v>450</v>
+      </c>
+      <c r="J7">
+        <v>410</v>
+      </c>
+      <c r="K7">
+        <v>240</v>
+      </c>
+      <c r="L7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="126" t="s">
+        <v>269</v>
+      </c>
+      <c r="B8" s="126"/>
+      <c r="C8" s="126">
+        <v>200</v>
+      </c>
+      <c r="D8" s="126"/>
+      <c r="E8" s="126">
+        <v>270</v>
+      </c>
+      <c r="F8" s="126"/>
+      <c r="G8">
+        <v>980</v>
+      </c>
+      <c r="H8">
+        <v>750</v>
+      </c>
+      <c r="I8">
+        <v>450</v>
+      </c>
+      <c r="J8">
+        <v>420</v>
+      </c>
+      <c r="K8">
+        <v>2300</v>
+      </c>
+      <c r="L8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="126" t="s">
+        <v>270</v>
+      </c>
+      <c r="B9" s="126"/>
+      <c r="C9" s="126">
+        <v>120</v>
+      </c>
+      <c r="D9" s="126"/>
+      <c r="E9" s="126">
+        <v>197</v>
+      </c>
+      <c r="F9" s="126"/>
+      <c r="G9">
+        <v>650</v>
+      </c>
+      <c r="H9">
+        <v>400</v>
+      </c>
+      <c r="I9">
+        <v>240</v>
+      </c>
+      <c r="J9">
+        <v>310</v>
+      </c>
+      <c r="K9">
+        <v>170</v>
+      </c>
+      <c r="L9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="126" t="s">
+        <v>271</v>
+      </c>
+      <c r="B10" s="126"/>
+      <c r="C10" s="126">
+        <v>120</v>
+      </c>
+      <c r="D10" s="126"/>
+      <c r="E10" s="126">
+        <v>260</v>
+      </c>
+      <c r="F10" s="126"/>
+      <c r="G10">
+        <v>930</v>
+      </c>
+      <c r="H10">
+        <v>685</v>
+      </c>
+      <c r="I10">
+        <v>490</v>
+      </c>
+      <c r="J10">
+        <v>430</v>
+      </c>
+      <c r="K10">
+        <v>240</v>
+      </c>
+      <c r="L10">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="126" t="s">
+        <v>272</v>
+      </c>
+      <c r="B11" s="126"/>
+      <c r="C11" s="126">
+        <v>60</v>
+      </c>
+      <c r="D11" s="126"/>
+      <c r="E11" s="126">
+        <v>330</v>
+      </c>
+      <c r="F11" s="126"/>
+      <c r="G11">
+        <v>1180</v>
+      </c>
+      <c r="H11">
+        <v>930</v>
+      </c>
+      <c r="I11">
+        <v>660</v>
+      </c>
+      <c r="J11">
+        <v>500</v>
+      </c>
+      <c r="K11">
+        <v>280</v>
+      </c>
+      <c r="L11">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="48"/>
+      <c r="B12" s="48"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="48"/>
+      <c r="B13" s="48"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="48"/>
+      <c r="B14" s="48"/>
+    </row>
+  </sheetData>
+  <mergeCells count="33">
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G1:K1"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Расчёт.xlsx
+++ b/Расчёт.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Professional\Downloads\интститут\курсач детмаш\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C47ED9DA-5D3A-4102-96FE-EE27852628FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE5F152-963E-4BC7-B908-BC6DCFC4A096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="812" activeTab="4" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="812" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
   </bookViews>
   <sheets>
     <sheet name="Электродвигатель" sheetId="1" r:id="rId1"/>
@@ -1438,34 +1438,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1474,37 +1465,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1534,22 +1513,55 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1564,26 +1576,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1594,16 +1591,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2200,23 +2200,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="97" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A2" s="107" t="s">
+      <c r="A2" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="100"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
       <c r="E2" s="19">
         <v>4</v>
       </c>
@@ -2224,22 +2224,22 @@
         <v>4</v>
       </c>
       <c r="G2" s="6"/>
-      <c r="I2" s="107" t="s">
+      <c r="I2" s="97" t="s">
         <v>54</v>
       </c>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
-      <c r="M2" s="100">
+      <c r="J2" s="98"/>
+      <c r="K2" s="98"/>
+      <c r="L2" s="98"/>
+      <c r="M2" s="98">
         <f>E2*E3</f>
         <v>6.4</v>
       </c>
-      <c r="N2" s="115"/>
-      <c r="Q2" s="107" t="s">
+      <c r="N2" s="99"/>
+      <c r="Q2" s="97" t="s">
         <v>29</v>
       </c>
-      <c r="R2" s="100"/>
-      <c r="S2" s="100"/>
+      <c r="R2" s="98"/>
+      <c r="S2" s="98"/>
       <c r="T2" s="8" t="s">
         <v>30</v>
       </c>
@@ -2249,11 +2249,11 @@
       <c r="V2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AC2" s="107" t="s">
+      <c r="AC2" s="97" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="100"/>
-      <c r="AE2" s="100"/>
+      <c r="AD2" s="98"/>
+      <c r="AE2" s="98"/>
       <c r="AF2" s="8" t="s">
         <v>44</v>
       </c>
@@ -2272,12 +2272,12 @@
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A3" s="99" t="s">
+      <c r="A3" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
       <c r="E3" s="20">
         <v>1.6</v>
       </c>
@@ -2285,19 +2285,19 @@
         <v>5</v>
       </c>
       <c r="G3" s="3"/>
-      <c r="I3" s="99" t="s">
+      <c r="I3" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="93"/>
-      <c r="K3" s="93"/>
-      <c r="L3" s="93"/>
-      <c r="M3" s="93"/>
-      <c r="N3" s="110"/>
-      <c r="Q3" s="99" t="s">
+      <c r="J3" s="94"/>
+      <c r="K3" s="94"/>
+      <c r="L3" s="94"/>
+      <c r="M3" s="94"/>
+      <c r="N3" s="105"/>
+      <c r="Q3" s="93" t="s">
         <v>132</v>
       </c>
-      <c r="R3" s="93"/>
-      <c r="S3" s="93"/>
+      <c r="R3" s="94"/>
+      <c r="S3" s="94"/>
       <c r="T3" s="1">
         <v>0.96</v>
       </c>
@@ -2308,11 +2308,11 @@
         <f>AVERAGE(T3:U3)</f>
         <v>0.97</v>
       </c>
-      <c r="AC3" s="99" t="s">
+      <c r="AC3" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="AD3" s="93"/>
-      <c r="AE3" s="93"/>
+      <c r="AD3" s="94"/>
+      <c r="AE3" s="94"/>
       <c r="AF3" s="1">
         <v>1.6</v>
       </c>
@@ -2337,30 +2337,30 @@
       </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A4" s="99" t="s">
+      <c r="A4" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="93"/>
-      <c r="C4" s="93"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="108" t="s">
+      <c r="B4" s="94"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="108"/>
-      <c r="G4" s="109"/>
-      <c r="I4" s="99" t="s">
+      <c r="F4" s="102"/>
+      <c r="G4" s="108"/>
+      <c r="I4" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="93"/>
-      <c r="K4" s="93"/>
-      <c r="L4" s="93"/>
-      <c r="M4" s="93"/>
-      <c r="N4" s="110"/>
-      <c r="Q4" s="99" t="s">
+      <c r="J4" s="94"/>
+      <c r="K4" s="94"/>
+      <c r="L4" s="94"/>
+      <c r="M4" s="94"/>
+      <c r="N4" s="105"/>
+      <c r="Q4" s="93" t="s">
         <v>49</v>
       </c>
-      <c r="R4" s="93"/>
-      <c r="S4" s="93"/>
+      <c r="R4" s="94"/>
+      <c r="S4" s="94"/>
       <c r="T4" s="1">
         <v>0.95</v>
       </c>
@@ -2371,11 +2371,11 @@
         <f t="shared" ref="V4:V12" si="1">AVERAGE(T4:U4)</f>
         <v>0.96</v>
       </c>
-      <c r="AC4" s="99" t="s">
+      <c r="AC4" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="AD4" s="93"/>
-      <c r="AE4" s="93"/>
+      <c r="AD4" s="94"/>
+      <c r="AE4" s="94"/>
       <c r="AF4" s="1">
         <v>1</v>
       </c>
@@ -2400,12 +2400,12 @@
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A5" s="99" t="s">
+      <c r="A5" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="93"/>
-      <c r="C5" s="93"/>
-      <c r="D5" s="93"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
       <c r="E5" s="21">
         <v>10000</v>
       </c>
@@ -2415,19 +2415,19 @@
       <c r="G5" s="3"/>
       <c r="I5" s="7"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="93" t="s">
+      <c r="K5" s="94" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="93"/>
-      <c r="M5" s="93" t="s">
+      <c r="L5" s="94"/>
+      <c r="M5" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="110"/>
-      <c r="Q5" s="99" t="s">
+      <c r="N5" s="105"/>
+      <c r="Q5" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="R5" s="93"/>
-      <c r="S5" s="93"/>
+      <c r="R5" s="94"/>
+      <c r="S5" s="94"/>
       <c r="T5" s="1">
         <v>0.95</v>
       </c>
@@ -2438,11 +2438,11 @@
         <f t="shared" si="1"/>
         <v>0.96</v>
       </c>
-      <c r="AC5" s="99" t="s">
+      <c r="AC5" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="AD5" s="93"/>
-      <c r="AE5" s="93"/>
+      <c r="AD5" s="94"/>
+      <c r="AE5" s="94"/>
       <c r="AF5" s="1">
         <v>3.15</v>
       </c>
@@ -2467,34 +2467,34 @@
       </c>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A6" s="99" t="s">
+      <c r="A6" s="93" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="93"/>
-      <c r="C6" s="93"/>
-      <c r="D6" s="93"/>
+      <c r="B6" s="94"/>
+      <c r="C6" s="94"/>
+      <c r="D6" s="94"/>
       <c r="E6" s="21">
         <v>0.9</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="3"/>
-      <c r="I6" s="99" t="s">
+      <c r="I6" s="93" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="93"/>
-      <c r="K6" s="108">
+      <c r="J6" s="94"/>
+      <c r="K6" s="102">
         <v>2</v>
       </c>
-      <c r="L6" s="108"/>
-      <c r="M6" s="93">
+      <c r="L6" s="102"/>
+      <c r="M6" s="94">
         <v>0.99</v>
       </c>
-      <c r="N6" s="110"/>
-      <c r="Q6" s="99" t="s">
+      <c r="N6" s="105"/>
+      <c r="Q6" s="93" t="s">
         <v>33</v>
       </c>
-      <c r="R6" s="93"/>
-      <c r="S6" s="93"/>
+      <c r="R6" s="94"/>
+      <c r="S6" s="94"/>
       <c r="T6" s="1">
         <v>0.92</v>
       </c>
@@ -2505,11 +2505,11 @@
         <f t="shared" si="1"/>
         <v>0.94</v>
       </c>
-      <c r="AC6" s="99" t="s">
+      <c r="AC6" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="AD6" s="93"/>
-      <c r="AE6" s="93"/>
+      <c r="AD6" s="94"/>
+      <c r="AE6" s="94"/>
       <c r="AF6" s="1">
         <v>12.5</v>
       </c>
@@ -2534,34 +2534,34 @@
       </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A7" s="99" t="s">
+      <c r="A7" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="93"/>
-      <c r="C7" s="93"/>
-      <c r="D7" s="93"/>
+      <c r="B7" s="94"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
       <c r="E7" s="21">
         <v>3</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="3"/>
-      <c r="I7" s="99" t="s">
+      <c r="I7" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="93"/>
-      <c r="K7" s="108">
+      <c r="J7" s="94"/>
+      <c r="K7" s="102">
         <v>2</v>
       </c>
-      <c r="L7" s="108"/>
-      <c r="M7" s="93">
+      <c r="L7" s="102"/>
+      <c r="M7" s="94">
         <v>0.98</v>
       </c>
-      <c r="N7" s="110"/>
-      <c r="Q7" s="99" t="s">
+      <c r="N7" s="105"/>
+      <c r="Q7" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="R7" s="93"/>
-      <c r="S7" s="93"/>
+      <c r="R7" s="94"/>
+      <c r="S7" s="94"/>
       <c r="T7" s="1">
         <v>0.72</v>
       </c>
@@ -2572,11 +2572,11 @@
         <f t="shared" si="1"/>
         <v>0.77</v>
       </c>
-      <c r="AC7" s="99" t="s">
+      <c r="AC7" s="93" t="s">
         <v>33</v>
       </c>
-      <c r="AD7" s="93"/>
-      <c r="AE7" s="93"/>
+      <c r="AD7" s="94"/>
+      <c r="AE7" s="94"/>
       <c r="AF7" s="1">
         <v>16</v>
       </c>
@@ -2601,35 +2601,35 @@
       </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A8" s="103" t="s">
+      <c r="A8" s="100" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="104"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
+      <c r="B8" s="101"/>
+      <c r="C8" s="101"/>
+      <c r="D8" s="101"/>
       <c r="E8" s="22">
         <v>2.2000000000000002</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="5"/>
-      <c r="I8" s="99" t="s">
+      <c r="I8" s="93" t="s">
         <v>257</v>
       </c>
-      <c r="J8" s="93"/>
-      <c r="K8" s="108">
+      <c r="J8" s="94"/>
+      <c r="K8" s="102">
         <v>0</v>
       </c>
-      <c r="L8" s="108"/>
-      <c r="M8" s="125">
+      <c r="L8" s="102"/>
+      <c r="M8" s="103">
         <f>V11</f>
         <v>0.95</v>
       </c>
-      <c r="N8" s="130"/>
-      <c r="Q8" s="99" t="s">
+      <c r="N8" s="104"/>
+      <c r="Q8" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="R8" s="93"/>
-      <c r="S8" s="93"/>
+      <c r="R8" s="94"/>
+      <c r="S8" s="94"/>
       <c r="T8" s="1">
         <v>0.7</v>
       </c>
@@ -2640,11 +2640,11 @@
         <f t="shared" si="1"/>
         <v>0.75</v>
       </c>
-      <c r="AC8" s="99" t="s">
+      <c r="AC8" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="AD8" s="93"/>
-      <c r="AE8" s="93"/>
+      <c r="AD8" s="94"/>
+      <c r="AE8" s="94"/>
       <c r="AF8" s="1">
         <v>10</v>
       </c>
@@ -2669,31 +2669,31 @@
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A9" s="116" t="s">
+      <c r="A9" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="117"/>
-      <c r="C9" s="117"/>
-      <c r="D9" s="117"/>
-      <c r="E9" s="117"/>
-      <c r="F9" s="117"/>
-      <c r="G9" s="118"/>
-      <c r="I9" s="99" t="s">
+      <c r="B9" s="110"/>
+      <c r="C9" s="110"/>
+      <c r="D9" s="110"/>
+      <c r="E9" s="110"/>
+      <c r="F9" s="110"/>
+      <c r="G9" s="111"/>
+      <c r="I9" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="J9" s="93"/>
-      <c r="K9" s="93"/>
-      <c r="L9" s="93"/>
-      <c r="M9" s="94">
+      <c r="J9" s="94"/>
+      <c r="K9" s="94"/>
+      <c r="L9" s="94"/>
+      <c r="M9" s="106">
         <f>M7^K7*M6^K6*M8^K8</f>
         <v>0.94128803999999988</v>
       </c>
-      <c r="N9" s="128"/>
-      <c r="Q9" s="99" t="s">
+      <c r="N9" s="107"/>
+      <c r="Q9" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="R9" s="93"/>
-      <c r="S9" s="93"/>
+      <c r="R9" s="94"/>
+      <c r="S9" s="94"/>
       <c r="T9" s="1">
         <v>0.75</v>
       </c>
@@ -2704,11 +2704,11 @@
         <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="AC9" s="99" t="s">
+      <c r="AC9" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="AD9" s="93"/>
-      <c r="AE9" s="93"/>
+      <c r="AD9" s="94"/>
+      <c r="AE9" s="94"/>
       <c r="AF9" s="1">
         <v>8</v>
       </c>
@@ -2733,30 +2733,30 @@
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A10" s="119" t="s">
+      <c r="A10" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="120"/>
-      <c r="C10" s="120"/>
-      <c r="D10" s="120"/>
-      <c r="E10" s="120"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="121"/>
-      <c r="I10" s="99" t="s">
+      <c r="B10" s="113"/>
+      <c r="C10" s="113"/>
+      <c r="D10" s="113"/>
+      <c r="E10" s="113"/>
+      <c r="F10" s="113"/>
+      <c r="G10" s="114"/>
+      <c r="I10" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="J10" s="93"/>
-      <c r="K10" s="93"/>
-      <c r="L10" s="93"/>
-      <c r="M10" s="108">
+      <c r="J10" s="94"/>
+      <c r="K10" s="94"/>
+      <c r="L10" s="94"/>
+      <c r="M10" s="102">
         <v>0.97</v>
       </c>
-      <c r="N10" s="109"/>
-      <c r="Q10" s="99" t="s">
+      <c r="N10" s="108"/>
+      <c r="Q10" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="R10" s="93"/>
-      <c r="S10" s="93"/>
+      <c r="R10" s="94"/>
+      <c r="S10" s="94"/>
       <c r="T10" s="1">
         <v>0.8</v>
       </c>
@@ -2767,11 +2767,11 @@
         <f t="shared" si="1"/>
         <v>0.85000000000000009</v>
       </c>
-      <c r="AC10" s="103" t="s">
+      <c r="AC10" s="100" t="s">
         <v>34</v>
       </c>
-      <c r="AD10" s="104"/>
-      <c r="AE10" s="104"/>
+      <c r="AD10" s="101"/>
+      <c r="AE10" s="101"/>
       <c r="AF10" s="4">
         <v>70</v>
       </c>
@@ -2796,31 +2796,31 @@
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A11" s="116" t="s">
+      <c r="A11" s="109" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="117"/>
-      <c r="C11" s="117"/>
-      <c r="D11" s="117"/>
-      <c r="E11" s="117"/>
-      <c r="F11" s="117"/>
-      <c r="G11" s="118"/>
-      <c r="I11" s="103" t="s">
+      <c r="B11" s="110"/>
+      <c r="C11" s="110"/>
+      <c r="D11" s="110"/>
+      <c r="E11" s="110"/>
+      <c r="F11" s="110"/>
+      <c r="G11" s="111"/>
+      <c r="I11" s="100" t="s">
         <v>55</v>
       </c>
-      <c r="J11" s="104"/>
-      <c r="K11" s="104"/>
-      <c r="L11" s="104"/>
-      <c r="M11" s="105">
+      <c r="J11" s="101"/>
+      <c r="K11" s="101"/>
+      <c r="L11" s="101"/>
+      <c r="M11" s="95">
         <f>M2/M10/M9</f>
         <v>7.0094783572623509</v>
       </c>
-      <c r="N11" s="129"/>
-      <c r="Q11" s="99" t="s">
+      <c r="N11" s="96"/>
+      <c r="Q11" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="R11" s="93"/>
-      <c r="S11" s="93"/>
+      <c r="R11" s="94"/>
+      <c r="S11" s="94"/>
       <c r="T11" s="1">
         <v>0.94</v>
       </c>
@@ -2839,22 +2839,22 @@
       <c r="AH11" s="1"/>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A12" s="107" t="s">
+      <c r="A12" s="97" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="100"/>
-      <c r="C12" s="100"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="100" t="s">
+      <c r="B12" s="98"/>
+      <c r="C12" s="98"/>
+      <c r="D12" s="98"/>
+      <c r="E12" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="100"/>
-      <c r="G12" s="115"/>
-      <c r="Q12" s="103" t="s">
+      <c r="F12" s="98"/>
+      <c r="G12" s="99"/>
+      <c r="Q12" s="100" t="s">
         <v>39</v>
       </c>
-      <c r="R12" s="104"/>
-      <c r="S12" s="104"/>
+      <c r="R12" s="101"/>
+      <c r="S12" s="101"/>
       <c r="T12" s="4">
         <v>0.92</v>
       </c>
@@ -2870,12 +2870,12 @@
       </c>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A13" s="99" t="s">
+      <c r="A13" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="93"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="93"/>
+      <c r="B13" s="94"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="94"/>
       <c r="E13" s="21">
         <v>400</v>
       </c>
@@ -2890,12 +2890,12 @@
       </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A14" s="99" t="s">
+      <c r="A14" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="93"/>
-      <c r="C14" s="93"/>
-      <c r="D14" s="93"/>
+      <c r="B14" s="94"/>
+      <c r="C14" s="94"/>
+      <c r="D14" s="94"/>
       <c r="E14" s="21">
         <v>400</v>
       </c>
@@ -2905,12 +2905,12 @@
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A15" s="103" t="s">
+      <c r="A15" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="104"/>
-      <c r="C15" s="104"/>
-      <c r="D15" s="104"/>
+      <c r="B15" s="101"/>
+      <c r="C15" s="101"/>
+      <c r="D15" s="101"/>
       <c r="E15" s="22">
         <v>300</v>
       </c>
@@ -2933,43 +2933,43 @@
       <c r="B19" s="66" t="s">
         <v>306</v>
       </c>
-      <c r="I19" s="107" t="s">
+      <c r="I19" s="97" t="s">
         <v>121</v>
       </c>
-      <c r="J19" s="115"/>
-      <c r="K19" s="107">
+      <c r="J19" s="99"/>
+      <c r="K19" s="97">
         <v>3000</v>
       </c>
-      <c r="L19" s="100"/>
-      <c r="M19" s="100"/>
-      <c r="N19" s="115"/>
-      <c r="O19" s="100">
+      <c r="L19" s="98"/>
+      <c r="M19" s="98"/>
+      <c r="N19" s="99"/>
+      <c r="O19" s="98">
         <v>1500</v>
       </c>
-      <c r="P19" s="100"/>
-      <c r="Q19" s="100"/>
-      <c r="R19" s="100"/>
-      <c r="S19" s="107">
+      <c r="P19" s="98"/>
+      <c r="Q19" s="98"/>
+      <c r="R19" s="98"/>
+      <c r="S19" s="97">
         <v>1000</v>
       </c>
-      <c r="T19" s="100"/>
-      <c r="U19" s="100"/>
-      <c r="V19" s="115"/>
-      <c r="W19" s="100">
+      <c r="T19" s="98"/>
+      <c r="U19" s="98"/>
+      <c r="V19" s="99"/>
+      <c r="W19" s="98">
         <v>750</v>
       </c>
-      <c r="X19" s="100"/>
-      <c r="Y19" s="100"/>
-      <c r="Z19" s="115"/>
+      <c r="X19" s="98"/>
+      <c r="Y19" s="98"/>
+      <c r="Z19" s="99"/>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B20" s="66" t="s">
         <v>308</v>
       </c>
-      <c r="I20" s="103" t="s">
+      <c r="I20" s="100" t="s">
         <v>116</v>
       </c>
-      <c r="J20" s="127"/>
+      <c r="J20" s="119"/>
       <c r="K20" s="12" t="s">
         <v>72</v>
       </c>
@@ -3023,10 +3023,10 @@
       <c r="B21" s="66" t="s">
         <v>307</v>
       </c>
-      <c r="I21" s="99">
+      <c r="I21" s="93">
         <v>0.37</v>
       </c>
-      <c r="J21" s="93"/>
+      <c r="J21" s="94"/>
       <c r="K21" s="26" t="s">
         <v>57</v>
       </c>
@@ -3064,10 +3064,10 @@
       <c r="B22" s="66" t="s">
         <v>309</v>
       </c>
-      <c r="I22" s="99">
+      <c r="I22" s="93">
         <v>0.55000000000000004</v>
       </c>
-      <c r="J22" s="93"/>
+      <c r="J22" s="94"/>
       <c r="K22" s="26" t="s">
         <v>57</v>
       </c>
@@ -3103,10 +3103,10 @@
       <c r="B23" s="66" t="s">
         <v>310</v>
       </c>
-      <c r="I23" s="99">
+      <c r="I23" s="93">
         <v>0.75</v>
       </c>
-      <c r="J23" s="93"/>
+      <c r="J23" s="94"/>
       <c r="K23" s="7" t="s">
         <v>58</v>
       </c>
@@ -3142,10 +3142,10 @@
       <c r="B24" s="66" t="s">
         <v>311</v>
       </c>
-      <c r="I24" s="99">
+      <c r="I24" s="93">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J24" s="93"/>
+      <c r="J24" s="94"/>
       <c r="K24" s="7" t="s">
         <v>59</v>
       </c>
@@ -3181,10 +3181,10 @@
       <c r="B25" s="66" t="s">
         <v>313</v>
       </c>
-      <c r="I25" s="99">
+      <c r="I25" s="93">
         <v>1.5</v>
       </c>
-      <c r="J25" s="93"/>
+      <c r="J25" s="94"/>
       <c r="K25" s="7" t="s">
         <v>60</v>
       </c>
@@ -3220,10 +3220,10 @@
       <c r="B26" s="66" t="s">
         <v>312</v>
       </c>
-      <c r="I26" s="99">
+      <c r="I26" s="93">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J26" s="93"/>
+      <c r="J26" s="94"/>
       <c r="K26" s="7" t="s">
         <v>87</v>
       </c>
@@ -3259,10 +3259,10 @@
       <c r="B27" s="66" t="s">
         <v>315</v>
       </c>
-      <c r="I27" s="99">
+      <c r="I27" s="93">
         <v>3</v>
       </c>
-      <c r="J27" s="93"/>
+      <c r="J27" s="94"/>
       <c r="K27" s="7" t="s">
         <v>61</v>
       </c>
@@ -3296,10 +3296,10 @@
       <c r="B28" s="66" t="s">
         <v>316</v>
       </c>
-      <c r="I28" s="99">
+      <c r="I28" s="93">
         <v>4</v>
       </c>
-      <c r="J28" s="93"/>
+      <c r="J28" s="94"/>
       <c r="K28" s="7" t="s">
         <v>62</v>
       </c>
@@ -3336,10 +3336,10 @@
       <c r="B29" t="s">
         <v>328</v>
       </c>
-      <c r="I29" s="99">
+      <c r="I29" s="93">
         <v>5.5</v>
       </c>
-      <c r="J29" s="93"/>
+      <c r="J29" s="94"/>
       <c r="K29" s="7" t="s">
         <v>63</v>
       </c>
@@ -3393,10 +3393,10 @@
       <c r="B30" t="s">
         <v>327</v>
       </c>
-      <c r="I30" s="99">
+      <c r="I30" s="93">
         <v>7.5</v>
       </c>
-      <c r="J30" s="93"/>
+      <c r="J30" s="94"/>
       <c r="K30" s="7" t="s">
         <v>64</v>
       </c>
@@ -3450,10 +3450,10 @@
       <c r="B31" t="s">
         <v>314</v>
       </c>
-      <c r="I31" s="99">
+      <c r="I31" s="93">
         <v>11</v>
       </c>
-      <c r="J31" s="93"/>
+      <c r="J31" s="94"/>
       <c r="K31" s="7" t="s">
         <v>65</v>
       </c>
@@ -3507,10 +3507,10 @@
       <c r="B32" t="s">
         <v>317</v>
       </c>
-      <c r="I32" s="99">
+      <c r="I32" s="93">
         <v>15</v>
       </c>
-      <c r="J32" s="93"/>
+      <c r="J32" s="94"/>
       <c r="K32" s="7" t="s">
         <v>66</v>
       </c>
@@ -3541,10 +3541,10 @@
       <c r="Z32" s="3"/>
     </row>
     <row r="33" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="I33" s="99">
+      <c r="I33" s="93">
         <v>18.5</v>
       </c>
-      <c r="J33" s="93"/>
+      <c r="J33" s="94"/>
       <c r="K33" s="7" t="s">
         <v>67</v>
       </c>
@@ -3578,10 +3578,10 @@
       <c r="B34" t="s">
         <v>320</v>
       </c>
-      <c r="I34" s="99">
+      <c r="I34" s="93">
         <v>22</v>
       </c>
-      <c r="J34" s="93"/>
+      <c r="J34" s="94"/>
       <c r="K34" s="7" t="s">
         <v>68</v>
       </c>
@@ -3612,10 +3612,10 @@
       <c r="Z34" s="3"/>
     </row>
     <row r="35" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="I35" s="103">
+      <c r="I35" s="100">
         <v>30</v>
       </c>
-      <c r="J35" s="104"/>
+      <c r="J35" s="101"/>
       <c r="K35" s="12" t="s">
         <v>69</v>
       </c>
@@ -3649,15 +3649,15 @@
       <c r="B36" t="s">
         <v>318</v>
       </c>
-      <c r="G36" s="126" t="s">
+      <c r="G36" s="118" t="s">
         <v>119</v>
       </c>
-      <c r="H36" s="126"/>
-      <c r="I36" s="116">
+      <c r="H36" s="118"/>
+      <c r="I36" s="109">
         <f>_xlfn.MINIFS(I21:J35,I21:J35,"&gt;="&amp;M11)</f>
         <v>7.5</v>
       </c>
-      <c r="J36" s="117"/>
+      <c r="J36" s="110"/>
       <c r="K36" s="9" t="str">
         <f>VLOOKUP($I$36,$I$21:$R$35,3)</f>
         <v>112M2</v>
@@ -3736,12 +3736,12 @@
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
       <c r="F38" s="16"/>
-      <c r="G38" s="107" t="s">
+      <c r="G38" s="97" t="s">
         <v>40</v>
       </c>
-      <c r="H38" s="100"/>
-      <c r="I38" s="100"/>
-      <c r="J38" s="115"/>
+      <c r="H38" s="98"/>
+      <c r="I38" s="98"/>
+      <c r="J38" s="99"/>
       <c r="K38" s="11"/>
       <c r="L38" s="18"/>
       <c r="M38" s="18"/>
@@ -3767,12 +3767,12 @@
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
       <c r="F39" s="16"/>
-      <c r="G39" s="99" t="s">
+      <c r="G39" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="H39" s="93"/>
-      <c r="I39" s="93"/>
-      <c r="J39" s="110"/>
+      <c r="H39" s="94"/>
+      <c r="I39" s="94"/>
+      <c r="J39" s="105"/>
       <c r="K39" s="7"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -3810,14 +3810,14 @@
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
-      <c r="G40" s="99" t="s">
+      <c r="G40" s="93" t="s">
         <v>118</v>
       </c>
-      <c r="H40" s="93"/>
-      <c r="I40" s="93" t="s">
+      <c r="H40" s="94"/>
+      <c r="I40" s="94" t="s">
         <v>117</v>
       </c>
-      <c r="J40" s="110"/>
+      <c r="J40" s="105"/>
       <c r="K40" s="27" t="s">
         <v>120</v>
       </c>
@@ -3864,15 +3864,15 @@
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
-      <c r="G41" s="122">
+      <c r="G41" s="115">
         <v>160</v>
       </c>
-      <c r="H41" s="123"/>
-      <c r="I41" s="111">
+      <c r="H41" s="116"/>
+      <c r="I41" s="120">
         <f t="shared" ref="I41:I46" si="4">$E$3*60000/PI()/G41</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="J41" s="112"/>
+      <c r="J41" s="121"/>
       <c r="K41" s="15">
         <f t="shared" ref="K41:K46" si="5">IF($I41,L$36/$I41,"-")</f>
         <v>15.15818455357075</v>
@@ -3882,15 +3882,15 @@
         <v>Прямозубая 2</v>
       </c>
       <c r="M41" s="31">
-        <f ca="1">IF(K41&lt;&gt;"-",SUMIF($AC:$AE,L41,$AJ:$AJ)-K41*SUMIF($AC:$AE,L41,$AK:$AK),0)</f>
+        <f t="shared" ref="M41:M46" ca="1" si="6">IF(K41&lt;&gt;"-",SUMIF($AC:$AE,L41,$AJ:$AJ)-K41*SUMIF($AC:$AE,L41,$AK:$AK),0)</f>
         <v>0.95497170733270809</v>
       </c>
       <c r="N41" s="8">
-        <f ca="1">M41*N$39</f>
+        <f t="shared" ref="N41:N46" ca="1" si="7">M41*N$39</f>
         <v>0.78204599858607271</v>
       </c>
       <c r="O41" s="38">
-        <f t="shared" ref="O41:O46" si="6">IF($I41,P$36/$I41,"-")</f>
+        <f t="shared" ref="O41:O46" si="8">IF($I41,P$36/$I41,"-")</f>
         <v>7.5398223686155026</v>
       </c>
       <c r="P41" s="39" t="str">
@@ -3898,15 +3898,15 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="Q41" s="40">
-        <f ca="1">IF(O41&lt;&gt;"-",SUMIF($AC:$AE,P41,$AJ:$AJ)-O41*SUMIF($AC:$AE,P41,$AK:$AK),0)</f>
+        <f t="shared" ref="Q41:Q46" ca="1" si="9">IF(O41&lt;&gt;"-",SUMIF($AC:$AE,P41,$AJ:$AJ)-O41*SUMIF($AC:$AE,P41,$AK:$AK),0)</f>
         <v>0.96143805509807656</v>
       </c>
       <c r="R41" s="39">
-        <f ca="1">Q41*R$39</f>
+        <f t="shared" ref="R41:R46" ca="1" si="10">Q41*R$39</f>
         <v>0.78915140422920127</v>
       </c>
       <c r="S41" s="15">
-        <f t="shared" ref="S41:S46" si="7">IF($I41,T$36/$I41,"-")</f>
+        <f t="shared" ref="S41:S46" si="11">IF($I41,T$36/$I41,"-")</f>
         <v>5.0265482457436681</v>
       </c>
       <c r="T41" s="8" t="str">
@@ -3914,15 +3914,15 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="U41" s="31">
-        <f ca="1">IF(S41&lt;&gt;"-",SUMIF($AC:$AE,T41,$AJ:$AJ)-S41*SUMIF($AC:$AE,T41,$AK:$AK),0)</f>
+        <f t="shared" ref="U41:U46" ca="1" si="12">IF(S41&lt;&gt;"-",SUMIF($AC:$AE,T41,$AJ:$AJ)-S41*SUMIF($AC:$AE,T41,$AK:$AK),0)</f>
         <v>0.969292036732051</v>
       </c>
       <c r="V41" s="8">
-        <f ca="1">U41*V$39</f>
+        <f t="shared" ref="V41:V46" ca="1" si="13">U41*V$39</f>
         <v>0.78464938124108341</v>
       </c>
       <c r="W41" s="15">
-        <f t="shared" ref="W41:W46" si="8">IF($I41,X$36/$I41,"-")</f>
+        <f t="shared" ref="W41:W46" si="14">IF($I41,X$36/$I41,"-")</f>
         <v>3.8065630985996322</v>
       </c>
       <c r="X41" s="8" t="str">
@@ -3930,11 +3930,11 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="Y41" s="31">
-        <f ca="1">IF(W41&lt;&gt;"-",SUMIF($AC:$AE,X41,$AJ:$AJ)-W41*SUMIF($AC:$AE,X41,$AK:$AK),0)</f>
+        <f t="shared" ref="Y41:Y46" ca="1" si="15">IF(W41&lt;&gt;"-",SUMIF($AC:$AE,X41,$AJ:$AJ)-W41*SUMIF($AC:$AE,X41,$AK:$AK),0)</f>
         <v>0.97310449031687618</v>
       </c>
       <c r="Z41" s="6">
-        <f ca="1">Y41*Z$39</f>
+        <f t="shared" ref="Z41:Z46" ca="1" si="16">Y41*Z$39</f>
         <v>0.77857587564473563</v>
       </c>
     </row>
@@ -3946,15 +3946,15 @@
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-      <c r="G42" s="124">
+      <c r="G42" s="117">
         <v>200</v>
       </c>
-      <c r="H42" s="125"/>
-      <c r="I42" s="102">
+      <c r="H42" s="103"/>
+      <c r="I42" s="122">
         <f t="shared" si="4"/>
         <v>152.78874536821954</v>
       </c>
-      <c r="J42" s="113"/>
+      <c r="J42" s="123"/>
       <c r="K42" s="13">
         <f t="shared" si="5"/>
         <v>18.947730691963439</v>
@@ -3964,28 +3964,28 @@
         <v>Прямозубая 2</v>
       </c>
       <c r="M42" s="30">
-        <f ca="1">IF(K42&lt;&gt;"-",SUMIF($AC:$AE,L42,$AJ:$AJ)-K42*SUMIF($AC:$AE,L42,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="6"/>
         <v>0.94723305521851664</v>
       </c>
       <c r="N42" s="1">
-        <f ca="1">M42*N$39</f>
+        <f t="shared" ca="1" si="7"/>
         <v>0.77570865699376879</v>
       </c>
       <c r="O42" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9.4247779607693793</v>
       </c>
       <c r="P42" s="25"/>
       <c r="Q42" s="35">
-        <f ca="1">IF(O42&lt;&gt;"-",SUMIF($AC:$AE,P42,$AJ:$AJ)-O42*SUMIF($AC:$AE,P42,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
       <c r="R42" s="25">
-        <f ca="1">Q42*R$39</f>
+        <f t="shared" ca="1" si="10"/>
         <v>0</v>
       </c>
       <c r="S42" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>6.2831853071795862</v>
       </c>
       <c r="T42" s="1" t="str">
@@ -3993,15 +3993,15 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="U42" s="30">
-        <f ca="1">IF(S42&lt;&gt;"-",SUMIF($AC:$AE,T42,$AJ:$AJ)-S42*SUMIF($AC:$AE,T42,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="12"/>
         <v>0.96536504591506378</v>
       </c>
       <c r="V42" s="1">
-        <f ca="1">U42*V$39</f>
+        <f t="shared" ca="1" si="13"/>
         <v>0.78147045188035424</v>
       </c>
       <c r="W42" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>4.7582038732495402</v>
       </c>
       <c r="X42" s="1" t="str">
@@ -4009,11 +4009,11 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="Y42" s="30">
-        <f ca="1">IF(W42&lt;&gt;"-",SUMIF($AC:$AE,X42,$AJ:$AJ)-W42*SUMIF($AC:$AE,X42,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="15"/>
         <v>0.97013061289609515</v>
       </c>
       <c r="Z42" s="3">
-        <f ca="1">Y42*Z$39</f>
+        <f t="shared" ca="1" si="16"/>
         <v>0.77619649168341942</v>
       </c>
     </row>
@@ -4025,15 +4025,15 @@
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
-      <c r="G43" s="99">
+      <c r="G43" s="93">
         <v>250</v>
       </c>
-      <c r="H43" s="93"/>
-      <c r="I43" s="102">
+      <c r="H43" s="94"/>
+      <c r="I43" s="122">
         <f t="shared" si="4"/>
         <v>122.23099629457563</v>
       </c>
-      <c r="J43" s="113"/>
+      <c r="J43" s="123"/>
       <c r="K43" s="13">
         <f t="shared" si="5"/>
         <v>23.684663364954297</v>
@@ -4043,28 +4043,28 @@
         <v>Прямозубая 2</v>
       </c>
       <c r="M43" s="30">
-        <f ca="1">IF(K43&lt;&gt;"-",SUMIF($AC:$AE,L43,$AJ:$AJ)-K43*SUMIF($AC:$AE,L43,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="6"/>
         <v>0.93755974007577747</v>
       </c>
       <c r="N43" s="1">
-        <f ca="1">M43*N$39</f>
+        <f t="shared" ca="1" si="7"/>
         <v>0.76778698000338896</v>
       </c>
       <c r="O43" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>11.780972450961723</v>
       </c>
       <c r="P43" s="1"/>
       <c r="Q43" s="30">
-        <f ca="1">IF(O43&lt;&gt;"-",SUMIF($AC:$AE,P43,$AJ:$AJ)-O43*SUMIF($AC:$AE,P43,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
       <c r="R43" s="1">
-        <f ca="1">Q43*R$39</f>
+        <f t="shared" ca="1" si="10"/>
         <v>0</v>
       </c>
       <c r="S43" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>7.8539816339744819</v>
       </c>
       <c r="T43" s="1" t="str">
@@ -4072,15 +4072,15 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="U43" s="30">
-        <f ca="1">IF(S43&lt;&gt;"-",SUMIF($AC:$AE,T43,$AJ:$AJ)-S43*SUMIF($AC:$AE,T43,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="12"/>
         <v>0.9604563073938297</v>
       </c>
       <c r="V43" s="1">
-        <f ca="1">U43*V$39</f>
+        <f t="shared" ca="1" si="13"/>
         <v>0.77749679017944284</v>
       </c>
       <c r="W43" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>5.9477548415619257</v>
       </c>
       <c r="X43" s="1" t="str">
@@ -4088,11 +4088,11 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="Y43" s="30">
-        <f ca="1">IF(W43&lt;&gt;"-",SUMIF($AC:$AE,X43,$AJ:$AJ)-W43*SUMIF($AC:$AE,X43,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="15"/>
         <v>0.96641326612011891</v>
       </c>
       <c r="Z43" s="3">
-        <f ca="1">Y43*Z$39</f>
+        <f t="shared" ca="1" si="16"/>
         <v>0.77322226173177433</v>
       </c>
     </row>
@@ -4101,15 +4101,15 @@
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
-      <c r="G44" s="99">
+      <c r="G44" s="93">
         <v>315</v>
       </c>
-      <c r="H44" s="93"/>
-      <c r="I44" s="102">
+      <c r="H44" s="94"/>
+      <c r="I44" s="122">
         <f t="shared" si="4"/>
         <v>97.008727217917169</v>
       </c>
-      <c r="J44" s="113"/>
+      <c r="J44" s="123"/>
       <c r="K44" s="13">
         <f t="shared" si="5"/>
         <v>29.842675839842414</v>
@@ -4119,50 +4119,50 @@
         <v>Прямозубая 2</v>
       </c>
       <c r="M44" s="30">
-        <f ca="1">IF(K44&lt;&gt;"-",SUMIF($AC:$AE,L44,$AJ:$AJ)-K44*SUMIF($AC:$AE,L44,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="6"/>
         <v>0.92498443039021649</v>
       </c>
       <c r="N44" s="1">
-        <f ca="1">M44*N$39</f>
+        <f t="shared" ca="1" si="7"/>
         <v>0.75748879991589524</v>
       </c>
       <c r="O44" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>14.844025288211771</v>
       </c>
       <c r="P44" s="1"/>
       <c r="Q44" s="30">
-        <f ca="1">IF(O44&lt;&gt;"-",SUMIF($AC:$AE,P44,$AJ:$AJ)-O44*SUMIF($AC:$AE,P44,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
       <c r="R44" s="1">
-        <f ca="1">Q44*R$39</f>
+        <f t="shared" ca="1" si="10"/>
         <v>0</v>
       </c>
       <c r="S44" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>9.8960168588078474</v>
       </c>
       <c r="T44" s="1"/>
       <c r="U44" s="30">
-        <f ca="1">IF(S44&lt;&gt;"-",SUMIF($AC:$AE,T44,$AJ:$AJ)-S44*SUMIF($AC:$AE,T44,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="V44" s="1">
-        <f ca="1">U44*V$39</f>
+        <f t="shared" ca="1" si="13"/>
         <v>0</v>
       </c>
       <c r="W44" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>7.4941711003680265</v>
       </c>
       <c r="X44" s="1"/>
       <c r="Y44" s="30">
-        <f ca="1">IF(W44&lt;&gt;"-",SUMIF($AC:$AE,X44,$AJ:$AJ)-W44*SUMIF($AC:$AE,X44,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="15"/>
         <v>0</v>
       </c>
       <c r="Z44" s="3">
-        <f ca="1">Y44*Z$39</f>
+        <f t="shared" ca="1" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -4174,65 +4174,65 @@
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="99">
+      <c r="G45" s="93">
         <v>400</v>
       </c>
-      <c r="H45" s="93"/>
-      <c r="I45" s="102">
+      <c r="H45" s="94"/>
+      <c r="I45" s="122">
         <f t="shared" si="4"/>
         <v>76.394372684109769</v>
       </c>
-      <c r="J45" s="113"/>
+      <c r="J45" s="123"/>
       <c r="K45" s="13">
         <f t="shared" si="5"/>
         <v>37.895461383926879</v>
       </c>
       <c r="L45" s="1"/>
       <c r="M45" s="30">
-        <f ca="1">IF(K45&lt;&gt;"-",SUMIF($AC:$AE,L45,$AJ:$AJ)-K45*SUMIF($AC:$AE,L45,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="N45" s="1">
-        <f ca="1">M45*N$39</f>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="O45" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>18.849555921538759</v>
       </c>
       <c r="P45" s="1"/>
       <c r="Q45" s="30">
-        <f ca="1">IF(O45&lt;&gt;"-",SUMIF($AC:$AE,P45,$AJ:$AJ)-O45*SUMIF($AC:$AE,P45,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
       <c r="R45" s="1">
-        <f ca="1">Q45*R$39</f>
+        <f t="shared" ca="1" si="10"/>
         <v>0</v>
       </c>
       <c r="S45" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>12.566370614359172</v>
       </c>
       <c r="T45" s="1"/>
       <c r="U45" s="30">
-        <f ca="1">IF(S45&lt;&gt;"-",SUMIF($AC:$AE,T45,$AJ:$AJ)-S45*SUMIF($AC:$AE,T45,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
       <c r="V45" s="1">
-        <f ca="1">U45*V$39</f>
+        <f t="shared" ca="1" si="13"/>
         <v>0</v>
       </c>
       <c r="W45" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>9.5164077464990804</v>
       </c>
       <c r="X45" s="1"/>
       <c r="Y45" s="30">
-        <f ca="1">IF(W45&lt;&gt;"-",SUMIF($AC:$AE,X45,$AJ:$AJ)-W45*SUMIF($AC:$AE,X45,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="15"/>
         <v>0</v>
       </c>
       <c r="Z45" s="3">
-        <f ca="1">Y45*Z$39</f>
+        <f t="shared" ca="1" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -4244,15 +4244,15 @@
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-      <c r="G46" s="103">
+      <c r="G46" s="100">
         <v>500</v>
       </c>
-      <c r="H46" s="104"/>
-      <c r="I46" s="106">
+      <c r="H46" s="101"/>
+      <c r="I46" s="124">
         <f t="shared" si="4"/>
         <v>61.115498147287816</v>
       </c>
-      <c r="J46" s="114"/>
+      <c r="J46" s="125"/>
       <c r="K46" s="14">
         <f t="shared" si="5"/>
         <v>47.369326729908593</v>
@@ -4261,15 +4261,15 @@
         <v>100</v>
       </c>
       <c r="M46" s="32">
-        <f ca="1">IF(K46&lt;&gt;"-",SUMIF($AC:$AE,L46,$AJ:$AJ)-K46*SUMIF($AC:$AE,L46,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="N46" s="4">
-        <f ca="1">M46*N$39</f>
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="O46" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>23.561944901923447</v>
       </c>
       <c r="P46" s="37" t="str">
@@ -4277,15 +4277,15 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="Q46" s="32">
-        <f ca="1">IF(O46&lt;&gt;"-",SUMIF($AC:$AE,P46,$AJ:$AJ)-O46*SUMIF($AC:$AE,P46,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="9"/>
         <v>0.91136892218148913</v>
       </c>
       <c r="R46" s="4">
-        <f ca="1">Q46*R$39</f>
+        <f t="shared" ca="1" si="10"/>
         <v>0.74805450116805416</v>
       </c>
       <c r="S46" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>15.707963267948964</v>
       </c>
       <c r="T46" s="4" t="str">
@@ -4293,15 +4293,15 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="U46" s="32">
-        <f ca="1">IF(S46&lt;&gt;"-",SUMIF($AC:$AE,T46,$AJ:$AJ)-S46*SUMIF($AC:$AE,T46,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="12"/>
         <v>0.93591261478765941</v>
       </c>
       <c r="V46" s="4">
-        <f ca="1">U46*V$39</f>
+        <f t="shared" ca="1" si="13"/>
         <v>0.75762848167488572</v>
       </c>
       <c r="W46" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>11.895509683123851</v>
       </c>
       <c r="X46" s="4" t="str">
@@ -4309,11 +4309,11 @@
         <v>Цилиндрическая 1</v>
       </c>
       <c r="Y46" s="32">
-        <f ca="1">IF(W46&lt;&gt;"-",SUMIF($AC:$AE,X46,$AJ:$AJ)-W46*SUMIF($AC:$AE,X46,$AK:$AK),0)</f>
+        <f t="shared" ca="1" si="15"/>
         <v>0.94782653224023794</v>
       </c>
       <c r="Z46" s="5">
-        <f ca="1">Y46*Z$39</f>
+        <f t="shared" ca="1" si="16"/>
         <v>0.75835111197354876</v>
       </c>
     </row>
@@ -4345,25 +4345,25 @@
       <c r="Z47" s="1"/>
     </row>
     <row r="48" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B48" s="107" t="s">
+      <c r="B48" s="97" t="s">
         <v>108</v>
       </c>
-      <c r="C48" s="100"/>
-      <c r="D48" s="100"/>
-      <c r="E48" s="100"/>
-      <c r="F48" s="100" t="str">
+      <c r="C48" s="98"/>
+      <c r="D48" s="98"/>
+      <c r="E48" s="98"/>
+      <c r="F48" s="98" t="str">
         <f>P46</f>
         <v>Цилиндрическая 1</v>
       </c>
-      <c r="G48" s="115"/>
+      <c r="G48" s="99"/>
       <c r="H48" s="16"/>
       <c r="I48" s="16"/>
       <c r="J48" s="16"/>
       <c r="K48" s="36"/>
-      <c r="L48" s="93" t="s">
+      <c r="L48" s="94" t="s">
         <v>56</v>
       </c>
-      <c r="M48" s="93"/>
+      <c r="M48" s="94"/>
       <c r="N48" s="28">
         <f ca="1">MAX(Z41:Z46,V41:V46,R41:R46,N41:N46)</f>
         <v>0.78915140422920127</v>
@@ -4381,12 +4381,12 @@
       <c r="Z48" s="1"/>
     </row>
     <row r="49" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B49" s="99" t="s">
+      <c r="B49" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="93"/>
-      <c r="D49" s="93"/>
-      <c r="E49" s="93"/>
+      <c r="C49" s="94"/>
+      <c r="D49" s="94"/>
+      <c r="E49" s="94"/>
       <c r="F49" s="46">
         <f>O41</f>
         <v>7.5398223686155026</v>
@@ -4411,12 +4411,12 @@
       <c r="Z49" s="1"/>
     </row>
     <row r="50" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B50" s="99" t="s">
+      <c r="B50" s="93" t="s">
         <v>96</v>
       </c>
-      <c r="C50" s="93"/>
-      <c r="D50" s="93"/>
-      <c r="E50" s="93"/>
+      <c r="C50" s="94"/>
+      <c r="D50" s="94"/>
+      <c r="E50" s="94"/>
       <c r="F50" s="16">
         <f>P36</f>
         <v>1440</v>
@@ -4433,12 +4433,12 @@
       <c r="Z50" s="1"/>
     </row>
     <row r="51" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B51" s="99" t="s">
+      <c r="B51" s="93" t="s">
         <v>103</v>
       </c>
-      <c r="C51" s="93"/>
-      <c r="D51" s="93"/>
-      <c r="E51" s="93"/>
+      <c r="C51" s="94"/>
+      <c r="D51" s="94"/>
+      <c r="E51" s="94"/>
       <c r="F51" s="1">
         <f>F50*PI()/30</f>
         <v>150.79644737231007</v>
@@ -4447,29 +4447,29 @@
         <v>330</v>
       </c>
       <c r="H51" s="16"/>
-      <c r="I51" s="116" t="s">
+      <c r="I51" s="109" t="s">
         <v>112</v>
       </c>
-      <c r="J51" s="118"/>
+      <c r="J51" s="111"/>
       <c r="K51" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="L51" s="100" t="s">
+      <c r="L51" s="98" t="s">
         <v>120</v>
       </c>
-      <c r="M51" s="100"/>
-      <c r="N51" s="97" t="s">
+      <c r="M51" s="98"/>
+      <c r="N51" s="126" t="s">
         <v>113</v>
       </c>
-      <c r="O51" s="97"/>
-      <c r="P51" s="100" t="s">
+      <c r="O51" s="126"/>
+      <c r="P51" s="98" t="s">
         <v>114</v>
       </c>
-      <c r="Q51" s="100"/>
-      <c r="R51" s="97" t="s">
+      <c r="Q51" s="98"/>
+      <c r="R51" s="126" t="s">
         <v>116</v>
       </c>
-      <c r="S51" s="97"/>
+      <c r="S51" s="126"/>
       <c r="T51" s="49"/>
       <c r="U51" s="49"/>
       <c r="V51" s="49"/>
@@ -4478,12 +4478,12 @@
       <c r="Z51" s="1"/>
     </row>
     <row r="52" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B52" s="99" t="s">
+      <c r="B52" s="93" t="s">
         <v>42</v>
       </c>
-      <c r="C52" s="93"/>
-      <c r="D52" s="93"/>
-      <c r="E52" s="93"/>
+      <c r="C52" s="94"/>
+      <c r="D52" s="94"/>
+      <c r="E52" s="94"/>
       <c r="F52" s="45">
         <f>I41</f>
         <v>190.98593171027443</v>
@@ -4492,33 +4492,33 @@
         <v>329</v>
       </c>
       <c r="H52" s="16"/>
-      <c r="I52" s="99" t="s">
+      <c r="I52" s="93" t="s">
         <v>115</v>
       </c>
-      <c r="J52" s="93"/>
+      <c r="J52" s="94"/>
       <c r="K52" s="42">
         <f>R36</f>
         <v>0.872</v>
       </c>
-      <c r="L52" s="100">
+      <c r="L52" s="98">
         <v>1</v>
       </c>
-      <c r="M52" s="100"/>
-      <c r="N52" s="95">
+      <c r="M52" s="98"/>
+      <c r="N52" s="129">
         <f>F50</f>
         <v>1440</v>
       </c>
-      <c r="O52" s="95"/>
-      <c r="P52" s="101">
+      <c r="O52" s="129"/>
+      <c r="P52" s="128">
         <f>F55</f>
         <v>49.735919716217296</v>
       </c>
-      <c r="Q52" s="101"/>
-      <c r="R52" s="97">
-        <f t="shared" ref="R52:R57" si="9">P52*N52*PI()/1000/30</f>
+      <c r="Q52" s="128"/>
+      <c r="R52" s="126">
+        <f t="shared" ref="R52:R54" si="17">P52*N52*PI()/1000/30</f>
         <v>7.5000000000000009</v>
       </c>
-      <c r="S52" s="97"/>
+      <c r="S52" s="126"/>
       <c r="T52" s="16"/>
       <c r="U52" s="30"/>
       <c r="X52" s="1"/>
@@ -4526,12 +4526,12 @@
       <c r="Z52" s="1"/>
     </row>
     <row r="53" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B53" s="99" t="s">
+      <c r="B53" s="93" t="s">
         <v>105</v>
       </c>
-      <c r="C53" s="93"/>
-      <c r="D53" s="93"/>
-      <c r="E53" s="93"/>
+      <c r="C53" s="94"/>
+      <c r="D53" s="94"/>
+      <c r="E53" s="94"/>
       <c r="F53" s="16">
         <f>G41</f>
         <v>160</v>
@@ -4540,33 +4540,33 @@
         <v>16</v>
       </c>
       <c r="H53" s="16"/>
-      <c r="I53" s="99" t="s">
+      <c r="I53" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="J53" s="93"/>
+      <c r="J53" s="94"/>
       <c r="K53" s="7">
         <f>M7</f>
         <v>0.98</v>
       </c>
-      <c r="L53" s="93">
+      <c r="L53" s="94">
         <v>1</v>
       </c>
-      <c r="M53" s="93"/>
-      <c r="N53" s="96">
+      <c r="M53" s="94"/>
+      <c r="N53" s="130">
         <f>N52/L53</f>
         <v>1440</v>
       </c>
-      <c r="O53" s="96"/>
-      <c r="P53" s="94">
+      <c r="O53" s="130"/>
+      <c r="P53" s="106">
         <f>P52*L53*K53</f>
         <v>48.741201321892952</v>
       </c>
-      <c r="Q53" s="94"/>
-      <c r="R53" s="98">
-        <f t="shared" si="9"/>
+      <c r="Q53" s="106"/>
+      <c r="R53" s="127">
+        <f t="shared" si="17"/>
         <v>7.3500000000000005</v>
       </c>
-      <c r="S53" s="98"/>
+      <c r="S53" s="127"/>
       <c r="T53" s="1"/>
       <c r="U53" s="67"/>
       <c r="V53" s="68"/>
@@ -4575,12 +4575,12 @@
       <c r="Z53" s="1"/>
     </row>
     <row r="54" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B54" s="99" t="s">
+      <c r="B54" s="93" t="s">
         <v>97</v>
       </c>
-      <c r="C54" s="93"/>
-      <c r="D54" s="93"/>
-      <c r="E54" s="93"/>
+      <c r="C54" s="94"/>
+      <c r="D54" s="94"/>
+      <c r="E54" s="94"/>
       <c r="F54" s="44">
         <f ca="1">F55*F49*PRODUCT(K53:K57)</f>
         <v>339.37130342425513</v>
@@ -4589,33 +4589,33 @@
         <v>99</v>
       </c>
       <c r="H54" s="16"/>
-      <c r="I54" s="99" t="s">
+      <c r="I54" s="93" t="s">
         <v>95</v>
       </c>
-      <c r="J54" s="93"/>
+      <c r="J54" s="94"/>
       <c r="K54" s="7">
         <f>M6</f>
         <v>0.99</v>
       </c>
-      <c r="L54" s="93">
+      <c r="L54" s="94">
         <v>1</v>
       </c>
-      <c r="M54" s="93"/>
-      <c r="N54" s="96">
+      <c r="M54" s="94"/>
+      <c r="N54" s="130">
         <f>N53/L54</f>
         <v>1440</v>
       </c>
-      <c r="O54" s="96"/>
-      <c r="P54" s="94">
+      <c r="O54" s="130"/>
+      <c r="P54" s="106">
         <f>P53*L54*K54</f>
         <v>48.253789308674023</v>
       </c>
-      <c r="Q54" s="94"/>
-      <c r="R54" s="98">
-        <f t="shared" si="9"/>
+      <c r="Q54" s="106"/>
+      <c r="R54" s="127">
+        <f t="shared" si="17"/>
         <v>7.2765000000000004</v>
       </c>
-      <c r="S54" s="98"/>
+      <c r="S54" s="127"/>
       <c r="T54" s="1"/>
       <c r="U54" s="67"/>
       <c r="V54" s="68"/>
@@ -4625,12 +4625,12 @@
       <c r="Z54" s="1"/>
     </row>
     <row r="55" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B55" s="99" t="s">
+      <c r="B55" s="93" t="s">
         <v>98</v>
       </c>
-      <c r="C55" s="93"/>
-      <c r="D55" s="93"/>
-      <c r="E55" s="93"/>
+      <c r="C55" s="94"/>
+      <c r="D55" s="94"/>
+      <c r="E55" s="94"/>
       <c r="F55" s="1">
         <f>F56/F51*1000</f>
         <v>49.735919716217296</v>
@@ -4639,34 +4639,34 @@
         <v>99</v>
       </c>
       <c r="H55" s="16"/>
-      <c r="I55" s="99" t="s">
+      <c r="I55" s="93" t="s">
         <v>94</v>
       </c>
-      <c r="J55" s="93"/>
+      <c r="J55" s="94"/>
       <c r="K55" s="43">
         <f ca="1">Q41</f>
         <v>0.96143805509807656</v>
       </c>
-      <c r="L55" s="94">
+      <c r="L55" s="106">
         <f>F49</f>
         <v>7.5398223686155026</v>
       </c>
-      <c r="M55" s="94"/>
-      <c r="N55" s="94">
+      <c r="M55" s="106"/>
+      <c r="N55" s="106">
         <f>N54/L55</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O55" s="94"/>
-      <c r="P55" s="102">
+      <c r="O55" s="106"/>
+      <c r="P55" s="122">
         <f ca="1">P54*L55*K55</f>
         <v>349.79520039605768</v>
       </c>
-      <c r="Q55" s="102"/>
-      <c r="R55" s="98">
+      <c r="Q55" s="122"/>
+      <c r="R55" s="127">
         <f ca="1">P55*N55*PI()/1000/30</f>
         <v>6.9959040079211547</v>
       </c>
-      <c r="S55" s="98"/>
+      <c r="S55" s="127"/>
       <c r="T55" s="1"/>
       <c r="U55" s="67"/>
       <c r="V55" s="68"/>
@@ -4676,12 +4676,12 @@
       <c r="Z55" s="1"/>
     </row>
     <row r="56" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B56" s="99" t="s">
+      <c r="B56" s="93" t="s">
         <v>298</v>
       </c>
-      <c r="C56" s="93"/>
-      <c r="D56" s="93"/>
-      <c r="E56" s="93"/>
+      <c r="C56" s="94"/>
+      <c r="D56" s="94"/>
+      <c r="E56" s="94"/>
       <c r="F56" s="1">
         <f>I36</f>
         <v>7.5</v>
@@ -4689,109 +4689,109 @@
       <c r="G56" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="I56" s="99" t="s">
+      <c r="I56" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="J56" s="93"/>
+      <c r="J56" s="94"/>
       <c r="K56" s="7">
         <f>M7</f>
         <v>0.98</v>
       </c>
-      <c r="L56" s="93">
+      <c r="L56" s="94">
         <v>1</v>
       </c>
-      <c r="M56" s="93"/>
-      <c r="N56" s="94">
+      <c r="M56" s="94"/>
+      <c r="N56" s="106">
         <f>N55/L56</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O56" s="94"/>
-      <c r="P56" s="102">
+      <c r="O56" s="106"/>
+      <c r="P56" s="122">
         <f ca="1">P55*L56*K56</f>
         <v>342.7992963881365</v>
       </c>
-      <c r="Q56" s="102"/>
-      <c r="R56" s="98">
+      <c r="Q56" s="122"/>
+      <c r="R56" s="127">
         <f ca="1">P56*N56*PI()/1000/30</f>
         <v>6.8559859277627302</v>
       </c>
-      <c r="S56" s="98"/>
+      <c r="S56" s="127"/>
       <c r="T56" s="1"/>
       <c r="U56" s="67"/>
       <c r="V56" s="68"/>
     </row>
     <row r="57" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B57" s="99" t="s">
+      <c r="B57" s="93" t="s">
         <v>101</v>
       </c>
-      <c r="C57" s="93"/>
-      <c r="D57" s="93"/>
-      <c r="E57" s="93"/>
+      <c r="C57" s="94"/>
+      <c r="D57" s="94"/>
+      <c r="E57" s="94"/>
       <c r="F57" s="1">
         <f>Q36</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="G57" s="50"/>
-      <c r="I57" s="99" t="s">
+      <c r="I57" s="93" t="s">
         <v>95</v>
       </c>
-      <c r="J57" s="93"/>
+      <c r="J57" s="94"/>
       <c r="K57" s="7">
         <f>M6</f>
         <v>0.99</v>
       </c>
-      <c r="L57" s="93">
+      <c r="L57" s="94">
         <v>1</v>
       </c>
-      <c r="M57" s="93"/>
-      <c r="N57" s="94">
+      <c r="M57" s="94"/>
+      <c r="N57" s="106">
         <f>N56/L57</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O57" s="94"/>
-      <c r="P57" s="102">
+      <c r="O57" s="106"/>
+      <c r="P57" s="122">
         <f ca="1">P56*L57*K57</f>
         <v>339.37130342425513</v>
       </c>
-      <c r="Q57" s="102"/>
-      <c r="R57" s="98">
+      <c r="Q57" s="122"/>
+      <c r="R57" s="127">
         <f ca="1">P57*N57*PI()/1000/30</f>
         <v>6.7874260684851038</v>
       </c>
-      <c r="S57" s="98"/>
+      <c r="S57" s="127"/>
       <c r="T57" s="1"/>
       <c r="U57" s="67"/>
       <c r="V57" s="68"/>
     </row>
     <row r="58" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B58" s="99" t="s">
+      <c r="B58" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="C58" s="93"/>
-      <c r="D58" s="93"/>
-      <c r="E58" s="93"/>
+      <c r="C58" s="94"/>
+      <c r="D58" s="94"/>
+      <c r="E58" s="94"/>
       <c r="F58" s="44">
         <f>MAX(F57,E8)</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="G58" s="50"/>
-      <c r="I58" s="103" t="s">
+      <c r="I58" s="100" t="s">
         <v>136</v>
       </c>
-      <c r="J58" s="104"/>
+      <c r="J58" s="101"/>
       <c r="K58" s="12"/>
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
-      <c r="N58" s="105">
+      <c r="N58" s="95">
         <f>N57</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O58" s="105"/>
-      <c r="P58" s="106">
+      <c r="O58" s="95"/>
+      <c r="P58" s="124">
         <f ca="1">P57</f>
         <v>339.37130342425513</v>
       </c>
-      <c r="Q58" s="106"/>
+      <c r="Q58" s="124"/>
       <c r="R58" s="4"/>
       <c r="S58" s="4"/>
       <c r="T58" s="16"/>
@@ -4799,12 +4799,12 @@
       <c r="V58" s="16"/>
     </row>
     <row r="59" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B59" s="99" t="s">
+      <c r="B59" s="93" t="s">
         <v>107</v>
       </c>
-      <c r="C59" s="93"/>
-      <c r="D59" s="93"/>
-      <c r="E59" s="93"/>
+      <c r="C59" s="94"/>
+      <c r="D59" s="94"/>
+      <c r="E59" s="94"/>
       <c r="F59" s="1">
         <f ca="1">K57*K55*K56*K54*K53</f>
         <v>0.90499014246468046</v>
@@ -4812,12 +4812,12 @@
       <c r="G59" s="50"/>
     </row>
     <row r="60" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B60" s="99" t="s">
+      <c r="B60" s="93" t="s">
         <v>109</v>
       </c>
-      <c r="C60" s="93"/>
-      <c r="D60" s="93"/>
-      <c r="E60" s="93"/>
+      <c r="C60" s="94"/>
+      <c r="D60" s="94"/>
+      <c r="E60" s="94"/>
       <c r="F60" s="1">
         <f ca="1">F59*K52</f>
         <v>0.78915140422920138</v>
@@ -4825,12 +4825,12 @@
       <c r="G60" s="50"/>
     </row>
     <row r="61" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B61" s="93" t="s">
+      <c r="B61" s="94" t="s">
         <v>135</v>
       </c>
-      <c r="C61" s="93"/>
-      <c r="D61" s="93"/>
-      <c r="E61" s="93"/>
+      <c r="C61" s="94"/>
+      <c r="D61" s="94"/>
+      <c r="E61" s="94"/>
       <c r="F61" s="69">
         <v>38</v>
       </c>
@@ -4857,57 +4857,82 @@
     </row>
   </sheetData>
   <mergeCells count="151">
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="S19:V19"/>
-    <mergeCell ref="W19:Z19"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="AC8:AE8"/>
-    <mergeCell ref="AC6:AE6"/>
-    <mergeCell ref="K19:N19"/>
-    <mergeCell ref="AC2:AE2"/>
-    <mergeCell ref="AC3:AE3"/>
-    <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="AC5:AE5"/>
-    <mergeCell ref="AC7:AE7"/>
-    <mergeCell ref="AC10:AE10"/>
-    <mergeCell ref="AC9:AE9"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="I4:N4"/>
-    <mergeCell ref="I3:N3"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="L54:M54"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="N56:O56"/>
+    <mergeCell ref="N57:O57"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="R53:S53"/>
+    <mergeCell ref="R54:S54"/>
+    <mergeCell ref="R55:S55"/>
+    <mergeCell ref="R56:S56"/>
+    <mergeCell ref="R57:S57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="I55:J55"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="P56:Q56"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="Q6:S6"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="G38:J38"/>
     <mergeCell ref="B55:E55"/>
     <mergeCell ref="B54:E54"/>
     <mergeCell ref="B53:E53"/>
@@ -4932,82 +4957,57 @@
     <mergeCell ref="B48:E48"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="I20:J20"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="Q6:S6"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="G39:J39"/>
-    <mergeCell ref="G38:J38"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="I58:J58"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="R53:S53"/>
-    <mergeCell ref="R54:S54"/>
-    <mergeCell ref="R55:S55"/>
-    <mergeCell ref="R56:S56"/>
-    <mergeCell ref="R57:S57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="I55:J55"/>
-    <mergeCell ref="I54:J54"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="P55:Q55"/>
-    <mergeCell ref="P56:Q56"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="L54:M54"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="L57:M57"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="N56:O56"/>
-    <mergeCell ref="N57:O57"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="AC8:AE8"/>
+    <mergeCell ref="AC6:AE6"/>
+    <mergeCell ref="K19:N19"/>
+    <mergeCell ref="AC2:AE2"/>
+    <mergeCell ref="AC3:AE3"/>
+    <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="AC5:AE5"/>
+    <mergeCell ref="AC7:AE7"/>
+    <mergeCell ref="AC10:AE10"/>
+    <mergeCell ref="AC9:AE9"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="S19:V19"/>
+    <mergeCell ref="W19:Z19"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -5023,33 +5023,33 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="126" t="s">
+      <c r="A2" s="118" t="s">
         <v>173</v>
       </c>
-      <c r="B2" s="126"/>
-      <c r="C2" s="126"/>
-      <c r="D2" s="126"/>
-      <c r="E2" s="126"/>
-      <c r="H2" s="126" t="s">
+      <c r="B2" s="118"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="H2" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="I2" s="126"/>
-      <c r="J2" s="126"/>
-      <c r="K2" s="126"/>
-      <c r="L2" s="126"/>
-      <c r="P2" s="126" t="s">
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="P2" s="118" t="s">
         <v>185</v>
       </c>
-      <c r="Q2" s="126"/>
-      <c r="R2" s="126"/>
-      <c r="S2" s="126"/>
-      <c r="T2" s="126"/>
+      <c r="Q2" s="118"/>
+      <c r="R2" s="118"/>
+      <c r="S2" s="118"/>
+      <c r="T2" s="118"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="126" t="s">
+      <c r="A3" s="118" t="s">
         <v>172</v>
       </c>
-      <c r="B3" s="126"/>
+      <c r="B3" s="118"/>
       <c r="D3" s="61">
         <f>Электродвигатель!$P$53</f>
         <v>48.741201321892952</v>
@@ -5057,11 +5057,11 @@
       <c r="E3" t="s">
         <v>99</v>
       </c>
-      <c r="H3" s="93" t="s">
+      <c r="H3" s="94" t="s">
         <v>172</v>
       </c>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
+      <c r="I3" s="94"/>
+      <c r="J3" s="94"/>
       <c r="K3" s="63">
         <f>D3</f>
         <v>48.741201321892952</v>
@@ -5082,10 +5082,10 @@
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="126" t="s">
+      <c r="A4" s="118" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="126"/>
+      <c r="B4" s="118"/>
       <c r="D4" s="62">
         <f>Электродвигатель!$N$52</f>
         <v>1440</v>
@@ -5093,11 +5093,11 @@
       <c r="E4" t="s">
         <v>104</v>
       </c>
-      <c r="H4" s="93" t="s">
+      <c r="H4" s="94" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="93"/>
-      <c r="J4" s="93"/>
+      <c r="I4" s="94"/>
+      <c r="J4" s="94"/>
       <c r="K4" s="64">
         <f>D4</f>
         <v>1440</v>
@@ -5119,27 +5119,27 @@
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H5" s="126" t="s">
+      <c r="H5" s="118" t="s">
         <v>176</v>
       </c>
-      <c r="I5" s="126"/>
-      <c r="J5" s="126"/>
-      <c r="K5" s="126"/>
-      <c r="L5" s="126"/>
-      <c r="P5" s="126" t="s">
+      <c r="I5" s="118"/>
+      <c r="J5" s="118"/>
+      <c r="K5" s="118"/>
+      <c r="L5" s="118"/>
+      <c r="P5" s="118" t="s">
         <v>124</v>
       </c>
-      <c r="Q5" s="126"/>
-      <c r="R5" s="126"/>
-      <c r="S5" s="126"/>
-      <c r="T5" s="126"/>
+      <c r="Q5" s="118"/>
+      <c r="R5" s="118"/>
+      <c r="S5" s="118"/>
+      <c r="T5" s="118"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="126" t="s">
+      <c r="A6" s="118" t="s">
         <v>118</v>
       </c>
-      <c r="B6" s="126"/>
-      <c r="C6" s="126"/>
+      <c r="B6" s="118"/>
+      <c r="C6" s="118"/>
       <c r="D6" s="66">
         <f>Электродвигатель!$F$61</f>
         <v>38</v>
@@ -5147,11 +5147,11 @@
       <c r="E6" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="126" t="s">
+      <c r="H6" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="I6" s="126"/>
-      <c r="J6" s="126"/>
+      <c r="I6" s="118"/>
+      <c r="J6" s="118"/>
       <c r="K6">
         <f>Передача!D55</f>
         <v>37.75</v>
@@ -5159,11 +5159,11 @@
       <c r="L6" t="s">
         <v>16</v>
       </c>
-      <c r="P6" s="126" t="s">
+      <c r="P6" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="Q6" s="126"/>
-      <c r="R6" s="126"/>
+      <c r="Q6" s="118"/>
+      <c r="R6" s="118"/>
       <c r="S6">
         <f>Передача!D60</f>
         <v>309.75</v>
@@ -5173,19 +5173,19 @@
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="145" t="s">
+      <c r="A7" s="131" t="s">
         <v>198</v>
       </c>
-      <c r="B7" s="145"/>
-      <c r="C7" s="145"/>
+      <c r="B7" s="131"/>
+      <c r="C7" s="131"/>
       <c r="D7" s="52">
         <v>0.8</v>
       </c>
-      <c r="H7" s="126" t="s">
+      <c r="H7" s="118" t="s">
         <v>184</v>
       </c>
-      <c r="I7" s="126"/>
-      <c r="J7" s="126"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="118"/>
       <c r="K7">
         <f>Передача!D54</f>
         <v>49</v>
@@ -5193,11 +5193,11 @@
       <c r="L7" t="s">
         <v>16</v>
       </c>
-      <c r="P7" s="126" t="s">
+      <c r="P7" s="118" t="s">
         <v>184</v>
       </c>
-      <c r="Q7" s="126"/>
-      <c r="R7" s="126"/>
+      <c r="Q7" s="118"/>
+      <c r="R7" s="118"/>
       <c r="S7">
         <f>Передача!D59</f>
         <v>321</v>
@@ -5207,19 +5207,19 @@
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="126" t="s">
+      <c r="A8" s="118" t="s">
         <v>194</v>
       </c>
-      <c r="B8" s="126"/>
-      <c r="C8" s="126"/>
+      <c r="B8" s="118"/>
+      <c r="C8" s="118"/>
       <c r="D8" s="71">
         <v>1.2</v>
       </c>
-      <c r="H8" s="126" t="s">
+      <c r="H8" s="118" t="s">
         <v>165</v>
       </c>
-      <c r="I8" s="126"/>
-      <c r="J8" s="126"/>
+      <c r="I8" s="118"/>
+      <c r="J8" s="118"/>
       <c r="K8">
         <f>Передача!D56</f>
         <v>62</v>
@@ -5227,11 +5227,11 @@
       <c r="L8" t="s">
         <v>16</v>
       </c>
-      <c r="P8" s="126" t="s">
+      <c r="P8" s="118" t="s">
         <v>165</v>
       </c>
-      <c r="Q8" s="126"/>
-      <c r="R8" s="126"/>
+      <c r="Q8" s="118"/>
+      <c r="R8" s="118"/>
       <c r="S8">
         <f>Передача!D61</f>
         <v>57</v>
@@ -5241,38 +5241,38 @@
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H9" s="126" t="s">
+      <c r="H9" s="118" t="s">
         <v>187</v>
       </c>
-      <c r="I9" s="126"/>
-      <c r="J9" s="126"/>
-      <c r="K9" s="126"/>
-      <c r="L9" s="126"/>
-      <c r="P9" s="126" t="s">
+      <c r="I9" s="118"/>
+      <c r="J9" s="118"/>
+      <c r="K9" s="118"/>
+      <c r="L9" s="118"/>
+      <c r="P9" s="118" t="s">
         <v>187</v>
       </c>
-      <c r="Q9" s="126"/>
-      <c r="R9" s="126"/>
-      <c r="S9" s="126"/>
-      <c r="T9" s="126"/>
+      <c r="Q9" s="118"/>
+      <c r="R9" s="118"/>
+      <c r="S9" s="118"/>
+      <c r="T9" s="118"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H10" s="126" t="s">
+      <c r="H10" s="118" t="s">
         <v>183</v>
       </c>
-      <c r="I10" s="126"/>
-      <c r="J10" s="126"/>
+      <c r="I10" s="118"/>
+      <c r="J10" s="118"/>
       <c r="K10">
         <v>7.5</v>
       </c>
       <c r="L10" s="65" t="s">
         <v>190</v>
       </c>
-      <c r="P10" s="126" t="s">
+      <c r="P10" s="118" t="s">
         <v>183</v>
       </c>
-      <c r="Q10" s="126"/>
-      <c r="R10" s="126"/>
+      <c r="Q10" s="118"/>
+      <c r="R10" s="118"/>
       <c r="S10">
         <v>5.4</v>
       </c>
@@ -5281,11 +5281,11 @@
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H11" s="126" t="s">
+      <c r="H11" s="118" t="s">
         <v>195</v>
       </c>
-      <c r="I11" s="126"/>
-      <c r="J11" s="126"/>
+      <c r="I11" s="118"/>
+      <c r="J11" s="118"/>
       <c r="K11">
         <f>K10*(K3)^(1/3)</f>
         <v>27.396389985469561</v>
@@ -5293,11 +5293,11 @@
       <c r="L11" t="s">
         <v>16</v>
       </c>
-      <c r="P11" s="126" t="s">
+      <c r="P11" s="118" t="s">
         <v>195</v>
       </c>
-      <c r="Q11" s="126"/>
-      <c r="R11" s="126"/>
+      <c r="Q11" s="118"/>
+      <c r="R11" s="118"/>
       <c r="S11">
         <f ca="1">S10*(S3)^(1/3)</f>
         <v>38.047989101548296</v>
@@ -5307,11 +5307,11 @@
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H12" s="126" t="s">
+      <c r="H12" s="118" t="s">
         <v>199</v>
       </c>
-      <c r="I12" s="126"/>
-      <c r="J12" s="126"/>
+      <c r="I12" s="118"/>
+      <c r="J12" s="118"/>
       <c r="K12">
         <f>MIN(MAX(K11,D6/D8),D6/D7)</f>
         <v>31.666666666666668</v>
@@ -5319,11 +5319,11 @@
       <c r="L12" t="s">
         <v>16</v>
       </c>
-      <c r="P12" s="126" t="s">
+      <c r="P12" s="118" t="s">
         <v>188</v>
       </c>
-      <c r="Q12" s="126"/>
-      <c r="R12" s="126"/>
+      <c r="Q12" s="118"/>
+      <c r="R12" s="118"/>
       <c r="S12" s="66">
         <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;S11)</f>
         <v>40</v>
@@ -5336,11 +5336,11 @@
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H13" s="126" t="s">
+      <c r="H13" s="118" t="s">
         <v>188</v>
       </c>
-      <c r="I13" s="126"/>
-      <c r="J13" s="126"/>
+      <c r="I13" s="118"/>
+      <c r="J13" s="118"/>
       <c r="K13" s="66">
         <f>_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;K12)</f>
         <v>32</v>
@@ -5351,11 +5351,11 @@
       <c r="M13" t="s">
         <v>197</v>
       </c>
-      <c r="P13" s="126" t="s">
+      <c r="P13" s="118" t="s">
         <v>196</v>
       </c>
-      <c r="Q13" s="126"/>
-      <c r="R13" s="126"/>
+      <c r="Q13" s="118"/>
+      <c r="R13" s="118"/>
       <c r="S13">
         <f ca="1">_xlfn.MINIFS($28:$28,$26:$26,"&gt;="&amp;S12)</f>
         <v>3.5</v>
@@ -5365,20 +5365,20 @@
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="126" t="s">
+      <c r="A14" s="118" t="s">
         <v>283</v>
       </c>
-      <c r="B14" s="126"/>
-      <c r="C14" s="126"/>
+      <c r="B14" s="118"/>
+      <c r="C14" s="118"/>
       <c r="D14">
         <f>Электродвигатель!$F$58</f>
         <v>2.2000000000000002</v>
       </c>
-      <c r="H14" s="126" t="s">
+      <c r="H14" s="118" t="s">
         <v>196</v>
       </c>
-      <c r="I14" s="126"/>
-      <c r="J14" s="126"/>
+      <c r="I14" s="118"/>
+      <c r="J14" s="118"/>
       <c r="K14">
         <f>_xlfn.MINIFS($28:$28,$26:$26,"&gt;="&amp;K13)</f>
         <v>3.5</v>
@@ -5386,11 +5386,11 @@
       <c r="L14" t="s">
         <v>16</v>
       </c>
-      <c r="P14" s="126" t="s">
+      <c r="P14" s="118" t="s">
         <v>192</v>
       </c>
-      <c r="Q14" s="126"/>
-      <c r="R14" s="126"/>
+      <c r="Q14" s="118"/>
+      <c r="R14" s="118"/>
       <c r="S14">
         <f ca="1">S12+2*S13</f>
         <v>47</v>
@@ -5400,11 +5400,11 @@
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H15" s="126" t="s">
+      <c r="H15" s="118" t="s">
         <v>192</v>
       </c>
-      <c r="I15" s="126"/>
-      <c r="J15" s="126"/>
+      <c r="I15" s="118"/>
+      <c r="J15" s="118"/>
       <c r="K15">
         <f>K13+2*K14</f>
         <v>39</v>
@@ -5412,11 +5412,11 @@
       <c r="L15" t="s">
         <v>16</v>
       </c>
-      <c r="P15" s="126" t="s">
+      <c r="P15" s="118" t="s">
         <v>262</v>
       </c>
-      <c r="Q15" s="126"/>
-      <c r="R15" s="126"/>
+      <c r="Q15" s="118"/>
+      <c r="R15" s="118"/>
       <c r="S15" s="66">
         <f ca="1">_xlfn.MINIFS(Подшипники!$A:$A,Подшипники!$A:$A,"&gt;="&amp;S14)</f>
         <v>50</v>
@@ -5426,11 +5426,11 @@
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H16" s="126" t="s">
+      <c r="H16" s="118" t="s">
         <v>262</v>
       </c>
-      <c r="I16" s="126"/>
-      <c r="J16" s="126"/>
+      <c r="I16" s="118"/>
+      <c r="J16" s="118"/>
       <c r="K16" s="66">
         <f>_xlfn.MINIFS(Подшипники!$A:$A,Подшипники!$A:$A,"&gt;="&amp;K15)</f>
         <v>40</v>
@@ -5438,11 +5438,11 @@
       <c r="L16" t="s">
         <v>16</v>
       </c>
-      <c r="P16" s="126" t="s">
+      <c r="P16" s="118" t="s">
         <v>196</v>
       </c>
-      <c r="Q16" s="126"/>
-      <c r="R16" s="126"/>
+      <c r="Q16" s="118"/>
+      <c r="R16" s="118"/>
       <c r="S16">
         <f ca="1">_xlfn.MINIFS($29:$29,$26:$26,"&gt;="&amp;S12)</f>
         <v>2.2999999999999998</v>
@@ -5452,11 +5452,11 @@
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H17" s="126" t="s">
+      <c r="H17" s="118" t="s">
         <v>196</v>
       </c>
-      <c r="I17" s="126"/>
-      <c r="J17" s="126"/>
+      <c r="I17" s="118"/>
+      <c r="J17" s="118"/>
       <c r="K17">
         <f>_xlfn.MINIFS($29:$29,$26:$26,"&gt;="&amp;K13)</f>
         <v>2</v>
@@ -5464,11 +5464,11 @@
       <c r="L17" t="s">
         <v>16</v>
       </c>
-      <c r="P17" s="126" t="s">
+      <c r="P17" s="118" t="s">
         <v>193</v>
       </c>
-      <c r="Q17" s="126"/>
-      <c r="R17" s="126"/>
+      <c r="Q17" s="118"/>
+      <c r="R17" s="118"/>
       <c r="S17">
         <f ca="1">S15+2*S16</f>
         <v>54.6</v>
@@ -5478,11 +5478,11 @@
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H18" s="126" t="s">
+      <c r="H18" s="118" t="s">
         <v>193</v>
       </c>
-      <c r="I18" s="126"/>
-      <c r="J18" s="126"/>
+      <c r="I18" s="118"/>
+      <c r="J18" s="118"/>
       <c r="K18">
         <f>K16+2*K17</f>
         <v>44</v>
@@ -5490,11 +5490,11 @@
       <c r="L18" t="s">
         <v>16</v>
       </c>
-      <c r="P18" s="126" t="s">
+      <c r="P18" s="118" t="s">
         <v>265</v>
       </c>
-      <c r="Q18" s="126"/>
-      <c r="R18" s="126"/>
+      <c r="Q18" s="118"/>
+      <c r="R18" s="118"/>
       <c r="S18" s="66">
         <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;S17)</f>
         <v>56</v>
@@ -5507,11 +5507,11 @@
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H19" s="126" t="s">
+      <c r="H19" s="118" t="s">
         <v>189</v>
       </c>
-      <c r="I19" s="126"/>
-      <c r="J19" s="126"/>
+      <c r="I19" s="118"/>
+      <c r="J19" s="118"/>
       <c r="K19" s="66">
         <f>_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;K18)</f>
         <v>45</v>
@@ -5524,10 +5524,10 @@
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A26" s="126" t="s">
+      <c r="A26" s="118" t="s">
         <v>181</v>
       </c>
-      <c r="B26" s="126"/>
+      <c r="B26" s="118"/>
       <c r="C26">
         <v>17</v>
       </c>
@@ -5563,10 +5563,10 @@
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A27" s="126" t="s">
+      <c r="A27" s="118" t="s">
         <v>182</v>
       </c>
-      <c r="B27" s="126"/>
+      <c r="B27" s="118"/>
       <c r="C27">
         <v>22</v>
       </c>
@@ -5599,10 +5599,10 @@
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A28" s="126" t="s">
+      <c r="A28" s="118" t="s">
         <v>179</v>
       </c>
-      <c r="B28" s="126"/>
+      <c r="B28" s="118"/>
       <c r="C28">
         <v>3</v>
       </c>
@@ -5635,10 +5635,10 @@
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A29" s="126" t="s">
+      <c r="A29" s="118" t="s">
         <v>180</v>
       </c>
-      <c r="B29" s="126"/>
+      <c r="B29" s="118"/>
       <c r="C29">
         <v>1.5</v>
       </c>
@@ -5672,6 +5672,35 @@
     </row>
   </sheetData>
   <mergeCells count="44">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="P5:T5"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="P16:R16"/>
+    <mergeCell ref="P17:R17"/>
+    <mergeCell ref="P18:R18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="P11:R11"/>
+    <mergeCell ref="P15:R15"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="H19:J19"/>
     <mergeCell ref="P9:T9"/>
     <mergeCell ref="P6:R6"/>
     <mergeCell ref="P7:R7"/>
@@ -5687,35 +5716,6 @@
     <mergeCell ref="H10:J10"/>
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="H9:L9"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="P16:R16"/>
-    <mergeCell ref="P17:R17"/>
-    <mergeCell ref="P18:R18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="P11:R11"/>
-    <mergeCell ref="P15:R15"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="P2:T2"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="P5:T5"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5731,45 +5731,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="94" t="s">
         <v>137</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A2" s="99" t="s">
+      <c r="A2" s="93" t="s">
         <v>108</v>
       </c>
-      <c r="B2" s="93"/>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93" t="str">
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94" t="str">
         <f>Электродвигатель!F48</f>
         <v>Цилиндрическая 1</v>
       </c>
-      <c r="F2" s="110"/>
-      <c r="K2" s="107" t="s">
+      <c r="F2" s="105"/>
+      <c r="K2" s="97" t="s">
         <v>150</v>
       </c>
-      <c r="L2" s="100"/>
-      <c r="M2" s="100"/>
-      <c r="N2" s="100"/>
-      <c r="O2" s="100"/>
-      <c r="P2" s="100"/>
-      <c r="Q2" s="100"/>
+      <c r="L2" s="98"/>
+      <c r="M2" s="98"/>
+      <c r="N2" s="98"/>
+      <c r="O2" s="98"/>
+      <c r="P2" s="98"/>
+      <c r="Q2" s="98"/>
       <c r="R2" s="1"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A3" s="99" t="s">
+      <c r="A3" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
       <c r="E3" s="56">
         <f>Электродвигатель!$F$49</f>
         <v>7.5398223686155026</v>
@@ -5801,12 +5801,12 @@
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A4" s="99" t="s">
+      <c r="A4" s="93" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="93"/>
-      <c r="C4" s="93"/>
-      <c r="D4" s="93"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
       <c r="E4" s="56">
         <f>Электродвигатель!$F$52</f>
         <v>190.98593171027443</v>
@@ -5841,12 +5841,12 @@
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A5" s="99" t="s">
+      <c r="A5" s="93" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="93"/>
-      <c r="C5" s="93"/>
-      <c r="D5" s="93"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
       <c r="E5" s="25">
         <f ca="1">Электродвигатель!$F$54</f>
         <v>339.37130342425513</v>
@@ -5881,12 +5881,12 @@
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A6" s="99" t="s">
+      <c r="A6" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="B6" s="93"/>
-      <c r="C6" s="93"/>
-      <c r="D6" s="93"/>
+      <c r="B6" s="94"/>
+      <c r="C6" s="94"/>
+      <c r="D6" s="94"/>
       <c r="E6" s="25">
         <f>Электродвигатель!$F$58</f>
         <v>2.2000000000000002</v>
@@ -5919,12 +5919,12 @@
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="118" t="s">
         <v>144</v>
       </c>
-      <c r="B7" s="126"/>
-      <c r="C7" s="126"/>
-      <c r="D7" s="126"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
       <c r="E7">
         <f>Электродвигатель!$E$5</f>
         <v>10000</v>
@@ -5959,14 +5959,14 @@
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A8" s="126" t="s">
+      <c r="A8" s="118" t="s">
         <v>138</v>
       </c>
-      <c r="B8" s="126"/>
-      <c r="C8" s="126"/>
-      <c r="D8" s="126"/>
-      <c r="E8" s="126"/>
-      <c r="F8" s="126"/>
+      <c r="B8" s="118"/>
+      <c r="C8" s="118"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="118"/>
       <c r="K8" s="7">
         <v>5</v>
       </c>
@@ -5995,12 +5995,12 @@
       <c r="S8" s="1"/>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A9" s="126" t="s">
+      <c r="A9" s="118" t="s">
         <v>143</v>
       </c>
-      <c r="B9" s="126"/>
-      <c r="C9" s="126"/>
-      <c r="D9" s="126"/>
+      <c r="B9" s="118"/>
+      <c r="C9" s="118"/>
+      <c r="D9" s="118"/>
       <c r="E9">
         <f>Электродвигатель!$E$15</f>
         <v>300</v>
@@ -6036,12 +6036,12 @@
       <c r="S9" s="54"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A10" s="99" t="s">
+      <c r="A10" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="93"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="93"/>
+      <c r="B10" s="94"/>
+      <c r="C10" s="94"/>
+      <c r="D10" s="94"/>
       <c r="E10" s="16">
         <f>Электродвигатель!$E$7</f>
         <v>3</v>
@@ -6077,12 +6077,12 @@
       <c r="S10" s="54"/>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A11" s="99" t="s">
+      <c r="A11" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="B11" s="93"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
+      <c r="B11" s="94"/>
+      <c r="C11" s="94"/>
+      <c r="D11" s="94"/>
       <c r="E11" s="47" t="s">
         <v>100</v>
       </c>
@@ -6117,12 +6117,12 @@
       <c r="S11" s="54"/>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A12" s="99" t="s">
+      <c r="A12" s="93" t="s">
         <v>128</v>
       </c>
-      <c r="B12" s="93"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="93"/>
+      <c r="B12" s="94"/>
+      <c r="C12" s="94"/>
+      <c r="D12" s="94"/>
       <c r="E12" s="55" t="s">
         <v>100</v>
       </c>
@@ -6157,14 +6157,14 @@
       <c r="S12" s="54"/>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A13" s="126" t="s">
+      <c r="A13" s="118" t="s">
         <v>139</v>
       </c>
-      <c r="B13" s="126"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="126"/>
-      <c r="E13" s="126"/>
-      <c r="F13" s="126"/>
+      <c r="B13" s="118"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="118"/>
+      <c r="F13" s="118"/>
       <c r="K13" s="7">
         <v>10</v>
       </c>
@@ -6193,12 +6193,12 @@
       <c r="S13" s="54"/>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A14" s="126" t="s">
+      <c r="A14" s="118" t="s">
         <v>142</v>
       </c>
-      <c r="B14" s="126"/>
-      <c r="C14" s="126"/>
-      <c r="D14" s="126"/>
+      <c r="B14" s="118"/>
+      <c r="C14" s="118"/>
+      <c r="D14" s="118"/>
       <c r="E14">
         <f>Вал!$D$6</f>
         <v>38</v>
@@ -6234,12 +6234,12 @@
       <c r="S14" s="54"/>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A15" s="93" t="s">
+      <c r="A15" s="94" t="s">
         <v>140</v>
       </c>
-      <c r="B15" s="93"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="93"/>
+      <c r="B15" s="94"/>
+      <c r="C15" s="94"/>
+      <c r="D15" s="94"/>
       <c r="E15">
         <f>Вал!$K$19</f>
         <v>45</v>
@@ -6274,12 +6274,12 @@
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A16" s="93" t="s">
+      <c r="A16" s="94" t="s">
         <v>141</v>
       </c>
-      <c r="B16" s="93"/>
-      <c r="C16" s="93"/>
-      <c r="D16" s="93"/>
+      <c r="B16" s="94"/>
+      <c r="C16" s="94"/>
+      <c r="D16" s="94"/>
       <c r="E16">
         <f ca="1">Вал!$S$18</f>
         <v>56</v>
@@ -6290,46 +6290,46 @@
       <c r="Z16" s="59"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G18" s="140" t="s">
+      <c r="G18" s="144" t="s">
         <v>153</v>
       </c>
-      <c r="H18" s="141"/>
-      <c r="I18" s="141"/>
-      <c r="J18" s="141"/>
+      <c r="H18" s="145"/>
+      <c r="I18" s="145"/>
+      <c r="J18" s="145"/>
       <c r="K18" s="82">
         <v>6</v>
       </c>
       <c r="L18" s="84"/>
       <c r="M18" s="77"/>
-      <c r="N18" s="140" t="s">
+      <c r="N18" s="144" t="s">
         <v>153</v>
       </c>
-      <c r="O18" s="141"/>
-      <c r="P18" s="141"/>
-      <c r="Q18" s="141"/>
+      <c r="O18" s="145"/>
+      <c r="P18" s="145"/>
+      <c r="Q18" s="145"/>
       <c r="R18" s="82">
         <v>7</v>
       </c>
       <c r="S18" s="84"/>
       <c r="T18" s="77"/>
-      <c r="U18" s="140" t="s">
+      <c r="U18" s="144" t="s">
         <v>153</v>
       </c>
-      <c r="V18" s="141"/>
-      <c r="W18" s="141"/>
-      <c r="X18" s="141"/>
+      <c r="V18" s="145"/>
+      <c r="W18" s="145"/>
+      <c r="X18" s="145"/>
       <c r="Y18" s="82">
         <v>8</v>
       </c>
       <c r="Z18" s="84"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G19" s="131" t="s">
+      <c r="G19" s="135" t="s">
         <v>149</v>
       </c>
-      <c r="H19" s="132"/>
-      <c r="I19" s="132"/>
-      <c r="J19" s="132"/>
+      <c r="H19" s="136"/>
+      <c r="I19" s="136"/>
+      <c r="J19" s="136"/>
       <c r="K19" s="78">
         <v>69</v>
       </c>
@@ -6337,12 +6337,12 @@
         <v>156</v>
       </c>
       <c r="M19" s="77"/>
-      <c r="N19" s="131" t="s">
+      <c r="N19" s="135" t="s">
         <v>149</v>
       </c>
-      <c r="O19" s="132"/>
-      <c r="P19" s="132"/>
-      <c r="Q19" s="132"/>
+      <c r="O19" s="136"/>
+      <c r="P19" s="136"/>
+      <c r="Q19" s="136"/>
       <c r="R19" s="78">
         <v>57</v>
       </c>
@@ -6350,12 +6350,12 @@
         <v>156</v>
       </c>
       <c r="T19" s="77"/>
-      <c r="U19" s="131" t="s">
+      <c r="U19" s="135" t="s">
         <v>149</v>
       </c>
-      <c r="V19" s="132"/>
-      <c r="W19" s="132"/>
-      <c r="X19" s="132"/>
+      <c r="V19" s="136"/>
+      <c r="W19" s="136"/>
+      <c r="X19" s="136"/>
       <c r="Y19" s="78">
         <v>64</v>
       </c>
@@ -6364,12 +6364,12 @@
       </c>
     </row>
     <row r="20" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G20" s="131" t="s">
+      <c r="G20" s="135" t="s">
         <v>154</v>
       </c>
-      <c r="H20" s="132"/>
-      <c r="I20" s="132"/>
-      <c r="J20" s="132"/>
+      <c r="H20" s="136"/>
+      <c r="I20" s="136"/>
+      <c r="J20" s="136"/>
       <c r="K20" s="75">
         <v>22.3</v>
       </c>
@@ -6377,12 +6377,12 @@
         <v>156</v>
       </c>
       <c r="M20" s="77"/>
-      <c r="N20" s="131" t="s">
+      <c r="N20" s="135" t="s">
         <v>154</v>
       </c>
-      <c r="O20" s="132"/>
-      <c r="P20" s="132"/>
-      <c r="Q20" s="132"/>
+      <c r="O20" s="136"/>
+      <c r="P20" s="136"/>
+      <c r="Q20" s="136"/>
       <c r="R20" s="75">
         <v>20</v>
       </c>
@@ -6390,12 +6390,12 @@
         <v>156</v>
       </c>
       <c r="T20" s="77"/>
-      <c r="U20" s="131" t="s">
+      <c r="U20" s="135" t="s">
         <v>154</v>
       </c>
-      <c r="V20" s="132"/>
-      <c r="W20" s="132"/>
-      <c r="X20" s="132"/>
+      <c r="V20" s="136"/>
+      <c r="W20" s="136"/>
+      <c r="X20" s="136"/>
       <c r="Y20" s="75">
         <v>25.3</v>
       </c>
@@ -6404,12 +6404,12 @@
       </c>
     </row>
     <row r="21" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G21" s="131" t="s">
+      <c r="G21" s="135" t="s">
         <v>146</v>
       </c>
-      <c r="H21" s="132"/>
-      <c r="I21" s="132"/>
-      <c r="J21" s="132"/>
+      <c r="H21" s="136"/>
+      <c r="I21" s="136"/>
+      <c r="J21" s="136"/>
       <c r="K21" s="75">
         <v>240</v>
       </c>
@@ -6417,12 +6417,12 @@
         <v>16</v>
       </c>
       <c r="M21" s="77"/>
-      <c r="N21" s="131" t="s">
+      <c r="N21" s="135" t="s">
         <v>146</v>
       </c>
-      <c r="O21" s="132"/>
-      <c r="P21" s="132"/>
-      <c r="Q21" s="132"/>
+      <c r="O21" s="136"/>
+      <c r="P21" s="136"/>
+      <c r="Q21" s="136"/>
       <c r="R21" s="75">
         <v>180</v>
       </c>
@@ -6430,12 +6430,12 @@
         <v>16</v>
       </c>
       <c r="T21" s="77"/>
-      <c r="U21" s="131" t="s">
+      <c r="U21" s="135" t="s">
         <v>146</v>
       </c>
-      <c r="V21" s="132"/>
-      <c r="W21" s="132"/>
-      <c r="X21" s="132"/>
+      <c r="V21" s="136"/>
+      <c r="W21" s="136"/>
+      <c r="X21" s="136"/>
       <c r="Y21" s="75">
         <v>180</v>
       </c>
@@ -6444,12 +6444,12 @@
       </c>
     </row>
     <row r="22" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G22" s="131" t="s">
+      <c r="G22" s="135" t="s">
         <v>155</v>
       </c>
-      <c r="H22" s="132"/>
-      <c r="I22" s="132"/>
-      <c r="J22" s="132"/>
+      <c r="H22" s="136"/>
+      <c r="I22" s="136"/>
+      <c r="J22" s="136"/>
       <c r="K22" s="75">
         <v>3.5</v>
       </c>
@@ -6457,12 +6457,12 @@
         <v>16</v>
       </c>
       <c r="M22" s="77"/>
-      <c r="N22" s="131" t="s">
+      <c r="N22" s="135" t="s">
         <v>155</v>
       </c>
-      <c r="O22" s="132"/>
-      <c r="P22" s="132"/>
-      <c r="Q22" s="132"/>
+      <c r="O22" s="136"/>
+      <c r="P22" s="136"/>
+      <c r="Q22" s="136"/>
       <c r="R22" s="75">
         <v>2.5</v>
       </c>
@@ -6470,12 +6470,12 @@
         <v>16</v>
       </c>
       <c r="T22" s="77"/>
-      <c r="U22" s="131" t="s">
+      <c r="U22" s="135" t="s">
         <v>155</v>
       </c>
-      <c r="V22" s="132"/>
-      <c r="W22" s="132"/>
-      <c r="X22" s="132"/>
+      <c r="V22" s="136"/>
+      <c r="W22" s="136"/>
+      <c r="X22" s="136"/>
       <c r="Y22" s="75">
         <v>3</v>
       </c>
@@ -6484,12 +6484,12 @@
       </c>
     </row>
     <row r="23" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G23" s="131" t="s">
+      <c r="G23" s="135" t="s">
         <v>0</v>
       </c>
-      <c r="H23" s="132"/>
-      <c r="I23" s="132"/>
-      <c r="J23" s="132"/>
+      <c r="H23" s="136"/>
+      <c r="I23" s="136"/>
+      <c r="J23" s="136"/>
       <c r="K23" s="75">
         <v>1510</v>
       </c>
@@ -6497,12 +6497,12 @@
         <v>159</v>
       </c>
       <c r="M23" s="77"/>
-      <c r="N23" s="131" t="s">
+      <c r="N23" s="135" t="s">
         <v>0</v>
       </c>
-      <c r="O23" s="132"/>
-      <c r="P23" s="132"/>
-      <c r="Q23" s="132"/>
+      <c r="O23" s="136"/>
+      <c r="P23" s="136"/>
+      <c r="Q23" s="136"/>
       <c r="R23" s="75">
         <v>2016</v>
       </c>
@@ -6510,12 +6510,12 @@
         <v>159</v>
       </c>
       <c r="T23" s="77"/>
-      <c r="U23" s="131" t="s">
+      <c r="U23" s="135" t="s">
         <v>0</v>
       </c>
-      <c r="V23" s="132"/>
-      <c r="W23" s="132"/>
-      <c r="X23" s="132"/>
+      <c r="V23" s="136"/>
+      <c r="W23" s="136"/>
+      <c r="X23" s="136"/>
       <c r="Y23" s="75">
         <v>2013</v>
       </c>
@@ -6524,12 +6524,12 @@
       </c>
     </row>
     <row r="24" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G24" s="131" t="s">
+      <c r="G24" s="135" t="s">
         <v>157</v>
       </c>
-      <c r="H24" s="132"/>
-      <c r="I24" s="132"/>
-      <c r="J24" s="132"/>
+      <c r="H24" s="136"/>
+      <c r="I24" s="136"/>
+      <c r="J24" s="136"/>
       <c r="K24" s="75">
         <v>554</v>
       </c>
@@ -6537,12 +6537,12 @@
         <v>159</v>
       </c>
       <c r="M24" s="77"/>
-      <c r="N24" s="131" t="s">
+      <c r="N24" s="135" t="s">
         <v>157</v>
       </c>
-      <c r="O24" s="132"/>
-      <c r="P24" s="132"/>
-      <c r="Q24" s="132"/>
+      <c r="O24" s="136"/>
+      <c r="P24" s="136"/>
+      <c r="Q24" s="136"/>
       <c r="R24" s="75">
         <v>734</v>
       </c>
@@ -6550,12 +6550,12 @@
         <v>159</v>
       </c>
       <c r="T24" s="77"/>
-      <c r="U24" s="131" t="s">
+      <c r="U24" s="135" t="s">
         <v>157</v>
       </c>
-      <c r="V24" s="132"/>
-      <c r="W24" s="132"/>
-      <c r="X24" s="132"/>
+      <c r="V24" s="136"/>
+      <c r="W24" s="136"/>
+      <c r="X24" s="136"/>
       <c r="Y24" s="75">
         <v>733</v>
       </c>
@@ -6564,12 +6564,12 @@
       </c>
     </row>
     <row r="25" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G25" s="133" t="s">
+      <c r="G25" s="137" t="s">
         <v>158</v>
       </c>
-      <c r="H25" s="134"/>
-      <c r="I25" s="134"/>
-      <c r="J25" s="134"/>
+      <c r="H25" s="138"/>
+      <c r="I25" s="138"/>
+      <c r="J25" s="138"/>
       <c r="K25" s="80">
         <v>0</v>
       </c>
@@ -6577,12 +6577,12 @@
         <v>159</v>
       </c>
       <c r="M25" s="77"/>
-      <c r="N25" s="133" t="s">
+      <c r="N25" s="137" t="s">
         <v>158</v>
       </c>
-      <c r="O25" s="134"/>
-      <c r="P25" s="134"/>
-      <c r="Q25" s="134"/>
+      <c r="O25" s="138"/>
+      <c r="P25" s="138"/>
+      <c r="Q25" s="138"/>
       <c r="R25" s="80">
         <v>0</v>
       </c>
@@ -6590,12 +6590,12 @@
         <v>159</v>
       </c>
       <c r="T25" s="77"/>
-      <c r="U25" s="133" t="s">
+      <c r="U25" s="137" t="s">
         <v>158</v>
       </c>
-      <c r="V25" s="134"/>
-      <c r="W25" s="134"/>
-      <c r="X25" s="134"/>
+      <c r="V25" s="138"/>
+      <c r="W25" s="138"/>
+      <c r="X25" s="138"/>
       <c r="Y25" s="80">
         <v>0</v>
       </c>
@@ -6604,74 +6604,74 @@
       </c>
     </row>
     <row r="26" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G26" s="135" t="s">
+      <c r="G26" s="132" t="s">
         <v>161</v>
       </c>
-      <c r="H26" s="136"/>
-      <c r="I26" s="136"/>
-      <c r="J26" s="136"/>
-      <c r="K26" s="136"/>
-      <c r="L26" s="137"/>
+      <c r="H26" s="133"/>
+      <c r="I26" s="133"/>
+      <c r="J26" s="133"/>
+      <c r="K26" s="133"/>
+      <c r="L26" s="134"/>
       <c r="M26" s="77"/>
-      <c r="N26" s="135" t="s">
+      <c r="N26" s="132" t="s">
         <v>161</v>
       </c>
-      <c r="O26" s="136"/>
-      <c r="P26" s="136"/>
-      <c r="Q26" s="136"/>
-      <c r="R26" s="136"/>
-      <c r="S26" s="137"/>
+      <c r="O26" s="133"/>
+      <c r="P26" s="133"/>
+      <c r="Q26" s="133"/>
+      <c r="R26" s="133"/>
+      <c r="S26" s="134"/>
       <c r="T26" s="77"/>
-      <c r="U26" s="135" t="s">
+      <c r="U26" s="132" t="s">
         <v>161</v>
       </c>
-      <c r="V26" s="136"/>
-      <c r="W26" s="136"/>
-      <c r="X26" s="136"/>
-      <c r="Y26" s="136"/>
-      <c r="Z26" s="137"/>
+      <c r="V26" s="133"/>
+      <c r="W26" s="133"/>
+      <c r="X26" s="133"/>
+      <c r="Y26" s="133"/>
+      <c r="Z26" s="134"/>
     </row>
     <row r="27" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G27" s="131" t="s">
+      <c r="G27" s="135" t="s">
         <v>162</v>
       </c>
-      <c r="H27" s="132"/>
-      <c r="I27" s="132"/>
-      <c r="J27" s="132"/>
+      <c r="H27" s="136"/>
+      <c r="I27" s="136"/>
+      <c r="J27" s="136"/>
       <c r="K27" s="87">
         <v>16</v>
       </c>
       <c r="L27" s="76"/>
       <c r="M27" s="77"/>
-      <c r="N27" s="131" t="s">
+      <c r="N27" s="135" t="s">
         <v>162</v>
       </c>
-      <c r="O27" s="132"/>
-      <c r="P27" s="132"/>
-      <c r="Q27" s="132"/>
+      <c r="O27" s="136"/>
+      <c r="P27" s="136"/>
+      <c r="Q27" s="136"/>
       <c r="R27" s="87">
         <v>17</v>
       </c>
       <c r="S27" s="76"/>
       <c r="T27" s="77"/>
-      <c r="U27" s="131" t="s">
+      <c r="U27" s="135" t="s">
         <v>162</v>
       </c>
-      <c r="V27" s="132"/>
-      <c r="W27" s="132"/>
-      <c r="X27" s="132"/>
+      <c r="V27" s="136"/>
+      <c r="W27" s="136"/>
+      <c r="X27" s="136"/>
       <c r="Y27" s="87">
         <v>14</v>
       </c>
       <c r="Z27" s="76"/>
     </row>
     <row r="28" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G28" s="138" t="s">
+      <c r="G28" s="139" t="s">
         <v>167</v>
       </c>
-      <c r="H28" s="139"/>
-      <c r="I28" s="139"/>
-      <c r="J28" s="139"/>
+      <c r="H28" s="140"/>
+      <c r="I28" s="140"/>
+      <c r="J28" s="140"/>
       <c r="K28" s="87">
         <v>0.3</v>
       </c>
@@ -6679,12 +6679,12 @@
         <v>16</v>
       </c>
       <c r="M28" s="77"/>
-      <c r="N28" s="138" t="s">
+      <c r="N28" s="139" t="s">
         <v>167</v>
       </c>
-      <c r="O28" s="139"/>
-      <c r="P28" s="139"/>
-      <c r="Q28" s="139"/>
+      <c r="O28" s="140"/>
+      <c r="P28" s="140"/>
+      <c r="Q28" s="140"/>
       <c r="R28" s="87">
         <v>-0.3</v>
       </c>
@@ -6692,12 +6692,12 @@
         <v>16</v>
       </c>
       <c r="T28" s="77"/>
-      <c r="U28" s="138" t="s">
+      <c r="U28" s="139" t="s">
         <v>167</v>
       </c>
-      <c r="V28" s="139"/>
-      <c r="W28" s="139"/>
-      <c r="X28" s="139"/>
+      <c r="V28" s="140"/>
+      <c r="W28" s="140"/>
+      <c r="X28" s="140"/>
       <c r="Y28" s="87">
         <v>0.3</v>
       </c>
@@ -6706,12 +6706,12 @@
       </c>
     </row>
     <row r="29" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G29" s="138" t="s">
+      <c r="G29" s="139" t="s">
         <v>166</v>
       </c>
-      <c r="H29" s="139"/>
-      <c r="I29" s="139"/>
-      <c r="J29" s="139"/>
+      <c r="H29" s="140"/>
+      <c r="I29" s="140"/>
+      <c r="J29" s="140"/>
       <c r="K29" s="87">
         <v>49</v>
       </c>
@@ -6719,12 +6719,12 @@
         <v>263</v>
       </c>
       <c r="M29" s="77"/>
-      <c r="N29" s="138" t="s">
+      <c r="N29" s="139" t="s">
         <v>166</v>
       </c>
-      <c r="O29" s="139"/>
-      <c r="P29" s="139"/>
-      <c r="Q29" s="139"/>
+      <c r="O29" s="140"/>
+      <c r="P29" s="140"/>
+      <c r="Q29" s="140"/>
       <c r="R29" s="87">
         <v>49</v>
       </c>
@@ -6732,12 +6732,12 @@
         <v>263</v>
       </c>
       <c r="T29" s="77"/>
-      <c r="U29" s="138" t="s">
+      <c r="U29" s="139" t="s">
         <v>166</v>
       </c>
-      <c r="V29" s="139"/>
-      <c r="W29" s="139"/>
-      <c r="X29" s="139"/>
+      <c r="V29" s="140"/>
+      <c r="W29" s="140"/>
+      <c r="X29" s="140"/>
       <c r="Y29" s="87">
         <v>49</v>
       </c>
@@ -6746,34 +6746,34 @@
       </c>
     </row>
     <row r="30" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G30" s="138" t="s">
+      <c r="G30" s="139" t="s">
         <v>168</v>
       </c>
-      <c r="H30" s="139"/>
-      <c r="I30" s="139"/>
-      <c r="J30" s="139"/>
+      <c r="H30" s="140"/>
+      <c r="I30" s="140"/>
+      <c r="J30" s="140"/>
       <c r="K30" s="87" t="s">
         <v>169</v>
       </c>
       <c r="L30" s="76"/>
       <c r="M30" s="77"/>
-      <c r="N30" s="138" t="s">
+      <c r="N30" s="139" t="s">
         <v>168</v>
       </c>
-      <c r="O30" s="139"/>
-      <c r="P30" s="139"/>
-      <c r="Q30" s="139"/>
+      <c r="O30" s="140"/>
+      <c r="P30" s="140"/>
+      <c r="Q30" s="140"/>
       <c r="R30" s="87" t="s">
         <v>169</v>
       </c>
       <c r="S30" s="76"/>
       <c r="T30" s="77"/>
-      <c r="U30" s="138" t="s">
+      <c r="U30" s="139" t="s">
         <v>168</v>
       </c>
-      <c r="V30" s="139"/>
-      <c r="W30" s="139"/>
-      <c r="X30" s="139"/>
+      <c r="V30" s="140"/>
+      <c r="W30" s="140"/>
+      <c r="X30" s="140"/>
       <c r="Y30" s="87" t="s">
         <v>169</v>
       </c>
@@ -6781,12 +6781,12 @@
     </row>
     <row r="31" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B31" s="86"/>
-      <c r="G31" s="131" t="s">
+      <c r="G31" s="135" t="s">
         <v>213</v>
       </c>
-      <c r="H31" s="132"/>
-      <c r="I31" s="132"/>
-      <c r="J31" s="132"/>
+      <c r="H31" s="136"/>
+      <c r="I31" s="136"/>
+      <c r="J31" s="136"/>
       <c r="K31" s="87">
         <v>56</v>
       </c>
@@ -6794,12 +6794,12 @@
         <v>16</v>
       </c>
       <c r="M31" s="77"/>
-      <c r="N31" s="131" t="s">
+      <c r="N31" s="135" t="s">
         <v>213</v>
       </c>
-      <c r="O31" s="132"/>
-      <c r="P31" s="132"/>
-      <c r="Q31" s="132"/>
+      <c r="O31" s="136"/>
+      <c r="P31" s="136"/>
+      <c r="Q31" s="136"/>
       <c r="R31" s="87">
         <v>42.5</v>
       </c>
@@ -6807,12 +6807,12 @@
         <v>16</v>
       </c>
       <c r="T31" s="77"/>
-      <c r="U31" s="131" t="s">
+      <c r="U31" s="135" t="s">
         <v>213</v>
       </c>
-      <c r="V31" s="132"/>
-      <c r="W31" s="132"/>
-      <c r="X31" s="132"/>
+      <c r="V31" s="136"/>
+      <c r="W31" s="136"/>
+      <c r="X31" s="136"/>
       <c r="Y31" s="87">
         <v>42</v>
       </c>
@@ -6821,12 +6821,12 @@
       </c>
     </row>
     <row r="32" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G32" s="131" t="s">
+      <c r="G32" s="135" t="s">
         <v>184</v>
       </c>
-      <c r="H32" s="132"/>
-      <c r="I32" s="132"/>
-      <c r="J32" s="132"/>
+      <c r="H32" s="136"/>
+      <c r="I32" s="136"/>
+      <c r="J32" s="136"/>
       <c r="K32" s="87">
         <v>65</v>
       </c>
@@ -6834,12 +6834,12 @@
         <v>16</v>
       </c>
       <c r="M32" s="77"/>
-      <c r="N32" s="131" t="s">
+      <c r="N32" s="135" t="s">
         <v>184</v>
       </c>
-      <c r="O32" s="132"/>
-      <c r="P32" s="132"/>
-      <c r="Q32" s="132"/>
+      <c r="O32" s="136"/>
+      <c r="P32" s="136"/>
+      <c r="Q32" s="136"/>
       <c r="R32" s="87">
         <v>49</v>
       </c>
@@ -6847,12 +6847,12 @@
         <v>16</v>
       </c>
       <c r="T32" s="77"/>
-      <c r="U32" s="131" t="s">
+      <c r="U32" s="135" t="s">
         <v>184</v>
       </c>
-      <c r="V32" s="132"/>
-      <c r="W32" s="132"/>
-      <c r="X32" s="132"/>
+      <c r="V32" s="136"/>
+      <c r="W32" s="136"/>
+      <c r="X32" s="136"/>
       <c r="Y32" s="87">
         <v>49.8</v>
       </c>
@@ -6861,12 +6861,12 @@
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G33" s="131" t="s">
+      <c r="G33" s="135" t="s">
         <v>175</v>
       </c>
-      <c r="H33" s="132"/>
-      <c r="I33" s="132"/>
-      <c r="J33" s="132"/>
+      <c r="H33" s="136"/>
+      <c r="I33" s="136"/>
+      <c r="J33" s="136"/>
       <c r="K33" s="87">
         <v>49.35</v>
       </c>
@@ -6874,12 +6874,12 @@
         <v>16</v>
       </c>
       <c r="M33" s="77"/>
-      <c r="N33" s="131" t="s">
+      <c r="N33" s="135" t="s">
         <v>175</v>
       </c>
-      <c r="O33" s="132"/>
-      <c r="P33" s="132"/>
-      <c r="Q33" s="132"/>
+      <c r="O33" s="136"/>
+      <c r="P33" s="136"/>
+      <c r="Q33" s="136"/>
       <c r="R33" s="87">
         <v>37.75</v>
       </c>
@@ -6887,12 +6887,12 @@
         <v>16</v>
       </c>
       <c r="T33" s="77"/>
-      <c r="U33" s="131" t="s">
+      <c r="U33" s="135" t="s">
         <v>175</v>
       </c>
-      <c r="V33" s="132"/>
-      <c r="W33" s="132"/>
-      <c r="X33" s="132"/>
+      <c r="V33" s="136"/>
+      <c r="W33" s="136"/>
+      <c r="X33" s="136"/>
       <c r="Y33" s="87">
         <v>36.6</v>
       </c>
@@ -6901,12 +6901,12 @@
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G34" s="131" t="s">
+      <c r="G34" s="135" t="s">
         <v>165</v>
       </c>
-      <c r="H34" s="132"/>
-      <c r="I34" s="132"/>
-      <c r="J34" s="132"/>
+      <c r="H34" s="136"/>
+      <c r="I34" s="136"/>
+      <c r="J34" s="136"/>
       <c r="K34" s="87">
         <v>40</v>
       </c>
@@ -6914,12 +6914,12 @@
         <v>16</v>
       </c>
       <c r="M34" s="77"/>
-      <c r="N34" s="131" t="s">
+      <c r="N34" s="135" t="s">
         <v>165</v>
       </c>
-      <c r="O34" s="132"/>
-      <c r="P34" s="132"/>
-      <c r="Q34" s="132"/>
+      <c r="O34" s="136"/>
+      <c r="P34" s="136"/>
+      <c r="Q34" s="136"/>
       <c r="R34" s="87">
         <v>62</v>
       </c>
@@ -6927,12 +6927,12 @@
         <v>16</v>
       </c>
       <c r="T34" s="77"/>
-      <c r="U34" s="133" t="s">
+      <c r="U34" s="137" t="s">
         <v>165</v>
       </c>
-      <c r="V34" s="134"/>
-      <c r="W34" s="134"/>
-      <c r="X34" s="134"/>
+      <c r="V34" s="138"/>
+      <c r="W34" s="138"/>
+      <c r="X34" s="138"/>
       <c r="Y34" s="87">
         <v>79</v>
       </c>
@@ -6941,74 +6941,74 @@
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G35" s="135" t="s">
+      <c r="G35" s="132" t="s">
         <v>124</v>
       </c>
-      <c r="H35" s="136"/>
-      <c r="I35" s="136"/>
-      <c r="J35" s="136"/>
-      <c r="K35" s="136"/>
-      <c r="L35" s="137"/>
+      <c r="H35" s="133"/>
+      <c r="I35" s="133"/>
+      <c r="J35" s="133"/>
+      <c r="K35" s="133"/>
+      <c r="L35" s="134"/>
       <c r="M35" s="77"/>
-      <c r="N35" s="135" t="s">
+      <c r="N35" s="132" t="s">
         <v>124</v>
       </c>
-      <c r="O35" s="136"/>
-      <c r="P35" s="136"/>
-      <c r="Q35" s="136"/>
-      <c r="R35" s="136"/>
-      <c r="S35" s="137"/>
+      <c r="O35" s="133"/>
+      <c r="P35" s="133"/>
+      <c r="Q35" s="133"/>
+      <c r="R35" s="133"/>
+      <c r="S35" s="134"/>
       <c r="T35" s="77"/>
-      <c r="U35" s="135" t="s">
+      <c r="U35" s="132" t="s">
         <v>124</v>
       </c>
-      <c r="V35" s="136"/>
-      <c r="W35" s="136"/>
-      <c r="X35" s="136"/>
-      <c r="Y35" s="136"/>
-      <c r="Z35" s="137"/>
+      <c r="V35" s="133"/>
+      <c r="W35" s="133"/>
+      <c r="X35" s="133"/>
+      <c r="Y35" s="133"/>
+      <c r="Z35" s="134"/>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G36" s="131" t="s">
+      <c r="G36" s="135" t="s">
         <v>162</v>
       </c>
-      <c r="H36" s="132"/>
-      <c r="I36" s="132"/>
-      <c r="J36" s="132"/>
+      <c r="H36" s="136"/>
+      <c r="I36" s="136"/>
+      <c r="J36" s="136"/>
       <c r="K36" s="87">
         <v>121</v>
       </c>
       <c r="L36" s="76"/>
       <c r="M36" s="77"/>
-      <c r="N36" s="131" t="s">
+      <c r="N36" s="135" t="s">
         <v>162</v>
       </c>
-      <c r="O36" s="132"/>
-      <c r="P36" s="132"/>
-      <c r="Q36" s="132"/>
+      <c r="O36" s="136"/>
+      <c r="P36" s="136"/>
+      <c r="Q36" s="136"/>
       <c r="R36" s="87">
         <v>127</v>
       </c>
       <c r="S36" s="76"/>
       <c r="T36" s="77"/>
-      <c r="U36" s="131" t="s">
+      <c r="U36" s="135" t="s">
         <v>162</v>
       </c>
-      <c r="V36" s="132"/>
-      <c r="W36" s="132"/>
-      <c r="X36" s="132"/>
+      <c r="V36" s="136"/>
+      <c r="W36" s="136"/>
+      <c r="X36" s="136"/>
       <c r="Y36" s="87">
         <v>106</v>
       </c>
       <c r="Z36" s="76"/>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G37" s="138" t="s">
+      <c r="G37" s="139" t="s">
         <v>167</v>
       </c>
-      <c r="H37" s="139"/>
-      <c r="I37" s="139"/>
-      <c r="J37" s="139"/>
+      <c r="H37" s="140"/>
+      <c r="I37" s="140"/>
+      <c r="J37" s="140"/>
       <c r="K37" s="87">
         <v>-0.22800000000000001</v>
       </c>
@@ -7016,12 +7016,12 @@
         <v>16</v>
       </c>
       <c r="M37" s="88"/>
-      <c r="N37" s="138" t="s">
+      <c r="N37" s="139" t="s">
         <v>167</v>
       </c>
-      <c r="O37" s="139"/>
-      <c r="P37" s="139"/>
-      <c r="Q37" s="139"/>
+      <c r="O37" s="140"/>
+      <c r="P37" s="140"/>
+      <c r="Q37" s="140"/>
       <c r="R37" s="87">
         <v>0.3</v>
       </c>
@@ -7029,12 +7029,12 @@
         <v>16</v>
       </c>
       <c r="T37" s="88"/>
-      <c r="U37" s="138" t="s">
+      <c r="U37" s="139" t="s">
         <v>167</v>
       </c>
-      <c r="V37" s="139"/>
-      <c r="W37" s="139"/>
-      <c r="X37" s="139"/>
+      <c r="V37" s="140"/>
+      <c r="W37" s="140"/>
+      <c r="X37" s="140"/>
       <c r="Y37" s="87">
         <v>-0.3</v>
       </c>
@@ -7043,12 +7043,12 @@
       </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G38" s="138" t="s">
+      <c r="G38" s="139" t="s">
         <v>166</v>
       </c>
-      <c r="H38" s="139"/>
-      <c r="I38" s="139"/>
-      <c r="J38" s="139"/>
+      <c r="H38" s="140"/>
+      <c r="I38" s="140"/>
+      <c r="J38" s="140"/>
       <c r="K38" s="87">
         <v>28.5</v>
       </c>
@@ -7056,12 +7056,12 @@
         <v>263</v>
       </c>
       <c r="M38" s="77"/>
-      <c r="N38" s="138" t="s">
+      <c r="N38" s="139" t="s">
         <v>166</v>
       </c>
-      <c r="O38" s="139"/>
-      <c r="P38" s="139"/>
-      <c r="Q38" s="139"/>
+      <c r="O38" s="140"/>
+      <c r="P38" s="140"/>
+      <c r="Q38" s="140"/>
       <c r="R38" s="87">
         <v>28.5</v>
       </c>
@@ -7069,12 +7069,12 @@
         <v>263</v>
       </c>
       <c r="T38" s="77"/>
-      <c r="U38" s="138" t="s">
+      <c r="U38" s="139" t="s">
         <v>166</v>
       </c>
-      <c r="V38" s="139"/>
-      <c r="W38" s="139"/>
-      <c r="X38" s="139"/>
+      <c r="V38" s="140"/>
+      <c r="W38" s="140"/>
+      <c r="X38" s="140"/>
       <c r="Y38" s="87">
         <v>28.5</v>
       </c>
@@ -7083,34 +7083,34 @@
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G39" s="138" t="s">
+      <c r="G39" s="139" t="s">
         <v>168</v>
       </c>
-      <c r="H39" s="139"/>
-      <c r="I39" s="139"/>
-      <c r="J39" s="139"/>
+      <c r="H39" s="140"/>
+      <c r="I39" s="140"/>
+      <c r="J39" s="140"/>
       <c r="K39" s="87" t="s">
         <v>170</v>
       </c>
       <c r="L39" s="76"/>
       <c r="M39" s="77"/>
-      <c r="N39" s="138" t="s">
+      <c r="N39" s="139" t="s">
         <v>168</v>
       </c>
-      <c r="O39" s="139"/>
-      <c r="P39" s="139"/>
-      <c r="Q39" s="139"/>
+      <c r="O39" s="140"/>
+      <c r="P39" s="140"/>
+      <c r="Q39" s="140"/>
       <c r="R39" s="87" t="s">
         <v>170</v>
       </c>
       <c r="S39" s="76"/>
       <c r="T39" s="77"/>
-      <c r="U39" s="138" t="s">
+      <c r="U39" s="139" t="s">
         <v>168</v>
       </c>
-      <c r="V39" s="139"/>
-      <c r="W39" s="139"/>
-      <c r="X39" s="139"/>
+      <c r="V39" s="140"/>
+      <c r="W39" s="140"/>
+      <c r="X39" s="140"/>
       <c r="Y39" s="87" t="s">
         <v>170</v>
       </c>
@@ -7118,12 +7118,12 @@
       <c r="AA39" s="86"/>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G40" s="131" t="s">
+      <c r="G40" s="135" t="s">
         <v>213</v>
       </c>
-      <c r="H40" s="132"/>
-      <c r="I40" s="132"/>
-      <c r="J40" s="132"/>
+      <c r="H40" s="136"/>
+      <c r="I40" s="136"/>
+      <c r="J40" s="136"/>
       <c r="K40" s="87">
         <v>423.5</v>
       </c>
@@ -7131,12 +7131,12 @@
         <v>16</v>
       </c>
       <c r="M40" s="77"/>
-      <c r="N40" s="131" t="s">
+      <c r="N40" s="135" t="s">
         <v>213</v>
       </c>
-      <c r="O40" s="132"/>
-      <c r="P40" s="132"/>
-      <c r="Q40" s="132"/>
+      <c r="O40" s="136"/>
+      <c r="P40" s="136"/>
+      <c r="Q40" s="136"/>
       <c r="R40" s="87">
         <v>317.5</v>
       </c>
@@ -7144,12 +7144,12 @@
         <v>16</v>
       </c>
       <c r="T40" s="77"/>
-      <c r="U40" s="131" t="s">
+      <c r="U40" s="135" t="s">
         <v>213</v>
       </c>
-      <c r="V40" s="132"/>
-      <c r="W40" s="132"/>
-      <c r="X40" s="132"/>
+      <c r="V40" s="136"/>
+      <c r="W40" s="136"/>
+      <c r="X40" s="136"/>
       <c r="Y40" s="87">
         <v>318</v>
       </c>
@@ -7159,12 +7159,12 @@
       <c r="AA40" s="86"/>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G41" s="131" t="s">
+      <c r="G41" s="135" t="s">
         <v>184</v>
       </c>
-      <c r="H41" s="132"/>
-      <c r="I41" s="132"/>
-      <c r="J41" s="132"/>
+      <c r="H41" s="136"/>
+      <c r="I41" s="136"/>
+      <c r="J41" s="136"/>
       <c r="K41" s="87">
         <v>428.9</v>
       </c>
@@ -7172,12 +7172,12 @@
         <v>16</v>
       </c>
       <c r="M41" s="77"/>
-      <c r="N41" s="131" t="s">
+      <c r="N41" s="135" t="s">
         <v>184</v>
       </c>
-      <c r="O41" s="132"/>
-      <c r="P41" s="132"/>
-      <c r="Q41" s="132"/>
+      <c r="O41" s="136"/>
+      <c r="P41" s="136"/>
+      <c r="Q41" s="136"/>
       <c r="R41" s="87">
         <v>321</v>
       </c>
@@ -7185,12 +7185,12 @@
         <v>16</v>
       </c>
       <c r="T41" s="77"/>
-      <c r="U41" s="131" t="s">
+      <c r="U41" s="135" t="s">
         <v>184</v>
       </c>
-      <c r="V41" s="132"/>
-      <c r="W41" s="132"/>
-      <c r="X41" s="132"/>
+      <c r="V41" s="136"/>
+      <c r="W41" s="136"/>
+      <c r="X41" s="136"/>
       <c r="Y41" s="87">
         <v>322</v>
       </c>
@@ -7200,12 +7200,12 @@
       <c r="AA41" s="86"/>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G42" s="131" t="s">
+      <c r="G42" s="135" t="s">
         <v>175</v>
       </c>
-      <c r="H42" s="132"/>
-      <c r="I42" s="132"/>
-      <c r="J42" s="132"/>
+      <c r="H42" s="136"/>
+      <c r="I42" s="136"/>
+      <c r="J42" s="136"/>
       <c r="K42" s="87">
         <v>413</v>
       </c>
@@ -7213,12 +7213,12 @@
         <v>16</v>
       </c>
       <c r="M42" s="77"/>
-      <c r="N42" s="131" t="s">
+      <c r="N42" s="135" t="s">
         <v>175</v>
       </c>
-      <c r="O42" s="132"/>
-      <c r="P42" s="132"/>
-      <c r="Q42" s="132"/>
+      <c r="O42" s="136"/>
+      <c r="P42" s="136"/>
+      <c r="Q42" s="136"/>
       <c r="R42" s="87">
         <v>309.75</v>
       </c>
@@ -7226,12 +7226,12 @@
         <v>16</v>
       </c>
       <c r="T42" s="77"/>
-      <c r="U42" s="131" t="s">
+      <c r="U42" s="135" t="s">
         <v>175</v>
       </c>
-      <c r="V42" s="132"/>
-      <c r="W42" s="132"/>
-      <c r="X42" s="132"/>
+      <c r="V42" s="136"/>
+      <c r="W42" s="136"/>
+      <c r="X42" s="136"/>
       <c r="Y42" s="87">
         <v>308.7</v>
       </c>
@@ -7241,12 +7241,12 @@
       <c r="AA42" s="16"/>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G43" s="133" t="s">
+      <c r="G43" s="137" t="s">
         <v>165</v>
       </c>
-      <c r="H43" s="134"/>
-      <c r="I43" s="134"/>
-      <c r="J43" s="134"/>
+      <c r="H43" s="138"/>
+      <c r="I43" s="138"/>
+      <c r="J43" s="138"/>
       <c r="K43" s="89">
         <v>36</v>
       </c>
@@ -7254,12 +7254,12 @@
         <v>16</v>
       </c>
       <c r="M43" s="77"/>
-      <c r="N43" s="133" t="s">
+      <c r="N43" s="137" t="s">
         <v>165</v>
       </c>
-      <c r="O43" s="134"/>
-      <c r="P43" s="134"/>
-      <c r="Q43" s="134"/>
+      <c r="O43" s="138"/>
+      <c r="P43" s="138"/>
+      <c r="Q43" s="138"/>
       <c r="R43" s="89">
         <v>57</v>
       </c>
@@ -7267,12 +7267,12 @@
         <v>16</v>
       </c>
       <c r="T43" s="77"/>
-      <c r="U43" s="133" t="s">
+      <c r="U43" s="137" t="s">
         <v>165</v>
       </c>
-      <c r="V43" s="134"/>
-      <c r="W43" s="134"/>
-      <c r="X43" s="134"/>
+      <c r="V43" s="138"/>
+      <c r="W43" s="138"/>
+      <c r="X43" s="138"/>
       <c r="Y43" s="89">
         <v>72</v>
       </c>
@@ -7286,12 +7286,12 @@
       <c r="AA44" s="86"/>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A45" s="135" t="s">
+      <c r="A45" s="132" t="s">
         <v>174</v>
       </c>
-      <c r="B45" s="136"/>
-      <c r="C45" s="136"/>
-      <c r="D45" s="136"/>
+      <c r="B45" s="133"/>
+      <c r="C45" s="133"/>
+      <c r="D45" s="133"/>
       <c r="E45" s="85">
         <v>7</v>
       </c>
@@ -7299,11 +7299,11 @@
       <c r="AA45" s="86"/>
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A46" s="131" t="s">
+      <c r="A46" s="135" t="s">
         <v>146</v>
       </c>
-      <c r="B46" s="132"/>
-      <c r="C46" s="132"/>
+      <c r="B46" s="136"/>
+      <c r="C46" s="136"/>
       <c r="D46" s="75">
         <f>HLOOKUP($E$45,$18:$43,4)</f>
         <v>180</v>
@@ -7317,11 +7317,11 @@
       <c r="AA46" s="86"/>
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A47" s="142" t="s">
+      <c r="A47" s="141" t="s">
         <v>155</v>
       </c>
-      <c r="B47" s="143"/>
-      <c r="C47" s="143"/>
+      <c r="B47" s="142"/>
+      <c r="C47" s="142"/>
       <c r="D47" s="80">
         <f>HLOOKUP($E$45,$18:$43,5)</f>
         <v>2.5</v>
@@ -7333,22 +7333,22 @@
       <c r="AA47" s="86"/>
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A48" s="138" t="s">
+      <c r="A48" s="139" t="s">
         <v>224</v>
       </c>
-      <c r="B48" s="139"/>
-      <c r="C48" s="139"/>
-      <c r="D48" s="139"/>
-      <c r="E48" s="144"/>
+      <c r="B48" s="140"/>
+      <c r="C48" s="140"/>
+      <c r="D48" s="140"/>
+      <c r="E48" s="143"/>
       <c r="L48" s="86"/>
       <c r="Z48" s="59"/>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A49" s="140" t="s">
+      <c r="A49" s="144" t="s">
         <v>0</v>
       </c>
-      <c r="B49" s="141"/>
-      <c r="C49" s="141"/>
+      <c r="B49" s="145"/>
+      <c r="C49" s="145"/>
       <c r="D49" s="82">
         <f>HLOOKUP($E$45,$18:$43,6)</f>
         <v>2016</v>
@@ -7359,11 +7359,11 @@
       <c r="Z49" s="59"/>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A50" s="131" t="s">
+      <c r="A50" s="135" t="s">
         <v>157</v>
       </c>
-      <c r="B50" s="132"/>
-      <c r="C50" s="132"/>
+      <c r="B50" s="136"/>
+      <c r="C50" s="136"/>
       <c r="D50" s="75">
         <f>HLOOKUP($E$45,$18:$43,7)</f>
         <v>734</v>
@@ -7374,11 +7374,11 @@
       <c r="Z50" s="59"/>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A51" s="133" t="s">
+      <c r="A51" s="137" t="s">
         <v>158</v>
       </c>
-      <c r="B51" s="134"/>
-      <c r="C51" s="134"/>
+      <c r="B51" s="138"/>
+      <c r="C51" s="138"/>
       <c r="D51" s="80">
         <f>HLOOKUP($E$45,$18:$43,8)</f>
         <v>0</v>
@@ -7389,21 +7389,21 @@
       <c r="Z51" s="59"/>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A52" s="138" t="s">
+      <c r="A52" s="139" t="s">
         <v>214</v>
       </c>
-      <c r="B52" s="139"/>
-      <c r="C52" s="139"/>
-      <c r="D52" s="139"/>
-      <c r="E52" s="144"/>
+      <c r="B52" s="140"/>
+      <c r="C52" s="140"/>
+      <c r="D52" s="140"/>
+      <c r="E52" s="143"/>
       <c r="Z52" s="59"/>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A53" s="135" t="s">
+      <c r="A53" s="132" t="s">
         <v>215</v>
       </c>
-      <c r="B53" s="136"/>
-      <c r="C53" s="136"/>
+      <c r="B53" s="133"/>
+      <c r="C53" s="133"/>
       <c r="D53" s="82">
         <f>HLOOKUP($E$45,$18:$43,14)</f>
         <v>42.5</v>
@@ -7414,11 +7414,11 @@
       <c r="Z53" s="59"/>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A54" s="138" t="s">
+      <c r="A54" s="139" t="s">
         <v>164</v>
       </c>
-      <c r="B54" s="139"/>
-      <c r="C54" s="139"/>
+      <c r="B54" s="140"/>
+      <c r="C54" s="140"/>
       <c r="D54" s="75">
         <f>HLOOKUP($E$45,$18:$43,15)</f>
         <v>49</v>
@@ -7429,11 +7429,11 @@
       <c r="Z54" s="59"/>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A55" s="138" t="s">
+      <c r="A55" s="139" t="s">
         <v>163</v>
       </c>
-      <c r="B55" s="139"/>
-      <c r="C55" s="139"/>
+      <c r="B55" s="140"/>
+      <c r="C55" s="140"/>
       <c r="D55" s="75">
         <f>HLOOKUP($E$45,$18:$43,16)</f>
         <v>37.75</v>
@@ -7444,11 +7444,11 @@
       <c r="Z55" s="59"/>
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A56" s="142" t="s">
+      <c r="A56" s="141" t="s">
         <v>165</v>
       </c>
-      <c r="B56" s="143"/>
-      <c r="C56" s="143"/>
+      <c r="B56" s="142"/>
+      <c r="C56" s="142"/>
       <c r="D56" s="80">
         <f>HLOOKUP($E$45,$18:$43,17)</f>
         <v>62</v>
@@ -7459,21 +7459,21 @@
       <c r="Z56" s="59"/>
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A57" s="138" t="s">
+      <c r="A57" s="139" t="s">
         <v>216</v>
       </c>
-      <c r="B57" s="139"/>
-      <c r="C57" s="139"/>
-      <c r="D57" s="139"/>
-      <c r="E57" s="144"/>
+      <c r="B57" s="140"/>
+      <c r="C57" s="140"/>
+      <c r="D57" s="140"/>
+      <c r="E57" s="143"/>
       <c r="Z57" s="59"/>
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A58" s="135" t="s">
+      <c r="A58" s="132" t="s">
         <v>215</v>
       </c>
-      <c r="B58" s="136"/>
-      <c r="C58" s="136"/>
+      <c r="B58" s="133"/>
+      <c r="C58" s="133"/>
       <c r="D58" s="82">
         <f>HLOOKUP($E$45,$18:$43,23)</f>
         <v>317.5</v>
@@ -7483,11 +7483,11 @@
       </c>
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A59" s="138" t="s">
+      <c r="A59" s="139" t="s">
         <v>164</v>
       </c>
-      <c r="B59" s="139"/>
-      <c r="C59" s="139"/>
+      <c r="B59" s="140"/>
+      <c r="C59" s="140"/>
       <c r="D59" s="75">
         <f>HLOOKUP($E$45,$18:$43,24)</f>
         <v>321</v>
@@ -7497,11 +7497,11 @@
       </c>
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A60" s="138" t="s">
+      <c r="A60" s="139" t="s">
         <v>284</v>
       </c>
-      <c r="B60" s="139"/>
-      <c r="C60" s="139"/>
+      <c r="B60" s="140"/>
+      <c r="C60" s="140"/>
       <c r="D60" s="75">
         <f>HLOOKUP($E$45,$18:$43,25)</f>
         <v>309.75</v>
@@ -7511,11 +7511,11 @@
       </c>
     </row>
     <row r="61" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A61" s="142" t="s">
+      <c r="A61" s="141" t="s">
         <v>165</v>
       </c>
-      <c r="B61" s="143"/>
-      <c r="C61" s="143"/>
+      <c r="B61" s="142"/>
+      <c r="C61" s="142"/>
       <c r="D61" s="80">
         <f>HLOOKUP($E$45,$18:$43,26)</f>
         <v>57</v>
@@ -7526,71 +7526,30 @@
     </row>
   </sheetData>
   <mergeCells count="113">
-    <mergeCell ref="N35:S35"/>
-    <mergeCell ref="N36:Q36"/>
-    <mergeCell ref="U41:X41"/>
-    <mergeCell ref="U42:X42"/>
-    <mergeCell ref="U43:X43"/>
-    <mergeCell ref="U27:X27"/>
-    <mergeCell ref="U28:X28"/>
-    <mergeCell ref="U29:X29"/>
-    <mergeCell ref="U30:X30"/>
-    <mergeCell ref="U31:X31"/>
-    <mergeCell ref="U32:X32"/>
-    <mergeCell ref="U33:X33"/>
-    <mergeCell ref="U34:X34"/>
-    <mergeCell ref="U35:Z35"/>
-    <mergeCell ref="U36:X36"/>
-    <mergeCell ref="U37:X37"/>
-    <mergeCell ref="U38:X38"/>
-    <mergeCell ref="U39:X39"/>
-    <mergeCell ref="U40:X40"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="N18:Q18"/>
-    <mergeCell ref="N19:Q19"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="N20:Q20"/>
-    <mergeCell ref="N21:Q21"/>
-    <mergeCell ref="N22:Q22"/>
-    <mergeCell ref="N23:Q23"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="N43:Q43"/>
+    <mergeCell ref="G31:J31"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="G34:J34"/>
+    <mergeCell ref="G35:L35"/>
+    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="G40:J40"/>
+    <mergeCell ref="G41:J41"/>
+    <mergeCell ref="G42:J42"/>
+    <mergeCell ref="N37:Q37"/>
+    <mergeCell ref="N38:Q38"/>
+    <mergeCell ref="N39:Q39"/>
+    <mergeCell ref="N40:Q40"/>
+    <mergeCell ref="N41:Q41"/>
+    <mergeCell ref="N42:Q42"/>
+    <mergeCell ref="N25:Q25"/>
+    <mergeCell ref="G43:J43"/>
+    <mergeCell ref="G36:J36"/>
+    <mergeCell ref="G37:J37"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="N32:Q32"/>
     <mergeCell ref="A45:D45"/>
     <mergeCell ref="G26:L26"/>
     <mergeCell ref="G27:J27"/>
@@ -7615,30 +7574,71 @@
     <mergeCell ref="N28:Q28"/>
     <mergeCell ref="U23:X23"/>
     <mergeCell ref="N24:Q24"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="N43:Q43"/>
-    <mergeCell ref="G31:J31"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="G33:J33"/>
-    <mergeCell ref="G34:J34"/>
-    <mergeCell ref="G35:L35"/>
-    <mergeCell ref="G39:J39"/>
-    <mergeCell ref="G40:J40"/>
-    <mergeCell ref="G41:J41"/>
-    <mergeCell ref="G42:J42"/>
-    <mergeCell ref="N37:Q37"/>
-    <mergeCell ref="N38:Q38"/>
-    <mergeCell ref="N39:Q39"/>
-    <mergeCell ref="N40:Q40"/>
-    <mergeCell ref="N41:Q41"/>
-    <mergeCell ref="N42:Q42"/>
-    <mergeCell ref="N25:Q25"/>
-    <mergeCell ref="G43:J43"/>
-    <mergeCell ref="G36:J36"/>
-    <mergeCell ref="G37:J37"/>
-    <mergeCell ref="G38:J38"/>
-    <mergeCell ref="N32:Q32"/>
+    <mergeCell ref="K2:Q2"/>
+    <mergeCell ref="N18:Q18"/>
+    <mergeCell ref="N19:Q19"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="N20:Q20"/>
+    <mergeCell ref="N21:Q21"/>
+    <mergeCell ref="N22:Q22"/>
+    <mergeCell ref="N23:Q23"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="N35:S35"/>
+    <mergeCell ref="N36:Q36"/>
+    <mergeCell ref="U41:X41"/>
+    <mergeCell ref="U42:X42"/>
+    <mergeCell ref="U43:X43"/>
+    <mergeCell ref="U27:X27"/>
+    <mergeCell ref="U28:X28"/>
+    <mergeCell ref="U29:X29"/>
+    <mergeCell ref="U30:X30"/>
+    <mergeCell ref="U31:X31"/>
+    <mergeCell ref="U32:X32"/>
+    <mergeCell ref="U33:X33"/>
+    <mergeCell ref="U34:X34"/>
+    <mergeCell ref="U35:Z35"/>
+    <mergeCell ref="U36:X36"/>
+    <mergeCell ref="U37:X37"/>
+    <mergeCell ref="U38:X38"/>
+    <mergeCell ref="U39:X39"/>
+    <mergeCell ref="U40:X40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7653,22 +7653,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="118" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A2" s="93" t="s">
+      <c r="A2" s="94" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="93"/>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
       <c r="E2" s="1">
         <f>Передача!$E$9</f>
         <v>300</v>
@@ -7681,12 +7681,12 @@
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
       <c r="E3" s="16">
         <f>Передача!$E$10</f>
         <v>3</v>
@@ -7694,45 +7694,45 @@
       <c r="F3" s="54" t="s">
         <v>134</v>
       </c>
-      <c r="J3" s="93" t="s">
+      <c r="J3" s="94" t="s">
         <v>224</v>
       </c>
-      <c r="K3" s="93"/>
-      <c r="L3" s="93"/>
-      <c r="M3" s="93"/>
-      <c r="N3" s="93"/>
-      <c r="T3" s="126" t="s">
+      <c r="K3" s="94"/>
+      <c r="L3" s="94"/>
+      <c r="M3" s="94"/>
+      <c r="N3" s="94"/>
+      <c r="T3" s="118" t="s">
         <v>160</v>
       </c>
-      <c r="U3" s="126"/>
-      <c r="V3" s="126"/>
-      <c r="W3" s="126"/>
-      <c r="X3" s="126" t="s">
+      <c r="U3" s="118"/>
+      <c r="V3" s="118"/>
+      <c r="W3" s="118"/>
+      <c r="X3" s="118" t="s">
         <v>187</v>
       </c>
-      <c r="Y3" s="126"/>
-      <c r="Z3" s="126" t="s">
+      <c r="Y3" s="118"/>
+      <c r="Z3" s="118" t="s">
         <v>176</v>
       </c>
-      <c r="AA3" s="126"/>
+      <c r="AA3" s="118"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A4" s="93" t="s">
+      <c r="A4" s="94" t="s">
         <v>209</v>
       </c>
-      <c r="B4" s="93"/>
-      <c r="C4" s="93"/>
-      <c r="D4" s="93"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
       <c r="E4" s="47" t="str">
         <f>Передача!$E$11</f>
         <v>?</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="J4" s="132" t="s">
+      <c r="J4" s="136" t="s">
         <v>0</v>
       </c>
-      <c r="K4" s="132"/>
-      <c r="L4" s="132"/>
+      <c r="K4" s="136"/>
+      <c r="L4" s="136"/>
       <c r="M4" s="78">
         <f>Передача!$D$49</f>
         <v>2016</v>
@@ -7740,38 +7740,38 @@
       <c r="N4" s="75" t="s">
         <v>159</v>
       </c>
-      <c r="T4" s="126" t="s">
+      <c r="T4" s="118" t="s">
         <v>250</v>
       </c>
-      <c r="U4" s="126"/>
-      <c r="V4" s="126"/>
-      <c r="W4" s="126"/>
-      <c r="X4" s="126">
+      <c r="U4" s="118"/>
+      <c r="V4" s="118"/>
+      <c r="W4" s="118"/>
+      <c r="X4" s="118">
         <v>0</v>
       </c>
-      <c r="Y4" s="126"/>
-      <c r="Z4" s="126">
+      <c r="Y4" s="118"/>
+      <c r="Z4" s="118">
         <f ca="1">E19</f>
         <v>56</v>
       </c>
-      <c r="AA4" s="126"/>
+      <c r="AA4" s="118"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A5" s="125" t="s">
+      <c r="A5" s="103" t="s">
         <v>211</v>
       </c>
-      <c r="B5" s="125"/>
-      <c r="C5" s="125"/>
-      <c r="D5" s="125"/>
+      <c r="B5" s="103"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
       <c r="E5" s="70" t="s">
         <v>210</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="J5" s="132" t="s">
+      <c r="J5" s="136" t="s">
         <v>157</v>
       </c>
-      <c r="K5" s="132"/>
-      <c r="L5" s="132"/>
+      <c r="K5" s="136"/>
+      <c r="L5" s="136"/>
       <c r="M5" s="78">
         <f>Передача!$D$50</f>
         <v>734</v>
@@ -7779,30 +7779,30 @@
       <c r="N5" s="75" t="s">
         <v>159</v>
       </c>
-      <c r="T5" s="126" t="s">
+      <c r="T5" s="118" t="s">
         <v>252</v>
       </c>
-      <c r="U5" s="126"/>
-      <c r="V5" s="126"/>
-      <c r="W5" s="126"/>
-      <c r="X5" s="126">
+      <c r="U5" s="118"/>
+      <c r="V5" s="118"/>
+      <c r="W5" s="118"/>
+      <c r="X5" s="118">
         <f ca="1">E19</f>
         <v>56</v>
       </c>
-      <c r="Y5" s="126"/>
-      <c r="Z5" s="126">
+      <c r="Y5" s="118"/>
+      <c r="Z5" s="118">
         <f>E18</f>
         <v>80</v>
       </c>
-      <c r="AA5" s="126"/>
+      <c r="AA5" s="118"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A6" s="126" t="s">
+      <c r="A6" s="118" t="s">
         <v>155</v>
       </c>
-      <c r="B6" s="126"/>
-      <c r="C6" s="126"/>
-      <c r="D6" s="126"/>
+      <c r="B6" s="118"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
       <c r="E6">
         <f>Передача!$D$47</f>
         <v>2.5</v>
@@ -7810,11 +7810,11 @@
       <c r="F6" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="132" t="s">
+      <c r="J6" s="136" t="s">
         <v>158</v>
       </c>
-      <c r="K6" s="132"/>
-      <c r="L6" s="132"/>
+      <c r="K6" s="136"/>
+      <c r="L6" s="136"/>
       <c r="M6" s="78">
         <f>Передача!$D$51</f>
         <v>0</v>
@@ -7822,28 +7822,28 @@
       <c r="N6" s="75" t="s">
         <v>159</v>
       </c>
-      <c r="T6" s="126" t="s">
+      <c r="T6" s="118" t="s">
         <v>236</v>
       </c>
-      <c r="U6" s="126"/>
-      <c r="V6" s="126"/>
-      <c r="W6" s="126"/>
-      <c r="X6" s="147">
+      <c r="U6" s="118"/>
+      <c r="V6" s="118"/>
+      <c r="W6" s="118"/>
+      <c r="X6" s="148">
         <v>0.3</v>
       </c>
-      <c r="Y6" s="147"/>
-      <c r="Z6" s="147">
+      <c r="Y6" s="148"/>
+      <c r="Z6" s="148">
         <v>0.3</v>
       </c>
-      <c r="AA6" s="147"/>
+      <c r="AA6" s="148"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="118" t="s">
         <v>213</v>
       </c>
-      <c r="B7" s="126"/>
-      <c r="C7" s="126"/>
-      <c r="D7" s="126"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
       <c r="E7">
         <f>Передача!$D$58</f>
         <v>317.5</v>
@@ -7851,30 +7851,30 @@
       <c r="F7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="T7" s="126" t="s">
+      <c r="T7" s="118" t="s">
         <v>247</v>
       </c>
-      <c r="U7" s="126"/>
-      <c r="V7" s="126"/>
-      <c r="W7" s="126"/>
-      <c r="X7" s="147">
+      <c r="U7" s="118"/>
+      <c r="V7" s="118"/>
+      <c r="W7" s="118"/>
+      <c r="X7" s="148">
         <f>2.1*10^5</f>
         <v>210000</v>
       </c>
-      <c r="Y7" s="147"/>
-      <c r="Z7" s="147">
+      <c r="Y7" s="148"/>
+      <c r="Z7" s="148">
         <f>2.1*10^5</f>
         <v>210000</v>
       </c>
-      <c r="AA7" s="147"/>
+      <c r="AA7" s="148"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A8" s="93" t="s">
+      <c r="A8" s="94" t="s">
         <v>184</v>
       </c>
-      <c r="B8" s="93"/>
-      <c r="C8" s="93"/>
-      <c r="D8" s="93"/>
+      <c r="B8" s="94"/>
+      <c r="C8" s="94"/>
+      <c r="D8" s="94"/>
       <c r="E8" s="1">
         <f>Передача!$D$59</f>
         <v>321</v>
@@ -7882,35 +7882,35 @@
       <c r="F8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="146" t="s">
+      <c r="J8" s="147" t="s">
         <v>253</v>
       </c>
-      <c r="K8" s="146"/>
-      <c r="L8" s="146"/>
-      <c r="M8" s="146"/>
-      <c r="N8" s="146"/>
-      <c r="T8" s="126" t="s">
+      <c r="K8" s="147"/>
+      <c r="L8" s="147"/>
+      <c r="M8" s="147"/>
+      <c r="N8" s="147"/>
+      <c r="T8" s="118" t="s">
         <v>246</v>
       </c>
-      <c r="U8" s="126"/>
-      <c r="V8" s="126"/>
-      <c r="W8" s="126"/>
-      <c r="X8" s="147">
+      <c r="U8" s="118"/>
+      <c r="V8" s="118"/>
+      <c r="W8" s="118"/>
+      <c r="X8" s="148">
         <v>330</v>
       </c>
-      <c r="Y8" s="147"/>
-      <c r="Z8" s="147">
+      <c r="Y8" s="148"/>
+      <c r="Z8" s="148">
         <v>330</v>
       </c>
-      <c r="AA8" s="147"/>
+      <c r="AA8" s="148"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A9" s="93" t="s">
+      <c r="A9" s="94" t="s">
         <v>175</v>
       </c>
-      <c r="B9" s="93"/>
-      <c r="C9" s="93"/>
-      <c r="D9" s="93"/>
+      <c r="B9" s="94"/>
+      <c r="C9" s="94"/>
+      <c r="D9" s="94"/>
       <c r="E9" s="1">
         <f>Передача!$D$60</f>
         <v>309.75</v>
@@ -7918,11 +7918,11 @@
       <c r="F9" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="126" t="s">
+      <c r="J9" s="118" t="s">
         <v>172</v>
       </c>
-      <c r="K9" s="126"/>
-      <c r="L9" s="126"/>
+      <c r="K9" s="118"/>
+      <c r="L9" s="118"/>
       <c r="M9">
         <f ca="1">Передача!$E$5</f>
         <v>339.37130342425513</v>
@@ -7930,30 +7930,30 @@
       <c r="N9" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="T9" s="126" t="s">
+      <c r="T9" s="118" t="s">
         <v>248</v>
       </c>
-      <c r="U9" s="126"/>
-      <c r="V9" s="126"/>
-      <c r="W9" s="126"/>
-      <c r="X9" s="126">
+      <c r="U9" s="118"/>
+      <c r="V9" s="118"/>
+      <c r="W9" s="118"/>
+      <c r="X9" s="118">
         <f ca="1">(X5*X5+X4*X4)/(X5*X5-X4*X4)-X6</f>
         <v>0.7</v>
       </c>
-      <c r="Y9" s="126"/>
-      <c r="Z9" s="126">
+      <c r="Y9" s="118"/>
+      <c r="Z9" s="118">
         <f ca="1">(Z5*Z5+Z4*Z4)/(Z5*Z5-Z4*Z4)+Z6</f>
         <v>3.22156862745098</v>
       </c>
-      <c r="AA9" s="126"/>
+      <c r="AA9" s="118"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A10" s="126" t="s">
+      <c r="A10" s="118" t="s">
         <v>165</v>
       </c>
-      <c r="B10" s="126"/>
-      <c r="C10" s="126"/>
-      <c r="D10" s="126"/>
+      <c r="B10" s="118"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="118"/>
       <c r="E10">
         <f>Передача!$D$61</f>
         <v>57</v>
@@ -7961,41 +7961,41 @@
       <c r="F10" t="s">
         <v>16</v>
       </c>
-      <c r="J10" s="126" t="s">
+      <c r="J10" s="118" t="s">
         <v>227</v>
       </c>
-      <c r="K10" s="126"/>
-      <c r="L10" s="126"/>
+      <c r="K10" s="118"/>
+      <c r="L10" s="118"/>
       <c r="M10" s="52">
         <v>3</v>
       </c>
       <c r="N10" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="T10" s="126" t="s">
+      <c r="T10" s="118" t="s">
         <v>249</v>
       </c>
-      <c r="U10" s="126"/>
-      <c r="V10" s="126"/>
-      <c r="W10" s="126"/>
-      <c r="X10" s="126">
+      <c r="U10" s="118"/>
+      <c r="V10" s="118"/>
+      <c r="W10" s="118"/>
+      <c r="X10" s="118">
         <f ca="1">0.5*X8*(1-(X4*X4/X5/X5))</f>
         <v>165</v>
       </c>
-      <c r="Y10" s="126"/>
-      <c r="Z10" s="126">
+      <c r="Y10" s="118"/>
+      <c r="Z10" s="118">
         <f ca="1">0.5*Z8*(1-(Z4*Z4/Z5/Z5))</f>
         <v>84.15</v>
       </c>
-      <c r="AA10" s="126"/>
+      <c r="AA10" s="118"/>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A11" s="126" t="s">
+      <c r="A11" s="118" t="s">
         <v>217</v>
       </c>
-      <c r="B11" s="126"/>
-      <c r="C11" s="126"/>
-      <c r="D11" s="126"/>
+      <c r="B11" s="118"/>
+      <c r="C11" s="118"/>
+      <c r="D11" s="118"/>
       <c r="E11">
         <f>_xlfn.MINIFS($32:$32,$31:$31,"&gt;="&amp;E7)</f>
         <v>5</v>
@@ -8003,11 +8003,11 @@
       <c r="F11" t="s">
         <v>16</v>
       </c>
-      <c r="J11" s="126" t="s">
+      <c r="J11" s="118" t="s">
         <v>229</v>
       </c>
-      <c r="K11" s="126"/>
-      <c r="L11" s="126"/>
+      <c r="K11" s="118"/>
+      <c r="L11" s="118"/>
       <c r="M11" s="52">
         <f>E35</f>
         <v>0.08</v>
@@ -8017,23 +8017,23 @@
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A12" s="126" t="s">
+      <c r="A12" s="118" t="s">
         <v>218</v>
       </c>
-      <c r="B12" s="126"/>
-      <c r="C12" s="126"/>
-      <c r="D12" s="126"/>
+      <c r="B12" s="118"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="118"/>
       <c r="E12" t="s">
         <v>219</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
       </c>
-      <c r="J12" s="126" t="s">
+      <c r="J12" s="118" t="s">
         <v>231</v>
       </c>
-      <c r="K12" s="126"/>
-      <c r="L12" s="126"/>
+      <c r="K12" s="118"/>
+      <c r="L12" s="118"/>
       <c r="M12" s="25">
         <f>E17</f>
         <v>57</v>
@@ -8046,23 +8046,23 @@
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A13" s="148" t="s">
+      <c r="A13" s="146" t="s">
         <v>220</v>
       </c>
-      <c r="B13" s="126"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="126"/>
+      <c r="B13" s="118"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="118"/>
       <c r="E13" t="s">
         <v>222</v>
       </c>
       <c r="F13" t="s">
         <v>221</v>
       </c>
-      <c r="J13" s="126" t="s">
+      <c r="J13" s="118" t="s">
         <v>228</v>
       </c>
-      <c r="K13" s="126"/>
-      <c r="L13" s="126"/>
+      <c r="K13" s="118"/>
+      <c r="L13" s="118"/>
       <c r="M13">
         <f ca="1">2000*M10*M9/(PI()*E19*E19*M12*M11)</f>
         <v>45.324768799937637</v>
@@ -8072,12 +8072,12 @@
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A14" s="126" t="s">
+      <c r="A14" s="118" t="s">
         <v>225</v>
       </c>
-      <c r="B14" s="126"/>
-      <c r="C14" s="126"/>
-      <c r="D14" s="126"/>
+      <c r="B14" s="118"/>
+      <c r="C14" s="118"/>
+      <c r="D14" s="118"/>
       <c r="E14">
         <f>2.2*E6+0.05*E10</f>
         <v>8.35</v>
@@ -8085,11 +8085,11 @@
       <c r="F14" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="126" t="s">
+      <c r="J14" s="118" t="s">
         <v>235</v>
       </c>
-      <c r="K14" s="126"/>
-      <c r="L14" s="126"/>
+      <c r="K14" s="118"/>
+      <c r="L14" s="118"/>
       <c r="M14">
         <f ca="1">1000*M13*E19*(X9/X7+Z9/Z7)</f>
         <v>47.398451032614524</v>
@@ -8099,12 +8099,12 @@
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A15" s="126" t="s">
+      <c r="A15" s="118" t="s">
         <v>223</v>
       </c>
-      <c r="B15" s="126"/>
-      <c r="C15" s="126"/>
-      <c r="D15" s="126"/>
+      <c r="B15" s="118"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="118"/>
       <c r="E15">
         <f ca="1">(E18-E19)/2</f>
         <v>12</v>
@@ -8112,11 +8112,11 @@
       <c r="F15" t="s">
         <v>16</v>
       </c>
-      <c r="J15" s="126" t="s">
+      <c r="J15" s="118" t="s">
         <v>242</v>
       </c>
-      <c r="K15" s="126"/>
-      <c r="L15" s="126"/>
+      <c r="K15" s="118"/>
+      <c r="L15" s="118"/>
       <c r="M15">
         <f>5.5*(E20+E22)</f>
         <v>0</v>
@@ -8129,20 +8129,20 @@
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A16" s="126" t="s">
+      <c r="A16" s="118" t="s">
         <v>240</v>
       </c>
-      <c r="B16" s="126"/>
-      <c r="C16" s="126"/>
-      <c r="D16" s="126"/>
+      <c r="B16" s="118"/>
+      <c r="C16" s="118"/>
+      <c r="D16" s="118"/>
       <c r="E16" s="52">
         <v>1</v>
       </c>
-      <c r="J16" s="126" t="s">
+      <c r="J16" s="118" t="s">
         <v>243</v>
       </c>
-      <c r="K16" s="126"/>
-      <c r="L16" s="126"/>
+      <c r="K16" s="118"/>
+      <c r="L16" s="118"/>
       <c r="N16" t="s">
         <v>241</v>
       </c>
@@ -8151,12 +8151,12 @@
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="126" t="s">
+      <c r="A17" s="118" t="s">
         <v>238</v>
       </c>
-      <c r="B17" s="126"/>
-      <c r="C17" s="126"/>
-      <c r="D17" s="126"/>
+      <c r="B17" s="118"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="118"/>
       <c r="E17">
         <f>E10*E16</f>
         <v>57</v>
@@ -8164,11 +8164,11 @@
       <c r="F17" t="s">
         <v>16</v>
       </c>
-      <c r="J17" s="126" t="s">
+      <c r="J17" s="118" t="s">
         <v>244</v>
       </c>
-      <c r="K17" s="126"/>
-      <c r="L17" s="126"/>
+      <c r="K17" s="118"/>
+      <c r="L17" s="118"/>
       <c r="M17" s="25">
         <f ca="1">SUM(M14:M16)</f>
         <v>47.398451032614524</v>
@@ -8178,23 +8178,23 @@
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="126" t="s">
+      <c r="A18" s="118" t="s">
         <v>239</v>
       </c>
-      <c r="B18" s="126"/>
-      <c r="C18" s="126"/>
-      <c r="D18" s="126"/>
+      <c r="B18" s="118"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="118"/>
       <c r="E18" s="52">
         <v>80</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
       </c>
-      <c r="J18" s="126" t="s">
+      <c r="J18" s="118" t="s">
         <v>251</v>
       </c>
-      <c r="K18" s="126"/>
-      <c r="L18" s="126"/>
+      <c r="K18" s="118"/>
+      <c r="L18" s="118"/>
       <c r="M18">
         <f ca="1">MAX(X10:AA10)*M14/M13</f>
         <v>172.54901960784315</v>
@@ -8204,12 +8204,12 @@
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="146" t="s">
+      <c r="A19" s="147" t="s">
         <v>237</v>
       </c>
-      <c r="B19" s="146"/>
-      <c r="C19" s="146"/>
-      <c r="D19" s="146"/>
+      <c r="B19" s="147"/>
+      <c r="C19" s="147"/>
+      <c r="D19" s="147"/>
       <c r="E19" s="77">
         <f ca="1">Вал!$S$18</f>
         <v>56</v>
@@ -8217,11 +8217,11 @@
       <c r="F19" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="J19" s="126" t="s">
+      <c r="J19" s="118" t="s">
         <v>245</v>
       </c>
-      <c r="K19" s="126"/>
-      <c r="L19" s="126"/>
+      <c r="K19" s="118"/>
+      <c r="L19" s="118"/>
       <c r="M19" s="90">
         <f ca="1">M18+M15</f>
         <v>172.54901960784315</v>
@@ -8231,12 +8231,12 @@
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="126" t="s">
+      <c r="A20" s="118" t="s">
         <v>292</v>
       </c>
-      <c r="B20" s="126"/>
-      <c r="C20" s="126"/>
-      <c r="D20" s="126"/>
+      <c r="B20" s="118"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="118"/>
       <c r="E20" s="52"/>
       <c r="F20" s="77" t="s">
         <v>241</v>
@@ -8246,23 +8246,23 @@
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="126" t="s">
+      <c r="A21" s="118" t="s">
         <v>293</v>
       </c>
-      <c r="B21" s="126"/>
-      <c r="C21" s="126"/>
-      <c r="D21" s="126"/>
+      <c r="B21" s="118"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="118"/>
       <c r="E21" s="92" t="s">
         <v>294</v>
       </c>
       <c r="F21" t="s">
         <v>16</v>
       </c>
-      <c r="J21" s="126" t="s">
+      <c r="J21" s="118" t="s">
         <v>264</v>
       </c>
-      <c r="K21" s="126"/>
-      <c r="L21" s="126"/>
+      <c r="K21" s="118"/>
+      <c r="L21" s="118"/>
       <c r="M21">
         <v>90</v>
       </c>
@@ -8274,32 +8274,32 @@
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="126" t="s">
+      <c r="A22" s="118" t="s">
         <v>295</v>
       </c>
-      <c r="B22" s="126"/>
-      <c r="C22" s="126"/>
-      <c r="D22" s="126"/>
+      <c r="B22" s="118"/>
+      <c r="C22" s="118"/>
+      <c r="D22" s="118"/>
       <c r="E22" s="52"/>
       <c r="F22" t="s">
         <v>241</v>
       </c>
-      <c r="J22" s="126" t="s">
+      <c r="J22" s="118" t="s">
         <v>256</v>
       </c>
-      <c r="K22" s="126"/>
-      <c r="L22" s="126"/>
+      <c r="K22" s="118"/>
+      <c r="L22" s="118"/>
       <c r="M22">
         <v>0.2</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="126" t="s">
+      <c r="A23" s="118" t="s">
         <v>296</v>
       </c>
-      <c r="B23" s="126"/>
-      <c r="C23" s="126"/>
-      <c r="D23" s="126"/>
+      <c r="B23" s="118"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="118"/>
       <c r="E23">
         <f ca="1">MAX(E10/4,(E15+E14)/2)</f>
         <v>14.25</v>
@@ -8307,11 +8307,11 @@
       <c r="F23" t="s">
         <v>16</v>
       </c>
-      <c r="J23" s="126" t="s">
+      <c r="J23" s="118" t="s">
         <v>255</v>
       </c>
-      <c r="K23" s="126"/>
-      <c r="L23" s="126"/>
+      <c r="K23" s="118"/>
+      <c r="L23" s="118"/>
       <c r="M23">
         <f ca="1">PI()*E19*M12*(M21-M15)*M22/1000</f>
         <v>180.50334750465515</v>
@@ -8321,10 +8321,10 @@
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="126" t="s">
+      <c r="A30" s="118" t="s">
         <v>181</v>
       </c>
-      <c r="B30" s="126"/>
+      <c r="B30" s="118"/>
       <c r="C30">
         <v>20</v>
       </c>
@@ -8351,10 +8351,10 @@
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="126" t="s">
+      <c r="A31" s="118" t="s">
         <v>182</v>
       </c>
-      <c r="B31" s="126"/>
+      <c r="B31" s="118"/>
       <c r="C31">
         <v>30</v>
       </c>
@@ -8381,10 +8381,10 @@
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="126" t="s">
+      <c r="A32" s="118" t="s">
         <v>212</v>
       </c>
-      <c r="B32" s="126"/>
+      <c r="B32" s="118"/>
       <c r="C32">
         <v>1</v>
       </c>
@@ -8411,170 +8411,97 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="126" t="s">
+      <c r="A34" s="118" t="s">
         <v>285</v>
       </c>
-      <c r="B34" s="126"/>
-      <c r="C34" s="126" t="s">
+      <c r="B34" s="118"/>
+      <c r="C34" s="118" t="s">
         <v>286</v>
       </c>
-      <c r="D34" s="126"/>
-      <c r="E34" s="126" t="s">
+      <c r="D34" s="118"/>
+      <c r="E34" s="118" t="s">
         <v>290</v>
       </c>
-      <c r="F34" s="126"/>
-      <c r="G34" s="126" t="s">
+      <c r="F34" s="118"/>
+      <c r="G34" s="118" t="s">
         <v>291</v>
       </c>
-      <c r="H34" s="126"/>
+      <c r="H34" s="118"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="126" t="s">
+      <c r="A35" s="118" t="s">
         <v>287</v>
       </c>
-      <c r="B35" s="126"/>
-      <c r="C35" s="126" t="s">
+      <c r="B35" s="118"/>
+      <c r="C35" s="118" t="s">
         <v>287</v>
       </c>
-      <c r="D35" s="126"/>
-      <c r="E35" s="126">
+      <c r="D35" s="118"/>
+      <c r="E35" s="118">
         <v>0.08</v>
       </c>
-      <c r="F35" s="126"/>
-      <c r="G35" s="126">
+      <c r="F35" s="118"/>
+      <c r="G35" s="118">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H35" s="126"/>
+      <c r="H35" s="118"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="126" t="s">
+      <c r="A36" s="118" t="s">
         <v>288</v>
       </c>
-      <c r="B36" s="126"/>
-      <c r="C36" s="126" t="s">
+      <c r="B36" s="118"/>
+      <c r="C36" s="118" t="s">
         <v>287</v>
       </c>
-      <c r="D36" s="126"/>
-      <c r="E36" s="126">
+      <c r="D36" s="118"/>
+      <c r="E36" s="118">
         <v>0.08</v>
       </c>
-      <c r="F36" s="126"/>
-      <c r="G36" s="126">
+      <c r="F36" s="118"/>
+      <c r="G36" s="118">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H36" s="126"/>
+      <c r="H36" s="118"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="126" t="s">
+      <c r="A37" s="118" t="s">
         <v>287</v>
       </c>
-      <c r="B37" s="126"/>
-      <c r="C37" s="126" t="s">
+      <c r="B37" s="118"/>
+      <c r="C37" s="118" t="s">
         <v>289</v>
       </c>
-      <c r="D37" s="126"/>
-      <c r="E37" s="126">
+      <c r="D37" s="118"/>
+      <c r="E37" s="118">
         <v>0.05</v>
       </c>
-      <c r="F37" s="126"/>
-      <c r="G37" s="126">
+      <c r="F37" s="118"/>
+      <c r="G37" s="118">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="H37" s="126"/>
+      <c r="H37" s="118"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="126" t="s">
+      <c r="A38" s="118" t="s">
         <v>288</v>
       </c>
-      <c r="B38" s="126"/>
-      <c r="C38" s="126" t="s">
+      <c r="B38" s="118"/>
+      <c r="C38" s="118" t="s">
         <v>289</v>
       </c>
-      <c r="D38" s="126"/>
-      <c r="E38" s="126">
+      <c r="D38" s="118"/>
+      <c r="E38" s="118">
         <v>0.05</v>
       </c>
-      <c r="F38" s="126"/>
-      <c r="G38" s="126">
+      <c r="F38" s="118"/>
+      <c r="G38" s="118">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="H38" s="126"/>
+      <c r="H38" s="118"/>
     </row>
   </sheetData>
   <mergeCells count="89">
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="T6:W6"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="T7:W7"/>
-    <mergeCell ref="T8:W8"/>
-    <mergeCell ref="T9:W9"/>
-    <mergeCell ref="T10:W10"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="X10:Y10"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="T3:W3"/>
-    <mergeCell ref="T4:W4"/>
-    <mergeCell ref="T5:W5"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="X5:Y5"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="Z5:AA5"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="Z8:AA8"/>
     <mergeCell ref="Z10:AA10"/>
     <mergeCell ref="J8:N8"/>
     <mergeCell ref="J23:L23"/>
@@ -8591,6 +8518,79 @@
     <mergeCell ref="J13:L13"/>
     <mergeCell ref="J11:L11"/>
     <mergeCell ref="J12:L12"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="Z8:AA8"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="T3:W3"/>
+    <mergeCell ref="T4:W4"/>
+    <mergeCell ref="T5:W5"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="T7:W7"/>
+    <mergeCell ref="T8:W8"/>
+    <mergeCell ref="T9:W9"/>
+    <mergeCell ref="T10:W10"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="T6:W6"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="G38:H38"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8607,12 +8607,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="126" t="s">
+      <c r="A2" s="118" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="126"/>
-      <c r="C2" s="126"/>
-      <c r="D2" s="126"/>
+      <c r="B2" s="118"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
       <c r="E2">
         <f>Передача!$D$46</f>
         <v>180</v>
@@ -8622,12 +8622,12 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="126" t="s">
+      <c r="A3" s="118" t="s">
         <v>202</v>
       </c>
-      <c r="B3" s="126"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="126"/>
+      <c r="B3" s="118"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3">
         <f>Передача!$D$55</f>
         <v>37.75</v>
@@ -8637,12 +8637,12 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="126" t="s">
+      <c r="A4" s="118" t="s">
         <v>177</v>
       </c>
-      <c r="B4" s="126"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="126"/>
+      <c r="B4" s="118"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="118"/>
       <c r="E4">
         <f>Передача!$D$56</f>
         <v>62</v>
@@ -8652,12 +8652,12 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="126" t="s">
+      <c r="A5" s="118" t="s">
         <v>203</v>
       </c>
-      <c r="B5" s="126"/>
-      <c r="C5" s="126"/>
-      <c r="D5" s="126"/>
+      <c r="B5" s="118"/>
+      <c r="C5" s="118"/>
+      <c r="D5" s="118"/>
       <c r="E5">
         <f>Передача!$D$60</f>
         <v>309.75</v>
@@ -8667,12 +8667,12 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="126" t="s">
+      <c r="A6" s="118" t="s">
         <v>178</v>
       </c>
-      <c r="B6" s="126"/>
-      <c r="C6" s="126"/>
-      <c r="D6" s="126"/>
+      <c r="B6" s="118"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
       <c r="E6">
         <f>Передача!$D$61</f>
         <v>57</v>
@@ -8682,12 +8682,12 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="118" t="s">
         <v>201</v>
       </c>
-      <c r="B7" s="126"/>
-      <c r="C7" s="126"/>
-      <c r="D7" s="126"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
       <c r="E7">
         <f>E2+E3/2+E5/2</f>
         <v>353.75</v>
@@ -8697,12 +8697,12 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="126" t="s">
+      <c r="A8" s="118" t="s">
         <v>200</v>
       </c>
-      <c r="B8" s="126"/>
-      <c r="C8" s="126"/>
-      <c r="D8" s="126"/>
+      <c r="B8" s="118"/>
+      <c r="C8" s="118"/>
+      <c r="D8" s="118"/>
       <c r="E8">
         <f>E7^(1/3)+3</f>
         <v>10.072378298355165</v>
@@ -8712,12 +8712,12 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="126" t="s">
+      <c r="A9" s="118" t="s">
         <v>204</v>
       </c>
-      <c r="B9" s="126"/>
-      <c r="C9" s="126"/>
-      <c r="D9" s="126"/>
+      <c r="B9" s="118"/>
+      <c r="C9" s="118"/>
+      <c r="D9" s="118"/>
       <c r="E9">
         <f>E8*3</f>
         <v>30.217134895065495</v>
@@ -8727,12 +8727,12 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="126" t="s">
+      <c r="A10" s="118" t="s">
         <v>205</v>
       </c>
-      <c r="B10" s="126"/>
-      <c r="C10" s="126"/>
-      <c r="D10" s="126"/>
+      <c r="B10" s="118"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="118"/>
       <c r="E10" s="52">
         <v>4</v>
       </c>
@@ -8741,12 +8741,12 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="126" t="s">
+      <c r="A11" s="118" t="s">
         <v>206</v>
       </c>
-      <c r="B11" s="126"/>
-      <c r="C11" s="126"/>
-      <c r="D11" s="126"/>
+      <c r="B11" s="118"/>
+      <c r="C11" s="118"/>
+      <c r="D11" s="118"/>
       <c r="E11" s="52">
         <v>20</v>
       </c>
@@ -8755,22 +8755,22 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="126" t="s">
+      <c r="A12" s="118" t="s">
         <v>208</v>
       </c>
-      <c r="B12" s="126"/>
-      <c r="C12" s="126"/>
-      <c r="D12" s="126"/>
-      <c r="E12" s="126"/>
-      <c r="F12" s="126"/>
+      <c r="B12" s="118"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="118"/>
+      <c r="F12" s="118"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="126" t="s">
+      <c r="A13" s="118" t="s">
         <v>207</v>
       </c>
-      <c r="B13" s="126"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="126"/>
+      <c r="B13" s="118"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="118"/>
       <c r="E13">
         <f>E7+2*E8+E10*2+E11*2</f>
         <v>421.89475659671035</v>
@@ -8780,12 +8780,12 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="126" t="s">
+      <c r="A14" s="118" t="s">
         <v>165</v>
       </c>
-      <c r="B14" s="126"/>
-      <c r="C14" s="126"/>
-      <c r="D14" s="126"/>
+      <c r="B14" s="118"/>
+      <c r="C14" s="118"/>
+      <c r="D14" s="118"/>
       <c r="E14">
         <f>E4+2*E8+2*E10</f>
         <v>90.144756596710323</v>
@@ -8795,12 +8795,12 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="126" t="s">
+      <c r="A15" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="126"/>
-      <c r="C15" s="126"/>
-      <c r="D15" s="126"/>
+      <c r="B15" s="118"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="118"/>
       <c r="E15">
         <f>E5+E8+E9+2*E10</f>
         <v>358.03951319342065</v>
@@ -8815,22 +8815,22 @@
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A17" s="126" t="s">
+      <c r="A17" s="118" t="s">
         <v>335</v>
       </c>
-      <c r="B17" s="126"/>
-      <c r="C17" s="126"/>
-      <c r="D17" s="126"/>
-      <c r="E17" s="126"/>
-      <c r="F17" s="126"/>
+      <c r="B17" s="118"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="118"/>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A18" s="126" t="s">
+      <c r="A18" s="118" t="s">
         <v>331</v>
       </c>
-      <c r="B18" s="126"/>
-      <c r="C18" s="126"/>
-      <c r="D18" s="126"/>
+      <c r="B18" s="118"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="118"/>
       <c r="E18">
         <f>Вал!$K$4*PI()/30</f>
         <v>150.79644737231007</v>
@@ -8840,12 +8840,12 @@
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A19" s="126" t="s">
+      <c r="A19" s="118" t="s">
         <v>332</v>
       </c>
-      <c r="B19" s="126"/>
-      <c r="C19" s="126"/>
-      <c r="D19" s="126"/>
+      <c r="B19" s="118"/>
+      <c r="C19" s="118"/>
+      <c r="D19" s="118"/>
       <c r="E19">
         <f>Корпус!$E$18*MAX(Вал!$K$19,Вал!$K$7)/1000</f>
         <v>7.3890259212431939</v>
@@ -8855,12 +8855,12 @@
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A20" s="126" t="s">
+      <c r="A20" s="118" t="s">
         <v>336</v>
       </c>
-      <c r="B20" s="126"/>
-      <c r="C20" s="126"/>
-      <c r="D20" s="126"/>
+      <c r="B20" s="118"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="118"/>
       <c r="E20" s="52">
         <v>504</v>
       </c>
@@ -8869,65 +8869,65 @@
       </c>
       <c r="R20" s="1"/>
       <c r="S20" s="36"/>
-      <c r="T20" s="126" t="s">
+      <c r="T20" s="118" t="s">
         <v>127</v>
       </c>
-      <c r="U20" s="126"/>
-      <c r="V20" s="93" t="s">
+      <c r="U20" s="118"/>
+      <c r="V20" s="94" t="s">
         <v>123</v>
       </c>
-      <c r="W20" s="93"/>
+      <c r="W20" s="94"/>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A21" s="126" t="s">
+      <c r="A21" s="118" t="s">
         <v>338</v>
       </c>
-      <c r="B21" s="126"/>
-      <c r="C21" s="126"/>
-      <c r="D21" s="126"/>
+      <c r="B21" s="118"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="118"/>
       <c r="E21" s="52"/>
       <c r="F21" t="s">
         <v>337</v>
       </c>
-      <c r="R21" s="98" t="s">
+      <c r="R21" s="127" t="s">
         <v>122</v>
       </c>
-      <c r="S21" s="98"/>
-      <c r="T21" s="93"/>
-      <c r="U21" s="93"/>
-      <c r="V21" s="93"/>
-      <c r="W21" s="93"/>
+      <c r="S21" s="127"/>
+      <c r="T21" s="94"/>
+      <c r="U21" s="94"/>
+      <c r="V21" s="94"/>
+      <c r="W21" s="94"/>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A22" s="126" t="s">
+      <c r="A22" s="118" t="s">
         <v>339</v>
       </c>
-      <c r="B22" s="126"/>
-      <c r="C22" s="126"/>
-      <c r="D22" s="126"/>
+      <c r="B22" s="118"/>
+      <c r="C22" s="118"/>
+      <c r="D22" s="118"/>
       <c r="E22" t="s">
         <v>340</v>
       </c>
-      <c r="R22" s="98" t="s">
+      <c r="R22" s="127" t="s">
         <v>124</v>
       </c>
-      <c r="S22" s="98"/>
-      <c r="T22" s="93" t="s">
+      <c r="S22" s="127"/>
+      <c r="T22" s="94" t="s">
         <v>125</v>
       </c>
-      <c r="U22" s="93"/>
-      <c r="V22" s="94" t="s">
+      <c r="U22" s="94"/>
+      <c r="V22" s="106" t="s">
         <v>126</v>
       </c>
-      <c r="W22" s="94"/>
+      <c r="W22" s="106"/>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A23" s="126" t="s">
+      <c r="A23" s="118" t="s">
         <v>341</v>
       </c>
-      <c r="B23" s="126"/>
-      <c r="C23" s="126"/>
-      <c r="D23" s="126"/>
+      <c r="B23" s="118"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="118"/>
       <c r="E23">
         <f>MAX(4*Передача!$D$47,10)</f>
         <v>10</v>
@@ -8960,12 +8960,20 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A3:D3"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="V22:W22"/>
     <mergeCell ref="T22:U22"/>
@@ -8975,20 +8983,12 @@
     <mergeCell ref="V20:W20"/>
     <mergeCell ref="T21:U21"/>
     <mergeCell ref="V21:W21"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A19:D19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -9002,7 +9002,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="126">
+      <c r="A1" s="118">
         <v>1</v>
       </c>
       <c r="B1">
@@ -9011,14 +9011,14 @@
       <c r="D1" s="48"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="126"/>
+      <c r="A2" s="118"/>
       <c r="B2">
         <v>1.05</v>
       </c>
       <c r="D2" s="48"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="126">
+      <c r="A3" s="118">
         <v>1.1000000000000001</v>
       </c>
       <c r="B3">
@@ -9027,14 +9027,14 @@
       <c r="D3" s="48"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="126"/>
+      <c r="A4" s="118"/>
       <c r="B4">
         <v>1.1499999999999999</v>
       </c>
       <c r="D4" s="48"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="126">
+      <c r="A5" s="118">
         <v>1.2</v>
       </c>
       <c r="B5">
@@ -9043,14 +9043,14 @@
       <c r="D5" s="48"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="126"/>
+      <c r="A6" s="118"/>
       <c r="B6">
         <v>1.3</v>
       </c>
       <c r="D6" s="48"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="126">
+      <c r="A7" s="118">
         <v>1.4</v>
       </c>
       <c r="B7">
@@ -9059,14 +9059,14 @@
       <c r="D7" s="48"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="126"/>
+      <c r="A8" s="118"/>
       <c r="B8">
         <v>1.5</v>
       </c>
       <c r="D8" s="48"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="126">
+      <c r="A9" s="118">
         <v>1.6</v>
       </c>
       <c r="B9">
@@ -9075,14 +9075,14 @@
       <c r="D9" s="48"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="126"/>
+      <c r="A10" s="118"/>
       <c r="B10">
         <v>1.7</v>
       </c>
       <c r="D10" s="48"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="126">
+      <c r="A11" s="118">
         <v>1.8</v>
       </c>
       <c r="B11">
@@ -9091,14 +9091,14 @@
       <c r="D11" s="48"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="126"/>
+      <c r="A12" s="118"/>
       <c r="B12">
         <v>1.9</v>
       </c>
       <c r="D12" s="48"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="126">
+      <c r="A13" s="118">
         <v>2</v>
       </c>
       <c r="B13">
@@ -9107,14 +9107,14 @@
       <c r="D13" s="48"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="126"/>
+      <c r="A14" s="118"/>
       <c r="B14">
         <v>2.1</v>
       </c>
       <c r="D14" s="48"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="126">
+      <c r="A15" s="118">
         <v>2.2000000000000002</v>
       </c>
       <c r="B15">
@@ -9123,14 +9123,14 @@
       <c r="D15" s="48"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="126"/>
+      <c r="A16" s="118"/>
       <c r="B16">
         <v>2.4</v>
       </c>
       <c r="D16" s="48"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="126">
+      <c r="A17" s="118">
         <v>2.5</v>
       </c>
       <c r="B17">
@@ -9139,14 +9139,14 @@
       <c r="D17" s="48"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="126"/>
+      <c r="A18" s="118"/>
       <c r="B18">
         <v>2.6</v>
       </c>
       <c r="D18" s="48"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="126">
+      <c r="A19" s="118">
         <v>2.8</v>
       </c>
       <c r="B19">
@@ -9155,14 +9155,14 @@
       <c r="D19" s="48"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="126"/>
+      <c r="A20" s="118"/>
       <c r="B20">
         <v>3</v>
       </c>
       <c r="D20" s="48"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="126">
+      <c r="A21" s="118">
         <v>3.2</v>
       </c>
       <c r="B21">
@@ -9171,14 +9171,14 @@
       <c r="D21" s="48"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="126"/>
+      <c r="A22" s="118"/>
       <c r="B22">
         <v>3.4</v>
       </c>
       <c r="D22" s="48"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="126">
+      <c r="A23" s="118">
         <v>3.6</v>
       </c>
       <c r="B23">
@@ -9187,14 +9187,14 @@
       <c r="D23" s="48"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="126"/>
+      <c r="A24" s="118"/>
       <c r="B24">
         <v>3.8</v>
       </c>
       <c r="D24" s="48"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="126">
+      <c r="A25" s="118">
         <v>4</v>
       </c>
       <c r="B25">
@@ -9203,14 +9203,14 @@
       <c r="D25" s="48"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="126"/>
+      <c r="A26" s="118"/>
       <c r="B26">
         <v>4.2</v>
       </c>
       <c r="D26" s="48"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="126">
+      <c r="A27" s="118">
         <v>4.5</v>
       </c>
       <c r="B27">
@@ -9219,14 +9219,14 @@
       <c r="D27" s="48"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="126"/>
+      <c r="A28" s="118"/>
       <c r="B28">
         <v>4.8</v>
       </c>
       <c r="D28" s="48"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="126">
+      <c r="A29" s="118">
         <v>5</v>
       </c>
       <c r="B29">
@@ -9235,14 +9235,14 @@
       <c r="D29" s="48"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="126"/>
+      <c r="A30" s="118"/>
       <c r="B30">
         <v>5.3</v>
       </c>
       <c r="D30" s="48"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="126">
+      <c r="A31" s="118">
         <v>5.6</v>
       </c>
       <c r="B31">
@@ -9251,14 +9251,14 @@
       <c r="D31" s="48"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="126"/>
+      <c r="A32" s="118"/>
       <c r="B32">
         <v>6</v>
       </c>
       <c r="D32" s="48"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="126">
+      <c r="A33" s="118">
         <v>6.3</v>
       </c>
       <c r="B33">
@@ -9267,14 +9267,14 @@
       <c r="D33" s="48"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="126"/>
+      <c r="A34" s="118"/>
       <c r="B34">
         <v>6.7</v>
       </c>
       <c r="D34" s="48"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="126">
+      <c r="A35" s="118">
         <v>7.1</v>
       </c>
       <c r="B35">
@@ -9283,14 +9283,14 @@
       <c r="D35" s="48"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="126"/>
+      <c r="A36" s="118"/>
       <c r="B36">
         <v>7.5</v>
       </c>
       <c r="D36" s="48"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="126">
+      <c r="A37" s="118">
         <v>8</v>
       </c>
       <c r="B37">
@@ -9299,14 +9299,14 @@
       <c r="D37" s="48"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="126"/>
+      <c r="A38" s="118"/>
       <c r="B38">
         <v>8.5</v>
       </c>
       <c r="D38" s="48"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="126">
+      <c r="A39" s="118">
         <v>9</v>
       </c>
       <c r="B39">
@@ -9315,7 +9315,7 @@
       <c r="D39" s="48"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="126"/>
+      <c r="A40" s="118"/>
       <c r="B40" s="61">
         <v>9.5</v>
       </c>
@@ -9323,7 +9323,7 @@
       <c r="E40" s="61"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="126">
+      <c r="A41" s="118">
         <v>10</v>
       </c>
       <c r="B41" s="48">
@@ -9331,13 +9331,13 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="126"/>
+      <c r="A42" s="118"/>
       <c r="B42" s="48">
         <v>10.5</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="126">
+      <c r="A43" s="118">
         <v>11</v>
       </c>
       <c r="B43" s="48">
@@ -9345,13 +9345,13 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="126"/>
+      <c r="A44" s="118"/>
       <c r="B44" s="48">
         <v>11.5</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="126">
+      <c r="A45" s="118">
         <v>12</v>
       </c>
       <c r="B45" s="48">
@@ -9359,13 +9359,13 @@
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="126"/>
+      <c r="A46" s="118"/>
       <c r="B46" s="48">
         <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="126">
+      <c r="A47" s="118">
         <v>14</v>
       </c>
       <c r="B47" s="48">
@@ -9373,13 +9373,13 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="126"/>
+      <c r="A48" s="118"/>
       <c r="B48" s="48">
         <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="126">
+      <c r="A49" s="118">
         <v>16</v>
       </c>
       <c r="B49" s="48">
@@ -9387,13 +9387,13 @@
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="126"/>
+      <c r="A50" s="118"/>
       <c r="B50" s="48">
         <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="126">
+      <c r="A51" s="118">
         <v>18</v>
       </c>
       <c r="B51" s="48">
@@ -9401,13 +9401,13 @@
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="126"/>
+      <c r="A52" s="118"/>
       <c r="B52" s="48">
         <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="126">
+      <c r="A53" s="118">
         <v>20</v>
       </c>
       <c r="B53" s="48">
@@ -9415,13 +9415,13 @@
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="126"/>
+      <c r="A54" s="118"/>
       <c r="B54" s="48">
         <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="126">
+      <c r="A55" s="118">
         <v>22</v>
       </c>
       <c r="B55" s="48">
@@ -9429,13 +9429,13 @@
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="126"/>
+      <c r="A56" s="118"/>
       <c r="B56" s="48">
         <v>24</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="126">
+      <c r="A57" s="118">
         <v>25</v>
       </c>
       <c r="B57" s="48">
@@ -9443,13 +9443,13 @@
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="126"/>
+      <c r="A58" s="118"/>
       <c r="B58" s="48">
         <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="126">
+      <c r="A59" s="118">
         <v>28</v>
       </c>
       <c r="B59" s="48">
@@ -9457,13 +9457,13 @@
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="126"/>
+      <c r="A60" s="118"/>
       <c r="B60" s="48">
         <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="126">
+      <c r="A61" s="118">
         <v>32</v>
       </c>
       <c r="B61" s="48">
@@ -9471,13 +9471,13 @@
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="126"/>
+      <c r="A62" s="118"/>
       <c r="B62" s="48">
         <v>34</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="126">
+      <c r="A63" s="118">
         <v>36</v>
       </c>
       <c r="B63" s="48">
@@ -9485,13 +9485,13 @@
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="126"/>
+      <c r="A64" s="118"/>
       <c r="B64" s="48">
         <v>38</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="126">
+      <c r="A65" s="118">
         <v>40</v>
       </c>
       <c r="B65" s="48">
@@ -9499,13 +9499,13 @@
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="126"/>
+      <c r="A66" s="118"/>
       <c r="B66" s="48">
         <v>42</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="126">
+      <c r="A67" s="118">
         <v>45</v>
       </c>
       <c r="B67" s="48">
@@ -9513,13 +9513,13 @@
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="126"/>
+      <c r="A68" s="118"/>
       <c r="B68" s="48">
         <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="126">
+      <c r="A69" s="118">
         <v>50</v>
       </c>
       <c r="B69" s="48">
@@ -9527,13 +9527,13 @@
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="126"/>
+      <c r="A70" s="118"/>
       <c r="B70" s="48">
         <v>53</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="126">
+      <c r="A71" s="118">
         <v>56</v>
       </c>
       <c r="B71" s="48">
@@ -9541,13 +9541,13 @@
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="126"/>
+      <c r="A72" s="118"/>
       <c r="B72" s="48">
         <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="126">
+      <c r="A73" s="118">
         <v>63</v>
       </c>
       <c r="B73" s="48">
@@ -9555,13 +9555,13 @@
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="126"/>
+      <c r="A74" s="118"/>
       <c r="B74" s="48">
         <v>67</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="126">
+      <c r="A75" s="118">
         <v>71</v>
       </c>
       <c r="B75" s="48">
@@ -9569,13 +9569,13 @@
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="126"/>
+      <c r="A76" s="118"/>
       <c r="B76" s="48">
         <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="126">
+      <c r="A77" s="118">
         <v>80</v>
       </c>
       <c r="B77" s="48">
@@ -9583,13 +9583,13 @@
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="126"/>
+      <c r="A78" s="118"/>
       <c r="B78" s="48">
         <v>85</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="126">
+      <c r="A79" s="118">
         <v>90</v>
       </c>
       <c r="B79" s="48">
@@ -9597,13 +9597,41 @@
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="126"/>
+      <c r="A80" s="118"/>
       <c r="B80" s="48">
         <v>95</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A35:A36"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="A3:A4"/>
@@ -9616,34 +9644,6 @@
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="A75:A76"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9668,37 +9668,37 @@
       <c r="A2">
         <v>4</v>
       </c>
-      <c r="E2" s="93" t="s">
+      <c r="E2" s="94" t="s">
         <v>224</v>
       </c>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="126" t="s">
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="118" t="s">
         <v>259</v>
       </c>
-      <c r="K2" s="126"/>
-      <c r="L2" s="126"/>
-      <c r="M2" s="126"/>
-      <c r="N2" s="126"/>
-      <c r="P2" s="126" t="s">
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
+      <c r="P2" s="118" t="s">
         <v>260</v>
       </c>
-      <c r="Q2" s="126"/>
-      <c r="R2" s="126"/>
-      <c r="S2" s="126"/>
-      <c r="T2" s="126"/>
+      <c r="Q2" s="118"/>
+      <c r="R2" s="118"/>
+      <c r="S2" s="118"/>
+      <c r="T2" s="118"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>5</v>
       </c>
-      <c r="E3" s="132" t="s">
+      <c r="E3" s="136" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="132"/>
-      <c r="G3" s="132"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="136"/>
       <c r="H3" s="60">
         <f>Передача!$D$49</f>
         <v>2016</v>
@@ -9723,11 +9723,11 @@
       <c r="A4">
         <v>6</v>
       </c>
-      <c r="E4" s="132" t="s">
+      <c r="E4" s="136" t="s">
         <v>157</v>
       </c>
-      <c r="F4" s="132"/>
-      <c r="G4" s="132"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
       <c r="H4" s="60">
         <f>Передача!$D$50</f>
         <v>734</v>
@@ -9735,21 +9735,21 @@
       <c r="I4" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="J4" s="126" t="s">
+      <c r="J4" s="118" t="s">
         <v>303</v>
       </c>
-      <c r="K4" s="126"/>
-      <c r="L4" s="126"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>7</v>
       </c>
-      <c r="E5" s="132" t="s">
+      <c r="E5" s="136" t="s">
         <v>158</v>
       </c>
-      <c r="F5" s="132"/>
-      <c r="G5" s="132"/>
+      <c r="F5" s="136"/>
+      <c r="G5" s="136"/>
       <c r="H5" s="60">
         <f>Передача!$D$51</f>
         <v>0</v>
@@ -9757,11 +9757,11 @@
       <c r="I5" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="J5" s="126" t="s">
+      <c r="J5" s="118" t="s">
         <v>118</v>
       </c>
-      <c r="K5" s="126"/>
-      <c r="L5" s="126"/>
+      <c r="K5" s="118"/>
+      <c r="L5" s="118"/>
       <c r="M5">
         <f>Вал!K16</f>
         <v>40</v>
@@ -9769,11 +9769,11 @@
       <c r="N5" t="s">
         <v>16</v>
       </c>
-      <c r="P5" s="126" t="s">
+      <c r="P5" s="118" t="s">
         <v>118</v>
       </c>
-      <c r="Q5" s="126"/>
-      <c r="R5" s="126"/>
+      <c r="Q5" s="118"/>
+      <c r="R5" s="118"/>
       <c r="S5">
         <f ca="1">Вал!S15</f>
         <v>50</v>
@@ -9786,20 +9786,20 @@
       <c r="A6">
         <v>8</v>
       </c>
-      <c r="J6" s="126" t="s">
+      <c r="J6" s="118" t="s">
         <v>258</v>
       </c>
-      <c r="K6" s="126"/>
-      <c r="L6" s="126"/>
+      <c r="K6" s="118"/>
+      <c r="L6" s="118"/>
       <c r="M6" s="52">
         <f>E16</f>
         <v>208</v>
       </c>
-      <c r="P6" s="126" t="s">
+      <c r="P6" s="118" t="s">
         <v>258</v>
       </c>
-      <c r="Q6" s="126"/>
-      <c r="R6" s="126"/>
+      <c r="Q6" s="118"/>
+      <c r="R6" s="118"/>
       <c r="S6" s="52">
         <f>E18</f>
         <v>210</v>
@@ -9819,38 +9819,38 @@
       <c r="A9">
         <v>15</v>
       </c>
-      <c r="E9" s="126" t="s">
+      <c r="E9" s="118" t="s">
         <v>302</v>
       </c>
-      <c r="F9" s="126"/>
-      <c r="G9" s="126"/>
-      <c r="H9" s="126"/>
-      <c r="I9" s="126"/>
-      <c r="J9" s="126"/>
-      <c r="K9" s="126"/>
-      <c r="L9" s="126"/>
-      <c r="M9" s="126"/>
+      <c r="F9" s="118"/>
+      <c r="G9" s="118"/>
+      <c r="H9" s="118"/>
+      <c r="I9" s="118"/>
+      <c r="J9" s="118"/>
+      <c r="K9" s="118"/>
+      <c r="L9" s="118"/>
+      <c r="M9" s="118"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>17</v>
       </c>
       <c r="D10" s="1"/>
-      <c r="E10" s="126">
+      <c r="E10" s="118">
         <v>200</v>
       </c>
-      <c r="F10" s="126"/>
-      <c r="G10" s="126"/>
-      <c r="H10" s="126">
+      <c r="F10" s="118"/>
+      <c r="G10" s="118"/>
+      <c r="H10" s="118">
         <v>300</v>
       </c>
-      <c r="I10" s="126"/>
-      <c r="J10" s="126"/>
-      <c r="K10" s="126">
+      <c r="I10" s="118"/>
+      <c r="J10" s="118"/>
+      <c r="K10" s="118">
         <v>400</v>
       </c>
-      <c r="L10" s="126"/>
-      <c r="M10" s="126"/>
+      <c r="L10" s="118"/>
+      <c r="M10" s="118"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11">
@@ -10344,6 +10344,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="J2:N2"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="E2:I2"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="E4:G4"/>
     <mergeCell ref="P6:R6"/>
     <mergeCell ref="J4:L4"/>
     <mergeCell ref="E10:G10"/>
@@ -10353,12 +10359,6 @@
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="E5:G5"/>
     <mergeCell ref="J5:L5"/>
-    <mergeCell ref="J2:N2"/>
-    <mergeCell ref="P2:T2"/>
-    <mergeCell ref="P5:R5"/>
-    <mergeCell ref="E2:I2"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="E4:G4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10373,37 +10373,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="118" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126" t="s">
+      <c r="B1" s="118"/>
+      <c r="C1" s="118" t="s">
         <v>182</v>
       </c>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126" t="s">
+      <c r="D1" s="118"/>
+      <c r="E1" s="118" t="s">
         <v>273</v>
       </c>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126" t="s">
+      <c r="F1" s="118"/>
+      <c r="G1" s="118" t="s">
         <v>276</v>
       </c>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
-      <c r="J1" s="126"/>
-      <c r="K1" s="126"/>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="126"/>
-      <c r="B2" s="126"/>
-      <c r="C2" s="126" t="s">
+      <c r="A2" s="118"/>
+      <c r="B2" s="118"/>
+      <c r="C2" s="118" t="s">
         <v>274</v>
       </c>
-      <c r="D2" s="126"/>
-      <c r="E2" s="126" t="s">
+      <c r="D2" s="118"/>
+      <c r="E2" s="118" t="s">
         <v>275</v>
       </c>
-      <c r="F2" s="126"/>
+      <c r="F2" s="118"/>
       <c r="G2" s="91" t="s">
         <v>277</v>
       </c>
@@ -10424,18 +10424,18 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="126" t="s">
+      <c r="A3" s="118" t="s">
         <v>267</v>
       </c>
-      <c r="B3" s="126"/>
-      <c r="C3" s="126">
+      <c r="B3" s="118"/>
+      <c r="C3" s="118">
         <v>1000</v>
       </c>
-      <c r="D3" s="126"/>
-      <c r="E3" s="126">
+      <c r="D3" s="118"/>
+      <c r="E3" s="118">
         <v>190</v>
       </c>
-      <c r="F3" s="126"/>
+      <c r="F3" s="118"/>
       <c r="G3">
         <v>520</v>
       </c>
@@ -10456,18 +10456,18 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="126">
+      <c r="A4" s="118">
         <v>45</v>
       </c>
-      <c r="B4" s="126"/>
-      <c r="C4" s="126">
+      <c r="B4" s="118"/>
+      <c r="C4" s="118">
         <v>120</v>
       </c>
-      <c r="D4" s="126"/>
-      <c r="E4" s="126">
+      <c r="D4" s="118"/>
+      <c r="E4" s="118">
         <v>227</v>
       </c>
-      <c r="F4" s="126"/>
+      <c r="F4" s="118"/>
       <c r="G4">
         <v>820</v>
       </c>
@@ -10488,18 +10488,18 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="126">
+      <c r="A5" s="118">
         <v>45</v>
       </c>
-      <c r="B5" s="126"/>
-      <c r="C5" s="126">
+      <c r="B5" s="118"/>
+      <c r="C5" s="118">
         <v>80</v>
       </c>
-      <c r="D5" s="126"/>
-      <c r="E5" s="126">
+      <c r="D5" s="118"/>
+      <c r="E5" s="118">
         <v>260</v>
       </c>
-      <c r="F5" s="126"/>
+      <c r="F5" s="118"/>
       <c r="G5">
         <v>900</v>
       </c>
@@ -10520,18 +10520,18 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="126" t="s">
+      <c r="A6" s="118" t="s">
         <v>268</v>
       </c>
-      <c r="B6" s="126"/>
-      <c r="C6" s="126">
+      <c r="B6" s="118"/>
+      <c r="C6" s="118">
         <v>200</v>
       </c>
-      <c r="D6" s="126"/>
-      <c r="E6" s="126">
+      <c r="D6" s="118"/>
+      <c r="E6" s="118">
         <v>240</v>
       </c>
-      <c r="F6" s="126"/>
+      <c r="F6" s="118"/>
       <c r="G6">
         <v>790</v>
       </c>
@@ -10552,18 +10552,18 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="118" t="s">
         <v>268</v>
       </c>
-      <c r="B7" s="126"/>
-      <c r="C7" s="126">
+      <c r="B7" s="118"/>
+      <c r="C7" s="118">
         <v>120</v>
       </c>
-      <c r="D7" s="126"/>
-      <c r="E7" s="126">
+      <c r="D7" s="118"/>
+      <c r="E7" s="118">
         <v>270</v>
       </c>
-      <c r="F7" s="126"/>
+      <c r="F7" s="118"/>
       <c r="G7">
         <v>980</v>
       </c>
@@ -10584,18 +10584,18 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="126" t="s">
+      <c r="A8" s="118" t="s">
         <v>269</v>
       </c>
-      <c r="B8" s="126"/>
-      <c r="C8" s="126">
+      <c r="B8" s="118"/>
+      <c r="C8" s="118">
         <v>200</v>
       </c>
-      <c r="D8" s="126"/>
-      <c r="E8" s="126">
+      <c r="D8" s="118"/>
+      <c r="E8" s="118">
         <v>270</v>
       </c>
-      <c r="F8" s="126"/>
+      <c r="F8" s="118"/>
       <c r="G8">
         <v>980</v>
       </c>
@@ -10616,18 +10616,18 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="126" t="s">
+      <c r="A9" s="118" t="s">
         <v>270</v>
       </c>
-      <c r="B9" s="126"/>
-      <c r="C9" s="126">
+      <c r="B9" s="118"/>
+      <c r="C9" s="118">
         <v>120</v>
       </c>
-      <c r="D9" s="126"/>
-      <c r="E9" s="126">
+      <c r="D9" s="118"/>
+      <c r="E9" s="118">
         <v>197</v>
       </c>
-      <c r="F9" s="126"/>
+      <c r="F9" s="118"/>
       <c r="G9">
         <v>650</v>
       </c>
@@ -10648,18 +10648,18 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="126" t="s">
+      <c r="A10" s="118" t="s">
         <v>271</v>
       </c>
-      <c r="B10" s="126"/>
-      <c r="C10" s="126">
+      <c r="B10" s="118"/>
+      <c r="C10" s="118">
         <v>120</v>
       </c>
-      <c r="D10" s="126"/>
-      <c r="E10" s="126">
+      <c r="D10" s="118"/>
+      <c r="E10" s="118">
         <v>260</v>
       </c>
-      <c r="F10" s="126"/>
+      <c r="F10" s="118"/>
       <c r="G10">
         <v>930</v>
       </c>
@@ -10680,18 +10680,18 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="126" t="s">
+      <c r="A11" s="118" t="s">
         <v>272</v>
       </c>
-      <c r="B11" s="126"/>
-      <c r="C11" s="126">
+      <c r="B11" s="118"/>
+      <c r="C11" s="118">
         <v>60</v>
       </c>
-      <c r="D11" s="126"/>
-      <c r="E11" s="126">
+      <c r="D11" s="118"/>
+      <c r="E11" s="118">
         <v>330</v>
       </c>
-      <c r="F11" s="126"/>
+      <c r="F11" s="118"/>
       <c r="G11">
         <v>1180</v>
       </c>
@@ -10725,6 +10725,23 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G1:K1"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="C3:D3"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="C2:D2"/>
@@ -10741,23 +10758,6 @@
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Расчёт.xlsx
+++ b/Расчёт.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Professional\Downloads\интститут\курсач детмаш\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE5F152-963E-4BC7-B908-BC6DCFC4A096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A19667-2A0F-4C85-88D9-F847AFC4DAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="812" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
   </bookViews>
   <sheets>
     <sheet name="Электродвигатель" sheetId="1" r:id="rId1"/>
     <sheet name="Вал" sheetId="4" r:id="rId2"/>
-    <sheet name="Передача" sheetId="2" r:id="rId3"/>
-    <sheet name="Колесо" sheetId="7" r:id="rId4"/>
-    <sheet name="Корпус" sheetId="3" r:id="rId5"/>
-    <sheet name="Ra40" sheetId="5" r:id="rId6"/>
-    <sheet name="Подшипники" sheetId="10" r:id="rId7"/>
-    <sheet name="Материалы" sheetId="11" r:id="rId8"/>
+    <sheet name="Крышки" sheetId="12" r:id="rId3"/>
+    <sheet name="Передача" sheetId="2" r:id="rId4"/>
+    <sheet name="Колесо" sheetId="7" r:id="rId5"/>
+    <sheet name="Корпус" sheetId="3" r:id="rId6"/>
+    <sheet name="Ra40" sheetId="5" r:id="rId7"/>
+    <sheet name="Подшипники" sheetId="10" r:id="rId8"/>
+    <sheet name="Материалы" sheetId="11" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="366">
   <si>
     <t>Окружная сила</t>
   </si>
@@ -412,24 +413,9 @@
     <t>Частота поля</t>
   </si>
   <si>
-    <t>Редуктор:</t>
-  </si>
-  <si>
-    <t>Страницы в атласе</t>
-  </si>
-  <si>
     <t>Колесо</t>
   </si>
   <si>
-    <t>238-239</t>
-  </si>
-  <si>
-    <t>193-194</t>
-  </si>
-  <si>
-    <t>Страницы в pdf</t>
-  </si>
-  <si>
     <t>Вариант передачи</t>
   </si>
   <si>
@@ -805,12 +791,6 @@
     <t>Диаметр внешний [мм]</t>
   </si>
   <si>
-    <t>Расчёт</t>
-  </si>
-  <si>
-    <t>H8/z8</t>
-  </si>
-  <si>
     <t>Сила запрессовки</t>
   </si>
   <si>
@@ -925,21 +905,12 @@
     <t>Шероховатость Ra</t>
   </si>
   <si>
-    <t>Ширина левого канала</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
     <t>Шероховатость вала Ra</t>
   </si>
   <si>
     <t>C</t>
   </si>
   <si>
-    <t>манжетта</t>
-  </si>
-  <si>
     <t>Мощность электродвигателя</t>
   </si>
   <si>
@@ -958,9 +929,6 @@
     <t>Схема установки</t>
   </si>
   <si>
-    <t>Порядко расчёта:</t>
-  </si>
-  <si>
     <t>Выбор схемы установки</t>
   </si>
   <si>
@@ -1079,6 +1047,102 @@
   </si>
   <si>
     <t>Гидроизоляция?</t>
+  </si>
+  <si>
+    <t>манжетта?</t>
+  </si>
+  <si>
+    <t>Размеры крышки:</t>
+  </si>
+  <si>
+    <t>delta</t>
+  </si>
+  <si>
+    <t>delta1</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>Канавка</t>
+  </si>
+  <si>
+    <t>2…3</t>
+  </si>
+  <si>
+    <t>Используются закладные крышки</t>
+  </si>
+  <si>
+    <t>Диаметр внешний</t>
+  </si>
+  <si>
+    <t>Левая внешняя</t>
+  </si>
+  <si>
+    <t>Внутреняя полость</t>
+  </si>
+  <si>
+    <t>Внешняя часть</t>
+  </si>
+  <si>
+    <t>Подшипник</t>
+  </si>
+  <si>
+    <t>Допуск</t>
+  </si>
+  <si>
+    <t>Отверстие под вал</t>
+  </si>
+  <si>
+    <t>Ширина впадин</t>
+  </si>
+  <si>
+    <t>Расчёт натяга</t>
+  </si>
+  <si>
+    <t>Материал</t>
+  </si>
+  <si>
+    <t>Ширина подшипников</t>
+  </si>
+  <si>
+    <t>Расстояние до корпуса a</t>
+  </si>
+  <si>
+    <t>Ширина крышки</t>
+  </si>
+  <si>
+    <t>Расстояение от торцев колец (а)</t>
+  </si>
+  <si>
+    <t>Длинна суммарная</t>
+  </si>
+  <si>
+    <t>H7/u8</t>
+  </si>
+  <si>
+    <t>Крышка тихоходного вала</t>
+  </si>
+  <si>
+    <t>Крышка быстроходного вала</t>
+  </si>
+  <si>
+    <t>Выбор гидроизолирующих элементов</t>
+  </si>
+  <si>
+    <t>Порядок расчёта:</t>
+  </si>
+  <si>
+    <t>H11/h11</t>
   </si>
 </sst>
 </file>
@@ -1127,7 +1191,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1173,6 +1237,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1306,7 +1376,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -1437,26 +1507,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1465,25 +1547,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1513,56 +1607,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1576,11 +1643,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1591,21 +1673,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1625,25 +1706,20 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>373380</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>518160</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>381909</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>8269</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="3634740" cy="395749"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Рисунок 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{663FF092-D9BC-489E-B5A6-1E2F3A22076A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09ACAE45-6000-4DA4-90DD-F24B8090F8CB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1659,8 +1735,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7345680" y="2308860"/>
-          <a:ext cx="6516009" cy="4648849"/>
+          <a:off x="13677900" y="4610100"/>
+          <a:ext cx="3634740" cy="395749"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1668,7 +1744,89 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>358139</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>30481</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4114801" cy="4061460"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Рисунок 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FDC2872-6F28-4BC5-B657-74FEE33C1057}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:srcRect l="19623" r="7796" b="7810"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6598919" y="396241"/>
+          <a:ext cx="4114801" cy="4061460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>83820</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2200582" cy="1876687"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Рисунок 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5603A65C-323D-418A-A33C-8A0F52F48028}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11811000" y="2720340"/>
+          <a:ext cx="2200582" cy="1876687"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>17</xdr:col>
@@ -1696,7 +1854,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1713,10 +1871,54 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>274320</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>126488</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>57833</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Рисунок 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{366D2F5C-157C-4C4B-9407-28D80DF4A567}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8176260" y="2659380"/>
+          <a:ext cx="5430008" cy="4896533"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2200,23 +2402,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="108" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A2" s="97" t="s">
+      <c r="A2" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
       <c r="E2" s="19">
         <v>4</v>
       </c>
@@ -2224,22 +2426,22 @@
         <v>4</v>
       </c>
       <c r="G2" s="6"/>
-      <c r="I2" s="97" t="s">
+      <c r="I2" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98">
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101">
         <f>E2*E3</f>
         <v>6.4</v>
       </c>
-      <c r="N2" s="99"/>
-      <c r="Q2" s="97" t="s">
+      <c r="N2" s="116"/>
+      <c r="Q2" s="108" t="s">
         <v>29</v>
       </c>
-      <c r="R2" s="98"/>
-      <c r="S2" s="98"/>
+      <c r="R2" s="101"/>
+      <c r="S2" s="101"/>
       <c r="T2" s="8" t="s">
         <v>30</v>
       </c>
@@ -2249,11 +2451,11 @@
       <c r="V2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AC2" s="97" t="s">
+      <c r="AC2" s="108" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="98"/>
-      <c r="AE2" s="98"/>
+      <c r="AD2" s="101"/>
+      <c r="AE2" s="101"/>
       <c r="AF2" s="8" t="s">
         <v>44</v>
       </c>
@@ -2272,7 +2474,7 @@
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="100" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="94"/>
@@ -2285,16 +2487,16 @@
         <v>5</v>
       </c>
       <c r="G3" s="3"/>
-      <c r="I3" s="93" t="s">
+      <c r="I3" s="100" t="s">
         <v>23</v>
       </c>
       <c r="J3" s="94"/>
       <c r="K3" s="94"/>
       <c r="L3" s="94"/>
       <c r="M3" s="94"/>
-      <c r="N3" s="105"/>
-      <c r="Q3" s="93" t="s">
-        <v>132</v>
+      <c r="N3" s="111"/>
+      <c r="Q3" s="100" t="s">
+        <v>127</v>
       </c>
       <c r="R3" s="94"/>
       <c r="S3" s="94"/>
@@ -2308,8 +2510,8 @@
         <f>AVERAGE(T3:U3)</f>
         <v>0.97</v>
       </c>
-      <c r="AC3" s="93" t="s">
-        <v>131</v>
+      <c r="AC3" s="100" t="s">
+        <v>126</v>
       </c>
       <c r="AD3" s="94"/>
       <c r="AE3" s="94"/>
@@ -2337,26 +2539,26 @@
       </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A4" s="93" t="s">
+      <c r="A4" s="100" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="94"/>
       <c r="C4" s="94"/>
       <c r="D4" s="94"/>
-      <c r="E4" s="102" t="s">
+      <c r="E4" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="102"/>
-      <c r="G4" s="108"/>
-      <c r="I4" s="93" t="s">
+      <c r="F4" s="109"/>
+      <c r="G4" s="110"/>
+      <c r="I4" s="100" t="s">
         <v>24</v>
       </c>
       <c r="J4" s="94"/>
       <c r="K4" s="94"/>
       <c r="L4" s="94"/>
       <c r="M4" s="94"/>
-      <c r="N4" s="105"/>
-      <c r="Q4" s="93" t="s">
+      <c r="N4" s="111"/>
+      <c r="Q4" s="100" t="s">
         <v>49</v>
       </c>
       <c r="R4" s="94"/>
@@ -2371,7 +2573,7 @@
         <f t="shared" ref="V4:V12" si="1">AVERAGE(T4:U4)</f>
         <v>0.96</v>
       </c>
-      <c r="AC4" s="93" t="s">
+      <c r="AC4" s="100" t="s">
         <v>48</v>
       </c>
       <c r="AD4" s="94"/>
@@ -2400,7 +2602,7 @@
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="100" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="94"/>
@@ -2422,8 +2624,8 @@
       <c r="M5" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="105"/>
-      <c r="Q5" s="93" t="s">
+      <c r="N5" s="111"/>
+      <c r="Q5" s="100" t="s">
         <v>32</v>
       </c>
       <c r="R5" s="94"/>
@@ -2438,7 +2640,7 @@
         <f t="shared" si="1"/>
         <v>0.96</v>
       </c>
-      <c r="AC5" s="93" t="s">
+      <c r="AC5" s="100" t="s">
         <v>32</v>
       </c>
       <c r="AD5" s="94"/>
@@ -2467,7 +2669,7 @@
       </c>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A6" s="93" t="s">
+      <c r="A6" s="100" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="94"/>
@@ -2478,19 +2680,19 @@
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="3"/>
-      <c r="I6" s="93" t="s">
+      <c r="I6" s="100" t="s">
         <v>26</v>
       </c>
       <c r="J6" s="94"/>
-      <c r="K6" s="102">
+      <c r="K6" s="109">
         <v>2</v>
       </c>
-      <c r="L6" s="102"/>
+      <c r="L6" s="109"/>
       <c r="M6" s="94">
         <v>0.99</v>
       </c>
-      <c r="N6" s="105"/>
-      <c r="Q6" s="93" t="s">
+      <c r="N6" s="111"/>
+      <c r="Q6" s="100" t="s">
         <v>33</v>
       </c>
       <c r="R6" s="94"/>
@@ -2505,7 +2707,7 @@
         <f t="shared" si="1"/>
         <v>0.94</v>
       </c>
-      <c r="AC6" s="93" t="s">
+      <c r="AC6" s="100" t="s">
         <v>45</v>
       </c>
       <c r="AD6" s="94"/>
@@ -2534,7 +2736,7 @@
       </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A7" s="93" t="s">
+      <c r="A7" s="100" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="94"/>
@@ -2545,19 +2747,19 @@
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="3"/>
-      <c r="I7" s="93" t="s">
+      <c r="I7" s="100" t="s">
         <v>28</v>
       </c>
       <c r="J7" s="94"/>
-      <c r="K7" s="102">
+      <c r="K7" s="109">
         <v>2</v>
       </c>
-      <c r="L7" s="102"/>
+      <c r="L7" s="109"/>
       <c r="M7" s="94">
         <v>0.98</v>
       </c>
-      <c r="N7" s="105"/>
-      <c r="Q7" s="93" t="s">
+      <c r="N7" s="111"/>
+      <c r="Q7" s="100" t="s">
         <v>34</v>
       </c>
       <c r="R7" s="94"/>
@@ -2572,7 +2774,7 @@
         <f t="shared" si="1"/>
         <v>0.77</v>
       </c>
-      <c r="AC7" s="93" t="s">
+      <c r="AC7" s="100" t="s">
         <v>33</v>
       </c>
       <c r="AD7" s="94"/>
@@ -2601,31 +2803,31 @@
       </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A8" s="100" t="s">
+      <c r="A8" s="104" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="101"/>
-      <c r="C8" s="101"/>
-      <c r="D8" s="101"/>
+      <c r="B8" s="105"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="105"/>
       <c r="E8" s="22">
         <v>2.2000000000000002</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="5"/>
-      <c r="I8" s="93" t="s">
-        <v>257</v>
+      <c r="I8" s="100" t="s">
+        <v>250</v>
       </c>
       <c r="J8" s="94"/>
-      <c r="K8" s="102">
+      <c r="K8" s="109">
         <v>0</v>
       </c>
-      <c r="L8" s="102"/>
-      <c r="M8" s="103">
+      <c r="L8" s="109"/>
+      <c r="M8" s="126">
         <f>V11</f>
         <v>0.95</v>
       </c>
-      <c r="N8" s="104"/>
-      <c r="Q8" s="93" t="s">
+      <c r="N8" s="131"/>
+      <c r="Q8" s="100" t="s">
         <v>35</v>
       </c>
       <c r="R8" s="94"/>
@@ -2640,7 +2842,7 @@
         <f t="shared" si="1"/>
         <v>0.75</v>
       </c>
-      <c r="AC8" s="93" t="s">
+      <c r="AC8" s="100" t="s">
         <v>46</v>
       </c>
       <c r="AD8" s="94"/>
@@ -2669,27 +2871,27 @@
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A9" s="109" t="s">
+      <c r="A9" s="117" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="110"/>
-      <c r="C9" s="110"/>
-      <c r="D9" s="110"/>
-      <c r="E9" s="110"/>
-      <c r="F9" s="110"/>
-      <c r="G9" s="111"/>
-      <c r="I9" s="93" t="s">
+      <c r="B9" s="118"/>
+      <c r="C9" s="118"/>
+      <c r="D9" s="118"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="118"/>
+      <c r="G9" s="119"/>
+      <c r="I9" s="100" t="s">
         <v>50</v>
       </c>
       <c r="J9" s="94"/>
       <c r="K9" s="94"/>
       <c r="L9" s="94"/>
-      <c r="M9" s="106">
+      <c r="M9" s="95">
         <f>M7^K7*M6^K6*M8^K8</f>
         <v>0.94128803999999988</v>
       </c>
-      <c r="N9" s="107"/>
-      <c r="Q9" s="93" t="s">
+      <c r="N9" s="129"/>
+      <c r="Q9" s="100" t="s">
         <v>36</v>
       </c>
       <c r="R9" s="94"/>
@@ -2704,7 +2906,7 @@
         <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="AC9" s="93" t="s">
+      <c r="AC9" s="100" t="s">
         <v>47</v>
       </c>
       <c r="AD9" s="94"/>
@@ -2733,26 +2935,26 @@
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A10" s="112" t="s">
+      <c r="A10" s="120" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="113"/>
-      <c r="C10" s="113"/>
-      <c r="D10" s="113"/>
-      <c r="E10" s="113"/>
-      <c r="F10" s="113"/>
-      <c r="G10" s="114"/>
-      <c r="I10" s="93" t="s">
+      <c r="B10" s="121"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="122"/>
+      <c r="I10" s="100" t="s">
         <v>51</v>
       </c>
       <c r="J10" s="94"/>
       <c r="K10" s="94"/>
       <c r="L10" s="94"/>
-      <c r="M10" s="102">
+      <c r="M10" s="109">
         <v>0.97</v>
       </c>
-      <c r="N10" s="108"/>
-      <c r="Q10" s="93" t="s">
+      <c r="N10" s="110"/>
+      <c r="Q10" s="100" t="s">
         <v>37</v>
       </c>
       <c r="R10" s="94"/>
@@ -2767,11 +2969,11 @@
         <f t="shared" si="1"/>
         <v>0.85000000000000009</v>
       </c>
-      <c r="AC10" s="100" t="s">
+      <c r="AC10" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="AD10" s="101"/>
-      <c r="AE10" s="101"/>
+      <c r="AD10" s="105"/>
+      <c r="AE10" s="105"/>
       <c r="AF10" s="4">
         <v>70</v>
       </c>
@@ -2796,27 +2998,27 @@
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A11" s="109" t="s">
+      <c r="A11" s="117" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="110"/>
-      <c r="C11" s="110"/>
-      <c r="D11" s="110"/>
-      <c r="E11" s="110"/>
-      <c r="F11" s="110"/>
-      <c r="G11" s="111"/>
-      <c r="I11" s="100" t="s">
+      <c r="B11" s="118"/>
+      <c r="C11" s="118"/>
+      <c r="D11" s="118"/>
+      <c r="E11" s="118"/>
+      <c r="F11" s="118"/>
+      <c r="G11" s="119"/>
+      <c r="I11" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J11" s="101"/>
-      <c r="K11" s="101"/>
-      <c r="L11" s="101"/>
-      <c r="M11" s="95">
+      <c r="J11" s="105"/>
+      <c r="K11" s="105"/>
+      <c r="L11" s="105"/>
+      <c r="M11" s="106">
         <f>M2/M10/M9</f>
         <v>7.0094783572623509</v>
       </c>
-      <c r="N11" s="96"/>
-      <c r="Q11" s="93" t="s">
+      <c r="N11" s="130"/>
+      <c r="Q11" s="100" t="s">
         <v>38</v>
       </c>
       <c r="R11" s="94"/>
@@ -2839,22 +3041,22 @@
       <c r="AH11" s="1"/>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A12" s="97" t="s">
+      <c r="A12" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="98"/>
-      <c r="C12" s="98"/>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98" t="s">
+      <c r="B12" s="101"/>
+      <c r="C12" s="101"/>
+      <c r="D12" s="101"/>
+      <c r="E12" s="101" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="98"/>
-      <c r="G12" s="99"/>
-      <c r="Q12" s="100" t="s">
+      <c r="F12" s="101"/>
+      <c r="G12" s="116"/>
+      <c r="Q12" s="104" t="s">
         <v>39</v>
       </c>
-      <c r="R12" s="101"/>
-      <c r="S12" s="101"/>
+      <c r="R12" s="105"/>
+      <c r="S12" s="105"/>
       <c r="T12" s="4">
         <v>0.92</v>
       </c>
@@ -2870,7 +3072,7 @@
       </c>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A13" s="93" t="s">
+      <c r="A13" s="100" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="94"/>
@@ -2890,7 +3092,7 @@
       </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A14" s="93" t="s">
+      <c r="A14" s="100" t="s">
         <v>15</v>
       </c>
       <c r="B14" s="94"/>
@@ -2905,12 +3107,12 @@
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A15" s="100" t="s">
+      <c r="A15" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="101"/>
-      <c r="C15" s="101"/>
-      <c r="D15" s="101"/>
+      <c r="B15" s="105"/>
+      <c r="C15" s="105"/>
+      <c r="D15" s="105"/>
       <c r="E15" s="22">
         <v>300</v>
       </c>
@@ -2919,57 +3121,44 @@
       </c>
       <c r="G15" s="5"/>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B18" s="66" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B19" s="66" t="s">
-        <v>306</v>
-      </c>
-      <c r="I19" s="97" t="s">
+    <row r="19" spans="9:29" x14ac:dyDescent="0.3">
+      <c r="I19" s="108" t="s">
         <v>121</v>
       </c>
-      <c r="J19" s="99"/>
-      <c r="K19" s="97">
+      <c r="J19" s="116"/>
+      <c r="K19" s="108">
         <v>3000</v>
       </c>
-      <c r="L19" s="98"/>
-      <c r="M19" s="98"/>
-      <c r="N19" s="99"/>
-      <c r="O19" s="98">
+      <c r="L19" s="101"/>
+      <c r="M19" s="101"/>
+      <c r="N19" s="116"/>
+      <c r="O19" s="101">
         <v>1500</v>
       </c>
-      <c r="P19" s="98"/>
-      <c r="Q19" s="98"/>
-      <c r="R19" s="98"/>
-      <c r="S19" s="97">
+      <c r="P19" s="101"/>
+      <c r="Q19" s="101"/>
+      <c r="R19" s="101"/>
+      <c r="S19" s="108">
         <v>1000</v>
       </c>
-      <c r="T19" s="98"/>
-      <c r="U19" s="98"/>
-      <c r="V19" s="99"/>
-      <c r="W19" s="98">
+      <c r="T19" s="101"/>
+      <c r="U19" s="101"/>
+      <c r="V19" s="116"/>
+      <c r="W19" s="101">
         <v>750</v>
       </c>
-      <c r="X19" s="98"/>
-      <c r="Y19" s="98"/>
-      <c r="Z19" s="99"/>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B20" s="66" t="s">
-        <v>308</v>
-      </c>
-      <c r="I20" s="100" t="s">
+      <c r="X19" s="101"/>
+      <c r="Y19" s="101"/>
+      <c r="Z19" s="116"/>
+      <c r="AC19" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="20" spans="9:29" x14ac:dyDescent="0.3">
+      <c r="I20" s="104" t="s">
         <v>116</v>
       </c>
-      <c r="J20" s="119"/>
+      <c r="J20" s="128"/>
       <c r="K20" s="12" t="s">
         <v>72</v>
       </c>
@@ -3018,12 +3207,12 @@
       <c r="Z20" s="5" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B21" s="66" t="s">
-        <v>307</v>
-      </c>
-      <c r="I21" s="93">
+      <c r="AC20" s="66" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="21" spans="9:29" x14ac:dyDescent="0.3">
+      <c r="I21" s="100">
         <v>0.37</v>
       </c>
       <c r="J21" s="94"/>
@@ -3059,12 +3248,12 @@
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
       <c r="Z21" s="3"/>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B22" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="I22" s="93">
+      <c r="AC21" s="66" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="22" spans="9:29" x14ac:dyDescent="0.3">
+      <c r="I22" s="100">
         <v>0.55000000000000004</v>
       </c>
       <c r="J22" s="94"/>
@@ -3098,12 +3287,12 @@
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
       <c r="Z22" s="3"/>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B23" s="66" t="s">
-        <v>310</v>
-      </c>
-      <c r="I23" s="93">
+      <c r="AC22" s="66" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="23" spans="9:29" x14ac:dyDescent="0.3">
+      <c r="I23" s="100">
         <v>0.75</v>
       </c>
       <c r="J23" s="94"/>
@@ -3137,12 +3326,12 @@
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
       <c r="Z23" s="3"/>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B24" s="66" t="s">
-        <v>311</v>
-      </c>
-      <c r="I24" s="93">
+      <c r="AC23" s="66" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="24" spans="9:29" x14ac:dyDescent="0.3">
+      <c r="I24" s="100">
         <v>1.1000000000000001</v>
       </c>
       <c r="J24" s="94"/>
@@ -3176,12 +3365,12 @@
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
       <c r="Z24" s="3"/>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B25" s="66" t="s">
-        <v>313</v>
-      </c>
-      <c r="I25" s="93">
+      <c r="AC24" s="66" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="25" spans="9:29" x14ac:dyDescent="0.3">
+      <c r="I25" s="100">
         <v>1.5</v>
       </c>
       <c r="J25" s="94"/>
@@ -3215,12 +3404,12 @@
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
       <c r="Z25" s="3"/>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B26" s="66" t="s">
-        <v>312</v>
-      </c>
-      <c r="I26" s="93">
+      <c r="AC25" s="66" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="26" spans="9:29" x14ac:dyDescent="0.3">
+      <c r="I26" s="100">
         <v>2.2000000000000002</v>
       </c>
       <c r="J26" s="94"/>
@@ -3254,12 +3443,12 @@
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
       <c r="Z26" s="3"/>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B27" s="66" t="s">
-        <v>315</v>
-      </c>
-      <c r="I27" s="93">
+      <c r="AC26" s="66" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="27" spans="9:29" x14ac:dyDescent="0.3">
+      <c r="I27" s="100">
         <v>3</v>
       </c>
       <c r="J27" s="94"/>
@@ -3291,12 +3480,12 @@
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="3"/>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B28" s="66" t="s">
-        <v>316</v>
-      </c>
-      <c r="I28" s="93">
+      <c r="AC27" s="66" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="28" spans="9:29" x14ac:dyDescent="0.3">
+      <c r="I28" s="100">
         <v>4</v>
       </c>
       <c r="J28" s="94"/>
@@ -3328,15 +3517,12 @@
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
       <c r="Z28" s="3"/>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>135</v>
-      </c>
-      <c r="B29" t="s">
-        <v>328</v>
-      </c>
-      <c r="I29" s="93">
+      <c r="AC28" s="66" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="29" spans="9:29" x14ac:dyDescent="0.3">
+      <c r="I29" s="100">
         <v>5.5</v>
       </c>
       <c r="J29" s="94"/>
@@ -3388,12 +3574,12 @@
       <c r="Z29" s="3">
         <v>0.83</v>
       </c>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B30" t="s">
-        <v>327</v>
-      </c>
-      <c r="I30" s="93">
+      <c r="AC29" s="66" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="30" spans="9:29" x14ac:dyDescent="0.3">
+      <c r="I30" s="100">
         <v>7.5</v>
       </c>
       <c r="J30" s="94"/>
@@ -3445,12 +3631,12 @@
       <c r="Z30" s="3">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B31" t="s">
-        <v>314</v>
-      </c>
-      <c r="I31" s="93">
+      <c r="AC30" s="66" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="31" spans="9:29" x14ac:dyDescent="0.3">
+      <c r="I31" s="100">
         <v>11</v>
       </c>
       <c r="J31" s="94"/>
@@ -3502,12 +3688,15 @@
       <c r="Z31" s="3">
         <v>0.87</v>
       </c>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B32" t="s">
+      <c r="AB31">
+        <v>135</v>
+      </c>
+      <c r="AC31" s="155" t="s">
         <v>317</v>
       </c>
-      <c r="I32" s="93">
+    </row>
+    <row r="32" spans="9:29" x14ac:dyDescent="0.3">
+      <c r="I32" s="100">
         <v>15</v>
       </c>
       <c r="J32" s="94"/>
@@ -3539,9 +3728,12 @@
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
       <c r="Z32" s="3"/>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="I33" s="93">
+      <c r="AC32" s="155" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="I33" s="100">
         <v>18.5</v>
       </c>
       <c r="J33" s="94"/>
@@ -3573,12 +3765,12 @@
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
       <c r="Z33" s="3"/>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B34" t="s">
-        <v>320</v>
-      </c>
-      <c r="I34" s="93">
+      <c r="AC33" s="155" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="I34" s="100">
         <v>22</v>
       </c>
       <c r="J34" s="94"/>
@@ -3610,12 +3802,15 @@
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
       <c r="Z34" s="3"/>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="I35" s="100">
+      <c r="AC34" s="155" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="I35" s="104">
         <v>30</v>
       </c>
-      <c r="J35" s="101"/>
+      <c r="J35" s="105"/>
       <c r="K35" s="12" t="s">
         <v>69</v>
       </c>
@@ -3644,20 +3839,20 @@
       <c r="X35" s="4"/>
       <c r="Y35" s="4"/>
       <c r="Z35" s="5"/>
-    </row>
-    <row r="36" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B36" t="s">
-        <v>318</v>
-      </c>
-      <c r="G36" s="118" t="s">
+      <c r="AC35" s="155" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="36" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="G36" s="127" t="s">
         <v>119</v>
       </c>
-      <c r="H36" s="118"/>
-      <c r="I36" s="109">
+      <c r="H36" s="127"/>
+      <c r="I36" s="117">
         <f>_xlfn.MINIFS(I21:J35,I21:J35,"&gt;="&amp;M11)</f>
         <v>7.5</v>
       </c>
-      <c r="J36" s="110"/>
+      <c r="J36" s="118"/>
       <c r="K36" s="9" t="str">
         <f>VLOOKUP($I$36,$I$21:$R$35,3)</f>
         <v>112M2</v>
@@ -3723,25 +3918,22 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B37" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B38" t="s">
-        <v>323</v>
-      </c>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AC37" s="90" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="38" spans="2:29" x14ac:dyDescent="0.3">
       <c r="C38" s="16"/>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
       <c r="F38" s="16"/>
-      <c r="G38" s="97" t="s">
+      <c r="G38" s="108" t="s">
         <v>40</v>
       </c>
-      <c r="H38" s="98"/>
-      <c r="I38" s="98"/>
-      <c r="J38" s="99"/>
+      <c r="H38" s="101"/>
+      <c r="I38" s="101"/>
+      <c r="J38" s="116"/>
       <c r="K38" s="11"/>
       <c r="L38" s="18"/>
       <c r="M38" s="18"/>
@@ -3758,21 +3950,21 @@
       <c r="X38" s="18"/>
       <c r="Y38" s="18"/>
       <c r="Z38" s="6"/>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B39" s="1" t="s">
-        <v>324</v>
-      </c>
+      <c r="AC38" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.3">
       <c r="C39" s="16"/>
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
       <c r="F39" s="16"/>
-      <c r="G39" s="93" t="s">
+      <c r="G39" s="100" t="s">
         <v>43</v>
       </c>
       <c r="H39" s="94"/>
       <c r="I39" s="94"/>
-      <c r="J39" s="105"/>
+      <c r="J39" s="111"/>
       <c r="K39" s="7"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -3801,23 +3993,23 @@
         <f>Z36*$M$9</f>
         <v>0.80009483399999992</v>
       </c>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B40" s="1" t="s">
-        <v>325</v>
-      </c>
+      <c r="AC39" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.3">
       <c r="C40" s="16"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
-      <c r="G40" s="93" t="s">
+      <c r="G40" s="100" t="s">
         <v>118</v>
       </c>
       <c r="H40" s="94"/>
       <c r="I40" s="94" t="s">
         <v>117</v>
       </c>
-      <c r="J40" s="105"/>
+      <c r="J40" s="111"/>
       <c r="K40" s="27" t="s">
         <v>120</v>
       </c>
@@ -3858,21 +4050,24 @@
       <c r="Z40" s="5" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="AC40" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.3">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
-      <c r="G41" s="115">
+      <c r="G41" s="123">
         <v>160</v>
       </c>
-      <c r="H41" s="116"/>
-      <c r="I41" s="120">
+      <c r="H41" s="124"/>
+      <c r="I41" s="112">
         <f t="shared" ref="I41:I46" si="4">$E$3*60000/PI()/G41</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="J41" s="121"/>
+      <c r="J41" s="113"/>
       <c r="K41" s="15">
         <f t="shared" ref="K41:K46" si="5">IF($I41,L$36/$I41,"-")</f>
         <v>15.15818455357075</v>
@@ -3937,24 +4132,24 @@
         <f t="shared" ref="Z41:Z46" ca="1" si="16">Y41*Z$39</f>
         <v>0.77857587564473563</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B42" s="25" t="s">
-        <v>333</v>
-      </c>
+      <c r="AC41" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.3">
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-      <c r="G42" s="117">
+      <c r="G42" s="125">
         <v>200</v>
       </c>
-      <c r="H42" s="103"/>
-      <c r="I42" s="122">
+      <c r="H42" s="126"/>
+      <c r="I42" s="103">
         <f t="shared" si="4"/>
         <v>152.78874536821954</v>
       </c>
-      <c r="J42" s="123"/>
+      <c r="J42" s="114"/>
       <c r="K42" s="13">
         <f t="shared" si="5"/>
         <v>18.947730691963439</v>
@@ -4016,24 +4211,24 @@
         <f t="shared" ca="1" si="16"/>
         <v>0.77619649168341942</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B43" s="25" t="s">
-        <v>326</v>
-      </c>
+      <c r="AC42" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.3">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
-      <c r="G43" s="93">
+      <c r="G43" s="100">
         <v>250</v>
       </c>
       <c r="H43" s="94"/>
-      <c r="I43" s="122">
+      <c r="I43" s="103">
         <f t="shared" si="4"/>
         <v>122.23099629457563</v>
       </c>
-      <c r="J43" s="123"/>
+      <c r="J43" s="114"/>
       <c r="K43" s="13">
         <f t="shared" si="5"/>
         <v>23.684663364954297</v>
@@ -4096,20 +4291,20 @@
         <v>0.77322226173177433</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.3">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
-      <c r="G44" s="93">
+      <c r="G44" s="100">
         <v>315</v>
       </c>
       <c r="H44" s="94"/>
-      <c r="I44" s="122">
+      <c r="I44" s="103">
         <f t="shared" si="4"/>
         <v>97.008727217917169</v>
       </c>
-      <c r="J44" s="123"/>
+      <c r="J44" s="114"/>
       <c r="K44" s="13">
         <f t="shared" si="5"/>
         <v>29.842675839842414</v>
@@ -4165,24 +4360,24 @@
         <f t="shared" ca="1" si="16"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B45" s="1" t="s">
-        <v>334</v>
-      </c>
+      <c r="AC44" s="25" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.3">
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="93">
+      <c r="G45" s="100">
         <v>400</v>
       </c>
       <c r="H45" s="94"/>
-      <c r="I45" s="122">
+      <c r="I45" s="103">
         <f t="shared" si="4"/>
         <v>76.394372684109769</v>
       </c>
-      <c r="J45" s="123"/>
+      <c r="J45" s="114"/>
       <c r="K45" s="13">
         <f t="shared" si="5"/>
         <v>37.895461383926879</v>
@@ -4235,24 +4430,24 @@
         <f t="shared" ca="1" si="16"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B46" s="49" t="s">
-        <v>319</v>
-      </c>
+      <c r="AC45" s="25" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.3">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-      <c r="G46" s="100">
+      <c r="G46" s="104">
         <v>500</v>
       </c>
-      <c r="H46" s="101"/>
-      <c r="I46" s="124">
+      <c r="H46" s="105"/>
+      <c r="I46" s="107">
         <f t="shared" si="4"/>
         <v>61.115498147287816</v>
       </c>
-      <c r="J46" s="125"/>
+      <c r="J46" s="115"/>
       <c r="K46" s="14">
         <f t="shared" si="5"/>
         <v>47.369326729908593</v>
@@ -4317,7 +4512,7 @@
         <v>0.75835111197354876</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -4343,19 +4538,22 @@
       <c r="X47" s="1"/>
       <c r="Y47" s="30"/>
       <c r="Z47" s="1"/>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B48" s="97" t="s">
+      <c r="AC47" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B48" s="108" t="s">
         <v>108</v>
       </c>
-      <c r="C48" s="98"/>
-      <c r="D48" s="98"/>
-      <c r="E48" s="98"/>
-      <c r="F48" s="98" t="str">
+      <c r="C48" s="101"/>
+      <c r="D48" s="101"/>
+      <c r="E48" s="101"/>
+      <c r="F48" s="101" t="str">
         <f>P46</f>
         <v>Цилиндрическая 1</v>
       </c>
-      <c r="G48" s="99"/>
+      <c r="G48" s="116"/>
       <c r="H48" s="16"/>
       <c r="I48" s="16"/>
       <c r="J48" s="16"/>
@@ -4379,9 +4577,12 @@
       <c r="X48" s="1"/>
       <c r="Y48" s="30"/>
       <c r="Z48" s="1"/>
+      <c r="AC48" s="49" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="49" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B49" s="93" t="s">
+      <c r="B49" s="100" t="s">
         <v>41</v>
       </c>
       <c r="C49" s="94"/>
@@ -4411,7 +4612,7 @@
       <c r="Z49" s="1"/>
     </row>
     <row r="50" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B50" s="93" t="s">
+      <c r="B50" s="100" t="s">
         <v>96</v>
       </c>
       <c r="C50" s="94"/>
@@ -4422,7 +4623,7 @@
         <v>1440</v>
       </c>
       <c r="G50" s="50" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="H50" s="16"/>
       <c r="P50" s="1"/>
@@ -4433,7 +4634,7 @@
       <c r="Z50" s="1"/>
     </row>
     <row r="51" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B51" s="93" t="s">
+      <c r="B51" s="100" t="s">
         <v>103</v>
       </c>
       <c r="C51" s="94"/>
@@ -4444,32 +4645,32 @@
         <v>150.79644737231007</v>
       </c>
       <c r="G51" s="50" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="H51" s="16"/>
-      <c r="I51" s="109" t="s">
+      <c r="I51" s="117" t="s">
         <v>112</v>
       </c>
-      <c r="J51" s="111"/>
+      <c r="J51" s="119"/>
       <c r="K51" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="L51" s="98" t="s">
+      <c r="L51" s="101" t="s">
         <v>120</v>
       </c>
-      <c r="M51" s="98"/>
-      <c r="N51" s="126" t="s">
+      <c r="M51" s="101"/>
+      <c r="N51" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="O51" s="126"/>
-      <c r="P51" s="98" t="s">
+      <c r="O51" s="98"/>
+      <c r="P51" s="101" t="s">
         <v>114</v>
       </c>
-      <c r="Q51" s="98"/>
-      <c r="R51" s="126" t="s">
+      <c r="Q51" s="101"/>
+      <c r="R51" s="98" t="s">
         <v>116</v>
       </c>
-      <c r="S51" s="126"/>
+      <c r="S51" s="98"/>
       <c r="T51" s="49"/>
       <c r="U51" s="49"/>
       <c r="V51" s="49"/>
@@ -4478,7 +4679,7 @@
       <c r="Z51" s="1"/>
     </row>
     <row r="52" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B52" s="93" t="s">
+      <c r="B52" s="100" t="s">
         <v>42</v>
       </c>
       <c r="C52" s="94"/>
@@ -4489,10 +4690,10 @@
         <v>190.98593171027443</v>
       </c>
       <c r="G52" s="50" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="H52" s="16"/>
-      <c r="I52" s="93" t="s">
+      <c r="I52" s="100" t="s">
         <v>115</v>
       </c>
       <c r="J52" s="94"/>
@@ -4500,25 +4701,25 @@
         <f>R36</f>
         <v>0.872</v>
       </c>
-      <c r="L52" s="98">
+      <c r="L52" s="101">
         <v>1</v>
       </c>
-      <c r="M52" s="98"/>
-      <c r="N52" s="129">
+      <c r="M52" s="101"/>
+      <c r="N52" s="96">
         <f>F50</f>
         <v>1440</v>
       </c>
-      <c r="O52" s="129"/>
-      <c r="P52" s="128">
+      <c r="O52" s="96"/>
+      <c r="P52" s="102">
         <f>F55</f>
         <v>49.735919716217296</v>
       </c>
-      <c r="Q52" s="128"/>
-      <c r="R52" s="126">
+      <c r="Q52" s="102"/>
+      <c r="R52" s="98">
         <f t="shared" ref="R52:R54" si="17">P52*N52*PI()/1000/30</f>
         <v>7.5000000000000009</v>
       </c>
-      <c r="S52" s="126"/>
+      <c r="S52" s="98"/>
       <c r="T52" s="16"/>
       <c r="U52" s="30"/>
       <c r="X52" s="1"/>
@@ -4526,7 +4727,7 @@
       <c r="Z52" s="1"/>
     </row>
     <row r="53" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B53" s="93" t="s">
+      <c r="B53" s="100" t="s">
         <v>105</v>
       </c>
       <c r="C53" s="94"/>
@@ -4540,7 +4741,7 @@
         <v>16</v>
       </c>
       <c r="H53" s="16"/>
-      <c r="I53" s="93" t="s">
+      <c r="I53" s="100" t="s">
         <v>28</v>
       </c>
       <c r="J53" s="94"/>
@@ -4552,21 +4753,21 @@
         <v>1</v>
       </c>
       <c r="M53" s="94"/>
-      <c r="N53" s="130">
+      <c r="N53" s="97">
         <f>N52/L53</f>
         <v>1440</v>
       </c>
-      <c r="O53" s="130"/>
-      <c r="P53" s="106">
+      <c r="O53" s="97"/>
+      <c r="P53" s="95">
         <f>P52*L53*K53</f>
         <v>48.741201321892952</v>
       </c>
-      <c r="Q53" s="106"/>
-      <c r="R53" s="127">
+      <c r="Q53" s="95"/>
+      <c r="R53" s="99">
         <f t="shared" si="17"/>
         <v>7.3500000000000005</v>
       </c>
-      <c r="S53" s="127"/>
+      <c r="S53" s="99"/>
       <c r="T53" s="1"/>
       <c r="U53" s="67"/>
       <c r="V53" s="68"/>
@@ -4575,7 +4776,7 @@
       <c r="Z53" s="1"/>
     </row>
     <row r="54" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B54" s="93" t="s">
+      <c r="B54" s="100" t="s">
         <v>97</v>
       </c>
       <c r="C54" s="94"/>
@@ -4589,7 +4790,7 @@
         <v>99</v>
       </c>
       <c r="H54" s="16"/>
-      <c r="I54" s="93" t="s">
+      <c r="I54" s="100" t="s">
         <v>95</v>
       </c>
       <c r="J54" s="94"/>
@@ -4601,21 +4802,21 @@
         <v>1</v>
       </c>
       <c r="M54" s="94"/>
-      <c r="N54" s="130">
+      <c r="N54" s="97">
         <f>N53/L54</f>
         <v>1440</v>
       </c>
-      <c r="O54" s="130"/>
-      <c r="P54" s="106">
+      <c r="O54" s="97"/>
+      <c r="P54" s="95">
         <f>P53*L54*K54</f>
         <v>48.253789308674023</v>
       </c>
-      <c r="Q54" s="106"/>
-      <c r="R54" s="127">
+      <c r="Q54" s="95"/>
+      <c r="R54" s="99">
         <f t="shared" si="17"/>
         <v>7.2765000000000004</v>
       </c>
-      <c r="S54" s="127"/>
+      <c r="S54" s="99"/>
       <c r="T54" s="1"/>
       <c r="U54" s="67"/>
       <c r="V54" s="68"/>
@@ -4625,7 +4826,7 @@
       <c r="Z54" s="1"/>
     </row>
     <row r="55" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B55" s="93" t="s">
+      <c r="B55" s="100" t="s">
         <v>98</v>
       </c>
       <c r="C55" s="94"/>
@@ -4639,7 +4840,7 @@
         <v>99</v>
       </c>
       <c r="H55" s="16"/>
-      <c r="I55" s="93" t="s">
+      <c r="I55" s="100" t="s">
         <v>94</v>
       </c>
       <c r="J55" s="94"/>
@@ -4647,26 +4848,26 @@
         <f ca="1">Q41</f>
         <v>0.96143805509807656</v>
       </c>
-      <c r="L55" s="106">
+      <c r="L55" s="95">
         <f>F49</f>
         <v>7.5398223686155026</v>
       </c>
-      <c r="M55" s="106"/>
-      <c r="N55" s="106">
+      <c r="M55" s="95"/>
+      <c r="N55" s="95">
         <f>N54/L55</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O55" s="106"/>
-      <c r="P55" s="122">
+      <c r="O55" s="95"/>
+      <c r="P55" s="103">
         <f ca="1">P54*L55*K55</f>
         <v>349.79520039605768</v>
       </c>
-      <c r="Q55" s="122"/>
-      <c r="R55" s="127">
+      <c r="Q55" s="103"/>
+      <c r="R55" s="99">
         <f ca="1">P55*N55*PI()/1000/30</f>
         <v>6.9959040079211547</v>
       </c>
-      <c r="S55" s="127"/>
+      <c r="S55" s="99"/>
       <c r="T55" s="1"/>
       <c r="U55" s="67"/>
       <c r="V55" s="68"/>
@@ -4676,8 +4877,8 @@
       <c r="Z55" s="1"/>
     </row>
     <row r="56" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B56" s="93" t="s">
-        <v>298</v>
+      <c r="B56" s="100" t="s">
+        <v>288</v>
       </c>
       <c r="C56" s="94"/>
       <c r="D56" s="94"/>
@@ -4689,7 +4890,7 @@
       <c r="G56" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="I56" s="93" t="s">
+      <c r="I56" s="100" t="s">
         <v>28</v>
       </c>
       <c r="J56" s="94"/>
@@ -4701,27 +4902,27 @@
         <v>1</v>
       </c>
       <c r="M56" s="94"/>
-      <c r="N56" s="106">
+      <c r="N56" s="95">
         <f>N55/L56</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O56" s="106"/>
-      <c r="P56" s="122">
+      <c r="O56" s="95"/>
+      <c r="P56" s="103">
         <f ca="1">P55*L56*K56</f>
         <v>342.7992963881365</v>
       </c>
-      <c r="Q56" s="122"/>
-      <c r="R56" s="127">
+      <c r="Q56" s="103"/>
+      <c r="R56" s="99">
         <f ca="1">P56*N56*PI()/1000/30</f>
         <v>6.8559859277627302</v>
       </c>
-      <c r="S56" s="127"/>
+      <c r="S56" s="99"/>
       <c r="T56" s="1"/>
       <c r="U56" s="67"/>
       <c r="V56" s="68"/>
     </row>
     <row r="57" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B57" s="93" t="s">
+      <c r="B57" s="100" t="s">
         <v>101</v>
       </c>
       <c r="C57" s="94"/>
@@ -4732,7 +4933,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="G57" s="50"/>
-      <c r="I57" s="93" t="s">
+      <c r="I57" s="100" t="s">
         <v>95</v>
       </c>
       <c r="J57" s="94"/>
@@ -4744,27 +4945,27 @@
         <v>1</v>
       </c>
       <c r="M57" s="94"/>
-      <c r="N57" s="106">
+      <c r="N57" s="95">
         <f>N56/L57</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O57" s="106"/>
-      <c r="P57" s="122">
+      <c r="O57" s="95"/>
+      <c r="P57" s="103">
         <f ca="1">P56*L57*K57</f>
         <v>339.37130342425513</v>
       </c>
-      <c r="Q57" s="122"/>
-      <c r="R57" s="127">
+      <c r="Q57" s="103"/>
+      <c r="R57" s="99">
         <f ca="1">P57*N57*PI()/1000/30</f>
         <v>6.7874260684851038</v>
       </c>
-      <c r="S57" s="127"/>
+      <c r="S57" s="99"/>
       <c r="T57" s="1"/>
       <c r="U57" s="67"/>
       <c r="V57" s="68"/>
     </row>
     <row r="58" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B58" s="93" t="s">
+      <c r="B58" s="100" t="s">
         <v>102</v>
       </c>
       <c r="C58" s="94"/>
@@ -4775,23 +4976,23 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="G58" s="50"/>
-      <c r="I58" s="100" t="s">
-        <v>136</v>
-      </c>
-      <c r="J58" s="101"/>
+      <c r="I58" s="104" t="s">
+        <v>131</v>
+      </c>
+      <c r="J58" s="105"/>
       <c r="K58" s="12"/>
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
-      <c r="N58" s="95">
+      <c r="N58" s="106">
         <f>N57</f>
         <v>190.98593171027443</v>
       </c>
-      <c r="O58" s="95"/>
-      <c r="P58" s="124">
+      <c r="O58" s="106"/>
+      <c r="P58" s="107">
         <f ca="1">P57</f>
         <v>339.37130342425513</v>
       </c>
-      <c r="Q58" s="124"/>
+      <c r="Q58" s="107"/>
       <c r="R58" s="4"/>
       <c r="S58" s="4"/>
       <c r="T58" s="16"/>
@@ -4799,7 +5000,7 @@
       <c r="V58" s="16"/>
     </row>
     <row r="59" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B59" s="93" t="s">
+      <c r="B59" s="100" t="s">
         <v>107</v>
       </c>
       <c r="C59" s="94"/>
@@ -4812,7 +5013,7 @@
       <c r="G59" s="50"/>
     </row>
     <row r="60" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B60" s="93" t="s">
+      <c r="B60" s="100" t="s">
         <v>109</v>
       </c>
       <c r="C60" s="94"/>
@@ -4826,7 +5027,7 @@
     </row>
     <row r="61" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B61" s="94" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C61" s="94"/>
       <c r="D61" s="94"/>
@@ -4857,16 +5058,123 @@
     </row>
   </sheetData>
   <mergeCells count="151">
-    <mergeCell ref="L54:M54"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="L57:M57"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="N56:O56"/>
-    <mergeCell ref="N57:O57"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="S19:V19"/>
+    <mergeCell ref="W19:Z19"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="AC8:AE8"/>
+    <mergeCell ref="AC6:AE6"/>
+    <mergeCell ref="K19:N19"/>
+    <mergeCell ref="AC2:AE2"/>
+    <mergeCell ref="AC3:AE3"/>
+    <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="AC5:AE5"/>
+    <mergeCell ref="AC7:AE7"/>
+    <mergeCell ref="AC10:AE10"/>
+    <mergeCell ref="AC9:AE9"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="Q6:S6"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B56:E56"/>
     <mergeCell ref="R51:S51"/>
     <mergeCell ref="R52:S52"/>
     <mergeCell ref="R53:S53"/>
@@ -4891,123 +5199,16 @@
     <mergeCell ref="L51:M51"/>
     <mergeCell ref="L52:M52"/>
     <mergeCell ref="L53:M53"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="I58:J58"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="Q6:S6"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="G39:J39"/>
-    <mergeCell ref="G38:J38"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="AC8:AE8"/>
-    <mergeCell ref="AC6:AE6"/>
-    <mergeCell ref="K19:N19"/>
-    <mergeCell ref="AC2:AE2"/>
-    <mergeCell ref="AC3:AE3"/>
-    <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="AC5:AE5"/>
-    <mergeCell ref="AC7:AE7"/>
-    <mergeCell ref="AC10:AE10"/>
-    <mergeCell ref="AC9:AE9"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="I4:N4"/>
-    <mergeCell ref="I3:N3"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="S19:V19"/>
-    <mergeCell ref="W19:Z19"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="L54:M54"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="N56:O56"/>
+    <mergeCell ref="N57:O57"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -5023,33 +5224,33 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="118" t="s">
-        <v>173</v>
-      </c>
-      <c r="B2" s="118"/>
-      <c r="C2" s="118"/>
-      <c r="D2" s="118"/>
-      <c r="E2" s="118"/>
-      <c r="H2" s="118" t="s">
-        <v>186</v>
-      </c>
-      <c r="I2" s="118"/>
-      <c r="J2" s="118"/>
-      <c r="K2" s="118"/>
-      <c r="L2" s="118"/>
-      <c r="P2" s="118" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q2" s="118"/>
-      <c r="R2" s="118"/>
-      <c r="S2" s="118"/>
-      <c r="T2" s="118"/>
+      <c r="A2" s="127" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2" s="127"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127"/>
+      <c r="H2" s="127" t="s">
+        <v>181</v>
+      </c>
+      <c r="I2" s="127"/>
+      <c r="J2" s="127"/>
+      <c r="K2" s="127"/>
+      <c r="L2" s="127"/>
+      <c r="P2" s="127" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q2" s="127"/>
+      <c r="R2" s="127"/>
+      <c r="S2" s="127"/>
+      <c r="T2" s="127"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="118" t="s">
-        <v>172</v>
-      </c>
-      <c r="B3" s="118"/>
+      <c r="A3" s="127" t="s">
+        <v>167</v>
+      </c>
+      <c r="B3" s="127"/>
       <c r="D3" s="61">
         <f>Электродвигатель!$P$53</f>
         <v>48.741201321892952</v>
@@ -5058,7 +5259,7 @@
         <v>99</v>
       </c>
       <c r="H3" s="94" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="I3" s="94"/>
       <c r="J3" s="94"/>
@@ -5070,7 +5271,7 @@
         <v>99</v>
       </c>
       <c r="P3" s="16" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="R3" s="16"/>
       <c r="S3">
@@ -5082,10 +5283,10 @@
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="118" t="s">
+      <c r="A4" s="127" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="118"/>
+      <c r="B4" s="127"/>
       <c r="D4" s="62">
         <f>Электродвигатель!$N$52</f>
         <v>1440</v>
@@ -5103,7 +5304,7 @@
         <v>1440</v>
       </c>
       <c r="L4" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="P4" s="16" t="s">
         <v>70</v>
@@ -5119,27 +5320,27 @@
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H5" s="118" t="s">
-        <v>176</v>
-      </c>
-      <c r="I5" s="118"/>
-      <c r="J5" s="118"/>
-      <c r="K5" s="118"/>
-      <c r="L5" s="118"/>
-      <c r="P5" s="118" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q5" s="118"/>
-      <c r="R5" s="118"/>
-      <c r="S5" s="118"/>
-      <c r="T5" s="118"/>
+      <c r="H5" s="127" t="s">
+        <v>171</v>
+      </c>
+      <c r="I5" s="127"/>
+      <c r="J5" s="127"/>
+      <c r="K5" s="127"/>
+      <c r="L5" s="127"/>
+      <c r="P5" s="127" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q5" s="127"/>
+      <c r="R5" s="127"/>
+      <c r="S5" s="127"/>
+      <c r="T5" s="127"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="118" t="s">
+      <c r="A6" s="127" t="s">
         <v>118</v>
       </c>
-      <c r="B6" s="118"/>
-      <c r="C6" s="118"/>
+      <c r="B6" s="127"/>
+      <c r="C6" s="127"/>
       <c r="D6" s="66">
         <f>Электродвигатель!$F$61</f>
         <v>38</v>
@@ -5147,11 +5348,11 @@
       <c r="E6" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="118" t="s">
-        <v>175</v>
-      </c>
-      <c r="I6" s="118"/>
-      <c r="J6" s="118"/>
+      <c r="H6" s="127" t="s">
+        <v>170</v>
+      </c>
+      <c r="I6" s="127"/>
+      <c r="J6" s="127"/>
       <c r="K6">
         <f>Передача!D55</f>
         <v>37.75</v>
@@ -5159,11 +5360,11 @@
       <c r="L6" t="s">
         <v>16</v>
       </c>
-      <c r="P6" s="118" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q6" s="118"/>
-      <c r="R6" s="118"/>
+      <c r="P6" s="127" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q6" s="127"/>
+      <c r="R6" s="127"/>
       <c r="S6">
         <f>Передача!D60</f>
         <v>309.75</v>
@@ -5173,19 +5374,19 @@
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="131" t="s">
-        <v>198</v>
-      </c>
-      <c r="B7" s="131"/>
-      <c r="C7" s="131"/>
+      <c r="A7" s="132" t="s">
+        <v>193</v>
+      </c>
+      <c r="B7" s="132"/>
+      <c r="C7" s="132"/>
       <c r="D7" s="52">
         <v>0.8</v>
       </c>
-      <c r="H7" s="118" t="s">
-        <v>184</v>
-      </c>
-      <c r="I7" s="118"/>
-      <c r="J7" s="118"/>
+      <c r="H7" s="127" t="s">
+        <v>179</v>
+      </c>
+      <c r="I7" s="127"/>
+      <c r="J7" s="127"/>
       <c r="K7">
         <f>Передача!D54</f>
         <v>49</v>
@@ -5193,11 +5394,11 @@
       <c r="L7" t="s">
         <v>16</v>
       </c>
-      <c r="P7" s="118" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q7" s="118"/>
-      <c r="R7" s="118"/>
+      <c r="P7" s="127" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q7" s="127"/>
+      <c r="R7" s="127"/>
       <c r="S7">
         <f>Передача!D59</f>
         <v>321</v>
@@ -5207,19 +5408,19 @@
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="118" t="s">
-        <v>194</v>
-      </c>
-      <c r="B8" s="118"/>
-      <c r="C8" s="118"/>
+      <c r="A8" s="127" t="s">
+        <v>189</v>
+      </c>
+      <c r="B8" s="127"/>
+      <c r="C8" s="127"/>
       <c r="D8" s="71">
         <v>1.2</v>
       </c>
-      <c r="H8" s="118" t="s">
-        <v>165</v>
-      </c>
-      <c r="I8" s="118"/>
-      <c r="J8" s="118"/>
+      <c r="H8" s="127" t="s">
+        <v>160</v>
+      </c>
+      <c r="I8" s="127"/>
+      <c r="J8" s="127"/>
       <c r="K8">
         <f>Передача!D56</f>
         <v>62</v>
@@ -5227,11 +5428,11 @@
       <c r="L8" t="s">
         <v>16</v>
       </c>
-      <c r="P8" s="118" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q8" s="118"/>
-      <c r="R8" s="118"/>
+      <c r="P8" s="127" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q8" s="127"/>
+      <c r="R8" s="127"/>
       <c r="S8">
         <f>Передача!D61</f>
         <v>57</v>
@@ -5241,51 +5442,51 @@
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H9" s="118" t="s">
-        <v>187</v>
-      </c>
-      <c r="I9" s="118"/>
-      <c r="J9" s="118"/>
-      <c r="K9" s="118"/>
-      <c r="L9" s="118"/>
-      <c r="P9" s="118" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q9" s="118"/>
-      <c r="R9" s="118"/>
-      <c r="S9" s="118"/>
-      <c r="T9" s="118"/>
+      <c r="H9" s="127" t="s">
+        <v>182</v>
+      </c>
+      <c r="I9" s="127"/>
+      <c r="J9" s="127"/>
+      <c r="K9" s="127"/>
+      <c r="L9" s="127"/>
+      <c r="P9" s="127" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q9" s="127"/>
+      <c r="R9" s="127"/>
+      <c r="S9" s="127"/>
+      <c r="T9" s="127"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H10" s="118" t="s">
-        <v>183</v>
-      </c>
-      <c r="I10" s="118"/>
-      <c r="J10" s="118"/>
+      <c r="H10" s="127" t="s">
+        <v>178</v>
+      </c>
+      <c r="I10" s="127"/>
+      <c r="J10" s="127"/>
       <c r="K10">
         <v>7.5</v>
       </c>
       <c r="L10" s="65" t="s">
-        <v>190</v>
-      </c>
-      <c r="P10" s="118" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q10" s="118"/>
-      <c r="R10" s="118"/>
+        <v>185</v>
+      </c>
+      <c r="P10" s="127" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q10" s="127"/>
+      <c r="R10" s="127"/>
       <c r="S10">
         <v>5.4</v>
       </c>
       <c r="T10" s="65" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H11" s="118" t="s">
-        <v>195</v>
-      </c>
-      <c r="I11" s="118"/>
-      <c r="J11" s="118"/>
+      <c r="H11" s="127" t="s">
+        <v>190</v>
+      </c>
+      <c r="I11" s="127"/>
+      <c r="J11" s="127"/>
       <c r="K11">
         <f>K10*(K3)^(1/3)</f>
         <v>27.396389985469561</v>
@@ -5293,11 +5494,11 @@
       <c r="L11" t="s">
         <v>16</v>
       </c>
-      <c r="P11" s="118" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q11" s="118"/>
-      <c r="R11" s="118"/>
+      <c r="P11" s="127" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q11" s="127"/>
+      <c r="R11" s="127"/>
       <c r="S11">
         <f ca="1">S10*(S3)^(1/3)</f>
         <v>38.047989101548296</v>
@@ -5307,11 +5508,11 @@
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H12" s="118" t="s">
-        <v>199</v>
-      </c>
-      <c r="I12" s="118"/>
-      <c r="J12" s="118"/>
+      <c r="H12" s="127" t="s">
+        <v>194</v>
+      </c>
+      <c r="I12" s="127"/>
+      <c r="J12" s="127"/>
       <c r="K12">
         <f>MIN(MAX(K11,D6/D8),D6/D7)</f>
         <v>31.666666666666668</v>
@@ -5319,11 +5520,11 @@
       <c r="L12" t="s">
         <v>16</v>
       </c>
-      <c r="P12" s="118" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q12" s="118"/>
-      <c r="R12" s="118"/>
+      <c r="P12" s="127" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q12" s="127"/>
+      <c r="R12" s="127"/>
       <c r="S12" s="66">
         <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;S11)</f>
         <v>40</v>
@@ -5332,15 +5533,15 @@
         <v>16</v>
       </c>
       <c r="U12" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H13" s="118" t="s">
-        <v>188</v>
-      </c>
-      <c r="I13" s="118"/>
-      <c r="J13" s="118"/>
+      <c r="H13" s="127" t="s">
+        <v>183</v>
+      </c>
+      <c r="I13" s="127"/>
+      <c r="J13" s="127"/>
       <c r="K13" s="66">
         <f>_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;K12)</f>
         <v>32</v>
@@ -5349,13 +5550,13 @@
         <v>16</v>
       </c>
       <c r="M13" t="s">
-        <v>197</v>
-      </c>
-      <c r="P13" s="118" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q13" s="118"/>
-      <c r="R13" s="118"/>
+        <v>192</v>
+      </c>
+      <c r="P13" s="127" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q13" s="127"/>
+      <c r="R13" s="127"/>
       <c r="S13">
         <f ca="1">_xlfn.MINIFS($28:$28,$26:$26,"&gt;="&amp;S12)</f>
         <v>3.5</v>
@@ -5365,20 +5566,20 @@
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="118" t="s">
-        <v>283</v>
-      </c>
-      <c r="B14" s="118"/>
-      <c r="C14" s="118"/>
+      <c r="A14" s="127" t="s">
+        <v>276</v>
+      </c>
+      <c r="B14" s="127"/>
+      <c r="C14" s="127"/>
       <c r="D14">
         <f>Электродвигатель!$F$58</f>
         <v>2.2000000000000002</v>
       </c>
-      <c r="H14" s="118" t="s">
-        <v>196</v>
-      </c>
-      <c r="I14" s="118"/>
-      <c r="J14" s="118"/>
+      <c r="H14" s="127" t="s">
+        <v>191</v>
+      </c>
+      <c r="I14" s="127"/>
+      <c r="J14" s="127"/>
       <c r="K14">
         <f>_xlfn.MINIFS($28:$28,$26:$26,"&gt;="&amp;K13)</f>
         <v>3.5</v>
@@ -5386,11 +5587,11 @@
       <c r="L14" t="s">
         <v>16</v>
       </c>
-      <c r="P14" s="118" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q14" s="118"/>
-      <c r="R14" s="118"/>
+      <c r="P14" s="127" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q14" s="127"/>
+      <c r="R14" s="127"/>
       <c r="S14">
         <f ca="1">S12+2*S13</f>
         <v>47</v>
@@ -5400,11 +5601,11 @@
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H15" s="118" t="s">
-        <v>192</v>
-      </c>
-      <c r="I15" s="118"/>
-      <c r="J15" s="118"/>
+      <c r="H15" s="127" t="s">
+        <v>187</v>
+      </c>
+      <c r="I15" s="127"/>
+      <c r="J15" s="127"/>
       <c r="K15">
         <f>K13+2*K14</f>
         <v>39</v>
@@ -5412,11 +5613,11 @@
       <c r="L15" t="s">
         <v>16</v>
       </c>
-      <c r="P15" s="118" t="s">
-        <v>262</v>
-      </c>
-      <c r="Q15" s="118"/>
-      <c r="R15" s="118"/>
+      <c r="P15" s="127" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q15" s="127"/>
+      <c r="R15" s="127"/>
       <c r="S15" s="66">
         <f ca="1">_xlfn.MINIFS(Подшипники!$A:$A,Подшипники!$A:$A,"&gt;="&amp;S14)</f>
         <v>50</v>
@@ -5426,11 +5627,11 @@
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H16" s="118" t="s">
-        <v>262</v>
-      </c>
-      <c r="I16" s="118"/>
-      <c r="J16" s="118"/>
+      <c r="H16" s="127" t="s">
+        <v>255</v>
+      </c>
+      <c r="I16" s="127"/>
+      <c r="J16" s="127"/>
       <c r="K16" s="66">
         <f>_xlfn.MINIFS(Подшипники!$A:$A,Подшипники!$A:$A,"&gt;="&amp;K15)</f>
         <v>40</v>
@@ -5438,96 +5639,165 @@
       <c r="L16" t="s">
         <v>16</v>
       </c>
-      <c r="P16" s="118" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q16" s="118"/>
-      <c r="R16" s="118"/>
+      <c r="P16" s="127" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q16" s="127"/>
+      <c r="R16" s="127"/>
       <c r="S16">
+        <f ca="1">_xlfn.MINIFS(Подшипники!$E$12:$E$24,Подшипники!$A$12:$A$24,"="&amp;$S$15)</f>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="H17" s="127" t="s">
+        <v>251</v>
+      </c>
+      <c r="I17" s="127"/>
+      <c r="J17" s="127"/>
+      <c r="K17">
+        <f>_xlfn.MINIFS(Подшипники!$E$12:$E$24,Подшипники!$A$12:$A$24,"="&amp;$K$16)</f>
+        <v>208</v>
+      </c>
+      <c r="P17" s="127" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q17" s="127"/>
+      <c r="R17" s="127"/>
+      <c r="S17">
+        <f ca="1">_xlfn.MINIFS(Подшипники!$F$12:$F$24,Подшипники!$E$12:$E$24,"="&amp;$S$16)</f>
+        <v>90</v>
+      </c>
+      <c r="T17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="H18" s="127" t="s">
+        <v>345</v>
+      </c>
+      <c r="I18" s="127"/>
+      <c r="J18" s="127"/>
+      <c r="K18">
+        <f>_xlfn.MINIFS(Подшипники!$F$12:$F$24,Подшипники!$E$12:$E$24,"="&amp;$K$17)</f>
+        <v>80</v>
+      </c>
+      <c r="L18" t="s">
+        <v>16</v>
+      </c>
+      <c r="P18" s="127" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q18" s="127"/>
+      <c r="R18" s="127"/>
+      <c r="S18">
+        <f ca="1">_xlfn.MINIFS(Подшипники!G12:G24,Подшипники!$E$12:$E$24,"="&amp;$S$16)</f>
+        <v>20</v>
+      </c>
+      <c r="T18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="H19" s="127" t="s">
+        <v>191</v>
+      </c>
+      <c r="I19" s="127"/>
+      <c r="J19" s="127"/>
+      <c r="K19">
+        <f>_xlfn.MINIFS($29:$29,$26:$26,"&gt;="&amp;K13)</f>
+        <v>2</v>
+      </c>
+      <c r="L19" t="s">
+        <v>16</v>
+      </c>
+      <c r="P19" s="127" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q19" s="127"/>
+      <c r="R19" s="127"/>
+      <c r="S19">
         <f ca="1">_xlfn.MINIFS($29:$29,$26:$26,"&gt;="&amp;S12)</f>
         <v>2.2999999999999998</v>
       </c>
-      <c r="T16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H17" s="118" t="s">
-        <v>196</v>
-      </c>
-      <c r="I17" s="118"/>
-      <c r="J17" s="118"/>
-      <c r="K17">
-        <f>_xlfn.MINIFS($29:$29,$26:$26,"&gt;="&amp;K13)</f>
-        <v>2</v>
-      </c>
-      <c r="L17" t="s">
-        <v>16</v>
-      </c>
-      <c r="P17" s="118" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q17" s="118"/>
-      <c r="R17" s="118"/>
-      <c r="S17">
-        <f ca="1">S15+2*S16</f>
+      <c r="T19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="H20" s="127" t="s">
+        <v>188</v>
+      </c>
+      <c r="I20" s="127"/>
+      <c r="J20" s="127"/>
+      <c r="K20">
+        <f>K16+2*K19</f>
+        <v>44</v>
+      </c>
+      <c r="L20" t="s">
+        <v>16</v>
+      </c>
+      <c r="P20" s="127" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q20" s="127"/>
+      <c r="R20" s="127"/>
+      <c r="S20">
+        <f ca="1">S15+2*S19</f>
         <v>54.6</v>
       </c>
-      <c r="T17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H18" s="118" t="s">
-        <v>193</v>
-      </c>
-      <c r="I18" s="118"/>
-      <c r="J18" s="118"/>
-      <c r="K18">
-        <f>K16+2*K17</f>
-        <v>44</v>
-      </c>
-      <c r="L18" t="s">
-        <v>16</v>
-      </c>
-      <c r="P18" s="118" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q18" s="118"/>
-      <c r="R18" s="118"/>
-      <c r="S18" s="66">
-        <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;S17)</f>
+      <c r="T20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="H21" s="127" t="s">
+        <v>184</v>
+      </c>
+      <c r="I21" s="127"/>
+      <c r="J21" s="127"/>
+      <c r="K21" s="66">
+        <f>_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;K20)</f>
+        <v>45</v>
+      </c>
+      <c r="L21" t="s">
+        <v>16</v>
+      </c>
+      <c r="M21" t="s">
+        <v>192</v>
+      </c>
+      <c r="P21" s="127" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q21" s="127"/>
+      <c r="R21" s="127"/>
+      <c r="S21" s="66">
+        <f ca="1">S15</f>
+        <v>50</v>
+      </c>
+      <c r="T21" t="s">
+        <v>16</v>
+      </c>
+      <c r="U21" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="S22">
+        <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;S20)</f>
         <v>56</v>
       </c>
-      <c r="T18" t="s">
-        <v>16</v>
-      </c>
-      <c r="U18" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H19" s="118" t="s">
-        <v>189</v>
-      </c>
-      <c r="I19" s="118"/>
-      <c r="J19" s="118"/>
-      <c r="K19" s="66">
-        <f>_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;K18)</f>
-        <v>45</v>
-      </c>
-      <c r="L19" t="s">
-        <v>16</v>
-      </c>
-      <c r="M19" t="s">
-        <v>197</v>
-      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P23" s="48"/>
+      <c r="Q23" s="48"/>
+      <c r="R23" s="48"/>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A26" s="118" t="s">
-        <v>181</v>
-      </c>
-      <c r="B26" s="118"/>
+      <c r="A26" s="127" t="s">
+        <v>176</v>
+      </c>
+      <c r="B26" s="127"/>
       <c r="C26">
         <v>17</v>
       </c>
@@ -5559,14 +5829,14 @@
         <v>90</v>
       </c>
       <c r="S26" t="s">
-        <v>297</v>
+        <v>334</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A27" s="118" t="s">
-        <v>182</v>
-      </c>
-      <c r="B27" s="118"/>
+      <c r="A27" s="127" t="s">
+        <v>177</v>
+      </c>
+      <c r="B27" s="127"/>
       <c r="C27">
         <v>22</v>
       </c>
@@ -5599,10 +5869,10 @@
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A28" s="118" t="s">
-        <v>179</v>
-      </c>
-      <c r="B28" s="118"/>
+      <c r="A28" s="127" t="s">
+        <v>174</v>
+      </c>
+      <c r="B28" s="127"/>
       <c r="C28">
         <v>3</v>
       </c>
@@ -5635,10 +5905,10 @@
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A29" s="118" t="s">
-        <v>180</v>
-      </c>
-      <c r="B29" s="118"/>
+      <c r="A29" s="127" t="s">
+        <v>175</v>
+      </c>
+      <c r="B29" s="127"/>
       <c r="C29">
         <v>1.5</v>
       </c>
@@ -5671,7 +5941,45 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="49">
+    <mergeCell ref="P21:R21"/>
+    <mergeCell ref="P9:T9"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="P8:R8"/>
+    <mergeCell ref="P19:R19"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="P13:R13"/>
+    <mergeCell ref="P14:R14"/>
+    <mergeCell ref="P10:R10"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="H9:L9"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="P11:R11"/>
+    <mergeCell ref="P15:R15"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="P16:R16"/>
+    <mergeCell ref="P17:R17"/>
+    <mergeCell ref="P18:R18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="P20:R20"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="P2:T2"/>
@@ -5683,39 +5991,6 @@
     <mergeCell ref="H6:J6"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="H3:J3"/>
-    <mergeCell ref="P16:R16"/>
-    <mergeCell ref="P17:R17"/>
-    <mergeCell ref="P18:R18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="P11:R11"/>
-    <mergeCell ref="P15:R15"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="P9:T9"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="P12:R12"/>
-    <mergeCell ref="P13:R13"/>
-    <mergeCell ref="P14:R14"/>
-    <mergeCell ref="P10:R10"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="H9:L9"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5723,6 +5998,353 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{721CC587-9EA7-4DCC-9ECD-B77E76609183}">
+  <dimension ref="A2:J27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="E4" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B8" s="133" t="s">
+        <v>342</v>
+      </c>
+      <c r="C8" s="48"/>
+      <c r="D8" t="s">
+        <v>339</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="133"/>
+      <c r="C9" s="48"/>
+      <c r="D9" t="s">
+        <v>340</v>
+      </c>
+      <c r="E9">
+        <v>0.5</v>
+      </c>
+      <c r="F9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B10" s="133"/>
+      <c r="C10" s="48"/>
+      <c r="D10" t="s">
+        <v>213</v>
+      </c>
+      <c r="E10">
+        <v>1.6</v>
+      </c>
+      <c r="F10">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="133"/>
+      <c r="C11" s="48"/>
+      <c r="D11" t="s">
+        <v>341</v>
+      </c>
+      <c r="E11">
+        <v>0.5</v>
+      </c>
+      <c r="F11">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>336</v>
+      </c>
+      <c r="E12">
+        <v>6</v>
+      </c>
+      <c r="F12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>337</v>
+      </c>
+      <c r="E13" s="152">
+        <f>E12*0.91666</f>
+        <v>5.4999599999999997</v>
+      </c>
+      <c r="F13" s="152">
+        <f>F12*0.91666</f>
+        <v>5.4999599999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>287</v>
+      </c>
+      <c r="E14">
+        <f>E21/2</f>
+        <v>3</v>
+      </c>
+      <c r="F14">
+        <f>I21/2</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="127" t="s">
+        <v>362</v>
+      </c>
+      <c r="D16" s="127"/>
+      <c r="E16" s="127"/>
+      <c r="F16" s="127"/>
+      <c r="G16" s="127" t="s">
+        <v>361</v>
+      </c>
+      <c r="H16" s="127"/>
+      <c r="I16" s="127"/>
+      <c r="J16" s="127"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>290</v>
+      </c>
+      <c r="D17" t="s">
+        <v>350</v>
+      </c>
+      <c r="E17" t="s">
+        <v>338</v>
+      </c>
+      <c r="F17" t="s">
+        <v>350</v>
+      </c>
+      <c r="G17" t="s">
+        <v>290</v>
+      </c>
+      <c r="H17" t="s">
+        <v>350</v>
+      </c>
+      <c r="I17" t="s">
+        <v>338</v>
+      </c>
+      <c r="J17" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="127" t="s">
+        <v>349</v>
+      </c>
+      <c r="B18" s="127"/>
+      <c r="C18">
+        <f>Вал!$K$18</f>
+        <v>80</v>
+      </c>
+      <c r="G18">
+        <f ca="1">Вал!S17</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="108" t="s">
+        <v>346</v>
+      </c>
+      <c r="B19" s="101"/>
+      <c r="C19" s="11">
+        <f>C18+1</f>
+        <v>81</v>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="E19" s="93">
+        <v>5</v>
+      </c>
+      <c r="F19" s="6"/>
+      <c r="G19" s="11">
+        <f ca="1">G18+1</f>
+        <v>91</v>
+      </c>
+      <c r="H19" s="8"/>
+      <c r="I19" s="154">
+        <v>5</v>
+      </c>
+      <c r="J19" s="6"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="100" t="s">
+        <v>342</v>
+      </c>
+      <c r="B20" s="94"/>
+      <c r="C20" s="7">
+        <f>C19-2*E9</f>
+        <v>80</v>
+      </c>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1">
+        <f>E8</f>
+        <v>5</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="7">
+        <f ca="1">G19-F9*2</f>
+        <v>90</v>
+      </c>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1">
+        <f>F8</f>
+        <v>5</v>
+      </c>
+      <c r="J20" s="3"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="104" t="s">
+        <v>348</v>
+      </c>
+      <c r="B21" s="105"/>
+      <c r="C21" s="12">
+        <f>C18+E14*2</f>
+        <v>86</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4">
+        <f>E12*1</f>
+        <v>6</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="G21" s="12">
+        <f ca="1">G18+2*F14</f>
+        <v>96</v>
+      </c>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4">
+        <f>F12</f>
+        <v>6</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="108" t="s">
+        <v>347</v>
+      </c>
+      <c r="B22" s="101"/>
+      <c r="C22" s="153">
+        <f>C18-E13*2</f>
+        <v>69.000079999999997</v>
+      </c>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8">
+        <f>E19+E20+E21-E23</f>
+        <v>10</v>
+      </c>
+      <c r="F22" s="6"/>
+      <c r="G22" s="153">
+        <f ca="1">G18-F13*2</f>
+        <v>79.000079999999997</v>
+      </c>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8">
+        <f>I19+I20+I21-I23</f>
+        <v>10</v>
+      </c>
+      <c r="J22" s="6"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="104" t="s">
+        <v>351</v>
+      </c>
+      <c r="B23" s="105"/>
+      <c r="C23" s="12">
+        <f>Вал!$K$16</f>
+        <v>40</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4">
+        <f>E12</f>
+        <v>6</v>
+      </c>
+      <c r="F23" s="5"/>
+      <c r="G23" s="12">
+        <f ca="1">Вал!S15</f>
+        <v>50</v>
+      </c>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4">
+        <f>F12</f>
+        <v>6</v>
+      </c>
+      <c r="J23" s="5"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="127" t="s">
+        <v>359</v>
+      </c>
+      <c r="B25" s="127"/>
+      <c r="E25">
+        <f>SUM(E19:E21)</f>
+        <v>16</v>
+      </c>
+      <c r="F25" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25">
+        <f>SUM(I19:I21)</f>
+        <v>16</v>
+      </c>
+      <c r="J25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="127" t="s">
+        <v>358</v>
+      </c>
+      <c r="B27" s="127"/>
+      <c r="C27" t="s">
+        <v>343</v>
+      </c>
+      <c r="D27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A18:B18"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4C98D27-F275-4550-B7FB-3917876B2935}">
   <dimension ref="A1:AA61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5732,7 +6354,7 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" s="94" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B1" s="94"/>
       <c r="C1" s="94"/>
@@ -5741,7 +6363,7 @@
       <c r="F1" s="94"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A2" s="93" t="s">
+      <c r="A2" s="100" t="s">
         <v>108</v>
       </c>
       <c r="B2" s="94"/>
@@ -5751,20 +6373,20 @@
         <f>Электродвигатель!F48</f>
         <v>Цилиндрическая 1</v>
       </c>
-      <c r="F2" s="105"/>
-      <c r="K2" s="97" t="s">
-        <v>150</v>
-      </c>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
+      <c r="F2" s="111"/>
+      <c r="K2" s="108" t="s">
+        <v>145</v>
+      </c>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="101"/>
+      <c r="P2" s="101"/>
+      <c r="Q2" s="101"/>
       <c r="R2" s="1"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="100" t="s">
         <v>41</v>
       </c>
       <c r="B3" s="94"/>
@@ -5776,32 +6398,32 @@
       </c>
       <c r="F3" s="50"/>
       <c r="K3" s="7" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="L3" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="P3" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="Q3" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="R3" s="25" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A4" s="93" t="s">
+      <c r="A4" s="100" t="s">
         <v>42</v>
       </c>
       <c r="B4" s="94"/>
@@ -5841,7 +6463,7 @@
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="100" t="s">
         <v>97</v>
       </c>
       <c r="B5" s="94"/>
@@ -5881,7 +6503,7 @@
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A6" s="93" t="s">
+      <c r="A6" s="100" t="s">
         <v>102</v>
       </c>
       <c r="B6" s="94"/>
@@ -5919,12 +6541,12 @@
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A7" s="118" t="s">
-        <v>144</v>
-      </c>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
+      <c r="A7" s="127" t="s">
+        <v>139</v>
+      </c>
+      <c r="B7" s="127"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
       <c r="E7">
         <f>Электродвигатель!$E$5</f>
         <v>10000</v>
@@ -5959,14 +6581,14 @@
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A8" s="118" t="s">
-        <v>138</v>
-      </c>
-      <c r="B8" s="118"/>
-      <c r="C8" s="118"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="118"/>
-      <c r="F8" s="118"/>
+      <c r="A8" s="127" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="127"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
+      <c r="F8" s="127"/>
       <c r="K8" s="7">
         <v>5</v>
       </c>
@@ -5995,12 +6617,12 @@
       <c r="S8" s="1"/>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A9" s="118" t="s">
-        <v>143</v>
-      </c>
-      <c r="B9" s="118"/>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
+      <c r="A9" s="127" t="s">
+        <v>138</v>
+      </c>
+      <c r="B9" s="127"/>
+      <c r="C9" s="127"/>
+      <c r="D9" s="127"/>
       <c r="E9">
         <f>Электродвигатель!$E$15</f>
         <v>300</v>
@@ -6036,7 +6658,7 @@
       <c r="S9" s="54"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A10" s="93" t="s">
+      <c r="A10" s="100" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="94"/>
@@ -6047,7 +6669,7 @@
         <v>3</v>
       </c>
       <c r="F10" s="50" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K10" s="58">
         <v>7</v>
@@ -6077,8 +6699,8 @@
       <c r="S10" s="54"/>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A11" s="93" t="s">
-        <v>209</v>
+      <c r="A11" s="100" t="s">
+        <v>204</v>
       </c>
       <c r="B11" s="94"/>
       <c r="C11" s="94"/>
@@ -6087,7 +6709,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="K11" s="58">
         <v>8</v>
@@ -6117,8 +6739,8 @@
       <c r="S11" s="54"/>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A12" s="93" t="s">
-        <v>128</v>
+      <c r="A12" s="100" t="s">
+        <v>123</v>
       </c>
       <c r="B12" s="94"/>
       <c r="C12" s="94"/>
@@ -6127,7 +6749,7 @@
         <v>100</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="K12" s="7">
         <v>9</v>
@@ -6157,14 +6779,14 @@
       <c r="S12" s="54"/>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A13" s="118" t="s">
-        <v>139</v>
-      </c>
-      <c r="B13" s="118"/>
-      <c r="C13" s="118"/>
-      <c r="D13" s="118"/>
-      <c r="E13" s="118"/>
-      <c r="F13" s="118"/>
+      <c r="A13" s="127" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13" s="127"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="127"/>
+      <c r="E13" s="127"/>
+      <c r="F13" s="127"/>
       <c r="K13" s="7">
         <v>10</v>
       </c>
@@ -6193,12 +6815,12 @@
       <c r="S13" s="54"/>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A14" s="118" t="s">
-        <v>142</v>
-      </c>
-      <c r="B14" s="118"/>
-      <c r="C14" s="118"/>
-      <c r="D14" s="118"/>
+      <c r="A14" s="127" t="s">
+        <v>137</v>
+      </c>
+      <c r="B14" s="127"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
       <c r="E14">
         <f>Вал!$D$6</f>
         <v>38</v>
@@ -6235,13 +6857,13 @@
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A15" s="94" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B15" s="94"/>
       <c r="C15" s="94"/>
       <c r="D15" s="94"/>
       <c r="E15">
-        <f>Вал!$K$19</f>
+        <f>Вал!$K$21</f>
         <v>45</v>
       </c>
       <c r="F15" t="s">
@@ -6275,14 +6897,14 @@
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A16" s="94" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B16" s="94"/>
       <c r="C16" s="94"/>
       <c r="D16" s="94"/>
       <c r="E16">
-        <f ca="1">Вал!$S$18</f>
-        <v>56</v>
+        <f ca="1">Вал!$S$21</f>
+        <v>50</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
@@ -6290,126 +6912,126 @@
       <c r="Z16" s="59"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G18" s="144" t="s">
-        <v>153</v>
-      </c>
-      <c r="H18" s="145"/>
-      <c r="I18" s="145"/>
-      <c r="J18" s="145"/>
+      <c r="G18" s="143" t="s">
+        <v>148</v>
+      </c>
+      <c r="H18" s="144"/>
+      <c r="I18" s="144"/>
+      <c r="J18" s="144"/>
       <c r="K18" s="82">
         <v>6</v>
       </c>
       <c r="L18" s="84"/>
       <c r="M18" s="77"/>
-      <c r="N18" s="144" t="s">
-        <v>153</v>
-      </c>
-      <c r="O18" s="145"/>
-      <c r="P18" s="145"/>
-      <c r="Q18" s="145"/>
+      <c r="N18" s="143" t="s">
+        <v>148</v>
+      </c>
+      <c r="O18" s="144"/>
+      <c r="P18" s="144"/>
+      <c r="Q18" s="144"/>
       <c r="R18" s="82">
         <v>7</v>
       </c>
       <c r="S18" s="84"/>
       <c r="T18" s="77"/>
-      <c r="U18" s="144" t="s">
-        <v>153</v>
-      </c>
-      <c r="V18" s="145"/>
-      <c r="W18" s="145"/>
-      <c r="X18" s="145"/>
+      <c r="U18" s="143" t="s">
+        <v>148</v>
+      </c>
+      <c r="V18" s="144"/>
+      <c r="W18" s="144"/>
+      <c r="X18" s="144"/>
       <c r="Y18" s="82">
         <v>8</v>
       </c>
       <c r="Z18" s="84"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G19" s="135" t="s">
-        <v>149</v>
-      </c>
-      <c r="H19" s="136"/>
-      <c r="I19" s="136"/>
-      <c r="J19" s="136"/>
+      <c r="G19" s="134" t="s">
+        <v>144</v>
+      </c>
+      <c r="H19" s="135"/>
+      <c r="I19" s="135"/>
+      <c r="J19" s="135"/>
       <c r="K19" s="78">
         <v>69</v>
       </c>
       <c r="L19" s="76" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="M19" s="77"/>
-      <c r="N19" s="135" t="s">
-        <v>149</v>
-      </c>
-      <c r="O19" s="136"/>
-      <c r="P19" s="136"/>
-      <c r="Q19" s="136"/>
+      <c r="N19" s="134" t="s">
+        <v>144</v>
+      </c>
+      <c r="O19" s="135"/>
+      <c r="P19" s="135"/>
+      <c r="Q19" s="135"/>
       <c r="R19" s="78">
         <v>57</v>
       </c>
       <c r="S19" s="76" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="T19" s="77"/>
-      <c r="U19" s="135" t="s">
-        <v>149</v>
-      </c>
-      <c r="V19" s="136"/>
-      <c r="W19" s="136"/>
-      <c r="X19" s="136"/>
+      <c r="U19" s="134" t="s">
+        <v>144</v>
+      </c>
+      <c r="V19" s="135"/>
+      <c r="W19" s="135"/>
+      <c r="X19" s="135"/>
       <c r="Y19" s="78">
         <v>64</v>
       </c>
       <c r="Z19" s="76" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G20" s="135" t="s">
-        <v>154</v>
-      </c>
-      <c r="H20" s="136"/>
-      <c r="I20" s="136"/>
-      <c r="J20" s="136"/>
+      <c r="G20" s="134" t="s">
+        <v>149</v>
+      </c>
+      <c r="H20" s="135"/>
+      <c r="I20" s="135"/>
+      <c r="J20" s="135"/>
       <c r="K20" s="75">
         <v>22.3</v>
       </c>
       <c r="L20" s="76" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="M20" s="77"/>
-      <c r="N20" s="135" t="s">
-        <v>154</v>
-      </c>
-      <c r="O20" s="136"/>
-      <c r="P20" s="136"/>
-      <c r="Q20" s="136"/>
+      <c r="N20" s="134" t="s">
+        <v>149</v>
+      </c>
+      <c r="O20" s="135"/>
+      <c r="P20" s="135"/>
+      <c r="Q20" s="135"/>
       <c r="R20" s="75">
         <v>20</v>
       </c>
       <c r="S20" s="76" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="T20" s="77"/>
-      <c r="U20" s="135" t="s">
-        <v>154</v>
-      </c>
-      <c r="V20" s="136"/>
-      <c r="W20" s="136"/>
-      <c r="X20" s="136"/>
+      <c r="U20" s="134" t="s">
+        <v>149</v>
+      </c>
+      <c r="V20" s="135"/>
+      <c r="W20" s="135"/>
+      <c r="X20" s="135"/>
       <c r="Y20" s="75">
         <v>25.3</v>
       </c>
       <c r="Z20" s="76" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G21" s="135" t="s">
-        <v>146</v>
-      </c>
-      <c r="H21" s="136"/>
-      <c r="I21" s="136"/>
-      <c r="J21" s="136"/>
+      <c r="G21" s="134" t="s">
+        <v>141</v>
+      </c>
+      <c r="H21" s="135"/>
+      <c r="I21" s="135"/>
+      <c r="J21" s="135"/>
       <c r="K21" s="75">
         <v>240</v>
       </c>
@@ -6417,12 +7039,12 @@
         <v>16</v>
       </c>
       <c r="M21" s="77"/>
-      <c r="N21" s="135" t="s">
-        <v>146</v>
-      </c>
-      <c r="O21" s="136"/>
-      <c r="P21" s="136"/>
-      <c r="Q21" s="136"/>
+      <c r="N21" s="134" t="s">
+        <v>141</v>
+      </c>
+      <c r="O21" s="135"/>
+      <c r="P21" s="135"/>
+      <c r="Q21" s="135"/>
       <c r="R21" s="75">
         <v>180</v>
       </c>
@@ -6430,12 +7052,12 @@
         <v>16</v>
       </c>
       <c r="T21" s="77"/>
-      <c r="U21" s="135" t="s">
-        <v>146</v>
-      </c>
-      <c r="V21" s="136"/>
-      <c r="W21" s="136"/>
-      <c r="X21" s="136"/>
+      <c r="U21" s="134" t="s">
+        <v>141</v>
+      </c>
+      <c r="V21" s="135"/>
+      <c r="W21" s="135"/>
+      <c r="X21" s="135"/>
       <c r="Y21" s="75">
         <v>180</v>
       </c>
@@ -6444,12 +7066,12 @@
       </c>
     </row>
     <row r="22" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G22" s="135" t="s">
-        <v>155</v>
-      </c>
-      <c r="H22" s="136"/>
-      <c r="I22" s="136"/>
-      <c r="J22" s="136"/>
+      <c r="G22" s="134" t="s">
+        <v>150</v>
+      </c>
+      <c r="H22" s="135"/>
+      <c r="I22" s="135"/>
+      <c r="J22" s="135"/>
       <c r="K22" s="75">
         <v>3.5</v>
       </c>
@@ -6457,12 +7079,12 @@
         <v>16</v>
       </c>
       <c r="M22" s="77"/>
-      <c r="N22" s="135" t="s">
-        <v>155</v>
-      </c>
-      <c r="O22" s="136"/>
-      <c r="P22" s="136"/>
-      <c r="Q22" s="136"/>
+      <c r="N22" s="134" t="s">
+        <v>150</v>
+      </c>
+      <c r="O22" s="135"/>
+      <c r="P22" s="135"/>
+      <c r="Q22" s="135"/>
       <c r="R22" s="75">
         <v>2.5</v>
       </c>
@@ -6470,12 +7092,12 @@
         <v>16</v>
       </c>
       <c r="T22" s="77"/>
-      <c r="U22" s="135" t="s">
-        <v>155</v>
-      </c>
-      <c r="V22" s="136"/>
-      <c r="W22" s="136"/>
-      <c r="X22" s="136"/>
+      <c r="U22" s="134" t="s">
+        <v>150</v>
+      </c>
+      <c r="V22" s="135"/>
+      <c r="W22" s="135"/>
+      <c r="X22" s="135"/>
       <c r="Y22" s="75">
         <v>3</v>
       </c>
@@ -6484,194 +7106,194 @@
       </c>
     </row>
     <row r="23" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G23" s="135" t="s">
+      <c r="G23" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="H23" s="136"/>
-      <c r="I23" s="136"/>
-      <c r="J23" s="136"/>
+      <c r="H23" s="135"/>
+      <c r="I23" s="135"/>
+      <c r="J23" s="135"/>
       <c r="K23" s="75">
         <v>1510</v>
       </c>
       <c r="L23" s="76" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="M23" s="77"/>
-      <c r="N23" s="135" t="s">
+      <c r="N23" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="O23" s="136"/>
-      <c r="P23" s="136"/>
-      <c r="Q23" s="136"/>
+      <c r="O23" s="135"/>
+      <c r="P23" s="135"/>
+      <c r="Q23" s="135"/>
       <c r="R23" s="75">
         <v>2016</v>
       </c>
       <c r="S23" s="76" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="T23" s="77"/>
-      <c r="U23" s="135" t="s">
+      <c r="U23" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="V23" s="136"/>
-      <c r="W23" s="136"/>
-      <c r="X23" s="136"/>
+      <c r="V23" s="135"/>
+      <c r="W23" s="135"/>
+      <c r="X23" s="135"/>
       <c r="Y23" s="75">
         <v>2013</v>
       </c>
       <c r="Z23" s="76" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G24" s="135" t="s">
-        <v>157</v>
-      </c>
-      <c r="H24" s="136"/>
-      <c r="I24" s="136"/>
-      <c r="J24" s="136"/>
+      <c r="G24" s="134" t="s">
+        <v>152</v>
+      </c>
+      <c r="H24" s="135"/>
+      <c r="I24" s="135"/>
+      <c r="J24" s="135"/>
       <c r="K24" s="75">
         <v>554</v>
       </c>
       <c r="L24" s="76" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="M24" s="77"/>
-      <c r="N24" s="135" t="s">
-        <v>157</v>
-      </c>
-      <c r="O24" s="136"/>
-      <c r="P24" s="136"/>
-      <c r="Q24" s="136"/>
+      <c r="N24" s="134" t="s">
+        <v>152</v>
+      </c>
+      <c r="O24" s="135"/>
+      <c r="P24" s="135"/>
+      <c r="Q24" s="135"/>
       <c r="R24" s="75">
         <v>734</v>
       </c>
       <c r="S24" s="76" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="T24" s="77"/>
-      <c r="U24" s="135" t="s">
-        <v>157</v>
-      </c>
-      <c r="V24" s="136"/>
-      <c r="W24" s="136"/>
-      <c r="X24" s="136"/>
+      <c r="U24" s="134" t="s">
+        <v>152</v>
+      </c>
+      <c r="V24" s="135"/>
+      <c r="W24" s="135"/>
+      <c r="X24" s="135"/>
       <c r="Y24" s="75">
         <v>733</v>
       </c>
       <c r="Z24" s="76" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G25" s="137" t="s">
-        <v>158</v>
-      </c>
-      <c r="H25" s="138"/>
-      <c r="I25" s="138"/>
-      <c r="J25" s="138"/>
+      <c r="G25" s="136" t="s">
+        <v>153</v>
+      </c>
+      <c r="H25" s="137"/>
+      <c r="I25" s="137"/>
+      <c r="J25" s="137"/>
       <c r="K25" s="80">
         <v>0</v>
       </c>
       <c r="L25" s="81" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="M25" s="77"/>
-      <c r="N25" s="137" t="s">
-        <v>158</v>
-      </c>
-      <c r="O25" s="138"/>
-      <c r="P25" s="138"/>
-      <c r="Q25" s="138"/>
+      <c r="N25" s="136" t="s">
+        <v>153</v>
+      </c>
+      <c r="O25" s="137"/>
+      <c r="P25" s="137"/>
+      <c r="Q25" s="137"/>
       <c r="R25" s="80">
         <v>0</v>
       </c>
       <c r="S25" s="81" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="T25" s="77"/>
-      <c r="U25" s="137" t="s">
-        <v>158</v>
-      </c>
-      <c r="V25" s="138"/>
-      <c r="W25" s="138"/>
-      <c r="X25" s="138"/>
+      <c r="U25" s="136" t="s">
+        <v>153</v>
+      </c>
+      <c r="V25" s="137"/>
+      <c r="W25" s="137"/>
+      <c r="X25" s="137"/>
       <c r="Y25" s="80">
         <v>0</v>
       </c>
       <c r="Z25" s="81" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G26" s="132" t="s">
-        <v>161</v>
-      </c>
-      <c r="H26" s="133"/>
-      <c r="I26" s="133"/>
-      <c r="J26" s="133"/>
-      <c r="K26" s="133"/>
-      <c r="L26" s="134"/>
+      <c r="G26" s="138" t="s">
+        <v>156</v>
+      </c>
+      <c r="H26" s="139"/>
+      <c r="I26" s="139"/>
+      <c r="J26" s="139"/>
+      <c r="K26" s="139"/>
+      <c r="L26" s="140"/>
       <c r="M26" s="77"/>
-      <c r="N26" s="132" t="s">
-        <v>161</v>
-      </c>
-      <c r="O26" s="133"/>
-      <c r="P26" s="133"/>
-      <c r="Q26" s="133"/>
-      <c r="R26" s="133"/>
-      <c r="S26" s="134"/>
+      <c r="N26" s="138" t="s">
+        <v>156</v>
+      </c>
+      <c r="O26" s="139"/>
+      <c r="P26" s="139"/>
+      <c r="Q26" s="139"/>
+      <c r="R26" s="139"/>
+      <c r="S26" s="140"/>
       <c r="T26" s="77"/>
-      <c r="U26" s="132" t="s">
-        <v>161</v>
-      </c>
-      <c r="V26" s="133"/>
-      <c r="W26" s="133"/>
-      <c r="X26" s="133"/>
-      <c r="Y26" s="133"/>
-      <c r="Z26" s="134"/>
+      <c r="U26" s="138" t="s">
+        <v>156</v>
+      </c>
+      <c r="V26" s="139"/>
+      <c r="W26" s="139"/>
+      <c r="X26" s="139"/>
+      <c r="Y26" s="139"/>
+      <c r="Z26" s="140"/>
     </row>
     <row r="27" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G27" s="135" t="s">
-        <v>162</v>
-      </c>
-      <c r="H27" s="136"/>
-      <c r="I27" s="136"/>
-      <c r="J27" s="136"/>
+      <c r="G27" s="134" t="s">
+        <v>157</v>
+      </c>
+      <c r="H27" s="135"/>
+      <c r="I27" s="135"/>
+      <c r="J27" s="135"/>
       <c r="K27" s="87">
         <v>16</v>
       </c>
       <c r="L27" s="76"/>
       <c r="M27" s="77"/>
-      <c r="N27" s="135" t="s">
-        <v>162</v>
-      </c>
-      <c r="O27" s="136"/>
-      <c r="P27" s="136"/>
-      <c r="Q27" s="136"/>
+      <c r="N27" s="134" t="s">
+        <v>157</v>
+      </c>
+      <c r="O27" s="135"/>
+      <c r="P27" s="135"/>
+      <c r="Q27" s="135"/>
       <c r="R27" s="87">
         <v>17</v>
       </c>
       <c r="S27" s="76"/>
       <c r="T27" s="77"/>
-      <c r="U27" s="135" t="s">
-        <v>162</v>
-      </c>
-      <c r="V27" s="136"/>
-      <c r="W27" s="136"/>
-      <c r="X27" s="136"/>
+      <c r="U27" s="134" t="s">
+        <v>157</v>
+      </c>
+      <c r="V27" s="135"/>
+      <c r="W27" s="135"/>
+      <c r="X27" s="135"/>
       <c r="Y27" s="87">
         <v>14</v>
       </c>
       <c r="Z27" s="76"/>
     </row>
     <row r="28" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G28" s="139" t="s">
-        <v>167</v>
-      </c>
-      <c r="H28" s="140"/>
-      <c r="I28" s="140"/>
-      <c r="J28" s="140"/>
+      <c r="G28" s="141" t="s">
+        <v>162</v>
+      </c>
+      <c r="H28" s="142"/>
+      <c r="I28" s="142"/>
+      <c r="J28" s="142"/>
       <c r="K28" s="87">
         <v>0.3</v>
       </c>
@@ -6679,12 +7301,12 @@
         <v>16</v>
       </c>
       <c r="M28" s="77"/>
-      <c r="N28" s="139" t="s">
-        <v>167</v>
-      </c>
-      <c r="O28" s="140"/>
-      <c r="P28" s="140"/>
-      <c r="Q28" s="140"/>
+      <c r="N28" s="141" t="s">
+        <v>162</v>
+      </c>
+      <c r="O28" s="142"/>
+      <c r="P28" s="142"/>
+      <c r="Q28" s="142"/>
       <c r="R28" s="87">
         <v>-0.3</v>
       </c>
@@ -6692,12 +7314,12 @@
         <v>16</v>
       </c>
       <c r="T28" s="77"/>
-      <c r="U28" s="139" t="s">
-        <v>167</v>
-      </c>
-      <c r="V28" s="140"/>
-      <c r="W28" s="140"/>
-      <c r="X28" s="140"/>
+      <c r="U28" s="141" t="s">
+        <v>162</v>
+      </c>
+      <c r="V28" s="142"/>
+      <c r="W28" s="142"/>
+      <c r="X28" s="142"/>
       <c r="Y28" s="87">
         <v>0.3</v>
       </c>
@@ -6706,87 +7328,87 @@
       </c>
     </row>
     <row r="29" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G29" s="139" t="s">
-        <v>166</v>
-      </c>
-      <c r="H29" s="140"/>
-      <c r="I29" s="140"/>
-      <c r="J29" s="140"/>
+      <c r="G29" s="141" t="s">
+        <v>161</v>
+      </c>
+      <c r="H29" s="142"/>
+      <c r="I29" s="142"/>
+      <c r="J29" s="142"/>
       <c r="K29" s="87">
         <v>49</v>
       </c>
       <c r="L29" s="79" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="M29" s="77"/>
-      <c r="N29" s="139" t="s">
-        <v>166</v>
-      </c>
-      <c r="O29" s="140"/>
-      <c r="P29" s="140"/>
-      <c r="Q29" s="140"/>
+      <c r="N29" s="141" t="s">
+        <v>161</v>
+      </c>
+      <c r="O29" s="142"/>
+      <c r="P29" s="142"/>
+      <c r="Q29" s="142"/>
       <c r="R29" s="87">
         <v>49</v>
       </c>
       <c r="S29" s="79" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="T29" s="77"/>
-      <c r="U29" s="139" t="s">
-        <v>166</v>
-      </c>
-      <c r="V29" s="140"/>
-      <c r="W29" s="140"/>
-      <c r="X29" s="140"/>
+      <c r="U29" s="141" t="s">
+        <v>161</v>
+      </c>
+      <c r="V29" s="142"/>
+      <c r="W29" s="142"/>
+      <c r="X29" s="142"/>
       <c r="Y29" s="87">
         <v>49</v>
       </c>
       <c r="Z29" s="79" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
     </row>
     <row r="30" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G30" s="139" t="s">
-        <v>168</v>
-      </c>
-      <c r="H30" s="140"/>
-      <c r="I30" s="140"/>
-      <c r="J30" s="140"/>
+      <c r="G30" s="141" t="s">
+        <v>163</v>
+      </c>
+      <c r="H30" s="142"/>
+      <c r="I30" s="142"/>
+      <c r="J30" s="142"/>
       <c r="K30" s="87" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="L30" s="76"/>
       <c r="M30" s="77"/>
-      <c r="N30" s="139" t="s">
-        <v>168</v>
-      </c>
-      <c r="O30" s="140"/>
-      <c r="P30" s="140"/>
-      <c r="Q30" s="140"/>
+      <c r="N30" s="141" t="s">
+        <v>163</v>
+      </c>
+      <c r="O30" s="142"/>
+      <c r="P30" s="142"/>
+      <c r="Q30" s="142"/>
       <c r="R30" s="87" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="S30" s="76"/>
       <c r="T30" s="77"/>
-      <c r="U30" s="139" t="s">
-        <v>168</v>
-      </c>
-      <c r="V30" s="140"/>
-      <c r="W30" s="140"/>
-      <c r="X30" s="140"/>
+      <c r="U30" s="141" t="s">
+        <v>163</v>
+      </c>
+      <c r="V30" s="142"/>
+      <c r="W30" s="142"/>
+      <c r="X30" s="142"/>
       <c r="Y30" s="87" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="Z30" s="76"/>
     </row>
     <row r="31" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B31" s="86"/>
-      <c r="G31" s="135" t="s">
-        <v>213</v>
-      </c>
-      <c r="H31" s="136"/>
-      <c r="I31" s="136"/>
-      <c r="J31" s="136"/>
+      <c r="G31" s="134" t="s">
+        <v>208</v>
+      </c>
+      <c r="H31" s="135"/>
+      <c r="I31" s="135"/>
+      <c r="J31" s="135"/>
       <c r="K31" s="87">
         <v>56</v>
       </c>
@@ -6794,12 +7416,12 @@
         <v>16</v>
       </c>
       <c r="M31" s="77"/>
-      <c r="N31" s="135" t="s">
-        <v>213</v>
-      </c>
-      <c r="O31" s="136"/>
-      <c r="P31" s="136"/>
-      <c r="Q31" s="136"/>
+      <c r="N31" s="134" t="s">
+        <v>208</v>
+      </c>
+      <c r="O31" s="135"/>
+      <c r="P31" s="135"/>
+      <c r="Q31" s="135"/>
       <c r="R31" s="87">
         <v>42.5</v>
       </c>
@@ -6807,12 +7429,12 @@
         <v>16</v>
       </c>
       <c r="T31" s="77"/>
-      <c r="U31" s="135" t="s">
-        <v>213</v>
-      </c>
-      <c r="V31" s="136"/>
-      <c r="W31" s="136"/>
-      <c r="X31" s="136"/>
+      <c r="U31" s="134" t="s">
+        <v>208</v>
+      </c>
+      <c r="V31" s="135"/>
+      <c r="W31" s="135"/>
+      <c r="X31" s="135"/>
       <c r="Y31" s="87">
         <v>42</v>
       </c>
@@ -6821,12 +7443,12 @@
       </c>
     </row>
     <row r="32" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="G32" s="135" t="s">
-        <v>184</v>
-      </c>
-      <c r="H32" s="136"/>
-      <c r="I32" s="136"/>
-      <c r="J32" s="136"/>
+      <c r="G32" s="134" t="s">
+        <v>179</v>
+      </c>
+      <c r="H32" s="135"/>
+      <c r="I32" s="135"/>
+      <c r="J32" s="135"/>
       <c r="K32" s="87">
         <v>65</v>
       </c>
@@ -6834,12 +7456,12 @@
         <v>16</v>
       </c>
       <c r="M32" s="77"/>
-      <c r="N32" s="135" t="s">
-        <v>184</v>
-      </c>
-      <c r="O32" s="136"/>
-      <c r="P32" s="136"/>
-      <c r="Q32" s="136"/>
+      <c r="N32" s="134" t="s">
+        <v>179</v>
+      </c>
+      <c r="O32" s="135"/>
+      <c r="P32" s="135"/>
+      <c r="Q32" s="135"/>
       <c r="R32" s="87">
         <v>49</v>
       </c>
@@ -6847,12 +7469,12 @@
         <v>16</v>
       </c>
       <c r="T32" s="77"/>
-      <c r="U32" s="135" t="s">
-        <v>184</v>
-      </c>
-      <c r="V32" s="136"/>
-      <c r="W32" s="136"/>
-      <c r="X32" s="136"/>
+      <c r="U32" s="134" t="s">
+        <v>179</v>
+      </c>
+      <c r="V32" s="135"/>
+      <c r="W32" s="135"/>
+      <c r="X32" s="135"/>
       <c r="Y32" s="87">
         <v>49.8</v>
       </c>
@@ -6861,12 +7483,12 @@
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G33" s="135" t="s">
-        <v>175</v>
-      </c>
-      <c r="H33" s="136"/>
-      <c r="I33" s="136"/>
-      <c r="J33" s="136"/>
+      <c r="G33" s="134" t="s">
+        <v>170</v>
+      </c>
+      <c r="H33" s="135"/>
+      <c r="I33" s="135"/>
+      <c r="J33" s="135"/>
       <c r="K33" s="87">
         <v>49.35</v>
       </c>
@@ -6874,12 +7496,12 @@
         <v>16</v>
       </c>
       <c r="M33" s="77"/>
-      <c r="N33" s="135" t="s">
-        <v>175</v>
-      </c>
-      <c r="O33" s="136"/>
-      <c r="P33" s="136"/>
-      <c r="Q33" s="136"/>
+      <c r="N33" s="134" t="s">
+        <v>170</v>
+      </c>
+      <c r="O33" s="135"/>
+      <c r="P33" s="135"/>
+      <c r="Q33" s="135"/>
       <c r="R33" s="87">
         <v>37.75</v>
       </c>
@@ -6887,12 +7509,12 @@
         <v>16</v>
       </c>
       <c r="T33" s="77"/>
-      <c r="U33" s="135" t="s">
-        <v>175</v>
-      </c>
-      <c r="V33" s="136"/>
-      <c r="W33" s="136"/>
-      <c r="X33" s="136"/>
+      <c r="U33" s="134" t="s">
+        <v>170</v>
+      </c>
+      <c r="V33" s="135"/>
+      <c r="W33" s="135"/>
+      <c r="X33" s="135"/>
       <c r="Y33" s="87">
         <v>36.6</v>
       </c>
@@ -6901,12 +7523,12 @@
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G34" s="135" t="s">
-        <v>165</v>
-      </c>
-      <c r="H34" s="136"/>
-      <c r="I34" s="136"/>
-      <c r="J34" s="136"/>
+      <c r="G34" s="134" t="s">
+        <v>160</v>
+      </c>
+      <c r="H34" s="135"/>
+      <c r="I34" s="135"/>
+      <c r="J34" s="135"/>
       <c r="K34" s="87">
         <v>40</v>
       </c>
@@ -6914,12 +7536,12 @@
         <v>16</v>
       </c>
       <c r="M34" s="77"/>
-      <c r="N34" s="135" t="s">
-        <v>165</v>
-      </c>
-      <c r="O34" s="136"/>
-      <c r="P34" s="136"/>
-      <c r="Q34" s="136"/>
+      <c r="N34" s="134" t="s">
+        <v>160</v>
+      </c>
+      <c r="O34" s="135"/>
+      <c r="P34" s="135"/>
+      <c r="Q34" s="135"/>
       <c r="R34" s="87">
         <v>62</v>
       </c>
@@ -6927,12 +7549,12 @@
         <v>16</v>
       </c>
       <c r="T34" s="77"/>
-      <c r="U34" s="137" t="s">
-        <v>165</v>
-      </c>
-      <c r="V34" s="138"/>
-      <c r="W34" s="138"/>
-      <c r="X34" s="138"/>
+      <c r="U34" s="136" t="s">
+        <v>160</v>
+      </c>
+      <c r="V34" s="137"/>
+      <c r="W34" s="137"/>
+      <c r="X34" s="137"/>
       <c r="Y34" s="87">
         <v>79</v>
       </c>
@@ -6941,74 +7563,74 @@
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G35" s="132" t="s">
-        <v>124</v>
-      </c>
-      <c r="H35" s="133"/>
-      <c r="I35" s="133"/>
-      <c r="J35" s="133"/>
-      <c r="K35" s="133"/>
-      <c r="L35" s="134"/>
+      <c r="G35" s="138" t="s">
+        <v>122</v>
+      </c>
+      <c r="H35" s="139"/>
+      <c r="I35" s="139"/>
+      <c r="J35" s="139"/>
+      <c r="K35" s="139"/>
+      <c r="L35" s="140"/>
       <c r="M35" s="77"/>
-      <c r="N35" s="132" t="s">
-        <v>124</v>
-      </c>
-      <c r="O35" s="133"/>
-      <c r="P35" s="133"/>
-      <c r="Q35" s="133"/>
-      <c r="R35" s="133"/>
-      <c r="S35" s="134"/>
+      <c r="N35" s="138" t="s">
+        <v>122</v>
+      </c>
+      <c r="O35" s="139"/>
+      <c r="P35" s="139"/>
+      <c r="Q35" s="139"/>
+      <c r="R35" s="139"/>
+      <c r="S35" s="140"/>
       <c r="T35" s="77"/>
-      <c r="U35" s="132" t="s">
-        <v>124</v>
-      </c>
-      <c r="V35" s="133"/>
-      <c r="W35" s="133"/>
-      <c r="X35" s="133"/>
-      <c r="Y35" s="133"/>
-      <c r="Z35" s="134"/>
+      <c r="U35" s="138" t="s">
+        <v>122</v>
+      </c>
+      <c r="V35" s="139"/>
+      <c r="W35" s="139"/>
+      <c r="X35" s="139"/>
+      <c r="Y35" s="139"/>
+      <c r="Z35" s="140"/>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G36" s="135" t="s">
-        <v>162</v>
-      </c>
-      <c r="H36" s="136"/>
-      <c r="I36" s="136"/>
-      <c r="J36" s="136"/>
+      <c r="G36" s="134" t="s">
+        <v>157</v>
+      </c>
+      <c r="H36" s="135"/>
+      <c r="I36" s="135"/>
+      <c r="J36" s="135"/>
       <c r="K36" s="87">
         <v>121</v>
       </c>
       <c r="L36" s="76"/>
       <c r="M36" s="77"/>
-      <c r="N36" s="135" t="s">
-        <v>162</v>
-      </c>
-      <c r="O36" s="136"/>
-      <c r="P36" s="136"/>
-      <c r="Q36" s="136"/>
+      <c r="N36" s="134" t="s">
+        <v>157</v>
+      </c>
+      <c r="O36" s="135"/>
+      <c r="P36" s="135"/>
+      <c r="Q36" s="135"/>
       <c r="R36" s="87">
         <v>127</v>
       </c>
       <c r="S36" s="76"/>
       <c r="T36" s="77"/>
-      <c r="U36" s="135" t="s">
-        <v>162</v>
-      </c>
-      <c r="V36" s="136"/>
-      <c r="W36" s="136"/>
-      <c r="X36" s="136"/>
+      <c r="U36" s="134" t="s">
+        <v>157</v>
+      </c>
+      <c r="V36" s="135"/>
+      <c r="W36" s="135"/>
+      <c r="X36" s="135"/>
       <c r="Y36" s="87">
         <v>106</v>
       </c>
       <c r="Z36" s="76"/>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G37" s="139" t="s">
-        <v>167</v>
-      </c>
-      <c r="H37" s="140"/>
-      <c r="I37" s="140"/>
-      <c r="J37" s="140"/>
+      <c r="G37" s="141" t="s">
+        <v>162</v>
+      </c>
+      <c r="H37" s="142"/>
+      <c r="I37" s="142"/>
+      <c r="J37" s="142"/>
       <c r="K37" s="87">
         <v>-0.22800000000000001</v>
       </c>
@@ -7016,12 +7638,12 @@
         <v>16</v>
       </c>
       <c r="M37" s="88"/>
-      <c r="N37" s="139" t="s">
-        <v>167</v>
-      </c>
-      <c r="O37" s="140"/>
-      <c r="P37" s="140"/>
-      <c r="Q37" s="140"/>
+      <c r="N37" s="141" t="s">
+        <v>162</v>
+      </c>
+      <c r="O37" s="142"/>
+      <c r="P37" s="142"/>
+      <c r="Q37" s="142"/>
       <c r="R37" s="87">
         <v>0.3</v>
       </c>
@@ -7029,12 +7651,12 @@
         <v>16</v>
       </c>
       <c r="T37" s="88"/>
-      <c r="U37" s="139" t="s">
-        <v>167</v>
-      </c>
-      <c r="V37" s="140"/>
-      <c r="W37" s="140"/>
-      <c r="X37" s="140"/>
+      <c r="U37" s="141" t="s">
+        <v>162</v>
+      </c>
+      <c r="V37" s="142"/>
+      <c r="W37" s="142"/>
+      <c r="X37" s="142"/>
       <c r="Y37" s="87">
         <v>-0.3</v>
       </c>
@@ -7043,87 +7665,87 @@
       </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G38" s="139" t="s">
-        <v>166</v>
-      </c>
-      <c r="H38" s="140"/>
-      <c r="I38" s="140"/>
-      <c r="J38" s="140"/>
+      <c r="G38" s="141" t="s">
+        <v>161</v>
+      </c>
+      <c r="H38" s="142"/>
+      <c r="I38" s="142"/>
+      <c r="J38" s="142"/>
       <c r="K38" s="87">
         <v>28.5</v>
       </c>
       <c r="L38" s="79" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="M38" s="77"/>
-      <c r="N38" s="139" t="s">
-        <v>166</v>
-      </c>
-      <c r="O38" s="140"/>
-      <c r="P38" s="140"/>
-      <c r="Q38" s="140"/>
+      <c r="N38" s="141" t="s">
+        <v>161</v>
+      </c>
+      <c r="O38" s="142"/>
+      <c r="P38" s="142"/>
+      <c r="Q38" s="142"/>
       <c r="R38" s="87">
         <v>28.5</v>
       </c>
       <c r="S38" s="79" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="T38" s="77"/>
-      <c r="U38" s="139" t="s">
-        <v>166</v>
-      </c>
-      <c r="V38" s="140"/>
-      <c r="W38" s="140"/>
-      <c r="X38" s="140"/>
+      <c r="U38" s="141" t="s">
+        <v>161</v>
+      </c>
+      <c r="V38" s="142"/>
+      <c r="W38" s="142"/>
+      <c r="X38" s="142"/>
       <c r="Y38" s="87">
         <v>28.5</v>
       </c>
       <c r="Z38" s="79" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G39" s="139" t="s">
-        <v>168</v>
-      </c>
-      <c r="H39" s="140"/>
-      <c r="I39" s="140"/>
-      <c r="J39" s="140"/>
+      <c r="G39" s="141" t="s">
+        <v>163</v>
+      </c>
+      <c r="H39" s="142"/>
+      <c r="I39" s="142"/>
+      <c r="J39" s="142"/>
       <c r="K39" s="87" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="L39" s="76"/>
       <c r="M39" s="77"/>
-      <c r="N39" s="139" t="s">
-        <v>168</v>
-      </c>
-      <c r="O39" s="140"/>
-      <c r="P39" s="140"/>
-      <c r="Q39" s="140"/>
+      <c r="N39" s="141" t="s">
+        <v>163</v>
+      </c>
+      <c r="O39" s="142"/>
+      <c r="P39" s="142"/>
+      <c r="Q39" s="142"/>
       <c r="R39" s="87" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="S39" s="76"/>
       <c r="T39" s="77"/>
-      <c r="U39" s="139" t="s">
-        <v>168</v>
-      </c>
-      <c r="V39" s="140"/>
-      <c r="W39" s="140"/>
-      <c r="X39" s="140"/>
+      <c r="U39" s="141" t="s">
+        <v>163</v>
+      </c>
+      <c r="V39" s="142"/>
+      <c r="W39" s="142"/>
+      <c r="X39" s="142"/>
       <c r="Y39" s="87" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="Z39" s="76"/>
       <c r="AA39" s="86"/>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G40" s="135" t="s">
-        <v>213</v>
-      </c>
-      <c r="H40" s="136"/>
-      <c r="I40" s="136"/>
-      <c r="J40" s="136"/>
+      <c r="G40" s="134" t="s">
+        <v>208</v>
+      </c>
+      <c r="H40" s="135"/>
+      <c r="I40" s="135"/>
+      <c r="J40" s="135"/>
       <c r="K40" s="87">
         <v>423.5</v>
       </c>
@@ -7131,12 +7753,12 @@
         <v>16</v>
       </c>
       <c r="M40" s="77"/>
-      <c r="N40" s="135" t="s">
-        <v>213</v>
-      </c>
-      <c r="O40" s="136"/>
-      <c r="P40" s="136"/>
-      <c r="Q40" s="136"/>
+      <c r="N40" s="134" t="s">
+        <v>208</v>
+      </c>
+      <c r="O40" s="135"/>
+      <c r="P40" s="135"/>
+      <c r="Q40" s="135"/>
       <c r="R40" s="87">
         <v>317.5</v>
       </c>
@@ -7144,12 +7766,12 @@
         <v>16</v>
       </c>
       <c r="T40" s="77"/>
-      <c r="U40" s="135" t="s">
-        <v>213</v>
-      </c>
-      <c r="V40" s="136"/>
-      <c r="W40" s="136"/>
-      <c r="X40" s="136"/>
+      <c r="U40" s="134" t="s">
+        <v>208</v>
+      </c>
+      <c r="V40" s="135"/>
+      <c r="W40" s="135"/>
+      <c r="X40" s="135"/>
       <c r="Y40" s="87">
         <v>318</v>
       </c>
@@ -7159,12 +7781,12 @@
       <c r="AA40" s="86"/>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G41" s="135" t="s">
-        <v>184</v>
-      </c>
-      <c r="H41" s="136"/>
-      <c r="I41" s="136"/>
-      <c r="J41" s="136"/>
+      <c r="G41" s="134" t="s">
+        <v>179</v>
+      </c>
+      <c r="H41" s="135"/>
+      <c r="I41" s="135"/>
+      <c r="J41" s="135"/>
       <c r="K41" s="87">
         <v>428.9</v>
       </c>
@@ -7172,12 +7794,12 @@
         <v>16</v>
       </c>
       <c r="M41" s="77"/>
-      <c r="N41" s="135" t="s">
-        <v>184</v>
-      </c>
-      <c r="O41" s="136"/>
-      <c r="P41" s="136"/>
-      <c r="Q41" s="136"/>
+      <c r="N41" s="134" t="s">
+        <v>179</v>
+      </c>
+      <c r="O41" s="135"/>
+      <c r="P41" s="135"/>
+      <c r="Q41" s="135"/>
       <c r="R41" s="87">
         <v>321</v>
       </c>
@@ -7185,12 +7807,12 @@
         <v>16</v>
       </c>
       <c r="T41" s="77"/>
-      <c r="U41" s="135" t="s">
-        <v>184</v>
-      </c>
-      <c r="V41" s="136"/>
-      <c r="W41" s="136"/>
-      <c r="X41" s="136"/>
+      <c r="U41" s="134" t="s">
+        <v>179</v>
+      </c>
+      <c r="V41" s="135"/>
+      <c r="W41" s="135"/>
+      <c r="X41" s="135"/>
       <c r="Y41" s="87">
         <v>322</v>
       </c>
@@ -7200,12 +7822,12 @@
       <c r="AA41" s="86"/>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G42" s="135" t="s">
-        <v>175</v>
-      </c>
-      <c r="H42" s="136"/>
-      <c r="I42" s="136"/>
-      <c r="J42" s="136"/>
+      <c r="G42" s="134" t="s">
+        <v>170</v>
+      </c>
+      <c r="H42" s="135"/>
+      <c r="I42" s="135"/>
+      <c r="J42" s="135"/>
       <c r="K42" s="87">
         <v>413</v>
       </c>
@@ -7213,12 +7835,12 @@
         <v>16</v>
       </c>
       <c r="M42" s="77"/>
-      <c r="N42" s="135" t="s">
-        <v>175</v>
-      </c>
-      <c r="O42" s="136"/>
-      <c r="P42" s="136"/>
-      <c r="Q42" s="136"/>
+      <c r="N42" s="134" t="s">
+        <v>170</v>
+      </c>
+      <c r="O42" s="135"/>
+      <c r="P42" s="135"/>
+      <c r="Q42" s="135"/>
       <c r="R42" s="87">
         <v>309.75</v>
       </c>
@@ -7226,12 +7848,12 @@
         <v>16</v>
       </c>
       <c r="T42" s="77"/>
-      <c r="U42" s="135" t="s">
-        <v>175</v>
-      </c>
-      <c r="V42" s="136"/>
-      <c r="W42" s="136"/>
-      <c r="X42" s="136"/>
+      <c r="U42" s="134" t="s">
+        <v>170</v>
+      </c>
+      <c r="V42" s="135"/>
+      <c r="W42" s="135"/>
+      <c r="X42" s="135"/>
       <c r="Y42" s="87">
         <v>308.7</v>
       </c>
@@ -7241,12 +7863,12 @@
       <c r="AA42" s="16"/>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="G43" s="137" t="s">
-        <v>165</v>
-      </c>
-      <c r="H43" s="138"/>
-      <c r="I43" s="138"/>
-      <c r="J43" s="138"/>
+      <c r="G43" s="136" t="s">
+        <v>160</v>
+      </c>
+      <c r="H43" s="137"/>
+      <c r="I43" s="137"/>
+      <c r="J43" s="137"/>
       <c r="K43" s="89">
         <v>36</v>
       </c>
@@ -7254,12 +7876,12 @@
         <v>16</v>
       </c>
       <c r="M43" s="77"/>
-      <c r="N43" s="137" t="s">
-        <v>165</v>
-      </c>
-      <c r="O43" s="138"/>
-      <c r="P43" s="138"/>
-      <c r="Q43" s="138"/>
+      <c r="N43" s="136" t="s">
+        <v>160</v>
+      </c>
+      <c r="O43" s="137"/>
+      <c r="P43" s="137"/>
+      <c r="Q43" s="137"/>
       <c r="R43" s="89">
         <v>57</v>
       </c>
@@ -7267,12 +7889,12 @@
         <v>16</v>
       </c>
       <c r="T43" s="77"/>
-      <c r="U43" s="137" t="s">
-        <v>165</v>
-      </c>
-      <c r="V43" s="138"/>
-      <c r="W43" s="138"/>
-      <c r="X43" s="138"/>
+      <c r="U43" s="136" t="s">
+        <v>160</v>
+      </c>
+      <c r="V43" s="137"/>
+      <c r="W43" s="137"/>
+      <c r="X43" s="137"/>
       <c r="Y43" s="89">
         <v>72</v>
       </c>
@@ -7286,12 +7908,12 @@
       <c r="AA44" s="86"/>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A45" s="132" t="s">
-        <v>174</v>
-      </c>
-      <c r="B45" s="133"/>
-      <c r="C45" s="133"/>
-      <c r="D45" s="133"/>
+      <c r="A45" s="138" t="s">
+        <v>169</v>
+      </c>
+      <c r="B45" s="139"/>
+      <c r="C45" s="139"/>
+      <c r="D45" s="139"/>
       <c r="E45" s="85">
         <v>7</v>
       </c>
@@ -7299,11 +7921,11 @@
       <c r="AA45" s="86"/>
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A46" s="135" t="s">
-        <v>146</v>
-      </c>
-      <c r="B46" s="136"/>
-      <c r="C46" s="136"/>
+      <c r="A46" s="134" t="s">
+        <v>141</v>
+      </c>
+      <c r="B46" s="135"/>
+      <c r="C46" s="135"/>
       <c r="D46" s="75">
         <f>HLOOKUP($E$45,$18:$43,4)</f>
         <v>180</v>
@@ -7317,11 +7939,11 @@
       <c r="AA46" s="86"/>
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A47" s="141" t="s">
-        <v>155</v>
-      </c>
-      <c r="B47" s="142"/>
-      <c r="C47" s="142"/>
+      <c r="A47" s="145" t="s">
+        <v>150</v>
+      </c>
+      <c r="B47" s="146"/>
+      <c r="C47" s="146"/>
       <c r="D47" s="80">
         <f>HLOOKUP($E$45,$18:$43,5)</f>
         <v>2.5</v>
@@ -7333,77 +7955,77 @@
       <c r="AA47" s="86"/>
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A48" s="139" t="s">
-        <v>224</v>
-      </c>
-      <c r="B48" s="140"/>
-      <c r="C48" s="140"/>
-      <c r="D48" s="140"/>
-      <c r="E48" s="143"/>
+      <c r="A48" s="141" t="s">
+        <v>219</v>
+      </c>
+      <c r="B48" s="142"/>
+      <c r="C48" s="142"/>
+      <c r="D48" s="142"/>
+      <c r="E48" s="147"/>
       <c r="L48" s="86"/>
       <c r="Z48" s="59"/>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A49" s="144" t="s">
+      <c r="A49" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="B49" s="145"/>
-      <c r="C49" s="145"/>
+      <c r="B49" s="144"/>
+      <c r="C49" s="144"/>
       <c r="D49" s="82">
         <f>HLOOKUP($E$45,$18:$43,6)</f>
         <v>2016</v>
       </c>
       <c r="E49" s="84" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="Z49" s="59"/>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A50" s="135" t="s">
-        <v>157</v>
-      </c>
-      <c r="B50" s="136"/>
-      <c r="C50" s="136"/>
+      <c r="A50" s="134" t="s">
+        <v>152</v>
+      </c>
+      <c r="B50" s="135"/>
+      <c r="C50" s="135"/>
       <c r="D50" s="75">
         <f>HLOOKUP($E$45,$18:$43,7)</f>
         <v>734</v>
       </c>
       <c r="E50" s="76" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="Z50" s="59"/>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A51" s="137" t="s">
-        <v>158</v>
-      </c>
-      <c r="B51" s="138"/>
-      <c r="C51" s="138"/>
+      <c r="A51" s="136" t="s">
+        <v>153</v>
+      </c>
+      <c r="B51" s="137"/>
+      <c r="C51" s="137"/>
       <c r="D51" s="80">
         <f>HLOOKUP($E$45,$18:$43,8)</f>
         <v>0</v>
       </c>
       <c r="E51" s="81" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="Z51" s="59"/>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A52" s="139" t="s">
-        <v>214</v>
-      </c>
-      <c r="B52" s="140"/>
-      <c r="C52" s="140"/>
-      <c r="D52" s="140"/>
-      <c r="E52" s="143"/>
+      <c r="A52" s="141" t="s">
+        <v>209</v>
+      </c>
+      <c r="B52" s="142"/>
+      <c r="C52" s="142"/>
+      <c r="D52" s="142"/>
+      <c r="E52" s="147"/>
       <c r="Z52" s="59"/>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A53" s="132" t="s">
-        <v>215</v>
-      </c>
-      <c r="B53" s="133"/>
-      <c r="C53" s="133"/>
+      <c r="A53" s="138" t="s">
+        <v>210</v>
+      </c>
+      <c r="B53" s="139"/>
+      <c r="C53" s="139"/>
       <c r="D53" s="82">
         <f>HLOOKUP($E$45,$18:$43,14)</f>
         <v>42.5</v>
@@ -7414,11 +8036,11 @@
       <c r="Z53" s="59"/>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A54" s="139" t="s">
-        <v>164</v>
-      </c>
-      <c r="B54" s="140"/>
-      <c r="C54" s="140"/>
+      <c r="A54" s="141" t="s">
+        <v>159</v>
+      </c>
+      <c r="B54" s="142"/>
+      <c r="C54" s="142"/>
       <c r="D54" s="75">
         <f>HLOOKUP($E$45,$18:$43,15)</f>
         <v>49</v>
@@ -7429,11 +8051,11 @@
       <c r="Z54" s="59"/>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A55" s="139" t="s">
-        <v>163</v>
-      </c>
-      <c r="B55" s="140"/>
-      <c r="C55" s="140"/>
+      <c r="A55" s="141" t="s">
+        <v>158</v>
+      </c>
+      <c r="B55" s="142"/>
+      <c r="C55" s="142"/>
       <c r="D55" s="75">
         <f>HLOOKUP($E$45,$18:$43,16)</f>
         <v>37.75</v>
@@ -7444,11 +8066,11 @@
       <c r="Z55" s="59"/>
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A56" s="141" t="s">
-        <v>165</v>
-      </c>
-      <c r="B56" s="142"/>
-      <c r="C56" s="142"/>
+      <c r="A56" s="145" t="s">
+        <v>160</v>
+      </c>
+      <c r="B56" s="146"/>
+      <c r="C56" s="146"/>
       <c r="D56" s="80">
         <f>HLOOKUP($E$45,$18:$43,17)</f>
         <v>62</v>
@@ -7459,21 +8081,21 @@
       <c r="Z56" s="59"/>
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A57" s="139" t="s">
-        <v>216</v>
-      </c>
-      <c r="B57" s="140"/>
-      <c r="C57" s="140"/>
-      <c r="D57" s="140"/>
-      <c r="E57" s="143"/>
+      <c r="A57" s="141" t="s">
+        <v>211</v>
+      </c>
+      <c r="B57" s="142"/>
+      <c r="C57" s="142"/>
+      <c r="D57" s="142"/>
+      <c r="E57" s="147"/>
       <c r="Z57" s="59"/>
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A58" s="132" t="s">
-        <v>215</v>
-      </c>
-      <c r="B58" s="133"/>
-      <c r="C58" s="133"/>
+      <c r="A58" s="138" t="s">
+        <v>210</v>
+      </c>
+      <c r="B58" s="139"/>
+      <c r="C58" s="139"/>
       <c r="D58" s="82">
         <f>HLOOKUP($E$45,$18:$43,23)</f>
         <v>317.5</v>
@@ -7483,11 +8105,11 @@
       </c>
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A59" s="139" t="s">
-        <v>164</v>
-      </c>
-      <c r="B59" s="140"/>
-      <c r="C59" s="140"/>
+      <c r="A59" s="141" t="s">
+        <v>159</v>
+      </c>
+      <c r="B59" s="142"/>
+      <c r="C59" s="142"/>
       <c r="D59" s="75">
         <f>HLOOKUP($E$45,$18:$43,24)</f>
         <v>321</v>
@@ -7497,11 +8119,11 @@
       </c>
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A60" s="139" t="s">
-        <v>284</v>
-      </c>
-      <c r="B60" s="140"/>
-      <c r="C60" s="140"/>
+      <c r="A60" s="141" t="s">
+        <v>277</v>
+      </c>
+      <c r="B60" s="142"/>
+      <c r="C60" s="142"/>
       <c r="D60" s="75">
         <f>HLOOKUP($E$45,$18:$43,25)</f>
         <v>309.75</v>
@@ -7511,11 +8133,11 @@
       </c>
     </row>
     <row r="61" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A61" s="141" t="s">
-        <v>165</v>
-      </c>
-      <c r="B61" s="142"/>
-      <c r="C61" s="142"/>
+      <c r="A61" s="145" t="s">
+        <v>160</v>
+      </c>
+      <c r="B61" s="146"/>
+      <c r="C61" s="146"/>
       <c r="D61" s="80">
         <f>HLOOKUP($E$45,$18:$43,26)</f>
         <v>57</v>
@@ -7526,6 +8148,95 @@
     </row>
   </sheetData>
   <mergeCells count="113">
+    <mergeCell ref="N35:S35"/>
+    <mergeCell ref="N36:Q36"/>
+    <mergeCell ref="U41:X41"/>
+    <mergeCell ref="U42:X42"/>
+    <mergeCell ref="U43:X43"/>
+    <mergeCell ref="U27:X27"/>
+    <mergeCell ref="U28:X28"/>
+    <mergeCell ref="U29:X29"/>
+    <mergeCell ref="U30:X30"/>
+    <mergeCell ref="U31:X31"/>
+    <mergeCell ref="U32:X32"/>
+    <mergeCell ref="U33:X33"/>
+    <mergeCell ref="U34:X34"/>
+    <mergeCell ref="U35:Z35"/>
+    <mergeCell ref="U36:X36"/>
+    <mergeCell ref="U37:X37"/>
+    <mergeCell ref="U38:X38"/>
+    <mergeCell ref="U39:X39"/>
+    <mergeCell ref="U40:X40"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="K2:Q2"/>
+    <mergeCell ref="N18:Q18"/>
+    <mergeCell ref="N19:Q19"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="N20:Q20"/>
+    <mergeCell ref="N21:Q21"/>
+    <mergeCell ref="N22:Q22"/>
+    <mergeCell ref="N23:Q23"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="G26:L26"/>
+    <mergeCell ref="G27:J27"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="N33:Q33"/>
+    <mergeCell ref="N34:Q34"/>
+    <mergeCell ref="U18:X18"/>
+    <mergeCell ref="U19:X19"/>
+    <mergeCell ref="U20:X20"/>
+    <mergeCell ref="U21:X21"/>
+    <mergeCell ref="U22:X22"/>
+    <mergeCell ref="N29:Q29"/>
+    <mergeCell ref="N30:Q30"/>
+    <mergeCell ref="N31:Q31"/>
+    <mergeCell ref="U26:Z26"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="U25:X25"/>
+    <mergeCell ref="N26:S26"/>
+    <mergeCell ref="N27:Q27"/>
+    <mergeCell ref="N28:Q28"/>
+    <mergeCell ref="U23:X23"/>
+    <mergeCell ref="N24:Q24"/>
     <mergeCell ref="G24:J24"/>
     <mergeCell ref="G25:J25"/>
     <mergeCell ref="N43:Q43"/>
@@ -7550,121 +8261,32 @@
     <mergeCell ref="G37:J37"/>
     <mergeCell ref="G38:J38"/>
     <mergeCell ref="N32:Q32"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="G26:L26"/>
-    <mergeCell ref="G27:J27"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="G30:J30"/>
-    <mergeCell ref="N33:Q33"/>
-    <mergeCell ref="N34:Q34"/>
-    <mergeCell ref="U18:X18"/>
-    <mergeCell ref="U19:X19"/>
-    <mergeCell ref="U20:X20"/>
-    <mergeCell ref="U21:X21"/>
-    <mergeCell ref="U22:X22"/>
-    <mergeCell ref="N29:Q29"/>
-    <mergeCell ref="N30:Q30"/>
-    <mergeCell ref="N31:Q31"/>
-    <mergeCell ref="U26:Z26"/>
-    <mergeCell ref="U24:X24"/>
-    <mergeCell ref="U25:X25"/>
-    <mergeCell ref="N26:S26"/>
-    <mergeCell ref="N27:Q27"/>
-    <mergeCell ref="N28:Q28"/>
-    <mergeCell ref="U23:X23"/>
-    <mergeCell ref="N24:Q24"/>
-    <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="N18:Q18"/>
-    <mergeCell ref="N19:Q19"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="N20:Q20"/>
-    <mergeCell ref="N21:Q21"/>
-    <mergeCell ref="N22:Q22"/>
-    <mergeCell ref="N23:Q23"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="N35:S35"/>
-    <mergeCell ref="N36:Q36"/>
-    <mergeCell ref="U41:X41"/>
-    <mergeCell ref="U42:X42"/>
-    <mergeCell ref="U43:X43"/>
-    <mergeCell ref="U27:X27"/>
-    <mergeCell ref="U28:X28"/>
-    <mergeCell ref="U29:X29"/>
-    <mergeCell ref="U30:X30"/>
-    <mergeCell ref="U31:X31"/>
-    <mergeCell ref="U32:X32"/>
-    <mergeCell ref="U33:X33"/>
-    <mergeCell ref="U34:X34"/>
-    <mergeCell ref="U35:Z35"/>
-    <mergeCell ref="U36:X36"/>
-    <mergeCell ref="U37:X37"/>
-    <mergeCell ref="U38:X38"/>
-    <mergeCell ref="U39:X39"/>
-    <mergeCell ref="U40:X40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC1D7275-A232-429A-A734-4E325D043F64}">
-  <dimension ref="A1:AA38"/>
+  <dimension ref="A1:AA40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="29" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="s">
-        <v>138</v>
-      </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
+      <c r="A1" s="127" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="94" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B2" s="94"/>
       <c r="C2" s="94"/>
@@ -7677,7 +8299,7 @@
         <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
@@ -7692,33 +8314,33 @@
         <v>3</v>
       </c>
       <c r="F3" s="54" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="J3" s="94" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="K3" s="94"/>
       <c r="L3" s="94"/>
       <c r="M3" s="94"/>
       <c r="N3" s="94"/>
-      <c r="T3" s="118" t="s">
-        <v>160</v>
-      </c>
-      <c r="U3" s="118"/>
-      <c r="V3" s="118"/>
-      <c r="W3" s="118"/>
-      <c r="X3" s="118" t="s">
-        <v>187</v>
-      </c>
-      <c r="Y3" s="118"/>
-      <c r="Z3" s="118" t="s">
-        <v>176</v>
-      </c>
-      <c r="AA3" s="118"/>
+      <c r="T3" s="127" t="s">
+        <v>155</v>
+      </c>
+      <c r="U3" s="127"/>
+      <c r="V3" s="127"/>
+      <c r="W3" s="127"/>
+      <c r="X3" s="127" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y3" s="127"/>
+      <c r="Z3" s="127" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA3" s="127"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="94" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B4" s="94"/>
       <c r="C4" s="94"/>
@@ -7728,81 +8350,81 @@
         <v>?</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="J4" s="136" t="s">
+      <c r="J4" s="135" t="s">
         <v>0</v>
       </c>
-      <c r="K4" s="136"/>
-      <c r="L4" s="136"/>
+      <c r="K4" s="135"/>
+      <c r="L4" s="135"/>
       <c r="M4" s="78">
         <f>Передача!$D$49</f>
         <v>2016</v>
       </c>
       <c r="N4" s="75" t="s">
-        <v>159</v>
-      </c>
-      <c r="T4" s="118" t="s">
-        <v>250</v>
-      </c>
-      <c r="U4" s="118"/>
-      <c r="V4" s="118"/>
-      <c r="W4" s="118"/>
-      <c r="X4" s="118">
+        <v>154</v>
+      </c>
+      <c r="T4" s="127" t="s">
+        <v>245</v>
+      </c>
+      <c r="U4" s="127"/>
+      <c r="V4" s="127"/>
+      <c r="W4" s="127"/>
+      <c r="X4" s="127">
         <v>0</v>
       </c>
-      <c r="Y4" s="118"/>
-      <c r="Z4" s="118">
+      <c r="Y4" s="127"/>
+      <c r="Z4" s="127">
         <f ca="1">E19</f>
-        <v>56</v>
-      </c>
-      <c r="AA4" s="118"/>
+        <v>50</v>
+      </c>
+      <c r="AA4" s="127"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A5" s="103" t="s">
-        <v>211</v>
-      </c>
-      <c r="B5" s="103"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
+      <c r="A5" s="126" t="s">
+        <v>206</v>
+      </c>
+      <c r="B5" s="126"/>
+      <c r="C5" s="126"/>
+      <c r="D5" s="126"/>
       <c r="E5" s="70" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="J5" s="136" t="s">
-        <v>157</v>
-      </c>
-      <c r="K5" s="136"/>
-      <c r="L5" s="136"/>
+      <c r="J5" s="135" t="s">
+        <v>152</v>
+      </c>
+      <c r="K5" s="135"/>
+      <c r="L5" s="135"/>
       <c r="M5" s="78">
         <f>Передача!$D$50</f>
         <v>734</v>
       </c>
       <c r="N5" s="75" t="s">
-        <v>159</v>
-      </c>
-      <c r="T5" s="118" t="s">
-        <v>252</v>
-      </c>
-      <c r="U5" s="118"/>
-      <c r="V5" s="118"/>
-      <c r="W5" s="118"/>
-      <c r="X5" s="118">
+        <v>154</v>
+      </c>
+      <c r="T5" s="127" t="s">
+        <v>247</v>
+      </c>
+      <c r="U5" s="127"/>
+      <c r="V5" s="127"/>
+      <c r="W5" s="127"/>
+      <c r="X5" s="127">
         <f ca="1">E19</f>
-        <v>56</v>
-      </c>
-      <c r="Y5" s="118"/>
-      <c r="Z5" s="118">
+        <v>50</v>
+      </c>
+      <c r="Y5" s="127"/>
+      <c r="Z5" s="127">
         <f>E18</f>
         <v>80</v>
       </c>
-      <c r="AA5" s="118"/>
+      <c r="AA5" s="127"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A6" s="118" t="s">
-        <v>155</v>
-      </c>
-      <c r="B6" s="118"/>
-      <c r="C6" s="118"/>
-      <c r="D6" s="118"/>
+      <c r="A6" s="127" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="127"/>
+      <c r="C6" s="127"/>
+      <c r="D6" s="127"/>
       <c r="E6">
         <f>Передача!$D$47</f>
         <v>2.5</v>
@@ -7810,40 +8432,40 @@
       <c r="F6" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="136" t="s">
-        <v>158</v>
-      </c>
-      <c r="K6" s="136"/>
-      <c r="L6" s="136"/>
+      <c r="J6" s="135" t="s">
+        <v>153</v>
+      </c>
+      <c r="K6" s="135"/>
+      <c r="L6" s="135"/>
       <c r="M6" s="78">
         <f>Передача!$D$51</f>
         <v>0</v>
       </c>
       <c r="N6" s="75" t="s">
-        <v>159</v>
-      </c>
-      <c r="T6" s="118" t="s">
-        <v>236</v>
-      </c>
-      <c r="U6" s="118"/>
-      <c r="V6" s="118"/>
-      <c r="W6" s="118"/>
-      <c r="X6" s="148">
-        <v>0.3</v>
-      </c>
-      <c r="Y6" s="148"/>
-      <c r="Z6" s="148">
-        <v>0.3</v>
-      </c>
-      <c r="AA6" s="148"/>
+        <v>154</v>
+      </c>
+      <c r="T6" s="127" t="s">
+        <v>354</v>
+      </c>
+      <c r="U6" s="127"/>
+      <c r="V6" s="127"/>
+      <c r="W6" s="127"/>
+      <c r="X6" s="127">
+        <v>45</v>
+      </c>
+      <c r="Y6" s="127"/>
+      <c r="Z6" s="127">
+        <v>45</v>
+      </c>
+      <c r="AA6" s="127"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A7" s="118" t="s">
-        <v>213</v>
-      </c>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
+      <c r="A7" s="127" t="s">
+        <v>208</v>
+      </c>
+      <c r="B7" s="127"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
       <c r="E7">
         <f>Передача!$D$58</f>
         <v>317.5</v>
@@ -7851,26 +8473,24 @@
       <c r="F7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="T7" s="118" t="s">
-        <v>247</v>
-      </c>
-      <c r="U7" s="118"/>
-      <c r="V7" s="118"/>
-      <c r="W7" s="118"/>
-      <c r="X7" s="148">
-        <f>2.1*10^5</f>
-        <v>210000</v>
-      </c>
-      <c r="Y7" s="148"/>
-      <c r="Z7" s="148">
-        <f>2.1*10^5</f>
-        <v>210000</v>
-      </c>
-      <c r="AA7" s="148"/>
+      <c r="T7" s="127" t="s">
+        <v>231</v>
+      </c>
+      <c r="U7" s="127"/>
+      <c r="V7" s="127"/>
+      <c r="W7" s="127"/>
+      <c r="X7" s="149">
+        <v>0.3</v>
+      </c>
+      <c r="Y7" s="149"/>
+      <c r="Z7" s="149">
+        <v>0.3</v>
+      </c>
+      <c r="AA7" s="149"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="94" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B8" s="94"/>
       <c r="C8" s="94"/>
@@ -7882,31 +8502,33 @@
       <c r="F8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="147" t="s">
-        <v>253</v>
-      </c>
-      <c r="K8" s="147"/>
-      <c r="L8" s="147"/>
-      <c r="M8" s="147"/>
-      <c r="N8" s="147"/>
-      <c r="T8" s="118" t="s">
-        <v>246</v>
-      </c>
-      <c r="U8" s="118"/>
-      <c r="V8" s="118"/>
-      <c r="W8" s="118"/>
-      <c r="X8" s="148">
-        <v>330</v>
-      </c>
-      <c r="Y8" s="148"/>
-      <c r="Z8" s="148">
-        <v>330</v>
-      </c>
-      <c r="AA8" s="148"/>
+      <c r="J8" s="148" t="s">
+        <v>353</v>
+      </c>
+      <c r="K8" s="148"/>
+      <c r="L8" s="148"/>
+      <c r="M8" s="148"/>
+      <c r="N8" s="148"/>
+      <c r="T8" s="127" t="s">
+        <v>242</v>
+      </c>
+      <c r="U8" s="127"/>
+      <c r="V8" s="127"/>
+      <c r="W8" s="127"/>
+      <c r="X8" s="149">
+        <f>2.1*10^5</f>
+        <v>210000</v>
+      </c>
+      <c r="Y8" s="149"/>
+      <c r="Z8" s="149">
+        <f>2.1*10^5</f>
+        <v>210000</v>
+      </c>
+      <c r="AA8" s="149"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="94" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B9" s="94"/>
       <c r="C9" s="94"/>
@@ -7918,11 +8540,11 @@
       <c r="F9" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="118" t="s">
-        <v>172</v>
-      </c>
-      <c r="K9" s="118"/>
-      <c r="L9" s="118"/>
+      <c r="J9" s="127" t="s">
+        <v>167</v>
+      </c>
+      <c r="K9" s="127"/>
+      <c r="L9" s="127"/>
       <c r="M9">
         <f ca="1">Передача!$E$5</f>
         <v>339.37130342425513</v>
@@ -7930,30 +8552,30 @@
       <c r="N9" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="T9" s="118" t="s">
-        <v>248</v>
-      </c>
-      <c r="U9" s="118"/>
-      <c r="V9" s="118"/>
-      <c r="W9" s="118"/>
-      <c r="X9" s="118">
-        <f ca="1">(X5*X5+X4*X4)/(X5*X5-X4*X4)-X6</f>
-        <v>0.7</v>
-      </c>
-      <c r="Y9" s="118"/>
-      <c r="Z9" s="118">
-        <f ca="1">(Z5*Z5+Z4*Z4)/(Z5*Z5-Z4*Z4)+Z6</f>
-        <v>3.22156862745098</v>
-      </c>
-      <c r="AA9" s="118"/>
+      <c r="T9" s="127" t="s">
+        <v>241</v>
+      </c>
+      <c r="U9" s="127"/>
+      <c r="V9" s="127"/>
+      <c r="W9" s="127"/>
+      <c r="X9" s="149">
+        <f>VLOOKUP(X6,Материалы!$A:$L,8)</f>
+        <v>650</v>
+      </c>
+      <c r="Y9" s="149"/>
+      <c r="Z9" s="149">
+        <f>VLOOKUP(Z6,Материалы!$A:$L,8)</f>
+        <v>650</v>
+      </c>
+      <c r="AA9" s="149"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A10" s="118" t="s">
-        <v>165</v>
-      </c>
-      <c r="B10" s="118"/>
-      <c r="C10" s="118"/>
-      <c r="D10" s="118"/>
+      <c r="A10" s="127" t="s">
+        <v>160</v>
+      </c>
+      <c r="B10" s="127"/>
+      <c r="C10" s="127"/>
+      <c r="D10" s="127"/>
       <c r="E10">
         <f>Передача!$D$61</f>
         <v>57</v>
@@ -7961,79 +8583,95 @@
       <c r="F10" t="s">
         <v>16</v>
       </c>
-      <c r="J10" s="118" t="s">
-        <v>227</v>
-      </c>
-      <c r="K10" s="118"/>
-      <c r="L10" s="118"/>
+      <c r="J10" s="127" t="s">
+        <v>222</v>
+      </c>
+      <c r="K10" s="127"/>
+      <c r="L10" s="127"/>
       <c r="M10" s="52">
         <v>3</v>
       </c>
       <c r="N10" s="25" t="s">
-        <v>230</v>
-      </c>
-      <c r="T10" s="118" t="s">
-        <v>249</v>
-      </c>
-      <c r="U10" s="118"/>
-      <c r="V10" s="118"/>
-      <c r="W10" s="118"/>
-      <c r="X10" s="118">
-        <f ca="1">0.5*X8*(1-(X4*X4/X5/X5))</f>
-        <v>165</v>
-      </c>
-      <c r="Y10" s="118"/>
-      <c r="Z10" s="118">
-        <f ca="1">0.5*Z8*(1-(Z4*Z4/Z5/Z5))</f>
-        <v>84.15</v>
-      </c>
-      <c r="AA10" s="118"/>
+        <v>225</v>
+      </c>
+      <c r="T10" s="127" t="s">
+        <v>243</v>
+      </c>
+      <c r="U10" s="127"/>
+      <c r="V10" s="127"/>
+      <c r="W10" s="127"/>
+      <c r="X10" s="127">
+        <f ca="1">(X5*X5+X4*X4)/(X5*X5-X4*X4)-X7</f>
+        <v>0.7</v>
+      </c>
+      <c r="Y10" s="127"/>
+      <c r="Z10" s="127">
+        <f ca="1">(Z5*Z5+Z4*Z4)/(Z5*Z5-Z4*Z4)+Z7</f>
+        <v>2.5820512820512818</v>
+      </c>
+      <c r="AA10" s="127"/>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A11" s="118" t="s">
-        <v>217</v>
-      </c>
-      <c r="B11" s="118"/>
-      <c r="C11" s="118"/>
-      <c r="D11" s="118"/>
+      <c r="A11" s="127" t="s">
+        <v>212</v>
+      </c>
+      <c r="B11" s="127"/>
+      <c r="C11" s="127"/>
+      <c r="D11" s="127"/>
       <c r="E11">
-        <f>_xlfn.MINIFS($32:$32,$31:$31,"&gt;="&amp;E7)</f>
+        <f>_xlfn.MINIFS($34:$34,$33:$33,"&gt;="&amp;E7)</f>
         <v>5</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
       </c>
-      <c r="J11" s="118" t="s">
+      <c r="J11" s="127" t="s">
+        <v>224</v>
+      </c>
+      <c r="K11" s="127"/>
+      <c r="L11" s="127"/>
+      <c r="M11" s="52">
+        <f>E37</f>
+        <v>0.08</v>
+      </c>
+      <c r="O11" t="s">
         <v>229</v>
       </c>
-      <c r="K11" s="118"/>
-      <c r="L11" s="118"/>
-      <c r="M11" s="52">
-        <f>E35</f>
-        <v>0.08</v>
-      </c>
-      <c r="O11" t="s">
-        <v>234</v>
-      </c>
+      <c r="T11" s="127" t="s">
+        <v>244</v>
+      </c>
+      <c r="U11" s="127"/>
+      <c r="V11" s="127"/>
+      <c r="W11" s="127"/>
+      <c r="X11" s="127">
+        <f ca="1">0.5*X9*(1-(X4*X4/X5/X5))</f>
+        <v>325</v>
+      </c>
+      <c r="Y11" s="127"/>
+      <c r="Z11" s="127">
+        <f ca="1">0.5*Z9*(1-(Z4*Z4/Z5/Z5))</f>
+        <v>198.046875</v>
+      </c>
+      <c r="AA11" s="127"/>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A12" s="118" t="s">
-        <v>218</v>
-      </c>
-      <c r="B12" s="118"/>
-      <c r="C12" s="118"/>
-      <c r="D12" s="118"/>
+      <c r="A12" s="127" t="s">
+        <v>213</v>
+      </c>
+      <c r="B12" s="127"/>
+      <c r="C12" s="127"/>
+      <c r="D12" s="127"/>
       <c r="E12" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
       </c>
-      <c r="J12" s="118" t="s">
-        <v>231</v>
-      </c>
-      <c r="K12" s="118"/>
-      <c r="L12" s="118"/>
+      <c r="J12" s="127" t="s">
+        <v>226</v>
+      </c>
+      <c r="K12" s="127"/>
+      <c r="L12" s="127"/>
       <c r="M12" s="25">
         <f>E17</f>
         <v>57</v>
@@ -8042,42 +8680,42 @@
         <v>16</v>
       </c>
       <c r="O12" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A13" s="146" t="s">
-        <v>220</v>
-      </c>
-      <c r="B13" s="118"/>
-      <c r="C13" s="118"/>
-      <c r="D13" s="118"/>
+      <c r="A13" s="150" t="s">
+        <v>215</v>
+      </c>
+      <c r="B13" s="127"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="127"/>
       <c r="E13" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F13" t="s">
-        <v>221</v>
-      </c>
-      <c r="J13" s="118" t="s">
-        <v>228</v>
-      </c>
-      <c r="K13" s="118"/>
-      <c r="L13" s="118"/>
+        <v>216</v>
+      </c>
+      <c r="J13" s="127" t="s">
+        <v>223</v>
+      </c>
+      <c r="K13" s="127"/>
+      <c r="L13" s="127"/>
       <c r="M13">
         <f ca="1">2000*M10*M9/(PI()*E19*E19*M12*M11)</f>
-        <v>45.324768799937637</v>
+        <v>56.855389982641753</v>
       </c>
       <c r="N13" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A14" s="118" t="s">
-        <v>225</v>
-      </c>
-      <c r="B14" s="118"/>
-      <c r="C14" s="118"/>
-      <c r="D14" s="118"/>
+      <c r="A14" s="127" t="s">
+        <v>220</v>
+      </c>
+      <c r="B14" s="127"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
       <c r="E14">
         <f>2.2*E6+0.05*E10</f>
         <v>8.35</v>
@@ -8085,78 +8723,78 @@
       <c r="F14" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="118" t="s">
-        <v>235</v>
-      </c>
-      <c r="K14" s="118"/>
-      <c r="L14" s="118"/>
+      <c r="J14" s="127" t="s">
+        <v>230</v>
+      </c>
+      <c r="K14" s="127"/>
+      <c r="L14" s="127"/>
       <c r="M14">
-        <f ca="1">1000*M13*E19*(X9/X7+Z9/Z7)</f>
-        <v>47.398451032614524</v>
+        <f ca="1">1000*M13*E19*(X10/X8+Z10/Z8)</f>
+        <v>44.429120377155947</v>
       </c>
       <c r="N14" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A15" s="118" t="s">
-        <v>223</v>
-      </c>
-      <c r="B15" s="118"/>
-      <c r="C15" s="118"/>
-      <c r="D15" s="118"/>
+      <c r="A15" s="127" t="s">
+        <v>218</v>
+      </c>
+      <c r="B15" s="127"/>
+      <c r="C15" s="127"/>
+      <c r="D15" s="127"/>
       <c r="E15">
         <f ca="1">(E18-E19)/2</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
       </c>
-      <c r="J15" s="118" t="s">
-        <v>242</v>
-      </c>
-      <c r="K15" s="118"/>
-      <c r="L15" s="118"/>
+      <c r="J15" s="127" t="s">
+        <v>237</v>
+      </c>
+      <c r="K15" s="127"/>
+      <c r="L15" s="127"/>
       <c r="M15">
-        <f>5.5*(E20+E22)</f>
-        <v>0</v>
+        <f>5.5*(E20+E30)</f>
+        <v>17.600000000000001</v>
       </c>
       <c r="N15" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="O15" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A16" s="118" t="s">
-        <v>240</v>
-      </c>
-      <c r="B16" s="118"/>
-      <c r="C16" s="118"/>
-      <c r="D16" s="118"/>
+      <c r="A16" s="127" t="s">
+        <v>235</v>
+      </c>
+      <c r="B16" s="127"/>
+      <c r="C16" s="127"/>
+      <c r="D16" s="127"/>
       <c r="E16" s="52">
         <v>1</v>
       </c>
-      <c r="J16" s="118" t="s">
-        <v>243</v>
-      </c>
-      <c r="K16" s="118"/>
-      <c r="L16" s="118"/>
+      <c r="J16" s="127" t="s">
+        <v>238</v>
+      </c>
+      <c r="K16" s="127"/>
+      <c r="L16" s="127"/>
       <c r="N16" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="O16" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="118" t="s">
-        <v>238</v>
-      </c>
-      <c r="B17" s="118"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="118"/>
+      <c r="A17" s="127" t="s">
+        <v>233</v>
+      </c>
+      <c r="B17" s="127"/>
+      <c r="C17" s="127"/>
+      <c r="D17" s="127"/>
       <c r="E17">
         <f>E10*E16</f>
         <v>57</v>
@@ -8164,406 +8802,449 @@
       <c r="F17" t="s">
         <v>16</v>
       </c>
-      <c r="J17" s="118" t="s">
-        <v>244</v>
-      </c>
-      <c r="K17" s="118"/>
-      <c r="L17" s="118"/>
+      <c r="J17" s="127" t="s">
+        <v>239</v>
+      </c>
+      <c r="K17" s="127"/>
+      <c r="L17" s="127"/>
       <c r="M17" s="25">
         <f ca="1">SUM(M14:M16)</f>
-        <v>47.398451032614524</v>
+        <v>62.029120377155948</v>
       </c>
       <c r="N17" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="118" t="s">
-        <v>239</v>
-      </c>
-      <c r="B18" s="118"/>
-      <c r="C18" s="118"/>
-      <c r="D18" s="118"/>
+      <c r="A18" s="127" t="s">
+        <v>234</v>
+      </c>
+      <c r="B18" s="127"/>
+      <c r="C18" s="127"/>
+      <c r="D18" s="127"/>
       <c r="E18" s="52">
         <v>80</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
       </c>
-      <c r="J18" s="118" t="s">
-        <v>251</v>
-      </c>
-      <c r="K18" s="118"/>
-      <c r="L18" s="118"/>
+      <c r="J18" s="127" t="s">
+        <v>246</v>
+      </c>
+      <c r="K18" s="127"/>
+      <c r="L18" s="127"/>
       <c r="M18">
-        <f ca="1">MAX(X10:AA10)*M14/M13</f>
-        <v>172.54901960784315</v>
+        <f ca="1">MAX(X11:AA11)*M14/M13</f>
+        <v>253.96825396825395</v>
       </c>
       <c r="N18" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="147" t="s">
-        <v>237</v>
-      </c>
-      <c r="B19" s="147"/>
-      <c r="C19" s="147"/>
-      <c r="D19" s="147"/>
+      <c r="A19" s="148" t="s">
+        <v>232</v>
+      </c>
+      <c r="B19" s="148"/>
+      <c r="C19" s="148"/>
+      <c r="D19" s="148"/>
       <c r="E19" s="77">
-        <f ca="1">Вал!$S$18</f>
-        <v>56</v>
+        <f ca="1">Вал!$S$21</f>
+        <v>50</v>
       </c>
       <c r="F19" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="J19" s="118" t="s">
-        <v>245</v>
-      </c>
-      <c r="K19" s="118"/>
-      <c r="L19" s="118"/>
+      <c r="J19" s="127" t="s">
+        <v>240</v>
+      </c>
+      <c r="K19" s="127"/>
+      <c r="L19" s="127"/>
       <c r="M19" s="90">
         <f ca="1">M18+M15</f>
-        <v>172.54901960784315</v>
+        <v>271.56825396825394</v>
       </c>
       <c r="N19" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="118" t="s">
-        <v>292</v>
-      </c>
-      <c r="B20" s="118"/>
-      <c r="C20" s="118"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="52"/>
+      <c r="A20" s="127" t="s">
+        <v>285</v>
+      </c>
+      <c r="B20" s="127"/>
+      <c r="C20" s="127"/>
+      <c r="D20" s="127"/>
+      <c r="E20" s="71">
+        <v>1.6</v>
+      </c>
       <c r="F20" s="77" t="s">
-        <v>241</v>
-      </c>
-      <c r="M20" t="s">
-        <v>254</v>
+        <v>236</v>
+      </c>
+      <c r="M20" s="151" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="118" t="s">
-        <v>293</v>
-      </c>
-      <c r="B21" s="118"/>
-      <c r="C21" s="118"/>
-      <c r="D21" s="118"/>
-      <c r="E21" s="92" t="s">
-        <v>294</v>
+      <c r="A21" s="127" t="s">
+        <v>287</v>
+      </c>
+      <c r="B21" s="127"/>
+      <c r="C21" s="127"/>
+      <c r="D21" s="127"/>
+      <c r="E21">
+        <f ca="1">MAX(E10/4,(E15+E14)/2)</f>
+        <v>14.25</v>
       </c>
       <c r="F21" t="s">
         <v>16</v>
       </c>
-      <c r="J21" s="118" t="s">
-        <v>264</v>
-      </c>
-      <c r="K21" s="118"/>
-      <c r="L21" s="118"/>
+      <c r="J21" s="127" t="s">
+        <v>257</v>
+      </c>
+      <c r="K21" s="127"/>
+      <c r="L21" s="127"/>
       <c r="M21">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="N21">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="O21" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="118" t="s">
-        <v>295</v>
-      </c>
-      <c r="B22" s="118"/>
-      <c r="C22" s="118"/>
-      <c r="D22" s="118"/>
-      <c r="E22" s="52"/>
+      <c r="A22" s="127" t="s">
+        <v>352</v>
+      </c>
+      <c r="B22" s="127"/>
+      <c r="C22" s="127"/>
+      <c r="D22" s="127"/>
+      <c r="E22">
+        <f ca="1">(E10-E21)/2</f>
+        <v>21.375</v>
+      </c>
       <c r="F22" t="s">
-        <v>241</v>
-      </c>
-      <c r="J22" s="118" t="s">
-        <v>256</v>
-      </c>
-      <c r="K22" s="118"/>
-      <c r="L22" s="118"/>
+        <v>16</v>
+      </c>
+      <c r="J22" s="127" t="s">
+        <v>249</v>
+      </c>
+      <c r="K22" s="127"/>
+      <c r="L22" s="127"/>
       <c r="M22">
         <v>0.2</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="118" t="s">
-        <v>296</v>
-      </c>
-      <c r="B23" s="118"/>
-      <c r="C23" s="118"/>
-      <c r="D23" s="118"/>
-      <c r="E23">
-        <f ca="1">MAX(E10/4,(E15+E14)/2)</f>
-        <v>14.25</v>
-      </c>
-      <c r="F23" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="118" t="s">
-        <v>255</v>
-      </c>
-      <c r="K23" s="118"/>
-      <c r="L23" s="118"/>
+      <c r="J23" s="127" t="s">
+        <v>248</v>
+      </c>
+      <c r="K23" s="127"/>
+      <c r="L23" s="127"/>
       <c r="M23">
         <f ca="1">PI()*E19*M12*(M21-M15)*M22/1000</f>
-        <v>180.50334750465515</v>
+        <v>86.670258127235229</v>
       </c>
       <c r="N23" t="s">
         <v>4</v>
       </c>
     </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" s="127" t="s">
+        <v>182</v>
+      </c>
+      <c r="B24" s="127"/>
+      <c r="C24" s="127"/>
+      <c r="D24" s="127"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" s="127" t="s">
+        <v>258</v>
+      </c>
+      <c r="B25" s="127"/>
+      <c r="C25" s="127"/>
+      <c r="D25" s="127"/>
+      <c r="E25">
+        <f ca="1">E19</f>
+        <v>50</v>
+      </c>
+      <c r="F25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="127" t="s">
+        <v>356</v>
+      </c>
+      <c r="B26" s="127"/>
+      <c r="C26" s="127"/>
+      <c r="D26" s="127"/>
+      <c r="E26">
+        <f>Корпус!$E$8</f>
+        <v>10.072378298355165</v>
+      </c>
+      <c r="F26" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="48"/>
+      <c r="K26" s="48"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" s="127" t="s">
+        <v>355</v>
+      </c>
+      <c r="B27" s="127"/>
+      <c r="C27" s="127"/>
+      <c r="D27" s="127"/>
+      <c r="E27">
+        <f ca="1">Вал!$S$18</f>
+        <v>20</v>
+      </c>
+      <c r="F27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" s="127" t="s">
+        <v>357</v>
+      </c>
+      <c r="B28" s="127"/>
+      <c r="C28" s="127"/>
+      <c r="D28" s="127"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" s="127" t="s">
+        <v>202</v>
+      </c>
+      <c r="B29" s="127"/>
+      <c r="C29" s="127"/>
+      <c r="D29" s="127"/>
+      <c r="E29">
+        <f ca="1">E27*2+2+E10+E26*2</f>
+        <v>119.14475659671032</v>
+      </c>
+      <c r="F29" t="s">
+        <v>16</v>
+      </c>
+    </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="118" t="s">
-        <v>181</v>
-      </c>
-      <c r="B30" s="118"/>
-      <c r="C30">
+      <c r="A30" s="127" t="s">
+        <v>286</v>
+      </c>
+      <c r="B30" s="127"/>
+      <c r="C30" s="127"/>
+      <c r="D30" s="127"/>
+      <c r="E30" s="52">
+        <v>1.6</v>
+      </c>
+      <c r="F30" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="127" t="s">
+        <v>176</v>
+      </c>
+      <c r="B32" s="127"/>
+      <c r="C32">
         <v>20</v>
       </c>
-      <c r="D30">
+      <c r="D32">
         <v>30</v>
       </c>
-      <c r="E30">
+      <c r="E32">
         <v>40</v>
       </c>
-      <c r="F30">
+      <c r="F32">
         <v>50</v>
       </c>
-      <c r="G30">
+      <c r="G32">
         <v>80</v>
       </c>
-      <c r="H30">
+      <c r="H32">
         <v>120</v>
       </c>
-      <c r="I30">
+      <c r="I32">
         <v>150</v>
       </c>
-      <c r="J30">
+      <c r="J32">
         <v>250</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="118" t="s">
-        <v>182</v>
-      </c>
-      <c r="B31" s="118"/>
-      <c r="C31">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="127" t="s">
+        <v>177</v>
+      </c>
+      <c r="B33" s="127"/>
+      <c r="C33">
         <v>30</v>
       </c>
-      <c r="D31">
+      <c r="D33">
         <v>40</v>
       </c>
-      <c r="E31">
+      <c r="E33">
         <v>50</v>
       </c>
-      <c r="F31">
+      <c r="F33">
         <v>80</v>
       </c>
-      <c r="G31">
+      <c r="G33">
         <v>120</v>
       </c>
-      <c r="H31">
+      <c r="H33">
         <v>150</v>
       </c>
-      <c r="I31">
+      <c r="I33">
         <v>250</v>
       </c>
-      <c r="J31">
+      <c r="J33">
         <v>500</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="118" t="s">
-        <v>212</v>
-      </c>
-      <c r="B32" s="118"/>
-      <c r="C32">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="127" t="s">
+        <v>207</v>
+      </c>
+      <c r="B34" s="127"/>
+      <c r="C34">
         <v>1</v>
       </c>
-      <c r="D32">
+      <c r="D34">
         <v>1.2</v>
       </c>
-      <c r="E32">
+      <c r="E34">
         <v>1.6</v>
       </c>
-      <c r="F32">
+      <c r="F34">
         <v>2</v>
       </c>
-      <c r="G32">
+      <c r="G34">
         <v>2.5</v>
       </c>
-      <c r="H32">
+      <c r="H34">
         <v>3</v>
       </c>
-      <c r="I32">
+      <c r="I34">
         <v>4</v>
       </c>
-      <c r="J32">
+      <c r="J34">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="118" t="s">
-        <v>285</v>
-      </c>
-      <c r="B34" s="118"/>
-      <c r="C34" s="118" t="s">
-        <v>286</v>
-      </c>
-      <c r="D34" s="118"/>
-      <c r="E34" s="118" t="s">
-        <v>290</v>
-      </c>
-      <c r="F34" s="118"/>
-      <c r="G34" s="118" t="s">
-        <v>291</v>
-      </c>
-      <c r="H34" s="118"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="118" t="s">
-        <v>287</v>
-      </c>
-      <c r="B35" s="118"/>
-      <c r="C35" s="118" t="s">
-        <v>287</v>
-      </c>
-      <c r="D35" s="118"/>
-      <c r="E35" s="118">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="127" t="s">
+        <v>278</v>
+      </c>
+      <c r="B36" s="127"/>
+      <c r="C36" s="127" t="s">
+        <v>279</v>
+      </c>
+      <c r="D36" s="127"/>
+      <c r="E36" s="127" t="s">
+        <v>283</v>
+      </c>
+      <c r="F36" s="127"/>
+      <c r="G36" s="127" t="s">
+        <v>284</v>
+      </c>
+      <c r="H36" s="127"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="127" t="s">
+        <v>280</v>
+      </c>
+      <c r="B37" s="127"/>
+      <c r="C37" s="127" t="s">
+        <v>280</v>
+      </c>
+      <c r="D37" s="127"/>
+      <c r="E37" s="127">
         <v>0.08</v>
       </c>
-      <c r="F35" s="118"/>
-      <c r="G35" s="118">
+      <c r="F37" s="127"/>
+      <c r="G37" s="127">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H35" s="118"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="118" t="s">
-        <v>288</v>
-      </c>
-      <c r="B36" s="118"/>
-      <c r="C36" s="118" t="s">
-        <v>287</v>
-      </c>
-      <c r="D36" s="118"/>
-      <c r="E36" s="118">
+      <c r="H37" s="127"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="127" t="s">
+        <v>281</v>
+      </c>
+      <c r="B38" s="127"/>
+      <c r="C38" s="127" t="s">
+        <v>280</v>
+      </c>
+      <c r="D38" s="127"/>
+      <c r="E38" s="127">
         <v>0.08</v>
       </c>
-      <c r="F36" s="118"/>
-      <c r="G36" s="118">
+      <c r="F38" s="127"/>
+      <c r="G38" s="127">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H36" s="118"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="118" t="s">
-        <v>287</v>
-      </c>
-      <c r="B37" s="118"/>
-      <c r="C37" s="118" t="s">
-        <v>289</v>
-      </c>
-      <c r="D37" s="118"/>
-      <c r="E37" s="118">
+      <c r="H38" s="127"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" s="127" t="s">
+        <v>280</v>
+      </c>
+      <c r="B39" s="127"/>
+      <c r="C39" s="127" t="s">
+        <v>282</v>
+      </c>
+      <c r="D39" s="127"/>
+      <c r="E39" s="127">
         <v>0.05</v>
       </c>
-      <c r="F37" s="118"/>
-      <c r="G37" s="118">
+      <c r="F39" s="127"/>
+      <c r="G39" s="127">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="H37" s="118"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="118" t="s">
-        <v>288</v>
-      </c>
-      <c r="B38" s="118"/>
-      <c r="C38" s="118" t="s">
-        <v>289</v>
-      </c>
-      <c r="D38" s="118"/>
-      <c r="E38" s="118">
+      <c r="H39" s="127"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" s="127" t="s">
+        <v>281</v>
+      </c>
+      <c r="B40" s="127"/>
+      <c r="C40" s="127" t="s">
+        <v>282</v>
+      </c>
+      <c r="D40" s="127"/>
+      <c r="E40" s="127">
         <v>0.05</v>
       </c>
-      <c r="F38" s="118"/>
-      <c r="G38" s="118">
+      <c r="F40" s="127"/>
+      <c r="G40" s="127">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="H38" s="118"/>
+      <c r="H40" s="127"/>
     </row>
   </sheetData>
-  <mergeCells count="89">
-    <mergeCell ref="Z10:AA10"/>
-    <mergeCell ref="J8:N8"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="J21:L21"/>
-    <mergeCell ref="Z9:AA9"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="J18:L18"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="J17:L17"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="Z5:AA5"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="Z8:AA8"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="T3:W3"/>
-    <mergeCell ref="T4:W4"/>
-    <mergeCell ref="T5:W5"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="X5:Y5"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="T7:W7"/>
-    <mergeCell ref="T8:W8"/>
-    <mergeCell ref="T9:W9"/>
-    <mergeCell ref="T10:W10"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="X10:Y10"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="T6:W6"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A7:D7"/>
+  <mergeCells count="98">
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A32:B32"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A13:D13"/>
@@ -8574,23 +9255,74 @@
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:D36"/>
     <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="T7:W7"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="T8:W8"/>
+    <mergeCell ref="T9:W9"/>
+    <mergeCell ref="T10:W10"/>
+    <mergeCell ref="T11:W11"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="Z9:AA9"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="T3:W3"/>
+    <mergeCell ref="T4:W4"/>
+    <mergeCell ref="T5:W5"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="Z8:AA8"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="X11:Y11"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="T6:W6"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="Z11:AA11"/>
+    <mergeCell ref="J8:N8"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="Z10:AA10"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="J18:L18"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8598,7 +9330,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B080B891-BABE-48BC-B741-A9DC893B6424}">
   <dimension ref="A2:W29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8607,12 +9339,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="118" t="s">
-        <v>146</v>
-      </c>
-      <c r="B2" s="118"/>
-      <c r="C2" s="118"/>
-      <c r="D2" s="118"/>
+      <c r="A2" s="127" t="s">
+        <v>141</v>
+      </c>
+      <c r="B2" s="127"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
       <c r="E2">
         <f>Передача!$D$46</f>
         <v>180</v>
@@ -8622,12 +9354,12 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="118" t="s">
-        <v>202</v>
-      </c>
-      <c r="B3" s="118"/>
-      <c r="C3" s="118"/>
-      <c r="D3" s="118"/>
+      <c r="A3" s="127" t="s">
+        <v>197</v>
+      </c>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
       <c r="E3">
         <f>Передача!$D$55</f>
         <v>37.75</v>
@@ -8637,12 +9369,12 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="118" t="s">
-        <v>177</v>
-      </c>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
+      <c r="A4" s="127" t="s">
+        <v>172</v>
+      </c>
+      <c r="B4" s="127"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="127"/>
       <c r="E4">
         <f>Передача!$D$56</f>
         <v>62</v>
@@ -8652,12 +9384,12 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="118" t="s">
-        <v>203</v>
-      </c>
-      <c r="B5" s="118"/>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
+      <c r="A5" s="127" t="s">
+        <v>198</v>
+      </c>
+      <c r="B5" s="127"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="127"/>
       <c r="E5">
         <f>Передача!$D$60</f>
         <v>309.75</v>
@@ -8667,12 +9399,12 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="118" t="s">
-        <v>178</v>
-      </c>
-      <c r="B6" s="118"/>
-      <c r="C6" s="118"/>
-      <c r="D6" s="118"/>
+      <c r="A6" s="127" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="127"/>
+      <c r="C6" s="127"/>
+      <c r="D6" s="127"/>
       <c r="E6">
         <f>Передача!$D$61</f>
         <v>57</v>
@@ -8682,12 +9414,12 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="118" t="s">
-        <v>201</v>
-      </c>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
+      <c r="A7" s="127" t="s">
+        <v>196</v>
+      </c>
+      <c r="B7" s="127"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
       <c r="E7">
         <f>E2+E3/2+E5/2</f>
         <v>353.75</v>
@@ -8697,12 +9429,12 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="118" t="s">
-        <v>200</v>
-      </c>
-      <c r="B8" s="118"/>
-      <c r="C8" s="118"/>
-      <c r="D8" s="118"/>
+      <c r="A8" s="127" t="s">
+        <v>195</v>
+      </c>
+      <c r="B8" s="127"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="127"/>
       <c r="E8">
         <f>E7^(1/3)+3</f>
         <v>10.072378298355165</v>
@@ -8712,12 +9444,12 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="118" t="s">
-        <v>204</v>
-      </c>
-      <c r="B9" s="118"/>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
+      <c r="A9" s="127" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="127"/>
+      <c r="C9" s="127"/>
+      <c r="D9" s="127"/>
       <c r="E9">
         <f>E8*3</f>
         <v>30.217134895065495</v>
@@ -8727,12 +9459,12 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="118" t="s">
-        <v>205</v>
-      </c>
-      <c r="B10" s="118"/>
-      <c r="C10" s="118"/>
-      <c r="D10" s="118"/>
+      <c r="A10" s="127" t="s">
+        <v>200</v>
+      </c>
+      <c r="B10" s="127"/>
+      <c r="C10" s="127"/>
+      <c r="D10" s="127"/>
       <c r="E10" s="52">
         <v>4</v>
       </c>
@@ -8741,12 +9473,12 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="118" t="s">
-        <v>206</v>
-      </c>
-      <c r="B11" s="118"/>
-      <c r="C11" s="118"/>
-      <c r="D11" s="118"/>
+      <c r="A11" s="127" t="s">
+        <v>201</v>
+      </c>
+      <c r="B11" s="127"/>
+      <c r="C11" s="127"/>
+      <c r="D11" s="127"/>
       <c r="E11" s="52">
         <v>20</v>
       </c>
@@ -8755,22 +9487,22 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="118" t="s">
-        <v>208</v>
-      </c>
-      <c r="B12" s="118"/>
-      <c r="C12" s="118"/>
-      <c r="D12" s="118"/>
-      <c r="E12" s="118"/>
-      <c r="F12" s="118"/>
+      <c r="A12" s="127" t="s">
+        <v>203</v>
+      </c>
+      <c r="B12" s="127"/>
+      <c r="C12" s="127"/>
+      <c r="D12" s="127"/>
+      <c r="E12" s="127"/>
+      <c r="F12" s="127"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="118" t="s">
-        <v>207</v>
-      </c>
-      <c r="B13" s="118"/>
-      <c r="C13" s="118"/>
-      <c r="D13" s="118"/>
+      <c r="A13" s="127" t="s">
+        <v>202</v>
+      </c>
+      <c r="B13" s="127"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="127"/>
       <c r="E13">
         <f>E7+2*E8+E10*2+E11*2</f>
         <v>421.89475659671035</v>
@@ -8780,12 +9512,12 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="118" t="s">
-        <v>165</v>
-      </c>
-      <c r="B14" s="118"/>
-      <c r="C14" s="118"/>
-      <c r="D14" s="118"/>
+      <c r="A14" s="127" t="s">
+        <v>160</v>
+      </c>
+      <c r="B14" s="127"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
       <c r="E14">
         <f>E4+2*E8+2*E10</f>
         <v>90.144756596710323</v>
@@ -8795,12 +9527,12 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="118" t="s">
+      <c r="A15" s="127" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="118"/>
-      <c r="C15" s="118"/>
-      <c r="D15" s="118"/>
+      <c r="B15" s="127"/>
+      <c r="C15" s="127"/>
+      <c r="D15" s="127"/>
       <c r="E15">
         <f>E5+E8+E9+2*E10</f>
         <v>358.03951319342065</v>
@@ -8811,43 +9543,43 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="K16" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A17" s="118" t="s">
-        <v>335</v>
-      </c>
-      <c r="B17" s="118"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="118"/>
-      <c r="F17" s="118"/>
+      <c r="A17" s="127" t="s">
+        <v>324</v>
+      </c>
+      <c r="B17" s="127"/>
+      <c r="C17" s="127"/>
+      <c r="D17" s="127"/>
+      <c r="E17" s="127"/>
+      <c r="F17" s="127"/>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A18" s="118" t="s">
-        <v>331</v>
-      </c>
-      <c r="B18" s="118"/>
-      <c r="C18" s="118"/>
-      <c r="D18" s="118"/>
+      <c r="A18" s="127" t="s">
+        <v>320</v>
+      </c>
+      <c r="B18" s="127"/>
+      <c r="C18" s="127"/>
+      <c r="D18" s="127"/>
       <c r="E18">
         <f>Вал!$K$4*PI()/30</f>
         <v>150.79644737231007</v>
       </c>
       <c r="F18" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A19" s="118" t="s">
-        <v>332</v>
-      </c>
-      <c r="B19" s="118"/>
-      <c r="C19" s="118"/>
-      <c r="D19" s="118"/>
+      <c r="A19" s="127" t="s">
+        <v>321</v>
+      </c>
+      <c r="B19" s="127"/>
+      <c r="C19" s="127"/>
+      <c r="D19" s="127"/>
       <c r="E19">
-        <f>Корпус!$E$18*MAX(Вал!$K$19,Вал!$K$7)/1000</f>
+        <f>Корпус!$E$18*MAX(Вал!$K$21,Вал!$K$7)/1000</f>
         <v>7.3890259212431939</v>
       </c>
       <c r="F19" t="s">
@@ -8855,79 +9587,67 @@
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A20" s="118" t="s">
-        <v>336</v>
-      </c>
-      <c r="B20" s="118"/>
-      <c r="C20" s="118"/>
-      <c r="D20" s="118"/>
+      <c r="A20" s="127" t="s">
+        <v>325</v>
+      </c>
+      <c r="B20" s="127"/>
+      <c r="C20" s="127"/>
+      <c r="D20" s="127"/>
       <c r="E20" s="52">
         <v>504</v>
       </c>
       <c r="F20" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="R20" s="1"/>
-      <c r="S20" s="36"/>
-      <c r="T20" s="118" t="s">
-        <v>127</v>
-      </c>
-      <c r="U20" s="118"/>
-      <c r="V20" s="94" t="s">
-        <v>123</v>
-      </c>
-      <c r="W20" s="94"/>
+      <c r="S20" s="92"/>
+      <c r="T20" s="48"/>
+      <c r="U20" s="48"/>
+      <c r="V20" s="16"/>
+      <c r="W20" s="16"/>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A21" s="118" t="s">
-        <v>338</v>
-      </c>
-      <c r="B21" s="118"/>
-      <c r="C21" s="118"/>
-      <c r="D21" s="118"/>
+      <c r="A21" s="127" t="s">
+        <v>327</v>
+      </c>
+      <c r="B21" s="127"/>
+      <c r="C21" s="127"/>
+      <c r="D21" s="127"/>
       <c r="E21" s="52"/>
       <c r="F21" t="s">
-        <v>337</v>
-      </c>
-      <c r="R21" s="127" t="s">
-        <v>122</v>
-      </c>
-      <c r="S21" s="127"/>
-      <c r="T21" s="94"/>
-      <c r="U21" s="94"/>
-      <c r="V21" s="94"/>
-      <c r="W21" s="94"/>
+        <v>326</v>
+      </c>
+      <c r="R21" s="67"/>
+      <c r="S21" s="67"/>
+      <c r="T21" s="16"/>
+      <c r="U21" s="16"/>
+      <c r="V21" s="16"/>
+      <c r="W21" s="16"/>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A22" s="118" t="s">
-        <v>339</v>
-      </c>
-      <c r="B22" s="118"/>
-      <c r="C22" s="118"/>
-      <c r="D22" s="118"/>
+      <c r="A22" s="127" t="s">
+        <v>328</v>
+      </c>
+      <c r="B22" s="127"/>
+      <c r="C22" s="127"/>
+      <c r="D22" s="127"/>
       <c r="E22" t="s">
-        <v>340</v>
-      </c>
-      <c r="R22" s="127" t="s">
-        <v>124</v>
-      </c>
-      <c r="S22" s="127"/>
-      <c r="T22" s="94" t="s">
-        <v>125</v>
-      </c>
-      <c r="U22" s="94"/>
-      <c r="V22" s="106" t="s">
-        <v>126</v>
-      </c>
-      <c r="W22" s="106"/>
+        <v>329</v>
+      </c>
+      <c r="R22" s="67"/>
+      <c r="S22" s="67"/>
+      <c r="T22" s="16"/>
+      <c r="U22" s="16"/>
+      <c r="V22" s="63"/>
+      <c r="W22" s="63"/>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A23" s="118" t="s">
-        <v>341</v>
-      </c>
-      <c r="B23" s="118"/>
-      <c r="C23" s="118"/>
-      <c r="D23" s="118"/>
+      <c r="A23" s="127" t="s">
+        <v>330</v>
+      </c>
+      <c r="B23" s="127"/>
+      <c r="C23" s="127"/>
+      <c r="D23" s="127"/>
       <c r="E23">
         <f>MAX(4*Передача!$D$47,10)</f>
         <v>10</v>
@@ -8940,32 +9660,33 @@
         <v>16</v>
       </c>
       <c r="N23" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="K27" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="I28" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="I29" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
+  <mergeCells count="21">
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A12:F12"/>
@@ -8974,21 +9695,12 @@
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -8996,13 +9708,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D8564D3-007A-4908-B584-B11BCC9DA655}">
   <dimension ref="A1:E80"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="118">
+      <c r="A1" s="127">
         <v>1</v>
       </c>
       <c r="B1">
@@ -9011,14 +9723,14 @@
       <c r="D1" s="48"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="118"/>
+      <c r="A2" s="127"/>
       <c r="B2">
         <v>1.05</v>
       </c>
       <c r="D2" s="48"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="118">
+      <c r="A3" s="127">
         <v>1.1000000000000001</v>
       </c>
       <c r="B3">
@@ -9027,14 +9739,14 @@
       <c r="D3" s="48"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="118"/>
+      <c r="A4" s="127"/>
       <c r="B4">
         <v>1.1499999999999999</v>
       </c>
       <c r="D4" s="48"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="118">
+      <c r="A5" s="127">
         <v>1.2</v>
       </c>
       <c r="B5">
@@ -9043,14 +9755,14 @@
       <c r="D5" s="48"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="118"/>
+      <c r="A6" s="127"/>
       <c r="B6">
         <v>1.3</v>
       </c>
       <c r="D6" s="48"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="118">
+      <c r="A7" s="127">
         <v>1.4</v>
       </c>
       <c r="B7">
@@ -9059,14 +9771,14 @@
       <c r="D7" s="48"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="118"/>
+      <c r="A8" s="127"/>
       <c r="B8">
         <v>1.5</v>
       </c>
       <c r="D8" s="48"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="118">
+      <c r="A9" s="127">
         <v>1.6</v>
       </c>
       <c r="B9">
@@ -9075,14 +9787,14 @@
       <c r="D9" s="48"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="118"/>
+      <c r="A10" s="127"/>
       <c r="B10">
         <v>1.7</v>
       </c>
       <c r="D10" s="48"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="118">
+      <c r="A11" s="127">
         <v>1.8</v>
       </c>
       <c r="B11">
@@ -9091,14 +9803,14 @@
       <c r="D11" s="48"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="118"/>
+      <c r="A12" s="127"/>
       <c r="B12">
         <v>1.9</v>
       </c>
       <c r="D12" s="48"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="118">
+      <c r="A13" s="127">
         <v>2</v>
       </c>
       <c r="B13">
@@ -9107,14 +9819,14 @@
       <c r="D13" s="48"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="118"/>
+      <c r="A14" s="127"/>
       <c r="B14">
         <v>2.1</v>
       </c>
       <c r="D14" s="48"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="118">
+      <c r="A15" s="127">
         <v>2.2000000000000002</v>
       </c>
       <c r="B15">
@@ -9123,14 +9835,14 @@
       <c r="D15" s="48"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="118"/>
+      <c r="A16" s="127"/>
       <c r="B16">
         <v>2.4</v>
       </c>
       <c r="D16" s="48"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="118">
+      <c r="A17" s="127">
         <v>2.5</v>
       </c>
       <c r="B17">
@@ -9139,14 +9851,14 @@
       <c r="D17" s="48"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="118"/>
+      <c r="A18" s="127"/>
       <c r="B18">
         <v>2.6</v>
       </c>
       <c r="D18" s="48"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="118">
+      <c r="A19" s="127">
         <v>2.8</v>
       </c>
       <c r="B19">
@@ -9155,14 +9867,14 @@
       <c r="D19" s="48"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="118"/>
+      <c r="A20" s="127"/>
       <c r="B20">
         <v>3</v>
       </c>
       <c r="D20" s="48"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="118">
+      <c r="A21" s="127">
         <v>3.2</v>
       </c>
       <c r="B21">
@@ -9171,14 +9883,14 @@
       <c r="D21" s="48"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="118"/>
+      <c r="A22" s="127"/>
       <c r="B22">
         <v>3.4</v>
       </c>
       <c r="D22" s="48"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="118">
+      <c r="A23" s="127">
         <v>3.6</v>
       </c>
       <c r="B23">
@@ -9187,14 +9899,14 @@
       <c r="D23" s="48"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="118"/>
+      <c r="A24" s="127"/>
       <c r="B24">
         <v>3.8</v>
       </c>
       <c r="D24" s="48"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="118">
+      <c r="A25" s="127">
         <v>4</v>
       </c>
       <c r="B25">
@@ -9203,14 +9915,14 @@
       <c r="D25" s="48"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="118"/>
+      <c r="A26" s="127"/>
       <c r="B26">
         <v>4.2</v>
       </c>
       <c r="D26" s="48"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="118">
+      <c r="A27" s="127">
         <v>4.5</v>
       </c>
       <c r="B27">
@@ -9219,14 +9931,14 @@
       <c r="D27" s="48"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="118"/>
+      <c r="A28" s="127"/>
       <c r="B28">
         <v>4.8</v>
       </c>
       <c r="D28" s="48"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="118">
+      <c r="A29" s="127">
         <v>5</v>
       </c>
       <c r="B29">
@@ -9235,14 +9947,14 @@
       <c r="D29" s="48"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="118"/>
+      <c r="A30" s="127"/>
       <c r="B30">
         <v>5.3</v>
       </c>
       <c r="D30" s="48"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="118">
+      <c r="A31" s="127">
         <v>5.6</v>
       </c>
       <c r="B31">
@@ -9251,14 +9963,14 @@
       <c r="D31" s="48"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="118"/>
+      <c r="A32" s="127"/>
       <c r="B32">
         <v>6</v>
       </c>
       <c r="D32" s="48"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="118">
+      <c r="A33" s="127">
         <v>6.3</v>
       </c>
       <c r="B33">
@@ -9267,14 +9979,14 @@
       <c r="D33" s="48"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="118"/>
+      <c r="A34" s="127"/>
       <c r="B34">
         <v>6.7</v>
       </c>
       <c r="D34" s="48"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="118">
+      <c r="A35" s="127">
         <v>7.1</v>
       </c>
       <c r="B35">
@@ -9283,14 +9995,14 @@
       <c r="D35" s="48"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="118"/>
+      <c r="A36" s="127"/>
       <c r="B36">
         <v>7.5</v>
       </c>
       <c r="D36" s="48"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="118">
+      <c r="A37" s="127">
         <v>8</v>
       </c>
       <c r="B37">
@@ -9299,14 +10011,14 @@
       <c r="D37" s="48"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="118"/>
+      <c r="A38" s="127"/>
       <c r="B38">
         <v>8.5</v>
       </c>
       <c r="D38" s="48"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="118">
+      <c r="A39" s="127">
         <v>9</v>
       </c>
       <c r="B39">
@@ -9315,7 +10027,7 @@
       <c r="D39" s="48"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="118"/>
+      <c r="A40" s="127"/>
       <c r="B40" s="61">
         <v>9.5</v>
       </c>
@@ -9323,7 +10035,7 @@
       <c r="E40" s="61"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="118">
+      <c r="A41" s="127">
         <v>10</v>
       </c>
       <c r="B41" s="48">
@@ -9331,13 +10043,13 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="118"/>
+      <c r="A42" s="127"/>
       <c r="B42" s="48">
         <v>10.5</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="118">
+      <c r="A43" s="127">
         <v>11</v>
       </c>
       <c r="B43" s="48">
@@ -9345,13 +10057,13 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="118"/>
+      <c r="A44" s="127"/>
       <c r="B44" s="48">
         <v>11.5</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="118">
+      <c r="A45" s="127">
         <v>12</v>
       </c>
       <c r="B45" s="48">
@@ -9359,13 +10071,13 @@
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="118"/>
+      <c r="A46" s="127"/>
       <c r="B46" s="48">
         <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="118">
+      <c r="A47" s="127">
         <v>14</v>
       </c>
       <c r="B47" s="48">
@@ -9373,13 +10085,13 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="118"/>
+      <c r="A48" s="127"/>
       <c r="B48" s="48">
         <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="118">
+      <c r="A49" s="127">
         <v>16</v>
       </c>
       <c r="B49" s="48">
@@ -9387,13 +10099,13 @@
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="118"/>
+      <c r="A50" s="127"/>
       <c r="B50" s="48">
         <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="118">
+      <c r="A51" s="127">
         <v>18</v>
       </c>
       <c r="B51" s="48">
@@ -9401,13 +10113,13 @@
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="118"/>
+      <c r="A52" s="127"/>
       <c r="B52" s="48">
         <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="118">
+      <c r="A53" s="127">
         <v>20</v>
       </c>
       <c r="B53" s="48">
@@ -9415,13 +10127,13 @@
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="118"/>
+      <c r="A54" s="127"/>
       <c r="B54" s="48">
         <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="118">
+      <c r="A55" s="127">
         <v>22</v>
       </c>
       <c r="B55" s="48">
@@ -9429,13 +10141,13 @@
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="118"/>
+      <c r="A56" s="127"/>
       <c r="B56" s="48">
         <v>24</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="118">
+      <c r="A57" s="127">
         <v>25</v>
       </c>
       <c r="B57" s="48">
@@ -9443,13 +10155,13 @@
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="118"/>
+      <c r="A58" s="127"/>
       <c r="B58" s="48">
         <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="118">
+      <c r="A59" s="127">
         <v>28</v>
       </c>
       <c r="B59" s="48">
@@ -9457,13 +10169,13 @@
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="118"/>
+      <c r="A60" s="127"/>
       <c r="B60" s="48">
         <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="118">
+      <c r="A61" s="127">
         <v>32</v>
       </c>
       <c r="B61" s="48">
@@ -9471,13 +10183,13 @@
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="118"/>
+      <c r="A62" s="127"/>
       <c r="B62" s="48">
         <v>34</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="118">
+      <c r="A63" s="127">
         <v>36</v>
       </c>
       <c r="B63" s="48">
@@ -9485,13 +10197,13 @@
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="118"/>
+      <c r="A64" s="127"/>
       <c r="B64" s="48">
         <v>38</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="118">
+      <c r="A65" s="127">
         <v>40</v>
       </c>
       <c r="B65" s="48">
@@ -9499,13 +10211,13 @@
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="118"/>
+      <c r="A66" s="127"/>
       <c r="B66" s="48">
         <v>42</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="118">
+      <c r="A67" s="127">
         <v>45</v>
       </c>
       <c r="B67" s="48">
@@ -9513,13 +10225,13 @@
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="118"/>
+      <c r="A68" s="127"/>
       <c r="B68" s="48">
         <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="118">
+      <c r="A69" s="127">
         <v>50</v>
       </c>
       <c r="B69" s="48">
@@ -9527,13 +10239,13 @@
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="118"/>
+      <c r="A70" s="127"/>
       <c r="B70" s="48">
         <v>53</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="118">
+      <c r="A71" s="127">
         <v>56</v>
       </c>
       <c r="B71" s="48">
@@ -9541,13 +10253,13 @@
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="118"/>
+      <c r="A72" s="127"/>
       <c r="B72" s="48">
         <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="118">
+      <c r="A73" s="127">
         <v>63</v>
       </c>
       <c r="B73" s="48">
@@ -9555,13 +10267,13 @@
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="118"/>
+      <c r="A74" s="127"/>
       <c r="B74" s="48">
         <v>67</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="118">
+      <c r="A75" s="127">
         <v>71</v>
       </c>
       <c r="B75" s="48">
@@ -9569,13 +10281,13 @@
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="118"/>
+      <c r="A76" s="127"/>
       <c r="B76" s="48">
         <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="118">
+      <c r="A77" s="127">
         <v>80</v>
       </c>
       <c r="B77" s="48">
@@ -9583,13 +10295,13 @@
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="118"/>
+      <c r="A78" s="127"/>
       <c r="B78" s="48">
         <v>85</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="118">
+      <c r="A79" s="127">
         <v>90</v>
       </c>
       <c r="B79" s="48">
@@ -9597,21 +10309,33 @@
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="118"/>
+      <c r="A80" s="127"/>
       <c r="B80" s="48">
         <v>95</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A35:A36"/>
     <mergeCell ref="A63:A64"/>
     <mergeCell ref="A41:A42"/>
     <mergeCell ref="A43:A44"/>
@@ -9624,32 +10348,20 @@
     <mergeCell ref="A57:A58"/>
     <mergeCell ref="A59:A60"/>
     <mergeCell ref="A61:A62"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="A75:A76"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D136A9F2-8845-4295-A8BD-25F04BE0EFA0}">
   <dimension ref="A1:T34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9669,99 +10381,99 @@
         <v>4</v>
       </c>
       <c r="E2" s="94" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="F2" s="94"/>
       <c r="G2" s="94"/>
       <c r="H2" s="94"/>
       <c r="I2" s="94"/>
-      <c r="J2" s="118" t="s">
-        <v>259</v>
-      </c>
-      <c r="K2" s="118"/>
-      <c r="L2" s="118"/>
-      <c r="M2" s="118"/>
-      <c r="N2" s="118"/>
-      <c r="P2" s="118" t="s">
-        <v>260</v>
-      </c>
-      <c r="Q2" s="118"/>
-      <c r="R2" s="118"/>
-      <c r="S2" s="118"/>
-      <c r="T2" s="118"/>
+      <c r="J2" s="127" t="s">
+        <v>252</v>
+      </c>
+      <c r="K2" s="127"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="127"/>
+      <c r="P2" s="127" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q2" s="127"/>
+      <c r="R2" s="127"/>
+      <c r="S2" s="127"/>
+      <c r="T2" s="127"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>5</v>
       </c>
-      <c r="E3" s="136" t="s">
+      <c r="E3" s="135" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="136"/>
-      <c r="G3" s="136"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
       <c r="H3" s="60">
         <f>Передача!$D$49</f>
         <v>2016</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="J3" s="48" t="s">
         <v>72</v>
       </c>
       <c r="K3" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="P3" s="48" t="s">
         <v>72</v>
       </c>
       <c r="Q3" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>6</v>
       </c>
-      <c r="E4" s="136" t="s">
-        <v>157</v>
-      </c>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
+      <c r="E4" s="135" t="s">
+        <v>152</v>
+      </c>
+      <c r="F4" s="135"/>
+      <c r="G4" s="135"/>
       <c r="H4" s="60">
         <f>Передача!$D$50</f>
         <v>734</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="J4" s="118" t="s">
-        <v>303</v>
-      </c>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118"/>
+        <v>154</v>
+      </c>
+      <c r="J4" s="127" t="s">
+        <v>293</v>
+      </c>
+      <c r="K4" s="127"/>
+      <c r="L4" s="127"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>7</v>
       </c>
-      <c r="E5" s="136" t="s">
-        <v>158</v>
-      </c>
-      <c r="F5" s="136"/>
-      <c r="G5" s="136"/>
+      <c r="E5" s="135" t="s">
+        <v>153</v>
+      </c>
+      <c r="F5" s="135"/>
+      <c r="G5" s="135"/>
       <c r="H5" s="60">
         <f>Передача!$D$51</f>
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="J5" s="118" t="s">
+        <v>154</v>
+      </c>
+      <c r="J5" s="127" t="s">
         <v>118</v>
       </c>
-      <c r="K5" s="118"/>
-      <c r="L5" s="118"/>
+      <c r="K5" s="127"/>
+      <c r="L5" s="127"/>
       <c r="M5">
         <f>Вал!K16</f>
         <v>40</v>
@@ -9769,11 +10481,11 @@
       <c r="N5" t="s">
         <v>16</v>
       </c>
-      <c r="P5" s="118" t="s">
+      <c r="P5" s="127" t="s">
         <v>118</v>
       </c>
-      <c r="Q5" s="118"/>
-      <c r="R5" s="118"/>
+      <c r="Q5" s="127"/>
+      <c r="R5" s="127"/>
       <c r="S5">
         <f ca="1">Вал!S15</f>
         <v>50</v>
@@ -9786,20 +10498,20 @@
       <c r="A6">
         <v>8</v>
       </c>
-      <c r="J6" s="118" t="s">
-        <v>258</v>
-      </c>
-      <c r="K6" s="118"/>
-      <c r="L6" s="118"/>
+      <c r="J6" s="127" t="s">
+        <v>251</v>
+      </c>
+      <c r="K6" s="127"/>
+      <c r="L6" s="127"/>
       <c r="M6" s="52">
         <f>E16</f>
         <v>208</v>
       </c>
-      <c r="P6" s="118" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q6" s="118"/>
-      <c r="R6" s="118"/>
+      <c r="P6" s="127" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q6" s="127"/>
+      <c r="R6" s="127"/>
       <c r="S6" s="52">
         <f>E18</f>
         <v>210</v>
@@ -9819,69 +10531,69 @@
       <c r="A9">
         <v>15</v>
       </c>
-      <c r="E9" s="118" t="s">
-        <v>302</v>
-      </c>
-      <c r="F9" s="118"/>
-      <c r="G9" s="118"/>
-      <c r="H9" s="118"/>
-      <c r="I9" s="118"/>
-      <c r="J9" s="118"/>
-      <c r="K9" s="118"/>
-      <c r="L9" s="118"/>
-      <c r="M9" s="118"/>
+      <c r="E9" s="127" t="s">
+        <v>292</v>
+      </c>
+      <c r="F9" s="127"/>
+      <c r="G9" s="127"/>
+      <c r="H9" s="127"/>
+      <c r="I9" s="127"/>
+      <c r="J9" s="127"/>
+      <c r="K9" s="127"/>
+      <c r="L9" s="127"/>
+      <c r="M9" s="127"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>17</v>
       </c>
       <c r="D10" s="1"/>
-      <c r="E10" s="118">
+      <c r="E10" s="127">
         <v>200</v>
       </c>
-      <c r="F10" s="118"/>
-      <c r="G10" s="118"/>
-      <c r="H10" s="118">
+      <c r="F10" s="127"/>
+      <c r="G10" s="127"/>
+      <c r="H10" s="127">
         <v>300</v>
       </c>
-      <c r="I10" s="118"/>
-      <c r="J10" s="118"/>
-      <c r="K10" s="118">
+      <c r="I10" s="127"/>
+      <c r="J10" s="127"/>
+      <c r="K10" s="127">
         <v>400</v>
       </c>
-      <c r="L10" s="118"/>
-      <c r="M10" s="118"/>
+      <c r="L10" s="127"/>
+      <c r="M10" s="127"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="F11" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="G11" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="H11" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="I11" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="J11" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="K11" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="L11" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="M11" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
@@ -10344,12 +11056,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="J2:N2"/>
-    <mergeCell ref="P2:T2"/>
-    <mergeCell ref="P5:R5"/>
-    <mergeCell ref="E2:I2"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="E4:G4"/>
     <mergeCell ref="P6:R6"/>
     <mergeCell ref="J4:L4"/>
     <mergeCell ref="E10:G10"/>
@@ -10359,12 +11065,18 @@
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="E5:G5"/>
     <mergeCell ref="J5:L5"/>
+    <mergeCell ref="J2:N2"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="E2:I2"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="E4:G4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32704C68-B145-4DB6-B0E3-AE1BF65D15BC}">
   <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10373,69 +11085,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="127" t="s">
+        <v>259</v>
+      </c>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118" t="s">
-        <v>182</v>
-      </c>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118" t="s">
+      <c r="F1" s="127"/>
+      <c r="G1" s="127" t="s">
+        <v>269</v>
+      </c>
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="127"/>
+      <c r="B2" s="127"/>
+      <c r="C2" s="127" t="s">
+        <v>267</v>
+      </c>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127" t="s">
+        <v>268</v>
+      </c>
+      <c r="F2" s="127"/>
+      <c r="G2" s="91" t="s">
+        <v>270</v>
+      </c>
+      <c r="H2" s="91" t="s">
+        <v>271</v>
+      </c>
+      <c r="I2" s="91" t="s">
+        <v>272</v>
+      </c>
+      <c r="J2" s="91" t="s">
         <v>273</v>
       </c>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118" t="s">
-        <v>276</v>
-      </c>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="118"/>
-      <c r="B2" s="118"/>
-      <c r="C2" s="118" t="s">
+      <c r="K2" s="91" t="s">
         <v>274</v>
       </c>
-      <c r="D2" s="118"/>
-      <c r="E2" s="118" t="s">
+      <c r="L2" s="91" t="s">
         <v>275</v>
       </c>
-      <c r="F2" s="118"/>
-      <c r="G2" s="91" t="s">
-        <v>277</v>
-      </c>
-      <c r="H2" s="91" t="s">
-        <v>278</v>
-      </c>
-      <c r="I2" s="91" t="s">
-        <v>279</v>
-      </c>
-      <c r="J2" s="91" t="s">
-        <v>280</v>
-      </c>
-      <c r="K2" s="91" t="s">
-        <v>281</v>
-      </c>
-      <c r="L2" s="91" t="s">
-        <v>282</v>
-      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="118" t="s">
-        <v>267</v>
-      </c>
-      <c r="B3" s="118"/>
-      <c r="C3" s="118">
+      <c r="A3" s="127" t="s">
+        <v>260</v>
+      </c>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127">
         <v>1000</v>
       </c>
-      <c r="D3" s="118"/>
-      <c r="E3" s="118">
+      <c r="D3" s="127"/>
+      <c r="E3" s="127">
         <v>190</v>
       </c>
-      <c r="F3" s="118"/>
+      <c r="F3" s="127"/>
       <c r="G3">
         <v>520</v>
       </c>
@@ -10456,18 +11168,18 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="118">
+      <c r="A4" s="127">
         <v>45</v>
       </c>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118">
+      <c r="B4" s="127"/>
+      <c r="C4" s="127">
         <v>120</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118">
+      <c r="D4" s="127"/>
+      <c r="E4" s="127">
         <v>227</v>
       </c>
-      <c r="F4" s="118"/>
+      <c r="F4" s="127"/>
       <c r="G4">
         <v>820</v>
       </c>
@@ -10488,18 +11200,18 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="118">
+      <c r="A5" s="127">
         <v>45</v>
       </c>
-      <c r="B5" s="118"/>
-      <c r="C5" s="118">
+      <c r="B5" s="127"/>
+      <c r="C5" s="127">
         <v>80</v>
       </c>
-      <c r="D5" s="118"/>
-      <c r="E5" s="118">
+      <c r="D5" s="127"/>
+      <c r="E5" s="127">
         <v>260</v>
       </c>
-      <c r="F5" s="118"/>
+      <c r="F5" s="127"/>
       <c r="G5">
         <v>900</v>
       </c>
@@ -10520,18 +11232,18 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="118" t="s">
-        <v>268</v>
-      </c>
-      <c r="B6" s="118"/>
-      <c r="C6" s="118">
+      <c r="A6" s="127" t="s">
+        <v>261</v>
+      </c>
+      <c r="B6" s="127"/>
+      <c r="C6" s="127">
         <v>200</v>
       </c>
-      <c r="D6" s="118"/>
-      <c r="E6" s="118">
+      <c r="D6" s="127"/>
+      <c r="E6" s="127">
         <v>240</v>
       </c>
-      <c r="F6" s="118"/>
+      <c r="F6" s="127"/>
       <c r="G6">
         <v>790</v>
       </c>
@@ -10552,18 +11264,18 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="118" t="s">
-        <v>268</v>
-      </c>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118">
+      <c r="A7" s="127" t="s">
+        <v>261</v>
+      </c>
+      <c r="B7" s="127"/>
+      <c r="C7" s="127">
         <v>120</v>
       </c>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118">
+      <c r="D7" s="127"/>
+      <c r="E7" s="127">
         <v>270</v>
       </c>
-      <c r="F7" s="118"/>
+      <c r="F7" s="127"/>
       <c r="G7">
         <v>980</v>
       </c>
@@ -10584,18 +11296,18 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="118" t="s">
-        <v>269</v>
-      </c>
-      <c r="B8" s="118"/>
-      <c r="C8" s="118">
+      <c r="A8" s="127" t="s">
+        <v>262</v>
+      </c>
+      <c r="B8" s="127"/>
+      <c r="C8" s="127">
         <v>200</v>
       </c>
-      <c r="D8" s="118"/>
-      <c r="E8" s="118">
+      <c r="D8" s="127"/>
+      <c r="E8" s="127">
         <v>270</v>
       </c>
-      <c r="F8" s="118"/>
+      <c r="F8" s="127"/>
       <c r="G8">
         <v>980</v>
       </c>
@@ -10616,18 +11328,18 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="118" t="s">
-        <v>270</v>
-      </c>
-      <c r="B9" s="118"/>
-      <c r="C9" s="118">
+      <c r="A9" s="127" t="s">
+        <v>263</v>
+      </c>
+      <c r="B9" s="127"/>
+      <c r="C9" s="127">
         <v>120</v>
       </c>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118">
+      <c r="D9" s="127"/>
+      <c r="E9" s="127">
         <v>197</v>
       </c>
-      <c r="F9" s="118"/>
+      <c r="F9" s="127"/>
       <c r="G9">
         <v>650</v>
       </c>
@@ -10648,18 +11360,18 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="118" t="s">
-        <v>271</v>
-      </c>
-      <c r="B10" s="118"/>
-      <c r="C10" s="118">
+      <c r="A10" s="127" t="s">
+        <v>264</v>
+      </c>
+      <c r="B10" s="127"/>
+      <c r="C10" s="127">
         <v>120</v>
       </c>
-      <c r="D10" s="118"/>
-      <c r="E10" s="118">
+      <c r="D10" s="127"/>
+      <c r="E10" s="127">
         <v>260</v>
       </c>
-      <c r="F10" s="118"/>
+      <c r="F10" s="127"/>
       <c r="G10">
         <v>930</v>
       </c>
@@ -10680,18 +11392,18 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="118" t="s">
-        <v>272</v>
-      </c>
-      <c r="B11" s="118"/>
-      <c r="C11" s="118">
+      <c r="A11" s="127" t="s">
+        <v>265</v>
+      </c>
+      <c r="B11" s="127"/>
+      <c r="C11" s="127">
         <v>60</v>
       </c>
-      <c r="D11" s="118"/>
-      <c r="E11" s="118">
+      <c r="D11" s="127"/>
+      <c r="E11" s="127">
         <v>330</v>
       </c>
-      <c r="F11" s="118"/>
+      <c r="F11" s="127"/>
       <c r="G11">
         <v>1180</v>
       </c>
@@ -10725,6 +11437,21 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="G1:K1"/>
@@ -10743,21 +11470,6 @@
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Расчёт.xlsx
+++ b/Расчёт.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Professional\Downloads\интститут\курсач детмаш\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0BC1553-D385-48B5-B19C-E3BAEEE1572B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B752255A-80C5-48CC-B3F0-B1CFEA11A6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="812" activeTab="1" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="378">
   <si>
     <t>Окружная сила</t>
   </si>
@@ -1142,6 +1142,45 @@
   </si>
   <si>
     <t>(272 HB)</t>
+  </si>
+  <si>
+    <t>K (коэффициент режима работы)</t>
+  </si>
+  <si>
+    <t>1,1-1,4 для транспортёров</t>
+  </si>
+  <si>
+    <t>Посадка</t>
+  </si>
+  <si>
+    <t>H7/k6</t>
+  </si>
+  <si>
+    <t>Расчёт на смятие</t>
+  </si>
+  <si>
+    <t>Ширина b</t>
+  </si>
+  <si>
+    <t>Шпонка</t>
+  </si>
+  <si>
+    <t>Высота шпонки h</t>
+  </si>
+  <si>
+    <t>Глубина паза t2 (внешний)</t>
+  </si>
+  <si>
+    <t>Глубина паза t1 (вала)</t>
+  </si>
+  <si>
+    <t>Материал вала</t>
+  </si>
+  <si>
+    <t>Предел текучести</t>
+  </si>
+  <si>
+    <t>Предел на смятие</t>
   </si>
 </sst>
 </file>
@@ -7118,18 +7157,11 @@
     <mergeCell ref="H6:J6"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="H3:J3"/>
-    <mergeCell ref="P11:R11"/>
-    <mergeCell ref="P15:R15"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="H14:J14"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="H15:J15"/>
     <mergeCell ref="H11:J11"/>
     <mergeCell ref="H13:J13"/>
-    <mergeCell ref="P16:R16"/>
-    <mergeCell ref="P17:R17"/>
-    <mergeCell ref="P18:R18"/>
     <mergeCell ref="H18:J18"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="P20:R20"/>
@@ -7138,6 +7170,7 @@
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="H20:J20"/>
+    <mergeCell ref="P21:R21"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="H7:J7"/>
     <mergeCell ref="A8:C8"/>
@@ -7149,12 +7182,18 @@
     <mergeCell ref="P13:R13"/>
     <mergeCell ref="P14:R14"/>
     <mergeCell ref="P10:R10"/>
-    <mergeCell ref="P21:R21"/>
+    <mergeCell ref="P11:R11"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="H14:J14"/>
     <mergeCell ref="P9:T9"/>
     <mergeCell ref="P6:R6"/>
     <mergeCell ref="P7:R7"/>
     <mergeCell ref="P8:R8"/>
     <mergeCell ref="P19:R19"/>
+    <mergeCell ref="P15:R15"/>
+    <mergeCell ref="P16:R16"/>
+    <mergeCell ref="P17:R17"/>
+    <mergeCell ref="P18:R18"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7331,8 +7370,8 @@
       </c>
       <c r="B19" s="104"/>
       <c r="C19" s="11">
-        <f>C18+1</f>
-        <v>81</v>
+        <f>C18</f>
+        <v>80</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="93">
@@ -7340,8 +7379,8 @@
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="11">
-        <f ca="1">G18+1</f>
-        <v>91</v>
+        <f ca="1">G18</f>
+        <v>90</v>
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="97">
@@ -7356,7 +7395,7 @@
       <c r="B20" s="100"/>
       <c r="C20" s="7">
         <f>C19-2*E9</f>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1">
@@ -7366,7 +7405,7 @@
       <c r="F20" s="3"/>
       <c r="G20" s="7">
         <f ca="1">G19-F9*2</f>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1">
@@ -9927,7 +9966,7 @@
       <c r="K15" s="124"/>
       <c r="L15" s="124"/>
       <c r="M15">
-        <f>5.5*(E20+'тихоходный вал'!E21)</f>
+        <f>5.5*(E20+'тихоходный вал'!E8)</f>
         <v>17.600000000000001</v>
       </c>
       <c r="N15" t="s">
@@ -10308,11 +10347,19 @@
     </row>
   </sheetData>
   <mergeCells count="91">
-    <mergeCell ref="Z10:AA10"/>
-    <mergeCell ref="X10:Y10"/>
     <mergeCell ref="J18:L18"/>
     <mergeCell ref="Z4:AA4"/>
     <mergeCell ref="Z9:AA9"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="Z8:AA8"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="T6:W6"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="Z11:AA11"/>
     <mergeCell ref="Z3:AA3"/>
     <mergeCell ref="T3:W3"/>
     <mergeCell ref="T4:W4"/>
@@ -10320,54 +10367,45 @@
     <mergeCell ref="X4:Y4"/>
     <mergeCell ref="X5:Y5"/>
     <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="Z8:AA8"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="T6:W6"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="Z10:AA10"/>
+    <mergeCell ref="X10:Y10"/>
     <mergeCell ref="Z5:AA5"/>
     <mergeCell ref="J13:L13"/>
     <mergeCell ref="J11:L11"/>
     <mergeCell ref="J12:L12"/>
     <mergeCell ref="X11:Y11"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="J17:L17"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="Z11:AA11"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="J10:L10"/>
     <mergeCell ref="T8:W8"/>
     <mergeCell ref="T9:W9"/>
     <mergeCell ref="T10:W10"/>
     <mergeCell ref="T11:W11"/>
     <mergeCell ref="J8:N8"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="J10:L10"/>
     <mergeCell ref="J23:L23"/>
     <mergeCell ref="J22:L22"/>
     <mergeCell ref="J21:L21"/>
-    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="J5:L5"/>
     <mergeCell ref="T7:W7"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J9:L9"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="A37:B37"/>
@@ -10383,6 +10421,7 @@
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A33:B33"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A38:B38"/>
@@ -10408,111 +10447,321 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F31C697-F4FB-4FAD-9F40-0B2C485D61BE}">
-  <dimension ref="A15:F21"/>
+  <dimension ref="A2:F37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="20" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="124" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="124" t="s">
         <v>181</v>
       </c>
-      <c r="B15" s="124"/>
-      <c r="C15" s="124"/>
-      <c r="D15" s="124"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="124" t="s">
+      <c r="B2" s="124"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="124" t="s">
         <v>257</v>
       </c>
-      <c r="B16" s="124"/>
-      <c r="C16" s="124"/>
-      <c r="D16" s="124"/>
-      <c r="E16">
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="124"/>
+      <c r="E3">
         <f ca="1">Колесо!E19</f>
         <v>55</v>
       </c>
-      <c r="F16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="124" t="s">
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="124" t="s">
         <v>351</v>
       </c>
-      <c r="B17" s="124"/>
-      <c r="C17" s="124"/>
-      <c r="D17" s="124"/>
-      <c r="E17">
+      <c r="B4" s="124"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="124"/>
+      <c r="E4">
         <f>Корпус!$E$8</f>
         <v>10.072378298355165</v>
       </c>
-      <c r="F17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="124" t="s">
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="124" t="s">
         <v>350</v>
       </c>
-      <c r="B18" s="124"/>
-      <c r="C18" s="124"/>
-      <c r="D18" s="124"/>
-      <c r="E18">
+      <c r="B5" s="124"/>
+      <c r="C5" s="124"/>
+      <c r="D5" s="124"/>
+      <c r="E5">
         <f ca="1">Вал!$S$18</f>
         <v>20</v>
       </c>
-      <c r="F18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="124" t="s">
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="124" t="s">
         <v>352</v>
       </c>
-      <c r="B19" s="124"/>
-      <c r="C19" s="124"/>
-      <c r="D19" s="124"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="124" t="s">
+      <c r="B6" s="124"/>
+      <c r="C6" s="124"/>
+      <c r="D6" s="124"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="124" t="s">
         <v>201</v>
       </c>
-      <c r="B20" s="124"/>
-      <c r="C20" s="124"/>
-      <c r="D20" s="124"/>
-      <c r="E20">
-        <f ca="1">E18*2+2+Колесо!E10+E17*2</f>
+      <c r="B7" s="124"/>
+      <c r="C7" s="124"/>
+      <c r="D7" s="124"/>
+      <c r="E7">
+        <f ca="1">E5*2+2+Колесо!E10+E4*2</f>
         <v>119.14475659671032</v>
       </c>
-      <c r="F20" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="124" t="s">
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="124" t="s">
         <v>285</v>
       </c>
-      <c r="B21" s="124"/>
-      <c r="C21" s="124"/>
-      <c r="D21" s="124"/>
-      <c r="E21" s="52">
+      <c r="B8" s="124"/>
+      <c r="C8" s="124"/>
+      <c r="D8" s="124"/>
+      <c r="E8" s="52">
         <v>1.6</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F8" t="s">
         <v>235</v>
       </c>
     </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="124" t="s">
+        <v>349</v>
+      </c>
+      <c r="B9" s="124"/>
+      <c r="C9" s="124"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="52" t="str">
+        <f>Материалы!A7</f>
+        <v>40Х</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="124" t="s">
+        <v>376</v>
+      </c>
+      <c r="B10" s="124"/>
+      <c r="C10" s="124"/>
+      <c r="D10" s="124"/>
+      <c r="E10">
+        <f>VLOOKUP($E$9, Материалы!A:L,8,FALSE)</f>
+        <v>640</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="124" t="s">
+        <v>377</v>
+      </c>
+      <c r="B11" s="124"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="124"/>
+      <c r="E11">
+        <f>VLOOKUP($E$9, Материалы!A:L,8,FALSE)</f>
+        <v>640</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="124" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="124"/>
+      <c r="C24" s="124"/>
+      <c r="D24" s="124"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="124" t="s">
+        <v>365</v>
+      </c>
+      <c r="B25" s="124"/>
+      <c r="C25" s="124"/>
+      <c r="D25" s="124"/>
+      <c r="E25">
+        <v>1.4</v>
+      </c>
+      <c r="F25" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="124" t="s">
+        <v>367</v>
+      </c>
+      <c r="B26" s="124"/>
+      <c r="C26" s="124"/>
+      <c r="D26" s="124"/>
+      <c r="E26" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="124" t="s">
+        <v>369</v>
+      </c>
+      <c r="B28" s="124"/>
+      <c r="C28" s="124"/>
+      <c r="D28" s="124"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="124" t="s">
+        <v>166</v>
+      </c>
+      <c r="B29" s="124"/>
+      <c r="C29" s="124"/>
+      <c r="D29" s="124"/>
+      <c r="E29">
+        <f ca="1">Электродвигатель!$P$56</f>
+        <v>342.7992963881365</v>
+      </c>
+      <c r="F29" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="124" t="s">
+        <v>118</v>
+      </c>
+      <c r="B30" s="124"/>
+      <c r="C30" s="124"/>
+      <c r="D30" s="124"/>
+      <c r="E30">
+        <f>Вал!$K$13</f>
+        <v>32</v>
+      </c>
+      <c r="F30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="124" t="s">
+        <v>371</v>
+      </c>
+      <c r="B31" s="124"/>
+      <c r="C31" s="124"/>
+      <c r="D31" s="124"/>
+      <c r="E31" s="124"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="124" t="s">
+        <v>370</v>
+      </c>
+      <c r="B32" s="124"/>
+      <c r="C32" s="124"/>
+      <c r="D32" s="124"/>
+      <c r="E32" s="52">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="124" t="s">
+        <v>372</v>
+      </c>
+      <c r="B33" s="124"/>
+      <c r="C33" s="124"/>
+      <c r="D33" s="124"/>
+      <c r="E33" s="52">
+        <v>8</v>
+      </c>
+      <c r="F33" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="124" t="s">
+        <v>374</v>
+      </c>
+      <c r="B34" s="124"/>
+      <c r="C34" s="124"/>
+      <c r="D34" s="124"/>
+      <c r="E34" s="52">
+        <v>5</v>
+      </c>
+      <c r="F34" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="124" t="s">
+        <v>206</v>
+      </c>
+      <c r="B35" s="124"/>
+      <c r="C35" s="124"/>
+      <c r="D35" s="124"/>
+      <c r="E35" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="F35" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="124" t="s">
+        <v>373</v>
+      </c>
+      <c r="B36" s="124"/>
+      <c r="C36" s="124"/>
+      <c r="D36" s="124"/>
+      <c r="E36" s="52">
+        <v>3.3</v>
+      </c>
+      <c r="F36" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="124" t="s">
+        <v>375</v>
+      </c>
+      <c r="B37" s="124"/>
+      <c r="C37" s="124"/>
+      <c r="D37" s="124"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A15:D15"/>
+  <mergeCells count="23">
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Расчёт.xlsx
+++ b/Расчёт.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Professional\Downloads\интститут\курсач детмаш\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B752255A-80C5-48CC-B3F0-B1CFEA11A6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A73725F4-E076-4A54-ABF6-ACEC85FEB3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="812" activeTab="1" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="812" activeTab="8" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
   </bookViews>
   <sheets>
     <sheet name="Электродвигатель" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="382">
   <si>
     <t>Окружная сила</t>
   </si>
@@ -1162,9 +1162,6 @@
     <t>Ширина b</t>
   </si>
   <si>
-    <t>Шпонка</t>
-  </si>
-  <si>
     <t>Высота шпонки h</t>
   </si>
   <si>
@@ -1174,13 +1171,28 @@
     <t>Глубина паза t1 (вала)</t>
   </si>
   <si>
-    <t>Материал вала</t>
-  </si>
-  <si>
     <t>Предел текучести</t>
   </si>
   <si>
     <t>Предел на смятие</t>
+  </si>
+  <si>
+    <t>Предел на смятие шпонки</t>
+  </si>
+  <si>
+    <t>Расчёт длинны шпонки из условия несмятия</t>
+  </si>
+  <si>
+    <t>МПа</t>
+  </si>
+  <si>
+    <t>Рабочая длинна шпонки</t>
+  </si>
+  <si>
+    <t>Минимальная высота шпонки</t>
+  </si>
+  <si>
+    <t>Высота смятия шпонки</t>
   </si>
 </sst>
 </file>
@@ -2053,16 +2065,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>510540</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>182880</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>501865</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>44096</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>174205</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>166016</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2085,7 +2097,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4168140" y="960120"/>
+          <a:off x="7299960" y="167640"/>
           <a:ext cx="6087325" cy="2010056"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -10360,6 +10372,9 @@
     <mergeCell ref="J14:L14"/>
     <mergeCell ref="Z6:AA6"/>
     <mergeCell ref="Z11:AA11"/>
+    <mergeCell ref="Z10:AA10"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="J13:L13"/>
     <mergeCell ref="Z3:AA3"/>
     <mergeCell ref="T3:W3"/>
     <mergeCell ref="T4:W4"/>
@@ -10367,10 +10382,7 @@
     <mergeCell ref="X4:Y4"/>
     <mergeCell ref="X5:Y5"/>
     <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="Z10:AA10"/>
-    <mergeCell ref="X10:Y10"/>
     <mergeCell ref="Z5:AA5"/>
-    <mergeCell ref="J13:L13"/>
     <mergeCell ref="J11:L11"/>
     <mergeCell ref="J12:L12"/>
     <mergeCell ref="X11:Y11"/>
@@ -10447,7 +10459,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F31C697-F4FB-4FAD-9F40-0B2C485D61BE}">
-  <dimension ref="A2:F37"/>
+  <dimension ref="A2:G43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="20" width="6.77734375" customWidth="1"/>
@@ -10557,7 +10569,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="124" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B10" s="124"/>
       <c r="C10" s="124"/>
@@ -10569,7 +10581,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="124" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B11" s="124"/>
       <c r="C11" s="124"/>
@@ -10643,8 +10655,8 @@
       <c r="C30" s="124"/>
       <c r="D30" s="124"/>
       <c r="E30">
-        <f>Вал!$K$13</f>
-        <v>32</v>
+        <f ca="1">Вал!S12</f>
+        <v>40</v>
       </c>
       <c r="F30" t="s">
         <v>16</v>
@@ -10652,12 +10664,13 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="124" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B31" s="124"/>
       <c r="C31" s="124"/>
       <c r="D31" s="124"/>
       <c r="E31" s="124"/>
+      <c r="F31" s="124"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="124" t="s">
@@ -10667,15 +10680,15 @@
       <c r="C32" s="124"/>
       <c r="D32" s="124"/>
       <c r="E32" s="52">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F32" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="124" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B33" s="124"/>
       <c r="C33" s="124"/>
@@ -10687,9 +10700,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="124" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B34" s="124"/>
       <c r="C34" s="124"/>
@@ -10701,7 +10714,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="124" t="s">
         <v>206</v>
       </c>
@@ -10715,9 +10728,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="124" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B36" s="124"/>
       <c r="C36" s="124"/>
@@ -10729,16 +10742,93 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="124" t="s">
-        <v>375</v>
-      </c>
-      <c r="B37" s="124"/>
-      <c r="C37" s="124"/>
-      <c r="D37" s="124"/>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="48"/>
+      <c r="B37" s="48"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="48"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="124" t="s">
+        <v>381</v>
+      </c>
+      <c r="B38" s="124"/>
+      <c r="C38" s="124"/>
+      <c r="D38" s="124"/>
+      <c r="E38">
+        <f>MIN(E34,E33-E34)</f>
+        <v>3</v>
+      </c>
+      <c r="F38" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="124" t="s">
+        <v>376</v>
+      </c>
+      <c r="B39" s="124"/>
+      <c r="C39" s="124"/>
+      <c r="D39" s="124"/>
+      <c r="E39" s="52">
+        <v>110</v>
+      </c>
+      <c r="F39" t="s">
+        <v>378</v>
+      </c>
+      <c r="G39" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="124" t="s">
+        <v>379</v>
+      </c>
+      <c r="B40" s="124"/>
+      <c r="C40" s="124"/>
+      <c r="D40" s="124"/>
+      <c r="E40">
+        <f ca="1">E29*2*1000/E30/E39/E38</f>
+        <v>51.939287331535837</v>
+      </c>
+      <c r="F40" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="124" t="s">
+        <v>201</v>
+      </c>
+      <c r="B41" s="124"/>
+      <c r="C41" s="124"/>
+      <c r="D41" s="124"/>
+      <c r="E41">
+        <f ca="1">E40+E32</f>
+        <v>63.939287331535837</v>
+      </c>
+      <c r="F41" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="48"/>
+      <c r="B42" s="48"/>
+      <c r="C42" s="48"/>
+      <c r="D42" s="48"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="48"/>
+      <c r="B43" s="48"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="48"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="26">
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A25:D25"/>
@@ -10752,14 +10842,12 @@
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A37:D37"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="A30:D30"/>
     <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A31:E31"/>
     <mergeCell ref="A34:D34"/>
     <mergeCell ref="A33:D33"/>
   </mergeCells>
@@ -10770,9 +10858,212 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CC16526-A479-4083-A8A6-C1DA4D6AD8E8}">
-  <dimension ref="A1"/>
+  <dimension ref="A6:F19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="14" width="6.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="124" t="s">
+        <v>369</v>
+      </c>
+      <c r="B6" s="124"/>
+      <c r="C6" s="124"/>
+      <c r="D6" s="124"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="124" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" s="124"/>
+      <c r="C7" s="124"/>
+      <c r="D7" s="124"/>
+      <c r="E7" s="61">
+        <f>Электродвигатель!$P$53</f>
+        <v>48.741201321892952</v>
+      </c>
+      <c r="F7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="124" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" s="124"/>
+      <c r="C8" s="124"/>
+      <c r="D8" s="124"/>
+      <c r="E8">
+        <f>Вал!K13</f>
+        <v>32</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="124" t="s">
+        <v>377</v>
+      </c>
+      <c r="B9" s="124"/>
+      <c r="C9" s="124"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="124"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="124" t="s">
+        <v>370</v>
+      </c>
+      <c r="B10" s="124"/>
+      <c r="C10" s="124"/>
+      <c r="D10" s="124"/>
+      <c r="E10" s="52">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="124" t="s">
+        <v>371</v>
+      </c>
+      <c r="B11" s="124"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="52">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="124" t="s">
+        <v>373</v>
+      </c>
+      <c r="B12" s="124"/>
+      <c r="C12" s="124"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="52">
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="124" t="s">
+        <v>206</v>
+      </c>
+      <c r="B13" s="124"/>
+      <c r="C13" s="124"/>
+      <c r="D13" s="124"/>
+      <c r="E13" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="124" t="s">
+        <v>372</v>
+      </c>
+      <c r="B14" s="124"/>
+      <c r="C14" s="124"/>
+      <c r="D14" s="124"/>
+      <c r="E14" s="52">
+        <v>3.3</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="48"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="124" t="s">
+        <v>380</v>
+      </c>
+      <c r="B16" s="124"/>
+      <c r="C16" s="124"/>
+      <c r="D16" s="124"/>
+      <c r="E16">
+        <f>MIN(E12,E11-E12)</f>
+        <v>3</v>
+      </c>
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="124" t="s">
+        <v>376</v>
+      </c>
+      <c r="B17" s="124"/>
+      <c r="C17" s="124"/>
+      <c r="D17" s="124"/>
+      <c r="E17" s="90">
+        <f>'тихоходный вал'!E39</f>
+        <v>110</v>
+      </c>
+      <c r="F17" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="124" t="s">
+        <v>379</v>
+      </c>
+      <c r="B18" s="124"/>
+      <c r="C18" s="124"/>
+      <c r="D18" s="124"/>
+      <c r="E18">
+        <f>E7*2*1000/E8/E17/E16</f>
+        <v>9.2312881291463924</v>
+      </c>
+      <c r="F18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="124" t="s">
+        <v>201</v>
+      </c>
+      <c r="B19" s="124"/>
+      <c r="C19" s="124"/>
+      <c r="D19" s="124"/>
+      <c r="E19">
+        <f>E18+E10</f>
+        <v>19.231288129146392</v>
+      </c>
+      <c r="F19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Расчёт.xlsx
+++ b/Расчёт.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Professional\Downloads\интститут\курсач детмаш\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A73725F4-E076-4A54-ABF6-ACEC85FEB3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{966D5585-7C20-4BA9-AA75-12DC92CCF878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="812" activeTab="8" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
   </bookViews>
@@ -20,10 +20,11 @@
     <sheet name="Колесо" sheetId="7" r:id="rId5"/>
     <sheet name="тихоходный вал" sheetId="14" r:id="rId6"/>
     <sheet name="вал-шестерня" sheetId="13" r:id="rId7"/>
-    <sheet name="Корпус" sheetId="3" r:id="rId8"/>
-    <sheet name="Ra40" sheetId="5" r:id="rId9"/>
-    <sheet name="Подшипники" sheetId="10" r:id="rId10"/>
-    <sheet name="Материалы" sheetId="11" r:id="rId11"/>
+    <sheet name="силы" sheetId="15" r:id="rId8"/>
+    <sheet name="Корпус" sheetId="3" r:id="rId9"/>
+    <sheet name="Ra40" sheetId="5" r:id="rId10"/>
+    <sheet name="Подшипники" sheetId="10" r:id="rId11"/>
+    <sheet name="Материалы" sheetId="11" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="393">
   <si>
     <t>Окружная сила</t>
   </si>
@@ -1193,6 +1194,39 @@
   </si>
   <si>
     <t>Высота смятия шпонки</t>
+  </si>
+  <si>
+    <t>Расчёт сил в узлах</t>
+  </si>
+  <si>
+    <t>Длинны</t>
+  </si>
+  <si>
+    <t>Длинна 12</t>
+  </si>
+  <si>
+    <t>Длинна 23</t>
+  </si>
+  <si>
+    <t>Длинна 34</t>
+  </si>
+  <si>
+    <t>Радиальная косольная сила</t>
+  </si>
+  <si>
+    <t>Осевая сила Fa</t>
+  </si>
+  <si>
+    <t>Радиальная сила Fr</t>
+  </si>
+  <si>
+    <t>Окружная сила Ft</t>
+  </si>
+  <si>
+    <t>Окружная консольная сила</t>
+  </si>
+  <si>
+    <t>Эквиавлетные коэффициент нагружения</t>
   </si>
 </sst>
 </file>
@@ -4328,10 +4362,10 @@
         <v>0.77619649168341942</v>
       </c>
       <c r="AB42">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="AC42" t="s">
-        <v>309</v>
+        <v>382</v>
       </c>
     </row>
     <row r="43" spans="2:29" x14ac:dyDescent="0.3">
@@ -4409,9 +4443,6 @@
         <f t="shared" ca="1" si="16"/>
         <v>0.77322226173177433</v>
       </c>
-      <c r="AC43" t="s">
-        <v>310</v>
-      </c>
     </row>
     <row r="44" spans="2:29" x14ac:dyDescent="0.3">
       <c r="C44" s="1"/>
@@ -4482,8 +4513,11 @@
         <f t="shared" ca="1" si="16"/>
         <v>0</v>
       </c>
-      <c r="AC44" s="1" t="s">
-        <v>311</v>
+      <c r="AB44">
+        <v>183</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="2:29" x14ac:dyDescent="0.3">
@@ -4552,8 +4586,8 @@
         <f t="shared" ca="1" si="16"/>
         <v>0</v>
       </c>
-      <c r="AC45" s="1" t="s">
-        <v>312</v>
+      <c r="AC45" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="2:29" x14ac:dyDescent="0.3">
@@ -4632,6 +4666,9 @@
       <c r="Z46" s="5">
         <f t="shared" ca="1" si="16"/>
         <v>0.75835111197354876</v>
+      </c>
+      <c r="AC46" s="1" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="2:29" x14ac:dyDescent="0.3">
@@ -4660,8 +4697,8 @@
       <c r="X47" s="1"/>
       <c r="Y47" s="30"/>
       <c r="Z47" s="1"/>
-      <c r="AC47" s="25" t="s">
-        <v>320</v>
+      <c r="AC47" s="1" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="2:29" x14ac:dyDescent="0.3">
@@ -4699,9 +4736,6 @@
       <c r="X48" s="1"/>
       <c r="Y48" s="30"/>
       <c r="Z48" s="1"/>
-      <c r="AC48" s="25" t="s">
-        <v>313</v>
-      </c>
     </row>
     <row r="49" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B49" s="99" t="s">
@@ -4732,6 +4766,9 @@
       <c r="X49" s="1"/>
       <c r="Y49" s="30"/>
       <c r="Z49" s="1"/>
+      <c r="AC49" s="25" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="50" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B50" s="99" t="s">
@@ -4754,8 +4791,8 @@
       <c r="X50" s="1"/>
       <c r="Y50" s="30"/>
       <c r="Z50" s="1"/>
-      <c r="AC50" s="1" t="s">
-        <v>321</v>
+      <c r="AC50" s="25" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="2:29" x14ac:dyDescent="0.3">
@@ -4802,9 +4839,6 @@
       <c r="X51" s="1"/>
       <c r="Y51" s="30"/>
       <c r="Z51" s="1"/>
-      <c r="AC51" s="49" t="s">
-        <v>307</v>
-      </c>
     </row>
     <row r="52" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B52" s="99" t="s">
@@ -4853,6 +4887,9 @@
       <c r="X52" s="1"/>
       <c r="Y52" s="30"/>
       <c r="Z52" s="1"/>
+      <c r="AC52" s="1" t="s">
+        <v>321</v>
+      </c>
     </row>
     <row r="53" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B53" s="99" t="s">
@@ -4902,6 +4939,9 @@
       <c r="X53" s="36"/>
       <c r="Y53" s="30"/>
       <c r="Z53" s="1"/>
+      <c r="AC53" s="49" t="s">
+        <v>307</v>
+      </c>
     </row>
     <row r="54" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B54" s="99" t="s">
@@ -5344,6 +5384,659 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D8564D3-007A-4908-B584-B11BCC9DA655}">
+  <dimension ref="A1:E80"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="124">
+        <v>1</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="D1" s="48"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="124"/>
+      <c r="B2">
+        <v>1.05</v>
+      </c>
+      <c r="D2" s="48"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="124">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D3" s="48"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="124"/>
+      <c r="B4">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="D4" s="48"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="124">
+        <v>1.2</v>
+      </c>
+      <c r="B5">
+        <v>1.2</v>
+      </c>
+      <c r="D5" s="48"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="124"/>
+      <c r="B6">
+        <v>1.3</v>
+      </c>
+      <c r="D6" s="48"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="124">
+        <v>1.4</v>
+      </c>
+      <c r="B7">
+        <v>1.4</v>
+      </c>
+      <c r="D7" s="48"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="124"/>
+      <c r="B8">
+        <v>1.5</v>
+      </c>
+      <c r="D8" s="48"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="124">
+        <v>1.6</v>
+      </c>
+      <c r="B9">
+        <v>1.6</v>
+      </c>
+      <c r="D9" s="48"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="124"/>
+      <c r="B10">
+        <v>1.7</v>
+      </c>
+      <c r="D10" s="48"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="124">
+        <v>1.8</v>
+      </c>
+      <c r="B11">
+        <v>1.8</v>
+      </c>
+      <c r="D11" s="48"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="124"/>
+      <c r="B12">
+        <v>1.9</v>
+      </c>
+      <c r="D12" s="48"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="124">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="D13" s="48"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="124"/>
+      <c r="B14">
+        <v>2.1</v>
+      </c>
+      <c r="D14" s="48"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="124">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D15" s="48"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="124"/>
+      <c r="B16">
+        <v>2.4</v>
+      </c>
+      <c r="D16" s="48"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="124">
+        <v>2.5</v>
+      </c>
+      <c r="B17">
+        <v>2.5</v>
+      </c>
+      <c r="D17" s="48"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="124"/>
+      <c r="B18">
+        <v>2.6</v>
+      </c>
+      <c r="D18" s="48"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="124">
+        <v>2.8</v>
+      </c>
+      <c r="B19">
+        <v>2.8</v>
+      </c>
+      <c r="D19" s="48"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="124"/>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="D20" s="48"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="124">
+        <v>3.2</v>
+      </c>
+      <c r="B21">
+        <v>3.2</v>
+      </c>
+      <c r="D21" s="48"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="124"/>
+      <c r="B22">
+        <v>3.4</v>
+      </c>
+      <c r="D22" s="48"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="124">
+        <v>3.6</v>
+      </c>
+      <c r="B23">
+        <v>3.6</v>
+      </c>
+      <c r="D23" s="48"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="124"/>
+      <c r="B24">
+        <v>3.8</v>
+      </c>
+      <c r="D24" s="48"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="124">
+        <v>4</v>
+      </c>
+      <c r="B25">
+        <v>4</v>
+      </c>
+      <c r="D25" s="48"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="124"/>
+      <c r="B26">
+        <v>4.2</v>
+      </c>
+      <c r="D26" s="48"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="124">
+        <v>4.5</v>
+      </c>
+      <c r="B27">
+        <v>4.5</v>
+      </c>
+      <c r="D27" s="48"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="124"/>
+      <c r="B28">
+        <v>4.8</v>
+      </c>
+      <c r="D28" s="48"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="124">
+        <v>5</v>
+      </c>
+      <c r="B29">
+        <v>5</v>
+      </c>
+      <c r="D29" s="48"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="124"/>
+      <c r="B30">
+        <v>5.3</v>
+      </c>
+      <c r="D30" s="48"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="124">
+        <v>5.6</v>
+      </c>
+      <c r="B31">
+        <v>5.6</v>
+      </c>
+      <c r="D31" s="48"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="124"/>
+      <c r="B32">
+        <v>6</v>
+      </c>
+      <c r="D32" s="48"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="124">
+        <v>6.3</v>
+      </c>
+      <c r="B33">
+        <v>6.3</v>
+      </c>
+      <c r="D33" s="48"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="124"/>
+      <c r="B34">
+        <v>6.7</v>
+      </c>
+      <c r="D34" s="48"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="124">
+        <v>7.1</v>
+      </c>
+      <c r="B35">
+        <v>7.1</v>
+      </c>
+      <c r="D35" s="48"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="124"/>
+      <c r="B36">
+        <v>7.5</v>
+      </c>
+      <c r="D36" s="48"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="124">
+        <v>8</v>
+      </c>
+      <c r="B37">
+        <v>8</v>
+      </c>
+      <c r="D37" s="48"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="124"/>
+      <c r="B38">
+        <v>8.5</v>
+      </c>
+      <c r="D38" s="48"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="124">
+        <v>9</v>
+      </c>
+      <c r="B39">
+        <v>9</v>
+      </c>
+      <c r="D39" s="48"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="124"/>
+      <c r="B40" s="61">
+        <v>9.5</v>
+      </c>
+      <c r="D40" s="48"/>
+      <c r="E40" s="61"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="124">
+        <v>10</v>
+      </c>
+      <c r="B41" s="48">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="124"/>
+      <c r="B42" s="48">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="124">
+        <v>11</v>
+      </c>
+      <c r="B43" s="48">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="124"/>
+      <c r="B44" s="48">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="124">
+        <v>12</v>
+      </c>
+      <c r="B45" s="48">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="124"/>
+      <c r="B46" s="48">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="124">
+        <v>14</v>
+      </c>
+      <c r="B47" s="48">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="124"/>
+      <c r="B48" s="48">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="124">
+        <v>16</v>
+      </c>
+      <c r="B49" s="48">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="124"/>
+      <c r="B50" s="48">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="124">
+        <v>18</v>
+      </c>
+      <c r="B51" s="48">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="124"/>
+      <c r="B52" s="48">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="124">
+        <v>20</v>
+      </c>
+      <c r="B53" s="48">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="124"/>
+      <c r="B54" s="48">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="124">
+        <v>22</v>
+      </c>
+      <c r="B55" s="48">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="124"/>
+      <c r="B56" s="48">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="124">
+        <v>25</v>
+      </c>
+      <c r="B57" s="48">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="124"/>
+      <c r="B58" s="48">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="124">
+        <v>28</v>
+      </c>
+      <c r="B59" s="48">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="124"/>
+      <c r="B60" s="48">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="124">
+        <v>32</v>
+      </c>
+      <c r="B61" s="48">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="124"/>
+      <c r="B62" s="48">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="124">
+        <v>36</v>
+      </c>
+      <c r="B63" s="48">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="124"/>
+      <c r="B64" s="48">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="124">
+        <v>40</v>
+      </c>
+      <c r="B65" s="48">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="124"/>
+      <c r="B66" s="48">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="124">
+        <v>45</v>
+      </c>
+      <c r="B67" s="48">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="124"/>
+      <c r="B68" s="48">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="124">
+        <v>50</v>
+      </c>
+      <c r="B69" s="48">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" s="124"/>
+      <c r="B70" s="48">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="124">
+        <v>56</v>
+      </c>
+      <c r="B71" s="48">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="124"/>
+      <c r="B72" s="48">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="124">
+        <v>63</v>
+      </c>
+      <c r="B73" s="48">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="124"/>
+      <c r="B74" s="48">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="124">
+        <v>71</v>
+      </c>
+      <c r="B75" s="48">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="124"/>
+      <c r="B76" s="48">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="124">
+        <v>80</v>
+      </c>
+      <c r="B77" s="48">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="124"/>
+      <c r="B78" s="48">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="124">
+        <v>90</v>
+      </c>
+      <c r="B79" s="48">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="124"/>
+      <c r="B80" s="48">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="40">
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A21:A22"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D136A9F2-8845-4295-A8BD-25F04BE0EFA0}">
   <dimension ref="A1:T34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6058,7 +6751,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32704C68-B145-4DB6-B0E3-AE1BF65D15BC}">
   <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10771,7 +11464,7 @@
       <c r="C39" s="124"/>
       <c r="D39" s="124"/>
       <c r="E39" s="52">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F39" t="s">
         <v>378</v>
@@ -10789,7 +11482,7 @@
       <c r="D40" s="124"/>
       <c r="E40">
         <f ca="1">E29*2*1000/E30/E39/E38</f>
-        <v>51.939287331535837</v>
+        <v>47.611013387241179</v>
       </c>
       <c r="F40" t="s">
         <v>16</v>
@@ -10804,7 +11497,7 @@
       <c r="D41" s="124"/>
       <c r="E41">
         <f ca="1">E40+E32</f>
-        <v>63.939287331535837</v>
+        <v>59.611013387241179</v>
       </c>
       <c r="F41" t="s">
         <v>16</v>
@@ -10824,11 +11517,12 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A31:F31"/>
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="A38:D38"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A25:D25"/>
@@ -10840,8 +11534,6 @@
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A11:D11"/>
@@ -10850,6 +11542,7 @@
     <mergeCell ref="A32:D32"/>
     <mergeCell ref="A34:D34"/>
     <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A31:F31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -11012,7 +11705,7 @@
       <c r="D17" s="124"/>
       <c r="E17" s="90">
         <f>'тихоходный вал'!E39</f>
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F17" t="s">
         <v>378</v>
@@ -11027,7 +11720,7 @@
       <c r="D18" s="124"/>
       <c r="E18">
         <f>E7*2*1000/E8/E17/E16</f>
-        <v>9.2312881291463924</v>
+        <v>8.462014118384193</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
@@ -11042,7 +11735,7 @@
       <c r="D19" s="124"/>
       <c r="E19">
         <f>E18+E10</f>
-        <v>19.231288129146392</v>
+        <v>18.462014118384193</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
@@ -11070,6 +11763,298 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{490D1B27-1B6E-4434-A576-709F124EC6EE}">
+  <dimension ref="A2:T11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="26" width="6.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A2" s="124" t="s">
+        <v>251</v>
+      </c>
+      <c r="B2" s="124"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="H2" s="124" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="124"/>
+      <c r="J2" s="124"/>
+      <c r="K2" s="124"/>
+      <c r="L2" s="124"/>
+      <c r="N2" s="124" t="s">
+        <v>252</v>
+      </c>
+      <c r="O2" s="124"/>
+      <c r="P2" s="124"/>
+      <c r="Q2" s="124"/>
+      <c r="R2" s="124"/>
+      <c r="S2" s="124"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A3" s="124" t="s">
+        <v>166</v>
+      </c>
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="61">
+        <f>Электродвигатель!$P$53</f>
+        <v>48.741201321892952</v>
+      </c>
+      <c r="F3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3" s="143" t="s">
+        <v>390</v>
+      </c>
+      <c r="I3" s="143"/>
+      <c r="J3" s="143"/>
+      <c r="K3" s="78">
+        <f>Передача!$D$49</f>
+        <v>2016</v>
+      </c>
+      <c r="L3" s="75" t="s">
+        <v>153</v>
+      </c>
+      <c r="N3" s="124" t="s">
+        <v>166</v>
+      </c>
+      <c r="O3" s="124"/>
+      <c r="P3" s="124"/>
+      <c r="Q3" s="124"/>
+      <c r="R3" s="61">
+        <f ca="1">Электродвигатель!$P$55</f>
+        <v>349.79520039605768</v>
+      </c>
+      <c r="S3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4" s="124" t="s">
+        <v>177</v>
+      </c>
+      <c r="B4" s="124"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="124"/>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H4" s="143" t="s">
+        <v>389</v>
+      </c>
+      <c r="I4" s="143"/>
+      <c r="J4" s="143"/>
+      <c r="K4" s="78">
+        <f>Передача!$D$50</f>
+        <v>734</v>
+      </c>
+      <c r="L4" s="75" t="s">
+        <v>153</v>
+      </c>
+      <c r="N4" s="124" t="s">
+        <v>177</v>
+      </c>
+      <c r="O4" s="124"/>
+      <c r="P4" s="124"/>
+      <c r="Q4" s="124"/>
+      <c r="R4">
+        <v>50</v>
+      </c>
+      <c r="S4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A5" s="124" t="s">
+        <v>391</v>
+      </c>
+      <c r="B5" s="124"/>
+      <c r="C5" s="124"/>
+      <c r="D5" s="124"/>
+      <c r="E5">
+        <f>E4*SQRT(E3)</f>
+        <v>698.14899070250726</v>
+      </c>
+      <c r="F5" t="s">
+        <v>153</v>
+      </c>
+      <c r="H5" s="143" t="s">
+        <v>388</v>
+      </c>
+      <c r="I5" s="143"/>
+      <c r="J5" s="143"/>
+      <c r="K5" s="78">
+        <f>Передача!$D$51</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="75" t="s">
+        <v>153</v>
+      </c>
+      <c r="N5" s="124" t="s">
+        <v>391</v>
+      </c>
+      <c r="O5" s="124"/>
+      <c r="P5" s="124"/>
+      <c r="Q5" s="124"/>
+      <c r="R5">
+        <f ca="1">R4*SQRT(R3)</f>
+        <v>935.14063166464132</v>
+      </c>
+      <c r="S5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A6" s="124" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" s="124"/>
+      <c r="C6" s="124"/>
+      <c r="D6" s="124"/>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N6" s="124" t="s">
+        <v>177</v>
+      </c>
+      <c r="O6" s="124"/>
+      <c r="P6" s="124"/>
+      <c r="Q6" s="124"/>
+      <c r="R6">
+        <v>3</v>
+      </c>
+      <c r="S6" t="s">
+        <v>57</v>
+      </c>
+      <c r="T6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A7" s="124" t="s">
+        <v>387</v>
+      </c>
+      <c r="B7" s="124"/>
+      <c r="C7" s="124"/>
+      <c r="D7" s="124"/>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>153</v>
+      </c>
+      <c r="H7" t="s">
+        <v>392</v>
+      </c>
+      <c r="N7" s="124" t="s">
+        <v>387</v>
+      </c>
+      <c r="O7" s="124"/>
+      <c r="P7" s="124"/>
+      <c r="Q7" s="124"/>
+      <c r="R7">
+        <f>R6*K3</f>
+        <v>6048</v>
+      </c>
+      <c r="S7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A8" s="124" t="s">
+        <v>383</v>
+      </c>
+      <c r="B8" s="124"/>
+      <c r="C8" s="124"/>
+      <c r="D8" s="124"/>
+      <c r="E8" s="124"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A9" s="124" t="s">
+        <v>384</v>
+      </c>
+      <c r="B9" s="124"/>
+      <c r="C9" s="124"/>
+      <c r="D9" s="52">
+        <v>50</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A10" s="124" t="s">
+        <v>385</v>
+      </c>
+      <c r="B10" s="124"/>
+      <c r="C10" s="124"/>
+      <c r="D10" s="52">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A11" s="124" t="s">
+        <v>386</v>
+      </c>
+      <c r="B11" s="124"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="52">
+        <v>50.5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="N2:S2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="N4:Q4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="N5:Q5"/>
+    <mergeCell ref="N7:Q7"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="N6:Q6"/>
+    <mergeCell ref="A6:D6"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B080B891-BABE-48BC-B741-A9DC893B6424}">
   <dimension ref="A2:W23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11318,6 +12303,10 @@
       </c>
       <c r="F19" t="s">
         <v>5</v>
+      </c>
+      <c r="I19">
+        <f>1432*30*PI()/1000*42.5/1000</f>
+        <v>5.7359198669242444</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.3">
@@ -11422,657 +12411,4 @@
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D8564D3-007A-4908-B584-B11BCC9DA655}">
-  <dimension ref="A1:E80"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="124">
-        <v>1</v>
-      </c>
-      <c r="B1">
-        <v>1</v>
-      </c>
-      <c r="D1" s="48"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="124"/>
-      <c r="B2">
-        <v>1.05</v>
-      </c>
-      <c r="D2" s="48"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="124">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B3">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D3" s="48"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="124"/>
-      <c r="B4">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="D4" s="48"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="124">
-        <v>1.2</v>
-      </c>
-      <c r="B5">
-        <v>1.2</v>
-      </c>
-      <c r="D5" s="48"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="124"/>
-      <c r="B6">
-        <v>1.3</v>
-      </c>
-      <c r="D6" s="48"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="124">
-        <v>1.4</v>
-      </c>
-      <c r="B7">
-        <v>1.4</v>
-      </c>
-      <c r="D7" s="48"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="124"/>
-      <c r="B8">
-        <v>1.5</v>
-      </c>
-      <c r="D8" s="48"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="124">
-        <v>1.6</v>
-      </c>
-      <c r="B9">
-        <v>1.6</v>
-      </c>
-      <c r="D9" s="48"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="124"/>
-      <c r="B10">
-        <v>1.7</v>
-      </c>
-      <c r="D10" s="48"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="124">
-        <v>1.8</v>
-      </c>
-      <c r="B11">
-        <v>1.8</v>
-      </c>
-      <c r="D11" s="48"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="124"/>
-      <c r="B12">
-        <v>1.9</v>
-      </c>
-      <c r="D12" s="48"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="124">
-        <v>2</v>
-      </c>
-      <c r="B13">
-        <v>2</v>
-      </c>
-      <c r="D13" s="48"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="124"/>
-      <c r="B14">
-        <v>2.1</v>
-      </c>
-      <c r="D14" s="48"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="124">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B15">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="D15" s="48"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="124"/>
-      <c r="B16">
-        <v>2.4</v>
-      </c>
-      <c r="D16" s="48"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="124">
-        <v>2.5</v>
-      </c>
-      <c r="B17">
-        <v>2.5</v>
-      </c>
-      <c r="D17" s="48"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="124"/>
-      <c r="B18">
-        <v>2.6</v>
-      </c>
-      <c r="D18" s="48"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="124">
-        <v>2.8</v>
-      </c>
-      <c r="B19">
-        <v>2.8</v>
-      </c>
-      <c r="D19" s="48"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="124"/>
-      <c r="B20">
-        <v>3</v>
-      </c>
-      <c r="D20" s="48"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="124">
-        <v>3.2</v>
-      </c>
-      <c r="B21">
-        <v>3.2</v>
-      </c>
-      <c r="D21" s="48"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="124"/>
-      <c r="B22">
-        <v>3.4</v>
-      </c>
-      <c r="D22" s="48"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="124">
-        <v>3.6</v>
-      </c>
-      <c r="B23">
-        <v>3.6</v>
-      </c>
-      <c r="D23" s="48"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="124"/>
-      <c r="B24">
-        <v>3.8</v>
-      </c>
-      <c r="D24" s="48"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="124">
-        <v>4</v>
-      </c>
-      <c r="B25">
-        <v>4</v>
-      </c>
-      <c r="D25" s="48"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="124"/>
-      <c r="B26">
-        <v>4.2</v>
-      </c>
-      <c r="D26" s="48"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="124">
-        <v>4.5</v>
-      </c>
-      <c r="B27">
-        <v>4.5</v>
-      </c>
-      <c r="D27" s="48"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="124"/>
-      <c r="B28">
-        <v>4.8</v>
-      </c>
-      <c r="D28" s="48"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="124">
-        <v>5</v>
-      </c>
-      <c r="B29">
-        <v>5</v>
-      </c>
-      <c r="D29" s="48"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="124"/>
-      <c r="B30">
-        <v>5.3</v>
-      </c>
-      <c r="D30" s="48"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="124">
-        <v>5.6</v>
-      </c>
-      <c r="B31">
-        <v>5.6</v>
-      </c>
-      <c r="D31" s="48"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="124"/>
-      <c r="B32">
-        <v>6</v>
-      </c>
-      <c r="D32" s="48"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="124">
-        <v>6.3</v>
-      </c>
-      <c r="B33">
-        <v>6.3</v>
-      </c>
-      <c r="D33" s="48"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="124"/>
-      <c r="B34">
-        <v>6.7</v>
-      </c>
-      <c r="D34" s="48"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="124">
-        <v>7.1</v>
-      </c>
-      <c r="B35">
-        <v>7.1</v>
-      </c>
-      <c r="D35" s="48"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="124"/>
-      <c r="B36">
-        <v>7.5</v>
-      </c>
-      <c r="D36" s="48"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="124">
-        <v>8</v>
-      </c>
-      <c r="B37">
-        <v>8</v>
-      </c>
-      <c r="D37" s="48"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="124"/>
-      <c r="B38">
-        <v>8.5</v>
-      </c>
-      <c r="D38" s="48"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="124">
-        <v>9</v>
-      </c>
-      <c r="B39">
-        <v>9</v>
-      </c>
-      <c r="D39" s="48"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="124"/>
-      <c r="B40" s="61">
-        <v>9.5</v>
-      </c>
-      <c r="D40" s="48"/>
-      <c r="E40" s="61"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="124">
-        <v>10</v>
-      </c>
-      <c r="B41" s="48">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="124"/>
-      <c r="B42" s="48">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="124">
-        <v>11</v>
-      </c>
-      <c r="B43" s="48">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="124"/>
-      <c r="B44" s="48">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="124">
-        <v>12</v>
-      </c>
-      <c r="B45" s="48">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="124"/>
-      <c r="B46" s="48">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="124">
-        <v>14</v>
-      </c>
-      <c r="B47" s="48">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="124"/>
-      <c r="B48" s="48">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="124">
-        <v>16</v>
-      </c>
-      <c r="B49" s="48">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="124"/>
-      <c r="B50" s="48">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="124">
-        <v>18</v>
-      </c>
-      <c r="B51" s="48">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="124"/>
-      <c r="B52" s="48">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="124">
-        <v>20</v>
-      </c>
-      <c r="B53" s="48">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="124"/>
-      <c r="B54" s="48">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="124">
-        <v>22</v>
-      </c>
-      <c r="B55" s="48">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="124"/>
-      <c r="B56" s="48">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="124">
-        <v>25</v>
-      </c>
-      <c r="B57" s="48">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="124"/>
-      <c r="B58" s="48">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="124">
-        <v>28</v>
-      </c>
-      <c r="B59" s="48">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="124"/>
-      <c r="B60" s="48">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="124">
-        <v>32</v>
-      </c>
-      <c r="B61" s="48">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="124"/>
-      <c r="B62" s="48">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="124">
-        <v>36</v>
-      </c>
-      <c r="B63" s="48">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="124"/>
-      <c r="B64" s="48">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="124">
-        <v>40</v>
-      </c>
-      <c r="B65" s="48">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="124"/>
-      <c r="B66" s="48">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="124">
-        <v>45</v>
-      </c>
-      <c r="B67" s="48">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="124"/>
-      <c r="B68" s="48">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="124">
-        <v>50</v>
-      </c>
-      <c r="B69" s="48">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="124"/>
-      <c r="B70" s="48">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="124">
-        <v>56</v>
-      </c>
-      <c r="B71" s="48">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="124"/>
-      <c r="B72" s="48">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="124">
-        <v>63</v>
-      </c>
-      <c r="B73" s="48">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="124"/>
-      <c r="B74" s="48">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="124">
-        <v>71</v>
-      </c>
-      <c r="B75" s="48">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="124"/>
-      <c r="B76" s="48">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="124">
-        <v>80</v>
-      </c>
-      <c r="B77" s="48">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="124"/>
-      <c r="B78" s="48">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="124">
-        <v>90</v>
-      </c>
-      <c r="B79" s="48">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="124"/>
-      <c r="B80" s="48">
-        <v>95</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A21:A22"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Расчёт.xlsx
+++ b/Расчёт.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Professional\Downloads\интститут\курсач детмаш\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9130D8F7-6739-4778-9CD8-8A3677498DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18854E6C-C0A5-47DB-879F-8CCD44108F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="812" activeTab="7" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="812" activeTab="9" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
   </bookViews>
   <sheets>
     <sheet name="Электродвигатель" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,13 @@
     <sheet name="Колесо" sheetId="7" r:id="rId5"/>
     <sheet name="тихоходный вал" sheetId="14" r:id="rId6"/>
     <sheet name="вал-шестерня" sheetId="13" r:id="rId7"/>
-    <sheet name="барабан" sheetId="16" r:id="rId8"/>
-    <sheet name="силы" sheetId="15" r:id="rId9"/>
-    <sheet name="Корпус" sheetId="3" r:id="rId10"/>
-    <sheet name="Ra40" sheetId="5" r:id="rId11"/>
-    <sheet name="Подшипники" sheetId="10" r:id="rId12"/>
-    <sheet name="Материалы" sheetId="11" r:id="rId13"/>
+    <sheet name="силы" sheetId="15" r:id="rId8"/>
+    <sheet name="Корпус" sheetId="3" r:id="rId9"/>
+    <sheet name="барабан" sheetId="16" r:id="rId10"/>
+    <sheet name="Муфта" sheetId="17" r:id="rId11"/>
+    <sheet name="Ra40" sheetId="5" r:id="rId12"/>
+    <sheet name="Подшипники" sheetId="10" r:id="rId13"/>
+    <sheet name="Материалы" sheetId="11" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -71,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="508">
   <si>
     <t>Окружная сила</t>
   </si>
@@ -1558,6 +1559,112 @@
   </si>
   <si>
     <t>Коэффициент радиальной силы</t>
+  </si>
+  <si>
+    <t>Длинна 45</t>
+  </si>
+  <si>
+    <t>1-муфта</t>
+  </si>
+  <si>
+    <t>2-первый подшипник</t>
+  </si>
+  <si>
+    <t>3-перая опора</t>
+  </si>
+  <si>
+    <t>4-вторая опора</t>
+  </si>
+  <si>
+    <t>5-второй подшипник</t>
+  </si>
+  <si>
+    <t>Радиальная от барабана</t>
+  </si>
+  <si>
+    <t>Окружная от барабана</t>
+  </si>
+  <si>
+    <t>Нормальная чистота (2)</t>
+  </si>
+  <si>
+    <t>Параметр точности</t>
+  </si>
+  <si>
+    <t>Угловое смещение</t>
+  </si>
+  <si>
+    <t>0.6/100</t>
+  </si>
+  <si>
+    <t>минут</t>
+  </si>
+  <si>
+    <t>мм/мм</t>
+  </si>
+  <si>
+    <r>
+      <t>Осевое смещение (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>ωs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Радиальное смещение (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Δs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>От передачи</t>
+  </si>
+  <si>
+    <t>От консоли</t>
+  </si>
+  <si>
+    <t>Радиальная консольная сила</t>
+  </si>
+  <si>
+    <t>Окржная консольная сила</t>
   </si>
 </sst>
 </file>
@@ -5879,492 +5986,1494 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B080B891-BABE-48BC-B741-A9DC893B6424}">
-  <dimension ref="A2:W33"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A782798A-CCB3-4606-8613-73DD636FD4B6}">
+  <dimension ref="A1:U58"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="12" width="6.77734375" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="132" t="s">
-        <v>139</v>
-      </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="132"/>
-      <c r="E2">
-        <f>Передача!$D$46</f>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C1">
+        <f ca="1">Электродвигатель!P58</f>
+        <v>339.37130342425513</v>
+      </c>
+      <c r="D1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="60">
+        <f>Вал!S4</f>
+        <v>190.98593171027443</v>
+      </c>
+      <c r="D2" t="s">
+        <v>104</v>
+      </c>
+      <c r="O2" s="132" t="s">
+        <v>95</v>
+      </c>
+      <c r="P2" s="132"/>
+      <c r="Q2" s="132"/>
+      <c r="R2" s="132"/>
+      <c r="S2" s="132"/>
+      <c r="T2" s="132"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <f>Электродвигатель!E14</f>
+        <v>400</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="O3" s="132" t="s">
+        <v>165</v>
+      </c>
+      <c r="P3" s="132"/>
+      <c r="Q3" s="132"/>
+      <c r="R3" s="132"/>
+      <c r="S3" s="60">
+        <f ca="1">C1</f>
+        <v>339.37130342425513</v>
+      </c>
+      <c r="T3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>467</v>
+      </c>
+      <c r="C4">
+        <f>Электродвигатель!F53</f>
+        <v>160</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="O4" s="110" t="s">
+        <v>486</v>
+      </c>
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110"/>
+      <c r="S4">
+        <f ca="1">2*1000*C1/C4</f>
+        <v>4242.1412928031887</v>
+      </c>
+      <c r="T4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="H5" s="16"/>
+      <c r="I5" s="107" t="s">
+        <v>360</v>
+      </c>
+      <c r="J5" s="108"/>
+      <c r="K5" s="108"/>
+      <c r="L5" s="115"/>
+      <c r="M5" s="1"/>
+      <c r="O5" s="132" t="s">
+        <v>487</v>
+      </c>
+      <c r="P5" s="132"/>
+      <c r="Q5" s="132"/>
+      <c r="R5" s="132"/>
+      <c r="S5" s="52">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="T5" t="s">
+        <v>57</v>
+      </c>
+      <c r="U5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="H6" s="48"/>
+      <c r="I6" s="102" t="s">
+        <v>459</v>
+      </c>
+      <c r="J6" s="16"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="1"/>
+      <c r="O6" s="132" t="s">
+        <v>150</v>
+      </c>
+      <c r="P6" s="132"/>
+      <c r="Q6" s="132"/>
+      <c r="R6" s="132"/>
+      <c r="S6">
+        <f ca="1">-S5*C1/C4*1000*2</f>
+        <v>-9756.9249734473342</v>
+      </c>
+      <c r="T6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B7" s="107" t="s">
         <v>180</v>
       </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="132" t="s">
-        <v>195</v>
-      </c>
-      <c r="B3" s="132"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="132"/>
-      <c r="E3">
-        <f>Передача!$D$55</f>
-        <v>37.75</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="132" t="s">
-        <v>170</v>
-      </c>
-      <c r="B4" s="132"/>
-      <c r="C4" s="132"/>
-      <c r="D4" s="132"/>
-      <c r="E4">
-        <f>Передача!$D$56</f>
-        <v>62</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="132" t="s">
-        <v>196</v>
-      </c>
-      <c r="B5" s="132"/>
-      <c r="C5" s="132"/>
-      <c r="D5" s="132"/>
-      <c r="E5">
-        <f>Передача!$D$60</f>
-        <v>309.75</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="132" t="s">
-        <v>171</v>
-      </c>
-      <c r="B6" s="132"/>
-      <c r="C6" s="132"/>
-      <c r="D6" s="132"/>
-      <c r="E6">
-        <f>Передача!$D$61</f>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="115"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="1"/>
+      <c r="O7" s="132" t="s">
+        <v>507</v>
+      </c>
+      <c r="P7" s="132"/>
+      <c r="Q7" s="132"/>
+      <c r="R7" s="132"/>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B8" s="109" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="110"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="F8" s="99"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="L8" s="3"/>
+      <c r="M8" s="1"/>
+      <c r="O8" s="132" t="s">
+        <v>506</v>
+      </c>
+      <c r="P8" s="132"/>
+      <c r="Q8" s="132"/>
+      <c r="R8" s="132"/>
+      <c r="S8">
+        <f>ABS(силы!R5)</f>
+        <v>2822.3999999999996</v>
+      </c>
+      <c r="T8" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B9" s="109" t="s">
+        <v>188</v>
+      </c>
+      <c r="C9" s="110"/>
+      <c r="D9" s="110"/>
+      <c r="E9" s="1">
+        <f ca="1">E8*(C1)^(1/3)</f>
+        <v>37.666228089886616</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="L9" s="3"/>
+      <c r="M9" s="1"/>
+      <c r="O9" s="132" t="s">
+        <v>376</v>
+      </c>
+      <c r="P9" s="132"/>
+      <c r="Q9" s="132"/>
+      <c r="R9" s="132"/>
+      <c r="S9" s="132"/>
+      <c r="T9" s="132"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B10" s="109" t="s">
+        <v>181</v>
+      </c>
+      <c r="C10" s="110"/>
+      <c r="D10" s="110"/>
+      <c r="E10" s="71">
+        <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;E9)</f>
+        <v>38</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="I10" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="1"/>
+      <c r="O10" s="132" t="s">
+        <v>377</v>
+      </c>
+      <c r="P10" s="132"/>
+      <c r="Q10" s="132"/>
+      <c r="R10" s="132"/>
+      <c r="S10" s="52">
+        <v>101.5</v>
+      </c>
+      <c r="T10" t="s">
+        <v>16</v>
+      </c>
+      <c r="U10" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B11" s="109" t="s">
+        <v>189</v>
+      </c>
+      <c r="C11" s="110"/>
+      <c r="D11" s="110"/>
+      <c r="E11" s="1">
+        <f ca="1">_xlfn.MINIFS(Вал!$28:$28,Вал!$26:$26,"&gt;="&amp;E10)</f>
+        <v>3.5</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="I11" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="L11" s="3"/>
+      <c r="M11" s="1"/>
+      <c r="O11" s="132" t="s">
+        <v>378</v>
+      </c>
+      <c r="P11" s="132"/>
+      <c r="Q11" s="132"/>
+      <c r="R11" s="132"/>
+      <c r="S11" s="52">
+        <v>74.5</v>
+      </c>
+      <c r="T11" t="s">
+        <v>16</v>
+      </c>
+      <c r="U11" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B12" s="109" t="s">
+        <v>185</v>
+      </c>
+      <c r="C12" s="110"/>
+      <c r="D12" s="110"/>
+      <c r="E12" s="1">
+        <f ca="1">E10+2*E11</f>
+        <v>45</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="I12" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="J12" s="1">
+        <v>52</v>
+      </c>
+      <c r="K12" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="L12" s="3"/>
+      <c r="M12" s="1"/>
+      <c r="O12" s="132" t="s">
+        <v>379</v>
+      </c>
+      <c r="P12" s="132"/>
+      <c r="Q12" s="132"/>
+      <c r="R12" s="132"/>
+      <c r="S12" s="52">
+        <v>320</v>
+      </c>
+      <c r="T12" t="s">
+        <v>16</v>
+      </c>
+      <c r="U12" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B13" s="109" t="s">
+        <v>250</v>
+      </c>
+      <c r="C13" s="110"/>
+      <c r="D13" s="110"/>
+      <c r="E13" s="71">
+        <f ca="1">_xlfn.MINIFS(Подшипники!$A:$A,Подшипники!$A:$A,"&gt;="&amp;E12)</f>
+        <v>45</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="I13" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="J13" s="1">
+        <v>58</v>
+      </c>
+      <c r="K13" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="L13" s="3"/>
+      <c r="M13" s="1"/>
+      <c r="O13" s="132" t="s">
+        <v>488</v>
+      </c>
+      <c r="P13" s="132"/>
+      <c r="Q13" s="132"/>
+      <c r="R13" s="132"/>
+      <c r="S13" s="52">
+        <v>74.5</v>
+      </c>
+      <c r="T13" t="s">
+        <v>16</v>
+      </c>
+      <c r="U13" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B14" s="109" t="s">
+        <v>189</v>
+      </c>
+      <c r="C14" s="110"/>
+      <c r="D14" s="110"/>
+      <c r="E14" s="1">
+        <f ca="1">_xlfn.MINIFS(Вал!$29:$29,Вал!$26:$26,"&gt;="&amp;E10)</f>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="I14" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="J14" s="1">
+        <v>10</v>
+      </c>
+      <c r="K14" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" s="3"/>
+      <c r="M14" s="1"/>
+      <c r="O14" s="132" t="s">
+        <v>390</v>
+      </c>
+      <c r="P14" s="132"/>
+      <c r="Q14" s="132"/>
+      <c r="R14" s="132"/>
+      <c r="S14" s="132"/>
+      <c r="T14" s="132"/>
+      <c r="U14" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B15" s="109" t="s">
+        <v>186</v>
+      </c>
+      <c r="C15" s="110"/>
+      <c r="D15" s="110"/>
+      <c r="E15" s="1">
+        <f ca="1">E13+2*E14</f>
+        <v>49.6</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="I15" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="J15" s="25">
+        <v>8</v>
+      </c>
+      <c r="K15" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="L15" s="3"/>
+      <c r="M15" s="1"/>
+      <c r="O15" s="132" t="s">
+        <v>495</v>
+      </c>
+      <c r="P15" s="132"/>
+      <c r="Q15" s="132"/>
+      <c r="R15" s="132"/>
+      <c r="S15">
+        <f ca="1">S4/2*(($S$12+$S$13)+($S$13))/($S$11+$S$12+$S$13)</f>
+        <v>2121.0706464015943</v>
+      </c>
+      <c r="T15" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B16" s="109" t="s">
+        <v>253</v>
+      </c>
+      <c r="C16" s="110"/>
+      <c r="D16" s="110"/>
+      <c r="E16" s="71">
+        <f ca="1">ROUNDUP(E15,0)</f>
+        <v>50</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="I16" s="106" t="s">
+        <v>481</v>
+      </c>
+      <c r="J16" s="25">
+        <v>0.5</v>
+      </c>
+      <c r="K16" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="L16" s="3"/>
+      <c r="M16" s="1"/>
+      <c r="O16" s="132" t="s">
+        <v>387</v>
+      </c>
+      <c r="P16" s="132"/>
+      <c r="Q16" s="132"/>
+      <c r="R16" s="132"/>
+      <c r="S16">
+        <f>S7*($S$10+$S$11+$S$12+$S$13)/($S$11+$S$12+$S$13)</f>
+        <v>0</v>
+      </c>
+      <c r="T16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B17" s="109" t="s">
+        <v>247</v>
+      </c>
+      <c r="C17" s="110"/>
+      <c r="D17" s="110"/>
+      <c r="E17" s="103">
+        <v>1309</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="I17" s="104" t="s">
+        <v>476</v>
+      </c>
+      <c r="J17" s="1">
+        <v>25</v>
+      </c>
+      <c r="K17" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="L17" s="3"/>
+      <c r="M17" s="1"/>
+      <c r="O17" s="132" t="s">
+        <v>494</v>
+      </c>
+      <c r="P17" s="132"/>
+      <c r="Q17" s="132"/>
+      <c r="R17" s="132"/>
+      <c r="S17">
+        <f ca="1">S6/2*(($S$12+$S$13)+($S$13))/($S$11+$S$12+$S$13)</f>
+        <v>-4878.4624867236671</v>
+      </c>
+      <c r="T17" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B18" s="109" t="s">
+        <v>333</v>
+      </c>
+      <c r="C18" s="110"/>
+      <c r="D18" s="110"/>
+      <c r="E18" s="1">
+        <v>100</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="I18" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="J18" s="1">
+        <f>0.2*J12*J12*J12</f>
+        <v>28121.600000000002</v>
+      </c>
+      <c r="K18" s="25" t="s">
+        <v>478</v>
+      </c>
+      <c r="L18" s="3"/>
+      <c r="M18" s="1"/>
+      <c r="O18" s="132" t="s">
+        <v>389</v>
+      </c>
+      <c r="P18" s="132"/>
+      <c r="Q18" s="132"/>
+      <c r="R18" s="132"/>
+      <c r="S18">
+        <f>S8*($S$10+$S$11+$S$12+$S$13)/($S$11+$S$12+$S$13)</f>
+        <v>3433.2179104477605</v>
+      </c>
+      <c r="T18" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B19" s="109" t="s">
+        <v>158</v>
+      </c>
+      <c r="C19" s="110"/>
+      <c r="D19" s="110"/>
+      <c r="E19" s="1">
+        <v>36</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="I19" s="105" t="s">
+        <v>479</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="K19" s="1"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="1"/>
+      <c r="O19" s="132" t="s">
+        <v>392</v>
+      </c>
+      <c r="P19" s="132"/>
+      <c r="Q19" s="132"/>
+      <c r="R19" s="132"/>
+      <c r="S19">
+        <f ca="1">S15+S16</f>
+        <v>2121.0706464015943</v>
+      </c>
+      <c r="T19" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B20" s="109" t="s">
+        <v>427</v>
+      </c>
+      <c r="C20" s="110"/>
+      <c r="D20" s="110"/>
+      <c r="E20" s="67">
+        <v>54</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="I20" s="105" t="s">
+        <v>480</v>
+      </c>
+      <c r="J20" s="1">
+        <f>(J13+J12)/2</f>
+        <v>55</v>
+      </c>
+      <c r="K20" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="L20" s="3"/>
+      <c r="M20" s="1"/>
+      <c r="O20" s="132" t="s">
+        <v>391</v>
+      </c>
+      <c r="P20" s="132"/>
+      <c r="Q20" s="132"/>
+      <c r="R20" s="132"/>
+      <c r="S20">
+        <f ca="1">S17+S18</f>
+        <v>-1445.2445762759066</v>
+      </c>
+      <c r="T20" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B21" s="109" t="s">
+        <v>428</v>
+      </c>
+      <c r="C21" s="110"/>
+      <c r="D21" s="110"/>
+      <c r="E21" s="67">
+        <v>22</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="I21" s="105" t="s">
+        <v>328</v>
+      </c>
+      <c r="J21" s="1">
+        <f>(J13-J12)/2-2*J16</f>
+        <v>2</v>
+      </c>
+      <c r="K21" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="L21" s="3"/>
+      <c r="O21" s="132" t="s">
+        <v>393</v>
+      </c>
+      <c r="P21" s="132"/>
+      <c r="Q21" s="132"/>
+      <c r="R21" s="132"/>
+      <c r="S21">
+        <f ca="1">SQRT(S19*S19+S20*S20)</f>
+        <v>2566.6461720076263</v>
+      </c>
+      <c r="T21" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B22" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1"/>
+      <c r="I22" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="J22" s="1" t="b">
+        <f ca="1">C1/J18*1000&lt;J17</f>
+        <v>1</v>
+      </c>
+      <c r="K22" s="1"/>
+      <c r="L22" s="3"/>
+      <c r="O22" s="132" t="s">
+        <v>394</v>
+      </c>
+      <c r="P22" s="132"/>
+      <c r="Q22" s="132"/>
+      <c r="R22" s="132"/>
+      <c r="S22" s="132"/>
+      <c r="T22" s="132"/>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>0.25</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2.54</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2.66</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="I23" s="106" t="s">
+        <v>483</v>
+      </c>
+      <c r="J23" s="1" t="b">
+        <f ca="1">2*C1*J19/J20/J15/J21/J24&lt;J25</f>
+        <v>1</v>
+      </c>
+      <c r="K23" s="1"/>
+      <c r="L23" s="3"/>
+      <c r="O23" s="132" t="s">
+        <v>495</v>
+      </c>
+      <c r="P23" s="132"/>
+      <c r="Q23" s="132"/>
+      <c r="R23" s="132"/>
+      <c r="S23">
+        <f ca="1">S4/2*(($S$11)+($S$11+$S$12))/($S$11+$S$12+$S$13)</f>
+        <v>2121.0706464015943</v>
+      </c>
+      <c r="T23" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="3"/>
+      <c r="I24" s="106" t="s">
+        <v>326</v>
+      </c>
+      <c r="J24" s="1">
+        <v>40</v>
+      </c>
+      <c r="K24" s="1"/>
+      <c r="L24" s="3"/>
+      <c r="O24" s="132" t="s">
+        <v>387</v>
+      </c>
+      <c r="P24" s="132"/>
+      <c r="Q24" s="132"/>
+      <c r="R24" s="132"/>
+      <c r="S24">
+        <f>-S7*($S$10)/($S$11+$S$12+$S$13)</f>
+        <v>0</v>
+      </c>
+      <c r="T24" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="5"/>
+      <c r="I25" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="J25" s="1">
+        <f>0.4*240</f>
+        <v>96</v>
+      </c>
+      <c r="K25" s="1"/>
+      <c r="L25" s="3"/>
+      <c r="O25" s="132" t="s">
+        <v>494</v>
+      </c>
+      <c r="P25" s="132"/>
+      <c r="Q25" s="132"/>
+      <c r="R25" s="132"/>
+      <c r="S25">
+        <f ca="1">S6/2*(($S$11)+($S$11+$S$12))/($S$11+$S$12+$S$13)</f>
+        <v>-4878.4624867236671</v>
+      </c>
+      <c r="T25" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="26" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="I26" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="J26" s="4" t="b">
+        <f ca="1">AND(J22,J23)</f>
+        <v>1</v>
+      </c>
+      <c r="K26" s="4"/>
+      <c r="L26" s="5"/>
+      <c r="O26" s="132" t="s">
+        <v>389</v>
+      </c>
+      <c r="P26" s="132"/>
+      <c r="Q26" s="132"/>
+      <c r="R26" s="132"/>
+      <c r="S26">
+        <f>-S8*($S$10)/($S$11+$S$12+$S$13)</f>
+        <v>-610.81791044776116</v>
+      </c>
+      <c r="T26" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="O27" s="132" t="s">
+        <v>392</v>
+      </c>
+      <c r="P27" s="132"/>
+      <c r="Q27" s="132"/>
+      <c r="R27" s="132"/>
+      <c r="S27">
+        <f ca="1">S23+S24</f>
+        <v>2121.0706464015943</v>
+      </c>
+      <c r="T27" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="28" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="O28" s="132" t="s">
+        <v>391</v>
+      </c>
+      <c r="P28" s="132"/>
+      <c r="Q28" s="132"/>
+      <c r="R28" s="132"/>
+      <c r="S28">
+        <f ca="1">S25+S26</f>
+        <v>-5489.2803971714284</v>
+      </c>
+      <c r="T28" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="O29" s="132" t="s">
+        <v>393</v>
+      </c>
+      <c r="P29" s="132"/>
+      <c r="Q29" s="132"/>
+      <c r="R29" s="132"/>
+      <c r="S29">
+        <f ca="1">SQRT(S27*S27+S28*S28)</f>
+        <v>5884.8228491431237</v>
+      </c>
+      <c r="T29" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="31" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="H31" s="132" t="s">
+        <v>403</v>
+      </c>
+      <c r="I31" s="132"/>
+      <c r="J31" s="132"/>
+      <c r="K31" s="132"/>
+      <c r="L31">
+        <f>Электродвигатель!$E$5</f>
+        <v>10000</v>
+      </c>
+      <c r="O31" s="132" t="s">
+        <v>399</v>
+      </c>
+      <c r="P31" s="132"/>
+      <c r="Q31" s="132"/>
+      <c r="R31" s="132"/>
+      <c r="S31">
+        <f ca="1">MAX(S29,S21)</f>
+        <v>5884.8228491431237</v>
+      </c>
+      <c r="T31" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="32" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="H32" s="132" t="s">
+        <v>396</v>
+      </c>
+      <c r="I32" s="132"/>
+      <c r="J32" s="132"/>
+      <c r="K32" s="132"/>
+      <c r="L32">
+        <f>Электродвигатель!$E$6</f>
+        <v>0.9</v>
+      </c>
+      <c r="O32" s="132" t="s">
+        <v>435</v>
+      </c>
+      <c r="P32" s="132"/>
+      <c r="Q32" s="132"/>
+      <c r="R32" s="132"/>
+      <c r="S32">
+        <f>Y6</f>
+        <v>0</v>
+      </c>
+      <c r="T32" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="33" spans="8:20" x14ac:dyDescent="0.3">
+      <c r="H33" s="132" t="s">
+        <v>397</v>
+      </c>
+      <c r="I33" s="132"/>
+      <c r="J33" s="132"/>
+      <c r="K33" s="132"/>
+      <c r="L33" s="97">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="8:20" x14ac:dyDescent="0.3">
+      <c r="H34" s="132" t="s">
+        <v>401</v>
+      </c>
+      <c r="I34" s="132"/>
+      <c r="J34" s="132"/>
+      <c r="K34" s="132"/>
+      <c r="L34" s="97">
+        <f>C23</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="8:20" x14ac:dyDescent="0.3">
+      <c r="H35" s="132" t="s">
+        <v>410</v>
+      </c>
+      <c r="I35" s="132"/>
+      <c r="J35" s="132"/>
+      <c r="K35" s="132"/>
+      <c r="L35" s="97">
+        <f>E23</f>
+        <v>2.66</v>
+      </c>
+      <c r="O35" s="132" t="s">
+        <v>395</v>
+      </c>
+      <c r="P35" s="132"/>
+      <c r="Q35" s="132"/>
+      <c r="R35" s="132"/>
+      <c r="S35" s="132"/>
+    </row>
+    <row r="36" spans="8:20" x14ac:dyDescent="0.3">
+      <c r="H36" s="132" t="s">
+        <v>434</v>
+      </c>
+      <c r="I36" s="132"/>
+      <c r="J36" s="132"/>
+      <c r="K36" s="132"/>
+      <c r="L36" s="97">
+        <v>1</v>
+      </c>
+      <c r="O36" s="132" t="s">
+        <v>398</v>
+      </c>
+      <c r="P36" s="132"/>
+      <c r="Q36" s="132"/>
+      <c r="R36" s="132"/>
+      <c r="S36" s="132"/>
+    </row>
+    <row r="37" spans="8:20" x14ac:dyDescent="0.3">
+      <c r="H37" s="132" t="s">
+        <v>432</v>
+      </c>
+      <c r="I37" s="132"/>
+      <c r="J37" s="132"/>
+      <c r="K37" s="132"/>
+      <c r="L37" s="52">
+        <v>1.6</v>
+      </c>
+      <c r="O37" s="132" t="s">
+        <v>431</v>
+      </c>
+      <c r="P37" s="132"/>
+      <c r="Q37" s="132"/>
+      <c r="R37" s="132"/>
+      <c r="S37">
+        <f>E21*1000</f>
+        <v>22000</v>
+      </c>
+      <c r="T37" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="38" spans="8:20" x14ac:dyDescent="0.3">
+      <c r="H38" s="132" t="s">
+        <v>424</v>
+      </c>
+      <c r="I38" s="132"/>
+      <c r="J38" s="132"/>
+      <c r="K38" s="132"/>
+      <c r="L38" s="52">
+        <v>1</v>
+      </c>
+      <c r="O38" s="132" t="s">
+        <v>400</v>
+      </c>
+      <c r="P38" s="132"/>
+      <c r="Q38" s="132"/>
+      <c r="R38" s="132"/>
+      <c r="S38">
+        <f ca="1">(S31*$C$23*$L$36+S32*$E$23)*$L$37*$L$38*$L$42</f>
+        <v>5931.9014319362686</v>
+      </c>
+      <c r="T38" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="39" spans="8:20" x14ac:dyDescent="0.3">
+      <c r="H39" s="132" t="s">
+        <v>433</v>
+      </c>
+      <c r="I39" s="132"/>
+      <c r="J39" s="132"/>
+      <c r="K39" s="132"/>
+      <c r="L39" s="97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="8:20" x14ac:dyDescent="0.3">
+      <c r="H40" s="132" t="s">
+        <v>412</v>
+      </c>
+      <c r="I40" s="132"/>
+      <c r="J40" s="132"/>
+      <c r="K40" s="132"/>
+      <c r="L40">
+        <f>Корпус!E30</f>
+        <v>22</v>
+      </c>
+      <c r="O40" s="132" t="s">
+        <v>402</v>
+      </c>
+      <c r="P40" s="132"/>
+      <c r="Q40" s="132"/>
+      <c r="R40" s="132"/>
+      <c r="S40" s="132"/>
+    </row>
+    <row r="41" spans="8:20" x14ac:dyDescent="0.3">
+      <c r="H41" s="132" t="s">
+        <v>422</v>
+      </c>
+      <c r="I41" s="132"/>
+      <c r="J41" s="132"/>
+      <c r="K41" s="132"/>
+      <c r="L41">
+        <f>Электродвигатель!$E$7</f>
+        <v>3</v>
+      </c>
+      <c r="O41" s="132" t="s">
+        <v>430</v>
+      </c>
+      <c r="P41" s="132"/>
+      <c r="Q41" s="132"/>
+      <c r="R41" s="132"/>
+      <c r="S41" s="88">
+        <f>E20*1000</f>
+        <v>54000</v>
+      </c>
+      <c r="T41" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="42" spans="8:20" x14ac:dyDescent="0.3">
+      <c r="H42" s="132" t="s">
+        <v>421</v>
+      </c>
+      <c r="I42" s="132"/>
+      <c r="J42" s="132"/>
+      <c r="K42" s="132"/>
+      <c r="L42" s="52">
+        <v>0.63</v>
+      </c>
+      <c r="O42" s="132" t="s">
+        <v>405</v>
+      </c>
+      <c r="P42" s="132"/>
+      <c r="Q42" s="132"/>
+      <c r="R42" s="132"/>
+      <c r="S42" s="132" t="b">
+        <f ca="1">S31&lt;(S41/2)</f>
+        <v>1</v>
+      </c>
+      <c r="T42" s="132"/>
+    </row>
+    <row r="43" spans="8:20" x14ac:dyDescent="0.3">
+      <c r="O43" s="132" t="s">
+        <v>406</v>
+      </c>
+      <c r="P43" s="132"/>
+      <c r="Q43" s="132"/>
+      <c r="R43" s="132"/>
+      <c r="S43" s="132" t="b">
+        <f ca="1">S31&gt;S42*0.01</f>
+        <v>1</v>
+      </c>
+      <c r="T43" s="132"/>
+    </row>
+    <row r="44" spans="8:20" x14ac:dyDescent="0.3">
+      <c r="O44" s="48"/>
+      <c r="P44" s="48"/>
+      <c r="Q44" s="48"/>
+      <c r="R44" s="48"/>
+    </row>
+    <row r="45" spans="8:20" x14ac:dyDescent="0.3">
+      <c r="O45" s="132" t="s">
+        <v>411</v>
+      </c>
+      <c r="P45" s="132"/>
+      <c r="Q45" s="132"/>
+      <c r="R45" s="132"/>
+      <c r="S45">
+        <f ca="1">(E18+E13)/2</f>
+        <v>72.5</v>
+      </c>
+      <c r="T45" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="8:20" x14ac:dyDescent="0.3">
+      <c r="O46" s="132" t="s">
+        <v>413</v>
+      </c>
+      <c r="P46" s="132"/>
+      <c r="Q46" s="132"/>
+      <c r="R46" s="132"/>
+      <c r="S46">
+        <f ca="1">IF(S3&gt;1000,4500*S3^(-0.5)*S45^(-0.5),45000*S3^(-0.83)*S45^(-0.5))</f>
+        <v>41.935629230014918</v>
+      </c>
+      <c r="T46" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="47" spans="8:20" x14ac:dyDescent="0.3">
+      <c r="O47" s="132" t="s">
+        <v>415</v>
+      </c>
+      <c r="P47" s="132"/>
+      <c r="Q47" s="132"/>
+      <c r="R47" s="132"/>
+      <c r="S47">
+        <f ca="1">MAX(MIN(4,$L$40/S46),0.1)</f>
+        <v>0.52461356617140653</v>
+      </c>
+      <c r="T47" t="s">
         <v>57</v>
       </c>
-      <c r="F6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="132" t="s">
-        <v>194</v>
-      </c>
-      <c r="B7" s="132"/>
-      <c r="C7" s="132"/>
-      <c r="D7" s="132"/>
-      <c r="E7">
-        <f>E2+E3/2+E5/2</f>
-        <v>353.75</v>
-      </c>
-      <c r="F7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="132" t="s">
+    </row>
+    <row r="48" spans="8:20" x14ac:dyDescent="0.3">
+      <c r="O48" s="132" t="s">
+        <v>496</v>
+      </c>
+      <c r="P48" s="132"/>
+    </row>
+    <row r="49" spans="15:21" x14ac:dyDescent="0.3">
+      <c r="O49" s="132" t="s">
+        <v>416</v>
+      </c>
+      <c r="P49" s="132"/>
+      <c r="Q49" s="132"/>
+      <c r="R49" s="132"/>
+      <c r="S49" s="52">
+        <f ca="1">0.0432*S47^0.68*S45^0.55*(1-1.141/S45^(1/3))</f>
+        <v>0.21345922614533333</v>
+      </c>
+      <c r="T49" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="50" spans="15:21" x14ac:dyDescent="0.3">
+      <c r="O50" s="132" t="s">
+        <v>414</v>
+      </c>
+      <c r="P50" s="132"/>
+      <c r="Q50" s="132"/>
+      <c r="R50" s="132"/>
+      <c r="S50" s="97">
+        <f>S41/22</f>
+        <v>2454.5454545454545</v>
+      </c>
+      <c r="T50" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="52" spans="15:21" x14ac:dyDescent="0.3">
+      <c r="O52" t="s">
         <v>193</v>
       </c>
-      <c r="B8" s="132"/>
-      <c r="C8" s="132"/>
-      <c r="D8" s="132"/>
-      <c r="E8">
-        <f>E7^(1/3)+3</f>
-        <v>10.072378298355165</v>
-      </c>
-      <c r="F8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="132" t="s">
-        <v>197</v>
-      </c>
-      <c r="B9" s="132"/>
-      <c r="C9" s="132"/>
-      <c r="D9" s="132"/>
-      <c r="E9">
-        <f>E8*3</f>
-        <v>30.217134895065495</v>
-      </c>
-      <c r="F9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="132"/>
-      <c r="B10" s="132"/>
-      <c r="C10" s="132"/>
-      <c r="D10" s="132"/>
-      <c r="E10" s="88"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="132"/>
-      <c r="B11" s="132"/>
-      <c r="C11" s="132"/>
-      <c r="D11" s="132"/>
-      <c r="E11" s="88"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="132" t="s">
-        <v>199</v>
-      </c>
-      <c r="B12" s="132"/>
-      <c r="C12" s="132"/>
-      <c r="D12" s="132"/>
-      <c r="E12" s="132"/>
-      <c r="F12" s="132"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="132" t="s">
-        <v>198</v>
-      </c>
-      <c r="B13" s="132"/>
-      <c r="C13" s="132"/>
-      <c r="D13" s="132"/>
-      <c r="E13">
-        <f>E7+2*E8</f>
-        <v>373.89475659671035</v>
-      </c>
-      <c r="F13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="132" t="s">
-        <v>158</v>
-      </c>
-      <c r="B14" s="132"/>
-      <c r="C14" s="132"/>
-      <c r="D14" s="132"/>
-      <c r="E14">
-        <f>E4+2*E8</f>
-        <v>82.144756596710323</v>
-      </c>
-      <c r="F14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="132" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="132"/>
-      <c r="C15" s="132"/>
-      <c r="D15" s="132"/>
-      <c r="E15">
-        <f>E5+E8+E9</f>
-        <v>350.03951319342065</v>
-      </c>
-      <c r="F15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A17" s="132" t="s">
-        <v>436</v>
-      </c>
-      <c r="B17" s="132"/>
-      <c r="C17" s="132"/>
-      <c r="D17" s="132"/>
-      <c r="E17">
-        <f>(E13*2+E14+E15)/3/1000</f>
-        <v>0.39332459432785055</v>
-      </c>
-      <c r="F17" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A18" s="132" t="s">
-        <v>438</v>
-      </c>
-      <c r="B18" s="132"/>
-      <c r="C18" s="132"/>
-      <c r="D18" s="132"/>
-      <c r="E18">
-        <f ca="1">Электродвигатель!P55</f>
-        <v>349.79520039605768</v>
-      </c>
-      <c r="F18" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A19" s="132" t="s">
-        <v>439</v>
-      </c>
-      <c r="B19" s="132"/>
-      <c r="C19" s="132"/>
-      <c r="D19" s="132"/>
-      <c r="E19">
-        <f ca="1">MAX(1.3*E18^0.25,6)</f>
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A20" s="132" t="s">
-        <v>440</v>
-      </c>
-      <c r="B20" s="132"/>
-      <c r="C20" s="132"/>
-      <c r="D20" s="132"/>
-      <c r="E20">
-        <f ca="1">ROUNDUP( E19*0.7,1)</f>
-        <v>4.2</v>
-      </c>
-      <c r="F20" t="s">
-        <v>16</v>
-      </c>
-      <c r="R20" s="1"/>
-      <c r="S20" s="90"/>
-      <c r="T20" s="48"/>
-      <c r="U20" s="48"/>
-      <c r="V20" s="16"/>
-      <c r="W20" s="16"/>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A21" s="132" t="s">
-        <v>342</v>
-      </c>
-      <c r="B21" s="132"/>
-      <c r="C21" s="132"/>
-      <c r="D21" s="132"/>
-      <c r="E21" s="132"/>
-      <c r="F21" s="132"/>
-      <c r="G21" t="s">
-        <v>100</v>
-      </c>
-      <c r="R21" s="66"/>
-      <c r="S21" s="66"/>
-      <c r="T21" s="16"/>
-      <c r="U21" s="16"/>
-      <c r="V21" s="16"/>
-      <c r="W21" s="16"/>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A22" s="132" t="s">
-        <v>441</v>
-      </c>
-      <c r="B22" s="132"/>
-      <c r="C22" s="132"/>
-      <c r="D22" s="132"/>
-      <c r="E22">
-        <f ca="1">Вал!$S$21*1.25+10</f>
-        <v>122.5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>16</v>
-      </c>
-      <c r="R22" s="66"/>
-      <c r="S22" s="66"/>
-      <c r="T22" s="16"/>
-      <c r="U22" s="16"/>
-      <c r="V22" s="62"/>
-      <c r="W22" s="62"/>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A23" s="132" t="s">
-        <v>442</v>
-      </c>
-      <c r="B23" s="132"/>
-      <c r="C23" s="132"/>
-      <c r="D23" s="132"/>
-      <c r="E23">
-        <f>Вал!$K$21*1.25+10</f>
-        <v>110</v>
-      </c>
-      <c r="F23" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A24" s="132" t="s">
-        <v>443</v>
-      </c>
-      <c r="B24" s="132"/>
-      <c r="C24" s="132"/>
-      <c r="D24" s="132"/>
-      <c r="E24">
-        <f ca="1">MAX(1.25*E18^(1/3),10)</f>
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A26" s="132" t="s">
-        <v>315</v>
-      </c>
-      <c r="B26" s="132"/>
-      <c r="C26" s="132"/>
-      <c r="D26" s="132"/>
-      <c r="E26" s="132"/>
-      <c r="F26" s="132"/>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A27" s="132" t="s">
-        <v>312</v>
-      </c>
-      <c r="B27" s="132"/>
-      <c r="C27" s="132"/>
-      <c r="D27" s="132"/>
-      <c r="E27">
-        <f>Вал!$K$4*PI()/30</f>
-        <v>150.79644737231007</v>
-      </c>
-      <c r="F27" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A28" s="132" t="s">
-        <v>313</v>
-      </c>
-      <c r="B28" s="132"/>
-      <c r="C28" s="132"/>
-      <c r="D28" s="132"/>
-      <c r="E28">
-        <f>Корпус!$E$27*MAX(Вал!$K$22,Вал!$K$7)/1000</f>
-        <v>7.3890259212431939</v>
-      </c>
-      <c r="F28" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A29" s="132" t="s">
-        <v>316</v>
-      </c>
-      <c r="B29" s="132"/>
-      <c r="C29" s="132"/>
-      <c r="D29" s="132"/>
-      <c r="E29" s="52">
-        <v>504</v>
-      </c>
-      <c r="F29" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A30" s="132" t="s">
-        <v>318</v>
-      </c>
-      <c r="B30" s="132"/>
-      <c r="C30" s="132"/>
-      <c r="D30" s="132"/>
-      <c r="E30" s="52">
-        <v>22</v>
-      </c>
-      <c r="F30" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A31" s="132" t="s">
-        <v>319</v>
-      </c>
-      <c r="B31" s="132"/>
-      <c r="C31" s="132"/>
-      <c r="D31" s="132"/>
-      <c r="E31" t="s">
-        <v>320</v>
-      </c>
-      <c r="F31" s="101" t="s">
-        <v>456</v>
-      </c>
-      <c r="G31" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A32" s="132" t="s">
-        <v>321</v>
-      </c>
-      <c r="B32" s="132"/>
-      <c r="C32" s="132"/>
-      <c r="D32" s="132"/>
-      <c r="E32">
-        <f>MAX(4*Передача!$D$47,10)</f>
-        <v>10</v>
-      </c>
-      <c r="F32">
-        <f>MAX(Передача!$D$58/4,10)</f>
-        <v>79.375</v>
-      </c>
-      <c r="G32" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E33">
-        <f>E32+E9</f>
-        <v>40.217134895065499</v>
-      </c>
-      <c r="F33">
-        <f>F32+E9</f>
-        <v>109.5921348950655</v>
-      </c>
+      <c r="P52" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>417</v>
+      </c>
+      <c r="R52" t="s">
+        <v>423</v>
+      </c>
+      <c r="S52" t="s">
+        <v>418</v>
+      </c>
+      <c r="T52" t="s">
+        <v>420</v>
+      </c>
+      <c r="U52" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="53" spans="15:21" x14ac:dyDescent="0.3">
+      <c r="O53" s="97">
+        <v>2.5670999999999999</v>
+      </c>
+      <c r="P53" s="97">
+        <v>2.2648999999999999</v>
+      </c>
+      <c r="Q53" s="97">
+        <v>5.4380999999999999E-2</v>
+      </c>
+      <c r="R53" s="97">
+        <f>1/3</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="S53" s="97">
+        <v>0.83</v>
+      </c>
+      <c r="T53" s="97">
+        <v>1</v>
+      </c>
+      <c r="U53" s="97">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="55" spans="15:21" x14ac:dyDescent="0.3">
+      <c r="O55" s="132" t="s">
+        <v>407</v>
+      </c>
+      <c r="P55" s="132"/>
+      <c r="Q55" s="132"/>
+      <c r="R55" s="132"/>
+      <c r="S55">
+        <f ca="1">MIN(0.3*(1-(O53-P53/S47^Q53)^S53*(S49*S50/T53/S38)^R53)^(-U53),50)</f>
+        <v>1.0652003303996018</v>
+      </c>
+      <c r="T55" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="56" spans="15:21" x14ac:dyDescent="0.3">
+      <c r="O56" s="132" t="s">
+        <v>137</v>
+      </c>
+      <c r="P56" s="132"/>
+      <c r="Q56" s="132"/>
+      <c r="R56" s="132"/>
+      <c r="S56" s="132">
+        <f ca="1">$L$39*S55*(S41/S38)^$L$33*10^6/60/S3</f>
+        <v>39464.30213377683</v>
+      </c>
+      <c r="T56" s="132"/>
+      <c r="U56" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="57" spans="15:21" x14ac:dyDescent="0.3">
+      <c r="O57" s="132" t="s">
+        <v>409</v>
+      </c>
+      <c r="P57" s="132"/>
+      <c r="Q57" s="132"/>
+      <c r="R57" s="132"/>
+      <c r="S57" s="132" t="b">
+        <f ca="1">S56&gt;$L$31</f>
+        <v>1</v>
+      </c>
+      <c r="T57" s="132"/>
+    </row>
+    <row r="58" spans="15:21" x14ac:dyDescent="0.3">
+      <c r="O58" s="132" t="s">
+        <v>164</v>
+      </c>
+      <c r="P58" s="132"/>
+      <c r="Q58" s="132"/>
+      <c r="R58" s="132"/>
+      <c r="S58" s="166" t="b">
+        <f ca="1">AND(S42,S43,S57)</f>
+        <v>1</v>
+      </c>
+      <c r="T58" s="166"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A31:D31"/>
+  <mergeCells count="81">
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="O6:R6"/>
+    <mergeCell ref="O5:R5"/>
+    <mergeCell ref="O4:R4"/>
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="H42:K42"/>
+    <mergeCell ref="H36:K36"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="H38:K38"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="H40:K40"/>
+    <mergeCell ref="O35:S35"/>
+    <mergeCell ref="H31:K31"/>
+    <mergeCell ref="H32:K32"/>
+    <mergeCell ref="H33:K33"/>
+    <mergeCell ref="H34:K34"/>
+    <mergeCell ref="H35:K35"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O56:R56"/>
+    <mergeCell ref="S56:T56"/>
+    <mergeCell ref="O57:R57"/>
+    <mergeCell ref="S57:T57"/>
+    <mergeCell ref="O58:R58"/>
+    <mergeCell ref="S58:T58"/>
+    <mergeCell ref="O46:R46"/>
+    <mergeCell ref="O47:R47"/>
+    <mergeCell ref="O49:R49"/>
+    <mergeCell ref="O50:R50"/>
+    <mergeCell ref="O55:R55"/>
+    <mergeCell ref="O48:P48"/>
+    <mergeCell ref="O42:R42"/>
+    <mergeCell ref="S42:T42"/>
+    <mergeCell ref="O43:R43"/>
+    <mergeCell ref="S43:T43"/>
+    <mergeCell ref="O45:R45"/>
+    <mergeCell ref="O36:S36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="O40:S40"/>
+    <mergeCell ref="O41:R41"/>
+    <mergeCell ref="O23:R23"/>
+    <mergeCell ref="O24:R24"/>
+    <mergeCell ref="O25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O18:R18"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="O20:R20"/>
+    <mergeCell ref="O21:R21"/>
+    <mergeCell ref="O22:T22"/>
+    <mergeCell ref="O14:T14"/>
+    <mergeCell ref="O15:R15"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="O17:R17"/>
+    <mergeCell ref="O13:R13"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="O9:T9"/>
+    <mergeCell ref="O10:R10"/>
+    <mergeCell ref="O11:R11"/>
+    <mergeCell ref="O12:R12"/>
+    <mergeCell ref="O2:T2"/>
+    <mergeCell ref="O3:R3"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B16:D16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5106C50C-21F5-4FE2-A0ED-C1B68F182EC0}">
+  <dimension ref="A2:G7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>503</v>
+      </c>
+      <c r="D3">
+        <v>0.3</v>
+      </c>
+      <c r="E3">
+        <f>D3*1.6</f>
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>498</v>
+      </c>
+      <c r="D4" t="s">
+        <v>499</v>
+      </c>
+      <c r="E4" t="s">
+        <v>501</v>
+      </c>
+      <c r="F4">
+        <f>0.6*34.5</f>
+        <v>20.7</v>
+      </c>
+      <c r="G4" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>458</v>
+      </c>
+      <c r="B7" s="60">
+        <f>Электродвигатель!P52</f>
+        <v>49.735919716217296</v>
+      </c>
+      <c r="C7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D8564D3-007A-4908-B584-B11BCC9DA655}">
   <dimension ref="A1:E80"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7017,7 +8126,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D136A9F2-8845-4295-A8BD-25F04BE0EFA0}">
   <dimension ref="A1:T34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7916,7 +9025,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32704C68-B145-4DB6-B0E3-AE1BF65D15BC}">
   <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -13030,1422 +14139,14 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A782798A-CCB3-4606-8613-73DD636FD4B6}">
-  <dimension ref="A1:U58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>458</v>
-      </c>
-      <c r="C1">
-        <f ca="1">Электродвигатель!P58</f>
-        <v>339.37130342425513</v>
-      </c>
-      <c r="D1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" s="60">
-        <f>Вал!S4</f>
-        <v>190.98593171027443</v>
-      </c>
-      <c r="D2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3">
-        <f>Электродвигатель!E14</f>
-        <v>400</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="O3" s="132" t="s">
-        <v>95</v>
-      </c>
-      <c r="P3" s="132"/>
-      <c r="Q3" s="132"/>
-      <c r="R3" s="132"/>
-      <c r="S3" s="132"/>
-      <c r="T3" s="132"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>467</v>
-      </c>
-      <c r="C4">
-        <f>Электродвигатель!F53</f>
-        <v>160</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="O4" s="132" t="s">
-        <v>165</v>
-      </c>
-      <c r="P4" s="132"/>
-      <c r="Q4" s="132"/>
-      <c r="R4" s="132"/>
-      <c r="S4" s="60">
-        <f ca="1">C1</f>
-        <v>339.37130342425513</v>
-      </c>
-      <c r="T4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H5" s="16"/>
-      <c r="I5" s="107" t="s">
-        <v>360</v>
-      </c>
-      <c r="J5" s="108"/>
-      <c r="K5" s="108"/>
-      <c r="L5" s="115"/>
-      <c r="M5" s="1"/>
-      <c r="O5" s="132" t="s">
-        <v>176</v>
-      </c>
-      <c r="P5" s="132"/>
-      <c r="Q5" s="132"/>
-      <c r="R5" s="132"/>
-      <c r="S5">
-        <v>50</v>
-      </c>
-      <c r="T5" t="s">
-        <v>57</v>
-      </c>
-      <c r="U5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="H6" s="48"/>
-      <c r="I6" s="102" t="s">
-        <v>459</v>
-      </c>
-      <c r="J6" s="16"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="1"/>
-      <c r="O6" s="132" t="s">
-        <v>384</v>
-      </c>
-      <c r="P6" s="132"/>
-      <c r="Q6" s="132"/>
-      <c r="R6" s="132"/>
-      <c r="S6">
-        <f ca="1">S5*SQRT(S4)</f>
-        <v>921.10165484632466</v>
-      </c>
-      <c r="T6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B7" s="107" t="s">
-        <v>180</v>
-      </c>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="115"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="7" t="s">
-        <v>464</v>
-      </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="1"/>
-      <c r="O7" s="132" t="s">
-        <v>176</v>
-      </c>
-      <c r="P7" s="132"/>
-      <c r="Q7" s="132"/>
-      <c r="R7" s="132"/>
-      <c r="T7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B8" s="109" t="s">
-        <v>176</v>
-      </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
-      <c r="E8" s="1">
-        <v>5.4</v>
-      </c>
-      <c r="F8" s="99"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="L8" s="3"/>
-      <c r="M8" s="1"/>
-      <c r="O8" s="132" t="s">
-        <v>380</v>
-      </c>
-      <c r="P8" s="132"/>
-      <c r="Q8" s="132"/>
-      <c r="R8" s="132"/>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B9" s="109" t="s">
-        <v>188</v>
-      </c>
-      <c r="C9" s="110"/>
-      <c r="D9" s="110"/>
-      <c r="E9" s="1">
-        <f ca="1">E8*(C1)^(1/3)</f>
-        <v>37.666228089886616</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="L9" s="3"/>
-      <c r="M9" s="1"/>
-      <c r="O9" s="132" t="s">
-        <v>376</v>
-      </c>
-      <c r="P9" s="132"/>
-      <c r="Q9" s="132"/>
-      <c r="R9" s="132"/>
-      <c r="S9" s="132"/>
-      <c r="T9" s="132"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B10" s="109" t="s">
-        <v>181</v>
-      </c>
-      <c r="C10" s="110"/>
-      <c r="D10" s="110"/>
-      <c r="E10" s="71">
-        <f ca="1">_xlfn.MINIFS('Ra40'!$B:$B,'Ra40'!$B:$B,"&gt;="&amp;E9)</f>
-        <v>38</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="1"/>
-      <c r="I10" s="7" t="s">
-        <v>485</v>
-      </c>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="1"/>
-      <c r="O10" s="132" t="s">
-        <v>377</v>
-      </c>
-      <c r="P10" s="132"/>
-      <c r="Q10" s="132"/>
-      <c r="R10" s="132"/>
-      <c r="S10" s="52">
-        <v>49</v>
-      </c>
-      <c r="T10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B11" s="109" t="s">
-        <v>189</v>
-      </c>
-      <c r="C11" s="110"/>
-      <c r="D11" s="110"/>
-      <c r="E11" s="1">
-        <f ca="1">_xlfn.MINIFS(Вал!$28:$28,Вал!$26:$26,"&gt;="&amp;E10)</f>
-        <v>3.5</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="1"/>
-      <c r="I11" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="L11" s="3"/>
-      <c r="M11" s="1"/>
-      <c r="O11" s="132" t="s">
-        <v>378</v>
-      </c>
-      <c r="P11" s="132"/>
-      <c r="Q11" s="132"/>
-      <c r="R11" s="132"/>
-      <c r="S11" s="52">
-        <v>49</v>
-      </c>
-      <c r="T11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B12" s="109" t="s">
-        <v>185</v>
-      </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="110"/>
-      <c r="E12" s="1">
-        <f ca="1">E10+2*E11</f>
-        <v>45</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="1"/>
-      <c r="I12" s="7" t="s">
-        <v>474</v>
-      </c>
-      <c r="J12" s="1">
-        <v>52</v>
-      </c>
-      <c r="K12" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="L12" s="3"/>
-      <c r="M12" s="1"/>
-      <c r="O12" s="132" t="s">
-        <v>379</v>
-      </c>
-      <c r="P12" s="132"/>
-      <c r="Q12" s="132"/>
-      <c r="R12" s="132"/>
-      <c r="S12" s="52">
-        <v>70</v>
-      </c>
-      <c r="T12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B13" s="109" t="s">
-        <v>250</v>
-      </c>
-      <c r="C13" s="110"/>
-      <c r="D13" s="110"/>
-      <c r="E13" s="71">
-        <f ca="1">_xlfn.MINIFS(Подшипники!$A:$A,Подшипники!$A:$A,"&gt;="&amp;E12)</f>
-        <v>45</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" s="1"/>
-      <c r="I13" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="J13" s="1">
-        <v>58</v>
-      </c>
-      <c r="K13" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="L13" s="3"/>
-      <c r="M13" s="1"/>
-      <c r="O13" s="132"/>
-      <c r="P13" s="132"/>
-      <c r="Q13" s="132"/>
-      <c r="R13" s="132"/>
-      <c r="S13" s="132"/>
-      <c r="T13" s="132"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B14" s="109" t="s">
-        <v>189</v>
-      </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="110"/>
-      <c r="E14" s="1">
-        <f ca="1">_xlfn.MINIFS(Вал!$29:$29,Вал!$26:$26,"&gt;="&amp;E10)</f>
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="1"/>
-      <c r="I14" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="J14" s="1">
-        <v>10</v>
-      </c>
-      <c r="K14" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="L14" s="3"/>
-      <c r="M14" s="1"/>
-      <c r="O14" s="132" t="s">
-        <v>390</v>
-      </c>
-      <c r="P14" s="132"/>
-      <c r="Q14" s="132"/>
-      <c r="R14" s="132"/>
-      <c r="S14" s="132"/>
-      <c r="T14" s="132"/>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B15" s="109" t="s">
-        <v>186</v>
-      </c>
-      <c r="C15" s="110"/>
-      <c r="D15" s="110"/>
-      <c r="E15" s="1">
-        <f ca="1">E13+2*E14</f>
-        <v>49.6</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" s="1"/>
-      <c r="I15" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="J15" s="25">
-        <v>8</v>
-      </c>
-      <c r="K15" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="L15" s="3"/>
-      <c r="M15" s="1"/>
-      <c r="O15" s="132" t="s">
-        <v>386</v>
-      </c>
-      <c r="P15" s="132"/>
-      <c r="Q15" s="132"/>
-      <c r="R15" s="132"/>
-      <c r="S15">
-        <f ca="1">$E$26*S11/(S10+S11)</f>
-        <v>2121.0706464015943</v>
-      </c>
-      <c r="T15" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B16" s="109" t="s">
-        <v>253</v>
-      </c>
-      <c r="C16" s="110"/>
-      <c r="D16" s="110"/>
-      <c r="E16" s="71">
-        <f ca="1">ROUNDUP(E15,0)</f>
-        <v>50</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" s="1"/>
-      <c r="I16" s="106" t="s">
-        <v>481</v>
-      </c>
-      <c r="J16" s="25">
-        <v>0.5</v>
-      </c>
-      <c r="K16" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="L16" s="3"/>
-      <c r="M16" s="1"/>
-      <c r="O16" s="132" t="s">
-        <v>387</v>
-      </c>
-      <c r="P16" s="132"/>
-      <c r="Q16" s="132"/>
-      <c r="R16" s="132"/>
-      <c r="S16">
-        <f ca="1">S6*S12/(S10+S11)</f>
-        <v>657.92975346166043</v>
-      </c>
-      <c r="T16" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B17" s="109" t="s">
-        <v>247</v>
-      </c>
-      <c r="C17" s="110"/>
-      <c r="D17" s="110"/>
-      <c r="E17" s="103">
-        <v>1210</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="G17" s="1"/>
-      <c r="I17" s="104" t="s">
-        <v>476</v>
-      </c>
-      <c r="J17" s="1">
-        <v>25</v>
-      </c>
-      <c r="K17" s="25" t="s">
-        <v>223</v>
-      </c>
-      <c r="L17" s="3"/>
-      <c r="M17" s="1"/>
-      <c r="O17" s="132" t="s">
-        <v>388</v>
-      </c>
-      <c r="P17" s="132"/>
-      <c r="Q17" s="132"/>
-      <c r="R17" s="132"/>
-      <c r="S17">
-        <f ca="1">$E$28*S11/(S10+S11)</f>
-        <v>4878.4624867236662</v>
-      </c>
-      <c r="T17" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B18" s="109" t="s">
-        <v>333</v>
-      </c>
-      <c r="C18" s="110"/>
-      <c r="D18" s="110"/>
-      <c r="E18" s="1">
-        <v>85</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18" s="1"/>
-      <c r="I18" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="J18" s="1">
-        <f>0.2*J12*J12*J12</f>
-        <v>28121.600000000002</v>
-      </c>
-      <c r="K18" s="25" t="s">
-        <v>478</v>
-      </c>
-      <c r="L18" s="3"/>
-      <c r="M18" s="1"/>
-      <c r="O18" s="132" t="s">
-        <v>389</v>
-      </c>
-      <c r="P18" s="132"/>
-      <c r="Q18" s="132"/>
-      <c r="R18" s="132"/>
-      <c r="S18">
-        <f>S8*S12/(S10+S11)</f>
-        <v>0</v>
-      </c>
-      <c r="T18" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B19" s="109" t="s">
-        <v>158</v>
-      </c>
-      <c r="C19" s="110"/>
-      <c r="D19" s="110"/>
-      <c r="E19" s="1">
-        <v>19</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G19" s="1"/>
-      <c r="I19" s="105" t="s">
-        <v>479</v>
-      </c>
-      <c r="J19" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="K19" s="1"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="1"/>
-      <c r="O19" s="132" t="s">
-        <v>392</v>
-      </c>
-      <c r="P19" s="132"/>
-      <c r="Q19" s="132"/>
-      <c r="R19" s="132"/>
-      <c r="S19">
-        <f ca="1">S15+S16</f>
-        <v>2779.0003998632546</v>
-      </c>
-      <c r="T19" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B20" s="109" t="s">
-        <v>427</v>
-      </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="110"/>
-      <c r="E20" s="67">
-        <v>22.8</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="1"/>
-      <c r="I20" s="105" t="s">
-        <v>480</v>
-      </c>
-      <c r="J20" s="1">
-        <f>(J13+J12)/2</f>
-        <v>55</v>
-      </c>
-      <c r="K20" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="L20" s="3"/>
-      <c r="M20" s="1"/>
-      <c r="O20" s="132" t="s">
-        <v>391</v>
-      </c>
-      <c r="P20" s="132"/>
-      <c r="Q20" s="132"/>
-      <c r="R20" s="132"/>
-      <c r="S20">
-        <f ca="1">S17+S18</f>
-        <v>4878.4624867236662</v>
-      </c>
-      <c r="T20" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B21" s="109" t="s">
-        <v>428</v>
-      </c>
-      <c r="C21" s="110"/>
-      <c r="D21" s="110"/>
-      <c r="E21" s="67">
-        <v>11</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="1"/>
-      <c r="I21" s="105" t="s">
-        <v>328</v>
-      </c>
-      <c r="J21" s="1">
-        <f>(J13-J12)/2-2*J16</f>
-        <v>2</v>
-      </c>
-      <c r="K21" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="L21" s="3"/>
-      <c r="O21" s="132" t="s">
-        <v>393</v>
-      </c>
-      <c r="P21" s="132"/>
-      <c r="Q21" s="132"/>
-      <c r="R21" s="132"/>
-      <c r="S21">
-        <f ca="1">SQRT(S19*S19+S20*S20)</f>
-        <v>5614.4669788689807</v>
-      </c>
-      <c r="T21" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B22" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1"/>
-      <c r="I22" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="J22" s="1" t="b">
-        <f ca="1">C1/J18*1000&lt;J17</f>
-        <v>1</v>
-      </c>
-      <c r="K22" s="1"/>
-      <c r="L22" s="3"/>
-      <c r="O22" s="132" t="s">
-        <v>394</v>
-      </c>
-      <c r="P22" s="132"/>
-      <c r="Q22" s="132"/>
-      <c r="R22" s="132"/>
-      <c r="S22" s="132"/>
-      <c r="T22" s="132"/>
-    </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B23">
-        <v>0.21</v>
-      </c>
-      <c r="C23" s="1">
-        <v>1</v>
-      </c>
-      <c r="D23" s="1">
-        <v>3.13</v>
-      </c>
-      <c r="E23" s="1">
-        <v>3.28</v>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="I23" s="106" t="s">
-        <v>483</v>
-      </c>
-      <c r="J23" s="1" t="b">
-        <f ca="1">2*C1*J19/J20/J15/J21/J24&lt;J25</f>
-        <v>1</v>
-      </c>
-      <c r="K23" s="1"/>
-      <c r="L23" s="3"/>
-      <c r="O23" s="132" t="s">
-        <v>386</v>
-      </c>
-      <c r="P23" s="132"/>
-      <c r="Q23" s="132"/>
-      <c r="R23" s="132"/>
-      <c r="S23">
-        <f ca="1">$E$26*S10/(S10+S11)</f>
-        <v>2121.0706464015943</v>
-      </c>
-      <c r="T23" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="3"/>
-      <c r="I24" s="106" t="s">
-        <v>326</v>
-      </c>
-      <c r="J24" s="1">
-        <v>40</v>
-      </c>
-      <c r="K24" s="1"/>
-      <c r="L24" s="3"/>
-      <c r="O24" s="132" t="s">
-        <v>387</v>
-      </c>
-      <c r="P24" s="132"/>
-      <c r="Q24" s="132"/>
-      <c r="R24" s="132"/>
-      <c r="S24">
-        <f ca="1">S6*(S10+S11+S12)/(S10+S11)</f>
-        <v>1579.031408307985</v>
-      </c>
-      <c r="T24" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="5"/>
-      <c r="I25" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="J25" s="1">
-        <f>0.4*240</f>
-        <v>96</v>
-      </c>
-      <c r="K25" s="1"/>
-      <c r="L25" s="3"/>
-      <c r="O25" s="132" t="s">
-        <v>388</v>
-      </c>
-      <c r="P25" s="132"/>
-      <c r="Q25" s="132"/>
-      <c r="R25" s="132"/>
-      <c r="S25">
-        <f ca="1">$E$28*S10/(S10+S11)</f>
-        <v>4878.4624867236662</v>
-      </c>
-      <c r="T25" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B26" s="108" t="s">
-        <v>486</v>
-      </c>
-      <c r="C26" s="108"/>
-      <c r="D26" s="108"/>
-      <c r="E26">
-        <f ca="1">2*1000*C1/C4</f>
-        <v>4242.1412928031887</v>
-      </c>
-      <c r="F26" t="s">
-        <v>152</v>
-      </c>
-      <c r="I26" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="J26" s="4" t="b">
-        <f ca="1">AND(J22,J23)</f>
-        <v>1</v>
-      </c>
-      <c r="K26" s="4"/>
-      <c r="L26" s="5"/>
-      <c r="O26" s="132" t="s">
-        <v>389</v>
-      </c>
-      <c r="P26" s="132"/>
-      <c r="Q26" s="132"/>
-      <c r="R26" s="132"/>
-      <c r="S26">
-        <f>S8*(S10+S11+S12)/(S10+S11)</f>
-        <v>0</v>
-      </c>
-      <c r="T26" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B27" s="132" t="s">
-        <v>487</v>
-      </c>
-      <c r="C27" s="132"/>
-      <c r="D27" s="132"/>
-      <c r="E27" s="52">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="F27" t="s">
-        <v>57</v>
-      </c>
-      <c r="O27" s="132" t="s">
-        <v>392</v>
-      </c>
-      <c r="P27" s="132"/>
-      <c r="Q27" s="132"/>
-      <c r="R27" s="132"/>
-      <c r="S27">
-        <f ca="1">S23+S24</f>
-        <v>3700.1020547095795</v>
-      </c>
-      <c r="T27" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B28" s="132" t="s">
-        <v>150</v>
-      </c>
-      <c r="C28" s="132"/>
-      <c r="D28" s="132"/>
-      <c r="E28">
-        <f ca="1">E26*E27</f>
-        <v>9756.9249734473324</v>
-      </c>
-      <c r="F28" t="s">
-        <v>152</v>
-      </c>
-      <c r="O28" s="132" t="s">
-        <v>391</v>
-      </c>
-      <c r="P28" s="132"/>
-      <c r="Q28" s="132"/>
-      <c r="R28" s="132"/>
-      <c r="S28">
-        <f ca="1">S25+S26</f>
-        <v>4878.4624867236662</v>
-      </c>
-      <c r="T28" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="O29" s="132" t="s">
-        <v>393</v>
-      </c>
-      <c r="P29" s="132"/>
-      <c r="Q29" s="132"/>
-      <c r="R29" s="132"/>
-      <c r="S29">
-        <f ca="1">SQRT(S27*S27+S28*S28)</f>
-        <v>6122.9201733842738</v>
-      </c>
-      <c r="T29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="H31" s="132" t="s">
-        <v>403</v>
-      </c>
-      <c r="I31" s="132"/>
-      <c r="J31" s="132"/>
-      <c r="K31" s="132"/>
-      <c r="L31">
-        <f>Электродвигатель!$E$5</f>
-        <v>10000</v>
-      </c>
-      <c r="O31" s="132" t="s">
-        <v>399</v>
-      </c>
-      <c r="P31" s="132"/>
-      <c r="Q31" s="132"/>
-      <c r="R31" s="132"/>
-      <c r="S31">
-        <f ca="1">MAX(S29,S21)</f>
-        <v>6122.9201733842738</v>
-      </c>
-      <c r="T31" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="H32" s="132" t="s">
-        <v>396</v>
-      </c>
-      <c r="I32" s="132"/>
-      <c r="J32" s="132"/>
-      <c r="K32" s="132"/>
-      <c r="L32">
-        <f>Электродвигатель!$E$6</f>
-        <v>0.9</v>
-      </c>
-      <c r="O32" s="132" t="s">
-        <v>435</v>
-      </c>
-      <c r="P32" s="132"/>
-      <c r="Q32" s="132"/>
-      <c r="R32" s="132"/>
-      <c r="S32">
-        <f>Y6</f>
-        <v>0</v>
-      </c>
-      <c r="T32" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="33" spans="8:20" x14ac:dyDescent="0.3">
-      <c r="H33" s="132" t="s">
-        <v>397</v>
-      </c>
-      <c r="I33" s="132"/>
-      <c r="J33" s="132"/>
-      <c r="K33" s="132"/>
-      <c r="L33" s="97">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="8:20" x14ac:dyDescent="0.3">
-      <c r="H34" s="132" t="s">
-        <v>401</v>
-      </c>
-      <c r="I34" s="132"/>
-      <c r="J34" s="132"/>
-      <c r="K34" s="132"/>
-      <c r="L34" s="97">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="8:20" x14ac:dyDescent="0.3">
-      <c r="H35" s="132" t="s">
-        <v>410</v>
-      </c>
-      <c r="I35" s="132"/>
-      <c r="J35" s="132"/>
-      <c r="K35" s="132"/>
-      <c r="L35" s="97">
-        <v>0</v>
-      </c>
-      <c r="O35" s="132" t="s">
-        <v>395</v>
-      </c>
-      <c r="P35" s="132"/>
-      <c r="Q35" s="132"/>
-      <c r="R35" s="132"/>
-      <c r="S35" s="132"/>
-    </row>
-    <row r="36" spans="8:20" x14ac:dyDescent="0.3">
-      <c r="H36" s="132" t="s">
-        <v>434</v>
-      </c>
-      <c r="I36" s="132"/>
-      <c r="J36" s="132"/>
-      <c r="K36" s="132"/>
-      <c r="L36" s="97">
-        <v>1</v>
-      </c>
-      <c r="O36" s="132" t="s">
-        <v>398</v>
-      </c>
-      <c r="P36" s="132"/>
-      <c r="Q36" s="132"/>
-      <c r="R36" s="132"/>
-      <c r="S36" s="132"/>
-    </row>
-    <row r="37" spans="8:20" x14ac:dyDescent="0.3">
-      <c r="H37" s="132" t="s">
-        <v>432</v>
-      </c>
-      <c r="I37" s="132"/>
-      <c r="J37" s="132"/>
-      <c r="K37" s="132"/>
-      <c r="L37" s="52">
-        <v>1.6</v>
-      </c>
-      <c r="O37" s="132" t="s">
-        <v>431</v>
-      </c>
-      <c r="P37" s="132"/>
-      <c r="Q37" s="132"/>
-      <c r="R37" s="132"/>
-      <c r="S37">
-        <f>E21*1000</f>
-        <v>11000</v>
-      </c>
-      <c r="T37" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="38" spans="8:20" x14ac:dyDescent="0.3">
-      <c r="H38" s="132" t="s">
-        <v>424</v>
-      </c>
-      <c r="I38" s="132"/>
-      <c r="J38" s="132"/>
-      <c r="K38" s="132"/>
-      <c r="L38" s="52">
-        <v>1</v>
-      </c>
-      <c r="O38" s="132" t="s">
-        <v>400</v>
-      </c>
-      <c r="P38" s="132"/>
-      <c r="Q38" s="132"/>
-      <c r="R38" s="132"/>
-      <c r="S38">
-        <f ca="1">(S31*$L$34*$L$36+S32*$L$35)*$L$37*$L$38*$L$42</f>
-        <v>6171.9035347713479</v>
-      </c>
-      <c r="T38" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="39" spans="8:20" x14ac:dyDescent="0.3">
-      <c r="H39" s="132" t="s">
-        <v>433</v>
-      </c>
-      <c r="I39" s="132"/>
-      <c r="J39" s="132"/>
-      <c r="K39" s="132"/>
-      <c r="L39" s="97">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="8:20" x14ac:dyDescent="0.3">
-      <c r="H40" s="132" t="s">
-        <v>412</v>
-      </c>
-      <c r="I40" s="132"/>
-      <c r="J40" s="132"/>
-      <c r="K40" s="132"/>
-      <c r="L40">
-        <f>Корпус!E30</f>
-        <v>22</v>
-      </c>
-      <c r="O40" s="132" t="s">
-        <v>402</v>
-      </c>
-      <c r="P40" s="132"/>
-      <c r="Q40" s="132"/>
-      <c r="R40" s="132"/>
-      <c r="S40" s="132"/>
-    </row>
-    <row r="41" spans="8:20" x14ac:dyDescent="0.3">
-      <c r="H41" s="132" t="s">
-        <v>422</v>
-      </c>
-      <c r="I41" s="132"/>
-      <c r="J41" s="132"/>
-      <c r="K41" s="132"/>
-      <c r="L41">
-        <f>Электродвигатель!$E$7</f>
-        <v>3</v>
-      </c>
-      <c r="O41" s="132" t="s">
-        <v>430</v>
-      </c>
-      <c r="P41" s="132"/>
-      <c r="Q41" s="132"/>
-      <c r="R41" s="132"/>
-      <c r="S41" s="88">
-        <f>E20*1000</f>
-        <v>22800</v>
-      </c>
-      <c r="T41" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="42" spans="8:20" x14ac:dyDescent="0.3">
-      <c r="H42" s="132" t="s">
-        <v>421</v>
-      </c>
-      <c r="I42" s="132"/>
-      <c r="J42" s="132"/>
-      <c r="K42" s="132"/>
-      <c r="L42" s="52">
-        <v>0.63</v>
-      </c>
-      <c r="O42" s="132" t="s">
-        <v>405</v>
-      </c>
-      <c r="P42" s="132"/>
-      <c r="Q42" s="132"/>
-      <c r="R42" s="132"/>
-      <c r="S42" s="132" t="b">
-        <f ca="1">S31&lt;(S41/2)</f>
-        <v>1</v>
-      </c>
-      <c r="T42" s="132"/>
-    </row>
-    <row r="43" spans="8:20" x14ac:dyDescent="0.3">
-      <c r="O43" s="132" t="s">
-        <v>406</v>
-      </c>
-      <c r="P43" s="132"/>
-      <c r="Q43" s="132"/>
-      <c r="R43" s="132"/>
-      <c r="S43" s="132" t="b">
-        <f ca="1">S31&gt;S42*0.01</f>
-        <v>1</v>
-      </c>
-      <c r="T43" s="132"/>
-    </row>
-    <row r="45" spans="8:20" x14ac:dyDescent="0.3">
-      <c r="O45" s="132" t="s">
-        <v>411</v>
-      </c>
-      <c r="P45" s="132"/>
-      <c r="Q45" s="132"/>
-      <c r="R45" s="132"/>
-      <c r="S45">
-        <f ca="1">(E18+E16)/2</f>
-        <v>67.5</v>
-      </c>
-      <c r="T45" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="46" spans="8:20" x14ac:dyDescent="0.3">
-      <c r="O46" s="132" t="s">
-        <v>413</v>
-      </c>
-      <c r="P46" s="132"/>
-      <c r="Q46" s="132"/>
-      <c r="R46" s="132"/>
-      <c r="S46">
-        <f ca="1">IF(S4&gt;1000,4500*S4^(-0.5)*S45^(-0.5),45000*S4^(-0.83)*S45^(-0.5))</f>
-        <v>43.461056628682243</v>
-      </c>
-      <c r="T46" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="47" spans="8:20" x14ac:dyDescent="0.3">
-      <c r="O47" s="132" t="s">
-        <v>415</v>
-      </c>
-      <c r="P47" s="132"/>
-      <c r="Q47" s="132"/>
-      <c r="R47" s="132"/>
-      <c r="S47">
-        <f ca="1">MAX(MIN(4,$L$40/S46),0.1)</f>
-        <v>0.50620030221448964</v>
-      </c>
-      <c r="T47" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="49" spans="15:21" x14ac:dyDescent="0.3">
-      <c r="O49" s="132" t="s">
-        <v>416</v>
-      </c>
-      <c r="P49" s="132"/>
-      <c r="Q49" s="132"/>
-      <c r="R49" s="132"/>
-      <c r="S49" s="52">
-        <v>0.4</v>
-      </c>
-      <c r="T49" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="50" spans="15:21" x14ac:dyDescent="0.3">
-      <c r="O50" s="132" t="s">
-        <v>414</v>
-      </c>
-      <c r="P50" s="132"/>
-      <c r="Q50" s="132"/>
-      <c r="R50" s="132"/>
-      <c r="S50" s="97">
-        <f>S41/22</f>
-        <v>1036.3636363636363</v>
-      </c>
-      <c r="T50" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="52" spans="15:21" x14ac:dyDescent="0.3">
-      <c r="O52" t="s">
-        <v>193</v>
-      </c>
-      <c r="P52" t="s">
-        <v>327</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>417</v>
-      </c>
-      <c r="R52" t="s">
-        <v>423</v>
-      </c>
-      <c r="S52" t="s">
-        <v>418</v>
-      </c>
-      <c r="T52" t="s">
-        <v>420</v>
-      </c>
-      <c r="U52" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="53" spans="15:21" x14ac:dyDescent="0.3">
-      <c r="O53" s="97">
-        <v>2.5670999999999999</v>
-      </c>
-      <c r="P53" s="97">
-        <v>1.9986999999999999</v>
-      </c>
-      <c r="Q53" s="97">
-        <v>7.1738999999999997E-2</v>
-      </c>
-      <c r="R53" s="97">
-        <f>1/3</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="S53" s="97">
-        <v>0.83</v>
-      </c>
-      <c r="T53" s="97">
-        <v>1</v>
-      </c>
-      <c r="U53" s="97">
-        <v>9.3000000000000007</v>
-      </c>
-    </row>
-    <row r="55" spans="15:21" x14ac:dyDescent="0.3">
-      <c r="O55" s="132" t="s">
-        <v>407</v>
-      </c>
-      <c r="P55" s="132"/>
-      <c r="Q55" s="132"/>
-      <c r="R55" s="132"/>
-      <c r="S55">
-        <f ca="1">MIN(0.3*(1-(O53-P53/S47^Q53)^S53*(S49*S50/T53/S38)^R53)^(-U53),50)</f>
-        <v>2.904029756489654</v>
-      </c>
-      <c r="T55" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="56" spans="15:21" x14ac:dyDescent="0.3">
-      <c r="O56" s="132" t="s">
-        <v>137</v>
-      </c>
-      <c r="P56" s="132"/>
-      <c r="Q56" s="132"/>
-      <c r="R56" s="132"/>
-      <c r="S56" s="132">
-        <f ca="1">$L$39*S55*(S41/S38)^$L$33*10^6/60/S4</f>
-        <v>7189.8834047445753</v>
-      </c>
-      <c r="T56" s="132"/>
-      <c r="U56" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="57" spans="15:21" x14ac:dyDescent="0.3">
-      <c r="O57" s="132" t="s">
-        <v>409</v>
-      </c>
-      <c r="P57" s="132"/>
-      <c r="Q57" s="132"/>
-      <c r="R57" s="132"/>
-      <c r="S57" s="132" t="b">
-        <f ca="1">S56&gt;$L$31</f>
-        <v>0</v>
-      </c>
-      <c r="T57" s="132"/>
-    </row>
-    <row r="58" spans="15:21" x14ac:dyDescent="0.3">
-      <c r="O58" s="132" t="s">
-        <v>164</v>
-      </c>
-      <c r="P58" s="132"/>
-      <c r="Q58" s="132"/>
-      <c r="R58" s="132"/>
-      <c r="S58" s="166" t="b">
-        <f ca="1">AND(S42,S43,S57)</f>
-        <v>0</v>
-      </c>
-      <c r="T58" s="166"/>
-    </row>
-  </sheetData>
-  <mergeCells count="82">
-    <mergeCell ref="H41:K41"/>
-    <mergeCell ref="H42:K42"/>
-    <mergeCell ref="H36:K36"/>
-    <mergeCell ref="H37:K37"/>
-    <mergeCell ref="H38:K38"/>
-    <mergeCell ref="H39:K39"/>
-    <mergeCell ref="H40:K40"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="O35:S35"/>
-    <mergeCell ref="H31:K31"/>
-    <mergeCell ref="H32:K32"/>
-    <mergeCell ref="H33:K33"/>
-    <mergeCell ref="H34:K34"/>
-    <mergeCell ref="H35:K35"/>
-    <mergeCell ref="O56:R56"/>
-    <mergeCell ref="S56:T56"/>
-    <mergeCell ref="O57:R57"/>
-    <mergeCell ref="S57:T57"/>
-    <mergeCell ref="O58:R58"/>
-    <mergeCell ref="S58:T58"/>
-    <mergeCell ref="O46:R46"/>
-    <mergeCell ref="O47:R47"/>
-    <mergeCell ref="O49:R49"/>
-    <mergeCell ref="O50:R50"/>
-    <mergeCell ref="O55:R55"/>
-    <mergeCell ref="O42:R42"/>
-    <mergeCell ref="S42:T42"/>
-    <mergeCell ref="O43:R43"/>
-    <mergeCell ref="S43:T43"/>
-    <mergeCell ref="O45:R45"/>
-    <mergeCell ref="O36:S36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="O40:S40"/>
-    <mergeCell ref="O41:R41"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O23:R23"/>
-    <mergeCell ref="O24:R24"/>
-    <mergeCell ref="O25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O18:R18"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="O20:R20"/>
-    <mergeCell ref="O21:R21"/>
-    <mergeCell ref="O22:T22"/>
-    <mergeCell ref="O13:T13"/>
-    <mergeCell ref="O14:T14"/>
-    <mergeCell ref="O15:R15"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="O17:R17"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="O9:T9"/>
-    <mergeCell ref="O10:R10"/>
-    <mergeCell ref="O11:R11"/>
-    <mergeCell ref="O12:R12"/>
-    <mergeCell ref="O3:T3"/>
-    <mergeCell ref="O4:R4"/>
-    <mergeCell ref="O5:R5"/>
-    <mergeCell ref="O6:R6"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B16:D16"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{490D1B27-1B6E-4434-A576-709F124EC6EE}">
-  <dimension ref="A1:T57"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="26" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="132" t="s">
         <v>248</v>
       </c>
@@ -14455,7 +14156,7 @@
       <c r="E1" s="132"/>
       <c r="F1" s="132"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="132" t="s">
         <v>165</v>
       </c>
@@ -14485,7 +14186,7 @@
       <c r="R2" s="132"/>
       <c r="S2" s="132"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="132" t="s">
         <v>70</v>
       </c>
@@ -14525,7 +14226,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="132" t="s">
         <v>176</v>
       </c>
@@ -14569,7 +14270,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="132" t="s">
         <v>384</v>
       </c>
@@ -14602,14 +14303,14 @@
       <c r="P5" s="132"/>
       <c r="Q5" s="132"/>
       <c r="R5">
-        <f ca="1">R4*SQRT(R3)</f>
-        <v>935.14063166464132</v>
+        <f>-U7*K3</f>
+        <v>-2822.3999999999996</v>
       </c>
       <c r="S5" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="132" t="s">
         <v>176</v>
       </c>
@@ -14629,7 +14330,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="132" t="s">
         <v>380</v>
       </c>
@@ -14657,8 +14358,11 @@
       <c r="S7" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U7">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="132" t="s">
         <v>376</v>
       </c>
@@ -14676,7 +14380,7 @@
       <c r="R8" s="132"/>
       <c r="S8" s="132"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="132" t="s">
         <v>377</v>
       </c>
@@ -14702,7 +14406,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="132" t="s">
         <v>378</v>
       </c>
@@ -14728,7 +14432,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="132" t="s">
         <v>379</v>
       </c>
@@ -14754,7 +14458,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="N12" s="132"/>
       <c r="O12" s="132"/>
       <c r="P12" s="132"/>
@@ -14762,7 +14466,7 @@
       <c r="R12" s="132"/>
       <c r="S12" s="132"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="132" t="s">
         <v>390</v>
       </c>
@@ -14780,7 +14484,7 @@
       <c r="R13" s="132"/>
       <c r="S13" s="132"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="132" t="s">
         <v>386</v>
       </c>
@@ -14808,7 +14512,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="132" t="s">
         <v>387</v>
       </c>
@@ -14829,14 +14533,14 @@
       <c r="P15" s="132"/>
       <c r="Q15" s="132"/>
       <c r="R15">
-        <f ca="1">R5*R11/(R9+R10)</f>
-        <v>667.9575940461724</v>
+        <f>R5*R11/(R9+R10)</f>
+        <v>-2015.9999999999998</v>
       </c>
       <c r="S15" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="132" t="s">
         <v>388</v>
       </c>
@@ -14894,14 +14598,14 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" s="132" t="s">
-        <v>392</v>
+        <v>504</v>
       </c>
       <c r="B18" s="132"/>
       <c r="C18" s="132"/>
       <c r="D18" s="132"/>
       <c r="E18">
-        <f>E14+E15</f>
-        <v>1360.5652403047661</v>
+        <f>SQRT(E14*E14+E16*E16)</f>
+        <v>1072.7315600838824</v>
       </c>
       <c r="F18" t="s">
         <v>152</v>
@@ -14913,8 +14617,8 @@
       <c r="P18" s="132"/>
       <c r="Q18" s="132"/>
       <c r="R18">
-        <f ca="1">R14+R15</f>
-        <v>1675.9575940461723</v>
+        <f>R14+R15</f>
+        <v>-1007.9999999999998</v>
       </c>
       <c r="S18" t="s">
         <v>152</v>
@@ -14922,14 +14626,14 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="132" t="s">
-        <v>391</v>
+        <v>505</v>
       </c>
       <c r="B19" s="132"/>
       <c r="C19" s="132"/>
       <c r="D19" s="132"/>
       <c r="E19">
-        <f>E16+E17</f>
-        <v>367</v>
+        <f>SQRT(E15*E15+E17*E17)</f>
+        <v>352.56524030476618</v>
       </c>
       <c r="F19" t="s">
         <v>152</v>
@@ -14957,7 +14661,7 @@
       <c r="D20" s="132"/>
       <c r="E20">
         <f>SQRT(E18*E18+E19*E19)</f>
-        <v>1409.1936606178606</v>
+        <v>1129.183443321393</v>
       </c>
       <c r="F20" t="s">
         <v>152</v>
@@ -14969,8 +14673,8 @@
       <c r="P20" s="132"/>
       <c r="Q20" s="132"/>
       <c r="R20">
-        <f ca="1">SQRT(R18*R18+R19*R19)</f>
-        <v>1715.6697983706056</v>
+        <f>SQRT(R18*R18+R19*R19)</f>
+        <v>1072.7315600838822</v>
       </c>
       <c r="S20" t="s">
         <v>152</v>
@@ -15043,8 +14747,8 @@
       <c r="P23" s="132"/>
       <c r="Q23" s="132"/>
       <c r="R23">
-        <f ca="1">R5*(R9+R10+R11)/(R9+R10)</f>
-        <v>1603.0982257108137</v>
+        <f>R5*(R9+R10+R11)/(R9+R10)</f>
+        <v>-4838.3999999999996</v>
       </c>
       <c r="S23" t="s">
         <v>152</v>
@@ -15108,14 +14812,14 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" s="132" t="s">
-        <v>392</v>
+        <v>504</v>
       </c>
       <c r="B26" s="132"/>
       <c r="C26" s="132"/>
       <c r="D26" s="132"/>
       <c r="E26">
-        <f>E22+E23</f>
-        <v>2058.7142310072732</v>
+        <f>SQRT(E22*E22+E24*E24)</f>
+        <v>1072.7315600838824</v>
       </c>
       <c r="F26" t="s">
         <v>152</v>
@@ -15127,8 +14831,8 @@
       <c r="P26" s="132"/>
       <c r="Q26" s="132"/>
       <c r="R26">
-        <f ca="1">R22+R23</f>
-        <v>2611.0982257108135</v>
+        <f>R22+R23</f>
+        <v>-3830.3999999999996</v>
       </c>
       <c r="S26" t="s">
         <v>152</v>
@@ -15136,14 +14840,14 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="132" t="s">
-        <v>391</v>
+        <v>505</v>
       </c>
       <c r="B27" s="132"/>
       <c r="C27" s="132"/>
       <c r="D27" s="132"/>
       <c r="E27">
-        <f>E24+E25</f>
-        <v>367</v>
+        <f>SQRT(E23*E23+E25*E25)</f>
+        <v>1050.7142310072734</v>
       </c>
       <c r="F27" t="s">
         <v>152</v>
@@ -15171,7 +14875,7 @@
       <c r="D28" s="132"/>
       <c r="E28">
         <f>SQRT(E26*E26+E27*E27)</f>
-        <v>2091.1703146687664</v>
+        <v>1501.5836291200055</v>
       </c>
       <c r="F28" t="s">
         <v>152</v>
@@ -15183,8 +14887,8 @@
       <c r="P28" s="132"/>
       <c r="Q28" s="132"/>
       <c r="R28">
-        <f ca="1">SQRT(R26*R26+R27*R27)</f>
-        <v>2636.7637255374548</v>
+        <f>SQRT(R26*R26+R27*R27)</f>
+        <v>3847.941418472999</v>
       </c>
       <c r="S28" t="s">
         <v>152</v>
@@ -15199,7 +14903,7 @@
       <c r="D30" s="132"/>
       <c r="E30">
         <f>MAX(E28,E20)</f>
-        <v>2091.1703146687664</v>
+        <v>1501.5836291200055</v>
       </c>
       <c r="F30" t="s">
         <v>152</v>
@@ -15211,8 +14915,8 @@
       <c r="P30" s="132"/>
       <c r="Q30" s="132"/>
       <c r="R30">
-        <f ca="1">MAX(R28,R20)</f>
-        <v>2636.7637255374548</v>
+        <f>MAX(R28,R20)</f>
+        <v>3847.941418472999</v>
       </c>
       <c r="S30" t="s">
         <v>152</v>
@@ -15376,7 +15080,7 @@
       <c r="D37" s="132"/>
       <c r="E37">
         <f>(E30*$L$34*$L$36+E31*$L$35)*$L$37*$L$38*$L$42</f>
-        <v>2107.8996771861166</v>
+        <v>1513.5962981529658</v>
       </c>
       <c r="F37" t="s">
         <v>152</v>
@@ -15397,8 +15101,8 @@
       <c r="P37" s="132"/>
       <c r="Q37" s="132"/>
       <c r="R37">
-        <f ca="1">(R30*$L$34*$L$36+R31*$L$35)*$L$37*$L$38*$L$42</f>
-        <v>2657.8578353417543</v>
+        <f>(R30*$L$34*$L$36+R31*$L$35)*$L$37*$L$38*$L$42</f>
+        <v>3878.724949820783</v>
       </c>
       <c r="S37" t="s">
         <v>152</v>
@@ -15795,7 +15499,7 @@
       <c r="Q54" s="132"/>
       <c r="R54">
         <f ca="1">MIN(0.3*(1-(N52-O52/R46^P52)^R52*(R48*R49/S52/R37)^Q52)^(-T52),50)</f>
-        <v>13.328603353369376</v>
+        <v>7.7775887136434854</v>
       </c>
       <c r="S54" t="s">
         <v>57</v>
@@ -15810,7 +15514,7 @@
       <c r="D55" s="132"/>
       <c r="E55" s="132">
         <f>$L$39*E54*(E40/E37)^$L$33*10^6/60/E3</f>
-        <v>2024679.962378395</v>
+        <v>5468598.3380485382</v>
       </c>
       <c r="F55" s="132"/>
       <c r="G55" t="s">
@@ -15824,7 +15528,7 @@
       <c r="Q55" s="132"/>
       <c r="R55" s="132">
         <f ca="1">$L$39*R54*(R40/R37)^$L$33*10^6/60/R3</f>
-        <v>1462667.643883571</v>
+        <v>274621.33564960217</v>
       </c>
       <c r="S55" s="132"/>
       <c r="T55" t="s">
@@ -16005,4 +15709,490 @@
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B080B891-BABE-48BC-B741-A9DC893B6424}">
+  <dimension ref="A2:W33"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="12" width="6.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="132" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2">
+        <f>Передача!$D$46</f>
+        <v>180</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="132" t="s">
+        <v>195</v>
+      </c>
+      <c r="B3" s="132"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="132"/>
+      <c r="E3">
+        <f>Передача!$D$55</f>
+        <v>37.75</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="132" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4" s="132"/>
+      <c r="C4" s="132"/>
+      <c r="D4" s="132"/>
+      <c r="E4">
+        <f>Передача!$D$56</f>
+        <v>62</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="132" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="132"/>
+      <c r="C5" s="132"/>
+      <c r="D5" s="132"/>
+      <c r="E5">
+        <f>Передача!$D$60</f>
+        <v>309.75</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="132" t="s">
+        <v>171</v>
+      </c>
+      <c r="B6" s="132"/>
+      <c r="C6" s="132"/>
+      <c r="D6" s="132"/>
+      <c r="E6">
+        <f>Передача!$D$61</f>
+        <v>57</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="132" t="s">
+        <v>194</v>
+      </c>
+      <c r="B7" s="132"/>
+      <c r="C7" s="132"/>
+      <c r="D7" s="132"/>
+      <c r="E7">
+        <f>E2+E3/2+E5/2</f>
+        <v>353.75</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="132" t="s">
+        <v>193</v>
+      </c>
+      <c r="B8" s="132"/>
+      <c r="C8" s="132"/>
+      <c r="D8" s="132"/>
+      <c r="E8">
+        <f>E7^(1/3)+3</f>
+        <v>10.072378298355165</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="132" t="s">
+        <v>197</v>
+      </c>
+      <c r="B9" s="132"/>
+      <c r="C9" s="132"/>
+      <c r="D9" s="132"/>
+      <c r="E9">
+        <f>E8*3</f>
+        <v>30.217134895065495</v>
+      </c>
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="132"/>
+      <c r="B10" s="132"/>
+      <c r="C10" s="132"/>
+      <c r="D10" s="132"/>
+      <c r="E10" s="88"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="132"/>
+      <c r="B11" s="132"/>
+      <c r="C11" s="132"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="88"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="132" t="s">
+        <v>199</v>
+      </c>
+      <c r="B12" s="132"/>
+      <c r="C12" s="132"/>
+      <c r="D12" s="132"/>
+      <c r="E12" s="132"/>
+      <c r="F12" s="132"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="132" t="s">
+        <v>198</v>
+      </c>
+      <c r="B13" s="132"/>
+      <c r="C13" s="132"/>
+      <c r="D13" s="132"/>
+      <c r="E13">
+        <f>E7+2*E8</f>
+        <v>373.89475659671035</v>
+      </c>
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="132" t="s">
+        <v>158</v>
+      </c>
+      <c r="B14" s="132"/>
+      <c r="C14" s="132"/>
+      <c r="D14" s="132"/>
+      <c r="E14">
+        <f>E4+2*E8</f>
+        <v>82.144756596710323</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="132" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="132"/>
+      <c r="C15" s="132"/>
+      <c r="D15" s="132"/>
+      <c r="E15">
+        <f>E5+E8+E9</f>
+        <v>350.03951319342065</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A17" s="132" t="s">
+        <v>436</v>
+      </c>
+      <c r="B17" s="132"/>
+      <c r="C17" s="132"/>
+      <c r="D17" s="132"/>
+      <c r="E17">
+        <f>(E13*2+E14+E15)/3/1000</f>
+        <v>0.39332459432785055</v>
+      </c>
+      <c r="F17" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A18" s="132" t="s">
+        <v>438</v>
+      </c>
+      <c r="B18" s="132"/>
+      <c r="C18" s="132"/>
+      <c r="D18" s="132"/>
+      <c r="E18">
+        <f ca="1">Электродвигатель!P55</f>
+        <v>349.79520039605768</v>
+      </c>
+      <c r="F18" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A19" s="132" t="s">
+        <v>439</v>
+      </c>
+      <c r="B19" s="132"/>
+      <c r="C19" s="132"/>
+      <c r="D19" s="132"/>
+      <c r="E19">
+        <f ca="1">MAX(1.3*E18^0.25,6)</f>
+        <v>6</v>
+      </c>
+      <c r="F19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A20" s="132" t="s">
+        <v>440</v>
+      </c>
+      <c r="B20" s="132"/>
+      <c r="C20" s="132"/>
+      <c r="D20" s="132"/>
+      <c r="E20">
+        <f ca="1">ROUNDUP( E19*0.7,1)</f>
+        <v>4.2</v>
+      </c>
+      <c r="F20" t="s">
+        <v>16</v>
+      </c>
+      <c r="R20" s="1"/>
+      <c r="S20" s="90"/>
+      <c r="T20" s="48"/>
+      <c r="U20" s="48"/>
+      <c r="V20" s="16"/>
+      <c r="W20" s="16"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A21" s="132" t="s">
+        <v>342</v>
+      </c>
+      <c r="B21" s="132"/>
+      <c r="C21" s="132"/>
+      <c r="D21" s="132"/>
+      <c r="E21" s="132"/>
+      <c r="F21" s="132"/>
+      <c r="G21" t="s">
+        <v>100</v>
+      </c>
+      <c r="R21" s="66"/>
+      <c r="S21" s="66"/>
+      <c r="T21" s="16"/>
+      <c r="U21" s="16"/>
+      <c r="V21" s="16"/>
+      <c r="W21" s="16"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A22" s="132" t="s">
+        <v>441</v>
+      </c>
+      <c r="B22" s="132"/>
+      <c r="C22" s="132"/>
+      <c r="D22" s="132"/>
+      <c r="E22">
+        <f ca="1">Вал!$S$21*1.25+10</f>
+        <v>122.5</v>
+      </c>
+      <c r="F22" t="s">
+        <v>16</v>
+      </c>
+      <c r="R22" s="66"/>
+      <c r="S22" s="66"/>
+      <c r="T22" s="16"/>
+      <c r="U22" s="16"/>
+      <c r="V22" s="62"/>
+      <c r="W22" s="62"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A23" s="132" t="s">
+        <v>442</v>
+      </c>
+      <c r="B23" s="132"/>
+      <c r="C23" s="132"/>
+      <c r="D23" s="132"/>
+      <c r="E23">
+        <f>Вал!$K$21*1.25+10</f>
+        <v>110</v>
+      </c>
+      <c r="F23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A24" s="132" t="s">
+        <v>443</v>
+      </c>
+      <c r="B24" s="132"/>
+      <c r="C24" s="132"/>
+      <c r="D24" s="132"/>
+      <c r="E24">
+        <f ca="1">MAX(1.25*E18^(1/3),10)</f>
+        <v>10</v>
+      </c>
+      <c r="F24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A26" s="132" t="s">
+        <v>315</v>
+      </c>
+      <c r="B26" s="132"/>
+      <c r="C26" s="132"/>
+      <c r="D26" s="132"/>
+      <c r="E26" s="132"/>
+      <c r="F26" s="132"/>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A27" s="132" t="s">
+        <v>312</v>
+      </c>
+      <c r="B27" s="132"/>
+      <c r="C27" s="132"/>
+      <c r="D27" s="132"/>
+      <c r="E27">
+        <f>Вал!$K$4*PI()/30</f>
+        <v>150.79644737231007</v>
+      </c>
+      <c r="F27" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A28" s="132" t="s">
+        <v>313</v>
+      </c>
+      <c r="B28" s="132"/>
+      <c r="C28" s="132"/>
+      <c r="D28" s="132"/>
+      <c r="E28">
+        <f>Корпус!$E$27*MAX(Вал!$K$22,Вал!$K$7)/1000</f>
+        <v>7.3890259212431939</v>
+      </c>
+      <c r="F28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A29" s="132" t="s">
+        <v>316</v>
+      </c>
+      <c r="B29" s="132"/>
+      <c r="C29" s="132"/>
+      <c r="D29" s="132"/>
+      <c r="E29" s="52">
+        <v>504</v>
+      </c>
+      <c r="F29" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A30" s="132" t="s">
+        <v>318</v>
+      </c>
+      <c r="B30" s="132"/>
+      <c r="C30" s="132"/>
+      <c r="D30" s="132"/>
+      <c r="E30" s="52">
+        <v>22</v>
+      </c>
+      <c r="F30" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A31" s="132" t="s">
+        <v>319</v>
+      </c>
+      <c r="B31" s="132"/>
+      <c r="C31" s="132"/>
+      <c r="D31" s="132"/>
+      <c r="E31" t="s">
+        <v>320</v>
+      </c>
+      <c r="F31" s="101" t="s">
+        <v>456</v>
+      </c>
+      <c r="G31" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A32" s="132" t="s">
+        <v>321</v>
+      </c>
+      <c r="B32" s="132"/>
+      <c r="C32" s="132"/>
+      <c r="D32" s="132"/>
+      <c r="E32">
+        <f>MAX(4*Передача!$D$47,10)</f>
+        <v>10</v>
+      </c>
+      <c r="F32">
+        <f>MAX(Передача!$D$58/4,10)</f>
+        <v>79.375</v>
+      </c>
+      <c r="G32" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E33">
+        <f>E32+E9</f>
+        <v>40.217134895065499</v>
+      </c>
+      <c r="F33">
+        <f>F32+E9</f>
+        <v>109.5921348950655</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="30">
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A31:D31"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Расчёт.xlsx
+++ b/Расчёт.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Professional\Downloads\интститут\курсач детмаш\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18854E6C-C0A5-47DB-879F-8CCD44108F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E7910F3-46F4-4980-B254-44E390AE7107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="812" activeTab="9" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="812" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
   </bookViews>
   <sheets>
     <sheet name="Электродвигатель" sheetId="1" r:id="rId1"/>
@@ -6253,7 +6253,7 @@
       <c r="Q10" s="132"/>
       <c r="R10" s="132"/>
       <c r="S10" s="52">
-        <v>101.5</v>
+        <v>111.5</v>
       </c>
       <c r="T10" t="s">
         <v>16</v>
@@ -6292,7 +6292,7 @@
       <c r="Q11" s="132"/>
       <c r="R11" s="132"/>
       <c r="S11" s="52">
-        <v>74.5</v>
+        <v>84.5</v>
       </c>
       <c r="T11" t="s">
         <v>16</v>
@@ -6374,7 +6374,7 @@
       <c r="Q13" s="132"/>
       <c r="R13" s="132"/>
       <c r="S13" s="52">
-        <v>74.5</v>
+        <v>84.5</v>
       </c>
       <c r="T13" t="s">
         <v>16</v>
@@ -6569,7 +6569,7 @@
       <c r="R18" s="132"/>
       <c r="S18">
         <f>S8*($S$10+$S$11+$S$12+$S$13)/($S$11+$S$12+$S$13)</f>
-        <v>3433.2179104477605</v>
+        <v>3465.9533742331282</v>
       </c>
       <c r="T18" t="s">
         <v>152</v>
@@ -6644,7 +6644,7 @@
       <c r="R20" s="132"/>
       <c r="S20">
         <f ca="1">S17+S18</f>
-        <v>-1445.2445762759066</v>
+        <v>-1412.5091124905389</v>
       </c>
       <c r="T20" t="s">
         <v>152</v>
@@ -6682,7 +6682,7 @@
       <c r="R21" s="132"/>
       <c r="S21">
         <f ca="1">SQRT(S19*S19+S20*S20)</f>
-        <v>2566.6461720076263</v>
+        <v>2548.3568588200687</v>
       </c>
       <c r="T21" t="s">
         <v>152</v>
@@ -6831,7 +6831,7 @@
       <c r="R26" s="132"/>
       <c r="S26">
         <f>-S8*($S$10)/($S$11+$S$12+$S$13)</f>
-        <v>-610.81791044776116</v>
+        <v>-643.55337423312881</v>
       </c>
       <c r="T26" t="s">
         <v>152</v>
@@ -6861,7 +6861,7 @@
       <c r="R28" s="132"/>
       <c r="S28">
         <f ca="1">S25+S26</f>
-        <v>-5489.2803971714284</v>
+        <v>-5522.0158609567961</v>
       </c>
       <c r="T28" t="s">
         <v>152</v>
@@ -6876,7 +6876,7 @@
       <c r="R29" s="132"/>
       <c r="S29">
         <f ca="1">SQRT(S27*S27+S28*S28)</f>
-        <v>5884.8228491431237</v>
+        <v>5915.3697987264422</v>
       </c>
       <c r="T29" t="s">
         <v>152</v>
@@ -6901,7 +6901,7 @@
       <c r="R31" s="132"/>
       <c r="S31">
         <f ca="1">MAX(S29,S21)</f>
-        <v>5884.8228491431237</v>
+        <v>5915.3697987264422</v>
       </c>
       <c r="T31" t="s">
         <v>152</v>
@@ -7034,7 +7034,7 @@
       <c r="R38" s="132"/>
       <c r="S38">
         <f ca="1">(S31*$C$23*$L$36+S32*$E$23)*$L$37*$L$38*$L$42</f>
-        <v>5931.9014319362686</v>
+        <v>5962.6927571162541</v>
       </c>
       <c r="T38" t="s">
         <v>152</v>
@@ -7273,7 +7273,7 @@
       <c r="R55" s="132"/>
       <c r="S55">
         <f ca="1">MIN(0.3*(1-(O53-P53/S47^Q53)^S53*(S49*S50/T53/S38)^R53)^(-U53),50)</f>
-        <v>1.0652003303996018</v>
+        <v>1.0627101670075869</v>
       </c>
       <c r="T55" t="s">
         <v>57</v>
@@ -7288,7 +7288,7 @@
       <c r="R56" s="132"/>
       <c r="S56" s="132">
         <f ca="1">$L$39*S55*(S41/S38)^$L$33*10^6/60/S3</f>
-        <v>39464.30213377683</v>
+        <v>38765.237830484068</v>
       </c>
       <c r="T56" s="132"/>
       <c r="U56" t="s">
@@ -7323,17 +7323,10 @@
     </row>
   </sheetData>
   <mergeCells count="81">
-    <mergeCell ref="O7:R7"/>
     <mergeCell ref="O6:R6"/>
     <mergeCell ref="O5:R5"/>
     <mergeCell ref="O4:R4"/>
     <mergeCell ref="H41:K41"/>
-    <mergeCell ref="H42:K42"/>
-    <mergeCell ref="H36:K36"/>
-    <mergeCell ref="H37:K37"/>
-    <mergeCell ref="H38:K38"/>
-    <mergeCell ref="H39:K39"/>
-    <mergeCell ref="H40:K40"/>
     <mergeCell ref="O35:S35"/>
     <mergeCell ref="H31:K31"/>
     <mergeCell ref="H32:K32"/>
@@ -7344,6 +7337,13 @@
     <mergeCell ref="O29:R29"/>
     <mergeCell ref="O31:R31"/>
     <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O36:S36"/>
+    <mergeCell ref="H42:K42"/>
+    <mergeCell ref="H36:K36"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="H38:K38"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="H40:K40"/>
     <mergeCell ref="O56:R56"/>
     <mergeCell ref="S56:T56"/>
     <mergeCell ref="O57:R57"/>
@@ -7361,7 +7361,6 @@
     <mergeCell ref="O43:R43"/>
     <mergeCell ref="S43:T43"/>
     <mergeCell ref="O45:R45"/>
-    <mergeCell ref="O36:S36"/>
     <mergeCell ref="O37:R37"/>
     <mergeCell ref="O38:R38"/>
     <mergeCell ref="O40:S40"/>
@@ -7381,27 +7380,28 @@
     <mergeCell ref="O16:R16"/>
     <mergeCell ref="O17:R17"/>
     <mergeCell ref="O13:R13"/>
+    <mergeCell ref="O2:T2"/>
+    <mergeCell ref="O3:R3"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
     <mergeCell ref="O8:R8"/>
     <mergeCell ref="O9:T9"/>
     <mergeCell ref="O10:R10"/>
     <mergeCell ref="O11:R11"/>
     <mergeCell ref="O12:R12"/>
-    <mergeCell ref="O2:T2"/>
-    <mergeCell ref="O3:R3"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="O7:R7"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="B16:D16"/>
   </mergeCells>
@@ -14452,7 +14452,7 @@
       <c r="P11" s="132"/>
       <c r="Q11" s="132"/>
       <c r="R11" s="52">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="S11" t="s">
         <v>16</v>
@@ -14534,7 +14534,7 @@
       <c r="Q15" s="132"/>
       <c r="R15">
         <f>R5*R11/(R9+R10)</f>
-        <v>-2015.9999999999998</v>
+        <v>-2303.9999999999995</v>
       </c>
       <c r="S15" t="s">
         <v>152</v>
@@ -14618,7 +14618,7 @@
       <c r="Q18" s="132"/>
       <c r="R18">
         <f>R14+R15</f>
-        <v>-1007.9999999999998</v>
+        <v>-1295.9999999999995</v>
       </c>
       <c r="S18" t="s">
         <v>152</v>
@@ -14674,7 +14674,7 @@
       <c r="Q20" s="132"/>
       <c r="R20">
         <f>SQRT(R18*R18+R19*R19)</f>
-        <v>1072.7315600838822</v>
+        <v>1346.9613951409294</v>
       </c>
       <c r="S20" t="s">
         <v>152</v>
@@ -14748,7 +14748,7 @@
       <c r="Q23" s="132"/>
       <c r="R23">
         <f>R5*(R9+R10+R11)/(R9+R10)</f>
-        <v>-4838.3999999999996</v>
+        <v>-5126.3999999999996</v>
       </c>
       <c r="S23" t="s">
         <v>152</v>
@@ -14832,7 +14832,7 @@
       <c r="Q26" s="132"/>
       <c r="R26">
         <f>R22+R23</f>
-        <v>-3830.3999999999996</v>
+        <v>-4118.3999999999996</v>
       </c>
       <c r="S26" t="s">
         <v>152</v>
@@ -14888,7 +14888,7 @@
       <c r="Q28" s="132"/>
       <c r="R28">
         <f>SQRT(R26*R26+R27*R27)</f>
-        <v>3847.941418472999</v>
+        <v>4134.7197680133049</v>
       </c>
       <c r="S28" t="s">
         <v>152</v>
@@ -14916,7 +14916,7 @@
       <c r="Q30" s="132"/>
       <c r="R30">
         <f>MAX(R28,R20)</f>
-        <v>3847.941418472999</v>
+        <v>4134.7197680133049</v>
       </c>
       <c r="S30" t="s">
         <v>152</v>
@@ -15102,7 +15102,7 @@
       <c r="Q37" s="132"/>
       <c r="R37">
         <f>(R30*$L$34*$L$36+R31*$L$35)*$L$37*$L$38*$L$42</f>
-        <v>3878.724949820783</v>
+        <v>4167.797526157412</v>
       </c>
       <c r="S37" t="s">
         <v>152</v>
@@ -15499,7 +15499,7 @@
       <c r="Q54" s="132"/>
       <c r="R54">
         <f ca="1">MIN(0.3*(1-(N52-O52/R46^P52)^R52*(R48*R49/S52/R37)^Q52)^(-T52),50)</f>
-        <v>7.7775887136434854</v>
+        <v>7.0952252074485367</v>
       </c>
       <c r="S54" t="s">
         <v>57</v>
@@ -15528,7 +15528,7 @@
       <c r="Q55" s="132"/>
       <c r="R55" s="132">
         <f ca="1">$L$39*R54*(R40/R37)^$L$33*10^6/60/R3</f>
-        <v>274621.33564960217</v>
+        <v>201930.8159054456</v>
       </c>
       <c r="S55" s="132"/>
       <c r="T55" t="s">

--- a/Расчёт.xlsx
+++ b/Расчёт.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Professional\Downloads\интститут\курсач детмаш\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E7910F3-46F4-4980-B254-44E390AE7107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4141E1CB-450A-45A3-B8F3-6E5DC51ED15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="812" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="812" firstSheet="1" activeTab="13" xr2:uid="{7E097F76-7D13-4899-AD2E-10ADA644057F}"/>
   </bookViews>
   <sheets>
     <sheet name="Электродвигатель" sheetId="1" r:id="rId1"/>
@@ -1118,9 +1118,6 @@
     <t>Длинна суммарная</t>
   </si>
   <si>
-    <t>H7/u8</t>
-  </si>
-  <si>
     <t>Крышка тихоходного вала</t>
   </si>
   <si>
@@ -1665,6 +1662,9 @@
   </si>
   <si>
     <t>Окржная консольная сила</t>
+  </si>
+  <si>
+    <t>H7/x8</t>
   </si>
 </sst>
 </file>
@@ -3839,7 +3839,7 @@
       <c r="Y19" s="108"/>
       <c r="Z19" s="115"/>
       <c r="AC19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="9:29" x14ac:dyDescent="0.3">
@@ -4420,7 +4420,7 @@
         <v>169</v>
       </c>
       <c r="AC32" s="65" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="33" spans="2:31" x14ac:dyDescent="0.3">
@@ -4500,7 +4500,7 @@
         <v>179</v>
       </c>
       <c r="AC34" s="65" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="35" spans="2:31" x14ac:dyDescent="0.3">
@@ -4540,7 +4540,7 @@
         <v>67</v>
       </c>
       <c r="AC35" s="96" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="36" spans="2:31" x14ac:dyDescent="0.3">
@@ -4623,7 +4623,7 @@
     </row>
     <row r="37" spans="2:31" x14ac:dyDescent="0.3">
       <c r="AC37" s="65" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="38" spans="2:31" x14ac:dyDescent="0.3">
@@ -4920,7 +4920,7 @@
         <v>198</v>
       </c>
       <c r="AC42" s="65" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="43" spans="2:31" x14ac:dyDescent="0.3">
@@ -5002,7 +5002,7 @@
         <v>177</v>
       </c>
       <c r="AC43" s="65" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="44" spans="2:31" x14ac:dyDescent="0.3">
@@ -5075,7 +5075,7 @@
         <v>0</v>
       </c>
       <c r="AA44" s="141" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AB44" s="142"/>
       <c r="AC44" s="71" t="s">
@@ -5232,7 +5232,7 @@
         <v>0.75835111197354876</v>
       </c>
       <c r="AC46" s="132" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AD46" s="132"/>
       <c r="AE46" s="132"/>
@@ -5267,7 +5267,7 @@
         <v>57</v>
       </c>
       <c r="AC47" s="71" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="48" spans="2:31" x14ac:dyDescent="0.3">
@@ -5309,7 +5309,7 @@
         <v>298</v>
       </c>
       <c r="AC48" s="71" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="49" spans="2:29" x14ac:dyDescent="0.3">
@@ -5345,7 +5345,7 @@
         <v>300</v>
       </c>
       <c r="AC49" s="71" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="50" spans="2:29" x14ac:dyDescent="0.3">
@@ -5373,7 +5373,7 @@
         <v>300</v>
       </c>
       <c r="AC50" s="71" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="51" spans="2:29" x14ac:dyDescent="0.3">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="M51" s="108"/>
       <c r="N51" s="145" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="O51" s="145"/>
       <c r="P51" s="108" t="s">
@@ -5424,7 +5424,7 @@
         <v>57</v>
       </c>
       <c r="AC51" s="71" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="52" spans="2:29" x14ac:dyDescent="0.3">
@@ -5478,7 +5478,7 @@
         <v>315</v>
       </c>
       <c r="AC52" s="71" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="53" spans="2:29" x14ac:dyDescent="0.3">
@@ -5528,7 +5528,7 @@
         <v>206</v>
       </c>
       <c r="AC53" s="71" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="54" spans="2:29" x14ac:dyDescent="0.3">
@@ -5578,7 +5578,7 @@
         <v>302</v>
       </c>
       <c r="AC54" s="71" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="55" spans="2:29" x14ac:dyDescent="0.3">
@@ -5629,7 +5629,7 @@
         <v>205</v>
       </c>
       <c r="AC55" s="71" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="56" spans="2:29" x14ac:dyDescent="0.3">
@@ -5992,7 +5992,7 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C1">
         <f ca="1">Электродвигатель!P58</f>
@@ -6054,7 +6054,7 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C4">
         <f>Электродвигатель!F53</f>
@@ -6066,7 +6066,7 @@
       <c r="F4" s="16"/>
       <c r="H4" s="16"/>
       <c r="O4" s="110" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="P4" s="110"/>
       <c r="Q4" s="110"/>
@@ -6082,14 +6082,14 @@
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="H5" s="16"/>
       <c r="I5" s="107" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J5" s="108"/>
       <c r="K5" s="108"/>
       <c r="L5" s="115"/>
       <c r="M5" s="1"/>
       <c r="O5" s="132" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="P5" s="132"/>
       <c r="Q5" s="132"/>
@@ -6107,7 +6107,7 @@
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="H6" s="48"/>
       <c r="I6" s="102" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J6" s="16"/>
       <c r="K6" s="1"/>
@@ -6138,14 +6138,14 @@
       <c r="G7" s="1"/>
       <c r="H7" s="48"/>
       <c r="I7" s="7" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="3"/>
       <c r="M7" s="1"/>
       <c r="O7" s="132" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="P7" s="132"/>
       <c r="Q7" s="132"/>
@@ -6170,16 +6170,16 @@
       <c r="G8" s="1"/>
       <c r="H8" s="48"/>
       <c r="I8" s="7" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="1"/>
       <c r="O8" s="132" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="P8" s="132"/>
       <c r="Q8" s="132"/>
@@ -6208,16 +6208,16 @@
       <c r="G9" s="1"/>
       <c r="H9" s="48"/>
       <c r="I9" s="7" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="1"/>
       <c r="O9" s="132" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="P9" s="132"/>
       <c r="Q9" s="132"/>
@@ -6240,14 +6240,14 @@
       </c>
       <c r="G10" s="1"/>
       <c r="I10" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="3"/>
       <c r="M10" s="1"/>
       <c r="O10" s="132" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="P10" s="132"/>
       <c r="Q10" s="132"/>
@@ -6259,7 +6259,7 @@
         <v>16</v>
       </c>
       <c r="U10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
@@ -6277,16 +6277,16 @@
       </c>
       <c r="G11" s="1"/>
       <c r="I11" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L11" s="3"/>
       <c r="M11" s="1"/>
       <c r="O11" s="132" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P11" s="132"/>
       <c r="Q11" s="132"/>
@@ -6298,7 +6298,7 @@
         <v>16</v>
       </c>
       <c r="U11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="G12" s="1"/>
       <c r="I12" s="7" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J12" s="1">
         <v>52</v>
@@ -6327,7 +6327,7 @@
       <c r="L12" s="3"/>
       <c r="M12" s="1"/>
       <c r="O12" s="132" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="P12" s="132"/>
       <c r="Q12" s="132"/>
@@ -6339,7 +6339,7 @@
         <v>16</v>
       </c>
       <c r="U12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
@@ -6368,7 +6368,7 @@
       <c r="L13" s="3"/>
       <c r="M13" s="1"/>
       <c r="O13" s="132" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="P13" s="132"/>
       <c r="Q13" s="132"/>
@@ -6380,7 +6380,7 @@
         <v>16</v>
       </c>
       <c r="U13" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
@@ -6409,7 +6409,7 @@
       <c r="L14" s="3"/>
       <c r="M14" s="1"/>
       <c r="O14" s="132" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="P14" s="132"/>
       <c r="Q14" s="132"/>
@@ -6417,7 +6417,7 @@
       <c r="S14" s="132"/>
       <c r="T14" s="132"/>
       <c r="U14" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="G15" s="1"/>
       <c r="I15" s="7" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="J15" s="25">
         <v>8</v>
@@ -6446,7 +6446,7 @@
       <c r="L15" s="3"/>
       <c r="M15" s="1"/>
       <c r="O15" s="132" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="P15" s="132"/>
       <c r="Q15" s="132"/>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="G16" s="1"/>
       <c r="I16" s="106" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="J16" s="25">
         <v>0.5</v>
@@ -6485,7 +6485,7 @@
       <c r="L16" s="3"/>
       <c r="M16" s="1"/>
       <c r="O16" s="132" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="P16" s="132"/>
       <c r="Q16" s="132"/>
@@ -6508,11 +6508,11 @@
         <v>1309</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G17" s="1"/>
       <c r="I17" s="104" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="J17" s="1">
         <v>25</v>
@@ -6523,7 +6523,7 @@
       <c r="L17" s="3"/>
       <c r="M17" s="1"/>
       <c r="O17" s="132" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
@@ -6550,19 +6550,19 @@
       </c>
       <c r="G18" s="1"/>
       <c r="I18" s="7" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J18" s="1">
         <f>0.2*J12*J12*J12</f>
         <v>28121.600000000002</v>
       </c>
       <c r="K18" s="25" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L18" s="3"/>
       <c r="M18" s="1"/>
       <c r="O18" s="132" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="P18" s="132"/>
       <c r="Q18" s="132"/>
@@ -6589,7 +6589,7 @@
       </c>
       <c r="G19" s="1"/>
       <c r="I19" s="105" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J19" s="1">
         <v>1.3</v>
@@ -6598,7 +6598,7 @@
       <c r="L19" s="3"/>
       <c r="M19" s="1"/>
       <c r="O19" s="132" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="P19" s="132"/>
       <c r="Q19" s="132"/>
@@ -6613,7 +6613,7 @@
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B20" s="109" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C20" s="110"/>
       <c r="D20" s="110"/>
@@ -6625,7 +6625,7 @@
       </c>
       <c r="G20" s="1"/>
       <c r="I20" s="105" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J20" s="1">
         <f>(J13+J12)/2</f>
@@ -6637,7 +6637,7 @@
       <c r="L20" s="3"/>
       <c r="M20" s="1"/>
       <c r="O20" s="132" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="P20" s="132"/>
       <c r="Q20" s="132"/>
@@ -6652,7 +6652,7 @@
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B21" s="109" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C21" s="110"/>
       <c r="D21" s="110"/>
@@ -6675,7 +6675,7 @@
       </c>
       <c r="L21" s="3"/>
       <c r="O21" s="132" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="P21" s="132"/>
       <c r="Q21" s="132"/>
@@ -6690,21 +6690,21 @@
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>471</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>472</v>
-      </c>
       <c r="E22" s="12" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="1"/>
       <c r="I22" s="7" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J22" s="1" t="b">
         <f ca="1">C1/J18*1000&lt;J17</f>
@@ -6713,7 +6713,7 @@
       <c r="K22" s="1"/>
       <c r="L22" s="3"/>
       <c r="O22" s="132" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P22" s="132"/>
       <c r="Q22" s="132"/>
@@ -6736,7 +6736,7 @@
       </c>
       <c r="F23" s="3"/>
       <c r="I23" s="106" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="J23" s="1" t="b">
         <f ca="1">2*C1*J19/J20/J15/J21/J24&lt;J25</f>
@@ -6745,7 +6745,7 @@
       <c r="K23" s="1"/>
       <c r="L23" s="3"/>
       <c r="O23" s="132" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="P23" s="132"/>
       <c r="Q23" s="132"/>
@@ -6772,7 +6772,7 @@
       <c r="K24" s="1"/>
       <c r="L24" s="3"/>
       <c r="O24" s="132" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="P24" s="132"/>
       <c r="Q24" s="132"/>
@@ -6791,7 +6791,7 @@
       <c r="E25" s="4"/>
       <c r="F25" s="5"/>
       <c r="I25" s="7" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J25" s="1">
         <f>0.4*240</f>
@@ -6800,7 +6800,7 @@
       <c r="K25" s="1"/>
       <c r="L25" s="3"/>
       <c r="O25" s="132" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="P25" s="132"/>
       <c r="Q25" s="132"/>
@@ -6824,7 +6824,7 @@
       <c r="K26" s="4"/>
       <c r="L26" s="5"/>
       <c r="O26" s="132" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="P26" s="132"/>
       <c r="Q26" s="132"/>
@@ -6839,7 +6839,7 @@
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.3">
       <c r="O27" s="132" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="P27" s="132"/>
       <c r="Q27" s="132"/>
@@ -6854,7 +6854,7 @@
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.3">
       <c r="O28" s="132" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="P28" s="132"/>
       <c r="Q28" s="132"/>
@@ -6869,7 +6869,7 @@
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.3">
       <c r="O29" s="132" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="P29" s="132"/>
       <c r="Q29" s="132"/>
@@ -6884,7 +6884,7 @@
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.3">
       <c r="H31" s="132" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I31" s="132"/>
       <c r="J31" s="132"/>
@@ -6894,7 +6894,7 @@
         <v>10000</v>
       </c>
       <c r="O31" s="132" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="P31" s="132"/>
       <c r="Q31" s="132"/>
@@ -6909,7 +6909,7 @@
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.3">
       <c r="H32" s="132" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I32" s="132"/>
       <c r="J32" s="132"/>
@@ -6919,7 +6919,7 @@
         <v>0.9</v>
       </c>
       <c r="O32" s="132" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P32" s="132"/>
       <c r="Q32" s="132"/>
@@ -6934,7 +6934,7 @@
     </row>
     <row r="33" spans="8:20" x14ac:dyDescent="0.3">
       <c r="H33" s="132" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I33" s="132"/>
       <c r="J33" s="132"/>
@@ -6945,7 +6945,7 @@
     </row>
     <row r="34" spans="8:20" x14ac:dyDescent="0.3">
       <c r="H34" s="132" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I34" s="132"/>
       <c r="J34" s="132"/>
@@ -6957,7 +6957,7 @@
     </row>
     <row r="35" spans="8:20" x14ac:dyDescent="0.3">
       <c r="H35" s="132" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I35" s="132"/>
       <c r="J35" s="132"/>
@@ -6967,7 +6967,7 @@
         <v>2.66</v>
       </c>
       <c r="O35" s="132" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="P35" s="132"/>
       <c r="Q35" s="132"/>
@@ -6976,7 +6976,7 @@
     </row>
     <row r="36" spans="8:20" x14ac:dyDescent="0.3">
       <c r="H36" s="132" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I36" s="132"/>
       <c r="J36" s="132"/>
@@ -6985,7 +6985,7 @@
         <v>1</v>
       </c>
       <c r="O36" s="132" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="P36" s="132"/>
       <c r="Q36" s="132"/>
@@ -6994,7 +6994,7 @@
     </row>
     <row r="37" spans="8:20" x14ac:dyDescent="0.3">
       <c r="H37" s="132" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I37" s="132"/>
       <c r="J37" s="132"/>
@@ -7003,7 +7003,7 @@
         <v>1.6</v>
       </c>
       <c r="O37" s="132" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="P37" s="132"/>
       <c r="Q37" s="132"/>
@@ -7018,7 +7018,7 @@
     </row>
     <row r="38" spans="8:20" x14ac:dyDescent="0.3">
       <c r="H38" s="132" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I38" s="132"/>
       <c r="J38" s="132"/>
@@ -7027,7 +7027,7 @@
         <v>1</v>
       </c>
       <c r="O38" s="132" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P38" s="132"/>
       <c r="Q38" s="132"/>
@@ -7042,7 +7042,7 @@
     </row>
     <row r="39" spans="8:20" x14ac:dyDescent="0.3">
       <c r="H39" s="132" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I39" s="132"/>
       <c r="J39" s="132"/>
@@ -7053,7 +7053,7 @@
     </row>
     <row r="40" spans="8:20" x14ac:dyDescent="0.3">
       <c r="H40" s="132" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I40" s="132"/>
       <c r="J40" s="132"/>
@@ -7063,7 +7063,7 @@
         <v>22</v>
       </c>
       <c r="O40" s="132" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="P40" s="132"/>
       <c r="Q40" s="132"/>
@@ -7072,7 +7072,7 @@
     </row>
     <row r="41" spans="8:20" x14ac:dyDescent="0.3">
       <c r="H41" s="132" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I41" s="132"/>
       <c r="J41" s="132"/>
@@ -7082,7 +7082,7 @@
         <v>3</v>
       </c>
       <c r="O41" s="132" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="P41" s="132"/>
       <c r="Q41" s="132"/>
@@ -7097,7 +7097,7 @@
     </row>
     <row r="42" spans="8:20" x14ac:dyDescent="0.3">
       <c r="H42" s="132" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I42" s="132"/>
       <c r="J42" s="132"/>
@@ -7106,7 +7106,7 @@
         <v>0.63</v>
       </c>
       <c r="O42" s="132" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="P42" s="132"/>
       <c r="Q42" s="132"/>
@@ -7119,7 +7119,7 @@
     </row>
     <row r="43" spans="8:20" x14ac:dyDescent="0.3">
       <c r="O43" s="132" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="P43" s="132"/>
       <c r="Q43" s="132"/>
@@ -7138,7 +7138,7 @@
     </row>
     <row r="45" spans="8:20" x14ac:dyDescent="0.3">
       <c r="O45" s="132" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="P45" s="132"/>
       <c r="Q45" s="132"/>
@@ -7153,7 +7153,7 @@
     </row>
     <row r="46" spans="8:20" x14ac:dyDescent="0.3">
       <c r="O46" s="132" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="P46" s="132"/>
       <c r="Q46" s="132"/>
@@ -7168,7 +7168,7 @@
     </row>
     <row r="47" spans="8:20" x14ac:dyDescent="0.3">
       <c r="O47" s="132" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="P47" s="132"/>
       <c r="Q47" s="132"/>
@@ -7183,13 +7183,13 @@
     </row>
     <row r="48" spans="8:20" x14ac:dyDescent="0.3">
       <c r="O48" s="132" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="P48" s="132"/>
     </row>
     <row r="49" spans="15:21" x14ac:dyDescent="0.3">
       <c r="O49" s="132" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P49" s="132"/>
       <c r="Q49" s="132"/>
@@ -7204,7 +7204,7 @@
     </row>
     <row r="50" spans="15:21" x14ac:dyDescent="0.3">
       <c r="O50" s="132" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="P50" s="132"/>
       <c r="Q50" s="132"/>
@@ -7225,19 +7225,19 @@
         <v>327</v>
       </c>
       <c r="Q52" t="s">
+        <v>416</v>
+      </c>
+      <c r="R52" t="s">
+        <v>422</v>
+      </c>
+      <c r="S52" t="s">
         <v>417</v>
       </c>
-      <c r="R52" t="s">
-        <v>423</v>
-      </c>
-      <c r="S52" t="s">
+      <c r="T52" t="s">
+        <v>419</v>
+      </c>
+      <c r="U52" t="s">
         <v>418</v>
-      </c>
-      <c r="T52" t="s">
-        <v>420</v>
-      </c>
-      <c r="U52" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="53" spans="15:21" x14ac:dyDescent="0.3">
@@ -7266,7 +7266,7 @@
     </row>
     <row r="55" spans="15:21" x14ac:dyDescent="0.3">
       <c r="O55" s="132" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="P55" s="132"/>
       <c r="Q55" s="132"/>
@@ -7292,12 +7292,12 @@
       </c>
       <c r="T56" s="132"/>
       <c r="U56" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="57" spans="15:21" x14ac:dyDescent="0.3">
       <c r="O57" s="132" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="P57" s="132"/>
       <c r="Q57" s="132"/>
@@ -7338,6 +7338,7 @@
     <mergeCell ref="O31:R31"/>
     <mergeCell ref="O32:R32"/>
     <mergeCell ref="O36:S36"/>
+    <mergeCell ref="O37:R37"/>
     <mergeCell ref="H42:K42"/>
     <mergeCell ref="H36:K36"/>
     <mergeCell ref="H37:K37"/>
@@ -7361,7 +7362,6 @@
     <mergeCell ref="O43:R43"/>
     <mergeCell ref="S43:T43"/>
     <mergeCell ref="O45:R45"/>
-    <mergeCell ref="O37:R37"/>
     <mergeCell ref="O38:R38"/>
     <mergeCell ref="O40:S40"/>
     <mergeCell ref="O41:R41"/>
@@ -7417,12 +7417,12 @@
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D3">
         <v>0.3</v>
@@ -7434,30 +7434,30 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>497</v>
+      </c>
+      <c r="D4" t="s">
         <v>498</v>
       </c>
-      <c r="D4" t="s">
-        <v>499</v>
-      </c>
       <c r="E4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F4">
         <f>0.6*34.5</f>
         <v>20.7</v>
       </c>
       <c r="G4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B7" s="60">
         <f>Электродвигатель!P52</f>
@@ -8308,10 +8308,10 @@
         <v>286</v>
       </c>
       <c r="H11" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="I11" s="4" t="s">
         <v>425</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>426</v>
       </c>
       <c r="J11" s="12" t="s">
         <v>284</v>
@@ -8323,10 +8323,10 @@
         <v>286</v>
       </c>
       <c r="M11" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="N11" s="4" t="s">
         <v>425</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>426</v>
       </c>
       <c r="O11" s="4" t="s">
         <v>284</v>
@@ -8338,10 +8338,10 @@
         <v>286</v>
       </c>
       <c r="R11" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="S11" s="4" t="s">
         <v>425</v>
-      </c>
-      <c r="S11" s="4" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
@@ -9915,7 +9915,7 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="H19" s="107" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I19" s="108"/>
       <c r="J19" s="108"/>
@@ -9924,7 +9924,7 @@
       </c>
       <c r="L19" s="6"/>
       <c r="P19" s="107" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Q19" s="108"/>
       <c r="R19" s="108"/>
@@ -10009,7 +10009,7 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="H23" s="109" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I23" s="110"/>
       <c r="J23" s="110"/>
@@ -10021,7 +10021,7 @@
         <v>4</v>
       </c>
       <c r="P23" s="109" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Q23" s="110"/>
       <c r="R23" s="110"/>
@@ -10035,7 +10035,7 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="H24" s="119" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I24" s="120"/>
       <c r="J24" s="120"/>
@@ -10047,7 +10047,7 @@
         <v>4</v>
       </c>
       <c r="P24" s="119" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="Q24" s="120"/>
       <c r="R24" s="120"/>
@@ -10378,13 +10378,13 @@
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C16" s="132" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D16" s="132"/>
       <c r="E16" s="132"/>
       <c r="F16" s="132"/>
       <c r="G16" s="132" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H16" s="132"/>
       <c r="I16" s="132"/>
@@ -10495,7 +10495,7 @@
         <v>6</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G21" s="12">
         <f ca="1">G18+2*F14</f>
@@ -10507,7 +10507,7 @@
         <v>6</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
@@ -11965,7 +11965,7 @@
         <v>251</v>
       </c>
       <c r="T38" s="75" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="U38" s="156" t="s">
         <v>159</v>
@@ -12865,7 +12865,7 @@
       <c r="K10" s="132"/>
       <c r="L10" s="132"/>
       <c r="M10" s="52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N10" s="25" t="s">
         <v>221</v>
@@ -12979,7 +12979,7 @@
       <c r="L13" s="132"/>
       <c r="M13">
         <f ca="1">2000*M10*M9/(PI()*E19*E19*M12*M11)</f>
-        <v>46.98792560548906</v>
+        <v>62.650567473985404</v>
       </c>
       <c r="N13" t="s">
         <v>223</v>
@@ -13006,7 +13006,7 @@
       <c r="L14" s="132"/>
       <c r="M14">
         <f ca="1">1000*M13*E19*(X10/X8+Z10/Z8)</f>
-        <v>46.673015345699184</v>
+        <v>62.230687127598905</v>
       </c>
       <c r="N14" t="s">
         <v>232</v>
@@ -13033,7 +13033,7 @@
       <c r="L15" s="132"/>
       <c r="M15">
         <f>5.5*(E20+'тихоходный вал'!E8)</f>
-        <v>13.200000000000003</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="N15" t="s">
         <v>232</v>
@@ -13085,7 +13085,7 @@
       <c r="L17" s="132"/>
       <c r="M17" s="25">
         <f ca="1">SUM(M14:M16)</f>
-        <v>59.873015345699187</v>
+        <v>79.830687127598907</v>
       </c>
       <c r="N17" t="s">
         <v>232</v>
@@ -13138,7 +13138,7 @@
       <c r="L19" s="132"/>
       <c r="M19" s="88">
         <f ca="1">M18+M15</f>
-        <v>336.02186948853614</v>
+        <v>340.42186948853617</v>
       </c>
       <c r="N19" t="s">
         <v>232</v>
@@ -13158,7 +13158,7 @@
         <v>232</v>
       </c>
       <c r="M20" s="92" t="s">
-        <v>348</v>
+        <v>507</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
@@ -13181,10 +13181,10 @@
       <c r="K21" s="132"/>
       <c r="L21" s="132"/>
       <c r="M21">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="N21">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="O21" t="s">
         <v>232</v>
@@ -13220,8 +13220,8 @@
       <c r="K23" s="132"/>
       <c r="L23" s="132"/>
       <c r="M23">
-        <f ca="1">PI()*E19*M12*(M21-M15)*M22/1000</f>
-        <v>104.00430975268226</v>
+        <f ca="1">PI()*E19*M12*(N21-M15)*M22/1000</f>
+        <v>268.67780019442915</v>
       </c>
       <c r="N23" t="s">
         <v>4</v>
@@ -13603,7 +13603,7 @@
       <c r="C8" s="132"/>
       <c r="D8" s="132"/>
       <c r="E8" s="52">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="F8" t="s">
         <v>232</v>
@@ -13623,7 +13623,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="132" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B10" s="132"/>
       <c r="C10" s="132"/>
@@ -13635,7 +13635,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="132" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B11" s="132"/>
       <c r="C11" s="132"/>
@@ -13655,7 +13655,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="132" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B19" s="132"/>
       <c r="C19" s="132"/>
@@ -13664,23 +13664,23 @@
         <v>1.4</v>
       </c>
       <c r="F19" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="132" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B20" s="132"/>
       <c r="C20" s="132"/>
       <c r="D20" s="132"/>
       <c r="E20" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="132" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B26" s="132"/>
       <c r="C26" s="132"/>
@@ -13689,12 +13689,12 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="132" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B28" s="132"/>
       <c r="C28" s="132"/>
@@ -13732,7 +13732,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="132" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B31" s="132"/>
       <c r="C31" s="132"/>
@@ -13742,7 +13742,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="132" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B32" s="132"/>
       <c r="C32" s="132"/>
@@ -13756,7 +13756,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="132" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B33" s="132"/>
       <c r="C33" s="132"/>
@@ -13770,7 +13770,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="132" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B34" s="132"/>
       <c r="C34" s="132"/>
@@ -13798,7 +13798,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="132" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B36" s="132"/>
       <c r="C36" s="132"/>
@@ -13818,7 +13818,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="132" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B38" s="132"/>
       <c r="C38" s="132"/>
@@ -13833,7 +13833,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="132" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B39" s="132"/>
       <c r="C39" s="132"/>
@@ -13842,7 +13842,7 @@
         <v>120</v>
       </c>
       <c r="F39" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G39" t="s">
         <v>100</v>
@@ -13850,7 +13850,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="132" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B40" s="132"/>
       <c r="C40" s="132"/>
@@ -13935,7 +13935,7 @@
   <sheetData>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="132" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B6" s="132"/>
       <c r="C6" s="132"/>
@@ -13973,7 +13973,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="132" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B9" s="132"/>
       <c r="C9" s="132"/>
@@ -13983,7 +13983,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="132" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B10" s="132"/>
       <c r="C10" s="132"/>
@@ -13997,7 +13997,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="132" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B11" s="132"/>
       <c r="C11" s="132"/>
@@ -14011,7 +14011,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="132" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B12" s="132"/>
       <c r="C12" s="132"/>
@@ -14039,7 +14039,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="132" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B14" s="132"/>
       <c r="C14" s="132"/>
@@ -14059,7 +14059,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="132" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B16" s="132"/>
       <c r="C16" s="132"/>
@@ -14074,7 +14074,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="132" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -14084,12 +14084,12 @@
         <v>120</v>
       </c>
       <c r="F17" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="132" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B18" s="132"/>
       <c r="C18" s="132"/>
@@ -14201,7 +14201,7 @@
         <v>310</v>
       </c>
       <c r="H3" s="153" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I3" s="153"/>
       <c r="J3" s="153"/>
@@ -14243,7 +14243,7 @@
         <v>100</v>
       </c>
       <c r="H4" s="153" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I4" s="153"/>
       <c r="J4" s="153"/>
@@ -14272,7 +14272,7 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="132" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B5" s="132"/>
       <c r="C5" s="132"/>
@@ -14285,7 +14285,7 @@
         <v>152</v>
       </c>
       <c r="H5" s="153" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I5" s="153"/>
       <c r="J5" s="153"/>
@@ -14297,7 +14297,7 @@
         <v>152</v>
       </c>
       <c r="N5" s="132" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O5" s="132"/>
       <c r="P5" s="132"/>
@@ -14332,7 +14332,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="132" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B7" s="132"/>
       <c r="C7" s="132"/>
@@ -14344,10 +14344,10 @@
         <v>152</v>
       </c>
       <c r="H7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="N7" s="132" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="O7" s="132"/>
       <c r="P7" s="132"/>
@@ -14364,7 +14364,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="132" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B8" s="132"/>
       <c r="C8" s="132"/>
@@ -14372,7 +14372,7 @@
       <c r="E8" s="132"/>
       <c r="F8" s="132"/>
       <c r="N8" s="132" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O8" s="132"/>
       <c r="P8" s="132"/>
@@ -14382,7 +14382,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="132" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B9" s="132"/>
       <c r="C9" s="132"/>
@@ -14394,7 +14394,7 @@
         <v>16</v>
       </c>
       <c r="N9" s="132" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="O9" 